--- a/slots/resources/sample/SpecialAuxiliary.xlsx
+++ b/slots/resources/sample/SpecialAuxiliary.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5769F00-6EAB-43D6-B00E-634236499D10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE0FA806-AF9E-4492-8D3E-28D9F0ED7496}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -173,7 +173,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="95">
   <si>
     <t>游戏ID</t>
   </si>
@@ -196,270 +196,287 @@
     <t>免费的固定奖励</t>
   </si>
   <si>
+    <t>描述</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>bool</t>
+  </si>
+  <si>
+    <t>Map&lt;int{,}int&gt;{;}</t>
+  </si>
+  <si>
+    <t>gameType</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>interflow</t>
+  </si>
+  <si>
+    <t>randCount</t>
+  </si>
+  <si>
+    <t>clientShowCount</t>
+  </si>
+  <si>
+    <t>1,1;2,1;3,1;4,1;5,1;6,1;7,1</t>
+  </si>
+  <si>
+    <t>拉火车绿火车MINI随几次为几节车厢</t>
+  </si>
+  <si>
+    <t>拉火车蓝火车MINOR</t>
+  </si>
+  <si>
+    <t>拉火车紫火车MAJOR</t>
+  </si>
+  <si>
+    <t>拉火车红火车GRAND</t>
+  </si>
+  <si>
+    <t>1,8;2,8;3,8;4,8;5,8;6,8;7,8</t>
+  </si>
+  <si>
+    <t>黄金列车</t>
+  </si>
+  <si>
+    <t>1,2;2,2;3,2;4,2;5,2;6,2;7,2</t>
+  </si>
+  <si>
+    <t>免费2选1</t>
+  </si>
+  <si>
+    <t>免费转</t>
+  </si>
+  <si>
+    <t>typeID</t>
+  </si>
+  <si>
+    <t>名称</t>
+  </si>
+  <si>
+    <t>全部</t>
+  </si>
+  <si>
+    <t>无</t>
+  </si>
+  <si>
+    <t>普通</t>
+  </si>
+  <si>
+    <t>免费</t>
+  </si>
+  <si>
+    <t>重转</t>
+  </si>
+  <si>
+    <t>选择标识</t>
+  </si>
+  <si>
+    <t>扩展旋转</t>
+  </si>
+  <si>
+    <t>通用免费1</t>
+  </si>
+  <si>
+    <t>通用免费2</t>
+  </si>
+  <si>
+    <t>通用免费3</t>
+  </si>
+  <si>
+    <t>通用免费4</t>
+  </si>
+  <si>
+    <t>通用免费5</t>
+  </si>
+  <si>
+    <t>通用免费6</t>
+  </si>
+  <si>
+    <t>通用免费7</t>
+  </si>
+  <si>
+    <t>通用免费8</t>
+  </si>
+  <si>
+    <t>通用免费9</t>
+  </si>
+  <si>
+    <t>通用免费10</t>
+  </si>
+  <si>
+    <t>通用免费11</t>
+  </si>
+  <si>
+    <t>通用免费12</t>
+  </si>
+  <si>
+    <t>通用免费13</t>
+  </si>
+  <si>
+    <t>通用免费14</t>
+  </si>
+  <si>
+    <t>通用免费15</t>
+  </si>
+  <si>
+    <t>通用免费16</t>
+  </si>
+  <si>
+    <t>免费1</t>
+  </si>
+  <si>
+    <t>通用重转1</t>
+  </si>
+  <si>
+    <t>通用重转2</t>
+  </si>
+  <si>
+    <t>通用重转3</t>
+  </si>
+  <si>
+    <t>通用重转4</t>
+  </si>
+  <si>
+    <t>通用重转5</t>
+  </si>
+  <si>
+    <t>通用重转6</t>
+  </si>
+  <si>
+    <t>通用重转7</t>
+  </si>
+  <si>
+    <t>通用重转8</t>
+  </si>
+  <si>
+    <t>通用重转9</t>
+  </si>
+  <si>
+    <t>通用重转10</t>
+  </si>
+  <si>
+    <t>通用重转11</t>
+  </si>
+  <si>
+    <t>通用重转12</t>
+  </si>
+  <si>
+    <t>通用普通1</t>
+  </si>
+  <si>
+    <t>通用普通2</t>
+  </si>
+  <si>
+    <t>通用普通3</t>
+  </si>
+  <si>
+    <t>通用普通4</t>
+  </si>
+  <si>
+    <t>通用普通5</t>
+  </si>
+  <si>
+    <t>通用普通6</t>
+  </si>
+  <si>
+    <t>通用普通7</t>
+  </si>
+  <si>
+    <t>通用普通8</t>
+  </si>
+  <si>
+    <t>通用普通9</t>
+  </si>
+  <si>
+    <t>通用普通10</t>
+  </si>
+  <si>
+    <t>小游戏模式ID</t>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>id</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1&amp;1-2&amp;1-3&amp;1-4&amp;1-5&amp;1-6&amp;1-7&amp;1-8&amp;1-9&amp;1-10&amp;1-11&amp;1;2,1&amp;1-2&amp;1-3&amp;1-4&amp;1-5&amp;1-6&amp;1-7&amp;1-8&amp;1-9&amp;1-10&amp;1-11&amp;1;3,1&amp;1-2&amp;1-3&amp;1-4&amp;1-5&amp;1-6&amp;1-7&amp;1-8&amp;1-9&amp;1-10&amp;1-11&amp;1;4,1&amp;1-2&amp;1-3&amp;1-4&amp;1-5&amp;1-6&amp;1-7&amp;1-8&amp;1-9&amp;1-10&amp;1-11&amp;1;5,1&amp;1-2&amp;1-3&amp;1-4&amp;1-5&amp;1-6&amp;1-7&amp;1-8&amp;1-9&amp;1-10&amp;1-11&amp;1;6,1&amp;1-2&amp;1-3&amp;1-4&amp;1-5&amp;1-6&amp;1-7&amp;1-8&amp;1-9&amp;1-10&amp;1-11&amp;1;7,1&amp;1-2&amp;1-3&amp;1-4&amp;1-5&amp;1-6&amp;1-7&amp;1-8&amp;1-9&amp;1-10&amp;1-11&amp;1;</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Map&lt;int{,}Map&lt;int{&amp;}int&gt;{-}&gt;{;}</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>freeRandAward</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1&amp;1;2,1&amp;1;3,1&amp;1;4,1&amp;1;5,1&amp;1;6,1&amp;1;7,1&amp;1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1001000701&amp;1&amp;1-1001000702&amp;1&amp;1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Map&lt;int{,}List&lt;List&lt;int&gt;{&amp;}&gt;{-}&gt;{;}</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1001000501&amp;1&amp;1-1001000502&amp;1&amp;1-1001000503&amp;1&amp;1-1001000504&amp;1&amp;1;2,1001000501&amp;1&amp;1-1001000502&amp;1&amp;1-1001000503&amp;1&amp;1-1001000504&amp;1&amp;1;3,1001000501&amp;1&amp;1-1001000502&amp;1&amp;1-1001000503&amp;1&amp;1-1001000504&amp;1&amp;1;4,1001000501&amp;1&amp;1-1001000502&amp;1&amp;1-1001000503&amp;1&amp;1-1001000504&amp;1&amp;1;5,1001000501&amp;1&amp;1-1001000502&amp;1&amp;1-1001000503&amp;1&amp;1-1001000504&amp;1&amp;1;6,1001000501&amp;1&amp;1-1001000502&amp;1&amp;1-1001000503&amp;1&amp;1-1001000504&amp;1&amp;1;7,1001000501&amp;1&amp;1-1001000502&amp;1&amp;1-1001000503&amp;1&amp;1-1001000504&amp;1&amp;1;8,1001000501&amp;1&amp;1-1001000502&amp;1&amp;1-1001000503&amp;1&amp;1-1001000504&amp;1&amp;1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
     <t>免费随机奖励</t>
-  </si>
-  <si>
-    <t>描述</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>bool</t>
-  </si>
-  <si>
-    <t>Map&lt;int{,}int&gt;{;}</t>
-  </si>
-  <si>
-    <t>List&lt;int&gt;{,}</t>
-  </si>
-  <si>
-    <t>gameType</t>
-  </si>
-  <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>interflow</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001000901,1001000902</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001000801,1001000802</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>List&lt;List&lt;int&gt;{,}&gt;{;}</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>地图全解锁送黄金列车/4个分散，转出触发局</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择拉火车，转出触发局</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>收集集满触发地图，8个场景，随机奖励为3个+黄金列车金币系数</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>freeAward</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>4/5个免费2选1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1001000702&amp;1&amp;1-1001000703&amp;1&amp;1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>spinType</t>
-  </si>
-  <si>
-    <t>randCount</t>
-  </si>
-  <si>
-    <t>clientShowCount</t>
-  </si>
-  <si>
-    <t>freeAward</t>
-  </si>
-  <si>
-    <t>1,1;2,1;3,1;4,1;5,1;6,1;7,1</t>
-  </si>
-  <si>
-    <t>拉火车绿火车MINI随几次为几节车厢</t>
-  </si>
-  <si>
-    <t>拉火车蓝火车MINOR</t>
-  </si>
-  <si>
-    <t>拉火车紫火车MAJOR</t>
-  </si>
-  <si>
-    <t>拉火车红火车GRAND</t>
-  </si>
-  <si>
-    <t>1,8;2,8;3,8;4,8;5,8;6,8;7,8</t>
-  </si>
-  <si>
-    <t>收集集满触发地图，8个场景，随机奖励为3个+黄金列车金币系数</t>
-  </si>
-  <si>
-    <t>黄金列车</t>
-  </si>
-  <si>
-    <t>1,2;2,2;3,2;4,2;5,2;6,2;7,2</t>
-  </si>
-  <si>
-    <t>1,1001000701&amp;1&amp;1-1001000702&amp;1&amp;1</t>
-  </si>
-  <si>
-    <t>免费2选1</t>
-  </si>
-  <si>
-    <t>免费转</t>
-  </si>
-  <si>
-    <t>地图全解锁送黄金列车/4个分散，转出触发局</t>
-  </si>
-  <si>
-    <t>选择拉火车，转出触发局</t>
-  </si>
-  <si>
-    <t>typeID</t>
-  </si>
-  <si>
-    <t>名称</t>
-  </si>
-  <si>
-    <t>全部</t>
-  </si>
-  <si>
-    <t>无</t>
-  </si>
-  <si>
-    <t>普通</t>
-  </si>
-  <si>
-    <t>免费</t>
-  </si>
-  <si>
-    <t>重转</t>
-  </si>
-  <si>
-    <t>选择标识</t>
-  </si>
-  <si>
-    <t>扩展旋转</t>
-  </si>
-  <si>
-    <t>通用免费1</t>
-  </si>
-  <si>
-    <t>通用免费2</t>
-  </si>
-  <si>
-    <t>通用免费3</t>
-  </si>
-  <si>
-    <t>通用免费4</t>
-  </si>
-  <si>
-    <t>通用免费5</t>
-  </si>
-  <si>
-    <t>通用免费6</t>
-  </si>
-  <si>
-    <t>通用免费7</t>
-  </si>
-  <si>
-    <t>通用免费8</t>
-  </si>
-  <si>
-    <t>通用免费9</t>
-  </si>
-  <si>
-    <t>通用免费10</t>
-  </si>
-  <si>
-    <t>通用免费11</t>
-  </si>
-  <si>
-    <t>通用免费12</t>
-  </si>
-  <si>
-    <t>通用免费13</t>
-  </si>
-  <si>
-    <t>通用免费14</t>
-  </si>
-  <si>
-    <t>通用免费15</t>
-  </si>
-  <si>
-    <t>通用免费16</t>
-  </si>
-  <si>
-    <t>免费1</t>
-  </si>
-  <si>
-    <t>通用重转1</t>
-  </si>
-  <si>
-    <t>通用重转2</t>
-  </si>
-  <si>
-    <t>通用重转3</t>
-  </si>
-  <si>
-    <t>通用重转4</t>
-  </si>
-  <si>
-    <t>通用重转5</t>
-  </si>
-  <si>
-    <t>通用重转6</t>
-  </si>
-  <si>
-    <t>通用重转7</t>
-  </si>
-  <si>
-    <t>通用重转8</t>
-  </si>
-  <si>
-    <t>通用重转9</t>
-  </si>
-  <si>
-    <t>通用重转10</t>
-  </si>
-  <si>
-    <t>通用重转11</t>
-  </si>
-  <si>
-    <t>通用重转12</t>
-  </si>
-  <si>
-    <t>通用普通1</t>
-  </si>
-  <si>
-    <t>通用普通2</t>
-  </si>
-  <si>
-    <t>通用普通3</t>
-  </si>
-  <si>
-    <t>通用普通4</t>
-  </si>
-  <si>
-    <t>通用普通5</t>
-  </si>
-  <si>
-    <t>通用普通6</t>
-  </si>
-  <si>
-    <t>通用普通7</t>
-  </si>
-  <si>
-    <t>通用普通8</t>
-  </si>
-  <si>
-    <t>通用普通9</t>
-  </si>
-  <si>
-    <t>通用普通10</t>
-  </si>
-  <si>
-    <t>小游戏模式ID</t>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>id</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,1&amp;1-2&amp;1-3&amp;1-4&amp;1-5&amp;1-6&amp;1-7&amp;1-8&amp;1-9&amp;1-10&amp;1-11&amp;1;2,1&amp;1-2&amp;1-3&amp;1-4&amp;1-5&amp;1-6&amp;1-7&amp;1-8&amp;1-9&amp;1-10&amp;1-11&amp;1;3,1&amp;1-2&amp;1-3&amp;1-4&amp;1-5&amp;1-6&amp;1-7&amp;1-8&amp;1-9&amp;1-10&amp;1-11&amp;1;4,1&amp;1-2&amp;1-3&amp;1-4&amp;1-5&amp;1-6&amp;1-7&amp;1-8&amp;1-9&amp;1-10&amp;1-11&amp;1;5,1&amp;1-2&amp;1-3&amp;1-4&amp;1-5&amp;1-6&amp;1-7&amp;1-8&amp;1-9&amp;1-10&amp;1-11&amp;1;6,1&amp;1-2&amp;1-3&amp;1-4&amp;1-5&amp;1-6&amp;1-7&amp;1-8&amp;1-9&amp;1-10&amp;1-11&amp;1;7,1&amp;1-2&amp;1-3&amp;1-4&amp;1-5&amp;1-6&amp;1-7&amp;1-8&amp;1-9&amp;1-10&amp;1-11&amp;1;</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Map&lt;int{,}Map&lt;int{&amp;}int&gt;{-}&gt;{;}</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>freeRandAward</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,1001000501&amp;1&amp;1-1001000502&amp;1&amp;1-1001000503&amp;1&amp;1-1001000504&amp;1&amp;1};2,1001000501&amp;1&amp;1-1001000502&amp;1&amp;1-1001000503&amp;1&amp;1-1001000504&amp;1&amp;1};3,1001000501&amp;1&amp;1-1001000502&amp;1&amp;1-1001000503&amp;1&amp;1-1001000504&amp;1&amp;1};4,1001000501&amp;1&amp;1-1001000502&amp;1&amp;1-1001000503&amp;1&amp;1-1001000504&amp;1&amp;1};5,1001000501&amp;1&amp;1-1001000502&amp;1&amp;1-1001000503&amp;1&amp;1-1001000504&amp;1&amp;1};6,1001000501&amp;1&amp;1-1001000502&amp;1&amp;1-1001000503&amp;1&amp;1-1001000504&amp;1&amp;1};7,1001000501&amp;1&amp;1-1001000502&amp;1&amp;1-1001000503&amp;1&amp;1-1001000504&amp;1&amp;1};8,1001000501&amp;1&amp;1-1001000502&amp;1&amp;1-1001000503&amp;1&amp;1-1001000504&amp;1&amp;1}</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Map&lt;int{,}List&lt;String&gt;{-}&gt;{;}</t>
-  </si>
-  <si>
-    <t>1,1&amp;1;2,1&amp;1;3,1&amp;1;4,1&amp;1;5,1&amp;1;6,1&amp;1;7,1&amp;1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>1001000801,1001000000</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>1001000901,1001000000</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -860,20 +877,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.125" customWidth="1"/>
+    <col min="3" max="3" width="8.25" customWidth="1"/>
     <col min="5" max="5" width="11.5" customWidth="1"/>
     <col min="6" max="6" width="38.75" customWidth="1"/>
     <col min="7" max="7" width="22.75" customWidth="1"/>
-    <col min="8" max="8" width="29.25" style="7" customWidth="1"/>
+    <col min="8" max="8" width="23.75" style="7" customWidth="1"/>
     <col min="9" max="9" width="32.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -897,69 +915,69 @@
         <v>6</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="H2" s="3" t="s">
-        <v>12</v>
+        <v>87</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="J2" s="1"/>
     </row>
     <row r="3" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="E3" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>18</v>
-      </c>
       <c r="H3" s="3" t="s">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="J3" s="3"/>
     </row>
@@ -991,17 +1009,17 @@
         <v>1</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H5" s="3">
         <v>1001000101</v>
       </c>
       <c r="I5" s="1"/>
       <c r="J5" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
@@ -1021,17 +1039,17 @@
         <v>1</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H6" s="3">
         <v>1001000201</v>
       </c>
       <c r="I6" s="1"/>
       <c r="J6" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
@@ -1051,17 +1069,17 @@
         <v>1</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H7" s="3">
         <v>1001000301</v>
       </c>
       <c r="I7" s="1"/>
       <c r="J7" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
@@ -1081,17 +1099,17 @@
         <v>1</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H8" s="3">
         <v>1001000401</v>
       </c>
       <c r="I8" s="1"/>
       <c r="J8" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
@@ -1111,17 +1129,17 @@
         <v>1</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="1" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>26</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
@@ -1141,17 +1159,17 @@
         <v>1</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H10" s="3">
         <v>1001000504</v>
       </c>
       <c r="I10" s="1"/>
       <c r="J10" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
@@ -1171,17 +1189,17 @@
         <v>1</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="1" t="s">
-        <v>29</v>
+        <v>81</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
@@ -1201,22 +1219,22 @@
         <v>1</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="I12" s="1"/>
       <c r="J12" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
-        <v>10010009</v>
+        <v>10010010</v>
       </c>
       <c r="B13" s="5">
         <v>100100</v>
@@ -1228,50 +1246,80 @@
         <v>0</v>
       </c>
       <c r="E13" s="1">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="I13" s="1"/>
       <c r="J13" s="1" t="s">
-        <v>32</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
-        <v>10010010</v>
+        <v>10010011</v>
       </c>
       <c r="B14" s="5">
         <v>100100</v>
       </c>
       <c r="C14" s="1">
+        <v>0</v>
+      </c>
+      <c r="D14" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" s="1">
+        <v>1</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H14" s="3"/>
+      <c r="I14" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="1">
+        <v>10010009</v>
+      </c>
+      <c r="B15" s="5">
+        <v>100100</v>
+      </c>
+      <c r="C15" s="1">
         <v>2</v>
       </c>
-      <c r="D14" s="1" t="b">
+      <c r="D15" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="E14" s="1">
-        <v>25</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1" t="s">
-        <v>33</v>
+      <c r="E15" s="1">
+        <v>24</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -1288,10 +1336,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -1299,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -1307,7 +1355,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -1315,7 +1363,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -1323,7 +1371,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -1331,7 +1379,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -1339,7 +1387,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
@@ -1347,7 +1395,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
@@ -1355,7 +1403,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
@@ -1363,7 +1411,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
@@ -1371,7 +1419,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
@@ -1379,7 +1427,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
@@ -1387,7 +1435,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
@@ -1395,7 +1443,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
@@ -1403,7 +1451,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
@@ -1411,7 +1459,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
@@ -1419,7 +1467,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
@@ -1427,7 +1475,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
@@ -1435,7 +1483,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
@@ -1443,7 +1491,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
@@ -1451,7 +1499,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
@@ -1459,7 +1507,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
@@ -1467,7 +1515,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
@@ -1475,7 +1523,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
@@ -1483,7 +1531,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
@@ -1491,7 +1539,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
@@ -1499,7 +1547,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
@@ -1507,7 +1555,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
@@ -1515,7 +1563,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
@@ -1523,7 +1571,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
@@ -1531,7 +1579,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
@@ -1539,7 +1587,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
@@ -1547,7 +1595,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
@@ -1555,7 +1603,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
@@ -1563,7 +1611,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
@@ -1571,7 +1619,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
@@ -1579,7 +1627,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
@@ -1587,7 +1635,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
@@ -1595,7 +1643,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
@@ -1603,7 +1651,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
@@ -1611,7 +1659,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
@@ -1619,7 +1667,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
@@ -1627,7 +1675,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
@@ -1635,7 +1683,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.2">
@@ -1643,7 +1691,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.2">
@@ -1651,7 +1699,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.2">
@@ -1659,7 +1707,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialAuxiliary.xlsx
+++ b/slots/resources/sample/SpecialAuxiliary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE0FA806-AF9E-4492-8D3E-28D9F0ED7496}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20009516-2A89-4A7A-A7E0-C389897C91B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -424,10 +424,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>1,1001000701&amp;1&amp;1-1001000702&amp;1&amp;1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>Map&lt;int{,}List&lt;List&lt;int&gt;{&amp;}&gt;{-}&gt;{;}</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -472,11 +468,15 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>1,1001000702&amp;1&amp;1-1001000703&amp;1&amp;1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>spinType</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1001000701&amp;1&amp;1-1001000702&amp;1&amp;1;2,1001000701&amp;1&amp;1-1001000702&amp;1&amp;1;3,1001000701&amp;1&amp;1-1001000702&amp;1&amp;1;4,1001000701&amp;1&amp;1-1001000702&amp;1&amp;1;5,1001000701&amp;1&amp;1-1001000702&amp;1&amp;1;6,1001000701&amp;1&amp;1-1001000702&amp;1&amp;1;7,1001000701&amp;1&amp;1-1001000702&amp;1&amp;1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1001000702&amp;1&amp;1-1001000703&amp;1&amp;1;2,1001000702&amp;1&amp;1-1001000703&amp;1&amp;1;3,1001000702&amp;1&amp;1-1001000703&amp;1&amp;1;4,1001000702&amp;1&amp;1-1001000703&amp;1&amp;1;5,1001000702&amp;1&amp;1-1001000703&amp;1&amp;1;6,1001000702&amp;1&amp;1-1001000703&amp;1&amp;1;7,1001000702&amp;1&amp;1-1001000703&amp;1&amp;1</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -915,7 +915,7 @@
         <v>6</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>7</v>
@@ -944,10 +944,10 @@
         <v>10</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J2" s="1"/>
     </row>
@@ -965,7 +965,7 @@
         <v>13</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>14</v>
@@ -974,7 +974,7 @@
         <v>15</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>79</v>
@@ -1136,10 +1136,10 @@
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="1" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="J11" s="1" t="s">
         <v>24</v>
@@ -1225,7 +1225,7 @@
         <v>16</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I12" s="1"/>
       <c r="J12" s="1" t="s">
@@ -1255,11 +1255,11 @@
         <v>16</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I13" s="1"/>
       <c r="J13" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
@@ -1286,10 +1286,10 @@
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
@@ -1315,11 +1315,11 @@
         <v>16</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I15" s="1"/>
       <c r="J15" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialAuxiliary.xlsx
+++ b/slots/resources/sample/SpecialAuxiliary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20009516-2A89-4A7A-A7E0-C389897C91B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7F2A087-F7C2-45DB-A97C-938D7C9D4224}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="3330" yWindow="1890" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialAuxiliary" sheetId="1" r:id="rId1"/>
@@ -886,7 +886,7 @@
     <col min="6" max="6" width="38.75" customWidth="1"/>
     <col min="7" max="7" width="22.75" customWidth="1"/>
     <col min="8" max="8" width="23.75" style="7" customWidth="1"/>
-    <col min="9" max="9" width="32.625" customWidth="1"/>
+    <col min="9" max="9" width="60.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">

--- a/slots/resources/sample/SpecialAuxiliary.xlsx
+++ b/slots/resources/sample/SpecialAuxiliary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7F2A087-F7C2-45DB-A97C-938D7C9D4224}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8BBB358-835B-49A4-9CDA-642029F582A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="3330" yWindow="1890" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialAuxiliary" sheetId="1" r:id="rId1"/>

--- a/slots/resources/sample/SpecialAuxiliary.xlsx
+++ b/slots/resources/sample/SpecialAuxiliary.xlsx
@@ -1,40 +1,46 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8BBB358-835B-49A4-9CDA-642029F582A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialAuxiliary" sheetId="1" r:id="rId1"/>
     <sheet name="desc" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>vidisJW</author>
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="C1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>vidisJW:</t>
@@ -43,7 +49,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -54,13 +59,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="D1" authorId="1">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>1 是
@@ -68,14 +72,70 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="E1" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>0 全部 
+1 无
+2 普通
+3 免费
+4 重转
+5 选择标识
+6 扩展旋转
+7 通用免费1
+8 通用免费2
+9 通用免费3
+10 通用免费4
+11 通用免费5
+12 通用免费6
+13 通用免费7
+14 通用免费8
+15 通用免费9
+16 通用免费10
+17 通用免费11
+18 通用免费12
+19 通用免费13
+20 通用免费14
+21 通用免费15
+22 通用免费16
+23 免费1
+24 通用重转1
+25 通用重转2
+26 通用重转3
+27 通用重转4
+28 通用重转5
+29 通用重转6
+30 通用重转7
+31 通用重转8
+32 通用重转9
+33 通用重转10
+34 通用重转11
+35 通用重转12
+36 通用普通1
+37 通用普通2
+38 通用普通3
+39 通用普通4
+40 通用普通5
+41 通用普通6
+42 通用普通7
+43 通用普通8
+44 通用普通9
+45 通用普通10</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>vidisJW:</t>
@@ -84,16 +144,14 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-格式：[{模式,[{次数,权重}]}]
-模式1,次数&amp;权重-次数&amp;权重;模式2,次数&amp;权重-次数&amp;权重</t>
+格式：模式1,次数&amp;权重-次数&amp;权重;模式2,次数&amp;权重-次数&amp;权重</t>
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="G1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -101,7 +159,6 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>vidisJW:</t>
@@ -111,7 +168,6 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -119,14 +175,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="H1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">vidisJW:  </t>
@@ -135,7 +190,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>对应小游戏奖励表中的ID
@@ -143,14 +197,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="I1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>vidisJW:</t>
@@ -159,12 +212,11 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-格式：[{模式,[{奖励ID,权重,次数},{奖励ID,权重,次数}]}]
-例如：[{1,[{200310,70,7},{200311,30,3}]}]  代表给予200310奖励ID7次，200311奖励ID3次</t>
+格式：模式1,奖励ID&amp;权重&amp;次数-奖励ID&amp;权重&amp;次数;模式2,奖励ID&amp;权重&amp;次数-奖励ID&amp;权重&amp;次数;
+例如：1,200310&amp;70&amp;7-200311&amp;30&amp;3  代表给予200310奖励ID7次，200311奖励ID3次</t>
         </r>
       </text>
     </comment>
@@ -173,7 +225,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="124">
+  <si>
+    <t>小游戏模式ID</t>
+  </si>
   <si>
     <t>游戏ID</t>
   </si>
@@ -196,6 +251,9 @@
     <t>免费的固定奖励</t>
   </si>
   <si>
+    <t>免费随机奖励</t>
+  </si>
+  <si>
     <t>描述</t>
   </si>
   <si>
@@ -205,9 +263,21 @@
     <t>bool</t>
   </si>
   <si>
+    <t>Map&lt;int{,}Map&lt;int{&amp;}int&gt;{-}&gt;{;}</t>
+  </si>
+  <si>
     <t>Map&lt;int{,}int&gt;{;}</t>
   </si>
   <si>
+    <t>List&lt;List&lt;int&gt;{,}&gt;{;}</t>
+  </si>
+  <si>
+    <t>Map&lt;int{,}List&lt;List&lt;int&gt;{&amp;}&gt;{-}&gt;{;}</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
     <t>gameType</t>
   </si>
   <si>
@@ -217,12 +287,24 @@
     <t>interflow</t>
   </si>
   <si>
+    <t>spinType</t>
+  </si>
+  <si>
     <t>randCount</t>
   </si>
   <si>
     <t>clientShowCount</t>
   </si>
   <si>
+    <t>freeAward</t>
+  </si>
+  <si>
+    <t>freeRandAward</t>
+  </si>
+  <si>
+    <t>1,5&amp;1-6&amp;3-7&amp;15-8&amp;18-9&amp;12-10&amp;8-11&amp;5-12&amp;1-13&amp;1;2,5&amp;1-6&amp;3-7&amp;15-8&amp;18-9&amp;12-10&amp;8-11&amp;5-12&amp;1-13&amp;1;3,5&amp;1-6&amp;3-7&amp;20-8&amp;15-9&amp;10-10&amp;5-11&amp;5-12&amp;1-13&amp;0;4,5&amp;1-6&amp;3-7&amp;20-8&amp;15-9&amp;10-10&amp;5-11&amp;5-12&amp;1-13&amp;0;5,5&amp;1-6&amp;3-7&amp;20-8&amp;15-9&amp;10-10&amp;5-11&amp;5-12&amp;1-13&amp;1;6,5&amp;1-6&amp;10-7&amp;20-8&amp;15-9&amp;10-10&amp;6-11&amp;3-12&amp;1-13&amp;0;7,5&amp;1-6&amp;10-7&amp;20-8&amp;15-9&amp;10-10&amp;5-11&amp;1-12&amp;0-13&amp;0</t>
+  </si>
+  <si>
     <t>1,1;2,1;3,1;4,1;5,1;6,1;7,1</t>
   </si>
   <si>
@@ -238,21 +320,141 @@
     <t>拉火车红火车GRAND</t>
   </si>
   <si>
+    <t>1,1&amp;1;2,1&amp;1;3,1&amp;1;4,1&amp;1;5,1&amp;1;6,1&amp;1;7,1&amp;1</t>
+  </si>
+  <si>
     <t>1,8;2,8;3,8;4,8;5,8;6,8;7,8</t>
   </si>
   <si>
+    <t>1,1001000501&amp;10&amp;1-1001000502&amp;10&amp;1-1001000503&amp;6&amp;1-1001000504&amp;1&amp;1;2,1001000501&amp;10&amp;1-1001000502&amp;10&amp;1-1001000503&amp;6&amp;1-1001000504&amp;1&amp;1;3,1001000501&amp;10&amp;1-1001000502&amp;10&amp;1-1001000503&amp;6&amp;1-1001000504&amp;1&amp;1;4,1001000501&amp;10&amp;1-1001000502&amp;10&amp;1-1001000503&amp;6&amp;1-1001000504&amp;1&amp;1;5,1001000501&amp;10&amp;1-1001000502&amp;10&amp;1-1001000503&amp;6&amp;1-1001000504&amp;1&amp;1;6,1001000501&amp;10&amp;1-1001000502&amp;10&amp;1-1001000503&amp;6&amp;1-1001000504&amp;1&amp;1;7,1001000501&amp;10&amp;1-1001000502&amp;10&amp;1-1001000503&amp;6&amp;1-1001000504&amp;1&amp;1;8,1001000501&amp;10&amp;1-1001000502&amp;10&amp;1-1001000503&amp;6&amp;1-1001000504&amp;1&amp;1</t>
+  </si>
+  <si>
+    <t>收集集满触发地图，8个场景，随机奖励为3个+黄金列车金币系数</t>
+  </si>
+  <si>
     <t>黄金列车</t>
   </si>
   <si>
     <t>1,2;2,2;3,2;4,2;5,2;6,2;7,2</t>
   </si>
   <si>
+    <t>1,1001000701&amp;1&amp;1-1001000702&amp;1&amp;1;2,1001000701&amp;1&amp;1-1001000702&amp;1&amp;1;3,1001000701&amp;1&amp;1-1001000702&amp;1&amp;1;4,1001000701&amp;1&amp;1-1001000702&amp;1&amp;1;5,1001000701&amp;1&amp;1-1001000702&amp;1&amp;1;6,1001000701&amp;1&amp;1-1001000702&amp;1&amp;1;7,1001000701&amp;1&amp;1-1001000702&amp;1&amp;1</t>
+  </si>
+  <si>
     <t>免费2选1</t>
   </si>
   <si>
+    <t>1001000801,1001000802</t>
+  </si>
+  <si>
     <t>免费转</t>
   </si>
   <si>
+    <t>1001000901,1001000902</t>
+  </si>
+  <si>
+    <t>选择拉火车，转出触发局</t>
+  </si>
+  <si>
+    <t>1,1001000702&amp;1&amp;1-1001000703&amp;1&amp;1;2,1001000702&amp;1&amp;1-1001000703&amp;1&amp;1;3,1001000702&amp;1&amp;1-1001000703&amp;1&amp;1;4,1001000702&amp;1&amp;1-1001000703&amp;1&amp;1;5,1001000702&amp;1&amp;1-1001000703&amp;1&amp;1;6,1001000702&amp;1&amp;1-1001000703&amp;1&amp;1;7,1001000702&amp;1&amp;1-1001000703&amp;1&amp;1</t>
+  </si>
+  <si>
+    <t>4/5个免费2选1</t>
+  </si>
+  <si>
+    <t>地图全解锁送黄金列车/4个分散，转出触发局</t>
+  </si>
+  <si>
+    <t>黄金列车2</t>
+  </si>
+  <si>
+    <t>黄金列车3</t>
+  </si>
+  <si>
+    <t>黄金列车4</t>
+  </si>
+  <si>
+    <t>黄金列车5</t>
+  </si>
+  <si>
+    <t>黄金列车6</t>
+  </si>
+  <si>
+    <t>黄金列车7</t>
+  </si>
+  <si>
+    <t>1,1001000710&amp;1&amp;1-1001000704&amp;1&amp;1;2,1001000710&amp;1&amp;1-1001000704&amp;1&amp;1;3,1001000710&amp;1&amp;1-1001000704&amp;1&amp;1;4,1001000710&amp;1&amp;1-1001000704&amp;1&amp;1;5,1001000710&amp;1&amp;1-1001000704&amp;1&amp;1;6,1001000710&amp;1&amp;1-1001000704&amp;1&amp;1;7,1001000710&amp;1&amp;1-1001000704&amp;1&amp;1</t>
+  </si>
+  <si>
+    <t>1,1001000711&amp;1&amp;1-1001000705&amp;1&amp;1;2,1001000711&amp;1&amp;1-1001000705&amp;1&amp;1;3,1001000711&amp;1&amp;1-1001000705&amp;1&amp;1;4,1001000711&amp;1&amp;1-1001000705&amp;1&amp;1;5,1001000711&amp;1&amp;1-1001000705&amp;1&amp;1;6,1001000711&amp;1&amp;1-1001000705&amp;1&amp;1;7,1001000711&amp;1&amp;1-1001000705&amp;1&amp;1</t>
+  </si>
+  <si>
+    <t>1,1001000712&amp;1&amp;1-1001000706&amp;1&amp;1;2,1001000712&amp;1&amp;1-1001000706&amp;1&amp;1;3,1001000712&amp;1&amp;1-1001000706&amp;1&amp;1;4,1001000712&amp;1&amp;1-1001000706&amp;1&amp;1;5,1001000712&amp;1&amp;1-1001000706&amp;1&amp;1;6,1001000712&amp;1&amp;1-1001000706&amp;1&amp;1;7,1001000712&amp;1&amp;1-1001000706&amp;1&amp;1</t>
+  </si>
+  <si>
+    <t>1,1001000713&amp;1&amp;1-1001000707&amp;1&amp;1;2,1001000713&amp;1&amp;1-1001000707&amp;1&amp;1;3,1001000713&amp;1&amp;1-1001000707&amp;1&amp;1;4,1001000713&amp;1&amp;1-1001000707&amp;1&amp;1;5,1001000713&amp;1&amp;1-1001000707&amp;1&amp;1;6,1001000713&amp;1&amp;1-1001000707&amp;1&amp;1;7,1001000713&amp;1&amp;1-1001000707&amp;1&amp;1</t>
+  </si>
+  <si>
+    <t>1,1001000714&amp;1&amp;1-1001000708&amp;1&amp;1;2,1001000714&amp;1&amp;1-1001000708&amp;1&amp;1;3,1001000714&amp;1&amp;1-1001000708&amp;1&amp;1;4,1001000714&amp;1&amp;1-1001000708&amp;1&amp;1;5,1001000714&amp;1&amp;1-1001000708&amp;1&amp;1;6,1001000714&amp;1&amp;1-1001000708&amp;1&amp;1;7,1001000714&amp;1&amp;1-1001000708&amp;1&amp;1</t>
+  </si>
+  <si>
+    <t>1,1001000715&amp;1&amp;1-1001000709&amp;1&amp;1;2,1001000715&amp;1&amp;1-1001000709&amp;1&amp;1;3,1001000715&amp;1&amp;1-1001000709&amp;1&amp;1;4,1001000715&amp;1&amp;1-1001000709&amp;1&amp;1;5,1001000715&amp;1&amp;1-1001000709&amp;1&amp;1;6,1001000715&amp;1&amp;1-1001000709&amp;1&amp;1;7,1001000715&amp;1&amp;1-1001000709&amp;1&amp;1</t>
+  </si>
+  <si>
+    <t>1001000801,1001000803</t>
+  </si>
+  <si>
+    <t>1001000801,1001000804</t>
+  </si>
+  <si>
+    <t>1001000801,1001000805</t>
+  </si>
+  <si>
+    <t>1001000801,1001000806</t>
+  </si>
+  <si>
+    <t>1001000801,1001000807</t>
+  </si>
+  <si>
+    <t>1001000801,1001000808</t>
+  </si>
+  <si>
+    <t>1,1001000716&amp;1&amp;1-1001000704&amp;1&amp;1;2,1001000716&amp;1&amp;1-1001000704&amp;1&amp;1;3,1001000716&amp;1&amp;1-1001000704&amp;1&amp;1;4,1001000716&amp;1&amp;1-1001000704&amp;1&amp;1;5,1001000716&amp;1&amp;1-1001000704&amp;1&amp;1;6,1001000716&amp;1&amp;1-1001000704&amp;1&amp;1;7,1001000716&amp;1&amp;1-1001000704&amp;1&amp;1</t>
+  </si>
+  <si>
+    <t>1,1001000717&amp;1&amp;1-1001000705&amp;1&amp;1;2,1001000717&amp;1&amp;1-1001000705&amp;1&amp;1;3,1001000717&amp;1&amp;1-1001000705&amp;1&amp;1;4,1001000717&amp;1&amp;1-1001000705&amp;1&amp;1;5,1001000717&amp;1&amp;1-1001000705&amp;1&amp;1;6,1001000717&amp;1&amp;1-1001000705&amp;1&amp;1;7,1001000717&amp;1&amp;1-1001000705&amp;1&amp;1</t>
+  </si>
+  <si>
+    <t>1,1001000718&amp;1&amp;1-1001000706&amp;1&amp;1;2,1001000718&amp;1&amp;1-1001000706&amp;1&amp;1;3,1001000718&amp;1&amp;1-1001000706&amp;1&amp;1;4,1001000718&amp;1&amp;1-1001000706&amp;1&amp;1;5,1001000718&amp;1&amp;1-1001000706&amp;1&amp;1;6,1001000718&amp;1&amp;1-1001000706&amp;1&amp;1;7,1001000718&amp;1&amp;1-1001000706&amp;1&amp;1</t>
+  </si>
+  <si>
+    <t>1,1001000719&amp;1&amp;1-1001000707&amp;1&amp;1;2,1001000719&amp;1&amp;1-1001000707&amp;1&amp;1;3,1001000719&amp;1&amp;1-1001000707&amp;1&amp;1;4,1001000719&amp;1&amp;1-1001000707&amp;1&amp;1;5,1001000719&amp;1&amp;1-1001000707&amp;1&amp;1;6,1001000719&amp;1&amp;1-1001000707&amp;1&amp;1;7,1001000719&amp;1&amp;1-1001000707&amp;1&amp;1</t>
+  </si>
+  <si>
+    <t>1,1001000720&amp;1&amp;1-1001000708&amp;1&amp;1;2,1001000720&amp;1&amp;1-1001000708&amp;1&amp;1;3,1001000720&amp;1&amp;1-1001000708&amp;1&amp;1;4,1001000720&amp;1&amp;1-1001000708&amp;1&amp;1;5,1001000720&amp;1&amp;1-1001000708&amp;1&amp;1;6,1001000720&amp;1&amp;1-1001000708&amp;1&amp;1;7,1001000720&amp;1&amp;1-1001000708&amp;1&amp;1</t>
+  </si>
+  <si>
+    <t>1,1001000721&amp;1&amp;1-1001000709&amp;1&amp;1;2,1001000721&amp;1&amp;1-1001000709&amp;1&amp;1;3,1001000721&amp;1&amp;1-1001000709&amp;1&amp;1;4,1001000721&amp;1&amp;1-1001000709&amp;1&amp;1;5,1001000721&amp;1&amp;1-1001000709&amp;1&amp;1;6,1001000721&amp;1&amp;1-1001000709&amp;1&amp;1;7,1001000721&amp;1&amp;1-1001000709&amp;1&amp;1</t>
+  </si>
+  <si>
+    <t>1001000901,1001000903</t>
+  </si>
+  <si>
+    <t>1001000901,1001000904</t>
+  </si>
+  <si>
+    <t>1001000901,1001000905</t>
+  </si>
+  <si>
+    <t>1001000901,1001000906</t>
+  </si>
+  <si>
+    <t>1001000901,1001000907</t>
+  </si>
+  <si>
+    <t>1001000901,1001000908</t>
+  </si>
+  <si>
     <t>typeID</t>
   </si>
   <si>
@@ -395,96 +597,19 @@
   </si>
   <si>
     <t>通用普通10</t>
-  </si>
-  <si>
-    <t>小游戏模式ID</t>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>id</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,1&amp;1-2&amp;1-3&amp;1-4&amp;1-5&amp;1-6&amp;1-7&amp;1-8&amp;1-9&amp;1-10&amp;1-11&amp;1;2,1&amp;1-2&amp;1-3&amp;1-4&amp;1-5&amp;1-6&amp;1-7&amp;1-8&amp;1-9&amp;1-10&amp;1-11&amp;1;3,1&amp;1-2&amp;1-3&amp;1-4&amp;1-5&amp;1-6&amp;1-7&amp;1-8&amp;1-9&amp;1-10&amp;1-11&amp;1;4,1&amp;1-2&amp;1-3&amp;1-4&amp;1-5&amp;1-6&amp;1-7&amp;1-8&amp;1-9&amp;1-10&amp;1-11&amp;1;5,1&amp;1-2&amp;1-3&amp;1-4&amp;1-5&amp;1-6&amp;1-7&amp;1-8&amp;1-9&amp;1-10&amp;1-11&amp;1;6,1&amp;1-2&amp;1-3&amp;1-4&amp;1-5&amp;1-6&amp;1-7&amp;1-8&amp;1-9&amp;1-10&amp;1-11&amp;1;7,1&amp;1-2&amp;1-3&amp;1-4&amp;1-5&amp;1-6&amp;1-7&amp;1-8&amp;1-9&amp;1-10&amp;1-11&amp;1;</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Map&lt;int{,}Map&lt;int{&amp;}int&gt;{-}&gt;{;}</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>freeRandAward</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,1&amp;1;2,1&amp;1;3,1&amp;1;4,1&amp;1;5,1&amp;1;6,1&amp;1;7,1&amp;1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Map&lt;int{,}List&lt;List&lt;int&gt;{&amp;}&gt;{-}&gt;{;}</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,1001000501&amp;1&amp;1-1001000502&amp;1&amp;1-1001000503&amp;1&amp;1-1001000504&amp;1&amp;1;2,1001000501&amp;1&amp;1-1001000502&amp;1&amp;1-1001000503&amp;1&amp;1-1001000504&amp;1&amp;1;3,1001000501&amp;1&amp;1-1001000502&amp;1&amp;1-1001000503&amp;1&amp;1-1001000504&amp;1&amp;1;4,1001000501&amp;1&amp;1-1001000502&amp;1&amp;1-1001000503&amp;1&amp;1-1001000504&amp;1&amp;1;5,1001000501&amp;1&amp;1-1001000502&amp;1&amp;1-1001000503&amp;1&amp;1-1001000504&amp;1&amp;1;6,1001000501&amp;1&amp;1-1001000502&amp;1&amp;1-1001000503&amp;1&amp;1-1001000504&amp;1&amp;1;7,1001000501&amp;1&amp;1-1001000502&amp;1&amp;1-1001000503&amp;1&amp;1-1001000504&amp;1&amp;1;8,1001000501&amp;1&amp;1-1001000502&amp;1&amp;1-1001000503&amp;1&amp;1-1001000504&amp;1&amp;1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>免费随机奖励</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>1001000901,1001000902</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>1001000801,1001000802</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>List&lt;List&lt;int&gt;{,}&gt;{;}</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>地图全解锁送黄金列车/4个分散，转出触发局</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>选择拉火车，转出触发局</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>收集集满触发地图，8个场景，随机奖励为3个+黄金列车金币系数</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>freeAward</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>4/5个免费2选1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>spinType</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,1001000701&amp;1&amp;1-1001000702&amp;1&amp;1;2,1001000701&amp;1&amp;1-1001000702&amp;1&amp;1;3,1001000701&amp;1&amp;1-1001000702&amp;1&amp;1;4,1001000701&amp;1&amp;1-1001000702&amp;1&amp;1;5,1001000701&amp;1&amp;1-1001000702&amp;1&amp;1;6,1001000701&amp;1&amp;1-1001000702&amp;1&amp;1;7,1001000701&amp;1&amp;1-1001000702&amp;1&amp;1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,1001000702&amp;1&amp;1-1001000703&amp;1&amp;1;2,1001000702&amp;1&amp;1-1001000703&amp;1&amp;1;3,1001000702&amp;1&amp;1-1001000703&amp;1&amp;1;4,1001000702&amp;1&amp;1-1001000703&amp;1&amp;1;5,1001000702&amp;1&amp;1-1001000703&amp;1&amp;1;6,1001000702&amp;1&amp;1-1001000703&amp;1&amp;1;7,1001000702&amp;1&amp;1-1001000703&amp;1&amp;1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -496,28 +621,166 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -525,46 +788,210 @@
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -572,51 +999,331 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="51">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 73" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
-    <cellStyle name="常规 80" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 73" xfId="49"/>
+    <cellStyle name="常规 80" xfId="50"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
-<customStorage xmlns="https://web.wps.cn/et/2018/main">
-  <book/>
-  <sheets/>
-</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -871,847 +1578,1928 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:J51"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14.125" customWidth="1"/>
     <col min="3" max="3" width="8.25" customWidth="1"/>
     <col min="5" max="5" width="11.5" customWidth="1"/>
     <col min="6" max="6" width="38.75" customWidth="1"/>
     <col min="7" max="7" width="22.75" customWidth="1"/>
-    <col min="8" max="8" width="23.75" style="7" customWidth="1"/>
+    <col min="8" max="8" width="23.75" style="1" customWidth="1"/>
     <col min="9" max="9" width="60.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="1" ht="16.5" spans="1:10">
       <c r="A1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="H1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="G2" s="1" t="s">
+    </row>
+    <row r="2" ht="16.5" spans="1:10">
+      <c r="A2" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="B2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="H2" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="J2" s="1"/>
-    </row>
-    <row r="3" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="6" t="s">
-        <v>76</v>
+        <v>14</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" s="2"/>
+    </row>
+    <row r="3" ht="16.5" hidden="1" spans="1:10">
+      <c r="A3" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>92</v>
+        <v>19</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>20</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>90</v>
+        <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>79</v>
+        <v>24</v>
       </c>
       <c r="J3" s="3"/>
     </row>
-    <row r="4" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
+    <row r="4" ht="16.5" hidden="1" spans="2:10">
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
       <c r="H4" s="3"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-    </row>
-    <row r="5" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="1">
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+    </row>
+    <row r="5" ht="16.5" spans="1:10">
+      <c r="A5" s="7">
         <v>10010001</v>
       </c>
-      <c r="B5" s="5">
-        <v>100100</v>
-      </c>
-      <c r="C5" s="1">
-        <v>1</v>
-      </c>
-      <c r="D5" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="E5" s="1">
-        <v>1</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>16</v>
+      <c r="B5" s="8">
+        <v>100100</v>
+      </c>
+      <c r="C5" s="2">
+        <v>1</v>
+      </c>
+      <c r="D5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="H5" s="3">
         <v>1001000101</v>
       </c>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="1">
+      <c r="I5" s="2"/>
+      <c r="J5" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" ht="16.5" spans="1:10">
+      <c r="A6" s="7">
         <v>10010002</v>
       </c>
-      <c r="B6" s="5">
-        <v>100100</v>
-      </c>
-      <c r="C6" s="1">
-        <v>1</v>
-      </c>
-      <c r="D6" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="E6" s="1">
-        <v>1</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>16</v>
+      <c r="B6" s="8">
+        <v>100100</v>
+      </c>
+      <c r="C6" s="2">
+        <v>1</v>
+      </c>
+      <c r="D6" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="H6" s="3">
         <v>1001000201</v>
       </c>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="1">
+      <c r="I6" s="2"/>
+      <c r="J6" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" ht="16.5" spans="1:10">
+      <c r="A7" s="7">
         <v>10010003</v>
       </c>
-      <c r="B7" s="5">
-        <v>100100</v>
-      </c>
-      <c r="C7" s="1">
-        <v>1</v>
-      </c>
-      <c r="D7" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="E7" s="1">
-        <v>1</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>16</v>
+      <c r="B7" s="8">
+        <v>100100</v>
+      </c>
+      <c r="C7" s="2">
+        <v>1</v>
+      </c>
+      <c r="D7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="H7" s="3">
         <v>1001000301</v>
       </c>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="1">
+      <c r="I7" s="2"/>
+      <c r="J7" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" ht="16.5" spans="1:10">
+      <c r="A8" s="7">
         <v>10010004</v>
       </c>
-      <c r="B8" s="5">
-        <v>100100</v>
-      </c>
-      <c r="C8" s="1">
-        <v>1</v>
-      </c>
-      <c r="D8" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="E8" s="1">
-        <v>1</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>16</v>
+      <c r="B8" s="8">
+        <v>100100</v>
+      </c>
+      <c r="C8" s="2">
+        <v>1</v>
+      </c>
+      <c r="D8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="H8" s="3">
         <v>1001000401</v>
       </c>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="1">
+      <c r="I8" s="2"/>
+      <c r="J8" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" ht="16.5" spans="1:10">
+      <c r="A9" s="7">
         <v>10010005</v>
       </c>
-      <c r="B9" s="5">
-        <v>100100</v>
-      </c>
-      <c r="C9" s="1">
-        <v>1</v>
-      </c>
-      <c r="D9" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="E9" s="1">
-        <v>1</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>21</v>
+      <c r="B9" s="8">
+        <v>100100</v>
+      </c>
+      <c r="C9" s="2">
+        <v>1</v>
+      </c>
+      <c r="D9" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="H9" s="3"/>
-      <c r="I9" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="1">
+      <c r="I9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" ht="16.5" spans="1:10">
+      <c r="A10" s="7">
         <v>10010006</v>
       </c>
-      <c r="B10" s="5">
-        <v>100100</v>
-      </c>
-      <c r="C10" s="1">
-        <v>1</v>
-      </c>
-      <c r="D10" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="E10" s="1">
-        <v>1</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>16</v>
+      <c r="B10" s="8">
+        <v>100100</v>
+      </c>
+      <c r="C10" s="2">
+        <v>1</v>
+      </c>
+      <c r="D10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="H10" s="3">
         <v>1001000504</v>
       </c>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="1">
+      <c r="I10" s="2"/>
+      <c r="J10" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" ht="16.5" spans="1:10">
+      <c r="A11" s="7">
         <v>10010007</v>
       </c>
-      <c r="B11" s="5">
-        <v>100100</v>
-      </c>
-      <c r="C11" s="1">
-        <v>0</v>
-      </c>
-      <c r="D11" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="E11" s="1">
-        <v>1</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>23</v>
+      <c r="B11" s="8">
+        <v>100100</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0</v>
+      </c>
+      <c r="D11" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" s="2">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="H11" s="3"/>
-      <c r="I11" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="J11" s="1" t="s">
+      <c r="I11" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" ht="16.5" spans="1:10">
+      <c r="A12" s="7">
+        <v>10010008</v>
+      </c>
+      <c r="B12" s="8">
+        <v>100100</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" ht="16.5" spans="1:10">
+      <c r="A13" s="7">
+        <v>10010010</v>
+      </c>
+      <c r="B13" s="8">
+        <v>100100</v>
+      </c>
+      <c r="C13" s="2">
+        <v>2</v>
+      </c>
+      <c r="D13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2">
+        <v>25</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" ht="16.5" spans="1:10">
+      <c r="A14" s="7">
+        <v>10010011</v>
+      </c>
+      <c r="B14" s="8">
+        <v>100100</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0</v>
+      </c>
+      <c r="D14" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" s="2">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H14" s="3"/>
+      <c r="I14" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" ht="16.5" spans="1:10">
+      <c r="A15" s="7">
+        <v>10010009</v>
+      </c>
+      <c r="B15" s="8">
+        <v>100100</v>
+      </c>
+      <c r="C15" s="2">
+        <v>2</v>
+      </c>
+      <c r="D15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E15" s="2">
         <v>24</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="1">
-        <v>10010008</v>
-      </c>
-      <c r="B12" s="5">
-        <v>100100</v>
-      </c>
-      <c r="C12" s="1">
-        <v>0</v>
-      </c>
-      <c r="D12" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="E12" s="1">
-        <v>1</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1" t="s">
+      <c r="F15" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" ht="16.5" spans="1:10">
+      <c r="A16" s="7">
+        <v>10010012</v>
+      </c>
+      <c r="B16" s="8">
+        <v>100100</v>
+      </c>
+      <c r="C16" s="2">
+        <v>1</v>
+      </c>
+      <c r="D16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E16" s="2">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H16" s="3">
+        <v>1001000505</v>
+      </c>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="17" ht="16.5" spans="1:10">
+      <c r="A17" s="7">
+        <v>10010013</v>
+      </c>
+      <c r="B17" s="8">
+        <v>100100</v>
+      </c>
+      <c r="C17" s="2">
+        <v>1</v>
+      </c>
+      <c r="D17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E17" s="2">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H17" s="3">
+        <v>1001000506</v>
+      </c>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" ht="16.5" spans="1:10">
+      <c r="A18" s="7">
+        <v>10010014</v>
+      </c>
+      <c r="B18" s="8">
+        <v>100100</v>
+      </c>
+      <c r="C18" s="2">
+        <v>1</v>
+      </c>
+      <c r="D18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E18" s="2">
+        <v>1</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H18" s="3">
+        <v>1001000507</v>
+      </c>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19" ht="16.5" spans="1:10">
+      <c r="A19" s="7">
+        <v>10010015</v>
+      </c>
+      <c r="B19" s="8">
+        <v>100100</v>
+      </c>
+      <c r="C19" s="2">
+        <v>1</v>
+      </c>
+      <c r="D19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E19" s="2">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H19" s="3">
+        <v>1001000508</v>
+      </c>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="20" ht="16.5" spans="1:10">
+      <c r="A20" s="7">
+        <v>10010016</v>
+      </c>
+      <c r="B20" s="8">
+        <v>100100</v>
+      </c>
+      <c r="C20" s="2">
+        <v>1</v>
+      </c>
+      <c r="D20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E20" s="2">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H20" s="3">
+        <v>1001000509</v>
+      </c>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" ht="16.5" spans="1:10">
+      <c r="A21" s="7">
+        <v>10010017</v>
+      </c>
+      <c r="B21" s="8">
+        <v>100100</v>
+      </c>
+      <c r="C21" s="2">
+        <v>1</v>
+      </c>
+      <c r="D21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E21" s="2">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H21" s="3">
+        <v>1001000510</v>
+      </c>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="22" ht="16.5" spans="1:10">
+      <c r="A22" s="7">
+        <v>10010018</v>
+      </c>
+      <c r="B22" s="8">
+        <v>100100</v>
+      </c>
+      <c r="C22" s="2">
+        <v>0</v>
+      </c>
+      <c r="D22" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E22" s="2">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H22" s="3"/>
+      <c r="I22" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" ht="16.5" spans="1:10">
+      <c r="A23" s="7">
+        <v>10010019</v>
+      </c>
+      <c r="B23" s="8">
+        <v>100100</v>
+      </c>
+      <c r="C23" s="2">
+        <v>0</v>
+      </c>
+      <c r="D23" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E23" s="2">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H23" s="3"/>
+      <c r="I23" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24" ht="16.5" spans="1:10">
+      <c r="A24" s="7">
+        <v>10010020</v>
+      </c>
+      <c r="B24" s="8">
+        <v>100100</v>
+      </c>
+      <c r="C24" s="2">
+        <v>0</v>
+      </c>
+      <c r="D24" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E24" s="2">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H24" s="3"/>
+      <c r="I24" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="25" ht="16.5" spans="1:10">
+      <c r="A25" s="7">
+        <v>10010021</v>
+      </c>
+      <c r="B25" s="8">
+        <v>100100</v>
+      </c>
+      <c r="C25" s="2">
+        <v>0</v>
+      </c>
+      <c r="D25" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" s="2">
+        <v>1</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H25" s="3"/>
+      <c r="I25" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="26" ht="16.5" spans="1:10">
+      <c r="A26" s="7">
+        <v>10010022</v>
+      </c>
+      <c r="B26" s="8">
+        <v>100100</v>
+      </c>
+      <c r="C26" s="2">
+        <v>0</v>
+      </c>
+      <c r="D26" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E26" s="2">
+        <v>1</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H26" s="3"/>
+      <c r="I26" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="27" ht="16.5" spans="1:10">
+      <c r="A27" s="7">
+        <v>10010023</v>
+      </c>
+      <c r="B27" s="8">
+        <v>100100</v>
+      </c>
+      <c r="C27" s="2">
+        <v>0</v>
+      </c>
+      <c r="D27" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E27" s="2">
+        <v>1</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H27" s="3"/>
+      <c r="I27" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="28" ht="16.5" spans="1:10">
+      <c r="A28" s="7">
+        <v>10010024</v>
+      </c>
+      <c r="B28" s="8">
+        <v>100100</v>
+      </c>
+      <c r="C28" s="2">
+        <v>0</v>
+      </c>
+      <c r="D28" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E28" s="2">
+        <v>1</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="29" ht="16.5" spans="1:10">
+      <c r="A29" s="7">
+        <v>10010025</v>
+      </c>
+      <c r="B29" s="8">
+        <v>100100</v>
+      </c>
+      <c r="C29" s="2">
+        <v>0</v>
+      </c>
+      <c r="D29" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E29" s="2">
+        <v>1</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="30" ht="16.5" spans="1:10">
+      <c r="A30" s="7">
+        <v>10010026</v>
+      </c>
+      <c r="B30" s="8">
+        <v>100100</v>
+      </c>
+      <c r="C30" s="2">
+        <v>0</v>
+      </c>
+      <c r="D30" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E30" s="2">
+        <v>1</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="31" ht="16.5" spans="1:10">
+      <c r="A31" s="7">
+        <v>10010027</v>
+      </c>
+      <c r="B31" s="8">
+        <v>100100</v>
+      </c>
+      <c r="C31" s="2">
+        <v>0</v>
+      </c>
+      <c r="D31" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E31" s="2">
+        <v>1</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="32" ht="16.5" spans="1:10">
+      <c r="A32" s="7">
+        <v>10010028</v>
+      </c>
+      <c r="B32" s="8">
+        <v>100100</v>
+      </c>
+      <c r="C32" s="2">
+        <v>0</v>
+      </c>
+      <c r="D32" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E32" s="2">
+        <v>1</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="33" ht="16.5" spans="1:10">
+      <c r="A33" s="7">
+        <v>10010029</v>
+      </c>
+      <c r="B33" s="8">
+        <v>100100</v>
+      </c>
+      <c r="C33" s="2">
+        <v>0</v>
+      </c>
+      <c r="D33" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E33" s="2">
+        <v>1</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="34" ht="16.5" spans="1:10">
+      <c r="A34" s="7">
+        <v>10010030</v>
+      </c>
+      <c r="B34" s="8">
+        <v>100100</v>
+      </c>
+      <c r="C34" s="2">
+        <v>0</v>
+      </c>
+      <c r="D34" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E34" s="2">
+        <v>1</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H34" s="3"/>
+      <c r="I34" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="35" ht="16.5" spans="1:10">
+      <c r="A35" s="7">
+        <v>10010031</v>
+      </c>
+      <c r="B35" s="8">
+        <v>100100</v>
+      </c>
+      <c r="C35" s="2">
+        <v>0</v>
+      </c>
+      <c r="D35" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E35" s="2">
+        <v>1</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H35" s="3"/>
+      <c r="I35" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="36" ht="16.5" spans="1:10">
+      <c r="A36" s="7">
+        <v>10010032</v>
+      </c>
+      <c r="B36" s="8">
+        <v>100100</v>
+      </c>
+      <c r="C36" s="2">
+        <v>0</v>
+      </c>
+      <c r="D36" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E36" s="2">
+        <v>1</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H36" s="3"/>
+      <c r="I36" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="37" ht="16.5" spans="1:10">
+      <c r="A37" s="7">
+        <v>10010033</v>
+      </c>
+      <c r="B37" s="8">
+        <v>100100</v>
+      </c>
+      <c r="C37" s="2">
+        <v>0</v>
+      </c>
+      <c r="D37" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E37" s="2">
+        <v>1</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H37" s="3"/>
+      <c r="I37" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="38" ht="16.5" spans="1:10">
+      <c r="A38" s="7">
+        <v>10010034</v>
+      </c>
+      <c r="B38" s="8">
+        <v>100100</v>
+      </c>
+      <c r="C38" s="2">
+        <v>0</v>
+      </c>
+      <c r="D38" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E38" s="2">
+        <v>1</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H38" s="3"/>
+      <c r="I38" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="39" ht="16.5" spans="1:10">
+      <c r="A39" s="7">
+        <v>10010035</v>
+      </c>
+      <c r="B39" s="8">
+        <v>100100</v>
+      </c>
+      <c r="C39" s="2">
+        <v>0</v>
+      </c>
+      <c r="D39" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E39" s="2">
+        <v>1</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H39" s="3"/>
+      <c r="I39" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="40" ht="16.5" spans="1:10">
+      <c r="A40" s="7">
+        <v>10010036</v>
+      </c>
+      <c r="B40" s="8">
+        <v>100100</v>
+      </c>
+      <c r="C40" s="2">
+        <v>2</v>
+      </c>
+      <c r="D40" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E40" s="2">
+        <v>24</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="I40" s="2"/>
+      <c r="J40" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="41" ht="16.5" spans="1:10">
+      <c r="A41" s="7">
+        <v>10010037</v>
+      </c>
+      <c r="B41" s="8">
+        <v>100100</v>
+      </c>
+      <c r="C41" s="2">
+        <v>2</v>
+      </c>
+      <c r="D41" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E41" s="2">
+        <v>24</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="I41" s="2"/>
+      <c r="J41" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="42" ht="16.5" spans="1:10">
+      <c r="A42" s="7">
+        <v>10010038</v>
+      </c>
+      <c r="B42" s="8">
+        <v>100100</v>
+      </c>
+      <c r="C42" s="2">
+        <v>2</v>
+      </c>
+      <c r="D42" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E42" s="2">
+        <v>24</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="I42" s="2"/>
+      <c r="J42" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="43" ht="16.5" spans="1:10">
+      <c r="A43" s="7">
+        <v>10010039</v>
+      </c>
+      <c r="B43" s="8">
+        <v>100100</v>
+      </c>
+      <c r="C43" s="2">
+        <v>2</v>
+      </c>
+      <c r="D43" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E43" s="2">
+        <v>24</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="I43" s="2"/>
+      <c r="J43" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="44" ht="16.5" spans="1:10">
+      <c r="A44" s="7">
+        <v>10010040</v>
+      </c>
+      <c r="B44" s="8">
+        <v>100100</v>
+      </c>
+      <c r="C44" s="2">
+        <v>2</v>
+      </c>
+      <c r="D44" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E44" s="2">
+        <v>24</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="I44" s="2"/>
+      <c r="J44" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="45" ht="16.5" spans="1:10">
+      <c r="A45" s="7">
+        <v>10010041</v>
+      </c>
+      <c r="B45" s="8">
+        <v>100100</v>
+      </c>
+      <c r="C45" s="2">
+        <v>2</v>
+      </c>
+      <c r="D45" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E45" s="2">
+        <v>24</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="I45" s="2"/>
+      <c r="J45" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="46" ht="16.5" spans="1:10">
+      <c r="A46" s="7">
+        <v>10010042</v>
+      </c>
+      <c r="B46" s="8">
+        <v>100100</v>
+      </c>
+      <c r="C46" s="2">
+        <v>2</v>
+      </c>
+      <c r="D46" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E46" s="2">
         <v>25</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="1">
-        <v>10010010</v>
-      </c>
-      <c r="B13" s="5">
-        <v>100100</v>
-      </c>
-      <c r="C13" s="1">
+      <c r="F46" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="I46" s="2"/>
+      <c r="J46" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="47" ht="16.5" spans="1:10">
+      <c r="A47" s="7">
+        <v>10010043</v>
+      </c>
+      <c r="B47" s="8">
+        <v>100100</v>
+      </c>
+      <c r="C47" s="2">
         <v>2</v>
       </c>
-      <c r="D13" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="E13" s="1">
+      <c r="D47" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E47" s="2">
         <v>25</v>
       </c>
-      <c r="F13" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="1">
-        <v>10010011</v>
-      </c>
-      <c r="B14" s="5">
-        <v>100100</v>
-      </c>
-      <c r="C14" s="1">
-        <v>0</v>
-      </c>
-      <c r="D14" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="E14" s="1">
-        <v>1</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H14" s="3"/>
-      <c r="I14" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="1">
-        <v>10010009</v>
-      </c>
-      <c r="B15" s="5">
-        <v>100100</v>
-      </c>
-      <c r="C15" s="1">
+      <c r="F47" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="I47" s="2"/>
+      <c r="J47" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="48" ht="16.5" spans="1:10">
+      <c r="A48" s="7">
+        <v>10010044</v>
+      </c>
+      <c r="B48" s="8">
+        <v>100100</v>
+      </c>
+      <c r="C48" s="2">
         <v>2</v>
       </c>
-      <c r="D15" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="E15" s="1">
-        <v>24</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1" t="s">
-        <v>87</v>
+      <c r="D48" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E48" s="2">
+        <v>25</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="I48" s="2"/>
+      <c r="J48" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="49" ht="16.5" spans="1:10">
+      <c r="A49" s="7">
+        <v>10010045</v>
+      </c>
+      <c r="B49" s="8">
+        <v>100100</v>
+      </c>
+      <c r="C49" s="2">
+        <v>2</v>
+      </c>
+      <c r="D49" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E49" s="2">
+        <v>25</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="I49" s="2"/>
+      <c r="J49" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="50" ht="16.5" spans="1:10">
+      <c r="A50" s="7">
+        <v>10010046</v>
+      </c>
+      <c r="B50" s="8">
+        <v>100100</v>
+      </c>
+      <c r="C50" s="2">
+        <v>2</v>
+      </c>
+      <c r="D50" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E50" s="2">
+        <v>25</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="I50" s="2"/>
+      <c r="J50" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="51" ht="16.5" spans="1:10">
+      <c r="A51" s="7">
+        <v>10010047</v>
+      </c>
+      <c r="B51" s="8">
+        <v>100100</v>
+      </c>
+      <c r="C51" s="2">
+        <v>2</v>
+      </c>
+      <c r="D51" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E51" s="2">
+        <v>25</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="I51" s="2"/>
+      <c r="J51" s="2" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B47"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="1"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>26</v>
+        <v>76</v>
       </c>
       <c r="B1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
       <c r="A14">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
       <c r="A15">
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
       <c r="A16">
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
       <c r="A17">
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
       <c r="A18">
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
       <c r="A19">
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
       <c r="A20">
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
       <c r="A21">
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
       <c r="A22">
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
       <c r="A23">
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
       <c r="A24">
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
       <c r="A25">
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
       <c r="A26">
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
       <c r="A27">
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
       <c r="A28">
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
       <c r="A29">
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
       <c r="A30">
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
       <c r="A31">
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
       <c r="A32">
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
       <c r="A33">
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
       <c r="A34">
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
       <c r="A35">
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
       <c r="A36">
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
       <c r="A37">
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
       <c r="A38">
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
       <c r="A39">
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
       <c r="A40">
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
       <c r="A41">
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
       <c r="A42">
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
       <c r="A43">
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
       <c r="A44">
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
       <c r="A45">
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
       <c r="A46">
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
       <c r="A47">
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>73</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/slots/resources/sample/SpecialAuxiliary.xlsx
+++ b/slots/resources/sample/SpecialAuxiliary.xlsx
@@ -225,7 +225,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="125">
   <si>
     <t>小游戏模式ID</t>
   </si>
@@ -302,13 +302,16 @@
     <t>freeRandAward</t>
   </si>
   <si>
+    <t>1,5&amp;1-6&amp;3-7&amp;18-8&amp;12-9&amp;8-10&amp;5-11&amp;3-12&amp;1;2,5&amp;1-6&amp;3-7&amp;15-8&amp;18-9&amp;12-10&amp;8-11&amp;5-12&amp;1-13&amp;1;3,5&amp;1-6&amp;3-7&amp;20-8&amp;15-9&amp;10-10&amp;5-11&amp;5-12&amp;1-13&amp;0;4,5&amp;1-6&amp;3-7&amp;20-8&amp;15-9&amp;10-10&amp;5-11&amp;5-12&amp;1-13&amp;0;5,5&amp;1-6&amp;3-7&amp;20-8&amp;15-9&amp;10-10&amp;5-11&amp;5-12&amp;1-13&amp;1;6,5&amp;1-6&amp;10-7&amp;20-8&amp;15-9&amp;10-10&amp;6-11&amp;3-12&amp;1-13&amp;0;7,5&amp;1-6&amp;10-7&amp;20-8&amp;15-9&amp;10-10&amp;5-11&amp;1-12&amp;0-13&amp;0</t>
+  </si>
+  <si>
+    <t>1,1;2,1;3,1;4,1;5,1;6,1;7,1</t>
+  </si>
+  <si>
+    <t>拉火车绿火车MINI随几次为几节车厢</t>
+  </si>
+  <si>
     <t>1,5&amp;1-6&amp;3-7&amp;15-8&amp;18-9&amp;12-10&amp;8-11&amp;5-12&amp;1-13&amp;1;2,5&amp;1-6&amp;3-7&amp;15-8&amp;18-9&amp;12-10&amp;8-11&amp;5-12&amp;1-13&amp;1;3,5&amp;1-6&amp;3-7&amp;20-8&amp;15-9&amp;10-10&amp;5-11&amp;5-12&amp;1-13&amp;0;4,5&amp;1-6&amp;3-7&amp;20-8&amp;15-9&amp;10-10&amp;5-11&amp;5-12&amp;1-13&amp;0;5,5&amp;1-6&amp;3-7&amp;20-8&amp;15-9&amp;10-10&amp;5-11&amp;5-12&amp;1-13&amp;1;6,5&amp;1-6&amp;10-7&amp;20-8&amp;15-9&amp;10-10&amp;6-11&amp;3-12&amp;1-13&amp;0;7,5&amp;1-6&amp;10-7&amp;20-8&amp;15-9&amp;10-10&amp;5-11&amp;1-12&amp;0-13&amp;0</t>
-  </si>
-  <si>
-    <t>1,1;2,1;3,1;4,1;5,1;6,1;7,1</t>
-  </si>
-  <si>
-    <t>拉火车绿火车MINI随几次为几节车厢</t>
   </si>
   <si>
     <t>拉火车蓝火车MINOR</t>
@@ -1746,7 +1749,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>26</v>
@@ -1756,7 +1759,7 @@
       </c>
       <c r="I6" s="2"/>
       <c r="J6" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:10">
@@ -1776,7 +1779,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>26</v>
@@ -1786,7 +1789,7 @@
       </c>
       <c r="I7" s="2"/>
       <c r="J7" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:10">
@@ -1806,7 +1809,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>26</v>
@@ -1816,7 +1819,7 @@
       </c>
       <c r="I8" s="2"/>
       <c r="J8" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:10">
@@ -1836,17 +1839,17 @@
         <v>1</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:10">
@@ -1866,7 +1869,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>26</v>
@@ -1876,7 +1879,7 @@
       </c>
       <c r="I10" s="2"/>
       <c r="J10" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:10">
@@ -1896,17 +1899,17 @@
         <v>1</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:10">
@@ -1926,17 +1929,17 @@
         <v>1</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I12" s="2"/>
       <c r="J12" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:10">
@@ -1956,17 +1959,17 @@
         <v>25</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:10">
@@ -1986,17 +1989,17 @@
         <v>1</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:10">
@@ -2016,17 +2019,17 @@
         <v>24</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I15" s="2"/>
       <c r="J15" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:10">
@@ -2046,7 +2049,7 @@
         <v>1</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>26</v>
@@ -2056,7 +2059,7 @@
       </c>
       <c r="I16" s="2"/>
       <c r="J16" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:10">
@@ -2076,7 +2079,7 @@
         <v>1</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>26</v>
@@ -2086,7 +2089,7 @@
       </c>
       <c r="I17" s="2"/>
       <c r="J17" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:10">
@@ -2106,7 +2109,7 @@
         <v>1</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>26</v>
@@ -2116,7 +2119,7 @@
       </c>
       <c r="I18" s="2"/>
       <c r="J18" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:10">
@@ -2136,7 +2139,7 @@
         <v>1</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>26</v>
@@ -2146,7 +2149,7 @@
       </c>
       <c r="I19" s="2"/>
       <c r="J19" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:10">
@@ -2166,7 +2169,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>26</v>
@@ -2176,7 +2179,7 @@
       </c>
       <c r="I20" s="2"/>
       <c r="J20" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:10">
@@ -2196,7 +2199,7 @@
         <v>1</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>26</v>
@@ -2206,7 +2209,7 @@
       </c>
       <c r="I21" s="2"/>
       <c r="J21" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:10">
@@ -2226,17 +2229,17 @@
         <v>1</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:10">
@@ -2256,17 +2259,17 @@
         <v>1</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:10">
@@ -2286,17 +2289,17 @@
         <v>1</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25" ht="16.5" spans="1:10">
@@ -2316,17 +2319,17 @@
         <v>1</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="26" ht="16.5" spans="1:10">
@@ -2346,17 +2349,17 @@
         <v>1</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27" ht="16.5" spans="1:10">
@@ -2376,17 +2379,17 @@
         <v>1</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H27" s="3"/>
       <c r="I27" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="28" ht="16.5" spans="1:10">
@@ -2406,17 +2409,17 @@
         <v>1</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I28" s="2"/>
       <c r="J28" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="29" ht="16.5" spans="1:10">
@@ -2436,17 +2439,17 @@
         <v>1</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I29" s="2"/>
       <c r="J29" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="30" ht="16.5" spans="1:10">
@@ -2466,17 +2469,17 @@
         <v>1</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I30" s="2"/>
       <c r="J30" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="31" ht="16.5" spans="1:10">
@@ -2496,17 +2499,17 @@
         <v>1</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I31" s="2"/>
       <c r="J31" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="32" ht="16.5" spans="1:10">
@@ -2526,17 +2529,17 @@
         <v>1</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I32" s="2"/>
       <c r="J32" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="33" ht="16.5" spans="1:10">
@@ -2556,17 +2559,17 @@
         <v>1</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I33" s="2"/>
       <c r="J33" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="34" ht="16.5" spans="1:10">
@@ -2586,17 +2589,17 @@
         <v>1</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="35" ht="16.5" spans="1:10">
@@ -2616,17 +2619,17 @@
         <v>1</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H35" s="3"/>
       <c r="I35" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="36" ht="16.5" spans="1:10">
@@ -2646,17 +2649,17 @@
         <v>1</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="37" ht="16.5" spans="1:10">
@@ -2676,17 +2679,17 @@
         <v>1</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H37" s="3"/>
       <c r="I37" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="38" ht="16.5" spans="1:10">
@@ -2706,17 +2709,17 @@
         <v>1</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H38" s="3"/>
       <c r="I38" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="39" ht="16.5" spans="1:10">
@@ -2736,17 +2739,17 @@
         <v>1</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="40" ht="16.5" spans="1:10">
@@ -2766,17 +2769,17 @@
         <v>24</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I40" s="2"/>
       <c r="J40" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="41" ht="16.5" spans="1:10">
@@ -2796,17 +2799,17 @@
         <v>24</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I41" s="2"/>
       <c r="J41" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="42" ht="16.5" spans="1:10">
@@ -2826,17 +2829,17 @@
         <v>24</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I42" s="2"/>
       <c r="J42" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="43" ht="16.5" spans="1:10">
@@ -2856,17 +2859,17 @@
         <v>24</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I43" s="2"/>
       <c r="J43" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="44" ht="16.5" spans="1:10">
@@ -2886,17 +2889,17 @@
         <v>24</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I44" s="2"/>
       <c r="J44" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="45" ht="16.5" spans="1:10">
@@ -2916,17 +2919,17 @@
         <v>24</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I45" s="2"/>
       <c r="J45" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="46" ht="16.5" spans="1:10">
@@ -2946,17 +2949,17 @@
         <v>25</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I46" s="2"/>
       <c r="J46" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="47" ht="16.5" spans="1:10">
@@ -2976,17 +2979,17 @@
         <v>25</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I47" s="2"/>
       <c r="J47" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="48" ht="16.5" spans="1:10">
@@ -3006,17 +3009,17 @@
         <v>25</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I48" s="2"/>
       <c r="J48" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="49" ht="16.5" spans="1:10">
@@ -3036,17 +3039,17 @@
         <v>25</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I49" s="2"/>
       <c r="J49" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="50" ht="16.5" spans="1:10">
@@ -3066,17 +3069,17 @@
         <v>25</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I50" s="2"/>
       <c r="J50" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="51" ht="16.5" spans="1:10">
@@ -3096,17 +3099,17 @@
         <v>25</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I51" s="2"/>
       <c r="J51" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -3124,10 +3127,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -3135,7 +3138,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3143,7 +3146,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -3151,7 +3154,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -3159,7 +3162,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -3167,7 +3170,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -3175,7 +3178,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -3183,7 +3186,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -3191,7 +3194,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -3199,7 +3202,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -3207,7 +3210,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -3215,7 +3218,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -3223,7 +3226,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -3231,7 +3234,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -3239,7 +3242,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -3247,7 +3250,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -3255,7 +3258,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -3263,7 +3266,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -3271,7 +3274,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -3279,7 +3282,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -3287,7 +3290,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -3295,7 +3298,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -3303,7 +3306,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -3311,7 +3314,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -3319,7 +3322,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -3327,7 +3330,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -3335,7 +3338,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -3343,7 +3346,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -3351,7 +3354,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -3359,7 +3362,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -3367,7 +3370,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -3375,7 +3378,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -3383,7 +3386,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -3391,7 +3394,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -3399,7 +3402,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -3407,7 +3410,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -3415,7 +3418,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -3423,7 +3426,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -3431,7 +3434,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -3439,7 +3442,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -3447,7 +3450,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -3455,7 +3458,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -3463,7 +3466,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -3471,7 +3474,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -3479,7 +3482,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -3487,7 +3490,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -3495,7 +3498,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialAuxiliary.xlsx
+++ b/slots/resources/sample/SpecialAuxiliary.xlsx
@@ -427,7 +427,7 @@
     <t>3_1</t>
   </si>
   <si>
-    <t>0_900_1|2_800_1|3_800_1|5_2500_1|8_1200_1|10_900_1|12_800_1|15_300_1|18_50_1|20_5_1|25_0_1|30_0_1</t>
+    <t>0_15000_3|10_500_3|15_500_3|20_1000_3|25_1000_3|30_1000_3|40_1000_3|50_1000_3|100_1000_3|150_1000_3|200_1000_3|300_1000_3</t>
   </si>
   <si>
     <t>4_5001003</t>
@@ -908,14 +908,13 @@
     </font>
     <font>
       <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -926,12 +925,13 @@
     </font>
     <font>
       <b/>
-      <sz val="9"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
@@ -1444,19 +1444,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -1468,7 +1466,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -1496,7 +1493,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1510,10 +1506,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1543,17 +1535,8 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1903,15 +1886,15 @@
     <col min="7" max="7" width="9.875" customWidth="1"/>
     <col min="8" max="8" width="16.25" customWidth="1"/>
     <col min="9" max="9" width="29.375" customWidth="1"/>
-    <col min="10" max="10" width="41.25" style="5" customWidth="1"/>
-    <col min="11" max="11" width="11.75" style="4" customWidth="1"/>
-    <col min="12" max="12" width="20.4416666666667" style="4" customWidth="1"/>
-    <col min="13" max="13" width="7.93333333333333" style="4" customWidth="1"/>
+    <col min="10" max="10" width="41.25" style="4" customWidth="1"/>
+    <col min="11" max="11" width="11.75" style="3" customWidth="1"/>
+    <col min="12" max="12" width="20.4416666666667" style="3" customWidth="1"/>
+    <col min="13" max="13" width="7.93333333333333" style="3" customWidth="1"/>
     <col min="14" max="14" width="11.325" customWidth="1"/>
     <col min="15" max="15" width="8.96666666666667" customWidth="1"/>
     <col min="16" max="16" width="93.375" customWidth="1"/>
     <col min="17" max="17" width="10.625" customWidth="1"/>
-    <col min="18" max="18" width="23.75" style="6" customWidth="1"/>
+    <col min="18" max="18" width="23.75" style="5" customWidth="1"/>
     <col min="19" max="19" width="60.875" customWidth="1"/>
     <col min="20" max="21" width="11.5"/>
   </cols>
@@ -1920,704 +1903,704 @@
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7" t="s">
+      <c r="C1" s="6"/>
+      <c r="D1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7" t="s">
+      <c r="E1" s="6"/>
+      <c r="F1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7" t="s">
+      <c r="H1" s="6"/>
+      <c r="I1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="28" t="s">
+      <c r="J1" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7" t="s">
+      <c r="K1" s="6"/>
+      <c r="L1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="M1" s="7"/>
-      <c r="N1" s="29" t="s">
+      <c r="M1" s="6"/>
+      <c r="N1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="O1" s="29" t="s">
+      <c r="O1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="29" t="s">
+      <c r="P1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="Q1" s="49" t="s">
+      <c r="Q1" s="42" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="2" s="3" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7" t="s">
+      <c r="C2" s="6"/>
+      <c r="D2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="7"/>
-      <c r="F2" s="10" t="s">
+      <c r="E2" s="6"/>
+      <c r="F2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="30" t="s">
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="10"/>
-      <c r="L2" s="31" t="s">
+      <c r="K2" s="8"/>
+      <c r="L2" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="M2" s="7"/>
-      <c r="N2" s="29" t="s">
+      <c r="M2" s="6"/>
+      <c r="N2" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="29" t="s">
+      <c r="O2" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="P2" s="31" t="s">
+      <c r="P2" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="Q2" s="50" t="s">
+      <c r="Q2" s="42" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="3" s="3" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11" t="s">
+      <c r="C3" s="9"/>
+      <c r="D3" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11" t="s">
+      <c r="E3" s="9"/>
+      <c r="F3" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="32" t="s">
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="K3" s="11"/>
-      <c r="L3" s="11" t="s">
+      <c r="K3" s="9"/>
+      <c r="L3" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="M3" s="11"/>
-      <c r="N3" s="29" t="s">
+      <c r="M3" s="9"/>
+      <c r="N3" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="O3" s="29" t="s">
+      <c r="O3" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="P3" s="29" t="s">
+      <c r="P3" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="Q3" s="51" t="s">
+      <c r="Q3" s="13" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="4" s="3" customFormat="1" ht="16.5" spans="2:17">
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="28"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="8"/>
-      <c r="O4" s="8"/>
-      <c r="P4" s="8"/>
-      <c r="Q4" s="8"/>
-    </row>
-    <row r="5" s="4" customFormat="1" ht="16.5" spans="1:18">
-      <c r="A5" s="13">
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+    </row>
+    <row r="5" s="3" customFormat="1" ht="16.5" spans="1:18">
+      <c r="A5" s="11">
         <v>30010001</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="12">
         <v>100100</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="11">
         <v>31001</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="F5" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13" t="s">
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="J5" s="33"/>
-      <c r="K5" s="15" t="s">
+      <c r="J5" s="29"/>
+      <c r="K5" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="L5" s="13" t="s">
+      <c r="L5" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="M5" s="13" t="s">
+      <c r="M5" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="N5" s="13"/>
-      <c r="O5" s="13"/>
-      <c r="P5" s="34" t="s">
+      <c r="N5" s="11"/>
+      <c r="O5" s="11"/>
+      <c r="P5" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="Q5" s="52" t="s">
+      <c r="Q5" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="R5" s="53"/>
-    </row>
-    <row r="6" s="4" customFormat="1" ht="16.5" spans="1:18">
-      <c r="A6" s="13">
+      <c r="R5" s="44"/>
+    </row>
+    <row r="6" s="3" customFormat="1" ht="16.5" spans="1:18">
+      <c r="A6" s="11">
         <v>30010002</v>
       </c>
-      <c r="B6" s="14">
+      <c r="B6" s="12">
         <v>100100</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="11">
         <v>31002</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="F6" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13" t="s">
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="33"/>
-      <c r="K6" s="15" t="s">
+      <c r="J6" s="29"/>
+      <c r="K6" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="L6" s="13" t="s">
+      <c r="L6" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="M6" s="13" t="s">
+      <c r="M6" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="N6" s="13"/>
-      <c r="O6" s="13"/>
-      <c r="P6" s="34" t="s">
+      <c r="N6" s="11"/>
+      <c r="O6" s="11"/>
+      <c r="P6" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="Q6" s="52" t="s">
+      <c r="Q6" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="R6" s="53"/>
-    </row>
-    <row r="7" s="4" customFormat="1" ht="16.5" spans="1:18">
-      <c r="A7" s="13">
+      <c r="R6" s="44"/>
+    </row>
+    <row r="7" s="3" customFormat="1" ht="16.5" spans="1:18">
+      <c r="A7" s="11">
         <v>30010003</v>
       </c>
-      <c r="B7" s="14">
+      <c r="B7" s="12">
         <v>100100</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="11">
         <v>31003</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="F7" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13" t="s">
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="J7" s="33"/>
-      <c r="K7" s="15" t="s">
+      <c r="J7" s="29"/>
+      <c r="K7" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="L7" s="13" t="s">
+      <c r="L7" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="M7" s="13" t="s">
+      <c r="M7" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="N7" s="13"/>
-      <c r="O7" s="13"/>
-      <c r="P7" s="34" t="s">
+      <c r="N7" s="11"/>
+      <c r="O7" s="11"/>
+      <c r="P7" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="Q7" s="52" t="s">
+      <c r="Q7" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="R7" s="53"/>
-    </row>
-    <row r="8" s="4" customFormat="1" ht="15" customHeight="1" spans="1:18">
-      <c r="A8" s="13">
+      <c r="R7" s="44"/>
+    </row>
+    <row r="8" s="3" customFormat="1" ht="15" customHeight="1" spans="1:18">
+      <c r="A8" s="11">
         <v>30010004</v>
       </c>
-      <c r="B8" s="14">
+      <c r="B8" s="12">
         <v>100100</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="11">
         <v>31004</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="E8" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="F8" s="13" t="s">
+      <c r="F8" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="13" t="s">
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="J8" s="33"/>
-      <c r="K8" s="15" t="s">
+      <c r="J8" s="29"/>
+      <c r="K8" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="L8" s="13" t="s">
+      <c r="L8" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="M8" s="13" t="s">
+      <c r="M8" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="N8" s="13"/>
-      <c r="O8" s="13"/>
-      <c r="P8" s="34" t="s">
+      <c r="N8" s="11"/>
+      <c r="O8" s="11"/>
+      <c r="P8" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="Q8" s="52" t="s">
+      <c r="Q8" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="R8" s="53"/>
-    </row>
-    <row r="9" s="4" customFormat="1" ht="15" customHeight="1" spans="1:18">
-      <c r="A9" s="15">
+      <c r="R8" s="44"/>
+    </row>
+    <row r="9" s="3" customFormat="1" ht="15" customHeight="1" spans="1:18">
+      <c r="A9" s="6">
         <v>30010005</v>
       </c>
-      <c r="B9" s="16">
+      <c r="B9" s="13">
         <v>100100</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="15">
+      <c r="D9" s="6">
         <v>31101</v>
       </c>
-      <c r="E9" s="15" t="s">
+      <c r="E9" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="F9" s="15" t="s">
+      <c r="F9" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="G9" s="15"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="15" t="s">
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="J9" s="35"/>
-      <c r="K9" s="15" t="s">
+      <c r="J9" s="25"/>
+      <c r="K9" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="L9" s="15" t="s">
+      <c r="L9" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="M9" s="15"/>
-      <c r="N9" s="15" t="s">
+      <c r="M9" s="6"/>
+      <c r="N9" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="O9" s="15"/>
-      <c r="P9" s="36"/>
-      <c r="Q9" s="36"/>
-      <c r="R9" s="53"/>
-    </row>
-    <row r="10" s="4" customFormat="1" ht="16.5" spans="1:18">
-      <c r="A10" s="17">
+      <c r="O9" s="6"/>
+      <c r="P9" s="8"/>
+      <c r="Q9" s="8"/>
+      <c r="R9" s="44"/>
+    </row>
+    <row r="10" s="3" customFormat="1" ht="16.5" spans="1:18">
+      <c r="A10" s="14">
         <v>30010006</v>
       </c>
-      <c r="B10" s="18">
+      <c r="B10" s="15">
         <v>100100</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="17">
+      <c r="D10" s="14">
         <v>31102</v>
       </c>
-      <c r="E10" s="17" t="s">
+      <c r="E10" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="F10" s="17" t="s">
+      <c r="F10" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="17" t="s">
+      <c r="G10" s="14"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="J10" s="37"/>
-      <c r="K10" s="17" t="s">
+      <c r="J10" s="31"/>
+      <c r="K10" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="L10" s="17" t="s">
+      <c r="L10" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="M10" s="17" t="s">
+      <c r="M10" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="N10" s="17" t="s">
+      <c r="N10" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="O10" s="17"/>
-      <c r="P10" s="17"/>
-      <c r="Q10" s="15"/>
-      <c r="R10" s="53"/>
-    </row>
-    <row r="11" s="4" customFormat="1" ht="16.5" spans="1:18">
-      <c r="A11" s="19">
+      <c r="O10" s="14"/>
+      <c r="P10" s="14"/>
+      <c r="Q10" s="6"/>
+      <c r="R10" s="44"/>
+    </row>
+    <row r="11" s="3" customFormat="1" ht="16.5" spans="1:18">
+      <c r="A11" s="16">
         <v>30010007</v>
       </c>
-      <c r="B11" s="20">
+      <c r="B11" s="17">
         <v>100100</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C11" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="21">
+      <c r="D11" s="18">
         <v>31201</v>
       </c>
-      <c r="E11" s="21" t="s">
+      <c r="E11" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="F11" s="19" t="s">
+      <c r="F11" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="G11" s="19">
+      <c r="G11" s="16">
         <v>2001001</v>
       </c>
-      <c r="H11" s="19" t="s">
+      <c r="H11" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="I11" s="19" t="s">
+      <c r="I11" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="J11" s="38">
+      <c r="J11" s="32">
         <v>10010091</v>
       </c>
-      <c r="K11" s="19"/>
-      <c r="L11" s="19"/>
-      <c r="M11" s="19"/>
-      <c r="N11" s="19"/>
-      <c r="O11" s="19"/>
-      <c r="P11" s="19"/>
-      <c r="Q11" s="15"/>
-      <c r="R11" s="53"/>
-    </row>
-    <row r="12" s="4" customFormat="1" ht="16.5" spans="1:18">
-      <c r="A12" s="22">
+      <c r="K11" s="16"/>
+      <c r="L11" s="16"/>
+      <c r="M11" s="16"/>
+      <c r="N11" s="16"/>
+      <c r="O11" s="16"/>
+      <c r="P11" s="16"/>
+      <c r="Q11" s="6"/>
+      <c r="R11" s="44"/>
+    </row>
+    <row r="12" s="3" customFormat="1" ht="16.5" spans="1:18">
+      <c r="A12" s="19">
         <v>30010008</v>
       </c>
-      <c r="B12" s="23">
+      <c r="B12" s="20">
         <v>100100</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="21">
+      <c r="D12" s="18">
         <v>31202</v>
       </c>
-      <c r="E12" s="21" t="s">
+      <c r="E12" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="F12" s="22" t="s">
+      <c r="F12" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="G12" s="22">
+      <c r="G12" s="19">
         <v>2001001</v>
       </c>
-      <c r="H12" s="22" t="s">
+      <c r="H12" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="I12" s="22" t="s">
+      <c r="I12" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="J12" s="39" t="s">
+      <c r="J12" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="K12" s="22"/>
-      <c r="L12" s="22"/>
-      <c r="M12" s="22"/>
-      <c r="N12" s="22"/>
-      <c r="O12" s="22"/>
-      <c r="P12" s="22"/>
-      <c r="Q12" s="15"/>
-      <c r="R12" s="53"/>
-    </row>
-    <row r="13" s="4" customFormat="1" ht="16.5" spans="1:18">
-      <c r="A13" s="24">
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
+      <c r="M12" s="19"/>
+      <c r="N12" s="19"/>
+      <c r="O12" s="19"/>
+      <c r="P12" s="19"/>
+      <c r="Q12" s="6"/>
+      <c r="R12" s="44"/>
+    </row>
+    <row r="13" s="3" customFormat="1" ht="16.5" spans="1:18">
+      <c r="A13" s="21">
         <v>30010009</v>
       </c>
-      <c r="B13" s="25">
+      <c r="B13" s="22">
         <v>100100</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="21">
+      <c r="D13" s="18">
         <v>31203</v>
       </c>
-      <c r="E13" s="21" t="s">
+      <c r="E13" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="F13" s="24" t="s">
+      <c r="F13" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="G13" s="24">
+      <c r="G13" s="21">
         <v>2001001</v>
       </c>
-      <c r="H13" s="24" t="s">
+      <c r="H13" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="I13" s="24" t="s">
+      <c r="I13" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="J13" s="40" t="s">
+      <c r="J13" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="K13" s="24"/>
-      <c r="L13" s="24"/>
-      <c r="M13" s="24"/>
-      <c r="N13" s="24"/>
-      <c r="O13" s="24"/>
-      <c r="P13" s="24"/>
-      <c r="Q13" s="15"/>
-      <c r="R13" s="53"/>
-    </row>
-    <row r="14" s="4" customFormat="1" ht="16.5" spans="1:18">
-      <c r="A14" s="21">
+      <c r="K13" s="21"/>
+      <c r="L13" s="21"/>
+      <c r="M13" s="21"/>
+      <c r="N13" s="21"/>
+      <c r="O13" s="21"/>
+      <c r="P13" s="21"/>
+      <c r="Q13" s="6"/>
+      <c r="R13" s="44"/>
+    </row>
+    <row r="14" s="3" customFormat="1" ht="16.5" spans="1:18">
+      <c r="A14" s="18">
         <v>30010010</v>
       </c>
-      <c r="B14" s="26">
+      <c r="B14" s="23">
         <v>100100</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="C14" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D14" s="27">
+      <c r="D14" s="24">
         <v>31301</v>
       </c>
-      <c r="E14" s="27" t="s">
+      <c r="E14" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="F14" s="21" t="s">
+      <c r="F14" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="G14" s="21"/>
-      <c r="H14" s="21"/>
-      <c r="I14" s="21" t="s">
+      <c r="G14" s="18"/>
+      <c r="H14" s="18"/>
+      <c r="I14" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="J14" s="41"/>
-      <c r="K14" s="21" t="s">
+      <c r="J14" s="35"/>
+      <c r="K14" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="L14" s="21" t="s">
+      <c r="L14" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="M14" s="21"/>
-      <c r="N14" s="21"/>
-      <c r="O14" s="21"/>
-      <c r="P14" s="42" t="s">
+      <c r="M14" s="18"/>
+      <c r="N14" s="18"/>
+      <c r="O14" s="18"/>
+      <c r="P14" s="36" t="s">
         <v>67</v>
       </c>
-      <c r="Q14" s="54" t="s">
+      <c r="Q14" s="45" t="s">
         <v>68</v>
       </c>
-      <c r="R14" s="36" t="s">
+      <c r="R14" s="8" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="15" s="4" customFormat="1" ht="16.5" spans="1:18">
-      <c r="A15" s="24">
+    <row r="15" s="3" customFormat="1" ht="16.5" spans="1:18">
+      <c r="A15" s="21">
         <v>30010011</v>
       </c>
-      <c r="B15" s="25">
+      <c r="B15" s="22">
         <v>100100</v>
       </c>
-      <c r="C15" s="14" t="s">
+      <c r="C15" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D15" s="27">
+      <c r="D15" s="24">
         <v>31302</v>
       </c>
-      <c r="E15" s="27" t="s">
+      <c r="E15" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="F15" s="24" t="s">
+      <c r="F15" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="G15" s="24"/>
-      <c r="H15" s="24"/>
-      <c r="I15" s="24" t="s">
+      <c r="G15" s="21"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="J15" s="40"/>
-      <c r="K15" s="24" t="s">
+      <c r="J15" s="34"/>
+      <c r="K15" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="L15" s="24" t="s">
+      <c r="L15" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="M15" s="24"/>
-      <c r="N15" s="24"/>
-      <c r="O15" s="24"/>
-      <c r="P15" s="24"/>
-      <c r="Q15" s="15"/>
-      <c r="R15" s="53"/>
-    </row>
-    <row r="16" s="4" customFormat="1" ht="16.5" spans="1:18">
-      <c r="A16" s="24">
+      <c r="M15" s="21"/>
+      <c r="N15" s="21"/>
+      <c r="O15" s="21"/>
+      <c r="P15" s="21"/>
+      <c r="Q15" s="6"/>
+      <c r="R15" s="44"/>
+    </row>
+    <row r="16" s="3" customFormat="1" ht="16.5" spans="1:18">
+      <c r="A16" s="21">
         <v>30010012</v>
       </c>
-      <c r="B16" s="25">
+      <c r="B16" s="22">
         <v>100100</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="C16" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D16" s="27">
+      <c r="D16" s="24">
         <v>31303</v>
       </c>
-      <c r="E16" s="27" t="s">
+      <c r="E16" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="F16" s="24" t="s">
+      <c r="F16" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="G16" s="24">
+      <c r="G16" s="21">
         <v>2001001</v>
       </c>
-      <c r="H16" s="24" t="s">
+      <c r="H16" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="I16" s="24" t="s">
+      <c r="I16" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="J16" s="40" t="s">
+      <c r="J16" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="K16" s="24"/>
-      <c r="L16" s="24"/>
-      <c r="M16" s="24"/>
-      <c r="N16" s="24"/>
-      <c r="O16" s="24"/>
-      <c r="P16" s="24"/>
-      <c r="Q16" s="15"/>
-      <c r="R16" s="53"/>
-    </row>
-    <row r="17" s="4" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A17" s="15">
+      <c r="K16" s="21"/>
+      <c r="L16" s="21"/>
+      <c r="M16" s="21"/>
+      <c r="N16" s="21"/>
+      <c r="O16" s="21"/>
+      <c r="P16" s="21"/>
+      <c r="Q16" s="6"/>
+      <c r="R16" s="44"/>
+    </row>
+    <row r="17" s="3" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A17" s="6">
         <v>30070001</v>
       </c>
-      <c r="B17" s="4">
+      <c r="B17" s="3">
         <v>100700</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D17" s="19">
+      <c r="D17" s="16">
         <v>34001</v>
       </c>
-      <c r="E17" s="19" t="s">
+      <c r="E17" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="F17" s="19" t="s">
+      <c r="F17" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="G17" s="16">
+      <c r="G17" s="13">
         <v>2007001</v>
       </c>
-      <c r="H17" s="15" t="s">
+      <c r="H17" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="I17" s="4" t="s">
+      <c r="I17" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="J17" s="43"/>
-    </row>
-    <row r="18" s="4" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A18" s="15">
+      <c r="J17" s="37"/>
+    </row>
+    <row r="18" s="3" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A18" s="6">
         <v>30070002</v>
       </c>
-      <c r="B18" s="4">
+      <c r="B18" s="3">
         <v>100700</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="16">
         <v>34002</v>
       </c>
-      <c r="E18" s="19" t="s">
+      <c r="E18" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="F18" s="19" t="s">
+      <c r="F18" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="G18" s="16">
+      <c r="G18" s="13">
         <v>2007001</v>
       </c>
-      <c r="H18" s="15" t="s">
+      <c r="H18" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="I18" s="4" t="s">
+      <c r="I18" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="J18" s="43"/>
+      <c r="J18" s="37"/>
     </row>
     <row r="19" spans="12:18">
       <c r="L19"/>
@@ -2630,145 +2613,111 @@
       <c r="R20"/>
     </row>
     <row r="21" spans="12:18">
-      <c r="L21" s="6"/>
+      <c r="L21" s="5"/>
       <c r="M21"/>
       <c r="R21"/>
     </row>
     <row r="22" ht="16.5" spans="10:18">
-      <c r="J22" s="44"/>
-      <c r="K22" s="45"/>
-      <c r="L22" s="6"/>
+      <c r="J22" s="38"/>
+      <c r="K22" s="39"/>
+      <c r="L22" s="5"/>
       <c r="M22"/>
       <c r="R22"/>
     </row>
     <row r="23" ht="16.5" spans="10:18">
-      <c r="J23" s="44"/>
-      <c r="K23" s="45"/>
-      <c r="L23" s="6"/>
+      <c r="J23" s="38"/>
+      <c r="K23" s="39"/>
+      <c r="L23" s="5"/>
       <c r="M23"/>
-      <c r="N23"/>
-      <c r="O23"/>
       <c r="R23"/>
     </row>
     <row r="24" ht="16.5" spans="10:18">
-      <c r="J24" s="44"/>
-      <c r="K24" s="45"/>
-      <c r="L24" s="6"/>
+      <c r="J24" s="38"/>
+      <c r="K24" s="39"/>
+      <c r="L24" s="5"/>
       <c r="M24"/>
-      <c r="N24"/>
-      <c r="O24"/>
-      <c r="P24"/>
-      <c r="Q24"/>
       <c r="R24"/>
     </row>
     <row r="25" ht="16.5" spans="10:18">
-      <c r="J25" s="44"/>
-      <c r="K25" s="45"/>
-      <c r="L25" s="6"/>
+      <c r="J25" s="38"/>
+      <c r="K25" s="39"/>
+      <c r="L25" s="5"/>
       <c r="M25"/>
-      <c r="N25"/>
-      <c r="O25"/>
-      <c r="P25"/>
-      <c r="Q25"/>
       <c r="R25"/>
     </row>
     <row r="26" ht="16.5" spans="10:18">
-      <c r="J26" s="44"/>
-      <c r="K26" s="46"/>
+      <c r="J26" s="38"/>
+      <c r="K26" s="40"/>
       <c r="L26" s="2"/>
       <c r="M26"/>
-      <c r="N26"/>
-      <c r="O26"/>
-      <c r="P26"/>
-      <c r="Q26"/>
       <c r="R26"/>
     </row>
     <row r="27" ht="16.5" spans="10:18">
-      <c r="J27" s="44"/>
-      <c r="K27" s="46"/>
+      <c r="J27" s="38"/>
+      <c r="K27" s="40"/>
       <c r="L27" s="2"/>
       <c r="M27"/>
-      <c r="N27"/>
-      <c r="O27"/>
-      <c r="P27"/>
-      <c r="Q27"/>
       <c r="R27"/>
     </row>
     <row r="28" ht="16.5" spans="10:18">
-      <c r="J28" s="44"/>
-      <c r="K28" s="47"/>
-      <c r="L28" s="48"/>
+      <c r="J28" s="38"/>
+      <c r="K28" s="41"/>
+      <c r="L28" s="4"/>
       <c r="M28"/>
-      <c r="N28"/>
-      <c r="O28"/>
-      <c r="P28"/>
-      <c r="Q28"/>
       <c r="R28"/>
     </row>
     <row r="29" ht="16.5" spans="10:18">
-      <c r="J29" s="44"/>
-      <c r="K29" s="47"/>
-      <c r="L29" s="48"/>
+      <c r="J29" s="38"/>
+      <c r="K29" s="41"/>
+      <c r="L29" s="4"/>
       <c r="M29"/>
-      <c r="N29"/>
-      <c r="O29"/>
-      <c r="P29"/>
-      <c r="Q29"/>
       <c r="R29"/>
     </row>
     <row r="30" ht="16.5" spans="10:18">
-      <c r="J30" s="44"/>
-      <c r="K30" s="47"/>
-      <c r="L30" s="48"/>
+      <c r="J30" s="38"/>
+      <c r="K30" s="41"/>
+      <c r="L30" s="4"/>
       <c r="M30"/>
-      <c r="N30"/>
-      <c r="O30"/>
-      <c r="P30"/>
-      <c r="Q30"/>
       <c r="R30"/>
     </row>
     <row r="31" ht="16.5" spans="10:18">
-      <c r="J31" s="44"/>
-      <c r="K31" s="47"/>
-      <c r="L31" s="48"/>
+      <c r="J31" s="38"/>
+      <c r="K31" s="41"/>
+      <c r="L31" s="4"/>
       <c r="M31"/>
-      <c r="N31"/>
-      <c r="O31"/>
-      <c r="P31"/>
-      <c r="Q31"/>
       <c r="R31"/>
     </row>
     <row r="32" ht="16.5" spans="10:18">
-      <c r="J32" s="44"/>
-      <c r="K32" s="47"/>
+      <c r="J32" s="38"/>
+      <c r="K32" s="41"/>
       <c r="L32"/>
       <c r="M32"/>
       <c r="R32"/>
     </row>
     <row r="33" ht="16.5" spans="10:18">
-      <c r="J33" s="44"/>
-      <c r="K33" s="47"/>
+      <c r="J33" s="38"/>
+      <c r="K33" s="41"/>
       <c r="L33"/>
       <c r="M33"/>
       <c r="R33"/>
     </row>
     <row r="34" ht="16.5" spans="10:18">
-      <c r="J34" s="44"/>
-      <c r="K34" s="47"/>
+      <c r="J34" s="38"/>
+      <c r="K34" s="41"/>
       <c r="L34"/>
       <c r="M34"/>
       <c r="R34"/>
     </row>
     <row r="35" ht="16.5" spans="10:18">
-      <c r="J35" s="44"/>
-      <c r="K35" s="47"/>
+      <c r="J35" s="38"/>
+      <c r="K35" s="41"/>
       <c r="L35"/>
       <c r="M35"/>
       <c r="R35"/>
     </row>
     <row r="36" ht="16.5" spans="10:18">
-      <c r="J36" s="44"/>
-      <c r="K36" s="47"/>
+      <c r="J36" s="38"/>
+      <c r="K36" s="41"/>
       <c r="L36"/>
       <c r="M36"/>
       <c r="R36"/>

--- a/slots/resources/sample/SpecialAuxiliary.xlsx
+++ b/slots/resources/sample/SpecialAuxiliary.xlsx
@@ -31,9 +31,9 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>vidisJW</author>
+    <author>Administrator</author>
     <author>C</author>
     <author/>
-    <author>Administrator</author>
   </authors>
   <commentList>
     <comment ref="D1" authorId="0">
@@ -90,6 +90,28 @@
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+修改ID_抽取权重|修改ID_抽取权重|……</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="2">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
           <t>C:</t>
         </r>
         <r>
@@ -103,7 +125,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="0">
+    <comment ref="M1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -125,7 +147,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="2">
+    <comment ref="O1" authorId="3">
       <text>
         <r>
           <rPr>
@@ -140,7 +162,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O1" authorId="2">
+    <comment ref="P1" authorId="3">
       <text>
         <r>
           <rPr>
@@ -169,7 +191,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P1" authorId="2">
+    <comment ref="Q1" authorId="3">
       <text>
         <r>
           <rPr>
@@ -193,7 +215,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q1" authorId="3">
+    <comment ref="R1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -219,12 +241,34 @@
         </r>
       </text>
     </comment>
+    <comment ref="J2" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+权重类的格式相同用此格式</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="178">
   <si>
     <t>小游戏模式ID</t>
   </si>
@@ -244,6 +288,9 @@
     <t>描述</t>
   </si>
   <si>
+    <t>修改图案策略组，多个修改中按概率抽取1个修改</t>
+  </si>
+  <si>
     <t>修改图案策略，改完后再进行中奖判断</t>
   </si>
   <si>
@@ -256,7 +303,7 @@
     <t>奖励类型B</t>
   </si>
   <si>
-    <t>计算类型&amp;倍数，中奖权重，最大出现次数，根据配置额外增加</t>
+    <t>倍数，中奖权重，最大出现次数，根据配置额外增加</t>
   </si>
   <si>
     <t>赋予值类型</t>
@@ -295,6 +342,9 @@
     <t>rollerMode</t>
   </si>
   <si>
+    <t>specialGroupGirdID</t>
+  </si>
+  <si>
     <t>specialGirdID</t>
   </si>
   <si>
@@ -461,6 +511,30 @@
   </si>
   <si>
     <t>14_1</t>
+  </si>
+  <si>
+    <t>财神</t>
+  </si>
+  <si>
+    <t>横财神第1行</t>
+  </si>
+  <si>
+    <t>10120051_1|10120052_1|10120053_1|10120054_1|10120055_1|10120056_1</t>
+  </si>
+  <si>
+    <t>横财神第2行</t>
+  </si>
+  <si>
+    <t>横财神第3行</t>
+  </si>
+  <si>
+    <t>正财神第2列</t>
+  </si>
+  <si>
+    <t>财神-第2次</t>
+  </si>
+  <si>
+    <t>财神-第3次</t>
   </si>
   <si>
     <t>typeID</t>
@@ -734,13 +808,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="6">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
-    <numFmt numFmtId="177" formatCode="0.00_ "/>
   </numFmts>
   <fonts count="29">
     <font>
@@ -907,6 +980,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
@@ -914,12 +993,13 @@
     </font>
     <font>
       <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -931,14 +1011,7 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -951,12 +1024,30 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="40">
+  <fills count="42">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -978,12 +1069,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.4"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -996,7 +1081,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.8"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1317,7 +1402,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1341,16 +1426,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1359,98 +1444,101 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1462,87 +1550,100 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="49" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -1876,990 +1977,1521 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U57"/>
+  <dimension ref="A1:V57"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14.125" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="12.2833333333333" customWidth="1"/>
     <col min="5" max="5" width="33.475" customWidth="1"/>
     <col min="6" max="6" width="15.125" customWidth="1"/>
     <col min="7" max="7" width="9.875" customWidth="1"/>
     <col min="8" max="8" width="16.25" customWidth="1"/>
-    <col min="9" max="9" width="29.375" customWidth="1"/>
-    <col min="10" max="10" width="41.25" style="4" customWidth="1"/>
-    <col min="11" max="11" width="11.75" style="3" customWidth="1"/>
-    <col min="12" max="12" width="20.4416666666667" style="3" customWidth="1"/>
-    <col min="13" max="13" width="7.93333333333333" style="3" customWidth="1"/>
-    <col min="14" max="14" width="11.325" customWidth="1"/>
-    <col min="15" max="15" width="8.96666666666667" customWidth="1"/>
-    <col min="16" max="16" width="93.375" customWidth="1"/>
-    <col min="17" max="17" width="10.625" customWidth="1"/>
-    <col min="18" max="18" width="23.75" style="5" customWidth="1"/>
-    <col min="19" max="19" width="60.875" customWidth="1"/>
-    <col min="20" max="21" width="11.5"/>
+    <col min="9" max="10" width="29.375" customWidth="1"/>
+    <col min="11" max="11" width="41.25" style="7" customWidth="1"/>
+    <col min="12" max="12" width="11.75" style="3" customWidth="1"/>
+    <col min="13" max="13" width="20.4416666666667" style="3" customWidth="1"/>
+    <col min="14" max="14" width="7.93333333333333" style="3" customWidth="1"/>
+    <col min="15" max="15" width="11.325" customWidth="1"/>
+    <col min="16" max="16" width="8.96666666666667" customWidth="1"/>
+    <col min="17" max="17" width="93.375" customWidth="1"/>
+    <col min="18" max="18" width="10.625" customWidth="1"/>
+    <col min="19" max="19" width="23.75" style="8" customWidth="1"/>
+    <col min="20" max="20" width="60.875" customWidth="1"/>
+    <col min="21" max="22" width="11.5"/>
   </cols>
   <sheetData>
-    <row r="1" s="3" customFormat="1" ht="16.5" spans="1:17">
+    <row r="1" s="3" customFormat="1" ht="16.5" spans="1:18">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6" t="s">
+      <c r="C1" s="9"/>
+      <c r="D1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6" t="s">
+      <c r="E1" s="9"/>
+      <c r="F1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6" t="s">
+      <c r="H1" s="9"/>
+      <c r="I1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="25" t="s">
+      <c r="J1" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6" t="s">
+      <c r="K1" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="M1" s="6"/>
-      <c r="N1" s="8" t="s">
+      <c r="L1" s="9"/>
+      <c r="M1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="N1" s="9"/>
+      <c r="O1" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="8" t="s">
+      <c r="P1" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="Q1" s="42" t="s">
+      <c r="Q1" s="11" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" s="3" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A2" s="7" t="s">
+      <c r="R1" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="6"/>
-      <c r="F2" s="8" t="s">
+    </row>
+    <row r="2" s="3" customFormat="1" ht="16.5" spans="1:18">
+      <c r="A2" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="26" t="s">
+      <c r="B2" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="9"/>
+      <c r="F2" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="8"/>
-      <c r="L2" s="27" t="s">
+      <c r="G2" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="M2" s="6"/>
-      <c r="N2" s="8" t="s">
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="8" t="s">
+      <c r="L2" s="11"/>
+      <c r="M2" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="9"/>
+      <c r="O2" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="P2" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q2" s="42" t="s">
+      <c r="P2" s="11" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" s="3" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A3" s="7" t="s">
+      <c r="Q2" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="R2" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="9" t="s">
+    </row>
+    <row r="3" s="3" customFormat="1" ht="16.5" spans="1:18">
+      <c r="A3" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9" t="s">
+      <c r="B3" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9" t="s">
+      <c r="C3" s="12"/>
+      <c r="D3" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="E3" s="12"/>
+      <c r="F3" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="28" t="s">
+      <c r="G3" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9" t="s">
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="M3" s="9"/>
-      <c r="N3" s="8" t="s">
+      <c r="K3" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="O3" s="8" t="s">
+      <c r="L3" s="12"/>
+      <c r="M3" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="P3" s="8" t="s">
+      <c r="N3" s="12"/>
+      <c r="O3" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="Q3" s="13" t="s">
+      <c r="P3" s="11" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="4" s="3" customFormat="1" ht="16.5" spans="2:17">
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="6"/>
-    </row>
-    <row r="5" s="3" customFormat="1" ht="16.5" spans="1:18">
-      <c r="A5" s="11">
+      <c r="Q3" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="R3" s="16" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" s="3" customFormat="1" ht="16.5" spans="2:18">
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="37"/>
+      <c r="K4" s="32"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="9"/>
+      <c r="P4" s="9"/>
+      <c r="Q4" s="9"/>
+      <c r="R4" s="9"/>
+    </row>
+    <row r="5" s="3" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A5" s="14">
         <v>30010001</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="15">
         <v>100100</v>
       </c>
-      <c r="C5" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" s="11">
+      <c r="C5" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" s="14">
         <v>31001</v>
       </c>
-      <c r="E5" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="F5" s="11" t="s">
+      <c r="E5" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="J5" s="14"/>
+      <c r="K5" s="38"/>
+      <c r="L5" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="M5" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="N5" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="O5" s="14"/>
+      <c r="P5" s="14"/>
+      <c r="Q5" s="49" t="s">
+        <v>38</v>
+      </c>
+      <c r="R5" s="50" t="s">
+        <v>39</v>
+      </c>
+      <c r="S5" s="51"/>
+    </row>
+    <row r="6" s="3" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A6" s="14">
+        <v>30010002</v>
+      </c>
+      <c r="B6" s="15">
+        <v>100100</v>
+      </c>
+      <c r="C6" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="J5" s="29"/>
-      <c r="K5" s="6" t="s">
+      <c r="D6" s="14">
+        <v>31002</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="L5" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="M5" s="11" t="s">
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="J6" s="14"/>
+      <c r="K6" s="38"/>
+      <c r="L6" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="N5" s="11"/>
-      <c r="O5" s="11"/>
-      <c r="P5" s="30" t="s">
+      <c r="M6" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="Q5" s="43" t="s">
+      <c r="N6" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="R5" s="44"/>
-    </row>
-    <row r="6" s="3" customFormat="1" ht="16.5" spans="1:18">
-      <c r="A6" s="11">
-        <v>30010002</v>
-      </c>
-      <c r="B6" s="12">
+      <c r="O6" s="14"/>
+      <c r="P6" s="14"/>
+      <c r="Q6" s="49" t="s">
+        <v>42</v>
+      </c>
+      <c r="R6" s="50" t="s">
+        <v>39</v>
+      </c>
+      <c r="S6" s="51"/>
+    </row>
+    <row r="7" s="3" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A7" s="14">
+        <v>30010003</v>
+      </c>
+      <c r="B7" s="15">
         <v>100100</v>
       </c>
-      <c r="C6" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" s="11">
-        <v>31002</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="F6" s="11" t="s">
+      <c r="C7" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11" t="s">
+      <c r="D7" s="14">
+        <v>31003</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" s="14"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="J7" s="14"/>
+      <c r="K7" s="38"/>
+      <c r="L7" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="M7" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="N7" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="O7" s="14"/>
+      <c r="P7" s="14"/>
+      <c r="Q7" s="49" t="s">
+        <v>45</v>
+      </c>
+      <c r="R7" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="29"/>
-      <c r="K6" s="6" t="s">
+      <c r="S7" s="51"/>
+    </row>
+    <row r="8" s="3" customFormat="1" ht="15" customHeight="1" spans="1:19">
+      <c r="A8" s="14">
+        <v>30010004</v>
+      </c>
+      <c r="B8" s="15">
+        <v>100100</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="14">
+        <v>31004</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="L6" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="M6" s="11" t="s">
+      <c r="G8" s="14"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="J8" s="14"/>
+      <c r="K8" s="38"/>
+      <c r="L8" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="N6" s="11"/>
-      <c r="O6" s="11"/>
-      <c r="P6" s="30" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q6" s="43" t="s">
+      <c r="M8" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="N8" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="R6" s="44"/>
-    </row>
-    <row r="7" s="3" customFormat="1" ht="16.5" spans="1:18">
-      <c r="A7" s="11">
-        <v>30010003</v>
-      </c>
-      <c r="B7" s="12">
+      <c r="O8" s="14"/>
+      <c r="P8" s="14"/>
+      <c r="Q8" s="49" t="s">
+        <v>48</v>
+      </c>
+      <c r="R8" s="50" t="s">
+        <v>39</v>
+      </c>
+      <c r="S8" s="51"/>
+    </row>
+    <row r="9" s="3" customFormat="1" ht="15" customHeight="1" spans="1:19">
+      <c r="A9" s="9">
+        <v>30010005</v>
+      </c>
+      <c r="B9" s="16">
         <v>100100</v>
       </c>
-      <c r="C7" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="11">
-        <v>31003</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="F7" s="11" t="s">
+      <c r="C9" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="J7" s="29"/>
-      <c r="K7" s="6" t="s">
+      <c r="D9" s="9">
+        <v>31101</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="F9" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="L7" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="M7" s="11" t="s">
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="J9" s="9"/>
+      <c r="K9" s="32"/>
+      <c r="L9" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="N7" s="11"/>
-      <c r="O7" s="11"/>
-      <c r="P7" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q7" s="43" t="s">
+      <c r="M9" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="N9" s="9"/>
+      <c r="O9" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="P9" s="9"/>
+      <c r="Q9" s="11"/>
+      <c r="R9" s="11"/>
+      <c r="S9" s="51"/>
+    </row>
+    <row r="10" s="3" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A10" s="17">
+        <v>30010006</v>
+      </c>
+      <c r="B10" s="18">
+        <v>100100</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" s="17">
+        <v>31102</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10" s="17"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="J10" s="17"/>
+      <c r="K10" s="39"/>
+      <c r="L10" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="M10" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="N10" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="R7" s="44"/>
-    </row>
-    <row r="8" s="3" customFormat="1" ht="15" customHeight="1" spans="1:18">
-      <c r="A8" s="11">
-        <v>30010004</v>
-      </c>
-      <c r="B8" s="12">
+      <c r="O10" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="P10" s="17"/>
+      <c r="Q10" s="17"/>
+      <c r="R10" s="9"/>
+      <c r="S10" s="51"/>
+    </row>
+    <row r="11" s="3" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A11" s="19">
+        <v>30010007</v>
+      </c>
+      <c r="B11" s="20">
         <v>100100</v>
       </c>
-      <c r="C8" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" s="11">
-        <v>31004</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="F8" s="11" t="s">
+      <c r="C11" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="J8" s="29"/>
-      <c r="K8" s="6" t="s">
+      <c r="D11" s="21">
+        <v>31201</v>
+      </c>
+      <c r="E11" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="G11" s="19">
+        <v>2001001</v>
+      </c>
+      <c r="H11" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="I11" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="J11" s="19"/>
+      <c r="K11" s="40">
+        <v>10010091</v>
+      </c>
+      <c r="L11" s="19"/>
+      <c r="M11" s="19"/>
+      <c r="N11" s="19"/>
+      <c r="O11" s="19"/>
+      <c r="P11" s="19"/>
+      <c r="Q11" s="19"/>
+      <c r="R11" s="9"/>
+      <c r="S11" s="51"/>
+    </row>
+    <row r="12" s="3" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A12" s="22">
+        <v>30010008</v>
+      </c>
+      <c r="B12" s="23">
+        <v>100100</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="21">
+        <v>31202</v>
+      </c>
+      <c r="E12" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="F12" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="G12" s="22">
+        <v>2001001</v>
+      </c>
+      <c r="H12" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="I12" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="J12" s="22"/>
+      <c r="K12" s="41" t="s">
+        <v>62</v>
+      </c>
+      <c r="L12" s="22"/>
+      <c r="M12" s="22"/>
+      <c r="N12" s="22"/>
+      <c r="O12" s="22"/>
+      <c r="P12" s="22"/>
+      <c r="Q12" s="22"/>
+      <c r="R12" s="9"/>
+      <c r="S12" s="51"/>
+    </row>
+    <row r="13" s="3" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A13" s="24">
+        <v>30010009</v>
+      </c>
+      <c r="B13" s="25">
+        <v>100100</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" s="21">
+        <v>31203</v>
+      </c>
+      <c r="E13" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="F13" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="G13" s="24">
+        <v>2001001</v>
+      </c>
+      <c r="H13" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="I13" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="J13" s="24"/>
+      <c r="K13" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="L13" s="24"/>
+      <c r="M13" s="24"/>
+      <c r="N13" s="24"/>
+      <c r="O13" s="24"/>
+      <c r="P13" s="24"/>
+      <c r="Q13" s="24"/>
+      <c r="R13" s="9"/>
+      <c r="S13" s="51"/>
+    </row>
+    <row r="14" s="3" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A14" s="21">
+        <v>30010010</v>
+      </c>
+      <c r="B14" s="26">
+        <v>100100</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" s="27">
+        <v>31301</v>
+      </c>
+      <c r="E14" s="27" t="s">
+        <v>66</v>
+      </c>
+      <c r="F14" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="L8" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="M8" s="11" t="s">
+      <c r="G14" s="21"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="J14" s="21"/>
+      <c r="K14" s="43"/>
+      <c r="L14" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="N8" s="11"/>
-      <c r="O8" s="11"/>
-      <c r="P8" s="30" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q8" s="43" t="s">
-        <v>37</v>
-      </c>
-      <c r="R8" s="44"/>
-    </row>
-    <row r="9" s="3" customFormat="1" ht="15" customHeight="1" spans="1:18">
-      <c r="A9" s="6">
-        <v>30010005</v>
-      </c>
-      <c r="B9" s="13">
+      <c r="M14" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="N14" s="21"/>
+      <c r="O14" s="21"/>
+      <c r="P14" s="21"/>
+      <c r="Q14" s="52" t="s">
+        <v>69</v>
+      </c>
+      <c r="R14" s="53" t="s">
+        <v>70</v>
+      </c>
+      <c r="S14" s="11" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15" s="3" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A15" s="24">
+        <v>30010011</v>
+      </c>
+      <c r="B15" s="25">
         <v>100100</v>
       </c>
-      <c r="C9" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" s="6">
-        <v>31101</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="F9" s="6" t="s">
+      <c r="C15" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="J9" s="25"/>
-      <c r="K9" s="6" t="s">
+      <c r="D15" s="27">
+        <v>31302</v>
+      </c>
+      <c r="E15" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="F15" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="L9" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="M9" s="6"/>
-      <c r="N9" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="O9" s="6"/>
-      <c r="P9" s="8"/>
-      <c r="Q9" s="8"/>
-      <c r="R9" s="44"/>
-    </row>
-    <row r="10" s="3" customFormat="1" ht="16.5" spans="1:18">
-      <c r="A10" s="14">
-        <v>30010006</v>
-      </c>
-      <c r="B10" s="15">
+      <c r="G15" s="24"/>
+      <c r="H15" s="24"/>
+      <c r="I15" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="J15" s="24"/>
+      <c r="K15" s="42"/>
+      <c r="L15" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="M15" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="N15" s="24"/>
+      <c r="O15" s="24"/>
+      <c r="P15" s="24"/>
+      <c r="Q15" s="24"/>
+      <c r="R15" s="9"/>
+      <c r="S15" s="51"/>
+    </row>
+    <row r="16" s="3" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A16" s="24">
+        <v>30010012</v>
+      </c>
+      <c r="B16" s="25">
         <v>100100</v>
       </c>
-      <c r="C10" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" s="14">
-        <v>31102</v>
-      </c>
-      <c r="E10" s="14" t="s">
+      <c r="C16" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16" s="27">
+        <v>31303</v>
+      </c>
+      <c r="E16" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="F16" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="F10" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="J10" s="31"/>
-      <c r="K10" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="L10" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="M10" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="N10" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="O10" s="14"/>
-      <c r="P10" s="14"/>
-      <c r="Q10" s="6"/>
-      <c r="R10" s="44"/>
-    </row>
-    <row r="11" s="3" customFormat="1" ht="16.5" spans="1:18">
-      <c r="A11" s="16">
-        <v>30010007</v>
-      </c>
-      <c r="B11" s="17">
-        <v>100100</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" s="18">
-        <v>31201</v>
-      </c>
-      <c r="E11" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="F11" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="G11" s="16">
+      <c r="G16" s="24">
         <v>2001001</v>
       </c>
-      <c r="H11" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="I11" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="J11" s="32">
-        <v>10010091</v>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="16"/>
-      <c r="O11" s="16"/>
-      <c r="P11" s="16"/>
-      <c r="Q11" s="6"/>
-      <c r="R11" s="44"/>
-    </row>
-    <row r="12" s="3" customFormat="1" ht="16.5" spans="1:18">
-      <c r="A12" s="19">
-        <v>30010008</v>
-      </c>
-      <c r="B12" s="20">
-        <v>100100</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" s="18">
-        <v>31202</v>
-      </c>
-      <c r="E12" s="18" t="s">
+      <c r="H16" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F12" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="G12" s="19">
-        <v>2001001</v>
-      </c>
-      <c r="H12" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="I12" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="J12" s="33" t="s">
-        <v>60</v>
-      </c>
-      <c r="K12" s="19"/>
-      <c r="L12" s="19"/>
-      <c r="M12" s="19"/>
-      <c r="N12" s="19"/>
-      <c r="O12" s="19"/>
-      <c r="P12" s="19"/>
-      <c r="Q12" s="6"/>
-      <c r="R12" s="44"/>
-    </row>
-    <row r="13" s="3" customFormat="1" ht="16.5" spans="1:18">
-      <c r="A13" s="21">
-        <v>30010009</v>
-      </c>
-      <c r="B13" s="22">
-        <v>100100</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="D13" s="18">
-        <v>31203</v>
-      </c>
-      <c r="E13" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="F13" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="G13" s="21">
-        <v>2001001</v>
-      </c>
-      <c r="H13" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="I13" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="J13" s="34" t="s">
-        <v>63</v>
-      </c>
-      <c r="K13" s="21"/>
-      <c r="L13" s="21"/>
-      <c r="M13" s="21"/>
-      <c r="N13" s="21"/>
-      <c r="O13" s="21"/>
-      <c r="P13" s="21"/>
-      <c r="Q13" s="6"/>
-      <c r="R13" s="44"/>
-    </row>
-    <row r="14" s="3" customFormat="1" ht="16.5" spans="1:18">
-      <c r="A14" s="18">
-        <v>30010010</v>
-      </c>
-      <c r="B14" s="23">
-        <v>100100</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14" s="24">
-        <v>31301</v>
-      </c>
-      <c r="E14" s="24" t="s">
+      <c r="I16" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="F14" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="G14" s="18"/>
-      <c r="H14" s="18"/>
-      <c r="I14" s="18" t="s">
+      <c r="J16" s="24"/>
+      <c r="K16" s="42" t="s">
         <v>65</v>
       </c>
-      <c r="J14" s="35"/>
-      <c r="K14" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="L14" s="18" t="s">
-        <v>66</v>
-      </c>
-      <c r="M14" s="18"/>
-      <c r="N14" s="18"/>
-      <c r="O14" s="18"/>
-      <c r="P14" s="36" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q14" s="45" t="s">
-        <v>68</v>
-      </c>
-      <c r="R14" s="8" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="15" s="3" customFormat="1" ht="16.5" spans="1:18">
-      <c r="A15" s="21">
-        <v>30010011</v>
-      </c>
-      <c r="B15" s="22">
-        <v>100100</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="D15" s="24">
-        <v>31302</v>
-      </c>
-      <c r="E15" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="F15" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="G15" s="21"/>
-      <c r="H15" s="21"/>
-      <c r="I15" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="J15" s="34"/>
-      <c r="K15" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="L15" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="M15" s="21"/>
-      <c r="N15" s="21"/>
-      <c r="O15" s="21"/>
-      <c r="P15" s="21"/>
-      <c r="Q15" s="6"/>
-      <c r="R15" s="44"/>
-    </row>
-    <row r="16" s="3" customFormat="1" ht="16.5" spans="1:18">
-      <c r="A16" s="21">
-        <v>30010012</v>
-      </c>
-      <c r="B16" s="22">
-        <v>100100</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="D16" s="24">
-        <v>31303</v>
-      </c>
-      <c r="E16" s="24" t="s">
-        <v>72</v>
-      </c>
-      <c r="F16" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="G16" s="21">
-        <v>2001001</v>
-      </c>
-      <c r="H16" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="I16" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="J16" s="34" t="s">
-        <v>63</v>
-      </c>
-      <c r="K16" s="21"/>
-      <c r="L16" s="21"/>
-      <c r="M16" s="21"/>
-      <c r="N16" s="21"/>
-      <c r="O16" s="21"/>
-      <c r="P16" s="21"/>
-      <c r="Q16" s="6"/>
-      <c r="R16" s="44"/>
-    </row>
-    <row r="17" s="3" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A17" s="6">
+      <c r="L16" s="24"/>
+      <c r="M16" s="24"/>
+      <c r="N16" s="24"/>
+      <c r="O16" s="24"/>
+      <c r="P16" s="24"/>
+      <c r="Q16" s="24"/>
+      <c r="R16" s="9"/>
+      <c r="S16" s="51"/>
+    </row>
+    <row r="17" s="3" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A17" s="9">
         <v>30070001</v>
       </c>
       <c r="B17" s="3">
         <v>100700</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D17" s="16">
+        <v>75</v>
+      </c>
+      <c r="D17" s="19">
         <v>34001</v>
       </c>
-      <c r="E17" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="F17" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="G17" s="13">
+      <c r="E17" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="F17" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="G17" s="16">
         <v>2007001</v>
       </c>
-      <c r="H17" s="6" t="s">
-        <v>56</v>
+      <c r="H17" s="9" t="s">
+        <v>58</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="J17" s="37"/>
-    </row>
-    <row r="18" s="3" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A18" s="6">
+        <v>78</v>
+      </c>
+      <c r="K17" s="44"/>
+    </row>
+    <row r="18" s="3" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A18" s="9">
         <v>30070002</v>
       </c>
       <c r="B18" s="3">
         <v>100700</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D18" s="16">
+        <v>75</v>
+      </c>
+      <c r="D18" s="19">
         <v>34002</v>
       </c>
-      <c r="E18" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="F18" s="16" t="s">
+      <c r="E18" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="F18" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="G18" s="16">
+        <v>2007001</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="G18" s="13">
-        <v>2007001</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="J18" s="37"/>
-    </row>
-    <row r="19" spans="12:18">
-      <c r="L19"/>
-      <c r="M19"/>
-      <c r="R19"/>
-    </row>
-    <row r="20" spans="12:18">
-      <c r="L20"/>
-      <c r="M20"/>
-      <c r="R20"/>
-    </row>
-    <row r="21" spans="12:18">
-      <c r="L21" s="5"/>
-      <c r="M21"/>
-      <c r="R21"/>
-    </row>
-    <row r="22" ht="16.5" spans="10:18">
-      <c r="J22" s="38"/>
-      <c r="K22" s="39"/>
-      <c r="L22" s="5"/>
-      <c r="M22"/>
-      <c r="R22"/>
-    </row>
-    <row r="23" ht="16.5" spans="10:18">
-      <c r="J23" s="38"/>
-      <c r="K23" s="39"/>
-      <c r="L23" s="5"/>
-      <c r="M23"/>
-      <c r="R23"/>
-    </row>
-    <row r="24" ht="16.5" spans="10:18">
-      <c r="J24" s="38"/>
-      <c r="K24" s="39"/>
-      <c r="L24" s="5"/>
-      <c r="M24"/>
-      <c r="R24"/>
-    </row>
-    <row r="25" ht="16.5" spans="10:18">
-      <c r="J25" s="38"/>
-      <c r="K25" s="39"/>
-      <c r="L25" s="5"/>
-      <c r="M25"/>
-      <c r="R25"/>
-    </row>
-    <row r="26" ht="16.5" spans="10:18">
-      <c r="J26" s="38"/>
-      <c r="K26" s="40"/>
-      <c r="L26" s="2"/>
-      <c r="M26"/>
-      <c r="R26"/>
-    </row>
-    <row r="27" ht="16.5" spans="10:18">
-      <c r="J27" s="38"/>
-      <c r="K27" s="40"/>
-      <c r="L27" s="2"/>
-      <c r="M27"/>
-      <c r="R27"/>
-    </row>
-    <row r="28" ht="16.5" spans="10:18">
-      <c r="J28" s="38"/>
-      <c r="K28" s="41"/>
-      <c r="L28" s="4"/>
-      <c r="M28"/>
-      <c r="R28"/>
-    </row>
-    <row r="29" ht="16.5" spans="10:18">
-      <c r="J29" s="38"/>
-      <c r="K29" s="41"/>
-      <c r="L29" s="4"/>
-      <c r="M29"/>
-      <c r="R29"/>
-    </row>
-    <row r="30" ht="16.5" spans="10:18">
-      <c r="J30" s="38"/>
-      <c r="K30" s="41"/>
-      <c r="L30" s="4"/>
-      <c r="M30"/>
-      <c r="R30"/>
-    </row>
-    <row r="31" ht="16.5" spans="10:18">
-      <c r="J31" s="38"/>
-      <c r="K31" s="41"/>
-      <c r="L31" s="4"/>
-      <c r="M31"/>
-      <c r="R31"/>
-    </row>
-    <row r="32" ht="16.5" spans="10:18">
-      <c r="J32" s="38"/>
-      <c r="K32" s="41"/>
-      <c r="L32"/>
-      <c r="M32"/>
-      <c r="R32"/>
-    </row>
-    <row r="33" ht="16.5" spans="10:18">
-      <c r="J33" s="38"/>
-      <c r="K33" s="41"/>
-      <c r="L33"/>
-      <c r="M33"/>
-      <c r="R33"/>
-    </row>
-    <row r="34" ht="16.5" spans="10:18">
-      <c r="J34" s="38"/>
-      <c r="K34" s="41"/>
-      <c r="L34"/>
-      <c r="M34"/>
-      <c r="R34"/>
-    </row>
-    <row r="35" ht="16.5" spans="10:18">
-      <c r="J35" s="38"/>
-      <c r="K35" s="41"/>
-      <c r="L35"/>
-      <c r="M35"/>
-      <c r="R35"/>
-    </row>
-    <row r="36" ht="16.5" spans="10:18">
-      <c r="J36" s="38"/>
-      <c r="K36" s="41"/>
-      <c r="L36"/>
-      <c r="M36"/>
-      <c r="R36"/>
-    </row>
-    <row r="37" ht="16.5" spans="18:21">
-      <c r="R37"/>
-      <c r="T37" s="1"/>
+      <c r="K18" s="44"/>
+    </row>
+    <row r="19" s="4" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A19" s="21">
+        <v>30120001</v>
+      </c>
+      <c r="B19" s="4">
+        <v>101200</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D19" s="21">
+        <v>32001</v>
+      </c>
+      <c r="E19" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="F19" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="G19" s="26">
+        <v>2012001</v>
+      </c>
+      <c r="H19" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="I19" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="J19" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="K19" s="45">
+        <v>10120041</v>
+      </c>
+    </row>
+    <row r="20" s="4" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A20" s="21">
+        <v>30120002</v>
+      </c>
+      <c r="B20" s="4">
+        <v>101200</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D20" s="21">
+        <v>32002</v>
+      </c>
+      <c r="E20" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="F20" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="G20" s="26">
+        <v>2012001</v>
+      </c>
+      <c r="H20" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="I20" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="J20" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="K20" s="45">
+        <v>10120042</v>
+      </c>
+    </row>
+    <row r="21" s="4" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A21" s="21">
+        <v>30120003</v>
+      </c>
+      <c r="B21" s="4">
+        <v>101200</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D21" s="21">
+        <v>32003</v>
+      </c>
+      <c r="E21" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="F21" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="G21" s="26">
+        <v>2012001</v>
+      </c>
+      <c r="H21" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="I21" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="J21" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="K21" s="45">
+        <v>10120043</v>
+      </c>
+    </row>
+    <row r="22" s="4" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A22" s="21">
+        <v>30120004</v>
+      </c>
+      <c r="B22" s="4">
+        <v>101200</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D22" s="21">
+        <v>32004</v>
+      </c>
+      <c r="E22" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="F22" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="G22" s="26">
+        <v>2012001</v>
+      </c>
+      <c r="H22" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="I22" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="J22" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="K22" s="45">
+        <v>10120044</v>
+      </c>
+    </row>
+    <row r="23" s="4" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A23" s="21">
+        <v>30120005</v>
+      </c>
+      <c r="B23" s="4">
+        <v>101200</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D23" s="21">
+        <v>32005</v>
+      </c>
+      <c r="E23" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="F23" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="G23" s="26">
+        <v>2012001</v>
+      </c>
+      <c r="H23" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="I23" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="J23" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="K23" s="45">
+        <v>10120045</v>
+      </c>
+    </row>
+    <row r="24" s="4" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A24" s="21">
+        <v>30120006</v>
+      </c>
+      <c r="B24" s="4">
+        <v>101200</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D24" s="21">
+        <v>32006</v>
+      </c>
+      <c r="E24" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="F24" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="G24" s="26">
+        <v>2012001</v>
+      </c>
+      <c r="H24" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="I24" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="J24" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="K24" s="45">
+        <v>10120046</v>
+      </c>
+    </row>
+    <row r="25" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A25" s="28">
+        <v>30120011</v>
+      </c>
+      <c r="B25" s="5">
+        <v>101200</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="D25" s="21">
+        <v>32101</v>
+      </c>
+      <c r="E25" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="F25" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="G25" s="29">
+        <v>2012001</v>
+      </c>
+      <c r="H25" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="I25" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="J25" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="K25" s="46">
+        <v>10120041</v>
+      </c>
+    </row>
+    <row r="26" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A26" s="28">
+        <v>30120012</v>
+      </c>
+      <c r="B26" s="5">
+        <v>101200</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="D26" s="21">
+        <v>32102</v>
+      </c>
+      <c r="E26" s="28" t="s">
+        <v>84</v>
+      </c>
+      <c r="F26" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="G26" s="29">
+        <v>2012001</v>
+      </c>
+      <c r="H26" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="I26" s="28" t="s">
+        <v>84</v>
+      </c>
+      <c r="J26" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="K26" s="46">
+        <v>10120042</v>
+      </c>
+    </row>
+    <row r="27" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A27" s="28">
+        <v>30120013</v>
+      </c>
+      <c r="B27" s="5">
+        <v>101200</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="D27" s="21">
+        <v>32103</v>
+      </c>
+      <c r="E27" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="F27" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="G27" s="29">
+        <v>2012001</v>
+      </c>
+      <c r="H27" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="I27" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="J27" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="K27" s="46">
+        <v>10120043</v>
+      </c>
+    </row>
+    <row r="28" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A28" s="28">
+        <v>30120014</v>
+      </c>
+      <c r="B28" s="5">
+        <v>101200</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="D28" s="21">
+        <v>32104</v>
+      </c>
+      <c r="E28" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="F28" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="G28" s="29">
+        <v>2012001</v>
+      </c>
+      <c r="H28" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="I28" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="J28" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="K28" s="46">
+        <v>10120044</v>
+      </c>
+    </row>
+    <row r="29" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A29" s="28">
+        <v>30120015</v>
+      </c>
+      <c r="B29" s="5">
+        <v>101200</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="D29" s="21">
+        <v>32105</v>
+      </c>
+      <c r="E29" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="F29" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="G29" s="29">
+        <v>2012001</v>
+      </c>
+      <c r="H29" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="I29" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="J29" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="K29" s="46">
+        <v>10120045</v>
+      </c>
+    </row>
+    <row r="30" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A30" s="28">
+        <v>30120016</v>
+      </c>
+      <c r="B30" s="5">
+        <v>101200</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="D30" s="21">
+        <v>32106</v>
+      </c>
+      <c r="E30" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="F30" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="G30" s="29">
+        <v>2012001</v>
+      </c>
+      <c r="H30" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="I30" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="J30" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="K30" s="46">
+        <v>10120046</v>
+      </c>
+    </row>
+    <row r="31" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A31" s="27">
+        <v>30120021</v>
+      </c>
+      <c r="B31" s="6">
+        <v>101200</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="D31" s="27">
+        <v>32201</v>
+      </c>
+      <c r="E31" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="F31" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="G31" s="30">
+        <v>2012001</v>
+      </c>
+      <c r="H31" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="I31" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="J31" s="27"/>
+      <c r="K31" s="47">
+        <v>10120041</v>
+      </c>
+    </row>
+    <row r="32" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A32" s="27">
+        <v>30120022</v>
+      </c>
+      <c r="B32" s="6">
+        <v>101200</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="D32" s="27">
+        <v>32202</v>
+      </c>
+      <c r="E32" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="F32" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="G32" s="30">
+        <v>2012001</v>
+      </c>
+      <c r="H32" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="I32" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="J32" s="27"/>
+      <c r="K32" s="47">
+        <v>10120042</v>
+      </c>
+    </row>
+    <row r="33" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A33" s="27">
+        <v>30120023</v>
+      </c>
+      <c r="B33" s="6">
+        <v>101200</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="D33" s="27">
+        <v>32203</v>
+      </c>
+      <c r="E33" s="27" t="s">
+        <v>85</v>
+      </c>
+      <c r="F33" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="G33" s="30">
+        <v>2012001</v>
+      </c>
+      <c r="H33" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="I33" s="27" t="s">
+        <v>85</v>
+      </c>
+      <c r="J33" s="27"/>
+      <c r="K33" s="47">
+        <v>10120043</v>
+      </c>
+    </row>
+    <row r="34" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A34" s="27">
+        <v>30120024</v>
+      </c>
+      <c r="B34" s="6">
+        <v>101200</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="D34" s="27">
+        <v>32204</v>
+      </c>
+      <c r="E34" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="F34" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="G34" s="30">
+        <v>2012001</v>
+      </c>
+      <c r="H34" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="I34" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="J34" s="27"/>
+      <c r="K34" s="47">
+        <v>10120044</v>
+      </c>
+    </row>
+    <row r="35" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A35" s="27">
+        <v>30120025</v>
+      </c>
+      <c r="B35" s="6">
+        <v>101200</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="D35" s="27">
+        <v>32205</v>
+      </c>
+      <c r="E35" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="F35" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="G35" s="30">
+        <v>2012001</v>
+      </c>
+      <c r="H35" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="I35" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="J35" s="27"/>
+      <c r="K35" s="47">
+        <v>10120045</v>
+      </c>
+    </row>
+    <row r="36" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A36" s="27">
+        <v>30120026</v>
+      </c>
+      <c r="B36" s="6">
+        <v>101200</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="D36" s="27">
+        <v>32206</v>
+      </c>
+      <c r="E36" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="F36" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="G36" s="30">
+        <v>2012001</v>
+      </c>
+      <c r="H36" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="I36" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="J36" s="27"/>
+      <c r="K36" s="47">
+        <v>10120046</v>
+      </c>
+    </row>
+    <row r="37" ht="16.5" spans="19:22">
+      <c r="S37"/>
       <c r="U37" s="1"/>
-    </row>
-    <row r="38" ht="16.5" spans="18:21">
-      <c r="R38"/>
-      <c r="T38" s="1"/>
+      <c r="V37" s="1"/>
+    </row>
+    <row r="38" ht="16.5" spans="19:22">
+      <c r="S38"/>
       <c r="U38" s="1"/>
-    </row>
-    <row r="39" ht="16.5" spans="18:21">
-      <c r="R39"/>
-      <c r="T39" s="1"/>
+      <c r="V38" s="1"/>
+    </row>
+    <row r="39" ht="16.5" spans="19:22">
+      <c r="S39"/>
       <c r="U39" s="1"/>
-    </row>
-    <row r="40" ht="16.5" spans="18:21">
-      <c r="R40"/>
-      <c r="T40" s="1"/>
+      <c r="V39" s="1"/>
+    </row>
+    <row r="40" ht="16.5" spans="19:22">
+      <c r="S40"/>
       <c r="U40" s="1"/>
-    </row>
-    <row r="41" ht="16.5" spans="18:21">
-      <c r="R41"/>
-      <c r="T41" s="1"/>
+      <c r="V40" s="1"/>
+    </row>
+    <row r="41" ht="16.5" spans="19:22">
+      <c r="S41"/>
       <c r="U41" s="1"/>
-    </row>
-    <row r="42" ht="16.5" spans="18:21">
-      <c r="R42"/>
-      <c r="T42" s="1"/>
+      <c r="V41" s="1"/>
+    </row>
+    <row r="42" ht="16.5" spans="19:22">
+      <c r="S42"/>
       <c r="U42" s="1"/>
-    </row>
-    <row r="43" ht="16.5" spans="18:21">
-      <c r="R43"/>
-      <c r="T43" s="1"/>
+      <c r="V42" s="1"/>
+    </row>
+    <row r="43" ht="16.5" spans="19:22">
+      <c r="S43"/>
       <c r="U43" s="1"/>
-    </row>
-    <row r="44" ht="16.5" spans="18:21">
-      <c r="R44"/>
-      <c r="T44" s="1"/>
+      <c r="V43" s="1"/>
+    </row>
+    <row r="44" ht="16.5" spans="19:22">
+      <c r="S44"/>
       <c r="U44" s="1"/>
-    </row>
-    <row r="45" ht="16.5" spans="18:21">
-      <c r="R45"/>
-      <c r="U45" s="1"/>
-    </row>
-    <row r="46" ht="16.5" spans="18:21">
-      <c r="R46"/>
-      <c r="T46" s="1"/>
+      <c r="V44" s="1"/>
+    </row>
+    <row r="45" ht="16.5" spans="19:22">
+      <c r="S45"/>
+      <c r="V45" s="1"/>
+    </row>
+    <row r="46" ht="16.5" spans="19:22">
+      <c r="S46"/>
       <c r="U46" s="1"/>
-    </row>
-    <row r="47" ht="16.5" spans="18:21">
-      <c r="R47"/>
-      <c r="T47" s="1"/>
+      <c r="V46" s="1"/>
+    </row>
+    <row r="47" ht="16.5" spans="19:22">
+      <c r="S47"/>
       <c r="U47" s="1"/>
-    </row>
-    <row r="48" ht="16.5" spans="18:21">
-      <c r="R48"/>
-      <c r="T48" s="1"/>
+      <c r="V47" s="1"/>
+    </row>
+    <row r="48" ht="16.5" spans="19:22">
+      <c r="S48"/>
       <c r="U48" s="1"/>
-    </row>
-    <row r="49" ht="16.5" spans="18:21">
-      <c r="R49"/>
-      <c r="T49" s="1"/>
+      <c r="V48" s="1"/>
+    </row>
+    <row r="49" ht="16.5" spans="19:22">
+      <c r="S49"/>
       <c r="U49" s="1"/>
-    </row>
-    <row r="50" ht="16.5" spans="18:21">
-      <c r="R50"/>
-      <c r="T50" s="1"/>
+      <c r="V49" s="1"/>
+    </row>
+    <row r="50" ht="16.5" spans="19:22">
+      <c r="S50"/>
       <c r="U50" s="1"/>
-    </row>
-    <row r="51" ht="16.5" spans="18:21">
-      <c r="R51"/>
-      <c r="T51" s="1"/>
+      <c r="V50" s="1"/>
+    </row>
+    <row r="51" ht="16.5" spans="19:22">
+      <c r="S51"/>
       <c r="U51" s="1"/>
-    </row>
-    <row r="52" ht="16.5" spans="18:21">
-      <c r="R52"/>
-      <c r="T52" s="1"/>
+      <c r="V51" s="1"/>
+    </row>
+    <row r="52" ht="16.5" spans="19:22">
+      <c r="S52"/>
       <c r="U52" s="1"/>
-    </row>
-    <row r="53" ht="16.5" spans="18:21">
-      <c r="R53"/>
-      <c r="T53" s="1"/>
+      <c r="V52" s="1"/>
+    </row>
+    <row r="53" ht="16.5" spans="19:22">
+      <c r="S53"/>
       <c r="U53" s="1"/>
-    </row>
-    <row r="54" ht="16.5" spans="18:21">
-      <c r="R54"/>
-      <c r="T54" s="1"/>
+      <c r="V53" s="1"/>
+    </row>
+    <row r="54" ht="16.5" spans="19:22">
+      <c r="S54"/>
       <c r="U54" s="1"/>
-    </row>
-    <row r="55" ht="16.5" spans="18:21">
-      <c r="R55"/>
-      <c r="T55" s="1"/>
+      <c r="V54" s="1"/>
+    </row>
+    <row r="55" ht="16.5" spans="19:22">
+      <c r="S55"/>
       <c r="U55" s="1"/>
-    </row>
-    <row r="56" ht="16.5" spans="18:21">
-      <c r="R56"/>
-      <c r="T56" s="1"/>
+      <c r="V55" s="1"/>
+    </row>
+    <row r="56" ht="16.5" spans="19:22">
+      <c r="S56"/>
       <c r="U56" s="1"/>
-    </row>
-    <row r="57" ht="16.5" spans="18:21">
-      <c r="R57"/>
-      <c r="T57" s="1"/>
+      <c r="V56" s="1"/>
+    </row>
+    <row r="57" ht="16.5" spans="19:22">
+      <c r="S57"/>
       <c r="U57" s="1"/>
+      <c r="V57" s="1"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>MOD(MID($A2,1,4),2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2">
     <cfRule type="expression" dxfId="0" priority="4">
       <formula>MOD(MID($A2,1,4),2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2">
-    <cfRule type="expression" dxfId="0" priority="5">
+    <cfRule type="expression" dxfId="0" priority="7">
       <formula>MOD(MID($A2,1,4),2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N1:N3">
-    <cfRule type="expression" dxfId="0" priority="3">
-      <formula>MOD(MID($A1,1,4),2)=1</formula>
+  <conditionalFormatting sqref="L2">
+    <cfRule type="expression" dxfId="0" priority="8">
+      <formula>MOD(MID($A2,1,4),2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K22:K24">
+    <cfRule type="expression" dxfId="0" priority="10">
+      <formula>MOD(MID($A22,1,4),2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K28:K30">
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>MOD(MID($A28,1,4),2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K34:K36">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>MOD(MID($A34,1,4),2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O1:O3">
-    <cfRule type="expression" dxfId="0" priority="2">
-      <formula>MOD(MID($A1,1,4),2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P1:Q1 Q2 P3:Q3">
     <cfRule type="expression" dxfId="0" priority="6">
       <formula>MOD(MID($A1,1,4),2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J22:J25 J28:J29 J32:J33">
-    <cfRule type="expression" dxfId="0" priority="7">
-      <formula>MOD(MID($A22,1,4),2)=1</formula>
+  <conditionalFormatting sqref="P1:P3">
+    <cfRule type="expression" dxfId="0" priority="5">
+      <formula>MOD(MID($A1,1,4),2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q1:R1 R2 Q3:R3">
+    <cfRule type="expression" dxfId="0" priority="9">
+      <formula>MOD(MID($A1,1,4),2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2876,10 +3508,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="B1" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -2887,7 +3519,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -2895,7 +3527,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:8">
@@ -2903,16 +3535,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:8">
@@ -2920,16 +3552,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:8">
@@ -2937,16 +3569,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:8">
@@ -2954,16 +3586,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="F7" s="1">
         <v>2</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:8">
@@ -2971,16 +3603,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="F8" s="1">
         <v>3</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:8">
@@ -2988,16 +3620,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="F9" s="1">
         <v>4</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:8">
@@ -3005,16 +3637,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="F10" s="1">
         <v>5</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:8">
@@ -3022,16 +3654,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="F11" s="1">
         <v>6</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:8">
@@ -3039,16 +3671,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="F12" s="1">
         <v>7</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:8">
@@ -3056,16 +3688,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="F13" s="1">
         <v>8</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:8">
@@ -3073,16 +3705,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="F14" s="1">
         <v>9</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:8">
@@ -3090,16 +3722,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="F15" s="1">
         <v>10</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:8">
@@ -3107,16 +3739,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F16" s="1">
         <v>11</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:8">
@@ -3124,16 +3756,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="F17" s="1">
         <v>12</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:8">
@@ -3141,16 +3773,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="F18" s="1">
         <v>13</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:8">
@@ -3158,16 +3790,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="F19" s="1">
         <v>14</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:8">
@@ -3175,16 +3807,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="F20" s="1">
         <v>15</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:8">
@@ -3192,16 +3824,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="F21" s="1">
         <v>16</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:8">
@@ -3209,16 +3841,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="F22" s="1">
         <v>17</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:8">
@@ -3226,16 +3858,16 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="F23" s="1">
         <v>18</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:8">
@@ -3243,16 +3875,16 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="F24" s="1">
         <v>19</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -3260,7 +3892,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -3268,7 +3900,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -3276,7 +3908,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -3284,7 +3916,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -3292,7 +3924,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -3300,7 +3932,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -3308,7 +3940,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -3316,7 +3948,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -3324,7 +3956,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -3332,7 +3964,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -3340,7 +3972,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -3348,7 +3980,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -3356,7 +3988,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -3364,7 +3996,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -3372,7 +4004,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -3380,7 +4012,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -3388,7 +4020,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -3396,7 +4028,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -3404,7 +4036,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -3412,7 +4044,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -3420,7 +4052,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -3428,7 +4060,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -3436,7 +4068,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialAuxiliary.xlsx
+++ b/slots/resources/sample/SpecialAuxiliary.xlsx
@@ -268,7 +268,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="179">
   <si>
     <t>小游戏模式ID</t>
   </si>
@@ -303,7 +303,7 @@
     <t>奖励类型B</t>
   </si>
   <si>
-    <t>倍数，中奖权重，最大出现次数，根据配置额外增加</t>
+    <t>单线押分倍数，中奖权重，最大出现次数，根据配置额外增加</t>
   </si>
   <si>
     <t>赋予值类型</t>
@@ -384,19 +384,22 @@
     <t>车厢数量</t>
   </si>
   <si>
-    <t>2_200_1|3_500_2|5_1000_3|8_1200_4|10_1000_4|12_1000_4|15_1000_4|18_0_0|20_0_0|25_0_0|30_0_0|40_0_0</t>
+    <t>5_200_1|10_500_2|15_1000_3|20_1200_4|25_1000_4|30_1000_4|40_1000_4|50_0_0|60_0_0|70_0_0|80_0_0|100_0_0</t>
   </si>
   <si>
     <t>1_0</t>
   </si>
   <si>
+    <t>单线押分倍数*单线押分 = 奖励金额</t>
+  </si>
+  <si>
     <t>拉火车-蓝火车</t>
   </si>
   <si>
     <t>拉火车蓝火车MINOR</t>
   </si>
   <si>
-    <t>2_0_0|3_500_2|5_1000_3|8_1000_4|10_1000_4|12_1000_4|15_1000_4|18_1000_4|20_500_3|25_0_0|30_0_0|40_0_0</t>
+    <t>5_0_0|10_500_2|15_1000_3|20_1000_4|25_1000_4|30_1000_4|40_1000_4|50_1000_4|60_500_3|70_0_0|80_0_0|100_0_0</t>
   </si>
   <si>
     <t>拉火车-紫火车</t>
@@ -405,7 +408,7 @@
     <t>拉火车紫火车MAJOR</t>
   </si>
   <si>
-    <t>2_0_0|3_0_0|5_1000_3|8_1000_4|10_1000_4|12_1000_4|15_1000_4|18_1000_4|20_1000_3|25_500_2|30_100_2|40_0_0</t>
+    <t>5_0_0|10_0_0|15_1000_3|20_1000_4|25_1000_4|30_1000_4|40_1000_4|50_1000_4|60_1000_3|70_500_2|80_100_2|100_0_0</t>
   </si>
   <si>
     <t>拉火车-红火车</t>
@@ -414,7 +417,7 @@
     <t>拉火车红火车GRAND</t>
   </si>
   <si>
-    <t>2_0_0|3_0_0|5_0_0|8_1000_4|10_1000_4|12_1000_4|15_1000_4|18_500_4|20_500_3|25_500_2|30_500_2|40_500_1</t>
+    <t>5_0_0|10_0_0|15_0_0|20_1000_4|25_1000_4|30_1000_4|40_1000_4|50_500_4|60_500_3|70_500_2|80_500_2|100_500_1</t>
   </si>
   <si>
     <t>保险箱-触发局</t>
@@ -987,11 +990,13 @@
     </font>
     <font>
       <b/>
-      <sz val="9"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1004,9 +1009,7 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -2197,7 +2200,9 @@
       <c r="R5" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="S5" s="51"/>
+      <c r="S5" s="51" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="6" s="3" customFormat="1" ht="16.5" spans="1:19">
       <c r="A6" s="14">
@@ -2213,7 +2218,7 @@
         <v>31002</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F6" s="14" t="s">
         <v>33</v>
@@ -2221,7 +2226,7 @@
       <c r="G6" s="14"/>
       <c r="H6" s="14"/>
       <c r="I6" s="14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J6" s="14"/>
       <c r="K6" s="38"/>
@@ -2237,7 +2242,7 @@
       <c r="O6" s="14"/>
       <c r="P6" s="14"/>
       <c r="Q6" s="49" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="R6" s="50" t="s">
         <v>39</v>
@@ -2258,7 +2263,7 @@
         <v>31003</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F7" s="14" t="s">
         <v>33</v>
@@ -2266,7 +2271,7 @@
       <c r="G7" s="14"/>
       <c r="H7" s="14"/>
       <c r="I7" s="14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J7" s="14"/>
       <c r="K7" s="38"/>
@@ -2282,7 +2287,7 @@
       <c r="O7" s="14"/>
       <c r="P7" s="14"/>
       <c r="Q7" s="49" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="R7" s="50" t="s">
         <v>39</v>
@@ -2303,7 +2308,7 @@
         <v>31004</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F8" s="14" t="s">
         <v>33</v>
@@ -2311,7 +2316,7 @@
       <c r="G8" s="14"/>
       <c r="H8" s="14"/>
       <c r="I8" s="14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J8" s="14"/>
       <c r="K8" s="38"/>
@@ -2327,7 +2332,7 @@
       <c r="O8" s="14"/>
       <c r="P8" s="14"/>
       <c r="Q8" s="49" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R8" s="50" t="s">
         <v>39</v>
@@ -2348,7 +2353,7 @@
         <v>31101</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>33</v>
@@ -2356,7 +2361,7 @@
       <c r="G9" s="9"/>
       <c r="H9" s="9"/>
       <c r="I9" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J9" s="9"/>
       <c r="K9" s="32"/>
@@ -2364,11 +2369,11 @@
         <v>35</v>
       </c>
       <c r="M9" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N9" s="9"/>
       <c r="O9" s="9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="P9" s="9"/>
       <c r="Q9" s="11"/>
@@ -2389,7 +2394,7 @@
         <v>31102</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F10" s="17" t="s">
         <v>33</v>
@@ -2397,7 +2402,7 @@
       <c r="G10" s="17"/>
       <c r="H10" s="17"/>
       <c r="I10" s="17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J10" s="17"/>
       <c r="K10" s="39"/>
@@ -2405,13 +2410,13 @@
         <v>35</v>
       </c>
       <c r="M10" s="17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="N10" s="17" t="s">
         <v>37</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="P10" s="17"/>
       <c r="Q10" s="17"/>
@@ -2432,19 +2437,19 @@
         <v>31201</v>
       </c>
       <c r="E11" s="21" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G11" s="19">
         <v>2001001</v>
       </c>
       <c r="H11" s="19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I11" s="19" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J11" s="19"/>
       <c r="K11" s="40">
@@ -2473,23 +2478,23 @@
         <v>31202</v>
       </c>
       <c r="E12" s="21" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F12" s="22" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G12" s="22">
         <v>2001001</v>
       </c>
       <c r="H12" s="22" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I12" s="22" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J12" s="22"/>
       <c r="K12" s="41" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L12" s="22"/>
       <c r="M12" s="22"/>
@@ -2514,23 +2519,23 @@
         <v>31203</v>
       </c>
       <c r="E13" s="21" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F13" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G13" s="24">
         <v>2001001</v>
       </c>
       <c r="H13" s="24" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I13" s="24" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J13" s="24"/>
       <c r="K13" s="42" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L13" s="24"/>
       <c r="M13" s="24"/>
@@ -2555,7 +2560,7 @@
         <v>31301</v>
       </c>
       <c r="E14" s="27" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F14" s="21" t="s">
         <v>33</v>
@@ -2563,7 +2568,7 @@
       <c r="G14" s="21"/>
       <c r="H14" s="21"/>
       <c r="I14" s="21" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J14" s="21"/>
       <c r="K14" s="43"/>
@@ -2571,19 +2576,19 @@
         <v>35</v>
       </c>
       <c r="M14" s="21" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="N14" s="21"/>
       <c r="O14" s="21"/>
       <c r="P14" s="21"/>
       <c r="Q14" s="52" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R14" s="53" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S14" s="11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15" s="3" customFormat="1" ht="16.5" spans="1:19">
@@ -2600,7 +2605,7 @@
         <v>31302</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F15" s="24" t="s">
         <v>33</v>
@@ -2608,7 +2613,7 @@
       <c r="G15" s="24"/>
       <c r="H15" s="24"/>
       <c r="I15" s="24" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J15" s="24"/>
       <c r="K15" s="42"/>
@@ -2616,7 +2621,7 @@
         <v>35</v>
       </c>
       <c r="M15" s="24" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="N15" s="24"/>
       <c r="O15" s="24"/>
@@ -2639,23 +2644,23 @@
         <v>31303</v>
       </c>
       <c r="E16" s="27" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F16" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G16" s="24">
         <v>2001001</v>
       </c>
       <c r="H16" s="24" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I16" s="24" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J16" s="24"/>
       <c r="K16" s="42" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L16" s="24"/>
       <c r="M16" s="24"/>
@@ -2674,25 +2679,25 @@
         <v>100700</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D17" s="19">
         <v>34001</v>
       </c>
       <c r="E17" s="19" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F17" s="19" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G17" s="16">
         <v>2007001</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K17" s="44"/>
     </row>
@@ -2704,25 +2709,25 @@
         <v>100700</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D18" s="19">
         <v>34002</v>
       </c>
       <c r="E18" s="19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F18" s="19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G18" s="16">
         <v>2007001</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K18" s="44"/>
     </row>
@@ -2734,28 +2739,28 @@
         <v>101200</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D19" s="21">
         <v>32001</v>
       </c>
       <c r="E19" s="21" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F19" s="21" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G19" s="26">
         <v>2012001</v>
       </c>
       <c r="H19" s="21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I19" s="21" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J19" s="21" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K19" s="45">
         <v>10120041</v>
@@ -2769,28 +2774,28 @@
         <v>101200</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D20" s="21">
         <v>32002</v>
       </c>
       <c r="E20" s="21" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F20" s="21" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G20" s="26">
         <v>2012001</v>
       </c>
       <c r="H20" s="21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I20" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="J20" s="21" t="s">
         <v>84</v>
-      </c>
-      <c r="J20" s="21" t="s">
-        <v>83</v>
       </c>
       <c r="K20" s="45">
         <v>10120042</v>
@@ -2804,28 +2809,28 @@
         <v>101200</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D21" s="21">
         <v>32003</v>
       </c>
       <c r="E21" s="21" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F21" s="21" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G21" s="26">
         <v>2012001</v>
       </c>
       <c r="H21" s="21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I21" s="21" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J21" s="21" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K21" s="45">
         <v>10120043</v>
@@ -2839,28 +2844,28 @@
         <v>101200</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D22" s="21">
         <v>32004</v>
       </c>
       <c r="E22" s="21" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F22" s="21" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G22" s="26">
         <v>2012001</v>
       </c>
       <c r="H22" s="21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I22" s="21" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J22" s="21" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K22" s="45">
         <v>10120044</v>
@@ -2874,28 +2879,28 @@
         <v>101200</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D23" s="21">
         <v>32005</v>
       </c>
       <c r="E23" s="21" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F23" s="21" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G23" s="26">
         <v>2012001</v>
       </c>
       <c r="H23" s="21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I23" s="21" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J23" s="21" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K23" s="45">
         <v>10120045</v>
@@ -2909,28 +2914,28 @@
         <v>101200</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D24" s="21">
         <v>32006</v>
       </c>
       <c r="E24" s="21" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F24" s="21" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G24" s="26">
         <v>2012001</v>
       </c>
       <c r="H24" s="21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I24" s="21" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J24" s="21" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K24" s="45">
         <v>10120046</v>
@@ -2944,28 +2949,28 @@
         <v>101200</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D25" s="21">
         <v>32101</v>
       </c>
       <c r="E25" s="28" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F25" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G25" s="29">
         <v>2012001</v>
       </c>
       <c r="H25" s="28" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I25" s="28" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J25" s="28" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K25" s="46">
         <v>10120041</v>
@@ -2979,28 +2984,28 @@
         <v>101200</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D26" s="21">
         <v>32102</v>
       </c>
       <c r="E26" s="28" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F26" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G26" s="29">
         <v>2012001</v>
       </c>
       <c r="H26" s="28" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I26" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="J26" s="28" t="s">
         <v>84</v>
-      </c>
-      <c r="J26" s="28" t="s">
-        <v>83</v>
       </c>
       <c r="K26" s="46">
         <v>10120042</v>
@@ -3014,28 +3019,28 @@
         <v>101200</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D27" s="21">
         <v>32103</v>
       </c>
       <c r="E27" s="28" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F27" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G27" s="29">
         <v>2012001</v>
       </c>
       <c r="H27" s="28" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I27" s="28" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J27" s="28" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K27" s="46">
         <v>10120043</v>
@@ -3049,28 +3054,28 @@
         <v>101200</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D28" s="21">
         <v>32104</v>
       </c>
       <c r="E28" s="28" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F28" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G28" s="29">
         <v>2012001</v>
       </c>
       <c r="H28" s="28" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I28" s="28" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J28" s="28" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K28" s="46">
         <v>10120044</v>
@@ -3084,28 +3089,28 @@
         <v>101200</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D29" s="21">
         <v>32105</v>
       </c>
       <c r="E29" s="28" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F29" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G29" s="29">
         <v>2012001</v>
       </c>
       <c r="H29" s="28" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I29" s="28" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J29" s="28" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K29" s="46">
         <v>10120045</v>
@@ -3119,28 +3124,28 @@
         <v>101200</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D30" s="21">
         <v>32106</v>
       </c>
       <c r="E30" s="28" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F30" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G30" s="29">
         <v>2012001</v>
       </c>
       <c r="H30" s="28" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I30" s="28" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J30" s="28" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K30" s="46">
         <v>10120046</v>
@@ -3154,25 +3159,25 @@
         <v>101200</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D31" s="27">
         <v>32201</v>
       </c>
       <c r="E31" s="27" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F31" s="27" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G31" s="30">
         <v>2012001</v>
       </c>
       <c r="H31" s="27" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I31" s="27" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J31" s="27"/>
       <c r="K31" s="47">
@@ -3187,25 +3192,25 @@
         <v>101200</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D32" s="27">
         <v>32202</v>
       </c>
       <c r="E32" s="27" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F32" s="27" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G32" s="30">
         <v>2012001</v>
       </c>
       <c r="H32" s="27" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I32" s="27" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J32" s="27"/>
       <c r="K32" s="47">
@@ -3220,25 +3225,25 @@
         <v>101200</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D33" s="27">
         <v>32203</v>
       </c>
       <c r="E33" s="27" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F33" s="27" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G33" s="30">
         <v>2012001</v>
       </c>
       <c r="H33" s="27" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I33" s="27" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J33" s="27"/>
       <c r="K33" s="47">
@@ -3253,25 +3258,25 @@
         <v>101200</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D34" s="27">
         <v>32204</v>
       </c>
       <c r="E34" s="27" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F34" s="27" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G34" s="30">
         <v>2012001</v>
       </c>
       <c r="H34" s="27" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I34" s="27" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J34" s="27"/>
       <c r="K34" s="47">
@@ -3286,25 +3291,25 @@
         <v>101200</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D35" s="27">
         <v>32205</v>
       </c>
       <c r="E35" s="27" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F35" s="27" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G35" s="30">
         <v>2012001</v>
       </c>
       <c r="H35" s="27" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I35" s="27" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J35" s="27"/>
       <c r="K35" s="47">
@@ -3319,25 +3324,25 @@
         <v>101200</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D36" s="27">
         <v>32206</v>
       </c>
       <c r="E36" s="27" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F36" s="27" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G36" s="30">
         <v>2012001</v>
       </c>
       <c r="H36" s="27" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I36" s="27" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J36" s="27"/>
       <c r="K36" s="47">
@@ -3508,10 +3513,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -3519,7 +3524,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3527,7 +3532,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:8">
@@ -3535,16 +3540,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:8">
@@ -3552,16 +3557,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:8">
@@ -3569,16 +3574,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:8">
@@ -3586,16 +3591,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F7" s="1">
         <v>2</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:8">
@@ -3603,16 +3608,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F8" s="1">
         <v>3</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:8">
@@ -3620,16 +3625,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F9" s="1">
         <v>4</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:8">
@@ -3637,16 +3642,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F10" s="1">
         <v>5</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:8">
@@ -3654,16 +3659,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F11" s="1">
         <v>6</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:8">
@@ -3671,16 +3676,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F12" s="1">
         <v>7</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:8">
@@ -3688,16 +3693,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F13" s="1">
         <v>8</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:8">
@@ -3705,16 +3710,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F14" s="1">
         <v>9</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:8">
@@ -3722,16 +3727,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F15" s="1">
         <v>10</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:8">
@@ -3739,16 +3744,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F16" s="1">
         <v>11</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:8">
@@ -3756,16 +3761,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F17" s="1">
         <v>12</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:8">
@@ -3773,16 +3778,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F18" s="1">
         <v>13</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:8">
@@ -3790,16 +3795,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F19" s="1">
         <v>14</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:8">
@@ -3807,16 +3812,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F20" s="1">
         <v>15</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:8">
@@ -3824,16 +3829,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F21" s="1">
         <v>16</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:8">
@@ -3841,16 +3846,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F22" s="1">
         <v>17</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:8">
@@ -3858,16 +3863,16 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F23" s="1">
         <v>18</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:8">
@@ -3875,16 +3880,16 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F24" s="1">
         <v>19</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -3892,7 +3897,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -3900,7 +3905,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -3908,7 +3913,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -3916,7 +3921,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -3924,7 +3929,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -3932,7 +3937,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -3940,7 +3945,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -3948,7 +3953,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -3956,7 +3961,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -3964,7 +3969,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -3972,7 +3977,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -3980,7 +3985,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -3988,7 +3993,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -3996,7 +4001,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -4004,7 +4009,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -4012,7 +4017,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -4020,7 +4025,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -4028,7 +4033,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -4036,7 +4041,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -4044,7 +4049,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -4052,7 +4057,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -4060,7 +4065,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -4068,7 +4073,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialAuxiliary.xlsx
+++ b/slots/resources/sample/SpecialAuxiliary.xlsx
@@ -268,7 +268,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="180">
   <si>
     <t>小游戏模式ID</t>
   </si>
@@ -384,7 +384,7 @@
     <t>车厢数量</t>
   </si>
   <si>
-    <t>5_200_1|10_500_2|15_1000_3|20_1200_4|25_1000_4|30_1000_4|40_1000_4|50_0_0|60_0_0|70_0_0|80_0_0|100_0_0</t>
+    <t>50_200_1|60_500_2|80_1300_3|90_1500_4|100_1500_4|110_1500_4|120_1500_4|130_1000_4|140_1000_4|150_0_0|180_0_0|200_0_0</t>
   </si>
   <si>
     <t>1_0</t>
@@ -399,7 +399,7 @@
     <t>拉火车蓝火车MINOR</t>
   </si>
   <si>
-    <t>5_0_0|10_500_2|15_1000_3|20_1000_4|25_1000_4|30_1000_4|40_1000_4|50_1000_4|60_500_3|70_0_0|80_0_0|100_0_0</t>
+    <t>50_0_0|60_0_0|80_1000_3|90_1500_4|100_2000_4|110_2000_4|120_1500_4|130_1000_4|140_1000_4|150_0_0|180_0_0|200_0_0</t>
   </si>
   <si>
     <t>拉火车-紫火车</t>
@@ -408,7 +408,7 @@
     <t>拉火车紫火车MAJOR</t>
   </si>
   <si>
-    <t>5_0_0|10_0_0|15_1000_3|20_1000_4|25_1000_4|30_1000_4|40_1000_4|50_1000_4|60_1000_3|70_500_2|80_100_2|100_0_0</t>
+    <t>50_0_0|60_0_0|80_1000_4|90_1000_4|100_1000_4|110_2000_4|120_2000_4|130_1400_4|140_1000_4|150_500_4|180_100_4|200_0_0</t>
   </si>
   <si>
     <t>拉火车-红火车</t>
@@ -417,7 +417,7 @@
     <t>拉火车红火车GRAND</t>
   </si>
   <si>
-    <t>5_0_0|10_0_0|15_0_0|20_1000_4|25_1000_4|30_1000_4|40_1000_4|50_500_4|60_500_3|70_500_2|80_500_2|100_500_1</t>
+    <t>50_0_0|60_0_0|80_0_0|90_1000_4|100_1500_4|110_1500_4|120_2000_4|130_1500_4|140_1000_4|150_500_4|180_500_4|200_500_4</t>
   </si>
   <si>
     <t>保险箱-触发局</t>
@@ -438,61 +438,64 @@
     <t>黄金列车-特殊美金不触发投资</t>
   </si>
   <si>
+    <t>5_0|6_0|7_10|8_10|9_8|10_8|11_5</t>
+  </si>
+  <si>
+    <t>免费模式2/1-免费旋转</t>
+  </si>
+  <si>
+    <t>8_1</t>
+  </si>
+  <si>
+    <t>使用基础滚轴重转</t>
+  </si>
+  <si>
+    <t>免费后选 - 免费模式</t>
+  </si>
+  <si>
+    <t>免费模式2/1-拉火车-绿/蓝/紫/红-触发局</t>
+  </si>
+  <si>
+    <t>免费后选 - 拉火车</t>
+  </si>
+  <si>
+    <t>10010021|10010022|10010023|10010024|10010025</t>
+  </si>
+  <si>
+    <t>免费模式2/1-拉火车-黄金火车-触发局</t>
+  </si>
+  <si>
+    <t>黄金列车触发局</t>
+  </si>
+  <si>
+    <t>10010031|10010032</t>
+  </si>
+  <si>
+    <t>投资地图 - 抽奖</t>
+  </si>
+  <si>
+    <t>投资游戏，图案18收集满150个后抽奖</t>
+  </si>
+  <si>
+    <t>3_1</t>
+  </si>
+  <si>
+    <t>0_15000_3|60_500_3|80_500_3|90_1000_3|100_1000_3|110_1000_3|120_1000_3|140_1000_3|150_1000_3|180_1000_3|200_1000_3|300_1000_3</t>
+  </si>
+  <si>
+    <t>4_5001003</t>
+  </si>
+  <si>
+    <t>平均押分，有概率倍数为0</t>
+  </si>
+  <si>
+    <t>投资地图- 连续抽中3次-拉火车-黄金火车</t>
+  </si>
+  <si>
+    <t>黄金列车-金额为投资游戏的总奖金</t>
+  </si>
+  <si>
     <t>5_1|6_3|7_18|8_12|9_8|10_5|11_1</t>
-  </si>
-  <si>
-    <t>免费模式2/1-免费旋转</t>
-  </si>
-  <si>
-    <t>8_1</t>
-  </si>
-  <si>
-    <t>使用基础滚轴重转</t>
-  </si>
-  <si>
-    <t>免费后选 - 免费模式</t>
-  </si>
-  <si>
-    <t>免费模式2/1-拉火车-绿/蓝/紫/红-触发局</t>
-  </si>
-  <si>
-    <t>免费后选 - 拉火车</t>
-  </si>
-  <si>
-    <t>10010021|10010022|10010023|10010024|10010025</t>
-  </si>
-  <si>
-    <t>免费模式2/1-拉火车-黄金火车-触发局</t>
-  </si>
-  <si>
-    <t>黄金列车触发局</t>
-  </si>
-  <si>
-    <t>10010031|10010032</t>
-  </si>
-  <si>
-    <t>投资地图 - 抽奖</t>
-  </si>
-  <si>
-    <t>投资游戏，图案18收集满150个后抽奖</t>
-  </si>
-  <si>
-    <t>3_1</t>
-  </si>
-  <si>
-    <t>0_15000_3|10_500_3|15_500_3|20_1000_3|25_1000_3|30_1000_3|40_1000_3|50_1000_3|100_1000_3|150_1000_3|200_1000_3|300_1000_3</t>
-  </si>
-  <si>
-    <t>4_5001003</t>
-  </si>
-  <si>
-    <t>平均押分，有概率倍数为0</t>
-  </si>
-  <si>
-    <t>投资地图- 连续抽中3次-拉火车-黄金火车</t>
-  </si>
-  <si>
-    <t>黄金列车-金额为投资游戏的总奖金</t>
   </si>
   <si>
     <t>投资地图 - 8次地图完成 - 黄金火车-触发局</t>
@@ -983,6 +986,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
@@ -998,18 +1012,7 @@
     <font>
       <b/>
       <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
       <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1993,7 +1996,7 @@
     <col min="9" max="10" width="29.375" customWidth="1"/>
     <col min="11" max="11" width="41.25" style="7" customWidth="1"/>
     <col min="12" max="12" width="11.75" style="3" customWidth="1"/>
-    <col min="13" max="13" width="20.4416666666667" style="3" customWidth="1"/>
+    <col min="13" max="13" width="34.4083333333333" style="3" customWidth="1"/>
     <col min="14" max="14" width="7.93333333333333" style="3" customWidth="1"/>
     <col min="15" max="15" width="11.325" customWidth="1"/>
     <col min="16" max="16" width="8.96666666666667" customWidth="1"/>
@@ -2621,7 +2624,7 @@
         <v>35</v>
       </c>
       <c r="M15" s="24" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="N15" s="24"/>
       <c r="O15" s="24"/>
@@ -2644,7 +2647,7 @@
         <v>31303</v>
       </c>
       <c r="E16" s="27" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F16" s="24" t="s">
         <v>52</v>
@@ -2679,16 +2682,16 @@
         <v>100700</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D17" s="19">
         <v>34001</v>
       </c>
       <c r="E17" s="19" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F17" s="19" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G17" s="16">
         <v>2007001</v>
@@ -2697,7 +2700,7 @@
         <v>59</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K17" s="44"/>
     </row>
@@ -2709,16 +2712,16 @@
         <v>100700</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D18" s="19">
         <v>34002</v>
       </c>
       <c r="E18" s="19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F18" s="19" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G18" s="16">
         <v>2007001</v>
@@ -2727,7 +2730,7 @@
         <v>59</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K18" s="44"/>
     </row>
@@ -2739,13 +2742,13 @@
         <v>101200</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D19" s="21">
         <v>32001</v>
       </c>
       <c r="E19" s="21" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F19" s="21" t="s">
         <v>52</v>
@@ -2757,10 +2760,10 @@
         <v>59</v>
       </c>
       <c r="I19" s="21" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J19" s="21" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K19" s="45">
         <v>10120041</v>
@@ -2774,13 +2777,13 @@
         <v>101200</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D20" s="21">
         <v>32002</v>
       </c>
       <c r="E20" s="21" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F20" s="21" t="s">
         <v>52</v>
@@ -2792,10 +2795,10 @@
         <v>59</v>
       </c>
       <c r="I20" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="J20" s="21" t="s">
         <v>85</v>
-      </c>
-      <c r="J20" s="21" t="s">
-        <v>84</v>
       </c>
       <c r="K20" s="45">
         <v>10120042</v>
@@ -2809,13 +2812,13 @@
         <v>101200</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D21" s="21">
         <v>32003</v>
       </c>
       <c r="E21" s="21" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F21" s="21" t="s">
         <v>52</v>
@@ -2827,10 +2830,10 @@
         <v>59</v>
       </c>
       <c r="I21" s="21" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J21" s="21" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K21" s="45">
         <v>10120043</v>
@@ -2844,13 +2847,13 @@
         <v>101200</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D22" s="21">
         <v>32004</v>
       </c>
       <c r="E22" s="21" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F22" s="21" t="s">
         <v>52</v>
@@ -2862,10 +2865,10 @@
         <v>59</v>
       </c>
       <c r="I22" s="21" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J22" s="21" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K22" s="45">
         <v>10120044</v>
@@ -2879,13 +2882,13 @@
         <v>101200</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D23" s="21">
         <v>32005</v>
       </c>
       <c r="E23" s="21" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F23" s="21" t="s">
         <v>52</v>
@@ -2897,10 +2900,10 @@
         <v>59</v>
       </c>
       <c r="I23" s="21" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J23" s="21" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K23" s="45">
         <v>10120045</v>
@@ -2914,13 +2917,13 @@
         <v>101200</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D24" s="21">
         <v>32006</v>
       </c>
       <c r="E24" s="21" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F24" s="21" t="s">
         <v>52</v>
@@ -2932,10 +2935,10 @@
         <v>59</v>
       </c>
       <c r="I24" s="21" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J24" s="21" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K24" s="45">
         <v>10120046</v>
@@ -2949,13 +2952,13 @@
         <v>101200</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D25" s="21">
         <v>32101</v>
       </c>
       <c r="E25" s="28" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F25" s="28" t="s">
         <v>52</v>
@@ -2967,10 +2970,10 @@
         <v>59</v>
       </c>
       <c r="I25" s="28" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J25" s="28" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K25" s="46">
         <v>10120041</v>
@@ -2984,13 +2987,13 @@
         <v>101200</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D26" s="21">
         <v>32102</v>
       </c>
       <c r="E26" s="28" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F26" s="28" t="s">
         <v>52</v>
@@ -3002,10 +3005,10 @@
         <v>59</v>
       </c>
       <c r="I26" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="J26" s="28" t="s">
         <v>85</v>
-      </c>
-      <c r="J26" s="28" t="s">
-        <v>84</v>
       </c>
       <c r="K26" s="46">
         <v>10120042</v>
@@ -3019,13 +3022,13 @@
         <v>101200</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D27" s="21">
         <v>32103</v>
       </c>
       <c r="E27" s="28" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F27" s="28" t="s">
         <v>52</v>
@@ -3037,10 +3040,10 @@
         <v>59</v>
       </c>
       <c r="I27" s="28" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J27" s="28" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K27" s="46">
         <v>10120043</v>
@@ -3054,13 +3057,13 @@
         <v>101200</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D28" s="21">
         <v>32104</v>
       </c>
       <c r="E28" s="28" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F28" s="28" t="s">
         <v>52</v>
@@ -3072,10 +3075,10 @@
         <v>59</v>
       </c>
       <c r="I28" s="28" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J28" s="28" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K28" s="46">
         <v>10120044</v>
@@ -3089,13 +3092,13 @@
         <v>101200</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D29" s="21">
         <v>32105</v>
       </c>
       <c r="E29" s="28" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F29" s="28" t="s">
         <v>52</v>
@@ -3107,10 +3110,10 @@
         <v>59</v>
       </c>
       <c r="I29" s="28" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J29" s="28" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K29" s="46">
         <v>10120045</v>
@@ -3124,13 +3127,13 @@
         <v>101200</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D30" s="21">
         <v>32106</v>
       </c>
       <c r="E30" s="28" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F30" s="28" t="s">
         <v>52</v>
@@ -3142,10 +3145,10 @@
         <v>59</v>
       </c>
       <c r="I30" s="28" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J30" s="28" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K30" s="46">
         <v>10120046</v>
@@ -3159,13 +3162,13 @@
         <v>101200</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D31" s="27">
         <v>32201</v>
       </c>
       <c r="E31" s="27" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F31" s="27" t="s">
         <v>52</v>
@@ -3177,7 +3180,7 @@
         <v>59</v>
       </c>
       <c r="I31" s="27" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J31" s="27"/>
       <c r="K31" s="47">
@@ -3192,13 +3195,13 @@
         <v>101200</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D32" s="27">
         <v>32202</v>
       </c>
       <c r="E32" s="27" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F32" s="27" t="s">
         <v>52</v>
@@ -3210,7 +3213,7 @@
         <v>59</v>
       </c>
       <c r="I32" s="27" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J32" s="27"/>
       <c r="K32" s="47">
@@ -3225,13 +3228,13 @@
         <v>101200</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D33" s="27">
         <v>32203</v>
       </c>
       <c r="E33" s="27" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F33" s="27" t="s">
         <v>52</v>
@@ -3243,7 +3246,7 @@
         <v>59</v>
       </c>
       <c r="I33" s="27" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J33" s="27"/>
       <c r="K33" s="47">
@@ -3258,13 +3261,13 @@
         <v>101200</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D34" s="27">
         <v>32204</v>
       </c>
       <c r="E34" s="27" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F34" s="27" t="s">
         <v>52</v>
@@ -3276,7 +3279,7 @@
         <v>59</v>
       </c>
       <c r="I34" s="27" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J34" s="27"/>
       <c r="K34" s="47">
@@ -3291,13 +3294,13 @@
         <v>101200</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D35" s="27">
         <v>32205</v>
       </c>
       <c r="E35" s="27" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F35" s="27" t="s">
         <v>52</v>
@@ -3309,7 +3312,7 @@
         <v>59</v>
       </c>
       <c r="I35" s="27" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J35" s="27"/>
       <c r="K35" s="47">
@@ -3324,13 +3327,13 @@
         <v>101200</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D36" s="27">
         <v>32206</v>
       </c>
       <c r="E36" s="27" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F36" s="27" t="s">
         <v>52</v>
@@ -3342,7 +3345,7 @@
         <v>59</v>
       </c>
       <c r="I36" s="27" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J36" s="27"/>
       <c r="K36" s="47">
@@ -3513,10 +3516,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -3524,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3532,7 +3535,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:8">
@@ -3540,16 +3543,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:8">
@@ -3557,16 +3560,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:8">
@@ -3574,16 +3577,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:8">
@@ -3591,16 +3594,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F7" s="1">
         <v>2</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:8">
@@ -3608,16 +3611,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F8" s="1">
         <v>3</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:8">
@@ -3625,16 +3628,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F9" s="1">
         <v>4</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:8">
@@ -3642,16 +3645,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F10" s="1">
         <v>5</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:8">
@@ -3659,16 +3662,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F11" s="1">
         <v>6</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:8">
@@ -3676,16 +3679,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F12" s="1">
         <v>7</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:8">
@@ -3693,16 +3696,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F13" s="1">
         <v>8</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:8">
@@ -3710,16 +3713,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F14" s="1">
         <v>9</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:8">
@@ -3727,16 +3730,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F15" s="1">
         <v>10</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:8">
@@ -3744,16 +3747,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F16" s="1">
         <v>11</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:8">
@@ -3761,16 +3764,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F17" s="1">
         <v>12</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:8">
@@ -3778,16 +3781,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F18" s="1">
         <v>13</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:8">
@@ -3795,16 +3798,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F19" s="1">
         <v>14</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:8">
@@ -3812,16 +3815,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F20" s="1">
         <v>15</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:8">
@@ -3829,16 +3832,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F21" s="1">
         <v>16</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:8">
@@ -3846,16 +3849,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F22" s="1">
         <v>17</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:8">
@@ -3863,16 +3866,16 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F23" s="1">
         <v>18</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:8">
@@ -3880,16 +3883,16 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F24" s="1">
         <v>19</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -3897,7 +3900,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -3905,7 +3908,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -3913,7 +3916,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -3921,7 +3924,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -3929,7 +3932,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -3937,7 +3940,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -3945,7 +3948,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -3953,7 +3956,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -3961,7 +3964,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -3969,7 +3972,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -3977,7 +3980,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -3985,7 +3988,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -3993,7 +3996,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -4001,7 +4004,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -4009,7 +4012,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -4017,7 +4020,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -4025,7 +4028,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -4033,7 +4036,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -4041,7 +4044,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -4049,7 +4052,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -4057,7 +4060,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -4065,7 +4068,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -4073,7 +4076,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialAuxiliary.xlsx
+++ b/slots/resources/sample/SpecialAuxiliary.xlsx
@@ -236,7 +236,7 @@
           <t>倍率类型：
 1 单线押分_0
 2 总押分_0
-3 
+3 平均单线押分_被动游戏ID
 4 平均押分_被动游戏ID</t>
         </r>
       </text>
@@ -268,7 +268,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="179">
   <si>
     <t>小游戏模式ID</t>
   </si>
@@ -378,13 +378,13 @@
     <t>总奖励 = 次数×(TypeC + TypeA + TypeB)</t>
   </si>
   <si>
-    <t>5_1|6_3|7_18|8_12|9_8|10_5|11_3|12_1</t>
+    <t>5_0|6_8|7_18|8_12|9_6|10_3|11_2|12_1</t>
   </si>
   <si>
     <t>车厢数量</t>
   </si>
   <si>
-    <t>50_200_1|60_500_2|80_1300_3|90_1500_4|100_1500_4|110_1500_4|120_1500_4|130_1000_4|140_1000_4|150_0_0|180_0_0|200_0_0</t>
+    <t>40_200_1|50_500_2|60_1300_3|70_1500_4|80_1500_4|90_1500_4|100_1500_4|110_1000_4|120_1000_4|130_0_0|150_0_0|200_0_0</t>
   </si>
   <si>
     <t>1_0</t>
@@ -399,7 +399,7 @@
     <t>拉火车蓝火车MINOR</t>
   </si>
   <si>
-    <t>50_0_0|60_0_0|80_1000_3|90_1500_4|100_2000_4|110_2000_4|120_1500_4|130_1000_4|140_1000_4|150_0_0|180_0_0|200_0_0</t>
+    <t>40_0_0|50_0_0|60_1000_3|70_1500_4|80_2000_4|90_2000_4|100_1500_4|110_1000_4|120_1000_4|130_0_0|150_0_0|200_0_0</t>
   </si>
   <si>
     <t>拉火车-紫火车</t>
@@ -408,7 +408,7 @@
     <t>拉火车紫火车MAJOR</t>
   </si>
   <si>
-    <t>50_0_0|60_0_0|80_1000_4|90_1000_4|100_1000_4|110_2000_4|120_2000_4|130_1400_4|140_1000_4|150_500_4|180_100_4|200_0_0</t>
+    <t>40_0_0|50_0_0|60_1000_4|70_1000_4|80_1000_4|90_2000_4|100_2000_4|110_1400_4|120_1000_4|130_500_4|150_100_4|200_0_0</t>
   </si>
   <si>
     <t>拉火车-红火车</t>
@@ -417,7 +417,7 @@
     <t>拉火车红火车GRAND</t>
   </si>
   <si>
-    <t>50_0_0|60_0_0|80_0_0|90_1000_4|100_1500_4|110_1500_4|120_2000_4|130_1500_4|140_1000_4|150_500_4|180_500_4|200_500_4</t>
+    <t>40_0_0|50_0_0|60_0_0|70_1000_4|80_1500_4|90_1500_4|100_2000_4|110_1500_4|120_1000_4|130_500_4|150_500_4|200_500_4</t>
   </si>
   <si>
     <t>保险箱-触发局</t>
@@ -483,19 +483,16 @@
     <t>0_15000_3|60_500_3|80_500_3|90_1000_3|100_1000_3|110_1000_3|120_1000_3|140_1000_3|150_1000_3|180_1000_3|200_1000_3|300_1000_3</t>
   </si>
   <si>
-    <t>4_5001003</t>
-  </si>
-  <si>
-    <t>平均押分，有概率倍数为0</t>
+    <t>4_0</t>
+  </si>
+  <si>
+    <t>平均单线押分，有概率倍数为0</t>
   </si>
   <si>
     <t>投资地图- 连续抽中3次-拉火车-黄金火车</t>
   </si>
   <si>
     <t>黄金列车-金额为投资游戏的总奖金</t>
-  </si>
-  <si>
-    <t>5_1|6_3|7_18|8_12|9_8|10_5|11_1</t>
   </si>
   <si>
     <t>投资地图 - 8次地图完成 - 黄金火车-触发局</t>
@@ -992,6 +989,13 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1018,13 +1022,6 @@
     </font>
     <font>
       <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2624,7 +2621,7 @@
         <v>35</v>
       </c>
       <c r="M15" s="24" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="N15" s="24"/>
       <c r="O15" s="24"/>
@@ -2647,7 +2644,7 @@
         <v>31303</v>
       </c>
       <c r="E16" s="27" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F16" s="24" t="s">
         <v>52</v>
@@ -2682,16 +2679,16 @@
         <v>100700</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D17" s="19">
         <v>34001</v>
       </c>
       <c r="E17" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="F17" s="19" t="s">
         <v>78</v>
-      </c>
-      <c r="F17" s="19" t="s">
-        <v>79</v>
       </c>
       <c r="G17" s="16">
         <v>2007001</v>
@@ -2700,7 +2697,7 @@
         <v>59</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K17" s="44"/>
     </row>
@@ -2712,16 +2709,16 @@
         <v>100700</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D18" s="19">
         <v>34002</v>
       </c>
       <c r="E18" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="F18" s="19" t="s">
         <v>81</v>
-      </c>
-      <c r="F18" s="19" t="s">
-        <v>82</v>
       </c>
       <c r="G18" s="16">
         <v>2007001</v>
@@ -2730,7 +2727,7 @@
         <v>59</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K18" s="44"/>
     </row>
@@ -2742,13 +2739,13 @@
         <v>101200</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D19" s="21">
         <v>32001</v>
       </c>
       <c r="E19" s="21" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F19" s="21" t="s">
         <v>52</v>
@@ -2760,10 +2757,10 @@
         <v>59</v>
       </c>
       <c r="I19" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="J19" s="21" t="s">
         <v>84</v>
-      </c>
-      <c r="J19" s="21" t="s">
-        <v>85</v>
       </c>
       <c r="K19" s="45">
         <v>10120041</v>
@@ -2777,13 +2774,13 @@
         <v>101200</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D20" s="21">
         <v>32002</v>
       </c>
       <c r="E20" s="21" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F20" s="21" t="s">
         <v>52</v>
@@ -2795,10 +2792,10 @@
         <v>59</v>
       </c>
       <c r="I20" s="21" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J20" s="21" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K20" s="45">
         <v>10120042</v>
@@ -2812,13 +2809,13 @@
         <v>101200</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D21" s="21">
         <v>32003</v>
       </c>
       <c r="E21" s="21" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F21" s="21" t="s">
         <v>52</v>
@@ -2830,10 +2827,10 @@
         <v>59</v>
       </c>
       <c r="I21" s="21" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J21" s="21" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K21" s="45">
         <v>10120043</v>
@@ -2847,13 +2844,13 @@
         <v>101200</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D22" s="21">
         <v>32004</v>
       </c>
       <c r="E22" s="21" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F22" s="21" t="s">
         <v>52</v>
@@ -2865,10 +2862,10 @@
         <v>59</v>
       </c>
       <c r="I22" s="21" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J22" s="21" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K22" s="45">
         <v>10120044</v>
@@ -2882,13 +2879,13 @@
         <v>101200</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D23" s="21">
         <v>32005</v>
       </c>
       <c r="E23" s="21" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F23" s="21" t="s">
         <v>52</v>
@@ -2900,10 +2897,10 @@
         <v>59</v>
       </c>
       <c r="I23" s="21" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J23" s="21" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K23" s="45">
         <v>10120045</v>
@@ -2917,13 +2914,13 @@
         <v>101200</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D24" s="21">
         <v>32006</v>
       </c>
       <c r="E24" s="21" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F24" s="21" t="s">
         <v>52</v>
@@ -2935,10 +2932,10 @@
         <v>59</v>
       </c>
       <c r="I24" s="21" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J24" s="21" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K24" s="45">
         <v>10120046</v>
@@ -2952,13 +2949,13 @@
         <v>101200</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D25" s="21">
         <v>32101</v>
       </c>
       <c r="E25" s="28" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F25" s="28" t="s">
         <v>52</v>
@@ -2970,10 +2967,10 @@
         <v>59</v>
       </c>
       <c r="I25" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="J25" s="28" t="s">
         <v>84</v>
-      </c>
-      <c r="J25" s="28" t="s">
-        <v>85</v>
       </c>
       <c r="K25" s="46">
         <v>10120041</v>
@@ -2987,13 +2984,13 @@
         <v>101200</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D26" s="21">
         <v>32102</v>
       </c>
       <c r="E26" s="28" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F26" s="28" t="s">
         <v>52</v>
@@ -3005,10 +3002,10 @@
         <v>59</v>
       </c>
       <c r="I26" s="28" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J26" s="28" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K26" s="46">
         <v>10120042</v>
@@ -3022,13 +3019,13 @@
         <v>101200</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D27" s="21">
         <v>32103</v>
       </c>
       <c r="E27" s="28" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F27" s="28" t="s">
         <v>52</v>
@@ -3040,10 +3037,10 @@
         <v>59</v>
       </c>
       <c r="I27" s="28" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J27" s="28" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K27" s="46">
         <v>10120043</v>
@@ -3057,13 +3054,13 @@
         <v>101200</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D28" s="21">
         <v>32104</v>
       </c>
       <c r="E28" s="28" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F28" s="28" t="s">
         <v>52</v>
@@ -3075,10 +3072,10 @@
         <v>59</v>
       </c>
       <c r="I28" s="28" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J28" s="28" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K28" s="46">
         <v>10120044</v>
@@ -3092,13 +3089,13 @@
         <v>101200</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D29" s="21">
         <v>32105</v>
       </c>
       <c r="E29" s="28" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F29" s="28" t="s">
         <v>52</v>
@@ -3110,10 +3107,10 @@
         <v>59</v>
       </c>
       <c r="I29" s="28" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J29" s="28" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K29" s="46">
         <v>10120045</v>
@@ -3127,13 +3124,13 @@
         <v>101200</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D30" s="21">
         <v>32106</v>
       </c>
       <c r="E30" s="28" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F30" s="28" t="s">
         <v>52</v>
@@ -3145,10 +3142,10 @@
         <v>59</v>
       </c>
       <c r="I30" s="28" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J30" s="28" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K30" s="46">
         <v>10120046</v>
@@ -3162,13 +3159,13 @@
         <v>101200</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D31" s="27">
         <v>32201</v>
       </c>
       <c r="E31" s="27" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F31" s="27" t="s">
         <v>52</v>
@@ -3180,7 +3177,7 @@
         <v>59</v>
       </c>
       <c r="I31" s="27" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J31" s="27"/>
       <c r="K31" s="47">
@@ -3195,13 +3192,13 @@
         <v>101200</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D32" s="27">
         <v>32202</v>
       </c>
       <c r="E32" s="27" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F32" s="27" t="s">
         <v>52</v>
@@ -3213,7 +3210,7 @@
         <v>59</v>
       </c>
       <c r="I32" s="27" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J32" s="27"/>
       <c r="K32" s="47">
@@ -3228,13 +3225,13 @@
         <v>101200</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D33" s="27">
         <v>32203</v>
       </c>
       <c r="E33" s="27" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F33" s="27" t="s">
         <v>52</v>
@@ -3246,7 +3243,7 @@
         <v>59</v>
       </c>
       <c r="I33" s="27" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J33" s="27"/>
       <c r="K33" s="47">
@@ -3261,13 +3258,13 @@
         <v>101200</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D34" s="27">
         <v>32204</v>
       </c>
       <c r="E34" s="27" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F34" s="27" t="s">
         <v>52</v>
@@ -3279,7 +3276,7 @@
         <v>59</v>
       </c>
       <c r="I34" s="27" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J34" s="27"/>
       <c r="K34" s="47">
@@ -3294,13 +3291,13 @@
         <v>101200</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D35" s="27">
         <v>32205</v>
       </c>
       <c r="E35" s="27" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F35" s="27" t="s">
         <v>52</v>
@@ -3312,7 +3309,7 @@
         <v>59</v>
       </c>
       <c r="I35" s="27" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J35" s="27"/>
       <c r="K35" s="47">
@@ -3327,13 +3324,13 @@
         <v>101200</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D36" s="27">
         <v>32206</v>
       </c>
       <c r="E36" s="27" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F36" s="27" t="s">
         <v>52</v>
@@ -3345,7 +3342,7 @@
         <v>59</v>
       </c>
       <c r="I36" s="27" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J36" s="27"/>
       <c r="K36" s="47">
@@ -3516,10 +3513,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B1" t="s">
         <v>91</v>
-      </c>
-      <c r="B1" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -3527,7 +3524,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3535,7 +3532,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:8">
@@ -3543,16 +3540,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
+        <v>94</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:8">
@@ -3560,16 +3557,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>98</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:8">
@@ -3577,16 +3574,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
       </c>
       <c r="G6" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:8">
@@ -3594,16 +3591,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F7" s="1">
         <v>2</v>
       </c>
       <c r="G7" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="H7" s="1" t="s">
         <v>104</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:8">
@@ -3611,16 +3608,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F8" s="1">
         <v>3</v>
       </c>
       <c r="G8" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H8" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:8">
@@ -3628,16 +3625,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F9" s="1">
         <v>4</v>
       </c>
       <c r="G9" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="H9" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:8">
@@ -3645,16 +3642,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F10" s="1">
         <v>5</v>
       </c>
       <c r="G10" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H10" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:8">
@@ -3662,16 +3659,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F11" s="1">
         <v>6</v>
       </c>
       <c r="G11" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="H11" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:8">
@@ -3679,16 +3676,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F12" s="1">
         <v>7</v>
       </c>
       <c r="G12" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="H12" s="1" t="s">
         <v>119</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:8">
@@ -3696,16 +3693,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F13" s="1">
         <v>8</v>
       </c>
       <c r="G13" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="H13" s="1" t="s">
         <v>122</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:8">
@@ -3713,16 +3710,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F14" s="1">
         <v>9</v>
       </c>
       <c r="G14" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="H14" s="1" t="s">
         <v>125</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:8">
@@ -3730,16 +3727,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F15" s="1">
         <v>10</v>
       </c>
       <c r="G15" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="H15" s="1" t="s">
         <v>128</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:8">
@@ -3747,16 +3744,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F16" s="1">
         <v>11</v>
       </c>
       <c r="G16" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="H16" s="1" t="s">
         <v>131</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:8">
@@ -3764,16 +3761,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F17" s="1">
         <v>12</v>
       </c>
       <c r="G17" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="H17" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:8">
@@ -3781,16 +3778,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F18" s="1">
         <v>13</v>
       </c>
       <c r="G18" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="H18" s="1" t="s">
         <v>137</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:8">
@@ -3798,16 +3795,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F19" s="1">
         <v>14</v>
       </c>
       <c r="G19" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="H19" s="1" t="s">
         <v>140</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:8">
@@ -3815,16 +3812,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F20" s="1">
         <v>15</v>
       </c>
       <c r="G20" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="H20" s="1" t="s">
         <v>143</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:8">
@@ -3832,16 +3829,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F21" s="1">
         <v>16</v>
       </c>
       <c r="G21" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="H21" s="1" t="s">
         <v>146</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:8">
@@ -3849,16 +3846,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F22" s="1">
         <v>17</v>
       </c>
       <c r="G22" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="H22" s="1" t="s">
         <v>149</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:8">
@@ -3866,16 +3863,16 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F23" s="1">
         <v>18</v>
       </c>
       <c r="G23" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="H23" s="1" t="s">
         <v>152</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:8">
@@ -3883,16 +3880,16 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F24" s="1">
         <v>19</v>
       </c>
       <c r="G24" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="H24" s="1" t="s">
         <v>155</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -3900,7 +3897,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -3908,7 +3905,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -3916,7 +3913,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -3924,7 +3921,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -3932,7 +3929,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -3940,7 +3937,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -3948,7 +3945,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -3956,7 +3953,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -3964,7 +3961,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -3972,7 +3969,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -3980,7 +3977,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -3988,7 +3985,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -3996,7 +3993,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -4004,7 +4001,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -4012,7 +4009,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -4020,7 +4017,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -4028,7 +4025,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -4036,7 +4033,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -4044,7 +4041,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -4052,7 +4049,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -4060,7 +4057,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -4068,7 +4065,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -4076,7 +4073,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialAuxiliary.xlsx
+++ b/slots/resources/sample/SpecialAuxiliary.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialAuxiliary" sheetId="1" r:id="rId1"/>
@@ -268,7 +268,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="180">
   <si>
     <t>小游戏模式ID</t>
   </si>
@@ -508,6 +508,9 @@
   </si>
   <si>
     <t>免费游戏</t>
+  </si>
+  <si>
+    <t>10070030|10070012</t>
   </si>
   <si>
     <t>麻将胡了-免费旋转-14次</t>
@@ -990,13 +993,26 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1008,20 +1024,7 @@
     </font>
     <font>
       <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
+      <sz val="18"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2699,7 +2702,9 @@
       <c r="I17" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="K17" s="44"/>
+      <c r="K17" s="44" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="18" s="3" customFormat="1" ht="16.5" spans="1:11">
       <c r="A18" s="9">
@@ -2715,10 +2720,10 @@
         <v>34002</v>
       </c>
       <c r="E18" s="19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F18" s="19" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G18" s="16">
         <v>2007001</v>
@@ -2729,7 +2734,9 @@
       <c r="I18" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="K18" s="44"/>
+      <c r="K18" s="44" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="19" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A19" s="21">
@@ -2739,13 +2746,13 @@
         <v>101200</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D19" s="21">
         <v>32001</v>
       </c>
       <c r="E19" s="21" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F19" s="21" t="s">
         <v>52</v>
@@ -2757,10 +2764,10 @@
         <v>59</v>
       </c>
       <c r="I19" s="21" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J19" s="21" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K19" s="45">
         <v>10120041</v>
@@ -2774,13 +2781,13 @@
         <v>101200</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D20" s="21">
         <v>32002</v>
       </c>
       <c r="E20" s="21" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F20" s="21" t="s">
         <v>52</v>
@@ -2792,10 +2799,10 @@
         <v>59</v>
       </c>
       <c r="I20" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="J20" s="21" t="s">
         <v>85</v>
-      </c>
-      <c r="J20" s="21" t="s">
-        <v>84</v>
       </c>
       <c r="K20" s="45">
         <v>10120042</v>
@@ -2809,13 +2816,13 @@
         <v>101200</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D21" s="21">
         <v>32003</v>
       </c>
       <c r="E21" s="21" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F21" s="21" t="s">
         <v>52</v>
@@ -2827,10 +2834,10 @@
         <v>59</v>
       </c>
       <c r="I21" s="21" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J21" s="21" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K21" s="45">
         <v>10120043</v>
@@ -2844,13 +2851,13 @@
         <v>101200</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D22" s="21">
         <v>32004</v>
       </c>
       <c r="E22" s="21" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F22" s="21" t="s">
         <v>52</v>
@@ -2862,10 +2869,10 @@
         <v>59</v>
       </c>
       <c r="I22" s="21" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J22" s="21" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K22" s="45">
         <v>10120044</v>
@@ -2879,13 +2886,13 @@
         <v>101200</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D23" s="21">
         <v>32005</v>
       </c>
       <c r="E23" s="21" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F23" s="21" t="s">
         <v>52</v>
@@ -2897,10 +2904,10 @@
         <v>59</v>
       </c>
       <c r="I23" s="21" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J23" s="21" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K23" s="45">
         <v>10120045</v>
@@ -2914,13 +2921,13 @@
         <v>101200</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D24" s="21">
         <v>32006</v>
       </c>
       <c r="E24" s="21" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F24" s="21" t="s">
         <v>52</v>
@@ -2932,10 +2939,10 @@
         <v>59</v>
       </c>
       <c r="I24" s="21" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J24" s="21" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K24" s="45">
         <v>10120046</v>
@@ -2949,13 +2956,13 @@
         <v>101200</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D25" s="21">
         <v>32101</v>
       </c>
       <c r="E25" s="28" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F25" s="28" t="s">
         <v>52</v>
@@ -2967,10 +2974,10 @@
         <v>59</v>
       </c>
       <c r="I25" s="28" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J25" s="28" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K25" s="46">
         <v>10120041</v>
@@ -2984,13 +2991,13 @@
         <v>101200</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D26" s="21">
         <v>32102</v>
       </c>
       <c r="E26" s="28" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F26" s="28" t="s">
         <v>52</v>
@@ -3002,10 +3009,10 @@
         <v>59</v>
       </c>
       <c r="I26" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="J26" s="28" t="s">
         <v>85</v>
-      </c>
-      <c r="J26" s="28" t="s">
-        <v>84</v>
       </c>
       <c r="K26" s="46">
         <v>10120042</v>
@@ -3019,13 +3026,13 @@
         <v>101200</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D27" s="21">
         <v>32103</v>
       </c>
       <c r="E27" s="28" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F27" s="28" t="s">
         <v>52</v>
@@ -3037,10 +3044,10 @@
         <v>59</v>
       </c>
       <c r="I27" s="28" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J27" s="28" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K27" s="46">
         <v>10120043</v>
@@ -3054,13 +3061,13 @@
         <v>101200</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D28" s="21">
         <v>32104</v>
       </c>
       <c r="E28" s="28" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F28" s="28" t="s">
         <v>52</v>
@@ -3072,10 +3079,10 @@
         <v>59</v>
       </c>
       <c r="I28" s="28" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J28" s="28" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K28" s="46">
         <v>10120044</v>
@@ -3089,13 +3096,13 @@
         <v>101200</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D29" s="21">
         <v>32105</v>
       </c>
       <c r="E29" s="28" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F29" s="28" t="s">
         <v>52</v>
@@ -3107,10 +3114,10 @@
         <v>59</v>
       </c>
       <c r="I29" s="28" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J29" s="28" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K29" s="46">
         <v>10120045</v>
@@ -3124,13 +3131,13 @@
         <v>101200</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D30" s="21">
         <v>32106</v>
       </c>
       <c r="E30" s="28" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F30" s="28" t="s">
         <v>52</v>
@@ -3142,10 +3149,10 @@
         <v>59</v>
       </c>
       <c r="I30" s="28" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J30" s="28" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K30" s="46">
         <v>10120046</v>
@@ -3159,13 +3166,13 @@
         <v>101200</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D31" s="27">
         <v>32201</v>
       </c>
       <c r="E31" s="27" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F31" s="27" t="s">
         <v>52</v>
@@ -3177,7 +3184,7 @@
         <v>59</v>
       </c>
       <c r="I31" s="27" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J31" s="27"/>
       <c r="K31" s="47">
@@ -3192,13 +3199,13 @@
         <v>101200</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D32" s="27">
         <v>32202</v>
       </c>
       <c r="E32" s="27" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F32" s="27" t="s">
         <v>52</v>
@@ -3210,7 +3217,7 @@
         <v>59</v>
       </c>
       <c r="I32" s="27" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J32" s="27"/>
       <c r="K32" s="47">
@@ -3225,13 +3232,13 @@
         <v>101200</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D33" s="27">
         <v>32203</v>
       </c>
       <c r="E33" s="27" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F33" s="27" t="s">
         <v>52</v>
@@ -3243,7 +3250,7 @@
         <v>59</v>
       </c>
       <c r="I33" s="27" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J33" s="27"/>
       <c r="K33" s="47">
@@ -3258,13 +3265,13 @@
         <v>101200</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D34" s="27">
         <v>32204</v>
       </c>
       <c r="E34" s="27" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F34" s="27" t="s">
         <v>52</v>
@@ -3276,7 +3283,7 @@
         <v>59</v>
       </c>
       <c r="I34" s="27" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J34" s="27"/>
       <c r="K34" s="47">
@@ -3291,13 +3298,13 @@
         <v>101200</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D35" s="27">
         <v>32205</v>
       </c>
       <c r="E35" s="27" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F35" s="27" t="s">
         <v>52</v>
@@ -3309,7 +3316,7 @@
         <v>59</v>
       </c>
       <c r="I35" s="27" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J35" s="27"/>
       <c r="K35" s="47">
@@ -3324,13 +3331,13 @@
         <v>101200</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D36" s="27">
         <v>32206</v>
       </c>
       <c r="E36" s="27" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F36" s="27" t="s">
         <v>52</v>
@@ -3342,7 +3349,7 @@
         <v>59</v>
       </c>
       <c r="I36" s="27" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J36" s="27"/>
       <c r="K36" s="47">
@@ -3513,10 +3520,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -3524,7 +3531,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3532,7 +3539,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:8">
@@ -3540,16 +3547,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:8">
@@ -3557,16 +3564,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:8">
@@ -3574,16 +3581,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:8">
@@ -3591,16 +3598,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F7" s="1">
         <v>2</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:8">
@@ -3608,16 +3615,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F8" s="1">
         <v>3</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:8">
@@ -3625,16 +3632,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F9" s="1">
         <v>4</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:8">
@@ -3642,16 +3649,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F10" s="1">
         <v>5</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:8">
@@ -3659,16 +3666,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F11" s="1">
         <v>6</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:8">
@@ -3676,16 +3683,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F12" s="1">
         <v>7</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:8">
@@ -3693,16 +3700,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F13" s="1">
         <v>8</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:8">
@@ -3710,16 +3717,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F14" s="1">
         <v>9</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:8">
@@ -3727,16 +3734,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F15" s="1">
         <v>10</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:8">
@@ -3744,16 +3751,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F16" s="1">
         <v>11</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:8">
@@ -3761,16 +3768,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F17" s="1">
         <v>12</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:8">
@@ -3778,16 +3785,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F18" s="1">
         <v>13</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:8">
@@ -3795,16 +3802,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F19" s="1">
         <v>14</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:8">
@@ -3812,16 +3819,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F20" s="1">
         <v>15</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:8">
@@ -3829,16 +3836,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F21" s="1">
         <v>16</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:8">
@@ -3846,16 +3853,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F22" s="1">
         <v>17</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:8">
@@ -3863,16 +3870,16 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F23" s="1">
         <v>18</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:8">
@@ -3880,16 +3887,16 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F24" s="1">
         <v>19</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -3897,7 +3904,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -3905,7 +3912,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -3913,7 +3920,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -3921,7 +3928,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -3929,7 +3936,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -3937,7 +3944,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -3945,7 +3952,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -3953,7 +3960,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -3961,7 +3968,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -3969,7 +3976,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -3977,7 +3984,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -3985,7 +3992,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -3993,7 +4000,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -4001,7 +4008,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -4009,7 +4016,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -4017,7 +4024,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -4025,7 +4032,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -4033,7 +4040,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -4041,7 +4048,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -4049,7 +4056,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -4057,7 +4064,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -4065,7 +4072,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -4073,7 +4080,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialAuxiliary.xlsx
+++ b/slots/resources/sample/SpecialAuxiliary.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialAuxiliary" sheetId="1" r:id="rId1"/>
@@ -268,7 +268,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="181">
   <si>
     <t>小游戏模式ID</t>
   </si>
@@ -538,6 +538,9 @@
   </si>
   <si>
     <t>财神-第2次</t>
+  </si>
+  <si>
+    <t>10120061_1|10120062_1|10120063_1|10120064_1|10120065_1|10120066_1</t>
   </si>
   <si>
     <t>财神-第3次</t>
@@ -988,12 +991,6 @@
     <font>
       <b/>
       <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1005,13 +1002,19 @@
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <b/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1993,7 +1996,8 @@
     <col min="6" max="6" width="15.125" customWidth="1"/>
     <col min="7" max="7" width="9.875" customWidth="1"/>
     <col min="8" max="8" width="16.25" customWidth="1"/>
-    <col min="9" max="10" width="29.375" customWidth="1"/>
+    <col min="9" max="9" width="29.375" customWidth="1"/>
+    <col min="10" max="10" width="42.5" customWidth="1"/>
     <col min="11" max="11" width="41.25" style="7" customWidth="1"/>
     <col min="12" max="12" width="11.75" style="3" customWidth="1"/>
     <col min="13" max="13" width="34.4083333333333" style="3" customWidth="1"/>
@@ -2977,7 +2981,7 @@
         <v>84</v>
       </c>
       <c r="J25" s="28" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="K25" s="46">
         <v>10120041</v>
@@ -3012,7 +3016,7 @@
         <v>86</v>
       </c>
       <c r="J26" s="28" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="K26" s="46">
         <v>10120042</v>
@@ -3047,7 +3051,7 @@
         <v>87</v>
       </c>
       <c r="J27" s="28" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="K27" s="46">
         <v>10120043</v>
@@ -3082,7 +3086,7 @@
         <v>88</v>
       </c>
       <c r="J28" s="28" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="K28" s="46">
         <v>10120044</v>
@@ -3117,7 +3121,7 @@
         <v>88</v>
       </c>
       <c r="J29" s="28" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="K29" s="46">
         <v>10120045</v>
@@ -3152,7 +3156,7 @@
         <v>88</v>
       </c>
       <c r="J30" s="28" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="K30" s="46">
         <v>10120046</v>
@@ -3166,7 +3170,7 @@
         <v>101200</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D31" s="27">
         <v>32201</v>
@@ -3199,7 +3203,7 @@
         <v>101200</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D32" s="27">
         <v>32202</v>
@@ -3232,7 +3236,7 @@
         <v>101200</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D33" s="27">
         <v>32203</v>
@@ -3265,7 +3269,7 @@
         <v>101200</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D34" s="27">
         <v>32204</v>
@@ -3298,7 +3302,7 @@
         <v>101200</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D35" s="27">
         <v>32205</v>
@@ -3331,7 +3335,7 @@
         <v>101200</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D36" s="27">
         <v>32206</v>
@@ -3520,10 +3524,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -3531,7 +3535,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3539,7 +3543,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:8">
@@ -3547,16 +3551,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:8">
@@ -3564,16 +3568,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:8">
@@ -3581,16 +3585,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:8">
@@ -3598,16 +3602,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F7" s="1">
         <v>2</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:8">
@@ -3615,16 +3619,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F8" s="1">
         <v>3</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:8">
@@ -3632,16 +3636,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F9" s="1">
         <v>4</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:8">
@@ -3649,16 +3653,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F10" s="1">
         <v>5</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:8">
@@ -3666,16 +3670,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F11" s="1">
         <v>6</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:8">
@@ -3683,16 +3687,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F12" s="1">
         <v>7</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:8">
@@ -3700,16 +3704,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F13" s="1">
         <v>8</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:8">
@@ -3717,16 +3721,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F14" s="1">
         <v>9</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:8">
@@ -3734,16 +3738,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F15" s="1">
         <v>10</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:8">
@@ -3751,16 +3755,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F16" s="1">
         <v>11</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:8">
@@ -3768,16 +3772,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F17" s="1">
         <v>12</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:8">
@@ -3785,16 +3789,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F18" s="1">
         <v>13</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:8">
@@ -3802,16 +3806,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F19" s="1">
         <v>14</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:8">
@@ -3819,16 +3823,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F20" s="1">
         <v>15</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:8">
@@ -3836,16 +3840,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F21" s="1">
         <v>16</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:8">
@@ -3853,16 +3857,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F22" s="1">
         <v>17</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:8">
@@ -3870,16 +3874,16 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F23" s="1">
         <v>18</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:8">
@@ -3887,16 +3891,16 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F24" s="1">
         <v>19</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -3904,7 +3908,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -3912,7 +3916,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -3920,7 +3924,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -3928,7 +3932,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -3936,7 +3940,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -3944,7 +3948,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -3952,7 +3956,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -3960,7 +3964,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -3968,7 +3972,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -3976,7 +3980,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -3984,7 +3988,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -3992,7 +3996,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -4000,7 +4004,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -4008,7 +4012,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -4016,7 +4020,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -4024,7 +4028,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -4032,7 +4036,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -4040,7 +4044,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -4048,7 +4052,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -4056,7 +4060,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -4064,7 +4068,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -4072,7 +4076,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -4080,7 +4084,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialAuxiliary.xlsx
+++ b/slots/resources/sample/SpecialAuxiliary.xlsx
@@ -510,7 +510,7 @@
     <t>免费游戏</t>
   </si>
   <si>
-    <t>10070030|10070012</t>
+    <t>10070030|10070010</t>
   </si>
   <si>
     <t>麻将胡了-免费旋转-14次</t>

--- a/slots/resources/sample/SpecialAuxiliary.xlsx
+++ b/slots/resources/sample/SpecialAuxiliary.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialAuxiliary" sheetId="1" r:id="rId1"/>
@@ -510,7 +510,7 @@
     <t>免费游戏</t>
   </si>
   <si>
-    <t>10070030|10070010</t>
+    <t>10070031|10070032|10070033|10070034|10070035|10070036|10070037|10070038|10070010</t>
   </si>
   <si>
     <t>麻将胡了-免费旋转-14次</t>
@@ -989,13 +989,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1007,6 +1000,7 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
@@ -1021,6 +1015,12 @@
     </font>
     <font>
       <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/slots/resources/sample/SpecialAuxiliary.xlsx
+++ b/slots/resources/sample/SpecialAuxiliary.xlsx
@@ -268,7 +268,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="183">
   <si>
     <t>小游戏模式ID</t>
   </si>
@@ -544,6 +544,12 @@
   </si>
   <si>
     <t>财神-第3次</t>
+  </si>
+  <si>
+    <t>10240021|10240022|10240023|10240024|10240025</t>
+  </si>
+  <si>
+    <t>10240031|10240032</t>
   </si>
   <si>
     <t>typeID</t>
@@ -989,19 +995,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1014,7 +1019,8 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
+      <b/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -3360,64 +3366,519 @@
         <v>10120046</v>
       </c>
     </row>
-    <row r="37" ht="16.5" spans="19:22">
-      <c r="S37"/>
-      <c r="U37" s="1"/>
-      <c r="V37" s="1"/>
-    </row>
-    <row r="38" ht="16.5" spans="19:22">
-      <c r="S38"/>
-      <c r="U38" s="1"/>
-      <c r="V38" s="1"/>
-    </row>
-    <row r="39" ht="16.5" spans="19:22">
-      <c r="S39"/>
-      <c r="U39" s="1"/>
-      <c r="V39" s="1"/>
-    </row>
-    <row r="40" ht="16.5" spans="19:22">
-      <c r="S40"/>
-      <c r="U40" s="1"/>
-      <c r="V40" s="1"/>
-    </row>
-    <row r="41" ht="16.5" spans="19:22">
-      <c r="S41"/>
-      <c r="U41" s="1"/>
-      <c r="V41" s="1"/>
-    </row>
-    <row r="42" ht="16.5" spans="19:22">
-      <c r="S42"/>
-      <c r="U42" s="1"/>
-      <c r="V42" s="1"/>
-    </row>
-    <row r="43" ht="16.5" spans="19:22">
-      <c r="S43"/>
-      <c r="U43" s="1"/>
-      <c r="V43" s="1"/>
-    </row>
-    <row r="44" ht="16.5" spans="19:22">
-      <c r="S44"/>
-      <c r="U44" s="1"/>
-      <c r="V44" s="1"/>
-    </row>
-    <row r="45" ht="16.5" spans="19:22">
-      <c r="S45"/>
-      <c r="V45" s="1"/>
-    </row>
-    <row r="46" ht="16.5" spans="19:22">
-      <c r="S46"/>
-      <c r="U46" s="1"/>
-      <c r="V46" s="1"/>
-    </row>
-    <row r="47" ht="16.5" spans="19:22">
-      <c r="S47"/>
-      <c r="U47" s="1"/>
-      <c r="V47" s="1"/>
-    </row>
-    <row r="48" ht="16.5" spans="19:22">
-      <c r="S48"/>
-      <c r="U48" s="1"/>
-      <c r="V48" s="1"/>
+    <row r="37" s="3" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A37" s="14">
+        <v>30240001</v>
+      </c>
+      <c r="B37" s="15">
+        <v>102400</v>
+      </c>
+      <c r="C37" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D37" s="14">
+        <v>32401</v>
+      </c>
+      <c r="E37" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="F37" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="G37" s="14"/>
+      <c r="H37" s="14"/>
+      <c r="I37" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="J37" s="14"/>
+      <c r="K37" s="38"/>
+      <c r="L37" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="M37" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="N37" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="O37" s="14"/>
+      <c r="P37" s="14"/>
+      <c r="Q37" s="49" t="s">
+        <v>38</v>
+      </c>
+      <c r="R37" s="50" t="s">
+        <v>39</v>
+      </c>
+      <c r="S37" s="51" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="38" s="3" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A38" s="14">
+        <v>30240002</v>
+      </c>
+      <c r="B38" s="15">
+        <v>102400</v>
+      </c>
+      <c r="C38" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D38" s="14">
+        <v>32402</v>
+      </c>
+      <c r="E38" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="F38" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="G38" s="14"/>
+      <c r="H38" s="14"/>
+      <c r="I38" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="J38" s="14"/>
+      <c r="K38" s="38"/>
+      <c r="L38" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="M38" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="N38" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="O38" s="14"/>
+      <c r="P38" s="14"/>
+      <c r="Q38" s="49" t="s">
+        <v>43</v>
+      </c>
+      <c r="R38" s="50" t="s">
+        <v>39</v>
+      </c>
+      <c r="S38" s="51"/>
+    </row>
+    <row r="39" s="3" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A39" s="14">
+        <v>30240003</v>
+      </c>
+      <c r="B39" s="15">
+        <v>102400</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D39" s="14">
+        <v>32403</v>
+      </c>
+      <c r="E39" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="F39" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="G39" s="14"/>
+      <c r="H39" s="14"/>
+      <c r="I39" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="J39" s="14"/>
+      <c r="K39" s="38"/>
+      <c r="L39" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="M39" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="N39" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="O39" s="14"/>
+      <c r="P39" s="14"/>
+      <c r="Q39" s="49" t="s">
+        <v>46</v>
+      </c>
+      <c r="R39" s="50" t="s">
+        <v>39</v>
+      </c>
+      <c r="S39" s="51"/>
+    </row>
+    <row r="40" s="3" customFormat="1" ht="15" customHeight="1" spans="1:19">
+      <c r="A40" s="14">
+        <v>30240004</v>
+      </c>
+      <c r="B40" s="15">
+        <v>102400</v>
+      </c>
+      <c r="C40" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D40" s="14">
+        <v>32404</v>
+      </c>
+      <c r="E40" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="F40" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="G40" s="14"/>
+      <c r="H40" s="14"/>
+      <c r="I40" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="J40" s="14"/>
+      <c r="K40" s="38"/>
+      <c r="L40" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="M40" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="N40" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="O40" s="14"/>
+      <c r="P40" s="14"/>
+      <c r="Q40" s="49" t="s">
+        <v>49</v>
+      </c>
+      <c r="R40" s="50" t="s">
+        <v>39</v>
+      </c>
+      <c r="S40" s="51"/>
+    </row>
+    <row r="41" s="3" customFormat="1" ht="15" customHeight="1" spans="1:19">
+      <c r="A41" s="9">
+        <v>30240005</v>
+      </c>
+      <c r="B41" s="16">
+        <v>102400</v>
+      </c>
+      <c r="C41" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D41" s="9">
+        <v>32411</v>
+      </c>
+      <c r="E41" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="G41" s="9"/>
+      <c r="H41" s="9"/>
+      <c r="I41" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="J41" s="9"/>
+      <c r="K41" s="32"/>
+      <c r="L41" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="M41" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="N41" s="9"/>
+      <c r="O41" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="P41" s="9"/>
+      <c r="Q41" s="11"/>
+      <c r="R41" s="11"/>
+      <c r="S41" s="51"/>
+    </row>
+    <row r="42" s="3" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A42" s="17">
+        <v>30240006</v>
+      </c>
+      <c r="B42" s="18">
+        <v>102400</v>
+      </c>
+      <c r="C42" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D42" s="17">
+        <v>32421</v>
+      </c>
+      <c r="E42" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="F42" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="G42" s="17"/>
+      <c r="H42" s="17"/>
+      <c r="I42" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="J42" s="17"/>
+      <c r="K42" s="39"/>
+      <c r="L42" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="M42" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="N42" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="O42" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="P42" s="17"/>
+      <c r="Q42" s="17"/>
+      <c r="R42" s="9"/>
+      <c r="S42" s="51"/>
+    </row>
+    <row r="43" s="3" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A43" s="19">
+        <v>30240007</v>
+      </c>
+      <c r="B43" s="20">
+        <v>102400</v>
+      </c>
+      <c r="C43" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D43" s="21">
+        <v>32431</v>
+      </c>
+      <c r="E43" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="F43" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="G43" s="19">
+        <v>2024001</v>
+      </c>
+      <c r="H43" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="I43" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="J43" s="19"/>
+      <c r="K43" s="40">
+        <v>10240091</v>
+      </c>
+      <c r="L43" s="19"/>
+      <c r="M43" s="19"/>
+      <c r="N43" s="19"/>
+      <c r="O43" s="19"/>
+      <c r="P43" s="19"/>
+      <c r="Q43" s="19"/>
+      <c r="R43" s="9"/>
+      <c r="S43" s="51"/>
+    </row>
+    <row r="44" s="3" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A44" s="22">
+        <v>30240008</v>
+      </c>
+      <c r="B44" s="23">
+        <v>102400</v>
+      </c>
+      <c r="C44" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D44" s="21">
+        <v>32432</v>
+      </c>
+      <c r="E44" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="F44" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="G44" s="22">
+        <v>2024001</v>
+      </c>
+      <c r="H44" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="I44" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="J44" s="22"/>
+      <c r="K44" s="41" t="s">
+        <v>92</v>
+      </c>
+      <c r="L44" s="22"/>
+      <c r="M44" s="22"/>
+      <c r="N44" s="22"/>
+      <c r="O44" s="22"/>
+      <c r="P44" s="22"/>
+      <c r="Q44" s="22"/>
+      <c r="R44" s="9"/>
+      <c r="S44" s="51"/>
+    </row>
+    <row r="45" s="3" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A45" s="24">
+        <v>30240009</v>
+      </c>
+      <c r="B45" s="25">
+        <v>102400</v>
+      </c>
+      <c r="C45" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D45" s="21">
+        <v>32433</v>
+      </c>
+      <c r="E45" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="F45" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="G45" s="24">
+        <v>2024001</v>
+      </c>
+      <c r="H45" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="I45" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="J45" s="24"/>
+      <c r="K45" s="42" t="s">
+        <v>93</v>
+      </c>
+      <c r="L45" s="24"/>
+      <c r="M45" s="24"/>
+      <c r="N45" s="24"/>
+      <c r="O45" s="24"/>
+      <c r="P45" s="24"/>
+      <c r="Q45" s="24"/>
+      <c r="R45" s="9"/>
+      <c r="S45" s="51"/>
+    </row>
+    <row r="46" s="3" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A46" s="21">
+        <v>30240010</v>
+      </c>
+      <c r="B46" s="26">
+        <v>102400</v>
+      </c>
+      <c r="C46" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D46" s="27">
+        <v>32441</v>
+      </c>
+      <c r="E46" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="F46" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="G46" s="21"/>
+      <c r="H46" s="21"/>
+      <c r="I46" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="J46" s="21"/>
+      <c r="K46" s="43"/>
+      <c r="L46" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="M46" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="N46" s="21"/>
+      <c r="O46" s="21"/>
+      <c r="P46" s="21"/>
+      <c r="Q46" s="52" t="s">
+        <v>70</v>
+      </c>
+      <c r="R46" s="53" t="s">
+        <v>71</v>
+      </c>
+      <c r="S46" s="11" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="47" s="3" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A47" s="24">
+        <v>30240011</v>
+      </c>
+      <c r="B47" s="25">
+        <v>102400</v>
+      </c>
+      <c r="C47" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D47" s="27">
+        <v>32442</v>
+      </c>
+      <c r="E47" s="27" t="s">
+        <v>73</v>
+      </c>
+      <c r="F47" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="G47" s="24"/>
+      <c r="H47" s="24"/>
+      <c r="I47" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="J47" s="24"/>
+      <c r="K47" s="42"/>
+      <c r="L47" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="M47" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="N47" s="24"/>
+      <c r="O47" s="24"/>
+      <c r="P47" s="24"/>
+      <c r="Q47" s="24"/>
+      <c r="R47" s="9"/>
+      <c r="S47" s="51"/>
+    </row>
+    <row r="48" s="3" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A48" s="24">
+        <v>30240012</v>
+      </c>
+      <c r="B48" s="25">
+        <v>102400</v>
+      </c>
+      <c r="C48" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D48" s="27">
+        <v>32443</v>
+      </c>
+      <c r="E48" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="F48" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="G48" s="24">
+        <v>2024001</v>
+      </c>
+      <c r="H48" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="I48" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="J48" s="24"/>
+      <c r="K48" s="42" t="s">
+        <v>93</v>
+      </c>
+      <c r="L48" s="24"/>
+      <c r="M48" s="24"/>
+      <c r="N48" s="24"/>
+      <c r="O48" s="24"/>
+      <c r="P48" s="24"/>
+      <c r="Q48" s="24"/>
+      <c r="R48" s="9"/>
+      <c r="S48" s="51"/>
     </row>
     <row r="49" ht="16.5" spans="19:22">
       <c r="S49"/>
@@ -3524,10 +3985,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -3535,7 +3996,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3543,7 +4004,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:8">
@@ -3551,16 +4012,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:8">
@@ -3568,16 +4029,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:8">
@@ -3585,16 +4046,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:8">
@@ -3602,16 +4063,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F7" s="1">
         <v>2</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:8">
@@ -3619,16 +4080,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F8" s="1">
         <v>3</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:8">
@@ -3636,16 +4097,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F9" s="1">
         <v>4</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:8">
@@ -3653,16 +4114,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F10" s="1">
         <v>5</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:8">
@@ -3670,16 +4131,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F11" s="1">
         <v>6</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:8">
@@ -3687,16 +4148,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F12" s="1">
         <v>7</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:8">
@@ -3704,16 +4165,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F13" s="1">
         <v>8</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:8">
@@ -3721,16 +4182,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F14" s="1">
         <v>9</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:8">
@@ -3738,16 +4199,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F15" s="1">
         <v>10</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:8">
@@ -3755,16 +4216,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F16" s="1">
         <v>11</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:8">
@@ -3772,16 +4233,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F17" s="1">
         <v>12</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:8">
@@ -3789,16 +4250,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F18" s="1">
         <v>13</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:8">
@@ -3806,16 +4267,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F19" s="1">
         <v>14</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:8">
@@ -3823,16 +4284,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F20" s="1">
         <v>15</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:8">
@@ -3840,16 +4301,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F21" s="1">
         <v>16</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:8">
@@ -3857,16 +4318,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F22" s="1">
         <v>17</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:8">
@@ -3874,16 +4335,16 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F23" s="1">
         <v>18</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:8">
@@ -3891,16 +4352,16 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F24" s="1">
         <v>19</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -3908,7 +4369,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -3916,7 +4377,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -3924,7 +4385,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -3932,7 +4393,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -3940,7 +4401,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -3948,7 +4409,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -3956,7 +4417,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -3964,7 +4425,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -3972,7 +4433,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -3980,7 +4441,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -3988,7 +4449,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -3996,7 +4457,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -4004,7 +4465,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -4012,7 +4473,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -4020,7 +4481,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -4028,7 +4489,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -4036,7 +4497,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -4044,7 +4505,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -4052,7 +4513,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -4060,7 +4521,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -4068,7 +4529,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -4076,7 +4537,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -4084,7 +4545,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialAuxiliary.xlsx
+++ b/slots/resources/sample/SpecialAuxiliary.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialAuxiliary" sheetId="1" r:id="rId1"/>
@@ -268,7 +268,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="193">
   <si>
     <t>小游戏模式ID</t>
   </si>
@@ -550,6 +550,36 @@
   </si>
   <si>
     <t>10240031|10240032</t>
+  </si>
+  <si>
+    <t>圣诞狂欢夜</t>
+  </si>
+  <si>
+    <t>圣诞狂欢夜-免费旋转-12次</t>
+  </si>
+  <si>
+    <t>10170031|10170032|10170033|10170034|10170035|10170036|10170037|10170038|10170010</t>
+  </si>
+  <si>
+    <t>圣诞狂欢夜-免费旋转-14次</t>
+  </si>
+  <si>
+    <t>雷神</t>
+  </si>
+  <si>
+    <t>冰冻玩法</t>
+  </si>
+  <si>
+    <t>10220011|10220099|10220012</t>
+  </si>
+  <si>
+    <t>改百搭图案出现概率</t>
+  </si>
+  <si>
+    <t>火焰玩法</t>
+  </si>
+  <si>
+    <t>10220021|10220099|10220012</t>
   </si>
   <si>
     <t>typeID</t>
@@ -1006,12 +1036,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1027,6 +1051,12 @@
     </font>
     <font>
       <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1066,6 +1096,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1091,12 +1127,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1559,107 +1589,107 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
+    <xf numFmtId="49" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="176" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="52">
@@ -2017,7 +2047,7 @@
     <col min="21" max="22" width="11.5"/>
   </cols>
   <sheetData>
-    <row r="1" s="3" customFormat="1" ht="16.5" spans="1:18">
+    <row r="1" s="3" customFormat="1" ht="16.5" spans="1:19">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2039,10 +2069,10 @@
       <c r="I1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="31" t="s">
+      <c r="J1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="32" t="s">
+      <c r="K1" s="11" t="s">
         <v>7</v>
       </c>
       <c r="L1" s="9"/>
@@ -2050,21 +2080,21 @@
         <v>8</v>
       </c>
       <c r="N1" s="9"/>
-      <c r="O1" s="11" t="s">
+      <c r="O1" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="11" t="s">
+      <c r="P1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="Q1" s="11" t="s">
+      <c r="Q1" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="R1" s="48" t="s">
+      <c r="R1" s="13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" s="3" customFormat="1" ht="16.5" spans="1:18">
-      <c r="A2" s="10" t="s">
+    <row r="2" s="3" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A2" s="14" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="9" t="s">
@@ -2075,7 +2105,7 @@
         <v>13</v>
       </c>
       <c r="E2" s="9"/>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="12" t="s">
         <v>14</v>
       </c>
       <c r="G2" s="9" t="s">
@@ -2083,75 +2113,75 @@
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="9"/>
-      <c r="J2" s="33" t="s">
+      <c r="J2" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="34" t="s">
+      <c r="K2" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="L2" s="11"/>
-      <c r="M2" s="33" t="s">
+      <c r="L2" s="12"/>
+      <c r="M2" s="15" t="s">
         <v>14</v>
       </c>
       <c r="N2" s="9"/>
-      <c r="O2" s="11" t="s">
+      <c r="O2" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="P2" s="11" t="s">
+      <c r="P2" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="Q2" s="33" t="s">
+      <c r="Q2" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="R2" s="48" t="s">
+      <c r="R2" s="13" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="3" s="3" customFormat="1" ht="16.5" spans="1:18">
-      <c r="A3" s="10" t="s">
+    <row r="3" s="3" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A3" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12" t="s">
+      <c r="C3" s="17"/>
+      <c r="D3" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12" t="s">
+      <c r="E3" s="17"/>
+      <c r="F3" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="35" t="s">
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="K3" s="36" t="s">
+      <c r="K3" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="L3" s="12"/>
-      <c r="M3" s="12" t="s">
+      <c r="L3" s="17"/>
+      <c r="M3" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="12"/>
-      <c r="O3" s="11" t="s">
+      <c r="N3" s="17"/>
+      <c r="O3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="P3" s="11" t="s">
+      <c r="P3" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="Q3" s="11" t="s">
+      <c r="Q3" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="R3" s="16" t="s">
+      <c r="R3" s="21" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="4" s="3" customFormat="1" ht="16.5" spans="2:18">
+    <row r="4" s="3" customFormat="1" ht="16.5" spans="1:19">
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
@@ -2160,8 +2190,8 @@
       <c r="G4" s="9"/>
       <c r="H4" s="9"/>
       <c r="I4" s="9"/>
-      <c r="J4" s="37"/>
-      <c r="K4" s="32"/>
+      <c r="J4" s="22"/>
+      <c r="K4" s="11"/>
       <c r="L4" s="9"/>
       <c r="M4" s="9"/>
       <c r="N4" s="9"/>
@@ -2171,195 +2201,195 @@
       <c r="R4" s="9"/>
     </row>
     <row r="5" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A5" s="14">
+      <c r="A5" s="23">
         <v>30010001</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="24">
         <v>100100</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="23">
         <v>31001</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F5" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="G5" s="14"/>
-      <c r="H5" s="14"/>
-      <c r="I5" s="14" t="s">
+      <c r="G5" s="23"/>
+      <c r="H5" s="23"/>
+      <c r="I5" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="J5" s="14"/>
-      <c r="K5" s="38"/>
+      <c r="J5" s="23"/>
+      <c r="K5" s="25"/>
       <c r="L5" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="M5" s="14" t="s">
+      <c r="M5" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="N5" s="14" t="s">
+      <c r="N5" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="O5" s="14"/>
-      <c r="P5" s="14"/>
-      <c r="Q5" s="49" t="s">
+      <c r="O5" s="23"/>
+      <c r="P5" s="23"/>
+      <c r="Q5" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="R5" s="50" t="s">
+      <c r="R5" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="S5" s="51" t="s">
+      <c r="S5" s="28" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="6" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A6" s="14">
+      <c r="A6" s="23">
         <v>30010002</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="24">
         <v>100100</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="23">
         <v>31002</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="F6" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14" t="s">
+      <c r="G6" s="23"/>
+      <c r="H6" s="23"/>
+      <c r="I6" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="J6" s="14"/>
-      <c r="K6" s="38"/>
+      <c r="J6" s="23"/>
+      <c r="K6" s="25"/>
       <c r="L6" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="M6" s="14" t="s">
+      <c r="M6" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="N6" s="14" t="s">
+      <c r="N6" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="O6" s="14"/>
-      <c r="P6" s="14"/>
-      <c r="Q6" s="49" t="s">
+      <c r="O6" s="23"/>
+      <c r="P6" s="23"/>
+      <c r="Q6" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="R6" s="50" t="s">
+      <c r="R6" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="S6" s="51"/>
+      <c r="S6" s="28"/>
     </row>
     <row r="7" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A7" s="14">
+      <c r="A7" s="23">
         <v>30010003</v>
       </c>
-      <c r="B7" s="15">
+      <c r="B7" s="24">
         <v>100100</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="23">
         <v>31003</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="E7" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="14" t="s">
+      <c r="G7" s="23"/>
+      <c r="H7" s="23"/>
+      <c r="I7" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="J7" s="14"/>
-      <c r="K7" s="38"/>
+      <c r="J7" s="23"/>
+      <c r="K7" s="25"/>
       <c r="L7" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="M7" s="14" t="s">
+      <c r="M7" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="N7" s="14" t="s">
+      <c r="N7" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="O7" s="14"/>
-      <c r="P7" s="14"/>
-      <c r="Q7" s="49" t="s">
+      <c r="O7" s="23"/>
+      <c r="P7" s="23"/>
+      <c r="Q7" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="R7" s="50" t="s">
+      <c r="R7" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="S7" s="51"/>
+      <c r="S7" s="28"/>
     </row>
     <row r="8" s="3" customFormat="1" ht="15" customHeight="1" spans="1:19">
-      <c r="A8" s="14">
+      <c r="A8" s="23">
         <v>30010004</v>
       </c>
-      <c r="B8" s="15">
+      <c r="B8" s="24">
         <v>100100</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="23">
         <v>31004</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="E8" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="14" t="s">
+      <c r="F8" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="14" t="s">
+      <c r="G8" s="23"/>
+      <c r="H8" s="23"/>
+      <c r="I8" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="J8" s="14"/>
-      <c r="K8" s="38"/>
+      <c r="J8" s="23"/>
+      <c r="K8" s="25"/>
       <c r="L8" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="M8" s="14" t="s">
+      <c r="M8" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="N8" s="14" t="s">
+      <c r="N8" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="O8" s="14"/>
-      <c r="P8" s="14"/>
-      <c r="Q8" s="49" t="s">
+      <c r="O8" s="23"/>
+      <c r="P8" s="23"/>
+      <c r="Q8" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="R8" s="50" t="s">
+      <c r="R8" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="S8" s="51"/>
+      <c r="S8" s="28"/>
     </row>
     <row r="9" s="3" customFormat="1" ht="15" customHeight="1" spans="1:19">
       <c r="A9" s="9">
         <v>30010005</v>
       </c>
-      <c r="B9" s="16">
+      <c r="B9" s="21">
         <v>100100</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="24" t="s">
         <v>31</v>
       </c>
       <c r="D9" s="9">
@@ -2377,7 +2407,7 @@
         <v>51</v>
       </c>
       <c r="J9" s="9"/>
-      <c r="K9" s="32"/>
+      <c r="K9" s="11"/>
       <c r="L9" s="9" t="s">
         <v>35</v>
       </c>
@@ -2389,300 +2419,300 @@
         <v>53</v>
       </c>
       <c r="P9" s="9"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="51"/>
+      <c r="Q9" s="12"/>
+      <c r="R9" s="12"/>
+      <c r="S9" s="28"/>
     </row>
     <row r="10" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A10" s="17">
+      <c r="A10" s="29">
         <v>30010006</v>
       </c>
-      <c r="B10" s="18">
+      <c r="B10" s="30">
         <v>100100</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="17">
+      <c r="D10" s="29">
         <v>31102</v>
       </c>
-      <c r="E10" s="17" t="s">
+      <c r="E10" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="F10" s="17" t="s">
+      <c r="F10" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="17" t="s">
+      <c r="G10" s="29"/>
+      <c r="H10" s="29"/>
+      <c r="I10" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="J10" s="17"/>
-      <c r="K10" s="39"/>
-      <c r="L10" s="17" t="s">
+      <c r="J10" s="29"/>
+      <c r="K10" s="31"/>
+      <c r="L10" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="M10" s="17" t="s">
+      <c r="M10" s="29" t="s">
         <v>56</v>
       </c>
-      <c r="N10" s="17" t="s">
+      <c r="N10" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="O10" s="17" t="s">
+      <c r="O10" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="P10" s="17"/>
-      <c r="Q10" s="17"/>
+      <c r="P10" s="29"/>
+      <c r="Q10" s="29"/>
       <c r="R10" s="9"/>
-      <c r="S10" s="51"/>
+      <c r="S10" s="28"/>
     </row>
     <row r="11" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A11" s="19">
+      <c r="A11" s="32">
         <v>30010007</v>
       </c>
-      <c r="B11" s="20">
+      <c r="B11" s="33">
         <v>100100</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="21">
+      <c r="D11" s="34">
         <v>31201</v>
       </c>
-      <c r="E11" s="21" t="s">
+      <c r="E11" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="F11" s="19" t="s">
+      <c r="F11" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="G11" s="19">
+      <c r="G11" s="32">
         <v>2001001</v>
       </c>
-      <c r="H11" s="19" t="s">
+      <c r="H11" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="I11" s="19" t="s">
+      <c r="I11" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="J11" s="19"/>
-      <c r="K11" s="40">
+      <c r="J11" s="32"/>
+      <c r="K11" s="35">
         <v>10010091</v>
       </c>
-      <c r="L11" s="19"/>
-      <c r="M11" s="19"/>
-      <c r="N11" s="19"/>
-      <c r="O11" s="19"/>
-      <c r="P11" s="19"/>
-      <c r="Q11" s="19"/>
+      <c r="L11" s="32"/>
+      <c r="M11" s="32"/>
+      <c r="N11" s="32"/>
+      <c r="O11" s="32"/>
+      <c r="P11" s="32"/>
+      <c r="Q11" s="32"/>
       <c r="R11" s="9"/>
-      <c r="S11" s="51"/>
+      <c r="S11" s="28"/>
     </row>
     <row r="12" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A12" s="22">
+      <c r="A12" s="36">
         <v>30010008</v>
       </c>
-      <c r="B12" s="23">
+      <c r="B12" s="37">
         <v>100100</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="D12" s="21">
+      <c r="D12" s="34">
         <v>31202</v>
       </c>
-      <c r="E12" s="21" t="s">
+      <c r="E12" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="F12" s="22" t="s">
+      <c r="F12" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="G12" s="22">
+      <c r="G12" s="36">
         <v>2001001</v>
       </c>
-      <c r="H12" s="22" t="s">
+      <c r="H12" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="I12" s="22" t="s">
+      <c r="I12" s="36" t="s">
         <v>62</v>
       </c>
-      <c r="J12" s="22"/>
-      <c r="K12" s="41" t="s">
+      <c r="J12" s="36"/>
+      <c r="K12" s="38" t="s">
         <v>63</v>
       </c>
-      <c r="L12" s="22"/>
-      <c r="M12" s="22"/>
-      <c r="N12" s="22"/>
-      <c r="O12" s="22"/>
-      <c r="P12" s="22"/>
-      <c r="Q12" s="22"/>
+      <c r="L12" s="36"/>
+      <c r="M12" s="36"/>
+      <c r="N12" s="36"/>
+      <c r="O12" s="36"/>
+      <c r="P12" s="36"/>
+      <c r="Q12" s="36"/>
       <c r="R12" s="9"/>
-      <c r="S12" s="51"/>
+      <c r="S12" s="28"/>
     </row>
     <row r="13" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A13" s="24">
+      <c r="A13" s="39">
         <v>30010009</v>
       </c>
-      <c r="B13" s="25">
+      <c r="B13" s="40">
         <v>100100</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="21">
+      <c r="D13" s="34">
         <v>31203</v>
       </c>
-      <c r="E13" s="21" t="s">
+      <c r="E13" s="34" t="s">
         <v>64</v>
       </c>
-      <c r="F13" s="24" t="s">
+      <c r="F13" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="G13" s="24">
+      <c r="G13" s="39">
         <v>2001001</v>
       </c>
-      <c r="H13" s="24" t="s">
+      <c r="H13" s="39" t="s">
         <v>59</v>
       </c>
-      <c r="I13" s="24" t="s">
+      <c r="I13" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="J13" s="24"/>
-      <c r="K13" s="42" t="s">
+      <c r="J13" s="39"/>
+      <c r="K13" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="L13" s="24"/>
-      <c r="M13" s="24"/>
-      <c r="N13" s="24"/>
-      <c r="O13" s="24"/>
-      <c r="P13" s="24"/>
-      <c r="Q13" s="24"/>
+      <c r="L13" s="39"/>
+      <c r="M13" s="39"/>
+      <c r="N13" s="39"/>
+      <c r="O13" s="39"/>
+      <c r="P13" s="39"/>
+      <c r="Q13" s="39"/>
       <c r="R13" s="9"/>
-      <c r="S13" s="51"/>
+      <c r="S13" s="28"/>
     </row>
     <row r="14" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A14" s="21">
+      <c r="A14" s="34">
         <v>30010010</v>
       </c>
-      <c r="B14" s="26">
+      <c r="B14" s="42">
         <v>100100</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="27">
+      <c r="D14" s="43">
         <v>31301</v>
       </c>
-      <c r="E14" s="27" t="s">
+      <c r="E14" s="43" t="s">
         <v>67</v>
       </c>
-      <c r="F14" s="21" t="s">
+      <c r="F14" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="G14" s="21"/>
-      <c r="H14" s="21"/>
-      <c r="I14" s="21" t="s">
+      <c r="G14" s="34"/>
+      <c r="H14" s="34"/>
+      <c r="I14" s="34" t="s">
         <v>68</v>
       </c>
-      <c r="J14" s="21"/>
-      <c r="K14" s="43"/>
-      <c r="L14" s="21" t="s">
+      <c r="J14" s="34"/>
+      <c r="K14" s="44"/>
+      <c r="L14" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="M14" s="21" t="s">
+      <c r="M14" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="N14" s="21"/>
-      <c r="O14" s="21"/>
-      <c r="P14" s="21"/>
-      <c r="Q14" s="52" t="s">
+      <c r="N14" s="34"/>
+      <c r="O14" s="34"/>
+      <c r="P14" s="34"/>
+      <c r="Q14" s="45" t="s">
         <v>70</v>
       </c>
-      <c r="R14" s="53" t="s">
+      <c r="R14" s="46" t="s">
         <v>71</v>
       </c>
-      <c r="S14" s="11" t="s">
+      <c r="S14" s="12" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="15" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A15" s="24">
+      <c r="A15" s="39">
         <v>30010011</v>
       </c>
-      <c r="B15" s="25">
+      <c r="B15" s="40">
         <v>100100</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="D15" s="27">
+      <c r="D15" s="43">
         <v>31302</v>
       </c>
-      <c r="E15" s="27" t="s">
+      <c r="E15" s="43" t="s">
         <v>73</v>
       </c>
-      <c r="F15" s="24" t="s">
+      <c r="F15" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="G15" s="24"/>
-      <c r="H15" s="24"/>
-      <c r="I15" s="24" t="s">
+      <c r="G15" s="39"/>
+      <c r="H15" s="39"/>
+      <c r="I15" s="39" t="s">
         <v>74</v>
       </c>
-      <c r="J15" s="24"/>
-      <c r="K15" s="42"/>
-      <c r="L15" s="24" t="s">
+      <c r="J15" s="39"/>
+      <c r="K15" s="41"/>
+      <c r="L15" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="M15" s="24" t="s">
+      <c r="M15" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="N15" s="24"/>
-      <c r="O15" s="24"/>
-      <c r="P15" s="24"/>
-      <c r="Q15" s="24"/>
+      <c r="N15" s="39"/>
+      <c r="O15" s="39"/>
+      <c r="P15" s="39"/>
+      <c r="Q15" s="39"/>
       <c r="R15" s="9"/>
-      <c r="S15" s="51"/>
+      <c r="S15" s="28"/>
     </row>
     <row r="16" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A16" s="24">
+      <c r="A16" s="39">
         <v>30010012</v>
       </c>
-      <c r="B16" s="25">
+      <c r="B16" s="40">
         <v>100100</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="C16" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="D16" s="27">
+      <c r="D16" s="43">
         <v>31303</v>
       </c>
-      <c r="E16" s="27" t="s">
+      <c r="E16" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="F16" s="24" t="s">
+      <c r="F16" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="G16" s="24">
+      <c r="G16" s="39">
         <v>2001001</v>
       </c>
-      <c r="H16" s="24" t="s">
+      <c r="H16" s="39" t="s">
         <v>59</v>
       </c>
-      <c r="I16" s="24" t="s">
+      <c r="I16" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="J16" s="24"/>
-      <c r="K16" s="42" t="s">
+      <c r="J16" s="39"/>
+      <c r="K16" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="L16" s="24"/>
-      <c r="M16" s="24"/>
-      <c r="N16" s="24"/>
-      <c r="O16" s="24"/>
-      <c r="P16" s="24"/>
-      <c r="Q16" s="24"/>
+      <c r="L16" s="39"/>
+      <c r="M16" s="39"/>
+      <c r="N16" s="39"/>
+      <c r="O16" s="39"/>
+      <c r="P16" s="39"/>
+      <c r="Q16" s="39"/>
       <c r="R16" s="9"/>
-      <c r="S16" s="51"/>
+      <c r="S16" s="28"/>
     </row>
     <row r="17" s="3" customFormat="1" ht="16.5" spans="1:11">
       <c r="A17" s="9">
@@ -2694,16 +2724,16 @@
       <c r="C17" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D17" s="19">
+      <c r="D17" s="32">
         <v>34001</v>
       </c>
-      <c r="E17" s="19" t="s">
+      <c r="E17" s="32" t="s">
         <v>77</v>
       </c>
-      <c r="F17" s="19" t="s">
+      <c r="F17" s="32" t="s">
         <v>78</v>
       </c>
-      <c r="G17" s="16">
+      <c r="G17" s="21">
         <v>2007001</v>
       </c>
       <c r="H17" s="9" t="s">
@@ -2712,7 +2742,7 @@
       <c r="I17" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="K17" s="44" t="s">
+      <c r="K17" s="47" t="s">
         <v>80</v>
       </c>
     </row>
@@ -2726,16 +2756,16 @@
       <c r="C18" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="32">
         <v>34002</v>
       </c>
-      <c r="E18" s="19" t="s">
+      <c r="E18" s="32" t="s">
         <v>81</v>
       </c>
-      <c r="F18" s="19" t="s">
+      <c r="F18" s="32" t="s">
         <v>82</v>
       </c>
-      <c r="G18" s="16">
+      <c r="G18" s="21">
         <v>2007001</v>
       </c>
       <c r="H18" s="9" t="s">
@@ -2744,12 +2774,12 @@
       <c r="I18" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="K18" s="44" t="s">
+      <c r="K18" s="47" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="19" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A19" s="21">
+      <c r="A19" s="34">
         <v>30120001</v>
       </c>
       <c r="B19" s="4">
@@ -2758,33 +2788,33 @@
       <c r="C19" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="D19" s="21">
+      <c r="D19" s="34">
         <v>32001</v>
       </c>
-      <c r="E19" s="21" t="s">
+      <c r="E19" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="F19" s="21" t="s">
+      <c r="F19" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="G19" s="26">
+      <c r="G19" s="42">
         <v>2012001</v>
       </c>
-      <c r="H19" s="21" t="s">
+      <c r="H19" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="I19" s="21" t="s">
+      <c r="I19" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="J19" s="21" t="s">
+      <c r="J19" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="K19" s="45">
+      <c r="K19" s="48">
         <v>10120041</v>
       </c>
     </row>
     <row r="20" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A20" s="21">
+      <c r="A20" s="34">
         <v>30120002</v>
       </c>
       <c r="B20" s="4">
@@ -2793,33 +2823,33 @@
       <c r="C20" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="D20" s="21">
+      <c r="D20" s="34">
         <v>32002</v>
       </c>
-      <c r="E20" s="21" t="s">
+      <c r="E20" s="34" t="s">
         <v>86</v>
       </c>
-      <c r="F20" s="21" t="s">
+      <c r="F20" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="G20" s="26">
+      <c r="G20" s="42">
         <v>2012001</v>
       </c>
-      <c r="H20" s="21" t="s">
+      <c r="H20" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="I20" s="21" t="s">
+      <c r="I20" s="34" t="s">
         <v>86</v>
       </c>
-      <c r="J20" s="21" t="s">
+      <c r="J20" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="K20" s="45">
+      <c r="K20" s="48">
         <v>10120042</v>
       </c>
     </row>
     <row r="21" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A21" s="21">
+      <c r="A21" s="34">
         <v>30120003</v>
       </c>
       <c r="B21" s="4">
@@ -2828,33 +2858,33 @@
       <c r="C21" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="D21" s="21">
+      <c r="D21" s="34">
         <v>32003</v>
       </c>
-      <c r="E21" s="21" t="s">
+      <c r="E21" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="F21" s="21" t="s">
+      <c r="F21" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="G21" s="26">
+      <c r="G21" s="42">
         <v>2012001</v>
       </c>
-      <c r="H21" s="21" t="s">
+      <c r="H21" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="I21" s="21" t="s">
+      <c r="I21" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="J21" s="21" t="s">
+      <c r="J21" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="K21" s="45">
+      <c r="K21" s="48">
         <v>10120043</v>
       </c>
     </row>
     <row r="22" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A22" s="21">
+      <c r="A22" s="34">
         <v>30120004</v>
       </c>
       <c r="B22" s="4">
@@ -2863,33 +2893,33 @@
       <c r="C22" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="D22" s="21">
+      <c r="D22" s="34">
         <v>32004</v>
       </c>
-      <c r="E22" s="21" t="s">
+      <c r="E22" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="F22" s="21" t="s">
+      <c r="F22" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="G22" s="26">
+      <c r="G22" s="42">
         <v>2012001</v>
       </c>
-      <c r="H22" s="21" t="s">
+      <c r="H22" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="I22" s="21" t="s">
+      <c r="I22" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="J22" s="21" t="s">
+      <c r="J22" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="K22" s="45">
+      <c r="K22" s="48">
         <v>10120044</v>
       </c>
     </row>
     <row r="23" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A23" s="21">
+      <c r="A23" s="34">
         <v>30120005</v>
       </c>
       <c r="B23" s="4">
@@ -2898,33 +2928,33 @@
       <c r="C23" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="D23" s="21">
+      <c r="D23" s="34">
         <v>32005</v>
       </c>
-      <c r="E23" s="21" t="s">
+      <c r="E23" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="F23" s="21" t="s">
+      <c r="F23" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="G23" s="26">
+      <c r="G23" s="42">
         <v>2012001</v>
       </c>
-      <c r="H23" s="21" t="s">
+      <c r="H23" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="I23" s="21" t="s">
+      <c r="I23" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="J23" s="21" t="s">
+      <c r="J23" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="K23" s="45">
+      <c r="K23" s="48">
         <v>10120045</v>
       </c>
     </row>
     <row r="24" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A24" s="21">
+      <c r="A24" s="34">
         <v>30120006</v>
       </c>
       <c r="B24" s="4">
@@ -2933,33 +2963,33 @@
       <c r="C24" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="D24" s="21">
+      <c r="D24" s="34">
         <v>32006</v>
       </c>
-      <c r="E24" s="21" t="s">
+      <c r="E24" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="F24" s="21" t="s">
+      <c r="F24" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="G24" s="26">
+      <c r="G24" s="42">
         <v>2012001</v>
       </c>
-      <c r="H24" s="21" t="s">
+      <c r="H24" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="I24" s="21" t="s">
+      <c r="I24" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="J24" s="21" t="s">
+      <c r="J24" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="K24" s="45">
+      <c r="K24" s="48">
         <v>10120046</v>
       </c>
     </row>
     <row r="25" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A25" s="28">
+      <c r="A25" s="49">
         <v>30120011</v>
       </c>
       <c r="B25" s="5">
@@ -2968,33 +2998,33 @@
       <c r="C25" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="D25" s="21">
+      <c r="D25" s="34">
         <v>32101</v>
       </c>
-      <c r="E25" s="28" t="s">
+      <c r="E25" s="49" t="s">
         <v>84</v>
       </c>
-      <c r="F25" s="28" t="s">
+      <c r="F25" s="49" t="s">
         <v>52</v>
       </c>
-      <c r="G25" s="29">
+      <c r="G25" s="50">
         <v>2012001</v>
       </c>
-      <c r="H25" s="28" t="s">
+      <c r="H25" s="49" t="s">
         <v>59</v>
       </c>
-      <c r="I25" s="28" t="s">
+      <c r="I25" s="49" t="s">
         <v>84</v>
       </c>
-      <c r="J25" s="28" t="s">
+      <c r="J25" s="49" t="s">
         <v>90</v>
       </c>
-      <c r="K25" s="46">
+      <c r="K25" s="51">
         <v>10120041</v>
       </c>
     </row>
     <row r="26" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A26" s="28">
+      <c r="A26" s="49">
         <v>30120012</v>
       </c>
       <c r="B26" s="5">
@@ -3003,33 +3033,33 @@
       <c r="C26" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="D26" s="21">
+      <c r="D26" s="34">
         <v>32102</v>
       </c>
-      <c r="E26" s="28" t="s">
+      <c r="E26" s="49" t="s">
         <v>86</v>
       </c>
-      <c r="F26" s="28" t="s">
+      <c r="F26" s="49" t="s">
         <v>52</v>
       </c>
-      <c r="G26" s="29">
+      <c r="G26" s="50">
         <v>2012001</v>
       </c>
-      <c r="H26" s="28" t="s">
+      <c r="H26" s="49" t="s">
         <v>59</v>
       </c>
-      <c r="I26" s="28" t="s">
+      <c r="I26" s="49" t="s">
         <v>86</v>
       </c>
-      <c r="J26" s="28" t="s">
+      <c r="J26" s="49" t="s">
         <v>90</v>
       </c>
-      <c r="K26" s="46">
+      <c r="K26" s="51">
         <v>10120042</v>
       </c>
     </row>
     <row r="27" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A27" s="28">
+      <c r="A27" s="49">
         <v>30120013</v>
       </c>
       <c r="B27" s="5">
@@ -3038,33 +3068,33 @@
       <c r="C27" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="D27" s="21">
+      <c r="D27" s="34">
         <v>32103</v>
       </c>
-      <c r="E27" s="28" t="s">
+      <c r="E27" s="49" t="s">
         <v>87</v>
       </c>
-      <c r="F27" s="28" t="s">
+      <c r="F27" s="49" t="s">
         <v>52</v>
       </c>
-      <c r="G27" s="29">
+      <c r="G27" s="50">
         <v>2012001</v>
       </c>
-      <c r="H27" s="28" t="s">
+      <c r="H27" s="49" t="s">
         <v>59</v>
       </c>
-      <c r="I27" s="28" t="s">
+      <c r="I27" s="49" t="s">
         <v>87</v>
       </c>
-      <c r="J27" s="28" t="s">
+      <c r="J27" s="49" t="s">
         <v>90</v>
       </c>
-      <c r="K27" s="46">
+      <c r="K27" s="51">
         <v>10120043</v>
       </c>
     </row>
     <row r="28" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A28" s="28">
+      <c r="A28" s="49">
         <v>30120014</v>
       </c>
       <c r="B28" s="5">
@@ -3073,33 +3103,33 @@
       <c r="C28" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="D28" s="21">
+      <c r="D28" s="34">
         <v>32104</v>
       </c>
-      <c r="E28" s="28" t="s">
+      <c r="E28" s="49" t="s">
         <v>88</v>
       </c>
-      <c r="F28" s="28" t="s">
+      <c r="F28" s="49" t="s">
         <v>52</v>
       </c>
-      <c r="G28" s="29">
+      <c r="G28" s="50">
         <v>2012001</v>
       </c>
-      <c r="H28" s="28" t="s">
+      <c r="H28" s="49" t="s">
         <v>59</v>
       </c>
-      <c r="I28" s="28" t="s">
+      <c r="I28" s="49" t="s">
         <v>88</v>
       </c>
-      <c r="J28" s="28" t="s">
+      <c r="J28" s="49" t="s">
         <v>90</v>
       </c>
-      <c r="K28" s="46">
+      <c r="K28" s="51">
         <v>10120044</v>
       </c>
     </row>
     <row r="29" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A29" s="28">
+      <c r="A29" s="49">
         <v>30120015</v>
       </c>
       <c r="B29" s="5">
@@ -3108,33 +3138,33 @@
       <c r="C29" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="D29" s="21">
+      <c r="D29" s="34">
         <v>32105</v>
       </c>
-      <c r="E29" s="28" t="s">
+      <c r="E29" s="49" t="s">
         <v>88</v>
       </c>
-      <c r="F29" s="28" t="s">
+      <c r="F29" s="49" t="s">
         <v>52</v>
       </c>
-      <c r="G29" s="29">
+      <c r="G29" s="50">
         <v>2012001</v>
       </c>
-      <c r="H29" s="28" t="s">
+      <c r="H29" s="49" t="s">
         <v>59</v>
       </c>
-      <c r="I29" s="28" t="s">
+      <c r="I29" s="49" t="s">
         <v>88</v>
       </c>
-      <c r="J29" s="28" t="s">
+      <c r="J29" s="49" t="s">
         <v>90</v>
       </c>
-      <c r="K29" s="46">
+      <c r="K29" s="51">
         <v>10120045</v>
       </c>
     </row>
     <row r="30" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A30" s="28">
+      <c r="A30" s="49">
         <v>30120016</v>
       </c>
       <c r="B30" s="5">
@@ -3143,33 +3173,33 @@
       <c r="C30" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="D30" s="21">
+      <c r="D30" s="34">
         <v>32106</v>
       </c>
-      <c r="E30" s="28" t="s">
+      <c r="E30" s="49" t="s">
         <v>88</v>
       </c>
-      <c r="F30" s="28" t="s">
+      <c r="F30" s="49" t="s">
         <v>52</v>
       </c>
-      <c r="G30" s="29">
+      <c r="G30" s="50">
         <v>2012001</v>
       </c>
-      <c r="H30" s="28" t="s">
+      <c r="H30" s="49" t="s">
         <v>59</v>
       </c>
-      <c r="I30" s="28" t="s">
+      <c r="I30" s="49" t="s">
         <v>88</v>
       </c>
-      <c r="J30" s="28" t="s">
+      <c r="J30" s="49" t="s">
         <v>90</v>
       </c>
-      <c r="K30" s="46">
+      <c r="K30" s="51">
         <v>10120046</v>
       </c>
     </row>
     <row r="31" s="6" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A31" s="27">
+      <c r="A31" s="43">
         <v>30120021</v>
       </c>
       <c r="B31" s="6">
@@ -3178,31 +3208,31 @@
       <c r="C31" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D31" s="27">
+      <c r="D31" s="43">
         <v>32201</v>
       </c>
-      <c r="E31" s="27" t="s">
+      <c r="E31" s="43" t="s">
         <v>84</v>
       </c>
-      <c r="F31" s="27" t="s">
+      <c r="F31" s="43" t="s">
         <v>52</v>
       </c>
-      <c r="G31" s="30">
+      <c r="G31" s="52">
         <v>2012001</v>
       </c>
-      <c r="H31" s="27" t="s">
+      <c r="H31" s="43" t="s">
         <v>59</v>
       </c>
-      <c r="I31" s="27" t="s">
+      <c r="I31" s="43" t="s">
         <v>84</v>
       </c>
-      <c r="J31" s="27"/>
-      <c r="K31" s="47">
+      <c r="J31" s="43"/>
+      <c r="K31" s="53">
         <v>10120041</v>
       </c>
     </row>
     <row r="32" s="6" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A32" s="27">
+      <c r="A32" s="43">
         <v>30120022</v>
       </c>
       <c r="B32" s="6">
@@ -3211,31 +3241,31 @@
       <c r="C32" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D32" s="27">
+      <c r="D32" s="43">
         <v>32202</v>
       </c>
-      <c r="E32" s="27" t="s">
+      <c r="E32" s="43" t="s">
         <v>86</v>
       </c>
-      <c r="F32" s="27" t="s">
+      <c r="F32" s="43" t="s">
         <v>52</v>
       </c>
-      <c r="G32" s="30">
+      <c r="G32" s="52">
         <v>2012001</v>
       </c>
-      <c r="H32" s="27" t="s">
+      <c r="H32" s="43" t="s">
         <v>59</v>
       </c>
-      <c r="I32" s="27" t="s">
+      <c r="I32" s="43" t="s">
         <v>86</v>
       </c>
-      <c r="J32" s="27"/>
-      <c r="K32" s="47">
+      <c r="J32" s="43"/>
+      <c r="K32" s="53">
         <v>10120042</v>
       </c>
     </row>
-    <row r="33" s="6" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A33" s="27">
+    <row r="33" s="6" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A33" s="43">
         <v>30120023</v>
       </c>
       <c r="B33" s="6">
@@ -3244,31 +3274,31 @@
       <c r="C33" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D33" s="27">
+      <c r="D33" s="43">
         <v>32203</v>
       </c>
-      <c r="E33" s="27" t="s">
+      <c r="E33" s="43" t="s">
         <v>87</v>
       </c>
-      <c r="F33" s="27" t="s">
+      <c r="F33" s="43" t="s">
         <v>52</v>
       </c>
-      <c r="G33" s="30">
+      <c r="G33" s="52">
         <v>2012001</v>
       </c>
-      <c r="H33" s="27" t="s">
+      <c r="H33" s="43" t="s">
         <v>59</v>
       </c>
-      <c r="I33" s="27" t="s">
+      <c r="I33" s="43" t="s">
         <v>87</v>
       </c>
-      <c r="J33" s="27"/>
-      <c r="K33" s="47">
+      <c r="J33" s="43"/>
+      <c r="K33" s="53">
         <v>10120043</v>
       </c>
     </row>
-    <row r="34" s="6" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A34" s="27">
+    <row r="34" s="6" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A34" s="43">
         <v>30120024</v>
       </c>
       <c r="B34" s="6">
@@ -3277,31 +3307,31 @@
       <c r="C34" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D34" s="27">
+      <c r="D34" s="43">
         <v>32204</v>
       </c>
-      <c r="E34" s="27" t="s">
+      <c r="E34" s="43" t="s">
         <v>88</v>
       </c>
-      <c r="F34" s="27" t="s">
+      <c r="F34" s="43" t="s">
         <v>52</v>
       </c>
-      <c r="G34" s="30">
+      <c r="G34" s="52">
         <v>2012001</v>
       </c>
-      <c r="H34" s="27" t="s">
+      <c r="H34" s="43" t="s">
         <v>59</v>
       </c>
-      <c r="I34" s="27" t="s">
+      <c r="I34" s="43" t="s">
         <v>88</v>
       </c>
-      <c r="J34" s="27"/>
-      <c r="K34" s="47">
+      <c r="J34" s="43"/>
+      <c r="K34" s="53">
         <v>10120044</v>
       </c>
     </row>
-    <row r="35" s="6" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A35" s="27">
+    <row r="35" s="6" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A35" s="43">
         <v>30120025</v>
       </c>
       <c r="B35" s="6">
@@ -3310,31 +3340,31 @@
       <c r="C35" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D35" s="27">
+      <c r="D35" s="43">
         <v>32205</v>
       </c>
-      <c r="E35" s="27" t="s">
+      <c r="E35" s="43" t="s">
         <v>88</v>
       </c>
-      <c r="F35" s="27" t="s">
+      <c r="F35" s="43" t="s">
         <v>52</v>
       </c>
-      <c r="G35" s="30">
+      <c r="G35" s="52">
         <v>2012001</v>
       </c>
-      <c r="H35" s="27" t="s">
+      <c r="H35" s="43" t="s">
         <v>59</v>
       </c>
-      <c r="I35" s="27" t="s">
+      <c r="I35" s="43" t="s">
         <v>88</v>
       </c>
-      <c r="J35" s="27"/>
-      <c r="K35" s="47">
+      <c r="J35" s="43"/>
+      <c r="K35" s="53">
         <v>10120045</v>
       </c>
     </row>
-    <row r="36" s="6" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A36" s="27">
+    <row r="36" s="6" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A36" s="43">
         <v>30120026</v>
       </c>
       <c r="B36" s="6">
@@ -3343,219 +3373,219 @@
       <c r="C36" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D36" s="27">
+      <c r="D36" s="43">
         <v>32206</v>
       </c>
-      <c r="E36" s="27" t="s">
+      <c r="E36" s="43" t="s">
         <v>88</v>
       </c>
-      <c r="F36" s="27" t="s">
+      <c r="F36" s="43" t="s">
         <v>52</v>
       </c>
-      <c r="G36" s="30">
+      <c r="G36" s="52">
         <v>2012001</v>
       </c>
-      <c r="H36" s="27" t="s">
+      <c r="H36" s="43" t="s">
         <v>59</v>
       </c>
-      <c r="I36" s="27" t="s">
+      <c r="I36" s="43" t="s">
         <v>88</v>
       </c>
-      <c r="J36" s="27"/>
-      <c r="K36" s="47">
+      <c r="J36" s="43"/>
+      <c r="K36" s="53">
         <v>10120046</v>
       </c>
     </row>
     <row r="37" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A37" s="14">
+      <c r="A37" s="23">
         <v>30240001</v>
       </c>
-      <c r="B37" s="15">
+      <c r="B37" s="24">
         <v>102400</v>
       </c>
-      <c r="C37" s="15" t="s">
+      <c r="C37" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="D37" s="14">
+      <c r="D37" s="23">
         <v>32401</v>
       </c>
-      <c r="E37" s="14" t="s">
+      <c r="E37" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="F37" s="14" t="s">
+      <c r="F37" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="14" t="s">
+      <c r="G37" s="23"/>
+      <c r="H37" s="23"/>
+      <c r="I37" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="J37" s="14"/>
-      <c r="K37" s="38"/>
+      <c r="J37" s="23"/>
+      <c r="K37" s="25"/>
       <c r="L37" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="M37" s="14" t="s">
+      <c r="M37" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="N37" s="14" t="s">
+      <c r="N37" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="O37" s="14"/>
-      <c r="P37" s="14"/>
-      <c r="Q37" s="49" t="s">
+      <c r="O37" s="23"/>
+      <c r="P37" s="23"/>
+      <c r="Q37" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="R37" s="50" t="s">
+      <c r="R37" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="S37" s="51" t="s">
+      <c r="S37" s="28" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="38" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A38" s="14">
+      <c r="A38" s="23">
         <v>30240002</v>
       </c>
-      <c r="B38" s="15">
+      <c r="B38" s="24">
         <v>102400</v>
       </c>
-      <c r="C38" s="15" t="s">
+      <c r="C38" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="D38" s="14">
+      <c r="D38" s="23">
         <v>32402</v>
       </c>
-      <c r="E38" s="14" t="s">
+      <c r="E38" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="F38" s="14" t="s">
+      <c r="F38" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="14" t="s">
+      <c r="G38" s="23"/>
+      <c r="H38" s="23"/>
+      <c r="I38" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="J38" s="14"/>
-      <c r="K38" s="38"/>
+      <c r="J38" s="23"/>
+      <c r="K38" s="25"/>
       <c r="L38" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="M38" s="14" t="s">
+      <c r="M38" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="N38" s="14" t="s">
+      <c r="N38" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="O38" s="14"/>
-      <c r="P38" s="14"/>
-      <c r="Q38" s="49" t="s">
+      <c r="O38" s="23"/>
+      <c r="P38" s="23"/>
+      <c r="Q38" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="R38" s="50" t="s">
+      <c r="R38" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="S38" s="51"/>
+      <c r="S38" s="28"/>
     </row>
     <row r="39" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A39" s="14">
+      <c r="A39" s="23">
         <v>30240003</v>
       </c>
-      <c r="B39" s="15">
+      <c r="B39" s="24">
         <v>102400</v>
       </c>
-      <c r="C39" s="15" t="s">
+      <c r="C39" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="D39" s="14">
+      <c r="D39" s="23">
         <v>32403</v>
       </c>
-      <c r="E39" s="14" t="s">
+      <c r="E39" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="F39" s="14" t="s">
+      <c r="F39" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="14" t="s">
+      <c r="G39" s="23"/>
+      <c r="H39" s="23"/>
+      <c r="I39" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="J39" s="14"/>
-      <c r="K39" s="38"/>
+      <c r="J39" s="23"/>
+      <c r="K39" s="25"/>
       <c r="L39" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="M39" s="14" t="s">
+      <c r="M39" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="N39" s="14" t="s">
+      <c r="N39" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="O39" s="14"/>
-      <c r="P39" s="14"/>
-      <c r="Q39" s="49" t="s">
+      <c r="O39" s="23"/>
+      <c r="P39" s="23"/>
+      <c r="Q39" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="R39" s="50" t="s">
+      <c r="R39" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="S39" s="51"/>
+      <c r="S39" s="28"/>
     </row>
     <row r="40" s="3" customFormat="1" ht="15" customHeight="1" spans="1:19">
-      <c r="A40" s="14">
+      <c r="A40" s="23">
         <v>30240004</v>
       </c>
-      <c r="B40" s="15">
+      <c r="B40" s="24">
         <v>102400</v>
       </c>
-      <c r="C40" s="15" t="s">
+      <c r="C40" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="D40" s="14">
+      <c r="D40" s="23">
         <v>32404</v>
       </c>
-      <c r="E40" s="14" t="s">
+      <c r="E40" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="F40" s="14" t="s">
+      <c r="F40" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="14" t="s">
+      <c r="G40" s="23"/>
+      <c r="H40" s="23"/>
+      <c r="I40" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="J40" s="14"/>
-      <c r="K40" s="38"/>
+      <c r="J40" s="23"/>
+      <c r="K40" s="25"/>
       <c r="L40" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="M40" s="14" t="s">
+      <c r="M40" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="N40" s="14" t="s">
+      <c r="N40" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="O40" s="14"/>
-      <c r="P40" s="14"/>
-      <c r="Q40" s="49" t="s">
+      <c r="O40" s="23"/>
+      <c r="P40" s="23"/>
+      <c r="Q40" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="R40" s="50" t="s">
+      <c r="R40" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="S40" s="51"/>
+      <c r="S40" s="28"/>
     </row>
     <row r="41" s="3" customFormat="1" ht="15" customHeight="1" spans="1:19">
       <c r="A41" s="9">
         <v>30240005</v>
       </c>
-      <c r="B41" s="16">
+      <c r="B41" s="21">
         <v>102400</v>
       </c>
-      <c r="C41" s="15" t="s">
+      <c r="C41" s="24" t="s">
         <v>31</v>
       </c>
       <c r="D41" s="9">
@@ -3573,7 +3603,7 @@
         <v>51</v>
       </c>
       <c r="J41" s="9"/>
-      <c r="K41" s="32"/>
+      <c r="K41" s="11"/>
       <c r="L41" s="9" t="s">
         <v>35</v>
       </c>
@@ -3585,342 +3615,486 @@
         <v>53</v>
       </c>
       <c r="P41" s="9"/>
-      <c r="Q41" s="11"/>
-      <c r="R41" s="11"/>
-      <c r="S41" s="51"/>
+      <c r="Q41" s="12"/>
+      <c r="R41" s="12"/>
+      <c r="S41" s="28"/>
     </row>
     <row r="42" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A42" s="17">
+      <c r="A42" s="29">
         <v>30240006</v>
       </c>
-      <c r="B42" s="18">
+      <c r="B42" s="30">
         <v>102400</v>
       </c>
-      <c r="C42" s="15" t="s">
+      <c r="C42" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="D42" s="17">
+      <c r="D42" s="29">
         <v>32421</v>
       </c>
-      <c r="E42" s="17" t="s">
+      <c r="E42" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="F42" s="17" t="s">
+      <c r="F42" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="G42" s="17"/>
-      <c r="H42" s="17"/>
-      <c r="I42" s="17" t="s">
+      <c r="G42" s="29"/>
+      <c r="H42" s="29"/>
+      <c r="I42" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="J42" s="17"/>
-      <c r="K42" s="39"/>
-      <c r="L42" s="17" t="s">
+      <c r="J42" s="29"/>
+      <c r="K42" s="31"/>
+      <c r="L42" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="M42" s="17" t="s">
+      <c r="M42" s="29" t="s">
         <v>56</v>
       </c>
-      <c r="N42" s="17" t="s">
+      <c r="N42" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="O42" s="17" t="s">
+      <c r="O42" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="P42" s="17"/>
-      <c r="Q42" s="17"/>
+      <c r="P42" s="29"/>
+      <c r="Q42" s="29"/>
       <c r="R42" s="9"/>
-      <c r="S42" s="51"/>
+      <c r="S42" s="28"/>
     </row>
     <row r="43" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A43" s="19">
+      <c r="A43" s="32">
         <v>30240007</v>
       </c>
-      <c r="B43" s="20">
+      <c r="B43" s="33">
         <v>102400</v>
       </c>
-      <c r="C43" s="15" t="s">
+      <c r="C43" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="D43" s="21">
+      <c r="D43" s="34">
         <v>32431</v>
       </c>
-      <c r="E43" s="21" t="s">
+      <c r="E43" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="F43" s="19" t="s">
+      <c r="F43" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="G43" s="19">
+      <c r="G43" s="32">
         <v>2024001</v>
       </c>
-      <c r="H43" s="19" t="s">
+      <c r="H43" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="I43" s="19" t="s">
+      <c r="I43" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="J43" s="19"/>
-      <c r="K43" s="40">
+      <c r="J43" s="32"/>
+      <c r="K43" s="35">
         <v>10240091</v>
       </c>
-      <c r="L43" s="19"/>
-      <c r="M43" s="19"/>
-      <c r="N43" s="19"/>
-      <c r="O43" s="19"/>
-      <c r="P43" s="19"/>
-      <c r="Q43" s="19"/>
+      <c r="L43" s="32"/>
+      <c r="M43" s="32"/>
+      <c r="N43" s="32"/>
+      <c r="O43" s="32"/>
+      <c r="P43" s="32"/>
+      <c r="Q43" s="32"/>
       <c r="R43" s="9"/>
-      <c r="S43" s="51"/>
+      <c r="S43" s="28"/>
     </row>
     <row r="44" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A44" s="22">
+      <c r="A44" s="36">
         <v>30240008</v>
       </c>
-      <c r="B44" s="23">
+      <c r="B44" s="37">
         <v>102400</v>
       </c>
-      <c r="C44" s="15" t="s">
+      <c r="C44" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="D44" s="21">
+      <c r="D44" s="34">
         <v>32432</v>
       </c>
-      <c r="E44" s="21" t="s">
+      <c r="E44" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="F44" s="22" t="s">
+      <c r="F44" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="G44" s="22">
+      <c r="G44" s="36">
         <v>2024001</v>
       </c>
-      <c r="H44" s="22" t="s">
+      <c r="H44" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="I44" s="22" t="s">
+      <c r="I44" s="36" t="s">
         <v>62</v>
       </c>
-      <c r="J44" s="22"/>
-      <c r="K44" s="41" t="s">
+      <c r="J44" s="36"/>
+      <c r="K44" s="38" t="s">
         <v>92</v>
       </c>
-      <c r="L44" s="22"/>
-      <c r="M44" s="22"/>
-      <c r="N44" s="22"/>
-      <c r="O44" s="22"/>
-      <c r="P44" s="22"/>
-      <c r="Q44" s="22"/>
+      <c r="L44" s="36"/>
+      <c r="M44" s="36"/>
+      <c r="N44" s="36"/>
+      <c r="O44" s="36"/>
+      <c r="P44" s="36"/>
+      <c r="Q44" s="36"/>
       <c r="R44" s="9"/>
-      <c r="S44" s="51"/>
+      <c r="S44" s="28"/>
     </row>
     <row r="45" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A45" s="24">
+      <c r="A45" s="39">
         <v>30240009</v>
       </c>
-      <c r="B45" s="25">
+      <c r="B45" s="40">
         <v>102400</v>
       </c>
-      <c r="C45" s="15" t="s">
+      <c r="C45" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="D45" s="21">
+      <c r="D45" s="34">
         <v>32433</v>
       </c>
-      <c r="E45" s="21" t="s">
+      <c r="E45" s="34" t="s">
         <v>64</v>
       </c>
-      <c r="F45" s="24" t="s">
+      <c r="F45" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="G45" s="24">
+      <c r="G45" s="39">
         <v>2024001</v>
       </c>
-      <c r="H45" s="24" t="s">
+      <c r="H45" s="39" t="s">
         <v>59</v>
       </c>
-      <c r="I45" s="24" t="s">
+      <c r="I45" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="J45" s="24"/>
-      <c r="K45" s="42" t="s">
+      <c r="J45" s="39"/>
+      <c r="K45" s="41" t="s">
         <v>93</v>
       </c>
-      <c r="L45" s="24"/>
-      <c r="M45" s="24"/>
-      <c r="N45" s="24"/>
-      <c r="O45" s="24"/>
-      <c r="P45" s="24"/>
-      <c r="Q45" s="24"/>
+      <c r="L45" s="39"/>
+      <c r="M45" s="39"/>
+      <c r="N45" s="39"/>
+      <c r="O45" s="39"/>
+      <c r="P45" s="39"/>
+      <c r="Q45" s="39"/>
       <c r="R45" s="9"/>
-      <c r="S45" s="51"/>
+      <c r="S45" s="28"/>
     </row>
     <row r="46" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A46" s="21">
+      <c r="A46" s="34">
         <v>30240010</v>
       </c>
-      <c r="B46" s="26">
+      <c r="B46" s="42">
         <v>102400</v>
       </c>
-      <c r="C46" s="15" t="s">
+      <c r="C46" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="D46" s="27">
+      <c r="D46" s="43">
         <v>32441</v>
       </c>
-      <c r="E46" s="27" t="s">
+      <c r="E46" s="43" t="s">
         <v>67</v>
       </c>
-      <c r="F46" s="21" t="s">
+      <c r="F46" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="G46" s="21"/>
-      <c r="H46" s="21"/>
-      <c r="I46" s="21" t="s">
+      <c r="G46" s="34"/>
+      <c r="H46" s="34"/>
+      <c r="I46" s="34" t="s">
         <v>68</v>
       </c>
-      <c r="J46" s="21"/>
-      <c r="K46" s="43"/>
-      <c r="L46" s="21" t="s">
+      <c r="J46" s="34"/>
+      <c r="K46" s="44"/>
+      <c r="L46" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="M46" s="21" t="s">
+      <c r="M46" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="N46" s="21"/>
-      <c r="O46" s="21"/>
-      <c r="P46" s="21"/>
-      <c r="Q46" s="52" t="s">
+      <c r="N46" s="34"/>
+      <c r="O46" s="34"/>
+      <c r="P46" s="34"/>
+      <c r="Q46" s="45" t="s">
         <v>70</v>
       </c>
-      <c r="R46" s="53" t="s">
+      <c r="R46" s="46" t="s">
         <v>71</v>
       </c>
-      <c r="S46" s="11" t="s">
+      <c r="S46" s="12" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="47" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A47" s="24">
+      <c r="A47" s="39">
         <v>30240011</v>
       </c>
-      <c r="B47" s="25">
+      <c r="B47" s="40">
         <v>102400</v>
       </c>
-      <c r="C47" s="15" t="s">
+      <c r="C47" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="D47" s="27">
+      <c r="D47" s="43">
         <v>32442</v>
       </c>
-      <c r="E47" s="27" t="s">
+      <c r="E47" s="43" t="s">
         <v>73</v>
       </c>
-      <c r="F47" s="24" t="s">
+      <c r="F47" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="G47" s="24"/>
-      <c r="H47" s="24"/>
-      <c r="I47" s="24" t="s">
+      <c r="G47" s="39"/>
+      <c r="H47" s="39"/>
+      <c r="I47" s="39" t="s">
         <v>74</v>
       </c>
-      <c r="J47" s="24"/>
-      <c r="K47" s="42"/>
-      <c r="L47" s="24" t="s">
+      <c r="J47" s="39"/>
+      <c r="K47" s="41"/>
+      <c r="L47" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="M47" s="24" t="s">
+      <c r="M47" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="N47" s="24"/>
-      <c r="O47" s="24"/>
-      <c r="P47" s="24"/>
-      <c r="Q47" s="24"/>
+      <c r="N47" s="39"/>
+      <c r="O47" s="39"/>
+      <c r="P47" s="39"/>
+      <c r="Q47" s="39"/>
       <c r="R47" s="9"/>
-      <c r="S47" s="51"/>
+      <c r="S47" s="28"/>
     </row>
     <row r="48" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A48" s="24">
+      <c r="A48" s="39">
         <v>30240012</v>
       </c>
-      <c r="B48" s="25">
+      <c r="B48" s="40">
         <v>102400</v>
       </c>
-      <c r="C48" s="15" t="s">
+      <c r="C48" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="D48" s="27">
+      <c r="D48" s="43">
         <v>32443</v>
       </c>
-      <c r="E48" s="27" t="s">
+      <c r="E48" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="F48" s="24" t="s">
+      <c r="F48" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="G48" s="24">
+      <c r="G48" s="39">
         <v>2024001</v>
       </c>
-      <c r="H48" s="24" t="s">
+      <c r="H48" s="39" t="s">
         <v>59</v>
       </c>
-      <c r="I48" s="24" t="s">
+      <c r="I48" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="J48" s="24"/>
-      <c r="K48" s="42" t="s">
+      <c r="J48" s="39"/>
+      <c r="K48" s="41" t="s">
         <v>93</v>
       </c>
-      <c r="L48" s="24"/>
-      <c r="M48" s="24"/>
-      <c r="N48" s="24"/>
-      <c r="O48" s="24"/>
-      <c r="P48" s="24"/>
-      <c r="Q48" s="24"/>
+      <c r="L48" s="39"/>
+      <c r="M48" s="39"/>
+      <c r="N48" s="39"/>
+      <c r="O48" s="39"/>
+      <c r="P48" s="39"/>
+      <c r="Q48" s="39"/>
       <c r="R48" s="9"/>
-      <c r="S48" s="51"/>
-    </row>
-    <row r="49" ht="16.5" spans="19:22">
-      <c r="S49"/>
-      <c r="U49" s="1"/>
-      <c r="V49" s="1"/>
-    </row>
-    <row r="50" ht="16.5" spans="19:22">
-      <c r="S50"/>
-      <c r="U50" s="1"/>
-      <c r="V50" s="1"/>
-    </row>
-    <row r="51" ht="16.5" spans="19:22">
-      <c r="S51"/>
-      <c r="U51" s="1"/>
-      <c r="V51" s="1"/>
-    </row>
-    <row r="52" ht="16.5" spans="19:22">
-      <c r="S52"/>
-      <c r="U52" s="1"/>
-      <c r="V52" s="1"/>
-    </row>
-    <row r="53" ht="16.5" spans="19:22">
+      <c r="S48" s="28"/>
+    </row>
+    <row r="49" s="3" customFormat="1" ht="16.5" spans="1:22">
+      <c r="A49" s="39">
+        <v>30170001</v>
+      </c>
+      <c r="B49" s="40">
+        <v>101700</v>
+      </c>
+      <c r="C49" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="D49" s="43">
+        <v>301701</v>
+      </c>
+      <c r="E49" s="43" t="s">
+        <v>95</v>
+      </c>
+      <c r="F49" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="G49" s="39">
+        <v>2017001</v>
+      </c>
+      <c r="H49" s="39" t="s">
+        <v>59</v>
+      </c>
+      <c r="I49" s="39" t="s">
+        <v>79</v>
+      </c>
+      <c r="J49" s="39"/>
+      <c r="K49" s="41" t="s">
+        <v>96</v>
+      </c>
+      <c r="L49" s="39"/>
+      <c r="M49" s="39"/>
+      <c r="N49" s="39"/>
+      <c r="O49" s="39"/>
+      <c r="P49" s="39"/>
+      <c r="Q49" s="39"/>
+      <c r="R49" s="9"/>
+      <c r="S49" s="28"/>
+    </row>
+    <row r="50" s="3" customFormat="1" ht="16.5" spans="1:22">
+      <c r="A50" s="39">
+        <v>30170002</v>
+      </c>
+      <c r="B50" s="40">
+        <v>101700</v>
+      </c>
+      <c r="C50" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="D50" s="43">
+        <v>301702</v>
+      </c>
+      <c r="E50" s="43" t="s">
+        <v>97</v>
+      </c>
+      <c r="F50" s="39" t="s">
+        <v>82</v>
+      </c>
+      <c r="G50" s="39">
+        <v>2017001</v>
+      </c>
+      <c r="H50" s="39" t="s">
+        <v>59</v>
+      </c>
+      <c r="I50" s="39" t="s">
+        <v>79</v>
+      </c>
+      <c r="J50" s="39"/>
+      <c r="K50" s="41" t="s">
+        <v>96</v>
+      </c>
+      <c r="L50" s="39"/>
+      <c r="M50" s="39"/>
+      <c r="N50" s="39"/>
+      <c r="O50" s="39"/>
+      <c r="P50" s="39"/>
+      <c r="Q50" s="39"/>
+      <c r="R50" s="9"/>
+      <c r="S50" s="28"/>
+    </row>
+    <row r="51" s="3" customFormat="1" ht="16.5" spans="1:22">
+      <c r="A51" s="39">
+        <v>30220001</v>
+      </c>
+      <c r="B51" s="40">
+        <v>102200</v>
+      </c>
+      <c r="C51" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="D51" s="43">
+        <v>302201</v>
+      </c>
+      <c r="E51" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="F51" s="39" t="s">
+        <v>52</v>
+      </c>
+      <c r="G51" s="39">
+        <v>2022001</v>
+      </c>
+      <c r="H51" s="39" t="s">
+        <v>59</v>
+      </c>
+      <c r="I51" s="39"/>
+      <c r="J51" s="39"/>
+      <c r="K51" s="41" t="s">
+        <v>100</v>
+      </c>
+      <c r="L51" s="39" t="s">
+        <v>101</v>
+      </c>
+      <c r="M51" s="39"/>
+      <c r="N51" s="39"/>
+      <c r="O51" s="39"/>
+      <c r="P51" s="39"/>
+      <c r="Q51" s="39"/>
+      <c r="R51" s="9"/>
+      <c r="S51" s="28"/>
+    </row>
+    <row r="52" s="3" customFormat="1" ht="16.5" spans="1:22">
+      <c r="A52" s="39">
+        <v>30220002</v>
+      </c>
+      <c r="B52" s="40">
+        <v>102200</v>
+      </c>
+      <c r="C52" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="D52" s="43">
+        <v>302202</v>
+      </c>
+      <c r="E52" s="43" t="s">
+        <v>102</v>
+      </c>
+      <c r="F52" s="39" t="s">
+        <v>52</v>
+      </c>
+      <c r="G52" s="39">
+        <v>2022001</v>
+      </c>
+      <c r="H52" s="39" t="s">
+        <v>59</v>
+      </c>
+      <c r="I52" s="39"/>
+      <c r="J52" s="39"/>
+      <c r="K52" s="41" t="s">
+        <v>103</v>
+      </c>
+      <c r="L52" s="39" t="s">
+        <v>101</v>
+      </c>
+      <c r="M52" s="39"/>
+      <c r="N52" s="39"/>
+      <c r="O52" s="39"/>
+      <c r="P52" s="39"/>
+      <c r="Q52" s="39"/>
+      <c r="R52" s="9"/>
+      <c r="S52" s="28"/>
+    </row>
+    <row r="53" ht="16.5" spans="1:22">
       <c r="S53"/>
       <c r="U53" s="1"/>
       <c r="V53" s="1"/>
     </row>
-    <row r="54" ht="16.5" spans="19:22">
+    <row r="54" ht="16.5" spans="1:22">
       <c r="S54"/>
       <c r="U54" s="1"/>
       <c r="V54" s="1"/>
     </row>
-    <row r="55" ht="16.5" spans="19:22">
+    <row r="55" ht="16.5" spans="1:22">
       <c r="S55"/>
       <c r="U55" s="1"/>
       <c r="V55" s="1"/>
     </row>
-    <row r="56" ht="16.5" spans="19:22">
+    <row r="56" ht="16.5" spans="1:22">
       <c r="S56"/>
       <c r="U56" s="1"/>
       <c r="V56" s="1"/>
     </row>
-    <row r="57" ht="16.5" spans="19:22">
+    <row r="57" ht="16.5" spans="1:22">
       <c r="S57"/>
       <c r="U57" s="1"/>
       <c r="V57" s="1"/>
@@ -3983,28 +4157,28 @@
   <dimension ref="A1:H47"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="7"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="B1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:8">
@@ -4012,16 +4186,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:8">
@@ -4029,16 +4203,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:8">
@@ -4046,16 +4220,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:8">
@@ -4063,16 +4237,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="F7" s="1">
         <v>2</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:8">
@@ -4080,16 +4254,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="F8" s="1">
         <v>3</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:8">
@@ -4097,16 +4271,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="F9" s="1">
         <v>4</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:8">
@@ -4114,16 +4288,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="F10" s="1">
         <v>5</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:8">
@@ -4131,16 +4305,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F11" s="1">
         <v>6</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:8">
@@ -4148,16 +4322,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="F12" s="1">
         <v>7</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:8">
@@ -4165,16 +4339,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="F13" s="1">
         <v>8</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:8">
@@ -4182,16 +4356,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="F14" s="1">
         <v>9</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:8">
@@ -4199,16 +4373,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="F15" s="1">
         <v>10</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:8">
@@ -4216,16 +4390,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="F16" s="1">
         <v>11</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:8">
@@ -4233,16 +4407,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="F17" s="1">
         <v>12</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:8">
@@ -4250,16 +4424,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="F18" s="1">
         <v>13</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:8">
@@ -4267,16 +4441,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="F19" s="1">
         <v>14</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:8">
@@ -4284,16 +4458,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="F20" s="1">
         <v>15</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:8">
@@ -4301,16 +4475,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="F21" s="1">
         <v>16</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:8">
@@ -4318,16 +4492,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="F22" s="1">
         <v>17</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:8">
@@ -4335,16 +4509,16 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="F23" s="1">
         <v>18</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:8">
@@ -4352,80 +4526,80 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="F24" s="1">
         <v>19</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25">
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26">
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
       <c r="A27">
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
       <c r="A28">
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
       <c r="A29">
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
       <c r="A30">
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
       <c r="A31">
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
       <c r="A32">
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -4433,7 +4607,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -4441,7 +4615,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -4449,7 +4623,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -4457,7 +4631,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -4465,7 +4639,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -4473,7 +4647,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -4481,7 +4655,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -4489,7 +4663,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -4497,7 +4671,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -4505,7 +4679,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -4513,7 +4687,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -4521,7 +4695,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -4529,7 +4703,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -4537,7 +4711,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -4545,7 +4719,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialAuxiliary.xlsx
+++ b/slots/resources/sample/SpecialAuxiliary.xlsx
@@ -268,7 +268,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="200">
   <si>
     <t>小游戏模式ID</t>
   </si>
@@ -580,6 +580,27 @@
   </si>
   <si>
     <t>10220021|10220099|10220012</t>
+  </si>
+  <si>
+    <t>杰克船长</t>
+  </si>
+  <si>
+    <t>免费游戏-免费旋转-10次</t>
+  </si>
+  <si>
+    <t>10_1</t>
+  </si>
+  <si>
+    <t>探宝玩法</t>
+  </si>
+  <si>
+    <t>探宝小游戏</t>
+  </si>
+  <si>
+    <t>探宝地区个数</t>
+  </si>
+  <si>
+    <t>20_200_1|40_500_2|60_1000_3|80_1500_3|100_1500_3|120_1500_3|140_1500_2|160_1500_2|180_1000_2|200_1000_2|220_500_2|240_200_1|</t>
   </si>
   <si>
     <t>typeID</t>
@@ -1025,6 +1046,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
@@ -1037,26 +1064,14 @@
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1068,8 +1083,14 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="42">
+  <fills count="43">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1091,6 +1112,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1447,7 +1474,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1471,16 +1498,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1489,92 +1516,92 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1584,12 +1611,13 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1610,7 +1638,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1619,19 +1647,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="176" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
@@ -1639,11 +1655,15 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="176" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1651,14 +1671,22 @@
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1691,6 +1719,14 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="52">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2034,7 +2070,7 @@
     <col min="8" max="8" width="16.25" customWidth="1"/>
     <col min="9" max="9" width="29.375" customWidth="1"/>
     <col min="10" max="10" width="42.5" customWidth="1"/>
-    <col min="11" max="11" width="41.25" style="7" customWidth="1"/>
+    <col min="11" max="11" width="41.25" style="8" customWidth="1"/>
     <col min="12" max="12" width="11.75" style="3" customWidth="1"/>
     <col min="13" max="13" width="34.4083333333333" style="3" customWidth="1"/>
     <col min="14" max="14" width="7.93333333333333" style="3" customWidth="1"/>
@@ -2042,7 +2078,7 @@
     <col min="16" max="16" width="8.96666666666667" customWidth="1"/>
     <col min="17" max="17" width="93.375" customWidth="1"/>
     <col min="18" max="18" width="10.625" customWidth="1"/>
-    <col min="19" max="19" width="23.75" style="8" customWidth="1"/>
+    <col min="19" max="19" width="23.75" style="9" customWidth="1"/>
     <col min="20" max="20" width="60.875" customWidth="1"/>
     <col min="21" max="22" width="11.5"/>
   </cols>
@@ -2051,671 +2087,671 @@
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9" t="s">
+      <c r="C1" s="10"/>
+      <c r="D1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9" t="s">
+      <c r="E1" s="10"/>
+      <c r="F1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9" t="s">
+      <c r="H1" s="10"/>
+      <c r="I1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="K1" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9" t="s">
+      <c r="L1" s="10"/>
+      <c r="M1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="9"/>
-      <c r="O1" s="12" t="s">
+      <c r="N1" s="10"/>
+      <c r="O1" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="12" t="s">
+      <c r="P1" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="Q1" s="12" t="s">
+      <c r="Q1" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="R1" s="13" t="s">
+      <c r="R1" s="14" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="2" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9" t="s">
+      <c r="C2" s="10"/>
+      <c r="D2" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="9"/>
-      <c r="F2" s="12" t="s">
+      <c r="E2" s="10"/>
+      <c r="F2" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="15" t="s">
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="16" t="s">
+      <c r="K2" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="L2" s="12"/>
-      <c r="M2" s="15" t="s">
+      <c r="L2" s="13"/>
+      <c r="M2" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="N2" s="9"/>
-      <c r="O2" s="12" t="s">
+      <c r="N2" s="10"/>
+      <c r="O2" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="P2" s="12" t="s">
+      <c r="P2" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="Q2" s="15" t="s">
+      <c r="Q2" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="R2" s="13" t="s">
+      <c r="R2" s="14" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="3" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17" t="s">
+      <c r="C3" s="18"/>
+      <c r="D3" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17" t="s">
+      <c r="E3" s="18"/>
+      <c r="F3" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="18" t="s">
+      <c r="G3" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="H3" s="17"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="19" t="s">
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="K3" s="20" t="s">
+      <c r="K3" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="L3" s="17"/>
-      <c r="M3" s="17" t="s">
+      <c r="L3" s="18"/>
+      <c r="M3" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="17"/>
-      <c r="O3" s="12" t="s">
+      <c r="N3" s="18"/>
+      <c r="O3" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="P3" s="12" t="s">
+      <c r="P3" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="Q3" s="12" t="s">
+      <c r="Q3" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="R3" s="21" t="s">
+      <c r="R3" s="22" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="4" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="22"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
-      <c r="N4" s="9"/>
-      <c r="O4" s="9"/>
-      <c r="P4" s="9"/>
-      <c r="Q4" s="9"/>
-      <c r="R4" s="9"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="12"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="10"/>
+      <c r="Q4" s="10"/>
+      <c r="R4" s="10"/>
     </row>
     <row r="5" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A5" s="23">
+      <c r="A5" s="24">
         <v>30010001</v>
       </c>
-      <c r="B5" s="24">
+      <c r="B5" s="25">
         <v>100100</v>
       </c>
-      <c r="C5" s="24" t="s">
+      <c r="C5" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="D5" s="23">
+      <c r="D5" s="24">
         <v>31001</v>
       </c>
-      <c r="E5" s="23" t="s">
+      <c r="E5" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="F5" s="23" t="s">
+      <c r="F5" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="G5" s="23"/>
-      <c r="H5" s="23"/>
-      <c r="I5" s="23" t="s">
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="J5" s="23"/>
-      <c r="K5" s="25"/>
-      <c r="L5" s="9" t="s">
+      <c r="J5" s="24"/>
+      <c r="K5" s="26"/>
+      <c r="L5" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="M5" s="23" t="s">
+      <c r="M5" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="N5" s="23" t="s">
+      <c r="N5" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="O5" s="23"/>
-      <c r="P5" s="23"/>
-      <c r="Q5" s="26" t="s">
+      <c r="O5" s="24"/>
+      <c r="P5" s="24"/>
+      <c r="Q5" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="R5" s="27" t="s">
+      <c r="R5" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="S5" s="28" t="s">
+      <c r="S5" s="29" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="6" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A6" s="23">
+      <c r="A6" s="24">
         <v>30010002</v>
       </c>
-      <c r="B6" s="24">
+      <c r="B6" s="25">
         <v>100100</v>
       </c>
-      <c r="C6" s="24" t="s">
+      <c r="C6" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="23">
+      <c r="D6" s="24">
         <v>31002</v>
       </c>
-      <c r="E6" s="23" t="s">
+      <c r="E6" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="F6" s="23" t="s">
+      <c r="F6" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="G6" s="23"/>
-      <c r="H6" s="23"/>
-      <c r="I6" s="23" t="s">
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="J6" s="23"/>
-      <c r="K6" s="25"/>
-      <c r="L6" s="9" t="s">
+      <c r="J6" s="24"/>
+      <c r="K6" s="26"/>
+      <c r="L6" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="M6" s="23" t="s">
+      <c r="M6" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="N6" s="23" t="s">
+      <c r="N6" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="O6" s="23"/>
-      <c r="P6" s="23"/>
-      <c r="Q6" s="26" t="s">
+      <c r="O6" s="24"/>
+      <c r="P6" s="24"/>
+      <c r="Q6" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="R6" s="27" t="s">
+      <c r="R6" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="S6" s="28"/>
+      <c r="S6" s="29"/>
     </row>
     <row r="7" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A7" s="23">
+      <c r="A7" s="24">
         <v>30010003</v>
       </c>
-      <c r="B7" s="24">
+      <c r="B7" s="25">
         <v>100100</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="C7" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="23">
+      <c r="D7" s="24">
         <v>31003</v>
       </c>
-      <c r="E7" s="23" t="s">
+      <c r="E7" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="23" t="s">
+      <c r="F7" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="G7" s="23"/>
-      <c r="H7" s="23"/>
-      <c r="I7" s="23" t="s">
+      <c r="G7" s="24"/>
+      <c r="H7" s="24"/>
+      <c r="I7" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="J7" s="23"/>
-      <c r="K7" s="25"/>
-      <c r="L7" s="9" t="s">
+      <c r="J7" s="24"/>
+      <c r="K7" s="26"/>
+      <c r="L7" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="M7" s="23" t="s">
+      <c r="M7" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="N7" s="23" t="s">
+      <c r="N7" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="O7" s="23"/>
-      <c r="P7" s="23"/>
-      <c r="Q7" s="26" t="s">
+      <c r="O7" s="24"/>
+      <c r="P7" s="24"/>
+      <c r="Q7" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="R7" s="27" t="s">
+      <c r="R7" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="S7" s="28"/>
+      <c r="S7" s="29"/>
     </row>
     <row r="8" s="3" customFormat="1" ht="15" customHeight="1" spans="1:19">
-      <c r="A8" s="23">
+      <c r="A8" s="24">
         <v>30010004</v>
       </c>
-      <c r="B8" s="24">
+      <c r="B8" s="25">
         <v>100100</v>
       </c>
-      <c r="C8" s="24" t="s">
+      <c r="C8" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="23">
+      <c r="D8" s="24">
         <v>31004</v>
       </c>
-      <c r="E8" s="23" t="s">
+      <c r="E8" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="23" t="s">
+      <c r="F8" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="G8" s="23"/>
-      <c r="H8" s="23"/>
-      <c r="I8" s="23" t="s">
+      <c r="G8" s="24"/>
+      <c r="H8" s="24"/>
+      <c r="I8" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="J8" s="23"/>
-      <c r="K8" s="25"/>
-      <c r="L8" s="9" t="s">
+      <c r="J8" s="24"/>
+      <c r="K8" s="26"/>
+      <c r="L8" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="M8" s="23" t="s">
+      <c r="M8" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="N8" s="23" t="s">
+      <c r="N8" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="O8" s="23"/>
-      <c r="P8" s="23"/>
-      <c r="Q8" s="26" t="s">
+      <c r="O8" s="24"/>
+      <c r="P8" s="24"/>
+      <c r="Q8" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="R8" s="27" t="s">
+      <c r="R8" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="S8" s="28"/>
+      <c r="S8" s="29"/>
     </row>
     <row r="9" s="3" customFormat="1" ht="15" customHeight="1" spans="1:19">
-      <c r="A9" s="9">
+      <c r="A9" s="10">
         <v>30010005</v>
       </c>
-      <c r="B9" s="21">
+      <c r="B9" s="22">
         <v>100100</v>
       </c>
-      <c r="C9" s="24" t="s">
+      <c r="C9" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="10">
         <v>31101</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="F9" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9" t="s">
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="J9" s="9"/>
-      <c r="K9" s="11"/>
-      <c r="L9" s="9" t="s">
+      <c r="J9" s="10"/>
+      <c r="K9" s="12"/>
+      <c r="L9" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="M9" s="9" t="s">
+      <c r="M9" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="N9" s="9"/>
-      <c r="O9" s="9" t="s">
+      <c r="N9" s="10"/>
+      <c r="O9" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="P9" s="9"/>
-      <c r="Q9" s="12"/>
-      <c r="R9" s="12"/>
-      <c r="S9" s="28"/>
+      <c r="P9" s="10"/>
+      <c r="Q9" s="13"/>
+      <c r="R9" s="13"/>
+      <c r="S9" s="29"/>
     </row>
     <row r="10" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A10" s="29">
+      <c r="A10" s="30">
         <v>30010006</v>
       </c>
-      <c r="B10" s="30">
+      <c r="B10" s="31">
         <v>100100</v>
       </c>
-      <c r="C10" s="24" t="s">
+      <c r="C10" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="30">
         <v>31102</v>
       </c>
-      <c r="E10" s="29" t="s">
+      <c r="E10" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="F10" s="29" t="s">
+      <c r="F10" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="G10" s="29"/>
-      <c r="H10" s="29"/>
-      <c r="I10" s="29" t="s">
+      <c r="G10" s="30"/>
+      <c r="H10" s="30"/>
+      <c r="I10" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="J10" s="29"/>
-      <c r="K10" s="31"/>
-      <c r="L10" s="29" t="s">
+      <c r="J10" s="30"/>
+      <c r="K10" s="32"/>
+      <c r="L10" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="M10" s="29" t="s">
+      <c r="M10" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="N10" s="29" t="s">
+      <c r="N10" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="O10" s="29" t="s">
+      <c r="O10" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="P10" s="29"/>
-      <c r="Q10" s="29"/>
-      <c r="R10" s="9"/>
-      <c r="S10" s="28"/>
+      <c r="P10" s="30"/>
+      <c r="Q10" s="30"/>
+      <c r="R10" s="10"/>
+      <c r="S10" s="29"/>
     </row>
     <row r="11" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A11" s="32">
+      <c r="A11" s="33">
         <v>30010007</v>
       </c>
-      <c r="B11" s="33">
+      <c r="B11" s="34">
         <v>100100</v>
       </c>
-      <c r="C11" s="24" t="s">
+      <c r="C11" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="34">
+      <c r="D11" s="35">
         <v>31201</v>
       </c>
-      <c r="E11" s="34" t="s">
+      <c r="E11" s="35" t="s">
         <v>57</v>
       </c>
-      <c r="F11" s="32" t="s">
+      <c r="F11" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="G11" s="32">
+      <c r="G11" s="33">
         <v>2001001</v>
       </c>
-      <c r="H11" s="32" t="s">
+      <c r="H11" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="I11" s="32" t="s">
+      <c r="I11" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="J11" s="32"/>
-      <c r="K11" s="35">
+      <c r="J11" s="33"/>
+      <c r="K11" s="36">
         <v>10010091</v>
       </c>
-      <c r="L11" s="32"/>
-      <c r="M11" s="32"/>
-      <c r="N11" s="32"/>
-      <c r="O11" s="32"/>
-      <c r="P11" s="32"/>
-      <c r="Q11" s="32"/>
-      <c r="R11" s="9"/>
-      <c r="S11" s="28"/>
+      <c r="L11" s="33"/>
+      <c r="M11" s="33"/>
+      <c r="N11" s="33"/>
+      <c r="O11" s="33"/>
+      <c r="P11" s="33"/>
+      <c r="Q11" s="33"/>
+      <c r="R11" s="10"/>
+      <c r="S11" s="29"/>
     </row>
     <row r="12" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A12" s="36">
+      <c r="A12" s="37">
         <v>30010008</v>
       </c>
-      <c r="B12" s="37">
+      <c r="B12" s="38">
         <v>100100</v>
       </c>
-      <c r="C12" s="24" t="s">
+      <c r="C12" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="D12" s="34">
+      <c r="D12" s="35">
         <v>31202</v>
       </c>
-      <c r="E12" s="34" t="s">
+      <c r="E12" s="35" t="s">
         <v>61</v>
       </c>
-      <c r="F12" s="36" t="s">
+      <c r="F12" s="37" t="s">
         <v>52</v>
       </c>
-      <c r="G12" s="36">
+      <c r="G12" s="37">
         <v>2001001</v>
       </c>
-      <c r="H12" s="36" t="s">
+      <c r="H12" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="I12" s="36" t="s">
+      <c r="I12" s="37" t="s">
         <v>62</v>
       </c>
-      <c r="J12" s="36"/>
-      <c r="K12" s="38" t="s">
+      <c r="J12" s="37"/>
+      <c r="K12" s="39" t="s">
         <v>63</v>
       </c>
-      <c r="L12" s="36"/>
-      <c r="M12" s="36"/>
-      <c r="N12" s="36"/>
-      <c r="O12" s="36"/>
-      <c r="P12" s="36"/>
-      <c r="Q12" s="36"/>
-      <c r="R12" s="9"/>
-      <c r="S12" s="28"/>
+      <c r="L12" s="37"/>
+      <c r="M12" s="37"/>
+      <c r="N12" s="37"/>
+      <c r="O12" s="37"/>
+      <c r="P12" s="37"/>
+      <c r="Q12" s="37"/>
+      <c r="R12" s="10"/>
+      <c r="S12" s="29"/>
     </row>
     <row r="13" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A13" s="39">
+      <c r="A13" s="40">
         <v>30010009</v>
       </c>
-      <c r="B13" s="40">
+      <c r="B13" s="41">
         <v>100100</v>
       </c>
-      <c r="C13" s="24" t="s">
+      <c r="C13" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="34">
+      <c r="D13" s="35">
         <v>31203</v>
       </c>
-      <c r="E13" s="34" t="s">
+      <c r="E13" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="F13" s="39" t="s">
+      <c r="F13" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="G13" s="39">
+      <c r="G13" s="40">
         <v>2001001</v>
       </c>
-      <c r="H13" s="39" t="s">
+      <c r="H13" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="I13" s="39" t="s">
+      <c r="I13" s="40" t="s">
         <v>65</v>
       </c>
-      <c r="J13" s="39"/>
-      <c r="K13" s="41" t="s">
+      <c r="J13" s="40"/>
+      <c r="K13" s="42" t="s">
         <v>66</v>
       </c>
-      <c r="L13" s="39"/>
-      <c r="M13" s="39"/>
-      <c r="N13" s="39"/>
-      <c r="O13" s="39"/>
-      <c r="P13" s="39"/>
-      <c r="Q13" s="39"/>
-      <c r="R13" s="9"/>
-      <c r="S13" s="28"/>
+      <c r="L13" s="40"/>
+      <c r="M13" s="40"/>
+      <c r="N13" s="40"/>
+      <c r="O13" s="40"/>
+      <c r="P13" s="40"/>
+      <c r="Q13" s="40"/>
+      <c r="R13" s="10"/>
+      <c r="S13" s="29"/>
     </row>
     <row r="14" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A14" s="34">
+      <c r="A14" s="35">
         <v>30010010</v>
       </c>
-      <c r="B14" s="42">
+      <c r="B14" s="43">
         <v>100100</v>
       </c>
-      <c r="C14" s="24" t="s">
+      <c r="C14" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="43">
+      <c r="D14" s="44">
         <v>31301</v>
       </c>
-      <c r="E14" s="43" t="s">
+      <c r="E14" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="F14" s="34" t="s">
+      <c r="F14" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="G14" s="34"/>
-      <c r="H14" s="34"/>
-      <c r="I14" s="34" t="s">
+      <c r="G14" s="35"/>
+      <c r="H14" s="35"/>
+      <c r="I14" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="J14" s="34"/>
-      <c r="K14" s="44"/>
-      <c r="L14" s="34" t="s">
+      <c r="J14" s="35"/>
+      <c r="K14" s="45"/>
+      <c r="L14" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="M14" s="34" t="s">
+      <c r="M14" s="35" t="s">
         <v>69</v>
       </c>
-      <c r="N14" s="34"/>
-      <c r="O14" s="34"/>
-      <c r="P14" s="34"/>
-      <c r="Q14" s="45" t="s">
+      <c r="N14" s="35"/>
+      <c r="O14" s="35"/>
+      <c r="P14" s="35"/>
+      <c r="Q14" s="46" t="s">
         <v>70</v>
       </c>
-      <c r="R14" s="46" t="s">
+      <c r="R14" s="47" t="s">
         <v>71</v>
       </c>
-      <c r="S14" s="12" t="s">
+      <c r="S14" s="13" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="15" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A15" s="39">
+      <c r="A15" s="40">
         <v>30010011</v>
       </c>
-      <c r="B15" s="40">
+      <c r="B15" s="41">
         <v>100100</v>
       </c>
-      <c r="C15" s="24" t="s">
+      <c r="C15" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="D15" s="43">
+      <c r="D15" s="44">
         <v>31302</v>
       </c>
-      <c r="E15" s="43" t="s">
+      <c r="E15" s="44" t="s">
         <v>73</v>
       </c>
-      <c r="F15" s="39" t="s">
+      <c r="F15" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="G15" s="39"/>
-      <c r="H15" s="39"/>
-      <c r="I15" s="39" t="s">
+      <c r="G15" s="40"/>
+      <c r="H15" s="40"/>
+      <c r="I15" s="40" t="s">
         <v>74</v>
       </c>
-      <c r="J15" s="39"/>
-      <c r="K15" s="41"/>
-      <c r="L15" s="39" t="s">
+      <c r="J15" s="40"/>
+      <c r="K15" s="42"/>
+      <c r="L15" s="40" t="s">
         <v>35</v>
       </c>
-      <c r="M15" s="39" t="s">
+      <c r="M15" s="40" t="s">
         <v>56</v>
       </c>
-      <c r="N15" s="39"/>
-      <c r="O15" s="39"/>
-      <c r="P15" s="39"/>
-      <c r="Q15" s="39"/>
-      <c r="R15" s="9"/>
-      <c r="S15" s="28"/>
+      <c r="N15" s="40"/>
+      <c r="O15" s="40"/>
+      <c r="P15" s="40"/>
+      <c r="Q15" s="40"/>
+      <c r="R15" s="10"/>
+      <c r="S15" s="29"/>
     </row>
     <row r="16" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A16" s="39">
+      <c r="A16" s="40">
         <v>30010012</v>
       </c>
-      <c r="B16" s="40">
+      <c r="B16" s="41">
         <v>100100</v>
       </c>
-      <c r="C16" s="24" t="s">
+      <c r="C16" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="D16" s="43">
+      <c r="D16" s="44">
         <v>31303</v>
       </c>
-      <c r="E16" s="43" t="s">
+      <c r="E16" s="44" t="s">
         <v>75</v>
       </c>
-      <c r="F16" s="39" t="s">
+      <c r="F16" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="G16" s="39">
+      <c r="G16" s="40">
         <v>2001001</v>
       </c>
-      <c r="H16" s="39" t="s">
+      <c r="H16" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="I16" s="39" t="s">
+      <c r="I16" s="40" t="s">
         <v>65</v>
       </c>
-      <c r="J16" s="39"/>
-      <c r="K16" s="41" t="s">
+      <c r="J16" s="40"/>
+      <c r="K16" s="42" t="s">
         <v>66</v>
       </c>
-      <c r="L16" s="39"/>
-      <c r="M16" s="39"/>
-      <c r="N16" s="39"/>
-      <c r="O16" s="39"/>
-      <c r="P16" s="39"/>
-      <c r="Q16" s="39"/>
-      <c r="R16" s="9"/>
-      <c r="S16" s="28"/>
+      <c r="L16" s="40"/>
+      <c r="M16" s="40"/>
+      <c r="N16" s="40"/>
+      <c r="O16" s="40"/>
+      <c r="P16" s="40"/>
+      <c r="Q16" s="40"/>
+      <c r="R16" s="10"/>
+      <c r="S16" s="29"/>
     </row>
     <row r="17" s="3" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A17" s="9">
+      <c r="A17" s="10">
         <v>30070001</v>
       </c>
       <c r="B17" s="3">
@@ -2724,30 +2760,30 @@
       <c r="C17" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D17" s="32">
+      <c r="D17" s="33">
         <v>34001</v>
       </c>
-      <c r="E17" s="32" t="s">
+      <c r="E17" s="33" t="s">
         <v>77</v>
       </c>
-      <c r="F17" s="32" t="s">
+      <c r="F17" s="33" t="s">
         <v>78</v>
       </c>
-      <c r="G17" s="21">
+      <c r="G17" s="22">
         <v>2007001</v>
       </c>
-      <c r="H17" s="9" t="s">
+      <c r="H17" s="10" t="s">
         <v>59</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="K17" s="47" t="s">
+      <c r="K17" s="48" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="18" s="3" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A18" s="9">
+      <c r="A18" s="10">
         <v>30070002</v>
       </c>
       <c r="B18" s="3">
@@ -2756,30 +2792,30 @@
       <c r="C18" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D18" s="32">
+      <c r="D18" s="33">
         <v>34002</v>
       </c>
-      <c r="E18" s="32" t="s">
+      <c r="E18" s="33" t="s">
         <v>81</v>
       </c>
-      <c r="F18" s="32" t="s">
+      <c r="F18" s="33" t="s">
         <v>82</v>
       </c>
-      <c r="G18" s="21">
+      <c r="G18" s="22">
         <v>2007001</v>
       </c>
-      <c r="H18" s="9" t="s">
+      <c r="H18" s="10" t="s">
         <v>59</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="K18" s="47" t="s">
+      <c r="K18" s="48" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="19" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A19" s="34">
+      <c r="A19" s="35">
         <v>30120001</v>
       </c>
       <c r="B19" s="4">
@@ -2788,33 +2824,33 @@
       <c r="C19" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="D19" s="34">
+      <c r="D19" s="35">
         <v>32001</v>
       </c>
-      <c r="E19" s="34" t="s">
+      <c r="E19" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="F19" s="34" t="s">
+      <c r="F19" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="G19" s="42">
+      <c r="G19" s="43">
         <v>2012001</v>
       </c>
-      <c r="H19" s="34" t="s">
+      <c r="H19" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="I19" s="34" t="s">
+      <c r="I19" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="J19" s="34" t="s">
+      <c r="J19" s="35" t="s">
         <v>85</v>
       </c>
-      <c r="K19" s="48">
+      <c r="K19" s="49">
         <v>10120041</v>
       </c>
     </row>
     <row r="20" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A20" s="34">
+      <c r="A20" s="35">
         <v>30120002</v>
       </c>
       <c r="B20" s="4">
@@ -2823,33 +2859,33 @@
       <c r="C20" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="D20" s="34">
+      <c r="D20" s="35">
         <v>32002</v>
       </c>
-      <c r="E20" s="34" t="s">
+      <c r="E20" s="35" t="s">
         <v>86</v>
       </c>
-      <c r="F20" s="34" t="s">
+      <c r="F20" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="G20" s="42">
+      <c r="G20" s="43">
         <v>2012001</v>
       </c>
-      <c r="H20" s="34" t="s">
+      <c r="H20" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="I20" s="34" t="s">
+      <c r="I20" s="35" t="s">
         <v>86</v>
       </c>
-      <c r="J20" s="34" t="s">
+      <c r="J20" s="35" t="s">
         <v>85</v>
       </c>
-      <c r="K20" s="48">
+      <c r="K20" s="49">
         <v>10120042</v>
       </c>
     </row>
     <row r="21" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A21" s="34">
+      <c r="A21" s="35">
         <v>30120003</v>
       </c>
       <c r="B21" s="4">
@@ -2858,33 +2894,33 @@
       <c r="C21" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="D21" s="34">
+      <c r="D21" s="35">
         <v>32003</v>
       </c>
-      <c r="E21" s="34" t="s">
+      <c r="E21" s="35" t="s">
         <v>87</v>
       </c>
-      <c r="F21" s="34" t="s">
+      <c r="F21" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="G21" s="42">
+      <c r="G21" s="43">
         <v>2012001</v>
       </c>
-      <c r="H21" s="34" t="s">
+      <c r="H21" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="I21" s="34" t="s">
+      <c r="I21" s="35" t="s">
         <v>87</v>
       </c>
-      <c r="J21" s="34" t="s">
+      <c r="J21" s="35" t="s">
         <v>85</v>
       </c>
-      <c r="K21" s="48">
+      <c r="K21" s="49">
         <v>10120043</v>
       </c>
     </row>
     <row r="22" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A22" s="34">
+      <c r="A22" s="35">
         <v>30120004</v>
       </c>
       <c r="B22" s="4">
@@ -2893,33 +2929,33 @@
       <c r="C22" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="D22" s="34">
+      <c r="D22" s="35">
         <v>32004</v>
       </c>
-      <c r="E22" s="34" t="s">
+      <c r="E22" s="35" t="s">
         <v>88</v>
       </c>
-      <c r="F22" s="34" t="s">
+      <c r="F22" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="G22" s="42">
+      <c r="G22" s="43">
         <v>2012001</v>
       </c>
-      <c r="H22" s="34" t="s">
+      <c r="H22" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="I22" s="34" t="s">
+      <c r="I22" s="35" t="s">
         <v>88</v>
       </c>
-      <c r="J22" s="34" t="s">
+      <c r="J22" s="35" t="s">
         <v>85</v>
       </c>
-      <c r="K22" s="48">
+      <c r="K22" s="49">
         <v>10120044</v>
       </c>
     </row>
     <row r="23" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A23" s="34">
+      <c r="A23" s="35">
         <v>30120005</v>
       </c>
       <c r="B23" s="4">
@@ -2928,33 +2964,33 @@
       <c r="C23" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="D23" s="34">
+      <c r="D23" s="35">
         <v>32005</v>
       </c>
-      <c r="E23" s="34" t="s">
+      <c r="E23" s="35" t="s">
         <v>88</v>
       </c>
-      <c r="F23" s="34" t="s">
+      <c r="F23" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="G23" s="42">
+      <c r="G23" s="43">
         <v>2012001</v>
       </c>
-      <c r="H23" s="34" t="s">
+      <c r="H23" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="I23" s="34" t="s">
+      <c r="I23" s="35" t="s">
         <v>88</v>
       </c>
-      <c r="J23" s="34" t="s">
+      <c r="J23" s="35" t="s">
         <v>85</v>
       </c>
-      <c r="K23" s="48">
+      <c r="K23" s="49">
         <v>10120045</v>
       </c>
     </row>
     <row r="24" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A24" s="34">
+      <c r="A24" s="35">
         <v>30120006</v>
       </c>
       <c r="B24" s="4">
@@ -2963,33 +2999,33 @@
       <c r="C24" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="D24" s="34">
+      <c r="D24" s="35">
         <v>32006</v>
       </c>
-      <c r="E24" s="34" t="s">
+      <c r="E24" s="35" t="s">
         <v>88</v>
       </c>
-      <c r="F24" s="34" t="s">
+      <c r="F24" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="G24" s="42">
+      <c r="G24" s="43">
         <v>2012001</v>
       </c>
-      <c r="H24" s="34" t="s">
+      <c r="H24" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="I24" s="34" t="s">
+      <c r="I24" s="35" t="s">
         <v>88</v>
       </c>
-      <c r="J24" s="34" t="s">
+      <c r="J24" s="35" t="s">
         <v>85</v>
       </c>
-      <c r="K24" s="48">
+      <c r="K24" s="49">
         <v>10120046</v>
       </c>
     </row>
     <row r="25" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A25" s="49">
+      <c r="A25" s="50">
         <v>30120011</v>
       </c>
       <c r="B25" s="5">
@@ -2998,33 +3034,33 @@
       <c r="C25" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="D25" s="34">
+      <c r="D25" s="35">
         <v>32101</v>
       </c>
-      <c r="E25" s="49" t="s">
+      <c r="E25" s="50" t="s">
         <v>84</v>
       </c>
-      <c r="F25" s="49" t="s">
+      <c r="F25" s="50" t="s">
         <v>52</v>
       </c>
-      <c r="G25" s="50">
+      <c r="G25" s="51">
         <v>2012001</v>
       </c>
-      <c r="H25" s="49" t="s">
+      <c r="H25" s="50" t="s">
         <v>59</v>
       </c>
-      <c r="I25" s="49" t="s">
+      <c r="I25" s="50" t="s">
         <v>84</v>
       </c>
-      <c r="J25" s="49" t="s">
+      <c r="J25" s="50" t="s">
         <v>90</v>
       </c>
-      <c r="K25" s="51">
+      <c r="K25" s="52">
         <v>10120041</v>
       </c>
     </row>
     <row r="26" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A26" s="49">
+      <c r="A26" s="50">
         <v>30120012</v>
       </c>
       <c r="B26" s="5">
@@ -3033,33 +3069,33 @@
       <c r="C26" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="D26" s="34">
+      <c r="D26" s="35">
         <v>32102</v>
       </c>
-      <c r="E26" s="49" t="s">
+      <c r="E26" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="F26" s="49" t="s">
+      <c r="F26" s="50" t="s">
         <v>52</v>
       </c>
-      <c r="G26" s="50">
+      <c r="G26" s="51">
         <v>2012001</v>
       </c>
-      <c r="H26" s="49" t="s">
+      <c r="H26" s="50" t="s">
         <v>59</v>
       </c>
-      <c r="I26" s="49" t="s">
+      <c r="I26" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="J26" s="49" t="s">
+      <c r="J26" s="50" t="s">
         <v>90</v>
       </c>
-      <c r="K26" s="51">
+      <c r="K26" s="52">
         <v>10120042</v>
       </c>
     </row>
     <row r="27" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A27" s="49">
+      <c r="A27" s="50">
         <v>30120013</v>
       </c>
       <c r="B27" s="5">
@@ -3068,33 +3104,33 @@
       <c r="C27" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="D27" s="34">
+      <c r="D27" s="35">
         <v>32103</v>
       </c>
-      <c r="E27" s="49" t="s">
+      <c r="E27" s="50" t="s">
         <v>87</v>
       </c>
-      <c r="F27" s="49" t="s">
+      <c r="F27" s="50" t="s">
         <v>52</v>
       </c>
-      <c r="G27" s="50">
+      <c r="G27" s="51">
         <v>2012001</v>
       </c>
-      <c r="H27" s="49" t="s">
+      <c r="H27" s="50" t="s">
         <v>59</v>
       </c>
-      <c r="I27" s="49" t="s">
+      <c r="I27" s="50" t="s">
         <v>87</v>
       </c>
-      <c r="J27" s="49" t="s">
+      <c r="J27" s="50" t="s">
         <v>90</v>
       </c>
-      <c r="K27" s="51">
+      <c r="K27" s="52">
         <v>10120043</v>
       </c>
     </row>
     <row r="28" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A28" s="49">
+      <c r="A28" s="50">
         <v>30120014</v>
       </c>
       <c r="B28" s="5">
@@ -3103,33 +3139,33 @@
       <c r="C28" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="D28" s="34">
+      <c r="D28" s="35">
         <v>32104</v>
       </c>
-      <c r="E28" s="49" t="s">
+      <c r="E28" s="50" t="s">
         <v>88</v>
       </c>
-      <c r="F28" s="49" t="s">
+      <c r="F28" s="50" t="s">
         <v>52</v>
       </c>
-      <c r="G28" s="50">
+      <c r="G28" s="51">
         <v>2012001</v>
       </c>
-      <c r="H28" s="49" t="s">
+      <c r="H28" s="50" t="s">
         <v>59</v>
       </c>
-      <c r="I28" s="49" t="s">
+      <c r="I28" s="50" t="s">
         <v>88</v>
       </c>
-      <c r="J28" s="49" t="s">
+      <c r="J28" s="50" t="s">
         <v>90</v>
       </c>
-      <c r="K28" s="51">
+      <c r="K28" s="52">
         <v>10120044</v>
       </c>
     </row>
     <row r="29" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A29" s="49">
+      <c r="A29" s="50">
         <v>30120015</v>
       </c>
       <c r="B29" s="5">
@@ -3138,33 +3174,33 @@
       <c r="C29" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="D29" s="34">
+      <c r="D29" s="35">
         <v>32105</v>
       </c>
-      <c r="E29" s="49" t="s">
+      <c r="E29" s="50" t="s">
         <v>88</v>
       </c>
-      <c r="F29" s="49" t="s">
+      <c r="F29" s="50" t="s">
         <v>52</v>
       </c>
-      <c r="G29" s="50">
+      <c r="G29" s="51">
         <v>2012001</v>
       </c>
-      <c r="H29" s="49" t="s">
+      <c r="H29" s="50" t="s">
         <v>59</v>
       </c>
-      <c r="I29" s="49" t="s">
+      <c r="I29" s="50" t="s">
         <v>88</v>
       </c>
-      <c r="J29" s="49" t="s">
+      <c r="J29" s="50" t="s">
         <v>90</v>
       </c>
-      <c r="K29" s="51">
+      <c r="K29" s="52">
         <v>10120045</v>
       </c>
     </row>
     <row r="30" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A30" s="49">
+      <c r="A30" s="50">
         <v>30120016</v>
       </c>
       <c r="B30" s="5">
@@ -3173,33 +3209,33 @@
       <c r="C30" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="D30" s="34">
+      <c r="D30" s="35">
         <v>32106</v>
       </c>
-      <c r="E30" s="49" t="s">
+      <c r="E30" s="50" t="s">
         <v>88</v>
       </c>
-      <c r="F30" s="49" t="s">
+      <c r="F30" s="50" t="s">
         <v>52</v>
       </c>
-      <c r="G30" s="50">
+      <c r="G30" s="51">
         <v>2012001</v>
       </c>
-      <c r="H30" s="49" t="s">
+      <c r="H30" s="50" t="s">
         <v>59</v>
       </c>
-      <c r="I30" s="49" t="s">
+      <c r="I30" s="50" t="s">
         <v>88</v>
       </c>
-      <c r="J30" s="49" t="s">
+      <c r="J30" s="50" t="s">
         <v>90</v>
       </c>
-      <c r="K30" s="51">
+      <c r="K30" s="52">
         <v>10120046</v>
       </c>
     </row>
     <row r="31" s="6" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A31" s="43">
+      <c r="A31" s="44">
         <v>30120021</v>
       </c>
       <c r="B31" s="6">
@@ -3208,31 +3244,31 @@
       <c r="C31" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D31" s="43">
+      <c r="D31" s="44">
         <v>32201</v>
       </c>
-      <c r="E31" s="43" t="s">
+      <c r="E31" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="F31" s="43" t="s">
+      <c r="F31" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="G31" s="52">
+      <c r="G31" s="53">
         <v>2012001</v>
       </c>
-      <c r="H31" s="43" t="s">
+      <c r="H31" s="44" t="s">
         <v>59</v>
       </c>
-      <c r="I31" s="43" t="s">
+      <c r="I31" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="J31" s="43"/>
-      <c r="K31" s="53">
+      <c r="J31" s="44"/>
+      <c r="K31" s="54">
         <v>10120041</v>
       </c>
     </row>
     <row r="32" s="6" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A32" s="43">
+      <c r="A32" s="44">
         <v>30120022</v>
       </c>
       <c r="B32" s="6">
@@ -3241,31 +3277,31 @@
       <c r="C32" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D32" s="43">
+      <c r="D32" s="44">
         <v>32202</v>
       </c>
-      <c r="E32" s="43" t="s">
+      <c r="E32" s="44" t="s">
         <v>86</v>
       </c>
-      <c r="F32" s="43" t="s">
+      <c r="F32" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="G32" s="52">
+      <c r="G32" s="53">
         <v>2012001</v>
       </c>
-      <c r="H32" s="43" t="s">
+      <c r="H32" s="44" t="s">
         <v>59</v>
       </c>
-      <c r="I32" s="43" t="s">
+      <c r="I32" s="44" t="s">
         <v>86</v>
       </c>
-      <c r="J32" s="43"/>
-      <c r="K32" s="53">
+      <c r="J32" s="44"/>
+      <c r="K32" s="54">
         <v>10120042</v>
       </c>
     </row>
     <row r="33" s="6" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A33" s="43">
+      <c r="A33" s="44">
         <v>30120023</v>
       </c>
       <c r="B33" s="6">
@@ -3274,31 +3310,31 @@
       <c r="C33" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D33" s="43">
+      <c r="D33" s="44">
         <v>32203</v>
       </c>
-      <c r="E33" s="43" t="s">
+      <c r="E33" s="44" t="s">
         <v>87</v>
       </c>
-      <c r="F33" s="43" t="s">
+      <c r="F33" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="G33" s="52">
+      <c r="G33" s="53">
         <v>2012001</v>
       </c>
-      <c r="H33" s="43" t="s">
+      <c r="H33" s="44" t="s">
         <v>59</v>
       </c>
-      <c r="I33" s="43" t="s">
+      <c r="I33" s="44" t="s">
         <v>87</v>
       </c>
-      <c r="J33" s="43"/>
-      <c r="K33" s="53">
+      <c r="J33" s="44"/>
+      <c r="K33" s="54">
         <v>10120043</v>
       </c>
     </row>
     <row r="34" s="6" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A34" s="43">
+      <c r="A34" s="44">
         <v>30120024</v>
       </c>
       <c r="B34" s="6">
@@ -3307,31 +3343,31 @@
       <c r="C34" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D34" s="43">
+      <c r="D34" s="44">
         <v>32204</v>
       </c>
-      <c r="E34" s="43" t="s">
+      <c r="E34" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="F34" s="43" t="s">
+      <c r="F34" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="G34" s="52">
+      <c r="G34" s="53">
         <v>2012001</v>
       </c>
-      <c r="H34" s="43" t="s">
+      <c r="H34" s="44" t="s">
         <v>59</v>
       </c>
-      <c r="I34" s="43" t="s">
+      <c r="I34" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="J34" s="43"/>
-      <c r="K34" s="53">
+      <c r="J34" s="44"/>
+      <c r="K34" s="54">
         <v>10120044</v>
       </c>
     </row>
     <row r="35" s="6" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A35" s="43">
+      <c r="A35" s="44">
         <v>30120025</v>
       </c>
       <c r="B35" s="6">
@@ -3340,31 +3376,31 @@
       <c r="C35" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D35" s="43">
+      <c r="D35" s="44">
         <v>32205</v>
       </c>
-      <c r="E35" s="43" t="s">
+      <c r="E35" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="F35" s="43" t="s">
+      <c r="F35" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="G35" s="52">
+      <c r="G35" s="53">
         <v>2012001</v>
       </c>
-      <c r="H35" s="43" t="s">
+      <c r="H35" s="44" t="s">
         <v>59</v>
       </c>
-      <c r="I35" s="43" t="s">
+      <c r="I35" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="J35" s="43"/>
-      <c r="K35" s="53">
+      <c r="J35" s="44"/>
+      <c r="K35" s="54">
         <v>10120045</v>
       </c>
     </row>
     <row r="36" s="6" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A36" s="43">
+      <c r="A36" s="44">
         <v>30120026</v>
       </c>
       <c r="B36" s="6">
@@ -3373,716 +3409,790 @@
       <c r="C36" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D36" s="43">
+      <c r="D36" s="44">
         <v>32206</v>
       </c>
-      <c r="E36" s="43" t="s">
+      <c r="E36" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="F36" s="43" t="s">
+      <c r="F36" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="G36" s="52">
+      <c r="G36" s="53">
         <v>2012001</v>
       </c>
-      <c r="H36" s="43" t="s">
+      <c r="H36" s="44" t="s">
         <v>59</v>
       </c>
-      <c r="I36" s="43" t="s">
+      <c r="I36" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="J36" s="43"/>
-      <c r="K36" s="53">
+      <c r="J36" s="44"/>
+      <c r="K36" s="54">
         <v>10120046</v>
       </c>
     </row>
     <row r="37" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A37" s="23">
+      <c r="A37" s="24">
         <v>30240001</v>
       </c>
-      <c r="B37" s="24">
+      <c r="B37" s="25">
         <v>102400</v>
       </c>
-      <c r="C37" s="24" t="s">
+      <c r="C37" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="D37" s="23">
+      <c r="D37" s="24">
         <v>32401</v>
       </c>
-      <c r="E37" s="23" t="s">
+      <c r="E37" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="F37" s="23" t="s">
+      <c r="F37" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="G37" s="23"/>
-      <c r="H37" s="23"/>
-      <c r="I37" s="23" t="s">
+      <c r="G37" s="24"/>
+      <c r="H37" s="24"/>
+      <c r="I37" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="J37" s="23"/>
-      <c r="K37" s="25"/>
-      <c r="L37" s="9" t="s">
+      <c r="J37" s="24"/>
+      <c r="K37" s="26"/>
+      <c r="L37" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="M37" s="23" t="s">
+      <c r="M37" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="N37" s="23" t="s">
+      <c r="N37" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="O37" s="23"/>
-      <c r="P37" s="23"/>
-      <c r="Q37" s="26" t="s">
+      <c r="O37" s="24"/>
+      <c r="P37" s="24"/>
+      <c r="Q37" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="R37" s="27" t="s">
+      <c r="R37" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="S37" s="28" t="s">
+      <c r="S37" s="29" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="38" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A38" s="23">
+      <c r="A38" s="24">
         <v>30240002</v>
       </c>
-      <c r="B38" s="24">
+      <c r="B38" s="25">
         <v>102400</v>
       </c>
-      <c r="C38" s="24" t="s">
+      <c r="C38" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="D38" s="23">
+      <c r="D38" s="24">
         <v>32402</v>
       </c>
-      <c r="E38" s="23" t="s">
+      <c r="E38" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="F38" s="23" t="s">
+      <c r="F38" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="G38" s="23"/>
-      <c r="H38" s="23"/>
-      <c r="I38" s="23" t="s">
+      <c r="G38" s="24"/>
+      <c r="H38" s="24"/>
+      <c r="I38" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="J38" s="23"/>
-      <c r="K38" s="25"/>
-      <c r="L38" s="9" t="s">
+      <c r="J38" s="24"/>
+      <c r="K38" s="26"/>
+      <c r="L38" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="M38" s="23" t="s">
+      <c r="M38" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="N38" s="23" t="s">
+      <c r="N38" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="O38" s="23"/>
-      <c r="P38" s="23"/>
-      <c r="Q38" s="26" t="s">
+      <c r="O38" s="24"/>
+      <c r="P38" s="24"/>
+      <c r="Q38" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="R38" s="27" t="s">
+      <c r="R38" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="S38" s="28"/>
+      <c r="S38" s="29"/>
     </row>
     <row r="39" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A39" s="23">
+      <c r="A39" s="24">
         <v>30240003</v>
       </c>
-      <c r="B39" s="24">
+      <c r="B39" s="25">
         <v>102400</v>
       </c>
-      <c r="C39" s="24" t="s">
+      <c r="C39" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="D39" s="23">
+      <c r="D39" s="24">
         <v>32403</v>
       </c>
-      <c r="E39" s="23" t="s">
+      <c r="E39" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="F39" s="23" t="s">
+      <c r="F39" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="G39" s="23"/>
-      <c r="H39" s="23"/>
-      <c r="I39" s="23" t="s">
+      <c r="G39" s="24"/>
+      <c r="H39" s="24"/>
+      <c r="I39" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="J39" s="23"/>
-      <c r="K39" s="25"/>
-      <c r="L39" s="9" t="s">
+      <c r="J39" s="24"/>
+      <c r="K39" s="26"/>
+      <c r="L39" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="M39" s="23" t="s">
+      <c r="M39" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="N39" s="23" t="s">
+      <c r="N39" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="O39" s="23"/>
-      <c r="P39" s="23"/>
-      <c r="Q39" s="26" t="s">
+      <c r="O39" s="24"/>
+      <c r="P39" s="24"/>
+      <c r="Q39" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="R39" s="27" t="s">
+      <c r="R39" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="S39" s="28"/>
+      <c r="S39" s="29"/>
     </row>
     <row r="40" s="3" customFormat="1" ht="15" customHeight="1" spans="1:19">
-      <c r="A40" s="23">
+      <c r="A40" s="24">
         <v>30240004</v>
       </c>
-      <c r="B40" s="24">
+      <c r="B40" s="25">
         <v>102400</v>
       </c>
-      <c r="C40" s="24" t="s">
+      <c r="C40" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="D40" s="23">
+      <c r="D40" s="24">
         <v>32404</v>
       </c>
-      <c r="E40" s="23" t="s">
+      <c r="E40" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="F40" s="23" t="s">
+      <c r="F40" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="G40" s="23"/>
-      <c r="H40" s="23"/>
-      <c r="I40" s="23" t="s">
+      <c r="G40" s="24"/>
+      <c r="H40" s="24"/>
+      <c r="I40" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="J40" s="23"/>
-      <c r="K40" s="25"/>
-      <c r="L40" s="9" t="s">
+      <c r="J40" s="24"/>
+      <c r="K40" s="26"/>
+      <c r="L40" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="M40" s="23" t="s">
+      <c r="M40" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="N40" s="23" t="s">
+      <c r="N40" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="O40" s="23"/>
-      <c r="P40" s="23"/>
-      <c r="Q40" s="26" t="s">
+      <c r="O40" s="24"/>
+      <c r="P40" s="24"/>
+      <c r="Q40" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="R40" s="27" t="s">
+      <c r="R40" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="S40" s="28"/>
+      <c r="S40" s="29"/>
     </row>
     <row r="41" s="3" customFormat="1" ht="15" customHeight="1" spans="1:19">
-      <c r="A41" s="9">
+      <c r="A41" s="10">
         <v>30240005</v>
       </c>
-      <c r="B41" s="21">
+      <c r="B41" s="22">
         <v>102400</v>
       </c>
-      <c r="C41" s="24" t="s">
+      <c r="C41" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="D41" s="9">
+      <c r="D41" s="10">
         <v>32411</v>
       </c>
-      <c r="E41" s="9" t="s">
+      <c r="E41" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="F41" s="9" t="s">
+      <c r="F41" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="G41" s="9"/>
-      <c r="H41" s="9"/>
-      <c r="I41" s="9" t="s">
+      <c r="G41" s="10"/>
+      <c r="H41" s="10"/>
+      <c r="I41" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="J41" s="9"/>
-      <c r="K41" s="11"/>
-      <c r="L41" s="9" t="s">
+      <c r="J41" s="10"/>
+      <c r="K41" s="12"/>
+      <c r="L41" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="M41" s="9" t="s">
+      <c r="M41" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="N41" s="9"/>
-      <c r="O41" s="9" t="s">
+      <c r="N41" s="10"/>
+      <c r="O41" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="P41" s="9"/>
-      <c r="Q41" s="12"/>
-      <c r="R41" s="12"/>
-      <c r="S41" s="28"/>
+      <c r="P41" s="10"/>
+      <c r="Q41" s="13"/>
+      <c r="R41" s="13"/>
+      <c r="S41" s="29"/>
     </row>
     <row r="42" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A42" s="29">
+      <c r="A42" s="30">
         <v>30240006</v>
       </c>
-      <c r="B42" s="30">
+      <c r="B42" s="31">
         <v>102400</v>
       </c>
-      <c r="C42" s="24" t="s">
+      <c r="C42" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="D42" s="29">
+      <c r="D42" s="30">
         <v>32421</v>
       </c>
-      <c r="E42" s="29" t="s">
+      <c r="E42" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="F42" s="29" t="s">
+      <c r="F42" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="G42" s="29"/>
-      <c r="H42" s="29"/>
-      <c r="I42" s="29" t="s">
+      <c r="G42" s="30"/>
+      <c r="H42" s="30"/>
+      <c r="I42" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="J42" s="29"/>
-      <c r="K42" s="31"/>
-      <c r="L42" s="29" t="s">
+      <c r="J42" s="30"/>
+      <c r="K42" s="32"/>
+      <c r="L42" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="M42" s="29" t="s">
+      <c r="M42" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="N42" s="29" t="s">
+      <c r="N42" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="O42" s="29" t="s">
+      <c r="O42" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="P42" s="29"/>
-      <c r="Q42" s="29"/>
-      <c r="R42" s="9"/>
-      <c r="S42" s="28"/>
+      <c r="P42" s="30"/>
+      <c r="Q42" s="30"/>
+      <c r="R42" s="10"/>
+      <c r="S42" s="29"/>
     </row>
     <row r="43" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A43" s="32">
+      <c r="A43" s="33">
         <v>30240007</v>
       </c>
-      <c r="B43" s="33">
+      <c r="B43" s="34">
         <v>102400</v>
       </c>
-      <c r="C43" s="24" t="s">
+      <c r="C43" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="D43" s="34">
+      <c r="D43" s="35">
         <v>32431</v>
       </c>
-      <c r="E43" s="34" t="s">
+      <c r="E43" s="35" t="s">
         <v>57</v>
       </c>
-      <c r="F43" s="32" t="s">
+      <c r="F43" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="G43" s="32">
+      <c r="G43" s="33">
         <v>2024001</v>
       </c>
-      <c r="H43" s="32" t="s">
+      <c r="H43" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="I43" s="32" t="s">
+      <c r="I43" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="J43" s="32"/>
-      <c r="K43" s="35">
+      <c r="J43" s="33"/>
+      <c r="K43" s="36">
         <v>10240091</v>
       </c>
-      <c r="L43" s="32"/>
-      <c r="M43" s="32"/>
-      <c r="N43" s="32"/>
-      <c r="O43" s="32"/>
-      <c r="P43" s="32"/>
-      <c r="Q43" s="32"/>
-      <c r="R43" s="9"/>
-      <c r="S43" s="28"/>
+      <c r="L43" s="33"/>
+      <c r="M43" s="33"/>
+      <c r="N43" s="33"/>
+      <c r="O43" s="33"/>
+      <c r="P43" s="33"/>
+      <c r="Q43" s="33"/>
+      <c r="R43" s="10"/>
+      <c r="S43" s="29"/>
     </row>
     <row r="44" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A44" s="36">
+      <c r="A44" s="37">
         <v>30240008</v>
       </c>
-      <c r="B44" s="37">
+      <c r="B44" s="38">
         <v>102400</v>
       </c>
-      <c r="C44" s="24" t="s">
+      <c r="C44" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="D44" s="34">
+      <c r="D44" s="35">
         <v>32432</v>
       </c>
-      <c r="E44" s="34" t="s">
+      <c r="E44" s="35" t="s">
         <v>61</v>
       </c>
-      <c r="F44" s="36" t="s">
+      <c r="F44" s="37" t="s">
         <v>52</v>
       </c>
-      <c r="G44" s="36">
+      <c r="G44" s="37">
         <v>2024001</v>
       </c>
-      <c r="H44" s="36" t="s">
+      <c r="H44" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="I44" s="36" t="s">
+      <c r="I44" s="37" t="s">
         <v>62</v>
       </c>
-      <c r="J44" s="36"/>
-      <c r="K44" s="38" t="s">
+      <c r="J44" s="37"/>
+      <c r="K44" s="39" t="s">
         <v>92</v>
       </c>
-      <c r="L44" s="36"/>
-      <c r="M44" s="36"/>
-      <c r="N44" s="36"/>
-      <c r="O44" s="36"/>
-      <c r="P44" s="36"/>
-      <c r="Q44" s="36"/>
-      <c r="R44" s="9"/>
-      <c r="S44" s="28"/>
+      <c r="L44" s="37"/>
+      <c r="M44" s="37"/>
+      <c r="N44" s="37"/>
+      <c r="O44" s="37"/>
+      <c r="P44" s="37"/>
+      <c r="Q44" s="37"/>
+      <c r="R44" s="10"/>
+      <c r="S44" s="29"/>
     </row>
     <row r="45" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A45" s="39">
+      <c r="A45" s="40">
         <v>30240009</v>
       </c>
-      <c r="B45" s="40">
+      <c r="B45" s="41">
         <v>102400</v>
       </c>
-      <c r="C45" s="24" t="s">
+      <c r="C45" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="D45" s="34">
+      <c r="D45" s="35">
         <v>32433</v>
       </c>
-      <c r="E45" s="34" t="s">
+      <c r="E45" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="F45" s="39" t="s">
+      <c r="F45" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="G45" s="39">
+      <c r="G45" s="40">
         <v>2024001</v>
       </c>
-      <c r="H45" s="39" t="s">
+      <c r="H45" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="I45" s="39" t="s">
+      <c r="I45" s="40" t="s">
         <v>65</v>
       </c>
-      <c r="J45" s="39"/>
-      <c r="K45" s="41" t="s">
+      <c r="J45" s="40"/>
+      <c r="K45" s="42" t="s">
         <v>93</v>
       </c>
-      <c r="L45" s="39"/>
-      <c r="M45" s="39"/>
-      <c r="N45" s="39"/>
-      <c r="O45" s="39"/>
-      <c r="P45" s="39"/>
-      <c r="Q45" s="39"/>
-      <c r="R45" s="9"/>
-      <c r="S45" s="28"/>
+      <c r="L45" s="40"/>
+      <c r="M45" s="40"/>
+      <c r="N45" s="40"/>
+      <c r="O45" s="40"/>
+      <c r="P45" s="40"/>
+      <c r="Q45" s="40"/>
+      <c r="R45" s="10"/>
+      <c r="S45" s="29"/>
     </row>
     <row r="46" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A46" s="34">
+      <c r="A46" s="35">
         <v>30240010</v>
       </c>
-      <c r="B46" s="42">
+      <c r="B46" s="43">
         <v>102400</v>
       </c>
-      <c r="C46" s="24" t="s">
+      <c r="C46" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="D46" s="43">
+      <c r="D46" s="44">
         <v>32441</v>
       </c>
-      <c r="E46" s="43" t="s">
+      <c r="E46" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="F46" s="34" t="s">
+      <c r="F46" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="G46" s="34"/>
-      <c r="H46" s="34"/>
-      <c r="I46" s="34" t="s">
+      <c r="G46" s="35"/>
+      <c r="H46" s="35"/>
+      <c r="I46" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="J46" s="34"/>
-      <c r="K46" s="44"/>
-      <c r="L46" s="34" t="s">
+      <c r="J46" s="35"/>
+      <c r="K46" s="45"/>
+      <c r="L46" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="M46" s="34" t="s">
+      <c r="M46" s="35" t="s">
         <v>69</v>
       </c>
-      <c r="N46" s="34"/>
-      <c r="O46" s="34"/>
-      <c r="P46" s="34"/>
-      <c r="Q46" s="45" t="s">
+      <c r="N46" s="35"/>
+      <c r="O46" s="35"/>
+      <c r="P46" s="35"/>
+      <c r="Q46" s="46" t="s">
         <v>70</v>
       </c>
-      <c r="R46" s="46" t="s">
+      <c r="R46" s="47" t="s">
         <v>71</v>
       </c>
-      <c r="S46" s="12" t="s">
+      <c r="S46" s="13" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="47" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A47" s="39">
+      <c r="A47" s="40">
         <v>30240011</v>
       </c>
-      <c r="B47" s="40">
+      <c r="B47" s="41">
         <v>102400</v>
       </c>
-      <c r="C47" s="24" t="s">
+      <c r="C47" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="D47" s="43">
+      <c r="D47" s="44">
         <v>32442</v>
       </c>
-      <c r="E47" s="43" t="s">
+      <c r="E47" s="44" t="s">
         <v>73</v>
       </c>
-      <c r="F47" s="39" t="s">
+      <c r="F47" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="G47" s="39"/>
-      <c r="H47" s="39"/>
-      <c r="I47" s="39" t="s">
+      <c r="G47" s="40"/>
+      <c r="H47" s="40"/>
+      <c r="I47" s="40" t="s">
         <v>74</v>
       </c>
-      <c r="J47" s="39"/>
-      <c r="K47" s="41"/>
-      <c r="L47" s="39" t="s">
+      <c r="J47" s="40"/>
+      <c r="K47" s="42"/>
+      <c r="L47" s="40" t="s">
         <v>35</v>
       </c>
-      <c r="M47" s="39" t="s">
+      <c r="M47" s="40" t="s">
         <v>56</v>
       </c>
-      <c r="N47" s="39"/>
-      <c r="O47" s="39"/>
-      <c r="P47" s="39"/>
-      <c r="Q47" s="39"/>
-      <c r="R47" s="9"/>
-      <c r="S47" s="28"/>
+      <c r="N47" s="40"/>
+      <c r="O47" s="40"/>
+      <c r="P47" s="40"/>
+      <c r="Q47" s="40"/>
+      <c r="R47" s="10"/>
+      <c r="S47" s="29"/>
     </row>
     <row r="48" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A48" s="39">
+      <c r="A48" s="40">
         <v>30240012</v>
       </c>
-      <c r="B48" s="40">
+      <c r="B48" s="41">
         <v>102400</v>
       </c>
-      <c r="C48" s="24" t="s">
+      <c r="C48" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="D48" s="43">
+      <c r="D48" s="44">
         <v>32443</v>
       </c>
-      <c r="E48" s="43" t="s">
+      <c r="E48" s="44" t="s">
         <v>75</v>
       </c>
-      <c r="F48" s="39" t="s">
+      <c r="F48" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="G48" s="39">
+      <c r="G48" s="40">
         <v>2024001</v>
       </c>
-      <c r="H48" s="39" t="s">
+      <c r="H48" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="I48" s="39" t="s">
+      <c r="I48" s="40" t="s">
         <v>65</v>
       </c>
-      <c r="J48" s="39"/>
-      <c r="K48" s="41" t="s">
+      <c r="J48" s="40"/>
+      <c r="K48" s="42" t="s">
         <v>93</v>
       </c>
-      <c r="L48" s="39"/>
-      <c r="M48" s="39"/>
-      <c r="N48" s="39"/>
-      <c r="O48" s="39"/>
-      <c r="P48" s="39"/>
-      <c r="Q48" s="39"/>
-      <c r="R48" s="9"/>
-      <c r="S48" s="28"/>
+      <c r="L48" s="40"/>
+      <c r="M48" s="40"/>
+      <c r="N48" s="40"/>
+      <c r="O48" s="40"/>
+      <c r="P48" s="40"/>
+      <c r="Q48" s="40"/>
+      <c r="R48" s="10"/>
+      <c r="S48" s="29"/>
     </row>
     <row r="49" s="3" customFormat="1" ht="16.5" spans="1:22">
-      <c r="A49" s="39">
+      <c r="A49" s="40">
         <v>30170001</v>
       </c>
-      <c r="B49" s="40">
+      <c r="B49" s="41">
         <v>101700</v>
       </c>
-      <c r="C49" s="24" t="s">
+      <c r="C49" s="25" t="s">
         <v>94</v>
       </c>
-      <c r="D49" s="43">
+      <c r="D49" s="44">
         <v>301701</v>
       </c>
-      <c r="E49" s="43" t="s">
+      <c r="E49" s="44" t="s">
         <v>95</v>
       </c>
-      <c r="F49" s="39" t="s">
+      <c r="F49" s="40" t="s">
         <v>78</v>
       </c>
-      <c r="G49" s="39">
+      <c r="G49" s="40">
         <v>2017001</v>
       </c>
-      <c r="H49" s="39" t="s">
+      <c r="H49" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="I49" s="39" t="s">
+      <c r="I49" s="40" t="s">
         <v>79</v>
       </c>
-      <c r="J49" s="39"/>
-      <c r="K49" s="41" t="s">
+      <c r="J49" s="40"/>
+      <c r="K49" s="42" t="s">
         <v>96</v>
       </c>
-      <c r="L49" s="39"/>
-      <c r="M49" s="39"/>
-      <c r="N49" s="39"/>
-      <c r="O49" s="39"/>
-      <c r="P49" s="39"/>
-      <c r="Q49" s="39"/>
-      <c r="R49" s="9"/>
-      <c r="S49" s="28"/>
+      <c r="L49" s="40"/>
+      <c r="M49" s="40"/>
+      <c r="N49" s="40"/>
+      <c r="O49" s="40"/>
+      <c r="P49" s="40"/>
+      <c r="Q49" s="40"/>
+      <c r="R49" s="10"/>
+      <c r="S49" s="29"/>
     </row>
     <row r="50" s="3" customFormat="1" ht="16.5" spans="1:22">
-      <c r="A50" s="39">
+      <c r="A50" s="40">
         <v>30170002</v>
       </c>
-      <c r="B50" s="40">
+      <c r="B50" s="41">
         <v>101700</v>
       </c>
-      <c r="C50" s="24" t="s">
+      <c r="C50" s="25" t="s">
         <v>94</v>
       </c>
-      <c r="D50" s="43">
+      <c r="D50" s="44">
         <v>301702</v>
       </c>
-      <c r="E50" s="43" t="s">
+      <c r="E50" s="44" t="s">
         <v>97</v>
       </c>
-      <c r="F50" s="39" t="s">
+      <c r="F50" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="G50" s="39">
+      <c r="G50" s="40">
         <v>2017001</v>
       </c>
-      <c r="H50" s="39" t="s">
+      <c r="H50" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="I50" s="39" t="s">
+      <c r="I50" s="40" t="s">
         <v>79</v>
       </c>
-      <c r="J50" s="39"/>
-      <c r="K50" s="41" t="s">
+      <c r="J50" s="40"/>
+      <c r="K50" s="42" t="s">
         <v>96</v>
       </c>
-      <c r="L50" s="39"/>
-      <c r="M50" s="39"/>
-      <c r="N50" s="39"/>
-      <c r="O50" s="39"/>
-      <c r="P50" s="39"/>
-      <c r="Q50" s="39"/>
-      <c r="R50" s="9"/>
-      <c r="S50" s="28"/>
+      <c r="L50" s="40"/>
+      <c r="M50" s="40"/>
+      <c r="N50" s="40"/>
+      <c r="O50" s="40"/>
+      <c r="P50" s="40"/>
+      <c r="Q50" s="40"/>
+      <c r="R50" s="10"/>
+      <c r="S50" s="29"/>
     </row>
     <row r="51" s="3" customFormat="1" ht="16.5" spans="1:22">
-      <c r="A51" s="39">
+      <c r="A51" s="40">
         <v>30220001</v>
       </c>
-      <c r="B51" s="40">
+      <c r="B51" s="41">
         <v>102200</v>
       </c>
-      <c r="C51" s="24" t="s">
+      <c r="C51" s="25" t="s">
         <v>98</v>
       </c>
-      <c r="D51" s="43">
+      <c r="D51" s="44">
         <v>302201</v>
       </c>
-      <c r="E51" s="43" t="s">
+      <c r="E51" s="44" t="s">
         <v>99</v>
       </c>
-      <c r="F51" s="39" t="s">
+      <c r="F51" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="G51" s="39">
+      <c r="G51" s="40">
         <v>2022001</v>
       </c>
-      <c r="H51" s="39" t="s">
+      <c r="H51" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="I51" s="39"/>
-      <c r="J51" s="39"/>
-      <c r="K51" s="41" t="s">
+      <c r="I51" s="40"/>
+      <c r="J51" s="40"/>
+      <c r="K51" s="42" t="s">
         <v>100</v>
       </c>
-      <c r="L51" s="39" t="s">
+      <c r="L51" s="40" t="s">
         <v>101</v>
       </c>
-      <c r="M51" s="39"/>
-      <c r="N51" s="39"/>
-      <c r="O51" s="39"/>
-      <c r="P51" s="39"/>
-      <c r="Q51" s="39"/>
-      <c r="R51" s="9"/>
-      <c r="S51" s="28"/>
+      <c r="M51" s="40"/>
+      <c r="N51" s="40"/>
+      <c r="O51" s="40"/>
+      <c r="P51" s="40"/>
+      <c r="Q51" s="40"/>
+      <c r="R51" s="10"/>
+      <c r="S51" s="29"/>
     </row>
     <row r="52" s="3" customFormat="1" ht="16.5" spans="1:22">
-      <c r="A52" s="39">
+      <c r="A52" s="40">
         <v>30220002</v>
       </c>
-      <c r="B52" s="40">
+      <c r="B52" s="41">
         <v>102200</v>
       </c>
-      <c r="C52" s="24" t="s">
+      <c r="C52" s="25" t="s">
         <v>98</v>
       </c>
-      <c r="D52" s="43">
+      <c r="D52" s="44">
         <v>302202</v>
       </c>
-      <c r="E52" s="43" t="s">
+      <c r="E52" s="44" t="s">
         <v>102</v>
       </c>
-      <c r="F52" s="39" t="s">
+      <c r="F52" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="G52" s="39">
+      <c r="G52" s="40">
         <v>2022001</v>
       </c>
-      <c r="H52" s="39" t="s">
+      <c r="H52" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="I52" s="39"/>
-      <c r="J52" s="39"/>
-      <c r="K52" s="41" t="s">
+      <c r="I52" s="40"/>
+      <c r="J52" s="40"/>
+      <c r="K52" s="42" t="s">
         <v>103</v>
       </c>
-      <c r="L52" s="39" t="s">
+      <c r="L52" s="40" t="s">
         <v>101</v>
       </c>
-      <c r="M52" s="39"/>
-      <c r="N52" s="39"/>
-      <c r="O52" s="39"/>
-      <c r="P52" s="39"/>
-      <c r="Q52" s="39"/>
-      <c r="R52" s="9"/>
-      <c r="S52" s="28"/>
-    </row>
-    <row r="53" ht="16.5" spans="1:22">
-      <c r="S53"/>
-      <c r="U53" s="1"/>
-      <c r="V53" s="1"/>
-    </row>
-    <row r="54" ht="16.5" spans="1:22">
-      <c r="S54"/>
-      <c r="U54" s="1"/>
-      <c r="V54" s="1"/>
+      <c r="M52" s="40"/>
+      <c r="N52" s="40"/>
+      <c r="O52" s="40"/>
+      <c r="P52" s="40"/>
+      <c r="Q52" s="40"/>
+      <c r="R52" s="10"/>
+      <c r="S52" s="29"/>
+    </row>
+    <row r="53" s="7" customFormat="1" ht="16.5" spans="1:22">
+      <c r="A53" s="55">
+        <v>30210001</v>
+      </c>
+      <c r="B53" s="56">
+        <v>102100</v>
+      </c>
+      <c r="C53" s="56" t="s">
+        <v>104</v>
+      </c>
+      <c r="D53" s="55">
+        <v>302101</v>
+      </c>
+      <c r="E53" s="55" t="s">
+        <v>105</v>
+      </c>
+      <c r="F53" s="55" t="s">
+        <v>106</v>
+      </c>
+      <c r="G53" s="55">
+        <v>2021001</v>
+      </c>
+      <c r="H53" s="55" t="s">
+        <v>59</v>
+      </c>
+      <c r="I53" s="55" t="s">
+        <v>79</v>
+      </c>
+      <c r="J53" s="55"/>
+      <c r="K53" s="57">
+        <v>10210031</v>
+      </c>
+      <c r="L53" s="55"/>
+      <c r="M53" s="55"/>
+      <c r="N53" s="55"/>
+      <c r="O53" s="55"/>
+      <c r="P53" s="55"/>
+      <c r="Q53" s="55"/>
+      <c r="R53" s="55"/>
+      <c r="S53" s="58"/>
+    </row>
+    <row r="54" s="7" customFormat="1" ht="16.5" spans="1:22">
+      <c r="A54" s="55">
+        <v>30210002</v>
+      </c>
+      <c r="B54" s="56">
+        <v>102100</v>
+      </c>
+      <c r="C54" s="56" t="s">
+        <v>104</v>
+      </c>
+      <c r="D54" s="55">
+        <v>302102</v>
+      </c>
+      <c r="E54" s="55" t="s">
+        <v>107</v>
+      </c>
+      <c r="F54" s="55" t="s">
+        <v>33</v>
+      </c>
+      <c r="G54" s="55"/>
+      <c r="H54" s="55"/>
+      <c r="I54" s="55" t="s">
+        <v>108</v>
+      </c>
+      <c r="J54" s="55"/>
+      <c r="K54" s="57">
+        <v>10210041</v>
+      </c>
+      <c r="L54" s="55"/>
+      <c r="M54" s="55" t="s">
+        <v>36</v>
+      </c>
+      <c r="N54" s="55" t="s">
+        <v>109</v>
+      </c>
+      <c r="O54" s="55"/>
+      <c r="P54" s="55"/>
+      <c r="Q54" s="55" t="s">
+        <v>110</v>
+      </c>
+      <c r="R54" s="55"/>
+      <c r="S54" s="58"/>
     </row>
     <row r="55" ht="16.5" spans="1:22">
       <c r="S55"/>
@@ -4159,10 +4269,10 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="B1" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -4170,7 +4280,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -4178,7 +4288,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:8">
@@ -4186,16 +4296,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:8">
@@ -4203,16 +4313,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:8">
@@ -4220,16 +4330,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:8">
@@ -4237,16 +4347,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="F7" s="1">
         <v>2</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:8">
@@ -4254,16 +4364,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="F8" s="1">
         <v>3</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:8">
@@ -4271,16 +4381,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="F9" s="1">
         <v>4</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:8">
@@ -4288,16 +4398,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="F10" s="1">
         <v>5</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:8">
@@ -4305,16 +4415,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="F11" s="1">
         <v>6</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:8">
@@ -4322,16 +4432,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="F12" s="1">
         <v>7</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:8">
@@ -4339,16 +4449,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="F13" s="1">
         <v>8</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:8">
@@ -4356,16 +4466,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="F14" s="1">
         <v>9</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:8">
@@ -4373,16 +4483,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="F15" s="1">
         <v>10</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:8">
@@ -4390,16 +4500,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="F16" s="1">
         <v>11</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:8">
@@ -4407,16 +4517,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="F17" s="1">
         <v>12</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:8">
@@ -4424,16 +4534,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="F18" s="1">
         <v>13</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:8">
@@ -4441,16 +4551,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="F19" s="1">
         <v>14</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:8">
@@ -4458,16 +4568,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="F20" s="1">
         <v>15</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:8">
@@ -4475,16 +4585,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="F21" s="1">
         <v>16</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:8">
@@ -4492,16 +4602,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="F22" s="1">
         <v>17</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:8">
@@ -4509,16 +4619,16 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="F23" s="1">
         <v>18</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:8">
@@ -4526,16 +4636,16 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="F24" s="1">
         <v>19</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -4543,7 +4653,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -4551,7 +4661,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -4559,7 +4669,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -4567,7 +4677,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -4575,7 +4685,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -4583,7 +4693,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -4591,7 +4701,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -4599,7 +4709,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -4607,7 +4717,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -4615,7 +4725,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -4623,7 +4733,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -4631,7 +4741,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -4639,7 +4749,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -4647,7 +4757,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -4655,7 +4765,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -4663,7 +4773,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -4671,7 +4781,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -4679,7 +4789,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -4687,7 +4797,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -4695,7 +4805,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -4703,7 +4813,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -4711,7 +4821,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -4719,7 +4829,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialAuxiliary.xlsx
+++ b/slots/resources/sample/SpecialAuxiliary.xlsx
@@ -268,7 +268,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="203">
   <si>
     <t>小游戏模式ID</t>
   </si>
@@ -570,7 +570,10 @@
     <t>冰冻玩法</t>
   </si>
   <si>
-    <t>10220011|10220099|10220012</t>
+    <t>8_30|10_30|12_20|15_20</t>
+  </si>
+  <si>
+    <t>10220011|10220012</t>
   </si>
   <si>
     <t>改百搭图案出现概率</t>
@@ -579,7 +582,7 @@
     <t>火焰玩法</t>
   </si>
   <si>
-    <t>10220021|10220099|10220012</t>
+    <t>10220021|10220012</t>
   </si>
   <si>
     <t>杰克船长</t>
@@ -601,6 +604,12 @@
   </si>
   <si>
     <t>20_200_1|40_500_2|60_1000_3|80_1500_3|100_1500_3|120_1500_3|140_1500_2|160_1500_2|180_1000_2|200_1000_2|220_500_2|240_200_1|</t>
+  </si>
+  <si>
+    <t>篮球巨星</t>
+  </si>
+  <si>
+    <t>7_1</t>
   </si>
   <si>
     <t>typeID</t>
@@ -1046,12 +1055,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
@@ -1059,13 +1062,12 @@
     </font>
     <font>
       <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1079,6 +1081,13 @@
     <font>
       <b/>
       <sz val="18"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -4045,7 +4054,7 @@
         <v>99</v>
       </c>
       <c r="F51" s="40" t="s">
-        <v>52</v>
+        <v>100</v>
       </c>
       <c r="G51" s="40">
         <v>2022001</v>
@@ -4056,10 +4065,10 @@
       <c r="I51" s="40"/>
       <c r="J51" s="40"/>
       <c r="K51" s="42" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L51" s="40" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M51" s="40"/>
       <c r="N51" s="40"/>
@@ -4083,10 +4092,10 @@
         <v>302202</v>
       </c>
       <c r="E52" s="44" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F52" s="40" t="s">
-        <v>52</v>
+        <v>100</v>
       </c>
       <c r="G52" s="40">
         <v>2022001</v>
@@ -4097,10 +4106,10 @@
       <c r="I52" s="40"/>
       <c r="J52" s="40"/>
       <c r="K52" s="42" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L52" s="40" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M52" s="40"/>
       <c r="N52" s="40"/>
@@ -4118,16 +4127,16 @@
         <v>102100</v>
       </c>
       <c r="C53" s="56" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D53" s="55">
         <v>302101</v>
       </c>
       <c r="E53" s="55" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F53" s="55" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G53" s="55">
         <v>2021001</v>
@@ -4159,13 +4168,13 @@
         <v>102100</v>
       </c>
       <c r="C54" s="56" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D54" s="55">
         <v>302102</v>
       </c>
       <c r="E54" s="55" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F54" s="55" t="s">
         <v>33</v>
@@ -4173,7 +4182,7 @@
       <c r="G54" s="55"/>
       <c r="H54" s="55"/>
       <c r="I54" s="55" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J54" s="55"/>
       <c r="K54" s="57">
@@ -4184,17 +4193,44 @@
         <v>36</v>
       </c>
       <c r="N54" s="55" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O54" s="55"/>
       <c r="P54" s="55"/>
       <c r="Q54" s="55" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="R54" s="55"/>
       <c r="S54" s="58"/>
     </row>
     <row r="55" ht="16.5" spans="1:22">
+      <c r="A55">
+        <v>30180001</v>
+      </c>
+      <c r="B55">
+        <v>101800</v>
+      </c>
+      <c r="C55" t="s">
+        <v>112</v>
+      </c>
+      <c r="D55">
+        <v>301801</v>
+      </c>
+      <c r="E55" t="s">
+        <v>79</v>
+      </c>
+      <c r="F55" t="s">
+        <v>113</v>
+      </c>
+      <c r="G55">
+        <v>2018001</v>
+      </c>
+      <c r="H55" s="55" t="s">
+        <v>59</v>
+      </c>
+      <c r="I55" t="s">
+        <v>79</v>
+      </c>
       <c r="S55"/>
       <c r="U55" s="1"/>
       <c r="V55" s="1"/>
@@ -4269,10 +4305,10 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B1" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -4280,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -4288,7 +4324,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:8">
@@ -4296,16 +4332,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
+        <v>118</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>112</v>
-      </c>
       <c r="H4" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:8">
@@ -4313,16 +4349,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:8">
@@ -4330,16 +4366,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:8">
@@ -4347,16 +4383,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F7" s="1">
         <v>2</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:8">
@@ -4364,16 +4400,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F8" s="1">
         <v>3</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:8">
@@ -4381,16 +4417,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F9" s="1">
         <v>4</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:8">
@@ -4398,16 +4434,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F10" s="1">
         <v>5</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:8">
@@ -4415,16 +4451,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F11" s="1">
         <v>6</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:8">
@@ -4432,16 +4468,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="F12" s="1">
         <v>7</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:8">
@@ -4449,16 +4485,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F13" s="1">
         <v>8</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:8">
@@ -4466,16 +4502,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F14" s="1">
         <v>9</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:8">
@@ -4483,16 +4519,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="F15" s="1">
         <v>10</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:8">
@@ -4500,16 +4536,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="F16" s="1">
         <v>11</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:8">
@@ -4517,16 +4553,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="F17" s="1">
         <v>12</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:8">
@@ -4534,16 +4570,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="F18" s="1">
         <v>13</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:8">
@@ -4551,16 +4587,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="F19" s="1">
         <v>14</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:8">
@@ -4568,16 +4604,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F20" s="1">
         <v>15</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:8">
@@ -4585,16 +4621,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="F21" s="1">
         <v>16</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:8">
@@ -4602,16 +4638,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="F22" s="1">
         <v>17</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:8">
@@ -4619,16 +4655,16 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="F23" s="1">
         <v>18</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:8">
@@ -4636,16 +4672,16 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="F24" s="1">
         <v>19</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -4653,7 +4689,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -4661,7 +4697,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -4669,7 +4705,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -4677,7 +4713,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -4685,7 +4721,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -4693,7 +4729,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -4701,7 +4737,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -4709,7 +4745,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -4717,7 +4753,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -4725,7 +4761,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -4733,7 +4769,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -4741,7 +4777,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -4749,7 +4785,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -4757,7 +4793,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -4765,7 +4801,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -4773,7 +4809,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -4781,7 +4817,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -4789,7 +4825,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -4797,7 +4833,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -4805,7 +4841,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -4813,7 +4849,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -4821,7 +4857,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -4829,7 +4865,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialAuxiliary.xlsx
+++ b/slots/resources/sample/SpecialAuxiliary.xlsx
@@ -1055,6 +1055,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
@@ -1067,7 +1072,9 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1079,27 +1086,20 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="18"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="43">
+  <fills count="44">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1127,6 +1127,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1483,7 +1489,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1507,16 +1513,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1525,92 +1531,92 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1621,12 +1627,13 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1647,7 +1654,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1656,19 +1663,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="176" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
@@ -1676,11 +1671,15 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="176" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1688,14 +1687,22 @@
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1736,6 +1743,14 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="52">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2079,7 +2094,7 @@
     <col min="8" max="8" width="16.25" customWidth="1"/>
     <col min="9" max="9" width="29.375" customWidth="1"/>
     <col min="10" max="10" width="42.5" customWidth="1"/>
-    <col min="11" max="11" width="41.25" style="8" customWidth="1"/>
+    <col min="11" max="11" width="41.25" style="9" customWidth="1"/>
     <col min="12" max="12" width="11.75" style="3" customWidth="1"/>
     <col min="13" max="13" width="34.4083333333333" style="3" customWidth="1"/>
     <col min="14" max="14" width="7.93333333333333" style="3" customWidth="1"/>
@@ -2087,7 +2102,7 @@
     <col min="16" max="16" width="8.96666666666667" customWidth="1"/>
     <col min="17" max="17" width="93.375" customWidth="1"/>
     <col min="18" max="18" width="10.625" customWidth="1"/>
-    <col min="19" max="19" width="23.75" style="9" customWidth="1"/>
+    <col min="19" max="19" width="23.75" style="10" customWidth="1"/>
     <col min="20" max="20" width="60.875" customWidth="1"/>
     <col min="21" max="22" width="11.5"/>
   </cols>
@@ -2096,671 +2111,671 @@
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10" t="s">
+      <c r="C1" s="11"/>
+      <c r="D1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10" t="s">
+      <c r="E1" s="11"/>
+      <c r="F1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10" t="s">
+      <c r="H1" s="11"/>
+      <c r="I1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="J1" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="K1" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10" t="s">
+      <c r="L1" s="11"/>
+      <c r="M1" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="10"/>
-      <c r="O1" s="13" t="s">
+      <c r="N1" s="11"/>
+      <c r="O1" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="13" t="s">
+      <c r="P1" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="Q1" s="13" t="s">
+      <c r="Q1" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="R1" s="14" t="s">
+      <c r="R1" s="15" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="2" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10" t="s">
+      <c r="C2" s="11"/>
+      <c r="D2" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="10"/>
-      <c r="F2" s="13" t="s">
+      <c r="E2" s="11"/>
+      <c r="F2" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="16" t="s">
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="17" t="s">
+      <c r="K2" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="L2" s="13"/>
-      <c r="M2" s="16" t="s">
+      <c r="L2" s="14"/>
+      <c r="M2" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="N2" s="10"/>
-      <c r="O2" s="13" t="s">
+      <c r="N2" s="11"/>
+      <c r="O2" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="P2" s="13" t="s">
+      <c r="P2" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="Q2" s="16" t="s">
+      <c r="Q2" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="R2" s="14" t="s">
+      <c r="R2" s="15" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="3" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18" t="s">
+      <c r="C3" s="19"/>
+      <c r="D3" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18" t="s">
+      <c r="E3" s="19"/>
+      <c r="F3" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="G3" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="20" t="s">
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="K3" s="21" t="s">
+      <c r="K3" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="L3" s="18"/>
-      <c r="M3" s="18" t="s">
+      <c r="L3" s="19"/>
+      <c r="M3" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="18"/>
-      <c r="O3" s="13" t="s">
+      <c r="N3" s="19"/>
+      <c r="O3" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="P3" s="13" t="s">
+      <c r="P3" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="Q3" s="13" t="s">
+      <c r="Q3" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="R3" s="22" t="s">
+      <c r="R3" s="23" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="4" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="23"/>
-      <c r="K4" s="12"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
-      <c r="N4" s="10"/>
-      <c r="O4" s="10"/>
-      <c r="P4" s="10"/>
-      <c r="Q4" s="10"/>
-      <c r="R4" s="10"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="24"/>
+      <c r="K4" s="13"/>
+      <c r="L4" s="11"/>
+      <c r="M4" s="11"/>
+      <c r="N4" s="11"/>
+      <c r="O4" s="11"/>
+      <c r="P4" s="11"/>
+      <c r="Q4" s="11"/>
+      <c r="R4" s="11"/>
     </row>
     <row r="5" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A5" s="24">
+      <c r="A5" s="25">
         <v>30010001</v>
       </c>
-      <c r="B5" s="25">
+      <c r="B5" s="26">
         <v>100100</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="C5" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="25">
         <v>31001</v>
       </c>
-      <c r="E5" s="24" t="s">
+      <c r="E5" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="F5" s="24" t="s">
+      <c r="F5" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="G5" s="24"/>
-      <c r="H5" s="24"/>
-      <c r="I5" s="24" t="s">
+      <c r="G5" s="25"/>
+      <c r="H5" s="25"/>
+      <c r="I5" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="J5" s="24"/>
-      <c r="K5" s="26"/>
-      <c r="L5" s="10" t="s">
+      <c r="J5" s="25"/>
+      <c r="K5" s="27"/>
+      <c r="L5" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="M5" s="24" t="s">
+      <c r="M5" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="N5" s="24" t="s">
+      <c r="N5" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="O5" s="24"/>
-      <c r="P5" s="24"/>
-      <c r="Q5" s="27" t="s">
+      <c r="O5" s="25"/>
+      <c r="P5" s="25"/>
+      <c r="Q5" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="R5" s="28" t="s">
+      <c r="R5" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="S5" s="29" t="s">
+      <c r="S5" s="30" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="6" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A6" s="24">
+      <c r="A6" s="25">
         <v>30010002</v>
       </c>
-      <c r="B6" s="25">
+      <c r="B6" s="26">
         <v>100100</v>
       </c>
-      <c r="C6" s="25" t="s">
+      <c r="C6" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="25">
         <v>31002</v>
       </c>
-      <c r="E6" s="24" t="s">
+      <c r="E6" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="F6" s="24" t="s">
+      <c r="F6" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="G6" s="24"/>
-      <c r="H6" s="24"/>
-      <c r="I6" s="24" t="s">
+      <c r="G6" s="25"/>
+      <c r="H6" s="25"/>
+      <c r="I6" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="J6" s="24"/>
-      <c r="K6" s="26"/>
-      <c r="L6" s="10" t="s">
+      <c r="J6" s="25"/>
+      <c r="K6" s="27"/>
+      <c r="L6" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="M6" s="24" t="s">
+      <c r="M6" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="N6" s="24" t="s">
+      <c r="N6" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="O6" s="24"/>
-      <c r="P6" s="24"/>
-      <c r="Q6" s="27" t="s">
+      <c r="O6" s="25"/>
+      <c r="P6" s="25"/>
+      <c r="Q6" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="R6" s="28" t="s">
+      <c r="R6" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="S6" s="29"/>
+      <c r="S6" s="30"/>
     </row>
     <row r="7" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A7" s="24">
+      <c r="A7" s="25">
         <v>30010003</v>
       </c>
-      <c r="B7" s="25">
+      <c r="B7" s="26">
         <v>100100</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="C7" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="25">
         <v>31003</v>
       </c>
-      <c r="E7" s="24" t="s">
+      <c r="E7" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="24" t="s">
+      <c r="F7" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="G7" s="24"/>
-      <c r="H7" s="24"/>
-      <c r="I7" s="24" t="s">
+      <c r="G7" s="25"/>
+      <c r="H7" s="25"/>
+      <c r="I7" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="J7" s="24"/>
-      <c r="K7" s="26"/>
-      <c r="L7" s="10" t="s">
+      <c r="J7" s="25"/>
+      <c r="K7" s="27"/>
+      <c r="L7" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="M7" s="24" t="s">
+      <c r="M7" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="N7" s="24" t="s">
+      <c r="N7" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="O7" s="24"/>
-      <c r="P7" s="24"/>
-      <c r="Q7" s="27" t="s">
+      <c r="O7" s="25"/>
+      <c r="P7" s="25"/>
+      <c r="Q7" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="R7" s="28" t="s">
+      <c r="R7" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="S7" s="29"/>
+      <c r="S7" s="30"/>
     </row>
     <row r="8" s="3" customFormat="1" ht="15" customHeight="1" spans="1:19">
-      <c r="A8" s="24">
+      <c r="A8" s="25">
         <v>30010004</v>
       </c>
-      <c r="B8" s="25">
+      <c r="B8" s="26">
         <v>100100</v>
       </c>
-      <c r="C8" s="25" t="s">
+      <c r="C8" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="24">
+      <c r="D8" s="25">
         <v>31004</v>
       </c>
-      <c r="E8" s="24" t="s">
+      <c r="E8" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="24" t="s">
+      <c r="F8" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="G8" s="24"/>
-      <c r="H8" s="24"/>
-      <c r="I8" s="24" t="s">
+      <c r="G8" s="25"/>
+      <c r="H8" s="25"/>
+      <c r="I8" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="J8" s="24"/>
-      <c r="K8" s="26"/>
-      <c r="L8" s="10" t="s">
+      <c r="J8" s="25"/>
+      <c r="K8" s="27"/>
+      <c r="L8" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="M8" s="24" t="s">
+      <c r="M8" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="N8" s="24" t="s">
+      <c r="N8" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="O8" s="24"/>
-      <c r="P8" s="24"/>
-      <c r="Q8" s="27" t="s">
+      <c r="O8" s="25"/>
+      <c r="P8" s="25"/>
+      <c r="Q8" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="R8" s="28" t="s">
+      <c r="R8" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="S8" s="29"/>
+      <c r="S8" s="30"/>
     </row>
     <row r="9" s="3" customFormat="1" ht="15" customHeight="1" spans="1:19">
-      <c r="A9" s="10">
+      <c r="A9" s="11">
         <v>30010005</v>
       </c>
-      <c r="B9" s="22">
+      <c r="B9" s="23">
         <v>100100</v>
       </c>
-      <c r="C9" s="25" t="s">
+      <c r="C9" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="11">
         <v>31101</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10" t="s">
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="J9" s="10"/>
-      <c r="K9" s="12"/>
-      <c r="L9" s="10" t="s">
+      <c r="J9" s="11"/>
+      <c r="K9" s="13"/>
+      <c r="L9" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="M9" s="10" t="s">
+      <c r="M9" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="N9" s="10"/>
-      <c r="O9" s="10" t="s">
+      <c r="N9" s="11"/>
+      <c r="O9" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="P9" s="10"/>
-      <c r="Q9" s="13"/>
-      <c r="R9" s="13"/>
-      <c r="S9" s="29"/>
+      <c r="P9" s="11"/>
+      <c r="Q9" s="14"/>
+      <c r="R9" s="14"/>
+      <c r="S9" s="30"/>
     </row>
     <row r="10" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A10" s="30">
+      <c r="A10" s="31">
         <v>30010006</v>
       </c>
-      <c r="B10" s="31">
+      <c r="B10" s="32">
         <v>100100</v>
       </c>
-      <c r="C10" s="25" t="s">
+      <c r="C10" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="30">
+      <c r="D10" s="31">
         <v>31102</v>
       </c>
-      <c r="E10" s="30" t="s">
+      <c r="E10" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="F10" s="30" t="s">
+      <c r="F10" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="G10" s="30"/>
-      <c r="H10" s="30"/>
-      <c r="I10" s="30" t="s">
+      <c r="G10" s="31"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="J10" s="30"/>
-      <c r="K10" s="32"/>
-      <c r="L10" s="30" t="s">
+      <c r="J10" s="31"/>
+      <c r="K10" s="33"/>
+      <c r="L10" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="M10" s="30" t="s">
+      <c r="M10" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="N10" s="30" t="s">
+      <c r="N10" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="O10" s="30" t="s">
+      <c r="O10" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="P10" s="30"/>
-      <c r="Q10" s="30"/>
-      <c r="R10" s="10"/>
-      <c r="S10" s="29"/>
+      <c r="P10" s="31"/>
+      <c r="Q10" s="31"/>
+      <c r="R10" s="11"/>
+      <c r="S10" s="30"/>
     </row>
     <row r="11" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A11" s="33">
+      <c r="A11" s="34">
         <v>30010007</v>
       </c>
-      <c r="B11" s="34">
+      <c r="B11" s="35">
         <v>100100</v>
       </c>
-      <c r="C11" s="25" t="s">
+      <c r="C11" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="35">
+      <c r="D11" s="36">
         <v>31201</v>
       </c>
-      <c r="E11" s="35" t="s">
+      <c r="E11" s="36" t="s">
         <v>57</v>
       </c>
-      <c r="F11" s="33" t="s">
+      <c r="F11" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="G11" s="33">
+      <c r="G11" s="34">
         <v>2001001</v>
       </c>
-      <c r="H11" s="33" t="s">
+      <c r="H11" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="I11" s="33" t="s">
+      <c r="I11" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="J11" s="33"/>
-      <c r="K11" s="36">
+      <c r="J11" s="34"/>
+      <c r="K11" s="37">
         <v>10010091</v>
       </c>
-      <c r="L11" s="33"/>
-      <c r="M11" s="33"/>
-      <c r="N11" s="33"/>
-      <c r="O11" s="33"/>
-      <c r="P11" s="33"/>
-      <c r="Q11" s="33"/>
-      <c r="R11" s="10"/>
-      <c r="S11" s="29"/>
+      <c r="L11" s="34"/>
+      <c r="M11" s="34"/>
+      <c r="N11" s="34"/>
+      <c r="O11" s="34"/>
+      <c r="P11" s="34"/>
+      <c r="Q11" s="34"/>
+      <c r="R11" s="11"/>
+      <c r="S11" s="30"/>
     </row>
     <row r="12" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A12" s="37">
+      <c r="A12" s="38">
         <v>30010008</v>
       </c>
-      <c r="B12" s="38">
+      <c r="B12" s="39">
         <v>100100</v>
       </c>
-      <c r="C12" s="25" t="s">
+      <c r="C12" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="D12" s="35">
+      <c r="D12" s="36">
         <v>31202</v>
       </c>
-      <c r="E12" s="35" t="s">
+      <c r="E12" s="36" t="s">
         <v>61</v>
       </c>
-      <c r="F12" s="37" t="s">
+      <c r="F12" s="38" t="s">
         <v>52</v>
       </c>
-      <c r="G12" s="37">
+      <c r="G12" s="38">
         <v>2001001</v>
       </c>
-      <c r="H12" s="37" t="s">
+      <c r="H12" s="38" t="s">
         <v>59</v>
       </c>
-      <c r="I12" s="37" t="s">
+      <c r="I12" s="38" t="s">
         <v>62</v>
       </c>
-      <c r="J12" s="37"/>
-      <c r="K12" s="39" t="s">
+      <c r="J12" s="38"/>
+      <c r="K12" s="40" t="s">
         <v>63</v>
       </c>
-      <c r="L12" s="37"/>
-      <c r="M12" s="37"/>
-      <c r="N12" s="37"/>
-      <c r="O12" s="37"/>
-      <c r="P12" s="37"/>
-      <c r="Q12" s="37"/>
-      <c r="R12" s="10"/>
-      <c r="S12" s="29"/>
+      <c r="L12" s="38"/>
+      <c r="M12" s="38"/>
+      <c r="N12" s="38"/>
+      <c r="O12" s="38"/>
+      <c r="P12" s="38"/>
+      <c r="Q12" s="38"/>
+      <c r="R12" s="11"/>
+      <c r="S12" s="30"/>
     </row>
     <row r="13" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A13" s="40">
+      <c r="A13" s="41">
         <v>30010009</v>
       </c>
-      <c r="B13" s="41">
+      <c r="B13" s="42">
         <v>100100</v>
       </c>
-      <c r="C13" s="25" t="s">
+      <c r="C13" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="35">
+      <c r="D13" s="36">
         <v>31203</v>
       </c>
-      <c r="E13" s="35" t="s">
+      <c r="E13" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="F13" s="40" t="s">
+      <c r="F13" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="G13" s="40">
+      <c r="G13" s="41">
         <v>2001001</v>
       </c>
-      <c r="H13" s="40" t="s">
+      <c r="H13" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="I13" s="40" t="s">
+      <c r="I13" s="41" t="s">
         <v>65</v>
       </c>
-      <c r="J13" s="40"/>
-      <c r="K13" s="42" t="s">
+      <c r="J13" s="41"/>
+      <c r="K13" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="L13" s="40"/>
-      <c r="M13" s="40"/>
-      <c r="N13" s="40"/>
-      <c r="O13" s="40"/>
-      <c r="P13" s="40"/>
-      <c r="Q13" s="40"/>
-      <c r="R13" s="10"/>
-      <c r="S13" s="29"/>
+      <c r="L13" s="41"/>
+      <c r="M13" s="41"/>
+      <c r="N13" s="41"/>
+      <c r="O13" s="41"/>
+      <c r="P13" s="41"/>
+      <c r="Q13" s="41"/>
+      <c r="R13" s="11"/>
+      <c r="S13" s="30"/>
     </row>
     <row r="14" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A14" s="35">
+      <c r="A14" s="36">
         <v>30010010</v>
       </c>
-      <c r="B14" s="43">
+      <c r="B14" s="44">
         <v>100100</v>
       </c>
-      <c r="C14" s="25" t="s">
+      <c r="C14" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="44">
+      <c r="D14" s="45">
         <v>31301</v>
       </c>
-      <c r="E14" s="44" t="s">
+      <c r="E14" s="45" t="s">
         <v>67</v>
       </c>
-      <c r="F14" s="35" t="s">
+      <c r="F14" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="G14" s="35"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="35" t="s">
+      <c r="G14" s="36"/>
+      <c r="H14" s="36"/>
+      <c r="I14" s="36" t="s">
         <v>68</v>
       </c>
-      <c r="J14" s="35"/>
-      <c r="K14" s="45"/>
-      <c r="L14" s="35" t="s">
+      <c r="J14" s="36"/>
+      <c r="K14" s="46"/>
+      <c r="L14" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="M14" s="35" t="s">
+      <c r="M14" s="36" t="s">
         <v>69</v>
       </c>
-      <c r="N14" s="35"/>
-      <c r="O14" s="35"/>
-      <c r="P14" s="35"/>
-      <c r="Q14" s="46" t="s">
+      <c r="N14" s="36"/>
+      <c r="O14" s="36"/>
+      <c r="P14" s="36"/>
+      <c r="Q14" s="47" t="s">
         <v>70</v>
       </c>
-      <c r="R14" s="47" t="s">
+      <c r="R14" s="48" t="s">
         <v>71</v>
       </c>
-      <c r="S14" s="13" t="s">
+      <c r="S14" s="14" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="15" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A15" s="40">
+      <c r="A15" s="41">
         <v>30010011</v>
       </c>
-      <c r="B15" s="41">
+      <c r="B15" s="42">
         <v>100100</v>
       </c>
-      <c r="C15" s="25" t="s">
+      <c r="C15" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="D15" s="44">
+      <c r="D15" s="45">
         <v>31302</v>
       </c>
-      <c r="E15" s="44" t="s">
+      <c r="E15" s="45" t="s">
         <v>73</v>
       </c>
-      <c r="F15" s="40" t="s">
+      <c r="F15" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="G15" s="40"/>
-      <c r="H15" s="40"/>
-      <c r="I15" s="40" t="s">
+      <c r="G15" s="41"/>
+      <c r="H15" s="41"/>
+      <c r="I15" s="41" t="s">
         <v>74</v>
       </c>
-      <c r="J15" s="40"/>
-      <c r="K15" s="42"/>
-      <c r="L15" s="40" t="s">
+      <c r="J15" s="41"/>
+      <c r="K15" s="43"/>
+      <c r="L15" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="M15" s="40" t="s">
+      <c r="M15" s="41" t="s">
         <v>56</v>
       </c>
-      <c r="N15" s="40"/>
-      <c r="O15" s="40"/>
-      <c r="P15" s="40"/>
-      <c r="Q15" s="40"/>
-      <c r="R15" s="10"/>
-      <c r="S15" s="29"/>
+      <c r="N15" s="41"/>
+      <c r="O15" s="41"/>
+      <c r="P15" s="41"/>
+      <c r="Q15" s="41"/>
+      <c r="R15" s="11"/>
+      <c r="S15" s="30"/>
     </row>
     <row r="16" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A16" s="40">
+      <c r="A16" s="41">
         <v>30010012</v>
       </c>
-      <c r="B16" s="41">
+      <c r="B16" s="42">
         <v>100100</v>
       </c>
-      <c r="C16" s="25" t="s">
+      <c r="C16" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="D16" s="44">
+      <c r="D16" s="45">
         <v>31303</v>
       </c>
-      <c r="E16" s="44" t="s">
+      <c r="E16" s="45" t="s">
         <v>75</v>
       </c>
-      <c r="F16" s="40" t="s">
+      <c r="F16" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="G16" s="40">
+      <c r="G16" s="41">
         <v>2001001</v>
       </c>
-      <c r="H16" s="40" t="s">
+      <c r="H16" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="I16" s="40" t="s">
+      <c r="I16" s="41" t="s">
         <v>65</v>
       </c>
-      <c r="J16" s="40"/>
-      <c r="K16" s="42" t="s">
+      <c r="J16" s="41"/>
+      <c r="K16" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="L16" s="40"/>
-      <c r="M16" s="40"/>
-      <c r="N16" s="40"/>
-      <c r="O16" s="40"/>
-      <c r="P16" s="40"/>
-      <c r="Q16" s="40"/>
-      <c r="R16" s="10"/>
-      <c r="S16" s="29"/>
+      <c r="L16" s="41"/>
+      <c r="M16" s="41"/>
+      <c r="N16" s="41"/>
+      <c r="O16" s="41"/>
+      <c r="P16" s="41"/>
+      <c r="Q16" s="41"/>
+      <c r="R16" s="11"/>
+      <c r="S16" s="30"/>
     </row>
     <row r="17" s="3" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A17" s="10">
+      <c r="A17" s="11">
         <v>30070001</v>
       </c>
       <c r="B17" s="3">
@@ -2769,30 +2784,30 @@
       <c r="C17" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D17" s="33">
+      <c r="D17" s="34">
         <v>34001</v>
       </c>
-      <c r="E17" s="33" t="s">
+      <c r="E17" s="34" t="s">
         <v>77</v>
       </c>
-      <c r="F17" s="33" t="s">
+      <c r="F17" s="34" t="s">
         <v>78</v>
       </c>
-      <c r="G17" s="22">
+      <c r="G17" s="23">
         <v>2007001</v>
       </c>
-      <c r="H17" s="10" t="s">
+      <c r="H17" s="11" t="s">
         <v>59</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="K17" s="48" t="s">
+      <c r="K17" s="49" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="18" s="3" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A18" s="10">
+      <c r="A18" s="11">
         <v>30070002</v>
       </c>
       <c r="B18" s="3">
@@ -2801,30 +2816,30 @@
       <c r="C18" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D18" s="33">
+      <c r="D18" s="34">
         <v>34002</v>
       </c>
-      <c r="E18" s="33" t="s">
+      <c r="E18" s="34" t="s">
         <v>81</v>
       </c>
-      <c r="F18" s="33" t="s">
+      <c r="F18" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="G18" s="22">
+      <c r="G18" s="23">
         <v>2007001</v>
       </c>
-      <c r="H18" s="10" t="s">
+      <c r="H18" s="11" t="s">
         <v>59</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="K18" s="48" t="s">
+      <c r="K18" s="49" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="19" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A19" s="35">
+      <c r="A19" s="36">
         <v>30120001</v>
       </c>
       <c r="B19" s="4">
@@ -2833,33 +2848,33 @@
       <c r="C19" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="D19" s="35">
+      <c r="D19" s="36">
         <v>32001</v>
       </c>
-      <c r="E19" s="35" t="s">
+      <c r="E19" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="F19" s="35" t="s">
+      <c r="F19" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="G19" s="43">
+      <c r="G19" s="44">
         <v>2012001</v>
       </c>
-      <c r="H19" s="35" t="s">
+      <c r="H19" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="I19" s="35" t="s">
+      <c r="I19" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="J19" s="35" t="s">
+      <c r="J19" s="36" t="s">
         <v>85</v>
       </c>
-      <c r="K19" s="49">
+      <c r="K19" s="50">
         <v>10120041</v>
       </c>
     </row>
     <row r="20" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A20" s="35">
+      <c r="A20" s="36">
         <v>30120002</v>
       </c>
       <c r="B20" s="4">
@@ -2868,33 +2883,33 @@
       <c r="C20" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="D20" s="35">
+      <c r="D20" s="36">
         <v>32002</v>
       </c>
-      <c r="E20" s="35" t="s">
+      <c r="E20" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="F20" s="35" t="s">
+      <c r="F20" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="G20" s="43">
+      <c r="G20" s="44">
         <v>2012001</v>
       </c>
-      <c r="H20" s="35" t="s">
+      <c r="H20" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="I20" s="35" t="s">
+      <c r="I20" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="J20" s="35" t="s">
+      <c r="J20" s="36" t="s">
         <v>85</v>
       </c>
-      <c r="K20" s="49">
+      <c r="K20" s="50">
         <v>10120042</v>
       </c>
     </row>
     <row r="21" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A21" s="35">
+      <c r="A21" s="36">
         <v>30120003</v>
       </c>
       <c r="B21" s="4">
@@ -2903,33 +2918,33 @@
       <c r="C21" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="D21" s="35">
+      <c r="D21" s="36">
         <v>32003</v>
       </c>
-      <c r="E21" s="35" t="s">
+      <c r="E21" s="36" t="s">
         <v>87</v>
       </c>
-      <c r="F21" s="35" t="s">
+      <c r="F21" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="G21" s="43">
+      <c r="G21" s="44">
         <v>2012001</v>
       </c>
-      <c r="H21" s="35" t="s">
+      <c r="H21" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="I21" s="35" t="s">
+      <c r="I21" s="36" t="s">
         <v>87</v>
       </c>
-      <c r="J21" s="35" t="s">
+      <c r="J21" s="36" t="s">
         <v>85</v>
       </c>
-      <c r="K21" s="49">
+      <c r="K21" s="50">
         <v>10120043</v>
       </c>
     </row>
     <row r="22" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A22" s="35">
+      <c r="A22" s="36">
         <v>30120004</v>
       </c>
       <c r="B22" s="4">
@@ -2938,33 +2953,33 @@
       <c r="C22" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="D22" s="35">
+      <c r="D22" s="36">
         <v>32004</v>
       </c>
-      <c r="E22" s="35" t="s">
+      <c r="E22" s="36" t="s">
         <v>88</v>
       </c>
-      <c r="F22" s="35" t="s">
+      <c r="F22" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="G22" s="43">
+      <c r="G22" s="44">
         <v>2012001</v>
       </c>
-      <c r="H22" s="35" t="s">
+      <c r="H22" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="I22" s="35" t="s">
+      <c r="I22" s="36" t="s">
         <v>88</v>
       </c>
-      <c r="J22" s="35" t="s">
+      <c r="J22" s="36" t="s">
         <v>85</v>
       </c>
-      <c r="K22" s="49">
+      <c r="K22" s="50">
         <v>10120044</v>
       </c>
     </row>
     <row r="23" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A23" s="35">
+      <c r="A23" s="36">
         <v>30120005</v>
       </c>
       <c r="B23" s="4">
@@ -2973,33 +2988,33 @@
       <c r="C23" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="D23" s="35">
+      <c r="D23" s="36">
         <v>32005</v>
       </c>
-      <c r="E23" s="35" t="s">
+      <c r="E23" s="36" t="s">
         <v>88</v>
       </c>
-      <c r="F23" s="35" t="s">
+      <c r="F23" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="G23" s="43">
+      <c r="G23" s="44">
         <v>2012001</v>
       </c>
-      <c r="H23" s="35" t="s">
+      <c r="H23" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="I23" s="35" t="s">
+      <c r="I23" s="36" t="s">
         <v>88</v>
       </c>
-      <c r="J23" s="35" t="s">
+      <c r="J23" s="36" t="s">
         <v>85</v>
       </c>
-      <c r="K23" s="49">
+      <c r="K23" s="50">
         <v>10120045</v>
       </c>
     </row>
     <row r="24" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A24" s="35">
+      <c r="A24" s="36">
         <v>30120006</v>
       </c>
       <c r="B24" s="4">
@@ -3008,33 +3023,33 @@
       <c r="C24" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="D24" s="35">
+      <c r="D24" s="36">
         <v>32006</v>
       </c>
-      <c r="E24" s="35" t="s">
+      <c r="E24" s="36" t="s">
         <v>88</v>
       </c>
-      <c r="F24" s="35" t="s">
+      <c r="F24" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="G24" s="43">
+      <c r="G24" s="44">
         <v>2012001</v>
       </c>
-      <c r="H24" s="35" t="s">
+      <c r="H24" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="I24" s="35" t="s">
+      <c r="I24" s="36" t="s">
         <v>88</v>
       </c>
-      <c r="J24" s="35" t="s">
+      <c r="J24" s="36" t="s">
         <v>85</v>
       </c>
-      <c r="K24" s="49">
+      <c r="K24" s="50">
         <v>10120046</v>
       </c>
     </row>
     <row r="25" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A25" s="50">
+      <c r="A25" s="51">
         <v>30120011</v>
       </c>
       <c r="B25" s="5">
@@ -3043,33 +3058,33 @@
       <c r="C25" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="D25" s="35">
+      <c r="D25" s="36">
         <v>32101</v>
       </c>
-      <c r="E25" s="50" t="s">
+      <c r="E25" s="51" t="s">
         <v>84</v>
       </c>
-      <c r="F25" s="50" t="s">
+      <c r="F25" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="G25" s="51">
+      <c r="G25" s="52">
         <v>2012001</v>
       </c>
-      <c r="H25" s="50" t="s">
+      <c r="H25" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="I25" s="50" t="s">
+      <c r="I25" s="51" t="s">
         <v>84</v>
       </c>
-      <c r="J25" s="50" t="s">
+      <c r="J25" s="51" t="s">
         <v>90</v>
       </c>
-      <c r="K25" s="52">
+      <c r="K25" s="53">
         <v>10120041</v>
       </c>
     </row>
     <row r="26" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A26" s="50">
+      <c r="A26" s="51">
         <v>30120012</v>
       </c>
       <c r="B26" s="5">
@@ -3078,33 +3093,33 @@
       <c r="C26" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="D26" s="35">
+      <c r="D26" s="36">
         <v>32102</v>
       </c>
-      <c r="E26" s="50" t="s">
+      <c r="E26" s="51" t="s">
         <v>86</v>
       </c>
-      <c r="F26" s="50" t="s">
+      <c r="F26" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="G26" s="51">
+      <c r="G26" s="52">
         <v>2012001</v>
       </c>
-      <c r="H26" s="50" t="s">
+      <c r="H26" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="I26" s="50" t="s">
+      <c r="I26" s="51" t="s">
         <v>86</v>
       </c>
-      <c r="J26" s="50" t="s">
+      <c r="J26" s="51" t="s">
         <v>90</v>
       </c>
-      <c r="K26" s="52">
+      <c r="K26" s="53">
         <v>10120042</v>
       </c>
     </row>
     <row r="27" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A27" s="50">
+      <c r="A27" s="51">
         <v>30120013</v>
       </c>
       <c r="B27" s="5">
@@ -3113,33 +3128,33 @@
       <c r="C27" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="D27" s="35">
+      <c r="D27" s="36">
         <v>32103</v>
       </c>
-      <c r="E27" s="50" t="s">
+      <c r="E27" s="51" t="s">
         <v>87</v>
       </c>
-      <c r="F27" s="50" t="s">
+      <c r="F27" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="G27" s="51">
+      <c r="G27" s="52">
         <v>2012001</v>
       </c>
-      <c r="H27" s="50" t="s">
+      <c r="H27" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="I27" s="50" t="s">
+      <c r="I27" s="51" t="s">
         <v>87</v>
       </c>
-      <c r="J27" s="50" t="s">
+      <c r="J27" s="51" t="s">
         <v>90</v>
       </c>
-      <c r="K27" s="52">
+      <c r="K27" s="53">
         <v>10120043</v>
       </c>
     </row>
     <row r="28" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A28" s="50">
+      <c r="A28" s="51">
         <v>30120014</v>
       </c>
       <c r="B28" s="5">
@@ -3148,33 +3163,33 @@
       <c r="C28" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="D28" s="35">
+      <c r="D28" s="36">
         <v>32104</v>
       </c>
-      <c r="E28" s="50" t="s">
+      <c r="E28" s="51" t="s">
         <v>88</v>
       </c>
-      <c r="F28" s="50" t="s">
+      <c r="F28" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="G28" s="51">
+      <c r="G28" s="52">
         <v>2012001</v>
       </c>
-      <c r="H28" s="50" t="s">
+      <c r="H28" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="I28" s="50" t="s">
+      <c r="I28" s="51" t="s">
         <v>88</v>
       </c>
-      <c r="J28" s="50" t="s">
+      <c r="J28" s="51" t="s">
         <v>90</v>
       </c>
-      <c r="K28" s="52">
+      <c r="K28" s="53">
         <v>10120044</v>
       </c>
     </row>
     <row r="29" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A29" s="50">
+      <c r="A29" s="51">
         <v>30120015</v>
       </c>
       <c r="B29" s="5">
@@ -3183,33 +3198,33 @@
       <c r="C29" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="D29" s="35">
+      <c r="D29" s="36">
         <v>32105</v>
       </c>
-      <c r="E29" s="50" t="s">
+      <c r="E29" s="51" t="s">
         <v>88</v>
       </c>
-      <c r="F29" s="50" t="s">
+      <c r="F29" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="G29" s="51">
+      <c r="G29" s="52">
         <v>2012001</v>
       </c>
-      <c r="H29" s="50" t="s">
+      <c r="H29" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="I29" s="50" t="s">
+      <c r="I29" s="51" t="s">
         <v>88</v>
       </c>
-      <c r="J29" s="50" t="s">
+      <c r="J29" s="51" t="s">
         <v>90</v>
       </c>
-      <c r="K29" s="52">
+      <c r="K29" s="53">
         <v>10120045</v>
       </c>
     </row>
     <row r="30" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A30" s="50">
+      <c r="A30" s="51">
         <v>30120016</v>
       </c>
       <c r="B30" s="5">
@@ -3218,33 +3233,33 @@
       <c r="C30" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="D30" s="35">
+      <c r="D30" s="36">
         <v>32106</v>
       </c>
-      <c r="E30" s="50" t="s">
+      <c r="E30" s="51" t="s">
         <v>88</v>
       </c>
-      <c r="F30" s="50" t="s">
+      <c r="F30" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="G30" s="51">
+      <c r="G30" s="52">
         <v>2012001</v>
       </c>
-      <c r="H30" s="50" t="s">
+      <c r="H30" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="I30" s="50" t="s">
+      <c r="I30" s="51" t="s">
         <v>88</v>
       </c>
-      <c r="J30" s="50" t="s">
+      <c r="J30" s="51" t="s">
         <v>90</v>
       </c>
-      <c r="K30" s="52">
+      <c r="K30" s="53">
         <v>10120046</v>
       </c>
     </row>
     <row r="31" s="6" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A31" s="44">
+      <c r="A31" s="45">
         <v>30120021</v>
       </c>
       <c r="B31" s="6">
@@ -3253,31 +3268,31 @@
       <c r="C31" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D31" s="44">
+      <c r="D31" s="45">
         <v>32201</v>
       </c>
-      <c r="E31" s="44" t="s">
+      <c r="E31" s="45" t="s">
         <v>84</v>
       </c>
-      <c r="F31" s="44" t="s">
+      <c r="F31" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="G31" s="53">
+      <c r="G31" s="54">
         <v>2012001</v>
       </c>
-      <c r="H31" s="44" t="s">
+      <c r="H31" s="45" t="s">
         <v>59</v>
       </c>
-      <c r="I31" s="44" t="s">
+      <c r="I31" s="45" t="s">
         <v>84</v>
       </c>
-      <c r="J31" s="44"/>
-      <c r="K31" s="54">
+      <c r="J31" s="45"/>
+      <c r="K31" s="55">
         <v>10120041</v>
       </c>
     </row>
     <row r="32" s="6" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A32" s="44">
+      <c r="A32" s="45">
         <v>30120022</v>
       </c>
       <c r="B32" s="6">
@@ -3286,31 +3301,31 @@
       <c r="C32" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D32" s="44">
+      <c r="D32" s="45">
         <v>32202</v>
       </c>
-      <c r="E32" s="44" t="s">
+      <c r="E32" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="F32" s="44" t="s">
+      <c r="F32" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="G32" s="53">
+      <c r="G32" s="54">
         <v>2012001</v>
       </c>
-      <c r="H32" s="44" t="s">
+      <c r="H32" s="45" t="s">
         <v>59</v>
       </c>
-      <c r="I32" s="44" t="s">
+      <c r="I32" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="J32" s="44"/>
-      <c r="K32" s="54">
+      <c r="J32" s="45"/>
+      <c r="K32" s="55">
         <v>10120042</v>
       </c>
     </row>
     <row r="33" s="6" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A33" s="44">
+      <c r="A33" s="45">
         <v>30120023</v>
       </c>
       <c r="B33" s="6">
@@ -3319,31 +3334,31 @@
       <c r="C33" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D33" s="44">
+      <c r="D33" s="45">
         <v>32203</v>
       </c>
-      <c r="E33" s="44" t="s">
+      <c r="E33" s="45" t="s">
         <v>87</v>
       </c>
-      <c r="F33" s="44" t="s">
+      <c r="F33" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="G33" s="53">
+      <c r="G33" s="54">
         <v>2012001</v>
       </c>
-      <c r="H33" s="44" t="s">
+      <c r="H33" s="45" t="s">
         <v>59</v>
       </c>
-      <c r="I33" s="44" t="s">
+      <c r="I33" s="45" t="s">
         <v>87</v>
       </c>
-      <c r="J33" s="44"/>
-      <c r="K33" s="54">
+      <c r="J33" s="45"/>
+      <c r="K33" s="55">
         <v>10120043</v>
       </c>
     </row>
     <row r="34" s="6" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A34" s="44">
+      <c r="A34" s="45">
         <v>30120024</v>
       </c>
       <c r="B34" s="6">
@@ -3352,31 +3367,31 @@
       <c r="C34" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D34" s="44">
+      <c r="D34" s="45">
         <v>32204</v>
       </c>
-      <c r="E34" s="44" t="s">
+      <c r="E34" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="F34" s="44" t="s">
+      <c r="F34" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="G34" s="53">
+      <c r="G34" s="54">
         <v>2012001</v>
       </c>
-      <c r="H34" s="44" t="s">
+      <c r="H34" s="45" t="s">
         <v>59</v>
       </c>
-      <c r="I34" s="44" t="s">
+      <c r="I34" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="J34" s="44"/>
-      <c r="K34" s="54">
+      <c r="J34" s="45"/>
+      <c r="K34" s="55">
         <v>10120044</v>
       </c>
     </row>
     <row r="35" s="6" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A35" s="44">
+      <c r="A35" s="45">
         <v>30120025</v>
       </c>
       <c r="B35" s="6">
@@ -3385,31 +3400,31 @@
       <c r="C35" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D35" s="44">
+      <c r="D35" s="45">
         <v>32205</v>
       </c>
-      <c r="E35" s="44" t="s">
+      <c r="E35" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="F35" s="44" t="s">
+      <c r="F35" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="G35" s="53">
+      <c r="G35" s="54">
         <v>2012001</v>
       </c>
-      <c r="H35" s="44" t="s">
+      <c r="H35" s="45" t="s">
         <v>59</v>
       </c>
-      <c r="I35" s="44" t="s">
+      <c r="I35" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="J35" s="44"/>
-      <c r="K35" s="54">
+      <c r="J35" s="45"/>
+      <c r="K35" s="55">
         <v>10120045</v>
       </c>
     </row>
     <row r="36" s="6" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A36" s="44">
+      <c r="A36" s="45">
         <v>30120026</v>
       </c>
       <c r="B36" s="6">
@@ -3418,822 +3433,829 @@
       <c r="C36" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D36" s="44">
+      <c r="D36" s="45">
         <v>32206</v>
       </c>
-      <c r="E36" s="44" t="s">
+      <c r="E36" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="F36" s="44" t="s">
+      <c r="F36" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="G36" s="53">
+      <c r="G36" s="54">
         <v>2012001</v>
       </c>
-      <c r="H36" s="44" t="s">
+      <c r="H36" s="45" t="s">
         <v>59</v>
       </c>
-      <c r="I36" s="44" t="s">
+      <c r="I36" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="J36" s="44"/>
-      <c r="K36" s="54">
+      <c r="J36" s="45"/>
+      <c r="K36" s="55">
         <v>10120046</v>
       </c>
     </row>
     <row r="37" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A37" s="24">
+      <c r="A37" s="25">
         <v>30240001</v>
       </c>
-      <c r="B37" s="25">
+      <c r="B37" s="26">
         <v>102400</v>
       </c>
-      <c r="C37" s="25" t="s">
+      <c r="C37" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="D37" s="24">
+      <c r="D37" s="25">
         <v>32401</v>
       </c>
-      <c r="E37" s="24" t="s">
+      <c r="E37" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="F37" s="24" t="s">
+      <c r="F37" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="G37" s="24"/>
-      <c r="H37" s="24"/>
-      <c r="I37" s="24" t="s">
+      <c r="G37" s="25"/>
+      <c r="H37" s="25"/>
+      <c r="I37" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="J37" s="24"/>
-      <c r="K37" s="26"/>
-      <c r="L37" s="10" t="s">
+      <c r="J37" s="25"/>
+      <c r="K37" s="27"/>
+      <c r="L37" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="M37" s="24" t="s">
+      <c r="M37" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="N37" s="24" t="s">
+      <c r="N37" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="O37" s="24"/>
-      <c r="P37" s="24"/>
-      <c r="Q37" s="27" t="s">
+      <c r="O37" s="25"/>
+      <c r="P37" s="25"/>
+      <c r="Q37" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="R37" s="28" t="s">
+      <c r="R37" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="S37" s="29" t="s">
+      <c r="S37" s="30" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="38" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A38" s="24">
+      <c r="A38" s="25">
         <v>30240002</v>
       </c>
-      <c r="B38" s="25">
+      <c r="B38" s="26">
         <v>102400</v>
       </c>
-      <c r="C38" s="25" t="s">
+      <c r="C38" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="D38" s="24">
+      <c r="D38" s="25">
         <v>32402</v>
       </c>
-      <c r="E38" s="24" t="s">
+      <c r="E38" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="F38" s="24" t="s">
+      <c r="F38" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="G38" s="24"/>
-      <c r="H38" s="24"/>
-      <c r="I38" s="24" t="s">
+      <c r="G38" s="25"/>
+      <c r="H38" s="25"/>
+      <c r="I38" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="J38" s="24"/>
-      <c r="K38" s="26"/>
-      <c r="L38" s="10" t="s">
+      <c r="J38" s="25"/>
+      <c r="K38" s="27"/>
+      <c r="L38" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="M38" s="24" t="s">
+      <c r="M38" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="N38" s="24" t="s">
+      <c r="N38" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="O38" s="24"/>
-      <c r="P38" s="24"/>
-      <c r="Q38" s="27" t="s">
+      <c r="O38" s="25"/>
+      <c r="P38" s="25"/>
+      <c r="Q38" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="R38" s="28" t="s">
+      <c r="R38" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="S38" s="29"/>
+      <c r="S38" s="30"/>
     </row>
     <row r="39" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A39" s="24">
+      <c r="A39" s="25">
         <v>30240003</v>
       </c>
-      <c r="B39" s="25">
+      <c r="B39" s="26">
         <v>102400</v>
       </c>
-      <c r="C39" s="25" t="s">
+      <c r="C39" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="D39" s="24">
+      <c r="D39" s="25">
         <v>32403</v>
       </c>
-      <c r="E39" s="24" t="s">
+      <c r="E39" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="F39" s="24" t="s">
+      <c r="F39" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="G39" s="24"/>
-      <c r="H39" s="24"/>
-      <c r="I39" s="24" t="s">
+      <c r="G39" s="25"/>
+      <c r="H39" s="25"/>
+      <c r="I39" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="J39" s="24"/>
-      <c r="K39" s="26"/>
-      <c r="L39" s="10" t="s">
+      <c r="J39" s="25"/>
+      <c r="K39" s="27"/>
+      <c r="L39" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="M39" s="24" t="s">
+      <c r="M39" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="N39" s="24" t="s">
+      <c r="N39" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="O39" s="24"/>
-      <c r="P39" s="24"/>
-      <c r="Q39" s="27" t="s">
+      <c r="O39" s="25"/>
+      <c r="P39" s="25"/>
+      <c r="Q39" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="R39" s="28" t="s">
+      <c r="R39" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="S39" s="29"/>
+      <c r="S39" s="30"/>
     </row>
     <row r="40" s="3" customFormat="1" ht="15" customHeight="1" spans="1:19">
-      <c r="A40" s="24">
+      <c r="A40" s="25">
         <v>30240004</v>
       </c>
-      <c r="B40" s="25">
+      <c r="B40" s="26">
         <v>102400</v>
       </c>
-      <c r="C40" s="25" t="s">
+      <c r="C40" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="D40" s="24">
+      <c r="D40" s="25">
         <v>32404</v>
       </c>
-      <c r="E40" s="24" t="s">
+      <c r="E40" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="F40" s="24" t="s">
+      <c r="F40" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="G40" s="24"/>
-      <c r="H40" s="24"/>
-      <c r="I40" s="24" t="s">
+      <c r="G40" s="25"/>
+      <c r="H40" s="25"/>
+      <c r="I40" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="J40" s="24"/>
-      <c r="K40" s="26"/>
-      <c r="L40" s="10" t="s">
+      <c r="J40" s="25"/>
+      <c r="K40" s="27"/>
+      <c r="L40" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="M40" s="24" t="s">
+      <c r="M40" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="N40" s="24" t="s">
+      <c r="N40" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="O40" s="24"/>
-      <c r="P40" s="24"/>
-      <c r="Q40" s="27" t="s">
+      <c r="O40" s="25"/>
+      <c r="P40" s="25"/>
+      <c r="Q40" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="R40" s="28" t="s">
+      <c r="R40" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="S40" s="29"/>
+      <c r="S40" s="30"/>
     </row>
     <row r="41" s="3" customFormat="1" ht="15" customHeight="1" spans="1:19">
-      <c r="A41" s="10">
+      <c r="A41" s="11">
         <v>30240005</v>
       </c>
-      <c r="B41" s="22">
+      <c r="B41" s="23">
         <v>102400</v>
       </c>
-      <c r="C41" s="25" t="s">
+      <c r="C41" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="D41" s="10">
+      <c r="D41" s="11">
         <v>32411</v>
       </c>
-      <c r="E41" s="10" t="s">
+      <c r="E41" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="F41" s="10" t="s">
+      <c r="F41" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="G41" s="10"/>
-      <c r="H41" s="10"/>
-      <c r="I41" s="10" t="s">
+      <c r="G41" s="11"/>
+      <c r="H41" s="11"/>
+      <c r="I41" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="J41" s="10"/>
-      <c r="K41" s="12"/>
-      <c r="L41" s="10" t="s">
+      <c r="J41" s="11"/>
+      <c r="K41" s="13"/>
+      <c r="L41" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="M41" s="10" t="s">
+      <c r="M41" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="N41" s="10"/>
-      <c r="O41" s="10" t="s">
+      <c r="N41" s="11"/>
+      <c r="O41" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="P41" s="10"/>
-      <c r="Q41" s="13"/>
-      <c r="R41" s="13"/>
-      <c r="S41" s="29"/>
+      <c r="P41" s="11"/>
+      <c r="Q41" s="14"/>
+      <c r="R41" s="14"/>
+      <c r="S41" s="30"/>
     </row>
     <row r="42" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A42" s="30">
+      <c r="A42" s="31">
         <v>30240006</v>
       </c>
-      <c r="B42" s="31">
+      <c r="B42" s="32">
         <v>102400</v>
       </c>
-      <c r="C42" s="25" t="s">
+      <c r="C42" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="D42" s="30">
+      <c r="D42" s="31">
         <v>32421</v>
       </c>
-      <c r="E42" s="30" t="s">
+      <c r="E42" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="F42" s="30" t="s">
+      <c r="F42" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="G42" s="30"/>
-      <c r="H42" s="30"/>
-      <c r="I42" s="30" t="s">
+      <c r="G42" s="31"/>
+      <c r="H42" s="31"/>
+      <c r="I42" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="J42" s="30"/>
-      <c r="K42" s="32"/>
-      <c r="L42" s="30" t="s">
+      <c r="J42" s="31"/>
+      <c r="K42" s="33"/>
+      <c r="L42" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="M42" s="30" t="s">
+      <c r="M42" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="N42" s="30" t="s">
+      <c r="N42" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="O42" s="30" t="s">
+      <c r="O42" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="P42" s="30"/>
-      <c r="Q42" s="30"/>
-      <c r="R42" s="10"/>
-      <c r="S42" s="29"/>
+      <c r="P42" s="31"/>
+      <c r="Q42" s="31"/>
+      <c r="R42" s="11"/>
+      <c r="S42" s="30"/>
     </row>
     <row r="43" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A43" s="33">
+      <c r="A43" s="34">
         <v>30240007</v>
       </c>
-      <c r="B43" s="34">
+      <c r="B43" s="35">
         <v>102400</v>
       </c>
-      <c r="C43" s="25" t="s">
+      <c r="C43" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="D43" s="35">
+      <c r="D43" s="36">
         <v>32431</v>
       </c>
-      <c r="E43" s="35" t="s">
+      <c r="E43" s="36" t="s">
         <v>57</v>
       </c>
-      <c r="F43" s="33" t="s">
+      <c r="F43" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="G43" s="33">
+      <c r="G43" s="34">
         <v>2024001</v>
       </c>
-      <c r="H43" s="33" t="s">
+      <c r="H43" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="I43" s="33" t="s">
+      <c r="I43" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="J43" s="33"/>
-      <c r="K43" s="36">
+      <c r="J43" s="34"/>
+      <c r="K43" s="37">
         <v>10240091</v>
       </c>
-      <c r="L43" s="33"/>
-      <c r="M43" s="33"/>
-      <c r="N43" s="33"/>
-      <c r="O43" s="33"/>
-      <c r="P43" s="33"/>
-      <c r="Q43" s="33"/>
-      <c r="R43" s="10"/>
-      <c r="S43" s="29"/>
+      <c r="L43" s="34"/>
+      <c r="M43" s="34"/>
+      <c r="N43" s="34"/>
+      <c r="O43" s="34"/>
+      <c r="P43" s="34"/>
+      <c r="Q43" s="34"/>
+      <c r="R43" s="11"/>
+      <c r="S43" s="30"/>
     </row>
     <row r="44" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A44" s="37">
+      <c r="A44" s="38">
         <v>30240008</v>
       </c>
-      <c r="B44" s="38">
+      <c r="B44" s="39">
         <v>102400</v>
       </c>
-      <c r="C44" s="25" t="s">
+      <c r="C44" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="D44" s="35">
+      <c r="D44" s="36">
         <v>32432</v>
       </c>
-      <c r="E44" s="35" t="s">
+      <c r="E44" s="36" t="s">
         <v>61</v>
       </c>
-      <c r="F44" s="37" t="s">
+      <c r="F44" s="38" t="s">
         <v>52</v>
       </c>
-      <c r="G44" s="37">
+      <c r="G44" s="38">
         <v>2024001</v>
       </c>
-      <c r="H44" s="37" t="s">
+      <c r="H44" s="38" t="s">
         <v>59</v>
       </c>
-      <c r="I44" s="37" t="s">
+      <c r="I44" s="38" t="s">
         <v>62</v>
       </c>
-      <c r="J44" s="37"/>
-      <c r="K44" s="39" t="s">
+      <c r="J44" s="38"/>
+      <c r="K44" s="40" t="s">
         <v>92</v>
       </c>
-      <c r="L44" s="37"/>
-      <c r="M44" s="37"/>
-      <c r="N44" s="37"/>
-      <c r="O44" s="37"/>
-      <c r="P44" s="37"/>
-      <c r="Q44" s="37"/>
-      <c r="R44" s="10"/>
-      <c r="S44" s="29"/>
+      <c r="L44" s="38"/>
+      <c r="M44" s="38"/>
+      <c r="N44" s="38"/>
+      <c r="O44" s="38"/>
+      <c r="P44" s="38"/>
+      <c r="Q44" s="38"/>
+      <c r="R44" s="11"/>
+      <c r="S44" s="30"/>
     </row>
     <row r="45" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A45" s="40">
+      <c r="A45" s="41">
         <v>30240009</v>
       </c>
-      <c r="B45" s="41">
+      <c r="B45" s="42">
         <v>102400</v>
       </c>
-      <c r="C45" s="25" t="s">
+      <c r="C45" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="D45" s="35">
+      <c r="D45" s="36">
         <v>32433</v>
       </c>
-      <c r="E45" s="35" t="s">
+      <c r="E45" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="F45" s="40" t="s">
+      <c r="F45" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="G45" s="40">
+      <c r="G45" s="41">
         <v>2024001</v>
       </c>
-      <c r="H45" s="40" t="s">
+      <c r="H45" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="I45" s="40" t="s">
+      <c r="I45" s="41" t="s">
         <v>65</v>
       </c>
-      <c r="J45" s="40"/>
-      <c r="K45" s="42" t="s">
+      <c r="J45" s="41"/>
+      <c r="K45" s="43" t="s">
         <v>93</v>
       </c>
-      <c r="L45" s="40"/>
-      <c r="M45" s="40"/>
-      <c r="N45" s="40"/>
-      <c r="O45" s="40"/>
-      <c r="P45" s="40"/>
-      <c r="Q45" s="40"/>
-      <c r="R45" s="10"/>
-      <c r="S45" s="29"/>
+      <c r="L45" s="41"/>
+      <c r="M45" s="41"/>
+      <c r="N45" s="41"/>
+      <c r="O45" s="41"/>
+      <c r="P45" s="41"/>
+      <c r="Q45" s="41"/>
+      <c r="R45" s="11"/>
+      <c r="S45" s="30"/>
     </row>
     <row r="46" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A46" s="35">
+      <c r="A46" s="36">
         <v>30240010</v>
       </c>
-      <c r="B46" s="43">
+      <c r="B46" s="44">
         <v>102400</v>
       </c>
-      <c r="C46" s="25" t="s">
+      <c r="C46" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="D46" s="44">
+      <c r="D46" s="45">
         <v>32441</v>
       </c>
-      <c r="E46" s="44" t="s">
+      <c r="E46" s="45" t="s">
         <v>67</v>
       </c>
-      <c r="F46" s="35" t="s">
+      <c r="F46" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="G46" s="35"/>
-      <c r="H46" s="35"/>
-      <c r="I46" s="35" t="s">
+      <c r="G46" s="36"/>
+      <c r="H46" s="36"/>
+      <c r="I46" s="36" t="s">
         <v>68</v>
       </c>
-      <c r="J46" s="35"/>
-      <c r="K46" s="45"/>
-      <c r="L46" s="35" t="s">
+      <c r="J46" s="36"/>
+      <c r="K46" s="46"/>
+      <c r="L46" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="M46" s="35" t="s">
+      <c r="M46" s="36" t="s">
         <v>69</v>
       </c>
-      <c r="N46" s="35"/>
-      <c r="O46" s="35"/>
-      <c r="P46" s="35"/>
-      <c r="Q46" s="46" t="s">
+      <c r="N46" s="36"/>
+      <c r="O46" s="36"/>
+      <c r="P46" s="36"/>
+      <c r="Q46" s="47" t="s">
         <v>70</v>
       </c>
-      <c r="R46" s="47" t="s">
+      <c r="R46" s="48" t="s">
         <v>71</v>
       </c>
-      <c r="S46" s="13" t="s">
+      <c r="S46" s="14" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="47" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A47" s="40">
+      <c r="A47" s="41">
         <v>30240011</v>
       </c>
-      <c r="B47" s="41">
+      <c r="B47" s="42">
         <v>102400</v>
       </c>
-      <c r="C47" s="25" t="s">
+      <c r="C47" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="D47" s="44">
+      <c r="D47" s="45">
         <v>32442</v>
       </c>
-      <c r="E47" s="44" t="s">
+      <c r="E47" s="45" t="s">
         <v>73</v>
       </c>
-      <c r="F47" s="40" t="s">
+      <c r="F47" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="G47" s="40"/>
-      <c r="H47" s="40"/>
-      <c r="I47" s="40" t="s">
+      <c r="G47" s="41"/>
+      <c r="H47" s="41"/>
+      <c r="I47" s="41" t="s">
         <v>74</v>
       </c>
-      <c r="J47" s="40"/>
-      <c r="K47" s="42"/>
-      <c r="L47" s="40" t="s">
+      <c r="J47" s="41"/>
+      <c r="K47" s="43"/>
+      <c r="L47" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="M47" s="40" t="s">
+      <c r="M47" s="41" t="s">
         <v>56</v>
       </c>
-      <c r="N47" s="40"/>
-      <c r="O47" s="40"/>
-      <c r="P47" s="40"/>
-      <c r="Q47" s="40"/>
-      <c r="R47" s="10"/>
-      <c r="S47" s="29"/>
+      <c r="N47" s="41"/>
+      <c r="O47" s="41"/>
+      <c r="P47" s="41"/>
+      <c r="Q47" s="41"/>
+      <c r="R47" s="11"/>
+      <c r="S47" s="30"/>
     </row>
     <row r="48" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A48" s="40">
+      <c r="A48" s="41">
         <v>30240012</v>
       </c>
-      <c r="B48" s="41">
+      <c r="B48" s="42">
         <v>102400</v>
       </c>
-      <c r="C48" s="25" t="s">
+      <c r="C48" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="D48" s="44">
+      <c r="D48" s="45">
         <v>32443</v>
       </c>
-      <c r="E48" s="44" t="s">
+      <c r="E48" s="45" t="s">
         <v>75</v>
       </c>
-      <c r="F48" s="40" t="s">
+      <c r="F48" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="G48" s="40">
+      <c r="G48" s="41">
         <v>2024001</v>
       </c>
-      <c r="H48" s="40" t="s">
+      <c r="H48" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="I48" s="40" t="s">
+      <c r="I48" s="41" t="s">
         <v>65</v>
       </c>
-      <c r="J48" s="40"/>
-      <c r="K48" s="42" t="s">
+      <c r="J48" s="41"/>
+      <c r="K48" s="43" t="s">
         <v>93</v>
       </c>
-      <c r="L48" s="40"/>
-      <c r="M48" s="40"/>
-      <c r="N48" s="40"/>
-      <c r="O48" s="40"/>
-      <c r="P48" s="40"/>
-      <c r="Q48" s="40"/>
-      <c r="R48" s="10"/>
-      <c r="S48" s="29"/>
+      <c r="L48" s="41"/>
+      <c r="M48" s="41"/>
+      <c r="N48" s="41"/>
+      <c r="O48" s="41"/>
+      <c r="P48" s="41"/>
+      <c r="Q48" s="41"/>
+      <c r="R48" s="11"/>
+      <c r="S48" s="30"/>
     </row>
     <row r="49" s="3" customFormat="1" ht="16.5" spans="1:22">
-      <c r="A49" s="40">
+      <c r="A49" s="41">
         <v>30170001</v>
       </c>
-      <c r="B49" s="41">
+      <c r="B49" s="42">
         <v>101700</v>
       </c>
-      <c r="C49" s="25" t="s">
+      <c r="C49" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="D49" s="44">
+      <c r="D49" s="45">
         <v>301701</v>
       </c>
-      <c r="E49" s="44" t="s">
+      <c r="E49" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="F49" s="40" t="s">
+      <c r="F49" s="41" t="s">
         <v>78</v>
       </c>
-      <c r="G49" s="40">
+      <c r="G49" s="41">
         <v>2017001</v>
       </c>
-      <c r="H49" s="40" t="s">
+      <c r="H49" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="I49" s="40" t="s">
+      <c r="I49" s="41" t="s">
         <v>79</v>
       </c>
-      <c r="J49" s="40"/>
-      <c r="K49" s="42" t="s">
+      <c r="J49" s="41"/>
+      <c r="K49" s="43" t="s">
         <v>96</v>
       </c>
-      <c r="L49" s="40"/>
-      <c r="M49" s="40"/>
-      <c r="N49" s="40"/>
-      <c r="O49" s="40"/>
-      <c r="P49" s="40"/>
-      <c r="Q49" s="40"/>
-      <c r="R49" s="10"/>
-      <c r="S49" s="29"/>
+      <c r="L49" s="41"/>
+      <c r="M49" s="41"/>
+      <c r="N49" s="41"/>
+      <c r="O49" s="41"/>
+      <c r="P49" s="41"/>
+      <c r="Q49" s="41"/>
+      <c r="R49" s="11"/>
+      <c r="S49" s="30"/>
     </row>
     <row r="50" s="3" customFormat="1" ht="16.5" spans="1:22">
-      <c r="A50" s="40">
+      <c r="A50" s="41">
         <v>30170002</v>
       </c>
-      <c r="B50" s="41">
+      <c r="B50" s="42">
         <v>101700</v>
       </c>
-      <c r="C50" s="25" t="s">
+      <c r="C50" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="D50" s="44">
+      <c r="D50" s="45">
         <v>301702</v>
       </c>
-      <c r="E50" s="44" t="s">
+      <c r="E50" s="45" t="s">
         <v>97</v>
       </c>
-      <c r="F50" s="40" t="s">
+      <c r="F50" s="41" t="s">
         <v>82</v>
       </c>
-      <c r="G50" s="40">
+      <c r="G50" s="41">
         <v>2017001</v>
       </c>
-      <c r="H50" s="40" t="s">
+      <c r="H50" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="I50" s="40" t="s">
+      <c r="I50" s="41" t="s">
         <v>79</v>
       </c>
-      <c r="J50" s="40"/>
-      <c r="K50" s="42" t="s">
+      <c r="J50" s="41"/>
+      <c r="K50" s="43" t="s">
         <v>96</v>
       </c>
-      <c r="L50" s="40"/>
-      <c r="M50" s="40"/>
-      <c r="N50" s="40"/>
-      <c r="O50" s="40"/>
-      <c r="P50" s="40"/>
-      <c r="Q50" s="40"/>
-      <c r="R50" s="10"/>
-      <c r="S50" s="29"/>
+      <c r="L50" s="41"/>
+      <c r="M50" s="41"/>
+      <c r="N50" s="41"/>
+      <c r="O50" s="41"/>
+      <c r="P50" s="41"/>
+      <c r="Q50" s="41"/>
+      <c r="R50" s="11"/>
+      <c r="S50" s="30"/>
     </row>
     <row r="51" s="3" customFormat="1" ht="16.5" spans="1:22">
-      <c r="A51" s="40">
+      <c r="A51" s="41">
         <v>30220001</v>
       </c>
-      <c r="B51" s="41">
+      <c r="B51" s="42">
         <v>102200</v>
       </c>
-      <c r="C51" s="25" t="s">
+      <c r="C51" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="D51" s="44">
+      <c r="D51" s="45">
         <v>302201</v>
       </c>
-      <c r="E51" s="44" t="s">
+      <c r="E51" s="45" t="s">
         <v>99</v>
       </c>
-      <c r="F51" s="40" t="s">
+      <c r="F51" s="41" t="s">
         <v>100</v>
       </c>
-      <c r="G51" s="40">
+      <c r="G51" s="41">
         <v>2022001</v>
       </c>
-      <c r="H51" s="40" t="s">
+      <c r="H51" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="I51" s="40"/>
-      <c r="J51" s="40"/>
-      <c r="K51" s="42" t="s">
+      <c r="I51" s="41"/>
+      <c r="J51" s="41"/>
+      <c r="K51" s="43" t="s">
         <v>101</v>
       </c>
-      <c r="L51" s="40" t="s">
+      <c r="L51" s="41" t="s">
         <v>102</v>
       </c>
-      <c r="M51" s="40"/>
-      <c r="N51" s="40"/>
-      <c r="O51" s="40"/>
-      <c r="P51" s="40"/>
-      <c r="Q51" s="40"/>
-      <c r="R51" s="10"/>
-      <c r="S51" s="29"/>
+      <c r="M51" s="41"/>
+      <c r="N51" s="41"/>
+      <c r="O51" s="41"/>
+      <c r="P51" s="41"/>
+      <c r="Q51" s="41"/>
+      <c r="R51" s="11"/>
+      <c r="S51" s="30"/>
     </row>
     <row r="52" s="3" customFormat="1" ht="16.5" spans="1:22">
-      <c r="A52" s="40">
+      <c r="A52" s="41">
         <v>30220002</v>
       </c>
-      <c r="B52" s="41">
+      <c r="B52" s="42">
         <v>102200</v>
       </c>
-      <c r="C52" s="25" t="s">
+      <c r="C52" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="D52" s="44">
+      <c r="D52" s="45">
         <v>302202</v>
       </c>
-      <c r="E52" s="44" t="s">
+      <c r="E52" s="45" t="s">
         <v>103</v>
       </c>
-      <c r="F52" s="40" t="s">
+      <c r="F52" s="41" t="s">
         <v>100</v>
       </c>
-      <c r="G52" s="40">
+      <c r="G52" s="41">
         <v>2022001</v>
       </c>
-      <c r="H52" s="40" t="s">
+      <c r="H52" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="I52" s="40"/>
-      <c r="J52" s="40"/>
-      <c r="K52" s="42" t="s">
+      <c r="I52" s="41"/>
+      <c r="J52" s="41"/>
+      <c r="K52" s="43" t="s">
         <v>104</v>
       </c>
-      <c r="L52" s="40" t="s">
+      <c r="L52" s="41" t="s">
         <v>102</v>
       </c>
-      <c r="M52" s="40"/>
-      <c r="N52" s="40"/>
-      <c r="O52" s="40"/>
-      <c r="P52" s="40"/>
-      <c r="Q52" s="40"/>
-      <c r="R52" s="10"/>
-      <c r="S52" s="29"/>
+      <c r="M52" s="41"/>
+      <c r="N52" s="41"/>
+      <c r="O52" s="41"/>
+      <c r="P52" s="41"/>
+      <c r="Q52" s="41"/>
+      <c r="R52" s="11"/>
+      <c r="S52" s="30"/>
     </row>
     <row r="53" s="7" customFormat="1" ht="16.5" spans="1:22">
-      <c r="A53" s="55">
+      <c r="A53" s="56">
         <v>30210001</v>
       </c>
-      <c r="B53" s="56">
+      <c r="B53" s="57">
         <v>102100</v>
       </c>
-      <c r="C53" s="56" t="s">
+      <c r="C53" s="57" t="s">
         <v>105</v>
       </c>
-      <c r="D53" s="55">
+      <c r="D53" s="56">
         <v>302101</v>
       </c>
-      <c r="E53" s="55" t="s">
+      <c r="E53" s="56" t="s">
         <v>106</v>
       </c>
-      <c r="F53" s="55" t="s">
+      <c r="F53" s="56" t="s">
         <v>107</v>
       </c>
-      <c r="G53" s="55">
+      <c r="G53" s="56">
         <v>2021001</v>
       </c>
-      <c r="H53" s="55" t="s">
+      <c r="H53" s="56" t="s">
         <v>59</v>
       </c>
-      <c r="I53" s="55" t="s">
+      <c r="I53" s="56" t="s">
         <v>79</v>
       </c>
-      <c r="J53" s="55"/>
-      <c r="K53" s="57">
+      <c r="J53" s="56"/>
+      <c r="K53" s="58">
         <v>10210031</v>
       </c>
-      <c r="L53" s="55"/>
-      <c r="M53" s="55"/>
-      <c r="N53" s="55"/>
-      <c r="O53" s="55"/>
-      <c r="P53" s="55"/>
-      <c r="Q53" s="55"/>
-      <c r="R53" s="55"/>
-      <c r="S53" s="58"/>
+      <c r="L53" s="56"/>
+      <c r="M53" s="56"/>
+      <c r="N53" s="56"/>
+      <c r="O53" s="56"/>
+      <c r="P53" s="56"/>
+      <c r="Q53" s="56"/>
+      <c r="R53" s="56"/>
+      <c r="S53" s="59"/>
     </row>
     <row r="54" s="7" customFormat="1" ht="16.5" spans="1:22">
-      <c r="A54" s="55">
+      <c r="A54" s="56">
         <v>30210002</v>
       </c>
-      <c r="B54" s="56">
+      <c r="B54" s="57">
         <v>102100</v>
       </c>
-      <c r="C54" s="56" t="s">
+      <c r="C54" s="57" t="s">
         <v>105</v>
       </c>
-      <c r="D54" s="55">
+      <c r="D54" s="56">
         <v>302102</v>
       </c>
-      <c r="E54" s="55" t="s">
+      <c r="E54" s="56" t="s">
         <v>108</v>
       </c>
-      <c r="F54" s="55" t="s">
+      <c r="F54" s="56" t="s">
         <v>33</v>
       </c>
-      <c r="G54" s="55"/>
-      <c r="H54" s="55"/>
-      <c r="I54" s="55" t="s">
+      <c r="G54" s="56"/>
+      <c r="H54" s="56"/>
+      <c r="I54" s="56" t="s">
         <v>109</v>
       </c>
-      <c r="J54" s="55"/>
-      <c r="K54" s="57">
+      <c r="J54" s="56"/>
+      <c r="K54" s="58">
         <v>10210041</v>
       </c>
-      <c r="L54" s="55"/>
-      <c r="M54" s="55" t="s">
+      <c r="L54" s="56"/>
+      <c r="M54" s="56" t="s">
         <v>36</v>
       </c>
-      <c r="N54" s="55" t="s">
+      <c r="N54" s="56" t="s">
         <v>110</v>
       </c>
-      <c r="O54" s="55"/>
-      <c r="P54" s="55"/>
-      <c r="Q54" s="55" t="s">
+      <c r="O54" s="56"/>
+      <c r="P54" s="56"/>
+      <c r="Q54" s="56" t="s">
         <v>111</v>
       </c>
-      <c r="R54" s="55"/>
-      <c r="S54" s="58"/>
-    </row>
-    <row r="55" ht="16.5" spans="1:22">
-      <c r="A55">
+      <c r="R54" s="56"/>
+      <c r="S54" s="59"/>
+    </row>
+    <row r="55" s="8" customFormat="1" ht="16.5" spans="1:22">
+      <c r="A55" s="60">
         <v>30180001</v>
       </c>
-      <c r="B55">
+      <c r="B55" s="61">
         <v>101800</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C55" s="61" t="s">
         <v>112</v>
       </c>
-      <c r="D55">
+      <c r="D55" s="60">
         <v>301801</v>
       </c>
-      <c r="E55" t="s">
+      <c r="E55" s="60" t="s">
         <v>79</v>
       </c>
-      <c r="F55" t="s">
+      <c r="F55" s="60" t="s">
         <v>113</v>
       </c>
-      <c r="G55">
+      <c r="G55" s="60">
         <v>2018001</v>
       </c>
-      <c r="H55" s="55" t="s">
+      <c r="H55" s="60" t="s">
         <v>59</v>
       </c>
-      <c r="I55" t="s">
+      <c r="I55" s="60" t="s">
         <v>79</v>
       </c>
-      <c r="S55"/>
-      <c r="U55" s="1"/>
-      <c r="V55" s="1"/>
+      <c r="J55" s="60"/>
+      <c r="K55" s="62"/>
+      <c r="L55" s="60"/>
+      <c r="M55" s="60"/>
+      <c r="N55" s="60"/>
+      <c r="O55" s="60"/>
+      <c r="P55" s="60"/>
+      <c r="Q55" s="60"/>
+      <c r="R55" s="60"/>
+      <c r="S55" s="63"/>
     </row>
     <row r="56" ht="16.5" spans="1:22">
       <c r="S56"/>

--- a/slots/resources/sample/SpecialAuxiliary.xlsx
+++ b/slots/resources/sample/SpecialAuxiliary.xlsx
@@ -268,7 +268,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="204">
   <si>
     <t>小游戏模式ID</t>
   </si>
@@ -322,6 +322,9 @@
   </si>
   <si>
     <t>String</t>
+  </si>
+  <si>
+    <t>list&lt;list&lt;int&gt;{_}&gt;{|}</t>
   </si>
   <si>
     <t>list&lt;int&gt;{_}</t>
@@ -1055,18 +1058,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
+      <sz val="18"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1079,6 +1072,17 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1086,14 +1090,13 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2191,54 +2194,54 @@
         <v>17</v>
       </c>
       <c r="Q2" s="17" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="R2" s="15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" s="3" customFormat="1" ht="16.5" spans="1:19">
       <c r="A3" s="16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" s="19"/>
       <c r="D3" s="19" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E3" s="19"/>
       <c r="F3" s="19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G3" s="20" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H3" s="19"/>
       <c r="I3" s="19"/>
       <c r="J3" s="21" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K3" s="22" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L3" s="19"/>
       <c r="M3" s="19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N3" s="19"/>
       <c r="O3" s="14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P3" s="14" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q3" s="14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R3" s="23" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" s="3" customFormat="1" ht="16.5" spans="1:19">
@@ -2268,43 +2271,43 @@
         <v>100100</v>
       </c>
       <c r="C5" s="26" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D5" s="25">
         <v>31001</v>
       </c>
       <c r="E5" s="25" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F5" s="25" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G5" s="25"/>
       <c r="H5" s="25"/>
       <c r="I5" s="25" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J5" s="25"/>
       <c r="K5" s="27"/>
       <c r="L5" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M5" s="25" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N5" s="25" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O5" s="25"/>
       <c r="P5" s="25"/>
       <c r="Q5" s="28" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="R5" s="29" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="S5" s="30" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" s="3" customFormat="1" ht="16.5" spans="1:19">
@@ -2315,40 +2318,40 @@
         <v>100100</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D6" s="25">
         <v>31002</v>
       </c>
       <c r="E6" s="25" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F6" s="25" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G6" s="25"/>
       <c r="H6" s="25"/>
       <c r="I6" s="25" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J6" s="25"/>
       <c r="K6" s="27"/>
       <c r="L6" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M6" s="25" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N6" s="25" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O6" s="25"/>
       <c r="P6" s="25"/>
       <c r="Q6" s="28" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="R6" s="29" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="S6" s="30"/>
     </row>
@@ -2360,40 +2363,40 @@
         <v>100100</v>
       </c>
       <c r="C7" s="26" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D7" s="25">
         <v>31003</v>
       </c>
       <c r="E7" s="25" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F7" s="25" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G7" s="25"/>
       <c r="H7" s="25"/>
       <c r="I7" s="25" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J7" s="25"/>
       <c r="K7" s="27"/>
       <c r="L7" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M7" s="25" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N7" s="25" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O7" s="25"/>
       <c r="P7" s="25"/>
       <c r="Q7" s="28" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R7" s="29" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="S7" s="30"/>
     </row>
@@ -2405,40 +2408,40 @@
         <v>100100</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D8" s="25">
         <v>31004</v>
       </c>
       <c r="E8" s="25" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F8" s="25" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G8" s="25"/>
       <c r="H8" s="25"/>
       <c r="I8" s="25" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J8" s="25"/>
       <c r="K8" s="27"/>
       <c r="L8" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M8" s="25" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N8" s="25" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O8" s="25"/>
       <c r="P8" s="25"/>
       <c r="Q8" s="28" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="R8" s="29" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="S8" s="30"/>
     </row>
@@ -2450,33 +2453,33 @@
         <v>100100</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D9" s="11">
         <v>31101</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G9" s="11"/>
       <c r="H9" s="11"/>
       <c r="I9" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J9" s="11"/>
       <c r="K9" s="13"/>
       <c r="L9" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M9" s="11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N9" s="11"/>
       <c r="O9" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P9" s="11"/>
       <c r="Q9" s="14"/>
@@ -2491,35 +2494,35 @@
         <v>100100</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D10" s="31">
         <v>31102</v>
       </c>
       <c r="E10" s="31" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F10" s="31" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G10" s="31"/>
       <c r="H10" s="31"/>
       <c r="I10" s="31" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J10" s="31"/>
       <c r="K10" s="33"/>
       <c r="L10" s="31" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M10" s="31" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N10" s="31" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O10" s="31" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P10" s="31"/>
       <c r="Q10" s="31"/>
@@ -2534,25 +2537,25 @@
         <v>100100</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D11" s="36">
         <v>31201</v>
       </c>
       <c r="E11" s="36" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F11" s="34" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G11" s="34">
         <v>2001001</v>
       </c>
       <c r="H11" s="34" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I11" s="34" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J11" s="34"/>
       <c r="K11" s="37">
@@ -2575,29 +2578,29 @@
         <v>100100</v>
       </c>
       <c r="C12" s="26" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D12" s="36">
         <v>31202</v>
       </c>
       <c r="E12" s="36" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F12" s="38" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G12" s="38">
         <v>2001001</v>
       </c>
       <c r="H12" s="38" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I12" s="38" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J12" s="38"/>
       <c r="K12" s="40" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L12" s="38"/>
       <c r="M12" s="38"/>
@@ -2616,29 +2619,29 @@
         <v>100100</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D13" s="36">
         <v>31203</v>
       </c>
       <c r="E13" s="36" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F13" s="41" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G13" s="41">
         <v>2001001</v>
       </c>
       <c r="H13" s="41" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I13" s="41" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J13" s="41"/>
       <c r="K13" s="43" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="L13" s="41"/>
       <c r="M13" s="41"/>
@@ -2657,41 +2660,41 @@
         <v>100100</v>
       </c>
       <c r="C14" s="26" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D14" s="45">
         <v>31301</v>
       </c>
       <c r="E14" s="45" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F14" s="36" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G14" s="36"/>
       <c r="H14" s="36"/>
       <c r="I14" s="36" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J14" s="36"/>
       <c r="K14" s="46"/>
       <c r="L14" s="36" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M14" s="36" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N14" s="36"/>
       <c r="O14" s="36"/>
       <c r="P14" s="36"/>
       <c r="Q14" s="47" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="R14" s="48" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S14" s="14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" s="3" customFormat="1" ht="16.5" spans="1:19">
@@ -2702,29 +2705,29 @@
         <v>100100</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D15" s="45">
         <v>31302</v>
       </c>
       <c r="E15" s="45" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F15" s="41" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G15" s="41"/>
       <c r="H15" s="41"/>
       <c r="I15" s="41" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J15" s="41"/>
       <c r="K15" s="43"/>
       <c r="L15" s="41" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M15" s="41" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N15" s="41"/>
       <c r="O15" s="41"/>
@@ -2741,29 +2744,29 @@
         <v>100100</v>
       </c>
       <c r="C16" s="26" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D16" s="45">
         <v>31303</v>
       </c>
       <c r="E16" s="45" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F16" s="41" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G16" s="41">
         <v>2001001</v>
       </c>
       <c r="H16" s="41" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I16" s="41" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J16" s="41"/>
       <c r="K16" s="43" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="L16" s="41"/>
       <c r="M16" s="41"/>
@@ -2782,28 +2785,28 @@
         <v>100700</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D17" s="34">
         <v>34001</v>
       </c>
       <c r="E17" s="34" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F17" s="34" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G17" s="23">
         <v>2007001</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K17" s="49" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18" s="3" customFormat="1" ht="16.5" spans="1:11">
@@ -2814,28 +2817,28 @@
         <v>100700</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D18" s="34">
         <v>34002</v>
       </c>
       <c r="E18" s="34" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F18" s="34" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G18" s="23">
         <v>2007001</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K18" s="49" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19" s="4" customFormat="1" ht="16.5" spans="1:11">
@@ -2846,28 +2849,28 @@
         <v>101200</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D19" s="36">
         <v>32001</v>
       </c>
       <c r="E19" s="36" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F19" s="36" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G19" s="44">
         <v>2012001</v>
       </c>
       <c r="H19" s="36" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I19" s="36" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J19" s="36" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K19" s="50">
         <v>10120041</v>
@@ -2881,28 +2884,28 @@
         <v>101200</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D20" s="36">
         <v>32002</v>
       </c>
       <c r="E20" s="36" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F20" s="36" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G20" s="44">
         <v>2012001</v>
       </c>
       <c r="H20" s="36" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I20" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="J20" s="36" t="s">
         <v>86</v>
-      </c>
-      <c r="J20" s="36" t="s">
-        <v>85</v>
       </c>
       <c r="K20" s="50">
         <v>10120042</v>
@@ -2916,28 +2919,28 @@
         <v>101200</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D21" s="36">
         <v>32003</v>
       </c>
       <c r="E21" s="36" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F21" s="36" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G21" s="44">
         <v>2012001</v>
       </c>
       <c r="H21" s="36" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I21" s="36" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J21" s="36" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K21" s="50">
         <v>10120043</v>
@@ -2951,28 +2954,28 @@
         <v>101200</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D22" s="36">
         <v>32004</v>
       </c>
       <c r="E22" s="36" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F22" s="36" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G22" s="44">
         <v>2012001</v>
       </c>
       <c r="H22" s="36" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I22" s="36" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J22" s="36" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K22" s="50">
         <v>10120044</v>
@@ -2986,28 +2989,28 @@
         <v>101200</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D23" s="36">
         <v>32005</v>
       </c>
       <c r="E23" s="36" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F23" s="36" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G23" s="44">
         <v>2012001</v>
       </c>
       <c r="H23" s="36" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I23" s="36" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J23" s="36" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K23" s="50">
         <v>10120045</v>
@@ -3021,28 +3024,28 @@
         <v>101200</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D24" s="36">
         <v>32006</v>
       </c>
       <c r="E24" s="36" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F24" s="36" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G24" s="44">
         <v>2012001</v>
       </c>
       <c r="H24" s="36" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I24" s="36" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J24" s="36" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K24" s="50">
         <v>10120046</v>
@@ -3056,28 +3059,28 @@
         <v>101200</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D25" s="36">
         <v>32101</v>
       </c>
       <c r="E25" s="51" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F25" s="51" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G25" s="52">
         <v>2012001</v>
       </c>
       <c r="H25" s="51" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I25" s="51" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J25" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K25" s="53">
         <v>10120041</v>
@@ -3091,28 +3094,28 @@
         <v>101200</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D26" s="36">
         <v>32102</v>
       </c>
       <c r="E26" s="51" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F26" s="51" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G26" s="52">
         <v>2012001</v>
       </c>
       <c r="H26" s="51" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I26" s="51" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J26" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K26" s="53">
         <v>10120042</v>
@@ -3126,28 +3129,28 @@
         <v>101200</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D27" s="36">
         <v>32103</v>
       </c>
       <c r="E27" s="51" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F27" s="51" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G27" s="52">
         <v>2012001</v>
       </c>
       <c r="H27" s="51" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I27" s="51" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J27" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K27" s="53">
         <v>10120043</v>
@@ -3161,28 +3164,28 @@
         <v>101200</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D28" s="36">
         <v>32104</v>
       </c>
       <c r="E28" s="51" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F28" s="51" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G28" s="52">
         <v>2012001</v>
       </c>
       <c r="H28" s="51" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I28" s="51" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J28" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K28" s="53">
         <v>10120044</v>
@@ -3196,28 +3199,28 @@
         <v>101200</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D29" s="36">
         <v>32105</v>
       </c>
       <c r="E29" s="51" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F29" s="51" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G29" s="52">
         <v>2012001</v>
       </c>
       <c r="H29" s="51" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I29" s="51" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J29" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K29" s="53">
         <v>10120045</v>
@@ -3231,28 +3234,28 @@
         <v>101200</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D30" s="36">
         <v>32106</v>
       </c>
       <c r="E30" s="51" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F30" s="51" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G30" s="52">
         <v>2012001</v>
       </c>
       <c r="H30" s="51" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I30" s="51" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J30" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K30" s="53">
         <v>10120046</v>
@@ -3266,25 +3269,25 @@
         <v>101200</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D31" s="45">
         <v>32201</v>
       </c>
       <c r="E31" s="45" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F31" s="45" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G31" s="54">
         <v>2012001</v>
       </c>
       <c r="H31" s="45" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I31" s="45" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J31" s="45"/>
       <c r="K31" s="55">
@@ -3299,25 +3302,25 @@
         <v>101200</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D32" s="45">
         <v>32202</v>
       </c>
       <c r="E32" s="45" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F32" s="45" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G32" s="54">
         <v>2012001</v>
       </c>
       <c r="H32" s="45" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I32" s="45" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J32" s="45"/>
       <c r="K32" s="55">
@@ -3332,25 +3335,25 @@
         <v>101200</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D33" s="45">
         <v>32203</v>
       </c>
       <c r="E33" s="45" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F33" s="45" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G33" s="54">
         <v>2012001</v>
       </c>
       <c r="H33" s="45" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I33" s="45" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J33" s="45"/>
       <c r="K33" s="55">
@@ -3365,25 +3368,25 @@
         <v>101200</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D34" s="45">
         <v>32204</v>
       </c>
       <c r="E34" s="45" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F34" s="45" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G34" s="54">
         <v>2012001</v>
       </c>
       <c r="H34" s="45" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I34" s="45" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J34" s="45"/>
       <c r="K34" s="55">
@@ -3398,25 +3401,25 @@
         <v>101200</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D35" s="45">
         <v>32205</v>
       </c>
       <c r="E35" s="45" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F35" s="45" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G35" s="54">
         <v>2012001</v>
       </c>
       <c r="H35" s="45" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I35" s="45" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J35" s="45"/>
       <c r="K35" s="55">
@@ -3431,25 +3434,25 @@
         <v>101200</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D36" s="45">
         <v>32206</v>
       </c>
       <c r="E36" s="45" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F36" s="45" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G36" s="54">
         <v>2012001</v>
       </c>
       <c r="H36" s="45" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I36" s="45" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J36" s="45"/>
       <c r="K36" s="55">
@@ -3464,43 +3467,43 @@
         <v>102400</v>
       </c>
       <c r="C37" s="26" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D37" s="25">
         <v>32401</v>
       </c>
       <c r="E37" s="25" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F37" s="25" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G37" s="25"/>
       <c r="H37" s="25"/>
       <c r="I37" s="25" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J37" s="25"/>
       <c r="K37" s="27"/>
       <c r="L37" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M37" s="25" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N37" s="25" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O37" s="25"/>
       <c r="P37" s="25"/>
       <c r="Q37" s="28" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="R37" s="29" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="S37" s="30" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="38" s="3" customFormat="1" ht="16.5" spans="1:19">
@@ -3511,40 +3514,40 @@
         <v>102400</v>
       </c>
       <c r="C38" s="26" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D38" s="25">
         <v>32402</v>
       </c>
       <c r="E38" s="25" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F38" s="25" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G38" s="25"/>
       <c r="H38" s="25"/>
       <c r="I38" s="25" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J38" s="25"/>
       <c r="K38" s="27"/>
       <c r="L38" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M38" s="25" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N38" s="25" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O38" s="25"/>
       <c r="P38" s="25"/>
       <c r="Q38" s="28" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="R38" s="29" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="S38" s="30"/>
     </row>
@@ -3556,40 +3559,40 @@
         <v>102400</v>
       </c>
       <c r="C39" s="26" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D39" s="25">
         <v>32403</v>
       </c>
       <c r="E39" s="25" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F39" s="25" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G39" s="25"/>
       <c r="H39" s="25"/>
       <c r="I39" s="25" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J39" s="25"/>
       <c r="K39" s="27"/>
       <c r="L39" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M39" s="25" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N39" s="25" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O39" s="25"/>
       <c r="P39" s="25"/>
       <c r="Q39" s="28" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R39" s="29" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="S39" s="30"/>
     </row>
@@ -3601,40 +3604,40 @@
         <v>102400</v>
       </c>
       <c r="C40" s="26" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D40" s="25">
         <v>32404</v>
       </c>
       <c r="E40" s="25" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F40" s="25" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G40" s="25"/>
       <c r="H40" s="25"/>
       <c r="I40" s="25" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J40" s="25"/>
       <c r="K40" s="27"/>
       <c r="L40" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M40" s="25" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N40" s="25" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O40" s="25"/>
       <c r="P40" s="25"/>
       <c r="Q40" s="28" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="R40" s="29" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="S40" s="30"/>
     </row>
@@ -3646,33 +3649,33 @@
         <v>102400</v>
       </c>
       <c r="C41" s="26" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D41" s="11">
         <v>32411</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G41" s="11"/>
       <c r="H41" s="11"/>
       <c r="I41" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J41" s="11"/>
       <c r="K41" s="13"/>
       <c r="L41" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M41" s="11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N41" s="11"/>
       <c r="O41" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P41" s="11"/>
       <c r="Q41" s="14"/>
@@ -3687,35 +3690,35 @@
         <v>102400</v>
       </c>
       <c r="C42" s="26" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D42" s="31">
         <v>32421</v>
       </c>
       <c r="E42" s="31" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F42" s="31" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G42" s="31"/>
       <c r="H42" s="31"/>
       <c r="I42" s="31" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J42" s="31"/>
       <c r="K42" s="33"/>
       <c r="L42" s="31" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M42" s="31" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N42" s="31" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O42" s="31" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P42" s="31"/>
       <c r="Q42" s="31"/>
@@ -3730,25 +3733,25 @@
         <v>102400</v>
       </c>
       <c r="C43" s="26" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D43" s="36">
         <v>32431</v>
       </c>
       <c r="E43" s="36" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F43" s="34" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G43" s="34">
         <v>2024001</v>
       </c>
       <c r="H43" s="34" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I43" s="34" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J43" s="34"/>
       <c r="K43" s="37">
@@ -3771,29 +3774,29 @@
         <v>102400</v>
       </c>
       <c r="C44" s="26" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D44" s="36">
         <v>32432</v>
       </c>
       <c r="E44" s="36" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F44" s="38" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G44" s="38">
         <v>2024001</v>
       </c>
       <c r="H44" s="38" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I44" s="38" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J44" s="38"/>
       <c r="K44" s="40" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L44" s="38"/>
       <c r="M44" s="38"/>
@@ -3812,29 +3815,29 @@
         <v>102400</v>
       </c>
       <c r="C45" s="26" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D45" s="36">
         <v>32433</v>
       </c>
       <c r="E45" s="36" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F45" s="41" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G45" s="41">
         <v>2024001</v>
       </c>
       <c r="H45" s="41" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I45" s="41" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J45" s="41"/>
       <c r="K45" s="43" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L45" s="41"/>
       <c r="M45" s="41"/>
@@ -3853,41 +3856,41 @@
         <v>102400</v>
       </c>
       <c r="C46" s="26" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D46" s="45">
         <v>32441</v>
       </c>
       <c r="E46" s="45" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F46" s="36" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G46" s="36"/>
       <c r="H46" s="36"/>
       <c r="I46" s="36" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J46" s="36"/>
       <c r="K46" s="46"/>
       <c r="L46" s="36" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M46" s="36" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N46" s="36"/>
       <c r="O46" s="36"/>
       <c r="P46" s="36"/>
       <c r="Q46" s="47" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="R46" s="48" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S46" s="14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="47" s="3" customFormat="1" ht="16.5" spans="1:19">
@@ -3898,29 +3901,29 @@
         <v>102400</v>
       </c>
       <c r="C47" s="26" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D47" s="45">
         <v>32442</v>
       </c>
       <c r="E47" s="45" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F47" s="41" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G47" s="41"/>
       <c r="H47" s="41"/>
       <c r="I47" s="41" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J47" s="41"/>
       <c r="K47" s="43"/>
       <c r="L47" s="41" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M47" s="41" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N47" s="41"/>
       <c r="O47" s="41"/>
@@ -3937,29 +3940,29 @@
         <v>102400</v>
       </c>
       <c r="C48" s="26" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D48" s="45">
         <v>32443</v>
       </c>
       <c r="E48" s="45" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F48" s="41" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G48" s="41">
         <v>2024001</v>
       </c>
       <c r="H48" s="41" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I48" s="41" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J48" s="41"/>
       <c r="K48" s="43" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L48" s="41"/>
       <c r="M48" s="41"/>
@@ -3978,29 +3981,29 @@
         <v>101700</v>
       </c>
       <c r="C49" s="26" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D49" s="45">
         <v>301701</v>
       </c>
       <c r="E49" s="45" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F49" s="41" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G49" s="41">
         <v>2017001</v>
       </c>
       <c r="H49" s="41" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I49" s="41" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J49" s="41"/>
       <c r="K49" s="43" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L49" s="41"/>
       <c r="M49" s="41"/>
@@ -4019,29 +4022,29 @@
         <v>101700</v>
       </c>
       <c r="C50" s="26" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D50" s="45">
         <v>301702</v>
       </c>
       <c r="E50" s="45" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F50" s="41" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G50" s="41">
         <v>2017001</v>
       </c>
       <c r="H50" s="41" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I50" s="41" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J50" s="41"/>
       <c r="K50" s="43" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L50" s="41"/>
       <c r="M50" s="41"/>
@@ -4060,30 +4063,30 @@
         <v>102200</v>
       </c>
       <c r="C51" s="26" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D51" s="45">
         <v>302201</v>
       </c>
       <c r="E51" s="45" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F51" s="41" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G51" s="41">
         <v>2022001</v>
       </c>
       <c r="H51" s="41" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I51" s="41"/>
       <c r="J51" s="41"/>
       <c r="K51" s="43" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L51" s="41" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M51" s="41"/>
       <c r="N51" s="41"/>
@@ -4101,30 +4104,30 @@
         <v>102200</v>
       </c>
       <c r="C52" s="26" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D52" s="45">
         <v>302202</v>
       </c>
       <c r="E52" s="45" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F52" s="41" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G52" s="41">
         <v>2022001</v>
       </c>
       <c r="H52" s="41" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I52" s="41"/>
       <c r="J52" s="41"/>
       <c r="K52" s="43" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L52" s="41" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M52" s="41"/>
       <c r="N52" s="41"/>
@@ -4142,29 +4145,29 @@
         <v>102100</v>
       </c>
       <c r="C53" s="57" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D53" s="56">
         <v>302101</v>
       </c>
       <c r="E53" s="56" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F53" s="56" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G53" s="56">
         <v>2021001</v>
       </c>
       <c r="H53" s="56" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I53" s="56" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J53" s="56"/>
       <c r="K53" s="58">
-        <v>10210031</v>
+        <v>10210042</v>
       </c>
       <c r="L53" s="56"/>
       <c r="M53" s="56"/>
@@ -4183,37 +4186,35 @@
         <v>102100</v>
       </c>
       <c r="C54" s="57" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D54" s="56">
         <v>302102</v>
       </c>
       <c r="E54" s="56" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F54" s="56" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G54" s="56"/>
       <c r="H54" s="56"/>
       <c r="I54" s="56" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J54" s="56"/>
-      <c r="K54" s="58">
-        <v>10210041</v>
-      </c>
+      <c r="K54" s="58"/>
       <c r="L54" s="56"/>
       <c r="M54" s="56" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N54" s="56" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O54" s="56"/>
       <c r="P54" s="56"/>
       <c r="Q54" s="56" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="R54" s="56"/>
       <c r="S54" s="59"/>
@@ -4226,28 +4227,30 @@
         <v>101800</v>
       </c>
       <c r="C55" s="61" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D55" s="60">
         <v>301801</v>
       </c>
       <c r="E55" s="60" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F55" s="60" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G55" s="60">
         <v>2018001</v>
       </c>
       <c r="H55" s="60" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I55" s="60" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J55" s="60"/>
-      <c r="K55" s="62"/>
+      <c r="K55" s="62">
+        <v>10180041</v>
+      </c>
       <c r="L55" s="60"/>
       <c r="M55" s="60"/>
       <c r="N55" s="60"/>
@@ -4327,10 +4330,10 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -4338,7 +4341,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -4346,7 +4349,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:8">
@@ -4354,16 +4357,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:8">
@@ -4371,16 +4374,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:8">
@@ -4388,16 +4391,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:8">
@@ -4405,16 +4408,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F7" s="1">
         <v>2</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:8">
@@ -4422,16 +4425,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F8" s="1">
         <v>3</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:8">
@@ -4439,16 +4442,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F9" s="1">
         <v>4</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:8">
@@ -4456,16 +4459,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F10" s="1">
         <v>5</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:8">
@@ -4473,16 +4476,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F11" s="1">
         <v>6</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:8">
@@ -4490,16 +4493,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F12" s="1">
         <v>7</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:8">
@@ -4507,16 +4510,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F13" s="1">
         <v>8</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:8">
@@ -4524,16 +4527,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F14" s="1">
         <v>9</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:8">
@@ -4541,16 +4544,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F15" s="1">
         <v>10</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:8">
@@ -4558,16 +4561,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F16" s="1">
         <v>11</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:8">
@@ -4575,16 +4578,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F17" s="1">
         <v>12</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:8">
@@ -4592,16 +4595,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F18" s="1">
         <v>13</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:8">
@@ -4609,16 +4612,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F19" s="1">
         <v>14</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:8">
@@ -4626,16 +4629,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F20" s="1">
         <v>15</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:8">
@@ -4643,16 +4646,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F21" s="1">
         <v>16</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:8">
@@ -4660,16 +4663,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F22" s="1">
         <v>17</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:8">
@@ -4677,16 +4680,16 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F23" s="1">
         <v>18</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:8">
@@ -4694,16 +4697,16 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F24" s="1">
         <v>19</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -4711,7 +4714,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -4719,7 +4722,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -4727,7 +4730,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -4735,7 +4738,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -4743,7 +4746,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -4751,7 +4754,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -4759,7 +4762,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -4767,7 +4770,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -4775,7 +4778,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -4783,7 +4786,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -4791,7 +4794,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -4799,7 +4802,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -4807,7 +4810,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -4815,7 +4818,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -4823,7 +4826,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -4831,7 +4834,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -4839,7 +4842,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -4847,7 +4850,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -4855,7 +4858,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -4863,7 +4866,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -4871,7 +4874,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -4879,7 +4882,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -4887,7 +4890,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialAuxiliary.xlsx
+++ b/slots/resources/sample/SpecialAuxiliary.xlsx
@@ -268,7 +268,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="206">
   <si>
     <t>小游戏模式ID</t>
   </si>
@@ -595,6 +595,12 @@
   </si>
   <si>
     <t>10_1</t>
+  </si>
+  <si>
+    <t>10210042|10210032</t>
+  </si>
+  <si>
+    <t>概率改出wild和scatter</t>
   </si>
   <si>
     <t>探宝玩法</t>
@@ -1059,25 +1065,17 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1096,7 +1094,15 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -4166,10 +4172,12 @@
         <v>80</v>
       </c>
       <c r="J53" s="56"/>
-      <c r="K53" s="58">
-        <v>10210042</v>
-      </c>
-      <c r="L53" s="56"/>
+      <c r="K53" s="58" t="s">
+        <v>109</v>
+      </c>
+      <c r="L53" s="56" t="s">
+        <v>110</v>
+      </c>
       <c r="M53" s="56"/>
       <c r="N53" s="56"/>
       <c r="O53" s="56"/>
@@ -4192,7 +4200,7 @@
         <v>302102</v>
       </c>
       <c r="E54" s="56" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F54" s="56" t="s">
         <v>34</v>
@@ -4200,7 +4208,7 @@
       <c r="G54" s="56"/>
       <c r="H54" s="56"/>
       <c r="I54" s="56" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="J54" s="56"/>
       <c r="K54" s="58"/>
@@ -4209,12 +4217,12 @@
         <v>37</v>
       </c>
       <c r="N54" s="56" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="O54" s="56"/>
       <c r="P54" s="56"/>
       <c r="Q54" s="56" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="R54" s="56"/>
       <c r="S54" s="59"/>
@@ -4227,7 +4235,7 @@
         <v>101800</v>
       </c>
       <c r="C55" s="61" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D55" s="60">
         <v>301801</v>
@@ -4236,7 +4244,7 @@
         <v>80</v>
       </c>
       <c r="F55" s="60" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G55" s="60">
         <v>2018001</v>
@@ -4330,10 +4338,10 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -4341,7 +4349,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -4349,7 +4357,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:8">
@@ -4357,16 +4365,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:8">
@@ -4374,16 +4382,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:8">
@@ -4391,16 +4399,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:8">
@@ -4408,16 +4416,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F7" s="1">
         <v>2</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:8">
@@ -4425,16 +4433,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F8" s="1">
         <v>3</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:8">
@@ -4442,16 +4450,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F9" s="1">
         <v>4</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:8">
@@ -4459,16 +4467,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F10" s="1">
         <v>5</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:8">
@@ -4476,16 +4484,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F11" s="1">
         <v>6</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:8">
@@ -4493,16 +4501,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F12" s="1">
         <v>7</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:8">
@@ -4510,16 +4518,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F13" s="1">
         <v>8</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:8">
@@ -4527,16 +4535,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F14" s="1">
         <v>9</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:8">
@@ -4544,16 +4552,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F15" s="1">
         <v>10</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:8">
@@ -4561,16 +4569,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F16" s="1">
         <v>11</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:8">
@@ -4578,16 +4586,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F17" s="1">
         <v>12</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:8">
@@ -4595,16 +4603,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F18" s="1">
         <v>13</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:8">
@@ -4612,16 +4620,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F19" s="1">
         <v>14</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:8">
@@ -4629,16 +4637,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F20" s="1">
         <v>15</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:8">
@@ -4646,16 +4654,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F21" s="1">
         <v>16</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:8">
@@ -4663,16 +4671,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F22" s="1">
         <v>17</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:8">
@@ -4680,16 +4688,16 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F23" s="1">
         <v>18</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:8">
@@ -4697,16 +4705,16 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F24" s="1">
         <v>19</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -4714,7 +4722,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -4722,7 +4730,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -4730,7 +4738,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -4738,7 +4746,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -4746,7 +4754,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -4754,7 +4762,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -4762,7 +4770,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -4770,7 +4778,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -4778,7 +4786,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -4786,7 +4794,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -4794,7 +4802,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -4802,7 +4810,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -4810,7 +4818,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -4818,7 +4826,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -4826,7 +4834,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -4834,7 +4842,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -4842,7 +4850,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -4850,7 +4858,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -4858,7 +4866,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -4866,7 +4874,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -4874,7 +4882,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -4882,7 +4890,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -4890,7 +4898,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialAuxiliary.xlsx
+++ b/slots/resources/sample/SpecialAuxiliary.xlsx
@@ -268,7 +268,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="211">
   <si>
     <t>小游戏模式ID</t>
   </si>
@@ -619,6 +619,21 @@
   </si>
   <si>
     <t>7_1</t>
+  </si>
+  <si>
+    <t>寒冰王座</t>
+  </si>
+  <si>
+    <t>免费游戏-免费旋转-15次</t>
+  </si>
+  <si>
+    <t>15_1</t>
+  </si>
+  <si>
+    <t>免费游戏-免费旋转-20次</t>
+  </si>
+  <si>
+    <t>20_1</t>
   </si>
   <si>
     <t>typeID</t>
@@ -899,7 +914,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -916,6 +931,17 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -1070,13 +1096,13 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1088,7 +1114,7 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1108,7 +1134,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="44">
+  <fills count="50">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1135,6 +1161,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.25"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1142,6 +1186,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1178,6 +1228,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.25"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1492,73 +1554,55 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1567,65 +1611,83 @@
     <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1637,12 +1699,16 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1663,7 +1729,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1672,7 +1738,118 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="1" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="1" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="1" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
@@ -1680,11 +1857,7 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="176" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
@@ -1692,74 +1865,15 @@
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="3" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="52">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2091,7 +2205,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:V57"/>
+  <dimension ref="A1:S58"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14.125" customWidth="1"/>
@@ -2103,7 +2217,7 @@
     <col min="8" max="8" width="16.25" customWidth="1"/>
     <col min="9" max="9" width="29.375" customWidth="1"/>
     <col min="10" max="10" width="42.5" customWidth="1"/>
-    <col min="11" max="11" width="41.25" style="9" customWidth="1"/>
+    <col min="11" max="11" width="41.25" style="13" customWidth="1"/>
     <col min="12" max="12" width="11.75" style="3" customWidth="1"/>
     <col min="13" max="13" width="34.4083333333333" style="3" customWidth="1"/>
     <col min="14" max="14" width="7.93333333333333" style="3" customWidth="1"/>
@@ -2111,7 +2225,7 @@
     <col min="16" max="16" width="8.96666666666667" customWidth="1"/>
     <col min="17" max="17" width="93.375" customWidth="1"/>
     <col min="18" max="18" width="10.625" customWidth="1"/>
-    <col min="19" max="19" width="23.75" style="10" customWidth="1"/>
+    <col min="19" max="19" width="23.75" style="14" customWidth="1"/>
     <col min="20" max="20" width="60.875" customWidth="1"/>
     <col min="21" max="22" width="11.5"/>
   </cols>
@@ -2120,671 +2234,671 @@
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11" t="s">
+      <c r="C1" s="15"/>
+      <c r="D1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11" t="s">
+      <c r="E1" s="15"/>
+      <c r="F1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11" t="s">
+      <c r="H1" s="15"/>
+      <c r="I1" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="13" t="s">
+      <c r="K1" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11" t="s">
+      <c r="L1" s="15"/>
+      <c r="M1" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="11"/>
-      <c r="O1" s="14" t="s">
+      <c r="N1" s="15"/>
+      <c r="O1" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="14" t="s">
+      <c r="P1" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="Q1" s="14" t="s">
+      <c r="Q1" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="R1" s="15" t="s">
+      <c r="R1" s="19" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="2" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11" t="s">
+      <c r="C2" s="15"/>
+      <c r="D2" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="11"/>
-      <c r="F2" s="14" t="s">
+      <c r="E2" s="15"/>
+      <c r="F2" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G2" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="17" t="s">
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="18" t="s">
+      <c r="K2" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="L2" s="14"/>
-      <c r="M2" s="17" t="s">
+      <c r="L2" s="18"/>
+      <c r="M2" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="N2" s="11"/>
-      <c r="O2" s="14" t="s">
+      <c r="N2" s="15"/>
+      <c r="O2" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="P2" s="14" t="s">
+      <c r="P2" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="Q2" s="17" t="s">
+      <c r="Q2" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="R2" s="15" t="s">
+      <c r="R2" s="19" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="3" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19" t="s">
+      <c r="C3" s="23"/>
+      <c r="D3" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="19"/>
-      <c r="F3" s="19" t="s">
+      <c r="E3" s="23"/>
+      <c r="F3" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="20" t="s">
+      <c r="G3" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="19"/>
-      <c r="I3" s="19"/>
-      <c r="J3" s="21" t="s">
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="22" t="s">
+      <c r="K3" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="L3" s="19"/>
-      <c r="M3" s="19" t="s">
+      <c r="L3" s="23"/>
+      <c r="M3" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="N3" s="19"/>
-      <c r="O3" s="14" t="s">
+      <c r="N3" s="23"/>
+      <c r="O3" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="P3" s="14" t="s">
+      <c r="P3" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="Q3" s="14" t="s">
+      <c r="Q3" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="R3" s="23" t="s">
+      <c r="R3" s="27" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="4" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="11"/>
-      <c r="J4" s="24"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
-      <c r="N4" s="11"/>
-      <c r="O4" s="11"/>
-      <c r="P4" s="11"/>
-      <c r="Q4" s="11"/>
-      <c r="R4" s="11"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="28"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="15"/>
+      <c r="O4" s="15"/>
+      <c r="P4" s="15"/>
+      <c r="Q4" s="15"/>
+      <c r="R4" s="15"/>
     </row>
     <row r="5" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A5" s="25">
+      <c r="A5" s="29">
         <v>30010001</v>
       </c>
-      <c r="B5" s="26">
+      <c r="B5" s="30">
         <v>100100</v>
       </c>
-      <c r="C5" s="26" t="s">
+      <c r="C5" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="29">
         <v>31001</v>
       </c>
-      <c r="E5" s="25" t="s">
+      <c r="E5" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="25" t="s">
+      <c r="F5" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="G5" s="25"/>
-      <c r="H5" s="25"/>
-      <c r="I5" s="25" t="s">
+      <c r="G5" s="29"/>
+      <c r="H5" s="29"/>
+      <c r="I5" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="J5" s="25"/>
-      <c r="K5" s="27"/>
-      <c r="L5" s="11" t="s">
+      <c r="J5" s="29"/>
+      <c r="K5" s="31"/>
+      <c r="L5" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="M5" s="25" t="s">
+      <c r="M5" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="N5" s="25" t="s">
+      <c r="N5" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="O5" s="25"/>
-      <c r="P5" s="25"/>
-      <c r="Q5" s="28" t="s">
+      <c r="O5" s="29"/>
+      <c r="P5" s="29"/>
+      <c r="Q5" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="R5" s="29" t="s">
+      <c r="R5" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="S5" s="30" t="s">
+      <c r="S5" s="34" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="6" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A6" s="25">
+      <c r="A6" s="29">
         <v>30010002</v>
       </c>
-      <c r="B6" s="26">
+      <c r="B6" s="30">
         <v>100100</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="29">
         <v>31002</v>
       </c>
-      <c r="E6" s="25" t="s">
+      <c r="E6" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="F6" s="25" t="s">
+      <c r="F6" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="G6" s="25"/>
-      <c r="H6" s="25"/>
-      <c r="I6" s="25" t="s">
+      <c r="G6" s="29"/>
+      <c r="H6" s="29"/>
+      <c r="I6" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="J6" s="25"/>
-      <c r="K6" s="27"/>
-      <c r="L6" s="11" t="s">
+      <c r="J6" s="29"/>
+      <c r="K6" s="31"/>
+      <c r="L6" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="M6" s="25" t="s">
+      <c r="M6" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="N6" s="25" t="s">
+      <c r="N6" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="O6" s="25"/>
-      <c r="P6" s="25"/>
-      <c r="Q6" s="28" t="s">
+      <c r="O6" s="29"/>
+      <c r="P6" s="29"/>
+      <c r="Q6" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="R6" s="29" t="s">
+      <c r="R6" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="S6" s="30"/>
+      <c r="S6" s="34"/>
     </row>
     <row r="7" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A7" s="25">
+      <c r="A7" s="29">
         <v>30010003</v>
       </c>
-      <c r="B7" s="26">
+      <c r="B7" s="30">
         <v>100100</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="C7" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="29">
         <v>31003</v>
       </c>
-      <c r="E7" s="25" t="s">
+      <c r="E7" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="25" t="s">
+      <c r="F7" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="G7" s="25"/>
-      <c r="H7" s="25"/>
-      <c r="I7" s="25" t="s">
+      <c r="G7" s="29"/>
+      <c r="H7" s="29"/>
+      <c r="I7" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="J7" s="25"/>
-      <c r="K7" s="27"/>
-      <c r="L7" s="11" t="s">
+      <c r="J7" s="29"/>
+      <c r="K7" s="31"/>
+      <c r="L7" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="M7" s="25" t="s">
+      <c r="M7" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="N7" s="25" t="s">
+      <c r="N7" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="O7" s="25"/>
-      <c r="P7" s="25"/>
-      <c r="Q7" s="28" t="s">
+      <c r="O7" s="29"/>
+      <c r="P7" s="29"/>
+      <c r="Q7" s="32" t="s">
         <v>47</v>
       </c>
-      <c r="R7" s="29" t="s">
+      <c r="R7" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="S7" s="30"/>
+      <c r="S7" s="34"/>
     </row>
     <row r="8" s="3" customFormat="1" ht="15" customHeight="1" spans="1:19">
-      <c r="A8" s="25">
+      <c r="A8" s="29">
         <v>30010004</v>
       </c>
-      <c r="B8" s="26">
+      <c r="B8" s="30">
         <v>100100</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="29">
         <v>31004</v>
       </c>
-      <c r="E8" s="25" t="s">
+      <c r="E8" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="F8" s="25" t="s">
+      <c r="F8" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="G8" s="25"/>
-      <c r="H8" s="25"/>
-      <c r="I8" s="25" t="s">
+      <c r="G8" s="29"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="J8" s="25"/>
-      <c r="K8" s="27"/>
-      <c r="L8" s="11" t="s">
+      <c r="J8" s="29"/>
+      <c r="K8" s="31"/>
+      <c r="L8" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="M8" s="25" t="s">
+      <c r="M8" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="N8" s="25" t="s">
+      <c r="N8" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="O8" s="25"/>
-      <c r="P8" s="25"/>
-      <c r="Q8" s="28" t="s">
+      <c r="O8" s="29"/>
+      <c r="P8" s="29"/>
+      <c r="Q8" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="R8" s="29" t="s">
+      <c r="R8" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="S8" s="30"/>
+      <c r="S8" s="34"/>
     </row>
     <row r="9" s="3" customFormat="1" ht="15" customHeight="1" spans="1:19">
-      <c r="A9" s="11">
+      <c r="A9" s="15">
         <v>30010005</v>
       </c>
-      <c r="B9" s="23">
+      <c r="B9" s="27">
         <v>100100</v>
       </c>
-      <c r="C9" s="26" t="s">
+      <c r="C9" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="15">
         <v>31101</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="E9" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="F9" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11" t="s">
+      <c r="G9" s="15"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="J9" s="11"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="11" t="s">
+      <c r="J9" s="15"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="M9" s="11" t="s">
+      <c r="M9" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="N9" s="11"/>
-      <c r="O9" s="11" t="s">
+      <c r="N9" s="15"/>
+      <c r="O9" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="14"/>
-      <c r="R9" s="14"/>
-      <c r="S9" s="30"/>
+      <c r="P9" s="15"/>
+      <c r="Q9" s="18"/>
+      <c r="R9" s="18"/>
+      <c r="S9" s="34"/>
     </row>
     <row r="10" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A10" s="31">
+      <c r="A10" s="35">
         <v>30010006</v>
       </c>
-      <c r="B10" s="32">
+      <c r="B10" s="36">
         <v>100100</v>
       </c>
-      <c r="C10" s="26" t="s">
+      <c r="C10" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="D10" s="31">
+      <c r="D10" s="35">
         <v>31102</v>
       </c>
-      <c r="E10" s="31" t="s">
+      <c r="E10" s="35" t="s">
         <v>55</v>
       </c>
-      <c r="F10" s="31" t="s">
+      <c r="F10" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="G10" s="31"/>
-      <c r="H10" s="31"/>
-      <c r="I10" s="31" t="s">
+      <c r="G10" s="35"/>
+      <c r="H10" s="35"/>
+      <c r="I10" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="J10" s="31"/>
-      <c r="K10" s="33"/>
-      <c r="L10" s="31" t="s">
+      <c r="J10" s="35"/>
+      <c r="K10" s="37"/>
+      <c r="L10" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="M10" s="31" t="s">
+      <c r="M10" s="35" t="s">
         <v>57</v>
       </c>
-      <c r="N10" s="31" t="s">
+      <c r="N10" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="O10" s="31" t="s">
+      <c r="O10" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="P10" s="31"/>
-      <c r="Q10" s="31"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="30"/>
+      <c r="P10" s="35"/>
+      <c r="Q10" s="35"/>
+      <c r="R10" s="15"/>
+      <c r="S10" s="34"/>
     </row>
     <row r="11" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A11" s="34">
+      <c r="A11" s="38">
         <v>30010007</v>
       </c>
-      <c r="B11" s="35">
+      <c r="B11" s="39">
         <v>100100</v>
       </c>
-      <c r="C11" s="26" t="s">
+      <c r="C11" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="36">
+      <c r="D11" s="40">
         <v>31201</v>
       </c>
-      <c r="E11" s="36" t="s">
+      <c r="E11" s="40" t="s">
         <v>58</v>
       </c>
-      <c r="F11" s="34" t="s">
+      <c r="F11" s="38" t="s">
         <v>59</v>
       </c>
-      <c r="G11" s="34">
+      <c r="G11" s="38">
         <v>2001001</v>
       </c>
-      <c r="H11" s="34" t="s">
+      <c r="H11" s="38" t="s">
         <v>60</v>
       </c>
-      <c r="I11" s="34" t="s">
+      <c r="I11" s="38" t="s">
         <v>61</v>
       </c>
-      <c r="J11" s="34"/>
-      <c r="K11" s="37">
+      <c r="J11" s="38"/>
+      <c r="K11" s="41">
         <v>10010091</v>
       </c>
-      <c r="L11" s="34"/>
-      <c r="M11" s="34"/>
-      <c r="N11" s="34"/>
-      <c r="O11" s="34"/>
-      <c r="P11" s="34"/>
-      <c r="Q11" s="34"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="30"/>
+      <c r="L11" s="38"/>
+      <c r="M11" s="38"/>
+      <c r="N11" s="38"/>
+      <c r="O11" s="38"/>
+      <c r="P11" s="38"/>
+      <c r="Q11" s="38"/>
+      <c r="R11" s="15"/>
+      <c r="S11" s="34"/>
     </row>
     <row r="12" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A12" s="38">
+      <c r="A12" s="42">
         <v>30010008</v>
       </c>
-      <c r="B12" s="39">
+      <c r="B12" s="43">
         <v>100100</v>
       </c>
-      <c r="C12" s="26" t="s">
+      <c r="C12" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="36">
+      <c r="D12" s="40">
         <v>31202</v>
       </c>
-      <c r="E12" s="36" t="s">
+      <c r="E12" s="40" t="s">
         <v>62</v>
       </c>
-      <c r="F12" s="38" t="s">
+      <c r="F12" s="42" t="s">
         <v>53</v>
       </c>
-      <c r="G12" s="38">
+      <c r="G12" s="42">
         <v>2001001</v>
       </c>
-      <c r="H12" s="38" t="s">
+      <c r="H12" s="42" t="s">
         <v>60</v>
       </c>
-      <c r="I12" s="38" t="s">
+      <c r="I12" s="42" t="s">
         <v>63</v>
       </c>
-      <c r="J12" s="38"/>
-      <c r="K12" s="40" t="s">
+      <c r="J12" s="42"/>
+      <c r="K12" s="44" t="s">
         <v>64</v>
       </c>
-      <c r="L12" s="38"/>
-      <c r="M12" s="38"/>
-      <c r="N12" s="38"/>
-      <c r="O12" s="38"/>
-      <c r="P12" s="38"/>
-      <c r="Q12" s="38"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="30"/>
+      <c r="L12" s="42"/>
+      <c r="M12" s="42"/>
+      <c r="N12" s="42"/>
+      <c r="O12" s="42"/>
+      <c r="P12" s="42"/>
+      <c r="Q12" s="42"/>
+      <c r="R12" s="15"/>
+      <c r="S12" s="34"/>
     </row>
     <row r="13" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A13" s="41">
+      <c r="A13" s="45">
         <v>30010009</v>
       </c>
-      <c r="B13" s="42">
+      <c r="B13" s="46">
         <v>100100</v>
       </c>
-      <c r="C13" s="26" t="s">
+      <c r="C13" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="D13" s="36">
+      <c r="D13" s="40">
         <v>31203</v>
       </c>
-      <c r="E13" s="36" t="s">
+      <c r="E13" s="40" t="s">
         <v>65</v>
       </c>
-      <c r="F13" s="41" t="s">
+      <c r="F13" s="45" t="s">
         <v>53</v>
       </c>
-      <c r="G13" s="41">
+      <c r="G13" s="45">
         <v>2001001</v>
       </c>
-      <c r="H13" s="41" t="s">
+      <c r="H13" s="45" t="s">
         <v>60</v>
       </c>
-      <c r="I13" s="41" t="s">
+      <c r="I13" s="45" t="s">
         <v>66</v>
       </c>
-      <c r="J13" s="41"/>
-      <c r="K13" s="43" t="s">
+      <c r="J13" s="45"/>
+      <c r="K13" s="47" t="s">
         <v>67</v>
       </c>
-      <c r="L13" s="41"/>
-      <c r="M13" s="41"/>
-      <c r="N13" s="41"/>
-      <c r="O13" s="41"/>
-      <c r="P13" s="41"/>
-      <c r="Q13" s="41"/>
-      <c r="R13" s="11"/>
-      <c r="S13" s="30"/>
+      <c r="L13" s="45"/>
+      <c r="M13" s="45"/>
+      <c r="N13" s="45"/>
+      <c r="O13" s="45"/>
+      <c r="P13" s="45"/>
+      <c r="Q13" s="45"/>
+      <c r="R13" s="15"/>
+      <c r="S13" s="34"/>
     </row>
     <row r="14" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A14" s="36">
+      <c r="A14" s="40">
         <v>30010010</v>
       </c>
-      <c r="B14" s="44">
+      <c r="B14" s="48">
         <v>100100</v>
       </c>
-      <c r="C14" s="26" t="s">
+      <c r="C14" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="D14" s="45">
+      <c r="D14" s="49">
         <v>31301</v>
       </c>
-      <c r="E14" s="45" t="s">
+      <c r="E14" s="49" t="s">
         <v>68</v>
       </c>
-      <c r="F14" s="36" t="s">
+      <c r="F14" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="G14" s="36"/>
-      <c r="H14" s="36"/>
-      <c r="I14" s="36" t="s">
+      <c r="G14" s="40"/>
+      <c r="H14" s="40"/>
+      <c r="I14" s="40" t="s">
         <v>69</v>
       </c>
-      <c r="J14" s="36"/>
-      <c r="K14" s="46"/>
-      <c r="L14" s="36" t="s">
+      <c r="J14" s="40"/>
+      <c r="K14" s="50"/>
+      <c r="L14" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="M14" s="36" t="s">
+      <c r="M14" s="40" t="s">
         <v>70</v>
       </c>
-      <c r="N14" s="36"/>
-      <c r="O14" s="36"/>
-      <c r="P14" s="36"/>
-      <c r="Q14" s="47" t="s">
+      <c r="N14" s="40"/>
+      <c r="O14" s="40"/>
+      <c r="P14" s="40"/>
+      <c r="Q14" s="51" t="s">
         <v>71</v>
       </c>
-      <c r="R14" s="48" t="s">
+      <c r="R14" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="S14" s="14" t="s">
+      <c r="S14" s="18" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="15" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A15" s="41">
+      <c r="A15" s="45">
         <v>30010011</v>
       </c>
-      <c r="B15" s="42">
+      <c r="B15" s="46">
         <v>100100</v>
       </c>
-      <c r="C15" s="26" t="s">
+      <c r="C15" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="D15" s="45">
+      <c r="D15" s="49">
         <v>31302</v>
       </c>
-      <c r="E15" s="45" t="s">
+      <c r="E15" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F15" s="41" t="s">
+      <c r="F15" s="45" t="s">
         <v>34</v>
       </c>
-      <c r="G15" s="41"/>
-      <c r="H15" s="41"/>
-      <c r="I15" s="41" t="s">
+      <c r="G15" s="45"/>
+      <c r="H15" s="45"/>
+      <c r="I15" s="45" t="s">
         <v>75</v>
       </c>
-      <c r="J15" s="41"/>
-      <c r="K15" s="43"/>
-      <c r="L15" s="41" t="s">
+      <c r="J15" s="45"/>
+      <c r="K15" s="47"/>
+      <c r="L15" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="M15" s="41" t="s">
+      <c r="M15" s="45" t="s">
         <v>57</v>
       </c>
-      <c r="N15" s="41"/>
-      <c r="O15" s="41"/>
-      <c r="P15" s="41"/>
-      <c r="Q15" s="41"/>
-      <c r="R15" s="11"/>
-      <c r="S15" s="30"/>
+      <c r="N15" s="45"/>
+      <c r="O15" s="45"/>
+      <c r="P15" s="45"/>
+      <c r="Q15" s="45"/>
+      <c r="R15" s="15"/>
+      <c r="S15" s="34"/>
     </row>
     <row r="16" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A16" s="41">
+      <c r="A16" s="45">
         <v>30010012</v>
       </c>
-      <c r="B16" s="42">
+      <c r="B16" s="46">
         <v>100100</v>
       </c>
-      <c r="C16" s="26" t="s">
+      <c r="C16" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="D16" s="45">
+      <c r="D16" s="49">
         <v>31303</v>
       </c>
-      <c r="E16" s="45" t="s">
+      <c r="E16" s="49" t="s">
         <v>76</v>
       </c>
-      <c r="F16" s="41" t="s">
+      <c r="F16" s="45" t="s">
         <v>53</v>
       </c>
-      <c r="G16" s="41">
+      <c r="G16" s="45">
         <v>2001001</v>
       </c>
-      <c r="H16" s="41" t="s">
+      <c r="H16" s="45" t="s">
         <v>60</v>
       </c>
-      <c r="I16" s="41" t="s">
+      <c r="I16" s="45" t="s">
         <v>66</v>
       </c>
-      <c r="J16" s="41"/>
-      <c r="K16" s="43" t="s">
+      <c r="J16" s="45"/>
+      <c r="K16" s="47" t="s">
         <v>67</v>
       </c>
-      <c r="L16" s="41"/>
-      <c r="M16" s="41"/>
-      <c r="N16" s="41"/>
-      <c r="O16" s="41"/>
-      <c r="P16" s="41"/>
-      <c r="Q16" s="41"/>
-      <c r="R16" s="11"/>
-      <c r="S16" s="30"/>
+      <c r="L16" s="45"/>
+      <c r="M16" s="45"/>
+      <c r="N16" s="45"/>
+      <c r="O16" s="45"/>
+      <c r="P16" s="45"/>
+      <c r="Q16" s="45"/>
+      <c r="R16" s="15"/>
+      <c r="S16" s="34"/>
     </row>
     <row r="17" s="3" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A17" s="11">
+      <c r="A17" s="15">
         <v>30070001</v>
       </c>
       <c r="B17" s="3">
@@ -2793,30 +2907,30 @@
       <c r="C17" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D17" s="34">
+      <c r="D17" s="38">
         <v>34001</v>
       </c>
-      <c r="E17" s="34" t="s">
+      <c r="E17" s="38" t="s">
         <v>78</v>
       </c>
-      <c r="F17" s="34" t="s">
+      <c r="F17" s="38" t="s">
         <v>79</v>
       </c>
-      <c r="G17" s="23">
+      <c r="G17" s="27">
         <v>2007001</v>
       </c>
-      <c r="H17" s="11" t="s">
+      <c r="H17" s="15" t="s">
         <v>60</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="K17" s="49" t="s">
+      <c r="K17" s="53" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="18" s="3" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A18" s="11">
+      <c r="A18" s="15">
         <v>30070002</v>
       </c>
       <c r="B18" s="3">
@@ -2825,30 +2939,30 @@
       <c r="C18" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D18" s="34">
+      <c r="D18" s="38">
         <v>34002</v>
       </c>
-      <c r="E18" s="34" t="s">
+      <c r="E18" s="38" t="s">
         <v>82</v>
       </c>
-      <c r="F18" s="34" t="s">
+      <c r="F18" s="38" t="s">
         <v>83</v>
       </c>
-      <c r="G18" s="23">
+      <c r="G18" s="27">
         <v>2007001</v>
       </c>
-      <c r="H18" s="11" t="s">
+      <c r="H18" s="15" t="s">
         <v>60</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="K18" s="49" t="s">
+      <c r="K18" s="53" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="19" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A19" s="36">
+      <c r="A19" s="40">
         <v>30120001</v>
       </c>
       <c r="B19" s="4">
@@ -2857,33 +2971,33 @@
       <c r="C19" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D19" s="36">
+      <c r="D19" s="40">
         <v>32001</v>
       </c>
-      <c r="E19" s="36" t="s">
+      <c r="E19" s="40" t="s">
         <v>85</v>
       </c>
-      <c r="F19" s="36" t="s">
+      <c r="F19" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="G19" s="44">
+      <c r="G19" s="48">
         <v>2012001</v>
       </c>
-      <c r="H19" s="36" t="s">
+      <c r="H19" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="I19" s="36" t="s">
+      <c r="I19" s="40" t="s">
         <v>85</v>
       </c>
-      <c r="J19" s="36" t="s">
+      <c r="J19" s="40" t="s">
         <v>86</v>
       </c>
-      <c r="K19" s="50">
+      <c r="K19" s="54">
         <v>10120041</v>
       </c>
     </row>
     <row r="20" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A20" s="36">
+      <c r="A20" s="40">
         <v>30120002</v>
       </c>
       <c r="B20" s="4">
@@ -2892,33 +3006,33 @@
       <c r="C20" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D20" s="36">
+      <c r="D20" s="40">
         <v>32002</v>
       </c>
-      <c r="E20" s="36" t="s">
+      <c r="E20" s="40" t="s">
         <v>87</v>
       </c>
-      <c r="F20" s="36" t="s">
+      <c r="F20" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="G20" s="44">
+      <c r="G20" s="48">
         <v>2012001</v>
       </c>
-      <c r="H20" s="36" t="s">
+      <c r="H20" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="I20" s="36" t="s">
+      <c r="I20" s="40" t="s">
         <v>87</v>
       </c>
-      <c r="J20" s="36" t="s">
+      <c r="J20" s="40" t="s">
         <v>86</v>
       </c>
-      <c r="K20" s="50">
+      <c r="K20" s="54">
         <v>10120042</v>
       </c>
     </row>
     <row r="21" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A21" s="36">
+      <c r="A21" s="40">
         <v>30120003</v>
       </c>
       <c r="B21" s="4">
@@ -2927,33 +3041,33 @@
       <c r="C21" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D21" s="36">
+      <c r="D21" s="40">
         <v>32003</v>
       </c>
-      <c r="E21" s="36" t="s">
+      <c r="E21" s="40" t="s">
         <v>88</v>
       </c>
-      <c r="F21" s="36" t="s">
+      <c r="F21" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="G21" s="44">
+      <c r="G21" s="48">
         <v>2012001</v>
       </c>
-      <c r="H21" s="36" t="s">
+      <c r="H21" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="I21" s="36" t="s">
+      <c r="I21" s="40" t="s">
         <v>88</v>
       </c>
-      <c r="J21" s="36" t="s">
+      <c r="J21" s="40" t="s">
         <v>86</v>
       </c>
-      <c r="K21" s="50">
+      <c r="K21" s="54">
         <v>10120043</v>
       </c>
     </row>
     <row r="22" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A22" s="36">
+      <c r="A22" s="40">
         <v>30120004</v>
       </c>
       <c r="B22" s="4">
@@ -2962,33 +3076,33 @@
       <c r="C22" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D22" s="36">
+      <c r="D22" s="40">
         <v>32004</v>
       </c>
-      <c r="E22" s="36" t="s">
+      <c r="E22" s="40" t="s">
         <v>89</v>
       </c>
-      <c r="F22" s="36" t="s">
+      <c r="F22" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="G22" s="44">
+      <c r="G22" s="48">
         <v>2012001</v>
       </c>
-      <c r="H22" s="36" t="s">
+      <c r="H22" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="I22" s="36" t="s">
+      <c r="I22" s="40" t="s">
         <v>89</v>
       </c>
-      <c r="J22" s="36" t="s">
+      <c r="J22" s="40" t="s">
         <v>86</v>
       </c>
-      <c r="K22" s="50">
+      <c r="K22" s="54">
         <v>10120044</v>
       </c>
     </row>
     <row r="23" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A23" s="36">
+      <c r="A23" s="40">
         <v>30120005</v>
       </c>
       <c r="B23" s="4">
@@ -2997,33 +3111,33 @@
       <c r="C23" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D23" s="36">
+      <c r="D23" s="40">
         <v>32005</v>
       </c>
-      <c r="E23" s="36" t="s">
+      <c r="E23" s="40" t="s">
         <v>89</v>
       </c>
-      <c r="F23" s="36" t="s">
+      <c r="F23" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="G23" s="44">
+      <c r="G23" s="48">
         <v>2012001</v>
       </c>
-      <c r="H23" s="36" t="s">
+      <c r="H23" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="I23" s="36" t="s">
+      <c r="I23" s="40" t="s">
         <v>89</v>
       </c>
-      <c r="J23" s="36" t="s">
+      <c r="J23" s="40" t="s">
         <v>86</v>
       </c>
-      <c r="K23" s="50">
+      <c r="K23" s="54">
         <v>10120045</v>
       </c>
     </row>
     <row r="24" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A24" s="36">
+      <c r="A24" s="40">
         <v>30120006</v>
       </c>
       <c r="B24" s="4">
@@ -3032,33 +3146,33 @@
       <c r="C24" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D24" s="36">
+      <c r="D24" s="40">
         <v>32006</v>
       </c>
-      <c r="E24" s="36" t="s">
+      <c r="E24" s="40" t="s">
         <v>89</v>
       </c>
-      <c r="F24" s="36" t="s">
+      <c r="F24" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="G24" s="44">
+      <c r="G24" s="48">
         <v>2012001</v>
       </c>
-      <c r="H24" s="36" t="s">
+      <c r="H24" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="I24" s="36" t="s">
+      <c r="I24" s="40" t="s">
         <v>89</v>
       </c>
-      <c r="J24" s="36" t="s">
+      <c r="J24" s="40" t="s">
         <v>86</v>
       </c>
-      <c r="K24" s="50">
+      <c r="K24" s="54">
         <v>10120046</v>
       </c>
     </row>
     <row r="25" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A25" s="51">
+      <c r="A25" s="55">
         <v>30120011</v>
       </c>
       <c r="B25" s="5">
@@ -3067,33 +3181,33 @@
       <c r="C25" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="D25" s="36">
+      <c r="D25" s="40">
         <v>32101</v>
       </c>
-      <c r="E25" s="51" t="s">
+      <c r="E25" s="55" t="s">
         <v>85</v>
       </c>
-      <c r="F25" s="51" t="s">
+      <c r="F25" s="55" t="s">
         <v>53</v>
       </c>
-      <c r="G25" s="52">
+      <c r="G25" s="56">
         <v>2012001</v>
       </c>
-      <c r="H25" s="51" t="s">
+      <c r="H25" s="55" t="s">
         <v>60</v>
       </c>
-      <c r="I25" s="51" t="s">
+      <c r="I25" s="55" t="s">
         <v>85</v>
       </c>
-      <c r="J25" s="51" t="s">
+      <c r="J25" s="55" t="s">
         <v>91</v>
       </c>
-      <c r="K25" s="53">
+      <c r="K25" s="57">
         <v>10120041</v>
       </c>
     </row>
     <row r="26" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A26" s="51">
+      <c r="A26" s="55">
         <v>30120012</v>
       </c>
       <c r="B26" s="5">
@@ -3102,33 +3216,33 @@
       <c r="C26" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="D26" s="36">
+      <c r="D26" s="40">
         <v>32102</v>
       </c>
-      <c r="E26" s="51" t="s">
+      <c r="E26" s="55" t="s">
         <v>87</v>
       </c>
-      <c r="F26" s="51" t="s">
+      <c r="F26" s="55" t="s">
         <v>53</v>
       </c>
-      <c r="G26" s="52">
+      <c r="G26" s="56">
         <v>2012001</v>
       </c>
-      <c r="H26" s="51" t="s">
+      <c r="H26" s="55" t="s">
         <v>60</v>
       </c>
-      <c r="I26" s="51" t="s">
+      <c r="I26" s="55" t="s">
         <v>87</v>
       </c>
-      <c r="J26" s="51" t="s">
+      <c r="J26" s="55" t="s">
         <v>91</v>
       </c>
-      <c r="K26" s="53">
+      <c r="K26" s="57">
         <v>10120042</v>
       </c>
     </row>
     <row r="27" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A27" s="51">
+      <c r="A27" s="55">
         <v>30120013</v>
       </c>
       <c r="B27" s="5">
@@ -3137,33 +3251,33 @@
       <c r="C27" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="D27" s="36">
+      <c r="D27" s="40">
         <v>32103</v>
       </c>
-      <c r="E27" s="51" t="s">
+      <c r="E27" s="55" t="s">
         <v>88</v>
       </c>
-      <c r="F27" s="51" t="s">
+      <c r="F27" s="55" t="s">
         <v>53</v>
       </c>
-      <c r="G27" s="52">
+      <c r="G27" s="56">
         <v>2012001</v>
       </c>
-      <c r="H27" s="51" t="s">
+      <c r="H27" s="55" t="s">
         <v>60</v>
       </c>
-      <c r="I27" s="51" t="s">
+      <c r="I27" s="55" t="s">
         <v>88</v>
       </c>
-      <c r="J27" s="51" t="s">
+      <c r="J27" s="55" t="s">
         <v>91</v>
       </c>
-      <c r="K27" s="53">
+      <c r="K27" s="57">
         <v>10120043</v>
       </c>
     </row>
     <row r="28" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A28" s="51">
+      <c r="A28" s="55">
         <v>30120014</v>
       </c>
       <c r="B28" s="5">
@@ -3172,33 +3286,33 @@
       <c r="C28" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="D28" s="36">
+      <c r="D28" s="40">
         <v>32104</v>
       </c>
-      <c r="E28" s="51" t="s">
+      <c r="E28" s="55" t="s">
         <v>89</v>
       </c>
-      <c r="F28" s="51" t="s">
+      <c r="F28" s="55" t="s">
         <v>53</v>
       </c>
-      <c r="G28" s="52">
+      <c r="G28" s="56">
         <v>2012001</v>
       </c>
-      <c r="H28" s="51" t="s">
+      <c r="H28" s="55" t="s">
         <v>60</v>
       </c>
-      <c r="I28" s="51" t="s">
+      <c r="I28" s="55" t="s">
         <v>89</v>
       </c>
-      <c r="J28" s="51" t="s">
+      <c r="J28" s="55" t="s">
         <v>91</v>
       </c>
-      <c r="K28" s="53">
+      <c r="K28" s="57">
         <v>10120044</v>
       </c>
     </row>
     <row r="29" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A29" s="51">
+      <c r="A29" s="55">
         <v>30120015</v>
       </c>
       <c r="B29" s="5">
@@ -3207,33 +3321,33 @@
       <c r="C29" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="D29" s="36">
+      <c r="D29" s="40">
         <v>32105</v>
       </c>
-      <c r="E29" s="51" t="s">
+      <c r="E29" s="55" t="s">
         <v>89</v>
       </c>
-      <c r="F29" s="51" t="s">
+      <c r="F29" s="55" t="s">
         <v>53</v>
       </c>
-      <c r="G29" s="52">
+      <c r="G29" s="56">
         <v>2012001</v>
       </c>
-      <c r="H29" s="51" t="s">
+      <c r="H29" s="55" t="s">
         <v>60</v>
       </c>
-      <c r="I29" s="51" t="s">
+      <c r="I29" s="55" t="s">
         <v>89</v>
       </c>
-      <c r="J29" s="51" t="s">
+      <c r="J29" s="55" t="s">
         <v>91</v>
       </c>
-      <c r="K29" s="53">
+      <c r="K29" s="57">
         <v>10120045</v>
       </c>
     </row>
     <row r="30" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A30" s="51">
+      <c r="A30" s="55">
         <v>30120016</v>
       </c>
       <c r="B30" s="5">
@@ -3242,33 +3356,33 @@
       <c r="C30" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="D30" s="36">
+      <c r="D30" s="40">
         <v>32106</v>
       </c>
-      <c r="E30" s="51" t="s">
+      <c r="E30" s="55" t="s">
         <v>89</v>
       </c>
-      <c r="F30" s="51" t="s">
+      <c r="F30" s="55" t="s">
         <v>53</v>
       </c>
-      <c r="G30" s="52">
+      <c r="G30" s="56">
         <v>2012001</v>
       </c>
-      <c r="H30" s="51" t="s">
+      <c r="H30" s="55" t="s">
         <v>60</v>
       </c>
-      <c r="I30" s="51" t="s">
+      <c r="I30" s="55" t="s">
         <v>89</v>
       </c>
-      <c r="J30" s="51" t="s">
+      <c r="J30" s="55" t="s">
         <v>91</v>
       </c>
-      <c r="K30" s="53">
+      <c r="K30" s="57">
         <v>10120046</v>
       </c>
     </row>
     <row r="31" s="6" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A31" s="45">
+      <c r="A31" s="49">
         <v>30120021</v>
       </c>
       <c r="B31" s="6">
@@ -3277,31 +3391,31 @@
       <c r="C31" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D31" s="45">
+      <c r="D31" s="49">
         <v>32201</v>
       </c>
-      <c r="E31" s="45" t="s">
+      <c r="E31" s="49" t="s">
         <v>85</v>
       </c>
-      <c r="F31" s="45" t="s">
+      <c r="F31" s="49" t="s">
         <v>53</v>
       </c>
-      <c r="G31" s="54">
+      <c r="G31" s="58">
         <v>2012001</v>
       </c>
-      <c r="H31" s="45" t="s">
+      <c r="H31" s="49" t="s">
         <v>60</v>
       </c>
-      <c r="I31" s="45" t="s">
+      <c r="I31" s="49" t="s">
         <v>85</v>
       </c>
-      <c r="J31" s="45"/>
-      <c r="K31" s="55">
+      <c r="J31" s="49"/>
+      <c r="K31" s="59">
         <v>10120041</v>
       </c>
     </row>
     <row r="32" s="6" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A32" s="45">
+      <c r="A32" s="49">
         <v>30120022</v>
       </c>
       <c r="B32" s="6">
@@ -3310,31 +3424,31 @@
       <c r="C32" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D32" s="45">
+      <c r="D32" s="49">
         <v>32202</v>
       </c>
-      <c r="E32" s="45" t="s">
+      <c r="E32" s="49" t="s">
         <v>87</v>
       </c>
-      <c r="F32" s="45" t="s">
+      <c r="F32" s="49" t="s">
         <v>53</v>
       </c>
-      <c r="G32" s="54">
+      <c r="G32" s="58">
         <v>2012001</v>
       </c>
-      <c r="H32" s="45" t="s">
+      <c r="H32" s="49" t="s">
         <v>60</v>
       </c>
-      <c r="I32" s="45" t="s">
+      <c r="I32" s="49" t="s">
         <v>87</v>
       </c>
-      <c r="J32" s="45"/>
-      <c r="K32" s="55">
+      <c r="J32" s="49"/>
+      <c r="K32" s="59">
         <v>10120042</v>
       </c>
     </row>
     <row r="33" s="6" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A33" s="45">
+      <c r="A33" s="49">
         <v>30120023</v>
       </c>
       <c r="B33" s="6">
@@ -3343,31 +3457,31 @@
       <c r="C33" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D33" s="45">
+      <c r="D33" s="49">
         <v>32203</v>
       </c>
-      <c r="E33" s="45" t="s">
+      <c r="E33" s="49" t="s">
         <v>88</v>
       </c>
-      <c r="F33" s="45" t="s">
+      <c r="F33" s="49" t="s">
         <v>53</v>
       </c>
-      <c r="G33" s="54">
+      <c r="G33" s="58">
         <v>2012001</v>
       </c>
-      <c r="H33" s="45" t="s">
+      <c r="H33" s="49" t="s">
         <v>60</v>
       </c>
-      <c r="I33" s="45" t="s">
+      <c r="I33" s="49" t="s">
         <v>88</v>
       </c>
-      <c r="J33" s="45"/>
-      <c r="K33" s="55">
+      <c r="J33" s="49"/>
+      <c r="K33" s="59">
         <v>10120043</v>
       </c>
     </row>
     <row r="34" s="6" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A34" s="45">
+      <c r="A34" s="49">
         <v>30120024</v>
       </c>
       <c r="B34" s="6">
@@ -3376,31 +3490,31 @@
       <c r="C34" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D34" s="45">
+      <c r="D34" s="49">
         <v>32204</v>
       </c>
-      <c r="E34" s="45" t="s">
+      <c r="E34" s="49" t="s">
         <v>89</v>
       </c>
-      <c r="F34" s="45" t="s">
+      <c r="F34" s="49" t="s">
         <v>53</v>
       </c>
-      <c r="G34" s="54">
+      <c r="G34" s="58">
         <v>2012001</v>
       </c>
-      <c r="H34" s="45" t="s">
+      <c r="H34" s="49" t="s">
         <v>60</v>
       </c>
-      <c r="I34" s="45" t="s">
+      <c r="I34" s="49" t="s">
         <v>89</v>
       </c>
-      <c r="J34" s="45"/>
-      <c r="K34" s="55">
+      <c r="J34" s="49"/>
+      <c r="K34" s="59">
         <v>10120044</v>
       </c>
     </row>
     <row r="35" s="6" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A35" s="45">
+      <c r="A35" s="49">
         <v>30120025</v>
       </c>
       <c r="B35" s="6">
@@ -3409,31 +3523,31 @@
       <c r="C35" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D35" s="45">
+      <c r="D35" s="49">
         <v>32205</v>
       </c>
-      <c r="E35" s="45" t="s">
+      <c r="E35" s="49" t="s">
         <v>89</v>
       </c>
-      <c r="F35" s="45" t="s">
+      <c r="F35" s="49" t="s">
         <v>53</v>
       </c>
-      <c r="G35" s="54">
+      <c r="G35" s="58">
         <v>2012001</v>
       </c>
-      <c r="H35" s="45" t="s">
+      <c r="H35" s="49" t="s">
         <v>60</v>
       </c>
-      <c r="I35" s="45" t="s">
+      <c r="I35" s="49" t="s">
         <v>89</v>
       </c>
-      <c r="J35" s="45"/>
-      <c r="K35" s="55">
+      <c r="J35" s="49"/>
+      <c r="K35" s="59">
         <v>10120045</v>
       </c>
     </row>
     <row r="36" s="6" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A36" s="45">
+      <c r="A36" s="49">
         <v>30120026</v>
       </c>
       <c r="B36" s="6">
@@ -3442,841 +3556,948 @@
       <c r="C36" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D36" s="45">
+      <c r="D36" s="49">
         <v>32206</v>
       </c>
-      <c r="E36" s="45" t="s">
+      <c r="E36" s="49" t="s">
         <v>89</v>
       </c>
-      <c r="F36" s="45" t="s">
+      <c r="F36" s="49" t="s">
         <v>53</v>
       </c>
-      <c r="G36" s="54">
+      <c r="G36" s="58">
         <v>2012001</v>
       </c>
-      <c r="H36" s="45" t="s">
+      <c r="H36" s="49" t="s">
         <v>60</v>
       </c>
-      <c r="I36" s="45" t="s">
+      <c r="I36" s="49" t="s">
         <v>89</v>
       </c>
-      <c r="J36" s="45"/>
-      <c r="K36" s="55">
+      <c r="J36" s="49"/>
+      <c r="K36" s="59">
         <v>10120046</v>
       </c>
     </row>
-    <row r="37" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A37" s="25">
+    <row r="37" s="7" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A37" s="60">
         <v>30240001</v>
       </c>
-      <c r="B37" s="26">
+      <c r="B37" s="61">
         <v>102400</v>
       </c>
-      <c r="C37" s="26" t="s">
+      <c r="C37" s="61" t="s">
         <v>32</v>
       </c>
-      <c r="D37" s="25">
+      <c r="D37" s="60">
         <v>32401</v>
       </c>
-      <c r="E37" s="25" t="s">
+      <c r="E37" s="60" t="s">
         <v>33</v>
       </c>
-      <c r="F37" s="25" t="s">
+      <c r="F37" s="60" t="s">
         <v>34</v>
       </c>
-      <c r="G37" s="25"/>
-      <c r="H37" s="25"/>
-      <c r="I37" s="25" t="s">
+      <c r="G37" s="60"/>
+      <c r="H37" s="60"/>
+      <c r="I37" s="60" t="s">
         <v>35</v>
       </c>
-      <c r="J37" s="25"/>
-      <c r="K37" s="27"/>
-      <c r="L37" s="11" t="s">
+      <c r="J37" s="60"/>
+      <c r="K37" s="62"/>
+      <c r="L37" s="63" t="s">
         <v>36</v>
       </c>
-      <c r="M37" s="25" t="s">
+      <c r="M37" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="N37" s="25" t="s">
+      <c r="N37" s="60" t="s">
         <v>38</v>
       </c>
-      <c r="O37" s="25"/>
-      <c r="P37" s="25"/>
-      <c r="Q37" s="28" t="s">
+      <c r="O37" s="60"/>
+      <c r="P37" s="60"/>
+      <c r="Q37" s="64" t="s">
         <v>39</v>
       </c>
-      <c r="R37" s="29" t="s">
+      <c r="R37" s="65" t="s">
         <v>40</v>
       </c>
-      <c r="S37" s="30" t="s">
+      <c r="S37" s="66" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="38" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A38" s="25">
+    <row r="38" s="7" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A38" s="60">
         <v>30240002</v>
       </c>
-      <c r="B38" s="26">
+      <c r="B38" s="61">
         <v>102400</v>
       </c>
-      <c r="C38" s="26" t="s">
+      <c r="C38" s="61" t="s">
         <v>32</v>
       </c>
-      <c r="D38" s="25">
+      <c r="D38" s="60">
         <v>32402</v>
       </c>
-      <c r="E38" s="25" t="s">
+      <c r="E38" s="60" t="s">
         <v>42</v>
       </c>
-      <c r="F38" s="25" t="s">
+      <c r="F38" s="60" t="s">
         <v>34</v>
       </c>
-      <c r="G38" s="25"/>
-      <c r="H38" s="25"/>
-      <c r="I38" s="25" t="s">
+      <c r="G38" s="60"/>
+      <c r="H38" s="60"/>
+      <c r="I38" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="J38" s="25"/>
-      <c r="K38" s="27"/>
-      <c r="L38" s="11" t="s">
+      <c r="J38" s="60"/>
+      <c r="K38" s="62"/>
+      <c r="L38" s="63" t="s">
         <v>36</v>
       </c>
-      <c r="M38" s="25" t="s">
+      <c r="M38" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="N38" s="25" t="s">
+      <c r="N38" s="60" t="s">
         <v>38</v>
       </c>
-      <c r="O38" s="25"/>
-      <c r="P38" s="25"/>
-      <c r="Q38" s="28" t="s">
+      <c r="O38" s="60"/>
+      <c r="P38" s="60"/>
+      <c r="Q38" s="64" t="s">
         <v>44</v>
       </c>
-      <c r="R38" s="29" t="s">
+      <c r="R38" s="65" t="s">
         <v>40</v>
       </c>
-      <c r="S38" s="30"/>
-    </row>
-    <row r="39" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A39" s="25">
+      <c r="S38" s="66"/>
+    </row>
+    <row r="39" s="7" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A39" s="60">
         <v>30240003</v>
       </c>
-      <c r="B39" s="26">
+      <c r="B39" s="61">
         <v>102400</v>
       </c>
-      <c r="C39" s="26" t="s">
+      <c r="C39" s="61" t="s">
         <v>32</v>
       </c>
-      <c r="D39" s="25">
+      <c r="D39" s="60">
         <v>32403</v>
       </c>
-      <c r="E39" s="25" t="s">
+      <c r="E39" s="60" t="s">
         <v>45</v>
       </c>
-      <c r="F39" s="25" t="s">
+      <c r="F39" s="60" t="s">
         <v>34</v>
       </c>
-      <c r="G39" s="25"/>
-      <c r="H39" s="25"/>
-      <c r="I39" s="25" t="s">
+      <c r="G39" s="60"/>
+      <c r="H39" s="60"/>
+      <c r="I39" s="60" t="s">
         <v>46</v>
       </c>
-      <c r="J39" s="25"/>
-      <c r="K39" s="27"/>
-      <c r="L39" s="11" t="s">
+      <c r="J39" s="60"/>
+      <c r="K39" s="62"/>
+      <c r="L39" s="63" t="s">
         <v>36</v>
       </c>
-      <c r="M39" s="25" t="s">
+      <c r="M39" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="N39" s="25" t="s">
+      <c r="N39" s="60" t="s">
         <v>38</v>
       </c>
-      <c r="O39" s="25"/>
-      <c r="P39" s="25"/>
-      <c r="Q39" s="28" t="s">
+      <c r="O39" s="60"/>
+      <c r="P39" s="60"/>
+      <c r="Q39" s="64" t="s">
         <v>47</v>
       </c>
-      <c r="R39" s="29" t="s">
+      <c r="R39" s="65" t="s">
         <v>40</v>
       </c>
-      <c r="S39" s="30"/>
-    </row>
-    <row r="40" s="3" customFormat="1" ht="15" customHeight="1" spans="1:19">
-      <c r="A40" s="25">
+      <c r="S39" s="66"/>
+    </row>
+    <row r="40" s="7" customFormat="1" ht="15" customHeight="1" spans="1:19">
+      <c r="A40" s="60">
         <v>30240004</v>
       </c>
-      <c r="B40" s="26">
+      <c r="B40" s="61">
         <v>102400</v>
       </c>
-      <c r="C40" s="26" t="s">
+      <c r="C40" s="61" t="s">
         <v>32</v>
       </c>
-      <c r="D40" s="25">
+      <c r="D40" s="60">
         <v>32404</v>
       </c>
-      <c r="E40" s="25" t="s">
+      <c r="E40" s="60" t="s">
         <v>48</v>
       </c>
-      <c r="F40" s="25" t="s">
+      <c r="F40" s="60" t="s">
         <v>34</v>
       </c>
-      <c r="G40" s="25"/>
-      <c r="H40" s="25"/>
-      <c r="I40" s="25" t="s">
+      <c r="G40" s="60"/>
+      <c r="H40" s="60"/>
+      <c r="I40" s="60" t="s">
         <v>49</v>
       </c>
-      <c r="J40" s="25"/>
-      <c r="K40" s="27"/>
-      <c r="L40" s="11" t="s">
+      <c r="J40" s="60"/>
+      <c r="K40" s="62"/>
+      <c r="L40" s="63" t="s">
         <v>36</v>
       </c>
-      <c r="M40" s="25" t="s">
+      <c r="M40" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="N40" s="25" t="s">
+      <c r="N40" s="60" t="s">
         <v>38</v>
       </c>
-      <c r="O40" s="25"/>
-      <c r="P40" s="25"/>
-      <c r="Q40" s="28" t="s">
+      <c r="O40" s="60"/>
+      <c r="P40" s="60"/>
+      <c r="Q40" s="64" t="s">
         <v>50</v>
       </c>
-      <c r="R40" s="29" t="s">
+      <c r="R40" s="65" t="s">
         <v>40</v>
       </c>
-      <c r="S40" s="30"/>
-    </row>
-    <row r="41" s="3" customFormat="1" ht="15" customHeight="1" spans="1:19">
-      <c r="A41" s="11">
+      <c r="S40" s="66"/>
+    </row>
+    <row r="41" s="7" customFormat="1" ht="15" customHeight="1" spans="1:19">
+      <c r="A41" s="63">
         <v>30240005</v>
       </c>
-      <c r="B41" s="23">
+      <c r="B41" s="67">
         <v>102400</v>
       </c>
-      <c r="C41" s="26" t="s">
+      <c r="C41" s="61" t="s">
         <v>32</v>
       </c>
-      <c r="D41" s="11">
+      <c r="D41" s="63">
         <v>32411</v>
       </c>
-      <c r="E41" s="11" t="s">
+      <c r="E41" s="63" t="s">
         <v>51</v>
       </c>
-      <c r="F41" s="11" t="s">
+      <c r="F41" s="63" t="s">
         <v>34</v>
       </c>
-      <c r="G41" s="11"/>
-      <c r="H41" s="11"/>
-      <c r="I41" s="11" t="s">
+      <c r="G41" s="63"/>
+      <c r="H41" s="63"/>
+      <c r="I41" s="63" t="s">
         <v>52</v>
       </c>
-      <c r="J41" s="11"/>
-      <c r="K41" s="13"/>
-      <c r="L41" s="11" t="s">
+      <c r="J41" s="63"/>
+      <c r="K41" s="68"/>
+      <c r="L41" s="63" t="s">
         <v>36</v>
       </c>
-      <c r="M41" s="11" t="s">
+      <c r="M41" s="63" t="s">
         <v>53</v>
       </c>
-      <c r="N41" s="11"/>
-      <c r="O41" s="11" t="s">
+      <c r="N41" s="63"/>
+      <c r="O41" s="63" t="s">
         <v>54</v>
       </c>
-      <c r="P41" s="11"/>
-      <c r="Q41" s="14"/>
-      <c r="R41" s="14"/>
-      <c r="S41" s="30"/>
-    </row>
-    <row r="42" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A42" s="31">
+      <c r="P41" s="63"/>
+      <c r="Q41" s="69"/>
+      <c r="R41" s="69"/>
+      <c r="S41" s="66"/>
+    </row>
+    <row r="42" s="7" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A42" s="60">
         <v>30240006</v>
       </c>
-      <c r="B42" s="32">
+      <c r="B42" s="61">
         <v>102400</v>
       </c>
-      <c r="C42" s="26" t="s">
+      <c r="C42" s="61" t="s">
         <v>32</v>
       </c>
-      <c r="D42" s="31">
+      <c r="D42" s="60">
         <v>32421</v>
       </c>
-      <c r="E42" s="31" t="s">
+      <c r="E42" s="60" t="s">
         <v>55</v>
       </c>
-      <c r="F42" s="31" t="s">
+      <c r="F42" s="60" t="s">
         <v>34</v>
       </c>
-      <c r="G42" s="31"/>
-      <c r="H42" s="31"/>
-      <c r="I42" s="31" t="s">
+      <c r="G42" s="60"/>
+      <c r="H42" s="60"/>
+      <c r="I42" s="60" t="s">
         <v>56</v>
       </c>
-      <c r="J42" s="31"/>
-      <c r="K42" s="33"/>
-      <c r="L42" s="31" t="s">
+      <c r="J42" s="60"/>
+      <c r="K42" s="62"/>
+      <c r="L42" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="M42" s="31" t="s">
+      <c r="M42" s="60" t="s">
         <v>57</v>
       </c>
-      <c r="N42" s="31" t="s">
+      <c r="N42" s="60" t="s">
         <v>38</v>
       </c>
-      <c r="O42" s="31" t="s">
+      <c r="O42" s="60" t="s">
         <v>54</v>
       </c>
-      <c r="P42" s="31"/>
-      <c r="Q42" s="31"/>
-      <c r="R42" s="11"/>
-      <c r="S42" s="30"/>
-    </row>
-    <row r="43" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A43" s="34">
+      <c r="P42" s="60"/>
+      <c r="Q42" s="60"/>
+      <c r="R42" s="63"/>
+      <c r="S42" s="66"/>
+    </row>
+    <row r="43" s="7" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A43" s="60">
         <v>30240007</v>
       </c>
-      <c r="B43" s="35">
+      <c r="B43" s="61">
         <v>102400</v>
       </c>
-      <c r="C43" s="26" t="s">
+      <c r="C43" s="61" t="s">
         <v>32</v>
       </c>
-      <c r="D43" s="36">
+      <c r="D43" s="60">
         <v>32431</v>
       </c>
-      <c r="E43" s="36" t="s">
+      <c r="E43" s="60" t="s">
         <v>58</v>
       </c>
-      <c r="F43" s="34" t="s">
+      <c r="F43" s="60" t="s">
         <v>59</v>
       </c>
-      <c r="G43" s="34">
+      <c r="G43" s="60">
         <v>2024001</v>
       </c>
-      <c r="H43" s="34" t="s">
+      <c r="H43" s="60" t="s">
         <v>60</v>
       </c>
-      <c r="I43" s="34" t="s">
+      <c r="I43" s="60" t="s">
         <v>61</v>
       </c>
-      <c r="J43" s="34"/>
-      <c r="K43" s="37">
+      <c r="J43" s="60"/>
+      <c r="K43" s="62">
         <v>10240091</v>
       </c>
-      <c r="L43" s="34"/>
-      <c r="M43" s="34"/>
-      <c r="N43" s="34"/>
-      <c r="O43" s="34"/>
-      <c r="P43" s="34"/>
-      <c r="Q43" s="34"/>
-      <c r="R43" s="11"/>
-      <c r="S43" s="30"/>
-    </row>
-    <row r="44" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A44" s="38">
+      <c r="L43" s="60"/>
+      <c r="M43" s="60"/>
+      <c r="N43" s="60"/>
+      <c r="O43" s="60"/>
+      <c r="P43" s="60"/>
+      <c r="Q43" s="60"/>
+      <c r="R43" s="63"/>
+      <c r="S43" s="66"/>
+    </row>
+    <row r="44" s="7" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A44" s="60">
         <v>30240008</v>
       </c>
-      <c r="B44" s="39">
+      <c r="B44" s="61">
         <v>102400</v>
       </c>
-      <c r="C44" s="26" t="s">
+      <c r="C44" s="61" t="s">
         <v>32</v>
       </c>
-      <c r="D44" s="36">
+      <c r="D44" s="60">
         <v>32432</v>
       </c>
-      <c r="E44" s="36" t="s">
+      <c r="E44" s="60" t="s">
         <v>62</v>
       </c>
-      <c r="F44" s="38" t="s">
+      <c r="F44" s="60" t="s">
         <v>53</v>
       </c>
-      <c r="G44" s="38">
+      <c r="G44" s="60">
         <v>2024001</v>
       </c>
-      <c r="H44" s="38" t="s">
+      <c r="H44" s="60" t="s">
         <v>60</v>
       </c>
-      <c r="I44" s="38" t="s">
+      <c r="I44" s="60" t="s">
         <v>63</v>
       </c>
-      <c r="J44" s="38"/>
-      <c r="K44" s="40" t="s">
+      <c r="J44" s="60"/>
+      <c r="K44" s="70" t="s">
         <v>93</v>
       </c>
-      <c r="L44" s="38"/>
-      <c r="M44" s="38"/>
-      <c r="N44" s="38"/>
-      <c r="O44" s="38"/>
-      <c r="P44" s="38"/>
-      <c r="Q44" s="38"/>
-      <c r="R44" s="11"/>
-      <c r="S44" s="30"/>
-    </row>
-    <row r="45" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A45" s="41">
+      <c r="L44" s="60"/>
+      <c r="M44" s="60"/>
+      <c r="N44" s="60"/>
+      <c r="O44" s="60"/>
+      <c r="P44" s="60"/>
+      <c r="Q44" s="60"/>
+      <c r="R44" s="63"/>
+      <c r="S44" s="66"/>
+    </row>
+    <row r="45" s="7" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A45" s="60">
         <v>30240009</v>
       </c>
-      <c r="B45" s="42">
+      <c r="B45" s="61">
         <v>102400</v>
       </c>
-      <c r="C45" s="26" t="s">
+      <c r="C45" s="61" t="s">
         <v>32</v>
       </c>
-      <c r="D45" s="36">
+      <c r="D45" s="60">
         <v>32433</v>
       </c>
-      <c r="E45" s="36" t="s">
+      <c r="E45" s="60" t="s">
         <v>65</v>
       </c>
-      <c r="F45" s="41" t="s">
+      <c r="F45" s="60" t="s">
         <v>53</v>
       </c>
-      <c r="G45" s="41">
+      <c r="G45" s="60">
         <v>2024001</v>
       </c>
-      <c r="H45" s="41" t="s">
+      <c r="H45" s="60" t="s">
         <v>60</v>
       </c>
-      <c r="I45" s="41" t="s">
+      <c r="I45" s="60" t="s">
         <v>66</v>
       </c>
-      <c r="J45" s="41"/>
-      <c r="K45" s="43" t="s">
+      <c r="J45" s="60"/>
+      <c r="K45" s="62" t="s">
         <v>94</v>
       </c>
-      <c r="L45" s="41"/>
-      <c r="M45" s="41"/>
-      <c r="N45" s="41"/>
-      <c r="O45" s="41"/>
-      <c r="P45" s="41"/>
-      <c r="Q45" s="41"/>
-      <c r="R45" s="11"/>
-      <c r="S45" s="30"/>
-    </row>
-    <row r="46" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A46" s="36">
+      <c r="L45" s="60"/>
+      <c r="M45" s="60"/>
+      <c r="N45" s="60"/>
+      <c r="O45" s="60"/>
+      <c r="P45" s="60"/>
+      <c r="Q45" s="60"/>
+      <c r="R45" s="63"/>
+      <c r="S45" s="66"/>
+    </row>
+    <row r="46" s="7" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A46" s="60">
         <v>30240010</v>
       </c>
-      <c r="B46" s="44">
+      <c r="B46" s="61">
         <v>102400</v>
       </c>
-      <c r="C46" s="26" t="s">
+      <c r="C46" s="61" t="s">
         <v>32</v>
       </c>
-      <c r="D46" s="45">
+      <c r="D46" s="60">
         <v>32441</v>
       </c>
-      <c r="E46" s="45" t="s">
+      <c r="E46" s="60" t="s">
         <v>68</v>
       </c>
-      <c r="F46" s="36" t="s">
+      <c r="F46" s="60" t="s">
         <v>34</v>
       </c>
-      <c r="G46" s="36"/>
-      <c r="H46" s="36"/>
-      <c r="I46" s="36" t="s">
+      <c r="G46" s="60"/>
+      <c r="H46" s="60"/>
+      <c r="I46" s="60" t="s">
         <v>69</v>
       </c>
-      <c r="J46" s="36"/>
-      <c r="K46" s="46"/>
-      <c r="L46" s="36" t="s">
+      <c r="J46" s="60"/>
+      <c r="K46" s="70"/>
+      <c r="L46" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="M46" s="36" t="s">
+      <c r="M46" s="60" t="s">
         <v>70</v>
       </c>
-      <c r="N46" s="36"/>
-      <c r="O46" s="36"/>
-      <c r="P46" s="36"/>
-      <c r="Q46" s="47" t="s">
+      <c r="N46" s="60"/>
+      <c r="O46" s="60"/>
+      <c r="P46" s="60"/>
+      <c r="Q46" s="64" t="s">
         <v>71</v>
       </c>
-      <c r="R46" s="48" t="s">
+      <c r="R46" s="71" t="s">
         <v>72</v>
       </c>
-      <c r="S46" s="14" t="s">
+      <c r="S46" s="69" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="47" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A47" s="41">
+    <row r="47" s="7" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A47" s="60">
         <v>30240011</v>
       </c>
-      <c r="B47" s="42">
+      <c r="B47" s="61">
         <v>102400</v>
       </c>
-      <c r="C47" s="26" t="s">
+      <c r="C47" s="61" t="s">
         <v>32</v>
       </c>
-      <c r="D47" s="45">
+      <c r="D47" s="60">
         <v>32442</v>
       </c>
-      <c r="E47" s="45" t="s">
+      <c r="E47" s="60" t="s">
         <v>74</v>
       </c>
-      <c r="F47" s="41" t="s">
+      <c r="F47" s="60" t="s">
         <v>34</v>
       </c>
-      <c r="G47" s="41"/>
-      <c r="H47" s="41"/>
-      <c r="I47" s="41" t="s">
+      <c r="G47" s="60"/>
+      <c r="H47" s="60"/>
+      <c r="I47" s="60" t="s">
         <v>75</v>
       </c>
-      <c r="J47" s="41"/>
-      <c r="K47" s="43"/>
-      <c r="L47" s="41" t="s">
+      <c r="J47" s="60"/>
+      <c r="K47" s="62"/>
+      <c r="L47" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="M47" s="41" t="s">
+      <c r="M47" s="60" t="s">
         <v>57</v>
       </c>
-      <c r="N47" s="41"/>
-      <c r="O47" s="41"/>
-      <c r="P47" s="41"/>
-      <c r="Q47" s="41"/>
-      <c r="R47" s="11"/>
-      <c r="S47" s="30"/>
-    </row>
-    <row r="48" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A48" s="41">
+      <c r="N47" s="60"/>
+      <c r="O47" s="60"/>
+      <c r="P47" s="60"/>
+      <c r="Q47" s="60"/>
+      <c r="R47" s="63"/>
+      <c r="S47" s="66"/>
+    </row>
+    <row r="48" s="7" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A48" s="60">
         <v>30240012</v>
       </c>
-      <c r="B48" s="42">
+      <c r="B48" s="61">
         <v>102400</v>
       </c>
-      <c r="C48" s="26" t="s">
+      <c r="C48" s="61" t="s">
         <v>32</v>
       </c>
-      <c r="D48" s="45">
+      <c r="D48" s="60">
         <v>32443</v>
       </c>
-      <c r="E48" s="45" t="s">
+      <c r="E48" s="60" t="s">
         <v>76</v>
       </c>
-      <c r="F48" s="41" t="s">
+      <c r="F48" s="60" t="s">
         <v>53</v>
       </c>
-      <c r="G48" s="41">
+      <c r="G48" s="60">
         <v>2024001</v>
       </c>
-      <c r="H48" s="41" t="s">
+      <c r="H48" s="60" t="s">
         <v>60</v>
       </c>
-      <c r="I48" s="41" t="s">
+      <c r="I48" s="60" t="s">
         <v>66</v>
       </c>
-      <c r="J48" s="41"/>
-      <c r="K48" s="43" t="s">
+      <c r="J48" s="60"/>
+      <c r="K48" s="62" t="s">
         <v>94</v>
       </c>
-      <c r="L48" s="41"/>
-      <c r="M48" s="41"/>
-      <c r="N48" s="41"/>
-      <c r="O48" s="41"/>
-      <c r="P48" s="41"/>
-      <c r="Q48" s="41"/>
-      <c r="R48" s="11"/>
-      <c r="S48" s="30"/>
-    </row>
-    <row r="49" s="3" customFormat="1" ht="16.5" spans="1:22">
-      <c r="A49" s="41">
+      <c r="L48" s="60"/>
+      <c r="M48" s="60"/>
+      <c r="N48" s="60"/>
+      <c r="O48" s="60"/>
+      <c r="P48" s="60"/>
+      <c r="Q48" s="60"/>
+      <c r="R48" s="63"/>
+      <c r="S48" s="66"/>
+    </row>
+    <row r="49" s="8" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A49" s="72">
         <v>30170001</v>
       </c>
-      <c r="B49" s="42">
+      <c r="B49" s="73">
         <v>101700</v>
       </c>
-      <c r="C49" s="26" t="s">
+      <c r="C49" s="73" t="s">
         <v>95</v>
       </c>
-      <c r="D49" s="45">
+      <c r="D49" s="72">
         <v>301701</v>
       </c>
-      <c r="E49" s="45" t="s">
+      <c r="E49" s="72" t="s">
         <v>96</v>
       </c>
-      <c r="F49" s="41" t="s">
+      <c r="F49" s="72" t="s">
         <v>79</v>
       </c>
-      <c r="G49" s="41">
+      <c r="G49" s="72">
         <v>2017001</v>
       </c>
-      <c r="H49" s="41" t="s">
+      <c r="H49" s="72" t="s">
         <v>60</v>
       </c>
-      <c r="I49" s="41" t="s">
+      <c r="I49" s="72" t="s">
         <v>80</v>
       </c>
-      <c r="J49" s="41"/>
-      <c r="K49" s="43" t="s">
+      <c r="J49" s="72"/>
+      <c r="K49" s="74" t="s">
         <v>97</v>
       </c>
-      <c r="L49" s="41"/>
-      <c r="M49" s="41"/>
-      <c r="N49" s="41"/>
-      <c r="O49" s="41"/>
-      <c r="P49" s="41"/>
-      <c r="Q49" s="41"/>
-      <c r="R49" s="11"/>
-      <c r="S49" s="30"/>
-    </row>
-    <row r="50" s="3" customFormat="1" ht="16.5" spans="1:22">
-      <c r="A50" s="41">
+      <c r="L49" s="72"/>
+      <c r="M49" s="72"/>
+      <c r="N49" s="72"/>
+      <c r="O49" s="72"/>
+      <c r="P49" s="72"/>
+      <c r="Q49" s="72"/>
+      <c r="R49" s="75"/>
+      <c r="S49" s="76"/>
+    </row>
+    <row r="50" s="8" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A50" s="72">
         <v>30170002</v>
       </c>
-      <c r="B50" s="42">
+      <c r="B50" s="73">
         <v>101700</v>
       </c>
-      <c r="C50" s="26" t="s">
+      <c r="C50" s="73" t="s">
         <v>95</v>
       </c>
-      <c r="D50" s="45">
+      <c r="D50" s="72">
         <v>301702</v>
       </c>
-      <c r="E50" s="45" t="s">
+      <c r="E50" s="72" t="s">
         <v>98</v>
       </c>
-      <c r="F50" s="41" t="s">
+      <c r="F50" s="72" t="s">
         <v>83</v>
       </c>
-      <c r="G50" s="41">
+      <c r="G50" s="72">
         <v>2017001</v>
       </c>
-      <c r="H50" s="41" t="s">
+      <c r="H50" s="72" t="s">
         <v>60</v>
       </c>
-      <c r="I50" s="41" t="s">
+      <c r="I50" s="72" t="s">
         <v>80</v>
       </c>
-      <c r="J50" s="41"/>
-      <c r="K50" s="43" t="s">
+      <c r="J50" s="72"/>
+      <c r="K50" s="74" t="s">
         <v>97</v>
       </c>
-      <c r="L50" s="41"/>
-      <c r="M50" s="41"/>
-      <c r="N50" s="41"/>
-      <c r="O50" s="41"/>
-      <c r="P50" s="41"/>
-      <c r="Q50" s="41"/>
-      <c r="R50" s="11"/>
-      <c r="S50" s="30"/>
-    </row>
-    <row r="51" s="3" customFormat="1" ht="16.5" spans="1:22">
-      <c r="A51" s="41">
+      <c r="L50" s="72"/>
+      <c r="M50" s="72"/>
+      <c r="N50" s="72"/>
+      <c r="O50" s="72"/>
+      <c r="P50" s="72"/>
+      <c r="Q50" s="72"/>
+      <c r="R50" s="75"/>
+      <c r="S50" s="76"/>
+    </row>
+    <row r="51" s="9" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A51" s="55">
         <v>30220001</v>
       </c>
-      <c r="B51" s="42">
+      <c r="B51" s="56">
         <v>102200</v>
       </c>
-      <c r="C51" s="26" t="s">
+      <c r="C51" s="56" t="s">
         <v>99</v>
       </c>
-      <c r="D51" s="45">
+      <c r="D51" s="55">
         <v>302201</v>
       </c>
-      <c r="E51" s="45" t="s">
+      <c r="E51" s="55" t="s">
         <v>100</v>
       </c>
-      <c r="F51" s="41" t="s">
+      <c r="F51" s="55" t="s">
         <v>101</v>
       </c>
-      <c r="G51" s="41">
+      <c r="G51" s="55">
         <v>2022001</v>
       </c>
-      <c r="H51" s="41" t="s">
+      <c r="H51" s="55" t="s">
         <v>60</v>
       </c>
-      <c r="I51" s="41"/>
-      <c r="J51" s="41"/>
-      <c r="K51" s="43" t="s">
+      <c r="I51" s="55"/>
+      <c r="J51" s="55"/>
+      <c r="K51" s="77" t="s">
         <v>102</v>
       </c>
-      <c r="L51" s="41" t="s">
+      <c r="L51" s="55" t="s">
         <v>103</v>
       </c>
-      <c r="M51" s="41"/>
-      <c r="N51" s="41"/>
-      <c r="O51" s="41"/>
-      <c r="P51" s="41"/>
-      <c r="Q51" s="41"/>
-      <c r="R51" s="11"/>
-      <c r="S51" s="30"/>
-    </row>
-    <row r="52" s="3" customFormat="1" ht="16.5" spans="1:22">
-      <c r="A52" s="41">
+      <c r="M51" s="55"/>
+      <c r="N51" s="55"/>
+      <c r="O51" s="55"/>
+      <c r="P51" s="55"/>
+      <c r="Q51" s="55"/>
+      <c r="R51" s="78"/>
+      <c r="S51" s="79"/>
+    </row>
+    <row r="52" s="9" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A52" s="55">
         <v>30220002</v>
       </c>
-      <c r="B52" s="42">
+      <c r="B52" s="56">
         <v>102200</v>
       </c>
-      <c r="C52" s="26" t="s">
+      <c r="C52" s="56" t="s">
         <v>99</v>
       </c>
-      <c r="D52" s="45">
+      <c r="D52" s="55">
         <v>302202</v>
       </c>
-      <c r="E52" s="45" t="s">
+      <c r="E52" s="55" t="s">
         <v>104</v>
       </c>
-      <c r="F52" s="41" t="s">
+      <c r="F52" s="55" t="s">
         <v>101</v>
       </c>
-      <c r="G52" s="41">
+      <c r="G52" s="55">
         <v>2022001</v>
       </c>
-      <c r="H52" s="41" t="s">
+      <c r="H52" s="55" t="s">
         <v>60</v>
       </c>
-      <c r="I52" s="41"/>
-      <c r="J52" s="41"/>
-      <c r="K52" s="43" t="s">
+      <c r="I52" s="55"/>
+      <c r="J52" s="55"/>
+      <c r="K52" s="77" t="s">
         <v>105</v>
       </c>
-      <c r="L52" s="41" t="s">
+      <c r="L52" s="55" t="s">
         <v>103</v>
       </c>
-      <c r="M52" s="41"/>
-      <c r="N52" s="41"/>
-      <c r="O52" s="41"/>
-      <c r="P52" s="41"/>
-      <c r="Q52" s="41"/>
-      <c r="R52" s="11"/>
-      <c r="S52" s="30"/>
-    </row>
-    <row r="53" s="7" customFormat="1" ht="16.5" spans="1:22">
-      <c r="A53" s="56">
+      <c r="M52" s="55"/>
+      <c r="N52" s="55"/>
+      <c r="O52" s="55"/>
+      <c r="P52" s="55"/>
+      <c r="Q52" s="55"/>
+      <c r="R52" s="78"/>
+      <c r="S52" s="79"/>
+    </row>
+    <row r="53" s="10" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A53" s="80">
         <v>30210001</v>
       </c>
-      <c r="B53" s="57">
+      <c r="B53" s="81">
         <v>102100</v>
       </c>
-      <c r="C53" s="57" t="s">
+      <c r="C53" s="81" t="s">
         <v>106</v>
       </c>
-      <c r="D53" s="56">
+      <c r="D53" s="80">
         <v>302101</v>
       </c>
-      <c r="E53" s="56" t="s">
+      <c r="E53" s="80" t="s">
         <v>107</v>
       </c>
-      <c r="F53" s="56" t="s">
+      <c r="F53" s="80" t="s">
         <v>108</v>
       </c>
-      <c r="G53" s="56">
+      <c r="G53" s="80">
         <v>2021001</v>
       </c>
-      <c r="H53" s="56" t="s">
+      <c r="H53" s="80" t="s">
         <v>60</v>
       </c>
-      <c r="I53" s="56" t="s">
+      <c r="I53" s="80" t="s">
         <v>80</v>
       </c>
-      <c r="J53" s="56"/>
-      <c r="K53" s="58" t="s">
+      <c r="J53" s="80"/>
+      <c r="K53" s="82" t="s">
         <v>109</v>
       </c>
-      <c r="L53" s="56" t="s">
+      <c r="L53" s="80" t="s">
         <v>110</v>
       </c>
-      <c r="M53" s="56"/>
-      <c r="N53" s="56"/>
-      <c r="O53" s="56"/>
-      <c r="P53" s="56"/>
-      <c r="Q53" s="56"/>
-      <c r="R53" s="56"/>
-      <c r="S53" s="59"/>
-    </row>
-    <row r="54" s="7" customFormat="1" ht="16.5" spans="1:22">
-      <c r="A54" s="56">
+      <c r="M53" s="80"/>
+      <c r="N53" s="80"/>
+      <c r="O53" s="80"/>
+      <c r="P53" s="80"/>
+      <c r="Q53" s="80"/>
+      <c r="R53" s="80"/>
+      <c r="S53" s="83"/>
+    </row>
+    <row r="54" s="10" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A54" s="80">
         <v>30210002</v>
       </c>
-      <c r="B54" s="57">
+      <c r="B54" s="81">
         <v>102100</v>
       </c>
-      <c r="C54" s="57" t="s">
+      <c r="C54" s="81" t="s">
         <v>106</v>
       </c>
-      <c r="D54" s="56">
+      <c r="D54" s="80">
         <v>302102</v>
       </c>
-      <c r="E54" s="56" t="s">
+      <c r="E54" s="80" t="s">
         <v>111</v>
       </c>
-      <c r="F54" s="56" t="s">
+      <c r="F54" s="80" t="s">
         <v>34</v>
       </c>
-      <c r="G54" s="56"/>
-      <c r="H54" s="56"/>
-      <c r="I54" s="56" t="s">
+      <c r="G54" s="80"/>
+      <c r="H54" s="80"/>
+      <c r="I54" s="80" t="s">
         <v>112</v>
       </c>
-      <c r="J54" s="56"/>
-      <c r="K54" s="58"/>
-      <c r="L54" s="56"/>
-      <c r="M54" s="56" t="s">
+      <c r="J54" s="80"/>
+      <c r="K54" s="82"/>
+      <c r="L54" s="80"/>
+      <c r="M54" s="80" t="s">
         <v>37</v>
       </c>
-      <c r="N54" s="56" t="s">
+      <c r="N54" s="80" t="s">
         <v>113</v>
       </c>
-      <c r="O54" s="56"/>
-      <c r="P54" s="56"/>
-      <c r="Q54" s="56" t="s">
+      <c r="O54" s="80"/>
+      <c r="P54" s="80"/>
+      <c r="Q54" s="80" t="s">
         <v>114</v>
       </c>
-      <c r="R54" s="56"/>
-      <c r="S54" s="59"/>
-    </row>
-    <row r="55" s="8" customFormat="1" ht="16.5" spans="1:22">
-      <c r="A55" s="60">
+      <c r="R54" s="80"/>
+      <c r="S54" s="83"/>
+    </row>
+    <row r="55" s="11" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A55" s="84">
         <v>30180001</v>
       </c>
-      <c r="B55" s="61">
+      <c r="B55" s="85">
         <v>101800</v>
       </c>
-      <c r="C55" s="61" t="s">
+      <c r="C55" s="85" t="s">
         <v>115</v>
       </c>
-      <c r="D55" s="60">
+      <c r="D55" s="84">
         <v>301801</v>
       </c>
-      <c r="E55" s="60" t="s">
+      <c r="E55" s="84" t="s">
         <v>80</v>
       </c>
-      <c r="F55" s="60" t="s">
+      <c r="F55" s="84" t="s">
         <v>116</v>
       </c>
-      <c r="G55" s="60">
+      <c r="G55" s="84">
         <v>2018001</v>
       </c>
-      <c r="H55" s="60" t="s">
+      <c r="H55" s="84" t="s">
         <v>60</v>
       </c>
-      <c r="I55" s="60" t="s">
+      <c r="I55" s="84" t="s">
         <v>80</v>
       </c>
-      <c r="J55" s="60"/>
-      <c r="K55" s="62">
+      <c r="J55" s="84"/>
+      <c r="K55" s="86">
         <v>10180041</v>
       </c>
-      <c r="L55" s="60"/>
-      <c r="M55" s="60"/>
-      <c r="N55" s="60"/>
-      <c r="O55" s="60"/>
-      <c r="P55" s="60"/>
-      <c r="Q55" s="60"/>
-      <c r="R55" s="60"/>
-      <c r="S55" s="63"/>
-    </row>
-    <row r="56" ht="16.5" spans="1:22">
-      <c r="S56"/>
-      <c r="U56" s="1"/>
-      <c r="V56" s="1"/>
-    </row>
-    <row r="57" ht="16.5" spans="1:22">
-      <c r="S57"/>
-      <c r="U57" s="1"/>
-      <c r="V57" s="1"/>
+      <c r="L55" s="84"/>
+      <c r="M55" s="84"/>
+      <c r="N55" s="84"/>
+      <c r="O55" s="84"/>
+      <c r="P55" s="84"/>
+      <c r="Q55" s="84"/>
+      <c r="R55" s="84"/>
+      <c r="S55" s="87"/>
+    </row>
+    <row r="56" s="12" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A56" s="88">
+        <v>30250001</v>
+      </c>
+      <c r="B56" s="89">
+        <v>102500</v>
+      </c>
+      <c r="C56" s="89" t="s">
+        <v>117</v>
+      </c>
+      <c r="D56" s="88">
+        <v>302501</v>
+      </c>
+      <c r="E56" s="88" t="s">
+        <v>107</v>
+      </c>
+      <c r="F56" s="88" t="s">
+        <v>108</v>
+      </c>
+      <c r="G56" s="88">
+        <v>2025001</v>
+      </c>
+      <c r="H56" s="88" t="s">
+        <v>60</v>
+      </c>
+      <c r="I56" s="88" t="s">
+        <v>80</v>
+      </c>
+      <c r="J56" s="88"/>
+      <c r="K56" s="90"/>
+      <c r="L56" s="88"/>
+      <c r="M56" s="88"/>
+      <c r="N56" s="88"/>
+      <c r="O56" s="88"/>
+      <c r="P56" s="88"/>
+      <c r="Q56" s="88"/>
+      <c r="R56" s="88"/>
+      <c r="S56" s="91"/>
+    </row>
+    <row r="57" s="12" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A57" s="88">
+        <v>30250002</v>
+      </c>
+      <c r="B57" s="89">
+        <v>102500</v>
+      </c>
+      <c r="C57" s="89" t="s">
+        <v>117</v>
+      </c>
+      <c r="D57" s="88">
+        <v>302502</v>
+      </c>
+      <c r="E57" s="88" t="s">
+        <v>118</v>
+      </c>
+      <c r="F57" s="88" t="s">
+        <v>119</v>
+      </c>
+      <c r="G57" s="88">
+        <v>2025001</v>
+      </c>
+      <c r="H57" s="88" t="s">
+        <v>60</v>
+      </c>
+      <c r="I57" s="88" t="s">
+        <v>80</v>
+      </c>
+      <c r="J57" s="88"/>
+      <c r="K57" s="90"/>
+      <c r="L57" s="88"/>
+      <c r="M57" s="88"/>
+      <c r="N57" s="88"/>
+      <c r="O57" s="88"/>
+      <c r="P57" s="88"/>
+      <c r="Q57" s="88"/>
+      <c r="R57" s="88"/>
+      <c r="S57" s="91"/>
+    </row>
+    <row r="58" s="12" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A58" s="88">
+        <v>30250003</v>
+      </c>
+      <c r="B58" s="89">
+        <v>102500</v>
+      </c>
+      <c r="C58" s="89" t="s">
+        <v>117</v>
+      </c>
+      <c r="D58" s="88">
+        <v>302503</v>
+      </c>
+      <c r="E58" s="88" t="s">
+        <v>120</v>
+      </c>
+      <c r="F58" s="88" t="s">
+        <v>121</v>
+      </c>
+      <c r="G58" s="88">
+        <v>2025001</v>
+      </c>
+      <c r="H58" s="88" t="s">
+        <v>60</v>
+      </c>
+      <c r="I58" s="88" t="s">
+        <v>80</v>
+      </c>
+      <c r="J58" s="88"/>
+      <c r="K58" s="90"/>
+      <c r="L58" s="88"/>
+      <c r="M58" s="88"/>
+      <c r="N58" s="88"/>
+      <c r="O58" s="88"/>
+      <c r="P58" s="88"/>
+      <c r="Q58" s="88"/>
+      <c r="R58" s="88"/>
+      <c r="S58" s="91"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2">
@@ -4338,10 +4559,10 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -4349,7 +4570,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -4357,7 +4578,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:8">
@@ -4365,16 +4586,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:8">
@@ -4382,16 +4603,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:8">
@@ -4399,16 +4620,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:8">
@@ -4416,16 +4637,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="F7" s="1">
         <v>2</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:8">
@@ -4433,16 +4654,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="F8" s="1">
         <v>3</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:8">
@@ -4450,16 +4671,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="F9" s="1">
         <v>4</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:8">
@@ -4467,16 +4688,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="F10" s="1">
         <v>5</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:8">
@@ -4484,16 +4705,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="F11" s="1">
         <v>6</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:8">
@@ -4501,16 +4722,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F12" s="1">
         <v>7</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:8">
@@ -4518,16 +4739,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="F13" s="1">
         <v>8</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:8">
@@ -4535,16 +4756,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="F14" s="1">
         <v>9</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:8">
@@ -4552,16 +4773,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="F15" s="1">
         <v>10</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:8">
@@ -4569,16 +4790,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="F16" s="1">
         <v>11</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:8">
@@ -4586,16 +4807,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="F17" s="1">
         <v>12</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:8">
@@ -4603,16 +4824,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="F18" s="1">
         <v>13</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:8">
@@ -4620,16 +4841,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="F19" s="1">
         <v>14</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:8">
@@ -4637,16 +4858,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="F20" s="1">
         <v>15</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:8">
@@ -4654,16 +4875,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="F21" s="1">
         <v>16</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:8">
@@ -4671,16 +4892,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="F22" s="1">
         <v>17</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:8">
@@ -4688,16 +4909,16 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="F23" s="1">
         <v>18</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:8">
@@ -4705,16 +4926,16 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="F24" s="1">
         <v>19</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -4722,7 +4943,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -4730,7 +4951,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -4738,7 +4959,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -4746,7 +4967,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -4754,7 +4975,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -4762,7 +4983,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -4770,7 +4991,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -4778,7 +4999,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -4786,7 +5007,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -4794,7 +5015,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -4802,7 +5023,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -4810,7 +5031,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -4818,7 +5039,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -4826,7 +5047,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -4834,7 +5055,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -4842,7 +5063,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -4850,7 +5071,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -4858,7 +5079,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -4866,7 +5087,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -4874,7 +5095,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -4882,7 +5103,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -4890,7 +5111,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -4898,7 +5119,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialAuxiliary.xlsx
+++ b/slots/resources/sample/SpecialAuxiliary.xlsx
@@ -268,7 +268,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="213">
   <si>
     <t>小游戏模式ID</t>
   </si>
@@ -597,10 +597,10 @@
     <t>10_1</t>
   </si>
   <si>
-    <t>10210042|10210032</t>
-  </si>
-  <si>
-    <t>概率改出wild和scatter</t>
+    <t>10210021|10210042|10210032</t>
+  </si>
+  <si>
+    <t>概率改出wild、scatter、bonus</t>
   </si>
   <si>
     <t>探宝玩法</t>
@@ -622,6 +622,12 @@
   </si>
   <si>
     <t>寒冰王座</t>
+  </si>
+  <si>
+    <t>10250021|10250032</t>
+  </si>
+  <si>
+    <t>概率出现百搭符号+概率改出SCATTER符号</t>
   </si>
   <si>
     <t>免费游戏-免费旋转-15次</t>
@@ -4411,8 +4417,12 @@
         <v>80</v>
       </c>
       <c r="J56" s="88"/>
-      <c r="K56" s="90"/>
-      <c r="L56" s="88"/>
+      <c r="K56" s="90" t="s">
+        <v>118</v>
+      </c>
+      <c r="L56" s="88" t="s">
+        <v>119</v>
+      </c>
       <c r="M56" s="88"/>
       <c r="N56" s="88"/>
       <c r="O56" s="88"/>
@@ -4435,10 +4445,10 @@
         <v>302502</v>
       </c>
       <c r="E57" s="88" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F57" s="88" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G57" s="88">
         <v>2025001</v>
@@ -4450,8 +4460,12 @@
         <v>80</v>
       </c>
       <c r="J57" s="88"/>
-      <c r="K57" s="90"/>
-      <c r="L57" s="88"/>
+      <c r="K57" s="90" t="s">
+        <v>118</v>
+      </c>
+      <c r="L57" s="88" t="s">
+        <v>119</v>
+      </c>
       <c r="M57" s="88"/>
       <c r="N57" s="88"/>
       <c r="O57" s="88"/>
@@ -4474,10 +4488,10 @@
         <v>302503</v>
       </c>
       <c r="E58" s="88" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F58" s="88" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G58" s="88">
         <v>2025001</v>
@@ -4489,8 +4503,12 @@
         <v>80</v>
       </c>
       <c r="J58" s="88"/>
-      <c r="K58" s="90"/>
-      <c r="L58" s="88"/>
+      <c r="K58" s="90" t="s">
+        <v>118</v>
+      </c>
+      <c r="L58" s="88" t="s">
+        <v>119</v>
+      </c>
       <c r="M58" s="88"/>
       <c r="N58" s="88"/>
       <c r="O58" s="88"/>
@@ -4559,10 +4577,10 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -4570,7 +4588,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -4578,7 +4596,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:8">
@@ -4586,16 +4604,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:8">
@@ -4603,16 +4621,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:8">
@@ -4620,16 +4638,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:8">
@@ -4637,16 +4655,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F7" s="1">
         <v>2</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:8">
@@ -4654,16 +4672,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F8" s="1">
         <v>3</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:8">
@@ -4671,16 +4689,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F9" s="1">
         <v>4</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:8">
@@ -4688,16 +4706,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F10" s="1">
         <v>5</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:8">
@@ -4705,16 +4723,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F11" s="1">
         <v>6</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:8">
@@ -4722,16 +4740,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F12" s="1">
         <v>7</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:8">
@@ -4739,16 +4757,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F13" s="1">
         <v>8</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:8">
@@ -4756,16 +4774,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F14" s="1">
         <v>9</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:8">
@@ -4773,16 +4791,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F15" s="1">
         <v>10</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:8">
@@ -4790,16 +4808,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F16" s="1">
         <v>11</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:8">
@@ -4807,16 +4825,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F17" s="1">
         <v>12</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:8">
@@ -4824,16 +4842,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F18" s="1">
         <v>13</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:8">
@@ -4841,16 +4859,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F19" s="1">
         <v>14</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:8">
@@ -4858,16 +4876,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F20" s="1">
         <v>15</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:8">
@@ -4875,16 +4893,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F21" s="1">
         <v>16</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:8">
@@ -4892,16 +4910,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F22" s="1">
         <v>17</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:8">
@@ -4909,16 +4927,16 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F23" s="1">
         <v>18</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:8">
@@ -4926,16 +4944,16 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F24" s="1">
         <v>19</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -4943,7 +4961,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -4951,7 +4969,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -4959,7 +4977,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -4967,7 +4985,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -4975,7 +4993,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -4983,7 +5001,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -4991,7 +5009,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -4999,7 +5017,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -5007,7 +5025,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -5015,7 +5033,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -5023,7 +5041,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -5031,7 +5049,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -5039,7 +5057,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -5047,7 +5065,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -5055,7 +5073,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -5063,7 +5081,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -5071,7 +5089,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -5079,7 +5097,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -5087,7 +5105,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -5095,7 +5113,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -5103,7 +5121,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -5111,7 +5129,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -5119,7 +5137,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialAuxiliary.xlsx
+++ b/slots/resources/sample/SpecialAuxiliary.xlsx
@@ -268,7 +268,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="216">
   <si>
     <t>小游戏模式ID</t>
   </si>
@@ -640,6 +640,15 @@
   </si>
   <si>
     <t>20_1</t>
+  </si>
+  <si>
+    <t>蒸汽时代</t>
+  </si>
+  <si>
+    <t>免费游戏-免费旋转-12次</t>
+  </si>
+  <si>
+    <t>免费游戏-免费旋转-14次</t>
   </si>
   <si>
     <t>typeID</t>
@@ -1102,6 +1111,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1115,12 +1130,6 @@
     <font>
       <b/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1140,7 +1149,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="50">
+  <fills count="48">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1179,12 +1188,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1198,6 +1201,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1234,18 +1243,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="-0.25"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1566,7 +1563,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1590,16 +1587,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="22" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1608,92 +1605,92 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1707,7 +1704,7 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1816,19 +1813,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="176" fontId="1" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="176" fontId="1" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -1836,25 +1821,35 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1864,14 +1859,14 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="3" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
@@ -2211,7 +2206,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S58"/>
+  <dimension ref="A1:S61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14.125" customWidth="1"/>
@@ -3611,7 +3606,7 @@
       </c>
       <c r="J37" s="60"/>
       <c r="K37" s="62"/>
-      <c r="L37" s="63" t="s">
+      <c r="L37" s="60" t="s">
         <v>36</v>
       </c>
       <c r="M37" s="60" t="s">
@@ -3622,13 +3617,13 @@
       </c>
       <c r="O37" s="60"/>
       <c r="P37" s="60"/>
-      <c r="Q37" s="64" t="s">
+      <c r="Q37" s="63" t="s">
         <v>39</v>
       </c>
-      <c r="R37" s="65" t="s">
+      <c r="R37" s="64" t="s">
         <v>40</v>
       </c>
-      <c r="S37" s="66" t="s">
+      <c r="S37" s="65" t="s">
         <v>41</v>
       </c>
     </row>
@@ -3658,7 +3653,7 @@
       </c>
       <c r="J38" s="60"/>
       <c r="K38" s="62"/>
-      <c r="L38" s="63" t="s">
+      <c r="L38" s="60" t="s">
         <v>36</v>
       </c>
       <c r="M38" s="60" t="s">
@@ -3669,13 +3664,13 @@
       </c>
       <c r="O38" s="60"/>
       <c r="P38" s="60"/>
-      <c r="Q38" s="64" t="s">
+      <c r="Q38" s="63" t="s">
         <v>44</v>
       </c>
-      <c r="R38" s="65" t="s">
+      <c r="R38" s="64" t="s">
         <v>40</v>
       </c>
-      <c r="S38" s="66"/>
+      <c r="S38" s="65"/>
     </row>
     <row r="39" s="7" customFormat="1" ht="16.5" spans="1:19">
       <c r="A39" s="60">
@@ -3703,7 +3698,7 @@
       </c>
       <c r="J39" s="60"/>
       <c r="K39" s="62"/>
-      <c r="L39" s="63" t="s">
+      <c r="L39" s="60" t="s">
         <v>36</v>
       </c>
       <c r="M39" s="60" t="s">
@@ -3714,13 +3709,13 @@
       </c>
       <c r="O39" s="60"/>
       <c r="P39" s="60"/>
-      <c r="Q39" s="64" t="s">
+      <c r="Q39" s="63" t="s">
         <v>47</v>
       </c>
-      <c r="R39" s="65" t="s">
+      <c r="R39" s="64" t="s">
         <v>40</v>
       </c>
-      <c r="S39" s="66"/>
+      <c r="S39" s="65"/>
     </row>
     <row r="40" s="7" customFormat="1" ht="15" customHeight="1" spans="1:19">
       <c r="A40" s="60">
@@ -3748,7 +3743,7 @@
       </c>
       <c r="J40" s="60"/>
       <c r="K40" s="62"/>
-      <c r="L40" s="63" t="s">
+      <c r="L40" s="60" t="s">
         <v>36</v>
       </c>
       <c r="M40" s="60" t="s">
@@ -3759,54 +3754,54 @@
       </c>
       <c r="O40" s="60"/>
       <c r="P40" s="60"/>
-      <c r="Q40" s="64" t="s">
+      <c r="Q40" s="63" t="s">
         <v>50</v>
       </c>
-      <c r="R40" s="65" t="s">
+      <c r="R40" s="64" t="s">
         <v>40</v>
       </c>
-      <c r="S40" s="66"/>
+      <c r="S40" s="65"/>
     </row>
     <row r="41" s="7" customFormat="1" ht="15" customHeight="1" spans="1:19">
-      <c r="A41" s="63">
+      <c r="A41" s="60">
         <v>30240005</v>
       </c>
-      <c r="B41" s="67">
+      <c r="B41" s="61">
         <v>102400</v>
       </c>
       <c r="C41" s="61" t="s">
         <v>32</v>
       </c>
-      <c r="D41" s="63">
+      <c r="D41" s="60">
         <v>32411</v>
       </c>
-      <c r="E41" s="63" t="s">
+      <c r="E41" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="F41" s="63" t="s">
+      <c r="F41" s="60" t="s">
         <v>34</v>
       </c>
-      <c r="G41" s="63"/>
-      <c r="H41" s="63"/>
-      <c r="I41" s="63" t="s">
+      <c r="G41" s="60"/>
+      <c r="H41" s="60"/>
+      <c r="I41" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="J41" s="63"/>
-      <c r="K41" s="68"/>
-      <c r="L41" s="63" t="s">
+      <c r="J41" s="60"/>
+      <c r="K41" s="62"/>
+      <c r="L41" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="M41" s="63" t="s">
+      <c r="M41" s="60" t="s">
         <v>53</v>
       </c>
-      <c r="N41" s="63"/>
-      <c r="O41" s="63" t="s">
+      <c r="N41" s="60"/>
+      <c r="O41" s="60" t="s">
         <v>54</v>
       </c>
-      <c r="P41" s="63"/>
-      <c r="Q41" s="69"/>
-      <c r="R41" s="69"/>
-      <c r="S41" s="66"/>
+      <c r="P41" s="60"/>
+      <c r="Q41" s="63"/>
+      <c r="R41" s="63"/>
+      <c r="S41" s="65"/>
     </row>
     <row r="42" s="7" customFormat="1" ht="16.5" spans="1:19">
       <c r="A42" s="60">
@@ -3848,8 +3843,8 @@
       </c>
       <c r="P42" s="60"/>
       <c r="Q42" s="60"/>
-      <c r="R42" s="63"/>
-      <c r="S42" s="66"/>
+      <c r="R42" s="60"/>
+      <c r="S42" s="65"/>
     </row>
     <row r="43" s="7" customFormat="1" ht="16.5" spans="1:19">
       <c r="A43" s="60">
@@ -3889,8 +3884,8 @@
       <c r="O43" s="60"/>
       <c r="P43" s="60"/>
       <c r="Q43" s="60"/>
-      <c r="R43" s="63"/>
-      <c r="S43" s="66"/>
+      <c r="R43" s="60"/>
+      <c r="S43" s="65"/>
     </row>
     <row r="44" s="7" customFormat="1" ht="16.5" spans="1:19">
       <c r="A44" s="60">
@@ -3921,7 +3916,7 @@
         <v>63</v>
       </c>
       <c r="J44" s="60"/>
-      <c r="K44" s="70" t="s">
+      <c r="K44" s="66" t="s">
         <v>93</v>
       </c>
       <c r="L44" s="60"/>
@@ -3930,8 +3925,8 @@
       <c r="O44" s="60"/>
       <c r="P44" s="60"/>
       <c r="Q44" s="60"/>
-      <c r="R44" s="63"/>
-      <c r="S44" s="66"/>
+      <c r="R44" s="60"/>
+      <c r="S44" s="65"/>
     </row>
     <row r="45" s="7" customFormat="1" ht="16.5" spans="1:19">
       <c r="A45" s="60">
@@ -3971,8 +3966,8 @@
       <c r="O45" s="60"/>
       <c r="P45" s="60"/>
       <c r="Q45" s="60"/>
-      <c r="R45" s="63"/>
-      <c r="S45" s="66"/>
+      <c r="R45" s="60"/>
+      <c r="S45" s="65"/>
     </row>
     <row r="46" s="7" customFormat="1" ht="16.5" spans="1:19">
       <c r="A46" s="60">
@@ -3999,7 +3994,7 @@
         <v>69</v>
       </c>
       <c r="J46" s="60"/>
-      <c r="K46" s="70"/>
+      <c r="K46" s="66"/>
       <c r="L46" s="60" t="s">
         <v>36</v>
       </c>
@@ -4009,13 +4004,13 @@
       <c r="N46" s="60"/>
       <c r="O46" s="60"/>
       <c r="P46" s="60"/>
-      <c r="Q46" s="64" t="s">
+      <c r="Q46" s="63" t="s">
         <v>71</v>
       </c>
-      <c r="R46" s="71" t="s">
+      <c r="R46" s="67" t="s">
         <v>72</v>
       </c>
-      <c r="S46" s="69" t="s">
+      <c r="S46" s="63" t="s">
         <v>73</v>
       </c>
     </row>
@@ -4055,8 +4050,8 @@
       <c r="O47" s="60"/>
       <c r="P47" s="60"/>
       <c r="Q47" s="60"/>
-      <c r="R47" s="63"/>
-      <c r="S47" s="66"/>
+      <c r="R47" s="60"/>
+      <c r="S47" s="65"/>
     </row>
     <row r="48" s="7" customFormat="1" ht="16.5" spans="1:19">
       <c r="A48" s="60">
@@ -4096,92 +4091,92 @@
       <c r="O48" s="60"/>
       <c r="P48" s="60"/>
       <c r="Q48" s="60"/>
-      <c r="R48" s="63"/>
-      <c r="S48" s="66"/>
+      <c r="R48" s="60"/>
+      <c r="S48" s="65"/>
     </row>
     <row r="49" s="8" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A49" s="72">
+      <c r="A49" s="68">
         <v>30170001</v>
       </c>
-      <c r="B49" s="73">
+      <c r="B49" s="69">
         <v>101700</v>
       </c>
-      <c r="C49" s="73" t="s">
+      <c r="C49" s="69" t="s">
         <v>95</v>
       </c>
-      <c r="D49" s="72">
+      <c r="D49" s="68">
         <v>301701</v>
       </c>
-      <c r="E49" s="72" t="s">
+      <c r="E49" s="68" t="s">
         <v>96</v>
       </c>
-      <c r="F49" s="72" t="s">
+      <c r="F49" s="68" t="s">
         <v>79</v>
       </c>
-      <c r="G49" s="72">
+      <c r="G49" s="68">
         <v>2017001</v>
       </c>
-      <c r="H49" s="72" t="s">
+      <c r="H49" s="68" t="s">
         <v>60</v>
       </c>
-      <c r="I49" s="72" t="s">
+      <c r="I49" s="68" t="s">
         <v>80</v>
       </c>
-      <c r="J49" s="72"/>
-      <c r="K49" s="74" t="s">
+      <c r="J49" s="68"/>
+      <c r="K49" s="70" t="s">
         <v>97</v>
       </c>
-      <c r="L49" s="72"/>
-      <c r="M49" s="72"/>
-      <c r="N49" s="72"/>
-      <c r="O49" s="72"/>
-      <c r="P49" s="72"/>
-      <c r="Q49" s="72"/>
-      <c r="R49" s="75"/>
-      <c r="S49" s="76"/>
+      <c r="L49" s="68"/>
+      <c r="M49" s="68"/>
+      <c r="N49" s="68"/>
+      <c r="O49" s="68"/>
+      <c r="P49" s="68"/>
+      <c r="Q49" s="68"/>
+      <c r="R49" s="68"/>
+      <c r="S49" s="71"/>
     </row>
     <row r="50" s="8" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A50" s="72">
+      <c r="A50" s="68">
         <v>30170002</v>
       </c>
-      <c r="B50" s="73">
+      <c r="B50" s="69">
         <v>101700</v>
       </c>
-      <c r="C50" s="73" t="s">
+      <c r="C50" s="69" t="s">
         <v>95</v>
       </c>
-      <c r="D50" s="72">
+      <c r="D50" s="68">
         <v>301702</v>
       </c>
-      <c r="E50" s="72" t="s">
+      <c r="E50" s="68" t="s">
         <v>98</v>
       </c>
-      <c r="F50" s="72" t="s">
+      <c r="F50" s="68" t="s">
         <v>83</v>
       </c>
-      <c r="G50" s="72">
+      <c r="G50" s="68">
         <v>2017001</v>
       </c>
-      <c r="H50" s="72" t="s">
+      <c r="H50" s="68" t="s">
         <v>60</v>
       </c>
-      <c r="I50" s="72" t="s">
+      <c r="I50" s="68" t="s">
         <v>80</v>
       </c>
-      <c r="J50" s="72"/>
-      <c r="K50" s="74" t="s">
+      <c r="J50" s="68"/>
+      <c r="K50" s="70" t="s">
         <v>97</v>
       </c>
-      <c r="L50" s="72"/>
-      <c r="M50" s="72"/>
-      <c r="N50" s="72"/>
-      <c r="O50" s="72"/>
-      <c r="P50" s="72"/>
-      <c r="Q50" s="72"/>
-      <c r="R50" s="75"/>
-      <c r="S50" s="76"/>
-    </row>
-    <row r="51" s="9" customFormat="1" ht="16.5" spans="1:19">
+      <c r="L50" s="68"/>
+      <c r="M50" s="68"/>
+      <c r="N50" s="68"/>
+      <c r="O50" s="68"/>
+      <c r="P50" s="68"/>
+      <c r="Q50" s="68"/>
+      <c r="R50" s="68"/>
+      <c r="S50" s="71"/>
+    </row>
+    <row r="51" s="5" customFormat="1" ht="16.5" spans="1:19">
       <c r="A51" s="55">
         <v>30220001</v>
       </c>
@@ -4208,7 +4203,7 @@
       </c>
       <c r="I51" s="55"/>
       <c r="J51" s="55"/>
-      <c r="K51" s="77" t="s">
+      <c r="K51" s="72" t="s">
         <v>102</v>
       </c>
       <c r="L51" s="55" t="s">
@@ -4219,10 +4214,10 @@
       <c r="O51" s="55"/>
       <c r="P51" s="55"/>
       <c r="Q51" s="55"/>
-      <c r="R51" s="78"/>
-      <c r="S51" s="79"/>
-    </row>
-    <row r="52" s="9" customFormat="1" ht="16.5" spans="1:19">
+      <c r="R51" s="55"/>
+      <c r="S51" s="73"/>
+    </row>
+    <row r="52" s="5" customFormat="1" ht="16.5" spans="1:19">
       <c r="A52" s="55">
         <v>30220002</v>
       </c>
@@ -4249,7 +4244,7 @@
       </c>
       <c r="I52" s="55"/>
       <c r="J52" s="55"/>
-      <c r="K52" s="77" t="s">
+      <c r="K52" s="72" t="s">
         <v>105</v>
       </c>
       <c r="L52" s="55" t="s">
@@ -4260,262 +4255,379 @@
       <c r="O52" s="55"/>
       <c r="P52" s="55"/>
       <c r="Q52" s="55"/>
-      <c r="R52" s="78"/>
-      <c r="S52" s="79"/>
-    </row>
-    <row r="53" s="10" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A53" s="80">
+      <c r="R52" s="55"/>
+      <c r="S52" s="73"/>
+    </row>
+    <row r="53" s="9" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A53" s="74">
         <v>30210001</v>
       </c>
-      <c r="B53" s="81">
+      <c r="B53" s="75">
         <v>102100</v>
       </c>
-      <c r="C53" s="81" t="s">
+      <c r="C53" s="75" t="s">
         <v>106</v>
       </c>
-      <c r="D53" s="80">
+      <c r="D53" s="74">
         <v>302101</v>
       </c>
-      <c r="E53" s="80" t="s">
+      <c r="E53" s="74" t="s">
         <v>107</v>
       </c>
-      <c r="F53" s="80" t="s">
+      <c r="F53" s="74" t="s">
         <v>108</v>
       </c>
-      <c r="G53" s="80">
+      <c r="G53" s="74">
         <v>2021001</v>
       </c>
-      <c r="H53" s="80" t="s">
+      <c r="H53" s="74" t="s">
         <v>60</v>
       </c>
-      <c r="I53" s="80" t="s">
+      <c r="I53" s="74" t="s">
         <v>80</v>
       </c>
-      <c r="J53" s="80"/>
-      <c r="K53" s="82" t="s">
+      <c r="J53" s="74"/>
+      <c r="K53" s="76" t="s">
         <v>109</v>
       </c>
-      <c r="L53" s="80" t="s">
+      <c r="L53" s="74" t="s">
         <v>110</v>
       </c>
-      <c r="M53" s="80"/>
-      <c r="N53" s="80"/>
-      <c r="O53" s="80"/>
-      <c r="P53" s="80"/>
-      <c r="Q53" s="80"/>
-      <c r="R53" s="80"/>
-      <c r="S53" s="83"/>
-    </row>
-    <row r="54" s="10" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A54" s="80">
+      <c r="M53" s="74"/>
+      <c r="N53" s="74"/>
+      <c r="O53" s="74"/>
+      <c r="P53" s="74"/>
+      <c r="Q53" s="74"/>
+      <c r="R53" s="74"/>
+      <c r="S53" s="77"/>
+    </row>
+    <row r="54" s="9" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A54" s="74">
         <v>30210002</v>
       </c>
-      <c r="B54" s="81">
+      <c r="B54" s="75">
         <v>102100</v>
       </c>
-      <c r="C54" s="81" t="s">
+      <c r="C54" s="75" t="s">
         <v>106</v>
       </c>
-      <c r="D54" s="80">
+      <c r="D54" s="74">
         <v>302102</v>
       </c>
-      <c r="E54" s="80" t="s">
+      <c r="E54" s="74" t="s">
         <v>111</v>
       </c>
-      <c r="F54" s="80" t="s">
+      <c r="F54" s="74" t="s">
         <v>34</v>
       </c>
-      <c r="G54" s="80"/>
-      <c r="H54" s="80"/>
-      <c r="I54" s="80" t="s">
+      <c r="G54" s="74"/>
+      <c r="H54" s="74"/>
+      <c r="I54" s="74" t="s">
         <v>112</v>
       </c>
-      <c r="J54" s="80"/>
-      <c r="K54" s="82"/>
-      <c r="L54" s="80"/>
-      <c r="M54" s="80" t="s">
+      <c r="J54" s="74"/>
+      <c r="K54" s="76"/>
+      <c r="L54" s="74"/>
+      <c r="M54" s="74" t="s">
         <v>37</v>
       </c>
-      <c r="N54" s="80" t="s">
+      <c r="N54" s="74" t="s">
         <v>113</v>
       </c>
-      <c r="O54" s="80"/>
-      <c r="P54" s="80"/>
-      <c r="Q54" s="80" t="s">
+      <c r="O54" s="74"/>
+      <c r="P54" s="74"/>
+      <c r="Q54" s="74" t="s">
         <v>114</v>
       </c>
-      <c r="R54" s="80"/>
-      <c r="S54" s="83"/>
-    </row>
-    <row r="55" s="11" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A55" s="84">
+      <c r="R54" s="74"/>
+      <c r="S54" s="77"/>
+    </row>
+    <row r="55" s="10" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A55" s="78">
         <v>30180001</v>
       </c>
-      <c r="B55" s="85">
+      <c r="B55" s="79">
         <v>101800</v>
       </c>
-      <c r="C55" s="85" t="s">
+      <c r="C55" s="79" t="s">
         <v>115</v>
       </c>
-      <c r="D55" s="84">
+      <c r="D55" s="78">
         <v>301801</v>
       </c>
-      <c r="E55" s="84" t="s">
+      <c r="E55" s="78" t="s">
         <v>80</v>
       </c>
-      <c r="F55" s="84" t="s">
+      <c r="F55" s="78" t="s">
         <v>116</v>
       </c>
-      <c r="G55" s="84">
+      <c r="G55" s="78">
         <v>2018001</v>
       </c>
-      <c r="H55" s="84" t="s">
+      <c r="H55" s="78" t="s">
         <v>60</v>
       </c>
-      <c r="I55" s="84" t="s">
+      <c r="I55" s="78" t="s">
         <v>80</v>
       </c>
-      <c r="J55" s="84"/>
-      <c r="K55" s="86">
+      <c r="J55" s="78"/>
+      <c r="K55" s="80">
         <v>10180041</v>
       </c>
-      <c r="L55" s="84"/>
-      <c r="M55" s="84"/>
-      <c r="N55" s="84"/>
-      <c r="O55" s="84"/>
-      <c r="P55" s="84"/>
-      <c r="Q55" s="84"/>
-      <c r="R55" s="84"/>
-      <c r="S55" s="87"/>
-    </row>
-    <row r="56" s="12" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A56" s="88">
+      <c r="L55" s="78"/>
+      <c r="M55" s="78"/>
+      <c r="N55" s="78"/>
+      <c r="O55" s="78"/>
+      <c r="P55" s="78"/>
+      <c r="Q55" s="78"/>
+      <c r="R55" s="78"/>
+      <c r="S55" s="81"/>
+    </row>
+    <row r="56" s="11" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A56" s="82">
         <v>30250001</v>
       </c>
-      <c r="B56" s="89">
+      <c r="B56" s="83">
         <v>102500</v>
       </c>
-      <c r="C56" s="89" t="s">
+      <c r="C56" s="83" t="s">
         <v>117</v>
       </c>
-      <c r="D56" s="88">
+      <c r="D56" s="82">
         <v>302501</v>
       </c>
-      <c r="E56" s="88" t="s">
+      <c r="E56" s="82" t="s">
         <v>107</v>
       </c>
-      <c r="F56" s="88" t="s">
+      <c r="F56" s="82" t="s">
         <v>108</v>
       </c>
-      <c r="G56" s="88">
+      <c r="G56" s="82">
         <v>2025001</v>
       </c>
-      <c r="H56" s="88" t="s">
+      <c r="H56" s="82" t="s">
         <v>60</v>
       </c>
-      <c r="I56" s="88" t="s">
+      <c r="I56" s="82" t="s">
         <v>80</v>
       </c>
-      <c r="J56" s="88"/>
-      <c r="K56" s="90" t="s">
+      <c r="J56" s="82"/>
+      <c r="K56" s="84" t="s">
         <v>118</v>
       </c>
-      <c r="L56" s="88" t="s">
+      <c r="L56" s="82" t="s">
         <v>119</v>
       </c>
-      <c r="M56" s="88"/>
-      <c r="N56" s="88"/>
-      <c r="O56" s="88"/>
-      <c r="P56" s="88"/>
-      <c r="Q56" s="88"/>
-      <c r="R56" s="88"/>
-      <c r="S56" s="91"/>
-    </row>
-    <row r="57" s="12" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A57" s="88">
+      <c r="M56" s="82"/>
+      <c r="N56" s="82"/>
+      <c r="O56" s="82"/>
+      <c r="P56" s="82"/>
+      <c r="Q56" s="82"/>
+      <c r="R56" s="82"/>
+      <c r="S56" s="85"/>
+    </row>
+    <row r="57" s="11" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A57" s="82">
         <v>30250002</v>
       </c>
-      <c r="B57" s="89">
+      <c r="B57" s="83">
         <v>102500</v>
       </c>
-      <c r="C57" s="89" t="s">
+      <c r="C57" s="83" t="s">
         <v>117</v>
       </c>
-      <c r="D57" s="88">
+      <c r="D57" s="82">
         <v>302502</v>
       </c>
-      <c r="E57" s="88" t="s">
+      <c r="E57" s="82" t="s">
         <v>120</v>
       </c>
-      <c r="F57" s="88" t="s">
+      <c r="F57" s="82" t="s">
         <v>121</v>
       </c>
-      <c r="G57" s="88">
+      <c r="G57" s="82">
         <v>2025001</v>
       </c>
-      <c r="H57" s="88" t="s">
+      <c r="H57" s="82" t="s">
         <v>60</v>
       </c>
-      <c r="I57" s="88" t="s">
+      <c r="I57" s="82" t="s">
         <v>80</v>
       </c>
-      <c r="J57" s="88"/>
-      <c r="K57" s="90" t="s">
+      <c r="J57" s="82"/>
+      <c r="K57" s="84" t="s">
         <v>118</v>
       </c>
-      <c r="L57" s="88" t="s">
+      <c r="L57" s="82" t="s">
         <v>119</v>
       </c>
-      <c r="M57" s="88"/>
-      <c r="N57" s="88"/>
-      <c r="O57" s="88"/>
-      <c r="P57" s="88"/>
-      <c r="Q57" s="88"/>
-      <c r="R57" s="88"/>
-      <c r="S57" s="91"/>
-    </row>
-    <row r="58" s="12" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A58" s="88">
+      <c r="M57" s="82"/>
+      <c r="N57" s="82"/>
+      <c r="O57" s="82"/>
+      <c r="P57" s="82"/>
+      <c r="Q57" s="82"/>
+      <c r="R57" s="82"/>
+      <c r="S57" s="85"/>
+    </row>
+    <row r="58" s="11" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A58" s="82">
         <v>30250003</v>
       </c>
-      <c r="B58" s="89">
+      <c r="B58" s="83">
         <v>102500</v>
       </c>
-      <c r="C58" s="89" t="s">
+      <c r="C58" s="83" t="s">
         <v>117</v>
       </c>
-      <c r="D58" s="88">
+      <c r="D58" s="82">
         <v>302503</v>
       </c>
-      <c r="E58" s="88" t="s">
+      <c r="E58" s="82" t="s">
         <v>122</v>
       </c>
-      <c r="F58" s="88" t="s">
+      <c r="F58" s="82" t="s">
         <v>123</v>
       </c>
-      <c r="G58" s="88">
+      <c r="G58" s="82">
         <v>2025001</v>
       </c>
-      <c r="H58" s="88" t="s">
+      <c r="H58" s="82" t="s">
         <v>60</v>
       </c>
-      <c r="I58" s="88" t="s">
+      <c r="I58" s="82" t="s">
         <v>80</v>
       </c>
-      <c r="J58" s="88"/>
-      <c r="K58" s="90" t="s">
+      <c r="J58" s="82"/>
+      <c r="K58" s="84" t="s">
         <v>118</v>
       </c>
-      <c r="L58" s="88" t="s">
+      <c r="L58" s="82" t="s">
         <v>119</v>
       </c>
-      <c r="M58" s="88"/>
-      <c r="N58" s="88"/>
-      <c r="O58" s="88"/>
-      <c r="P58" s="88"/>
-      <c r="Q58" s="88"/>
-      <c r="R58" s="88"/>
-      <c r="S58" s="91"/>
+      <c r="M58" s="82"/>
+      <c r="N58" s="82"/>
+      <c r="O58" s="82"/>
+      <c r="P58" s="82"/>
+      <c r="Q58" s="82"/>
+      <c r="R58" s="82"/>
+      <c r="S58" s="85"/>
+    </row>
+    <row r="59" s="12" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A59" s="86">
+        <v>30230001</v>
+      </c>
+      <c r="B59" s="87">
+        <v>102300</v>
+      </c>
+      <c r="C59" s="87" t="s">
+        <v>124</v>
+      </c>
+      <c r="D59" s="86">
+        <v>302301</v>
+      </c>
+      <c r="E59" s="86" t="s">
+        <v>107</v>
+      </c>
+      <c r="F59" s="86" t="s">
+        <v>108</v>
+      </c>
+      <c r="G59" s="86">
+        <v>2023001</v>
+      </c>
+      <c r="H59" s="86" t="s">
+        <v>60</v>
+      </c>
+      <c r="I59" s="86" t="s">
+        <v>80</v>
+      </c>
+      <c r="J59" s="86"/>
+      <c r="K59" s="88"/>
+      <c r="L59" s="86"/>
+      <c r="M59" s="86"/>
+      <c r="N59" s="86"/>
+      <c r="O59" s="86"/>
+      <c r="P59" s="86"/>
+      <c r="Q59" s="86"/>
+      <c r="R59" s="86"/>
+      <c r="S59" s="89"/>
+    </row>
+    <row r="60" s="12" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A60" s="86">
+        <v>30230002</v>
+      </c>
+      <c r="B60" s="87">
+        <v>102300</v>
+      </c>
+      <c r="C60" s="87" t="s">
+        <v>124</v>
+      </c>
+      <c r="D60" s="86">
+        <v>302302</v>
+      </c>
+      <c r="E60" s="86" t="s">
+        <v>125</v>
+      </c>
+      <c r="F60" s="86" t="s">
+        <v>79</v>
+      </c>
+      <c r="G60" s="86">
+        <v>2023001</v>
+      </c>
+      <c r="H60" s="86" t="s">
+        <v>60</v>
+      </c>
+      <c r="I60" s="86" t="s">
+        <v>80</v>
+      </c>
+      <c r="J60" s="86"/>
+      <c r="K60" s="88"/>
+      <c r="L60" s="86"/>
+      <c r="M60" s="86"/>
+      <c r="N60" s="86"/>
+      <c r="O60" s="86"/>
+      <c r="P60" s="86"/>
+      <c r="Q60" s="86"/>
+      <c r="R60" s="86"/>
+      <c r="S60" s="89"/>
+    </row>
+    <row r="61" s="12" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A61" s="86">
+        <v>30230003</v>
+      </c>
+      <c r="B61" s="87">
+        <v>102300</v>
+      </c>
+      <c r="C61" s="87" t="s">
+        <v>124</v>
+      </c>
+      <c r="D61" s="86">
+        <v>302303</v>
+      </c>
+      <c r="E61" s="86" t="s">
+        <v>126</v>
+      </c>
+      <c r="F61" s="86" t="s">
+        <v>83</v>
+      </c>
+      <c r="G61" s="86">
+        <v>2023001</v>
+      </c>
+      <c r="H61" s="86" t="s">
+        <v>60</v>
+      </c>
+      <c r="I61" s="86" t="s">
+        <v>80</v>
+      </c>
+      <c r="J61" s="86"/>
+      <c r="K61" s="88"/>
+      <c r="L61" s="86"/>
+      <c r="M61" s="86"/>
+      <c r="N61" s="86"/>
+      <c r="O61" s="86"/>
+      <c r="P61" s="86"/>
+      <c r="Q61" s="86"/>
+      <c r="R61" s="86"/>
+      <c r="S61" s="89"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2">
@@ -4577,10 +4689,10 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -4588,7 +4700,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -4596,7 +4708,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:8">
@@ -4604,16 +4716,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
+        <v>131</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>125</v>
-      </c>
       <c r="H4" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:8">
@@ -4621,16 +4733,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:8">
@@ -4638,16 +4750,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:8">
@@ -4655,16 +4767,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F7" s="1">
         <v>2</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:8">
@@ -4672,16 +4784,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F8" s="1">
         <v>3</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:8">
@@ -4689,16 +4801,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F9" s="1">
         <v>4</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:8">
@@ -4706,16 +4818,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F10" s="1">
         <v>5</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:8">
@@ -4723,16 +4835,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="F11" s="1">
         <v>6</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:8">
@@ -4740,16 +4852,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="F12" s="1">
         <v>7</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:8">
@@ -4757,16 +4869,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="F13" s="1">
         <v>8</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:8">
@@ -4774,16 +4886,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="F14" s="1">
         <v>9</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:8">
@@ -4791,16 +4903,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="F15" s="1">
         <v>10</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:8">
@@ -4808,16 +4920,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F16" s="1">
         <v>11</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:8">
@@ -4825,16 +4937,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="F17" s="1">
         <v>12</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:8">
@@ -4842,16 +4954,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="F18" s="1">
         <v>13</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:8">
@@ -4859,16 +4971,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F19" s="1">
         <v>14</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:8">
@@ -4876,16 +4988,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F20" s="1">
         <v>15</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:8">
@@ -4893,16 +5005,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="F21" s="1">
         <v>16</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:8">
@@ -4910,16 +5022,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F22" s="1">
         <v>17</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:8">
@@ -4927,16 +5039,16 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="F23" s="1">
         <v>18</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:8">
@@ -4944,16 +5056,16 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F24" s="1">
         <v>19</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -4961,7 +5073,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -4969,7 +5081,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -4977,7 +5089,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -4985,7 +5097,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -4993,7 +5105,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -5001,7 +5113,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -5009,7 +5121,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -5017,7 +5129,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -5025,7 +5137,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -5033,7 +5145,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -5041,7 +5153,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -5049,7 +5161,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -5057,7 +5169,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -5065,7 +5177,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -5073,7 +5185,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -5081,7 +5193,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -5089,7 +5201,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -5097,7 +5209,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -5105,7 +5217,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -5113,7 +5225,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -5121,7 +5233,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -5129,7 +5241,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -5137,7 +5249,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialAuxiliary.xlsx
+++ b/slots/resources/sample/SpecialAuxiliary.xlsx
@@ -1105,6 +1105,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
@@ -1112,17 +1117,6 @@
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1136,6 +1130,12 @@
     </font>
     <font>
       <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>

--- a/slots/resources/sample/SpecialAuxiliary.xlsx
+++ b/slots/resources/sample/SpecialAuxiliary.xlsx
@@ -268,7 +268,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="218">
   <si>
     <t>小游戏模式ID</t>
   </si>
@@ -643,6 +643,12 @@
   </si>
   <si>
     <t>蒸汽时代</t>
+  </si>
+  <si>
+    <t>10230021|10230031</t>
+  </si>
+  <si>
+    <t>概率改出百搭+概率改出免费+1</t>
   </si>
   <si>
     <t>免费游戏-免费旋转-12次</t>
@@ -1105,7 +1111,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1116,7 +1124,19 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1129,21 +1149,7 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -4541,8 +4547,12 @@
         <v>80</v>
       </c>
       <c r="J59" s="86"/>
-      <c r="K59" s="88"/>
-      <c r="L59" s="86"/>
+      <c r="K59" s="88" t="s">
+        <v>125</v>
+      </c>
+      <c r="L59" s="86" t="s">
+        <v>126</v>
+      </c>
       <c r="M59" s="86"/>
       <c r="N59" s="86"/>
       <c r="O59" s="86"/>
@@ -4565,7 +4575,7 @@
         <v>302302</v>
       </c>
       <c r="E60" s="86" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F60" s="86" t="s">
         <v>79</v>
@@ -4580,8 +4590,12 @@
         <v>80</v>
       </c>
       <c r="J60" s="86"/>
-      <c r="K60" s="88"/>
-      <c r="L60" s="86"/>
+      <c r="K60" s="88" t="s">
+        <v>125</v>
+      </c>
+      <c r="L60" s="86" t="s">
+        <v>126</v>
+      </c>
       <c r="M60" s="86"/>
       <c r="N60" s="86"/>
       <c r="O60" s="86"/>
@@ -4604,7 +4618,7 @@
         <v>302303</v>
       </c>
       <c r="E61" s="86" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F61" s="86" t="s">
         <v>83</v>
@@ -4619,8 +4633,12 @@
         <v>80</v>
       </c>
       <c r="J61" s="86"/>
-      <c r="K61" s="88"/>
-      <c r="L61" s="86"/>
+      <c r="K61" s="88" t="s">
+        <v>125</v>
+      </c>
+      <c r="L61" s="86" t="s">
+        <v>126</v>
+      </c>
       <c r="M61" s="86"/>
       <c r="N61" s="86"/>
       <c r="O61" s="86"/>
@@ -4689,10 +4707,10 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -4700,7 +4718,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -4708,7 +4726,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:8">
@@ -4716,16 +4734,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:8">
@@ -4733,16 +4751,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:8">
@@ -4750,16 +4768,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:8">
@@ -4767,16 +4785,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F7" s="1">
         <v>2</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:8">
@@ -4784,16 +4802,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F8" s="1">
         <v>3</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:8">
@@ -4801,16 +4819,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F9" s="1">
         <v>4</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:8">
@@ -4818,16 +4836,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F10" s="1">
         <v>5</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:8">
@@ -4835,16 +4853,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F11" s="1">
         <v>6</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:8">
@@ -4852,16 +4870,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F12" s="1">
         <v>7</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:8">
@@ -4869,16 +4887,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F13" s="1">
         <v>8</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:8">
@@ -4886,16 +4904,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F14" s="1">
         <v>9</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:8">
@@ -4903,16 +4921,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F15" s="1">
         <v>10</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:8">
@@ -4920,16 +4938,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F16" s="1">
         <v>11</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:8">
@@ -4937,16 +4955,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F17" s="1">
         <v>12</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:8">
@@ -4954,16 +4972,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F18" s="1">
         <v>13</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:8">
@@ -4971,16 +4989,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F19" s="1">
         <v>14</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:8">
@@ -4988,16 +5006,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F20" s="1">
         <v>15</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:8">
@@ -5005,16 +5023,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F21" s="1">
         <v>16</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:8">
@@ -5022,16 +5040,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F22" s="1">
         <v>17</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:8">
@@ -5039,16 +5057,16 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F23" s="1">
         <v>18</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:8">
@@ -5056,16 +5074,16 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F24" s="1">
         <v>19</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -5073,7 +5091,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -5081,7 +5099,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -5089,7 +5107,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -5097,7 +5115,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -5105,7 +5123,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -5113,7 +5131,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -5121,7 +5139,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -5129,7 +5147,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -5137,7 +5155,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -5145,7 +5163,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -5153,7 +5171,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -5161,7 +5179,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -5169,7 +5187,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -5177,7 +5195,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -5185,7 +5203,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -5193,7 +5211,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -5201,7 +5219,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -5209,7 +5227,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -5217,7 +5235,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -5225,7 +5243,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -5233,7 +5251,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -5241,7 +5259,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -5249,7 +5267,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialAuxiliary.xlsx
+++ b/slots/resources/sample/SpecialAuxiliary.xlsx
@@ -268,7 +268,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="218">
   <si>
     <t>小游戏模式ID</t>
   </si>
@@ -643,6 +643,12 @@
   </si>
   <si>
     <t>蒸汽时代</t>
+  </si>
+  <si>
+    <t>10230021|10230031</t>
+  </si>
+  <si>
+    <t>概率改出百搭+概率改出免费+1</t>
   </si>
   <si>
     <t>免费游戏-免费旋转-12次</t>
@@ -1106,13 +1112,14 @@
     </font>
     <font>
       <b/>
-      <sz val="9"/>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
+      <b/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1129,13 +1136,6 @@
     </font>
     <font>
       <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
@@ -1143,7 +1143,13 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -4541,8 +4547,12 @@
         <v>80</v>
       </c>
       <c r="J59" s="86"/>
-      <c r="K59" s="88"/>
-      <c r="L59" s="86"/>
+      <c r="K59" s="88" t="s">
+        <v>125</v>
+      </c>
+      <c r="L59" s="86" t="s">
+        <v>126</v>
+      </c>
       <c r="M59" s="86"/>
       <c r="N59" s="86"/>
       <c r="O59" s="86"/>
@@ -4565,7 +4575,7 @@
         <v>302302</v>
       </c>
       <c r="E60" s="86" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F60" s="86" t="s">
         <v>79</v>
@@ -4580,8 +4590,12 @@
         <v>80</v>
       </c>
       <c r="J60" s="86"/>
-      <c r="K60" s="88"/>
-      <c r="L60" s="86"/>
+      <c r="K60" s="88" t="s">
+        <v>125</v>
+      </c>
+      <c r="L60" s="86" t="s">
+        <v>126</v>
+      </c>
       <c r="M60" s="86"/>
       <c r="N60" s="86"/>
       <c r="O60" s="86"/>
@@ -4604,7 +4618,7 @@
         <v>302303</v>
       </c>
       <c r="E61" s="86" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F61" s="86" t="s">
         <v>83</v>
@@ -4619,8 +4633,12 @@
         <v>80</v>
       </c>
       <c r="J61" s="86"/>
-      <c r="K61" s="88"/>
-      <c r="L61" s="86"/>
+      <c r="K61" s="88" t="s">
+        <v>125</v>
+      </c>
+      <c r="L61" s="86" t="s">
+        <v>126</v>
+      </c>
       <c r="M61" s="86"/>
       <c r="N61" s="86"/>
       <c r="O61" s="86"/>
@@ -4689,10 +4707,10 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -4700,7 +4718,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -4708,7 +4726,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:8">
@@ -4716,16 +4734,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:8">
@@ -4733,16 +4751,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:8">
@@ -4750,16 +4768,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:8">
@@ -4767,16 +4785,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F7" s="1">
         <v>2</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:8">
@@ -4784,16 +4802,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F8" s="1">
         <v>3</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:8">
@@ -4801,16 +4819,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F9" s="1">
         <v>4</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:8">
@@ -4818,16 +4836,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F10" s="1">
         <v>5</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:8">
@@ -4835,16 +4853,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F11" s="1">
         <v>6</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:8">
@@ -4852,16 +4870,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F12" s="1">
         <v>7</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:8">
@@ -4869,16 +4887,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F13" s="1">
         <v>8</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:8">
@@ -4886,16 +4904,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F14" s="1">
         <v>9</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:8">
@@ -4903,16 +4921,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F15" s="1">
         <v>10</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:8">
@@ -4920,16 +4938,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F16" s="1">
         <v>11</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:8">
@@ -4937,16 +4955,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F17" s="1">
         <v>12</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:8">
@@ -4954,16 +4972,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F18" s="1">
         <v>13</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:8">
@@ -4971,16 +4989,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F19" s="1">
         <v>14</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:8">
@@ -4988,16 +5006,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F20" s="1">
         <v>15</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:8">
@@ -5005,16 +5023,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F21" s="1">
         <v>16</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:8">
@@ -5022,16 +5040,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F22" s="1">
         <v>17</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:8">
@@ -5039,16 +5057,16 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F23" s="1">
         <v>18</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:8">
@@ -5056,16 +5074,16 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F24" s="1">
         <v>19</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -5073,7 +5091,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -5081,7 +5099,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -5089,7 +5107,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -5097,7 +5115,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -5105,7 +5123,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -5113,7 +5131,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -5121,7 +5139,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -5129,7 +5147,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -5137,7 +5155,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -5145,7 +5163,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -5153,7 +5171,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -5161,7 +5179,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -5169,7 +5187,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -5177,7 +5195,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -5185,7 +5203,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -5193,7 +5211,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -5201,7 +5219,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -5209,7 +5227,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -5217,7 +5235,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -5225,7 +5243,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -5233,7 +5251,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -5241,7 +5259,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -5249,7 +5267,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialAuxiliary.xlsx
+++ b/slots/resources/sample/SpecialAuxiliary.xlsx
@@ -268,7 +268,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="225">
   <si>
     <t>小游戏模式ID</t>
   </si>
@@ -645,10 +645,37 @@
     <t>蒸汽时代</t>
   </si>
   <si>
+    <t>10230021|10230031</t>
+  </si>
+  <si>
+    <t>概率改出百搭+概率改出免费+1</t>
+  </si>
+  <si>
     <t>免费游戏-免费旋转-12次</t>
   </si>
   <si>
     <t>免费游戏-免费旋转-14次</t>
+  </si>
+  <si>
+    <t>金蛇招财</t>
+  </si>
+  <si>
+    <t>金钱兔模式-免费旋转-8次</t>
+  </si>
+  <si>
+    <t>金钱兔模式</t>
+  </si>
+  <si>
+    <t>改出奖金符号</t>
+  </si>
+  <si>
+    <t>奖金符号收集奖励</t>
+  </si>
+  <si>
+    <t>8_10000</t>
+  </si>
+  <si>
+    <t>金钱兔</t>
   </si>
   <si>
     <t>typeID</t>
@@ -1106,13 +1133,14 @@
     </font>
     <font>
       <b/>
-      <sz val="9"/>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
+      <b/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1122,7 +1150,7 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1142,14 +1170,13 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="48">
+  <fills count="49">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1207,6 +1234,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.25"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1563,7 +1596,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1587,16 +1620,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1605,92 +1638,92 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1706,12 +1739,13 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1732,7 +1766,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1741,19 +1775,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="176" fontId="1" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
@@ -1761,11 +1783,15 @@
     <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="176" fontId="1" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="1" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1773,14 +1799,22 @@
     <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1875,6 +1909,14 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="52">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2206,7 +2248,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S61"/>
+  <dimension ref="A1:S65"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14.125" customWidth="1"/>
@@ -2218,15 +2260,15 @@
     <col min="8" max="8" width="16.25" customWidth="1"/>
     <col min="9" max="9" width="29.375" customWidth="1"/>
     <col min="10" max="10" width="42.5" customWidth="1"/>
-    <col min="11" max="11" width="41.25" style="13" customWidth="1"/>
-    <col min="12" max="12" width="11.75" style="3" customWidth="1"/>
+    <col min="11" max="11" width="41.25" style="14" customWidth="1"/>
+    <col min="12" max="12" width="36.0333333333333" style="3" customWidth="1"/>
     <col min="13" max="13" width="34.4083333333333" style="3" customWidth="1"/>
     <col min="14" max="14" width="7.93333333333333" style="3" customWidth="1"/>
     <col min="15" max="15" width="11.325" customWidth="1"/>
     <col min="16" max="16" width="8.96666666666667" customWidth="1"/>
     <col min="17" max="17" width="93.375" customWidth="1"/>
     <col min="18" max="18" width="10.625" customWidth="1"/>
-    <col min="19" max="19" width="23.75" style="14" customWidth="1"/>
+    <col min="19" max="19" width="23.75" style="15" customWidth="1"/>
     <col min="20" max="20" width="60.875" customWidth="1"/>
     <col min="21" max="22" width="11.5"/>
   </cols>
@@ -2235,671 +2277,671 @@
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15" t="s">
+      <c r="C1" s="16"/>
+      <c r="D1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15" t="s">
+      <c r="E1" s="16"/>
+      <c r="F1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15" t="s">
+      <c r="H1" s="16"/>
+      <c r="I1" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="J1" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="17" t="s">
+      <c r="K1" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15" t="s">
+      <c r="L1" s="16"/>
+      <c r="M1" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="15"/>
-      <c r="O1" s="18" t="s">
+      <c r="N1" s="16"/>
+      <c r="O1" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="18" t="s">
+      <c r="P1" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="Q1" s="18" t="s">
+      <c r="Q1" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="R1" s="19" t="s">
+      <c r="R1" s="20" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="2" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15" t="s">
+      <c r="C2" s="16"/>
+      <c r="D2" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="15"/>
-      <c r="F2" s="18" t="s">
+      <c r="E2" s="16"/>
+      <c r="F2" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="15" t="s">
+      <c r="G2" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="21" t="s">
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="22" t="s">
+      <c r="K2" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="L2" s="18"/>
-      <c r="M2" s="21" t="s">
+      <c r="L2" s="19"/>
+      <c r="M2" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="N2" s="15"/>
-      <c r="O2" s="18" t="s">
+      <c r="N2" s="16"/>
+      <c r="O2" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="P2" s="18" t="s">
+      <c r="P2" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="Q2" s="21" t="s">
+      <c r="Q2" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="R2" s="19" t="s">
+      <c r="R2" s="20" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="3" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="23" t="s">
+      <c r="B3" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23" t="s">
+      <c r="C3" s="24"/>
+      <c r="D3" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="23"/>
-      <c r="F3" s="23" t="s">
+      <c r="E3" s="24"/>
+      <c r="F3" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="24" t="s">
+      <c r="G3" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
-      <c r="J3" s="25" t="s">
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="26" t="s">
+      <c r="K3" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="L3" s="23"/>
-      <c r="M3" s="23" t="s">
+      <c r="L3" s="24"/>
+      <c r="M3" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="N3" s="23"/>
-      <c r="O3" s="18" t="s">
+      <c r="N3" s="24"/>
+      <c r="O3" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="P3" s="18" t="s">
+      <c r="P3" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="Q3" s="18" t="s">
+      <c r="Q3" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="R3" s="27" t="s">
+      <c r="R3" s="28" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="4" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="15"/>
-      <c r="J4" s="28"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="15"/>
-      <c r="O4" s="15"/>
-      <c r="P4" s="15"/>
-      <c r="Q4" s="15"/>
-      <c r="R4" s="15"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="29"/>
+      <c r="K4" s="18"/>
+      <c r="L4" s="16"/>
+      <c r="M4" s="16"/>
+      <c r="N4" s="16"/>
+      <c r="O4" s="16"/>
+      <c r="P4" s="16"/>
+      <c r="Q4" s="16"/>
+      <c r="R4" s="16"/>
     </row>
     <row r="5" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A5" s="29">
+      <c r="A5" s="30">
         <v>30010001</v>
       </c>
-      <c r="B5" s="30">
+      <c r="B5" s="31">
         <v>100100</v>
       </c>
-      <c r="C5" s="30" t="s">
+      <c r="C5" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="30">
         <v>31001</v>
       </c>
-      <c r="E5" s="29" t="s">
+      <c r="E5" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="29" t="s">
+      <c r="F5" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29" t="s">
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="J5" s="29"/>
-      <c r="K5" s="31"/>
-      <c r="L5" s="15" t="s">
+      <c r="J5" s="30"/>
+      <c r="K5" s="32"/>
+      <c r="L5" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="M5" s="29" t="s">
+      <c r="M5" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="N5" s="29" t="s">
+      <c r="N5" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="O5" s="29"/>
-      <c r="P5" s="29"/>
-      <c r="Q5" s="32" t="s">
+      <c r="O5" s="30"/>
+      <c r="P5" s="30"/>
+      <c r="Q5" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="R5" s="33" t="s">
+      <c r="R5" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="S5" s="34" t="s">
+      <c r="S5" s="35" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="6" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A6" s="29">
+      <c r="A6" s="30">
         <v>30010002</v>
       </c>
-      <c r="B6" s="30">
+      <c r="B6" s="31">
         <v>100100</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="C6" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="29">
+      <c r="D6" s="30">
         <v>31002</v>
       </c>
-      <c r="E6" s="29" t="s">
+      <c r="E6" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="F6" s="29" t="s">
+      <c r="F6" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="G6" s="29"/>
-      <c r="H6" s="29"/>
-      <c r="I6" s="29" t="s">
+      <c r="G6" s="30"/>
+      <c r="H6" s="30"/>
+      <c r="I6" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="J6" s="29"/>
-      <c r="K6" s="31"/>
-      <c r="L6" s="15" t="s">
+      <c r="J6" s="30"/>
+      <c r="K6" s="32"/>
+      <c r="L6" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="M6" s="29" t="s">
+      <c r="M6" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="N6" s="29" t="s">
+      <c r="N6" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="O6" s="29"/>
-      <c r="P6" s="29"/>
-      <c r="Q6" s="32" t="s">
+      <c r="O6" s="30"/>
+      <c r="P6" s="30"/>
+      <c r="Q6" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="R6" s="33" t="s">
+      <c r="R6" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="S6" s="34"/>
+      <c r="S6" s="35"/>
     </row>
     <row r="7" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A7" s="29">
+      <c r="A7" s="30">
         <v>30010003</v>
       </c>
-      <c r="B7" s="30">
+      <c r="B7" s="31">
         <v>100100</v>
       </c>
-      <c r="C7" s="30" t="s">
+      <c r="C7" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="30">
         <v>31003</v>
       </c>
-      <c r="E7" s="29" t="s">
+      <c r="E7" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="29" t="s">
+      <c r="F7" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="G7" s="29"/>
-      <c r="H7" s="29"/>
-      <c r="I7" s="29" t="s">
+      <c r="G7" s="30"/>
+      <c r="H7" s="30"/>
+      <c r="I7" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="J7" s="29"/>
-      <c r="K7" s="31"/>
-      <c r="L7" s="15" t="s">
+      <c r="J7" s="30"/>
+      <c r="K7" s="32"/>
+      <c r="L7" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="M7" s="29" t="s">
+      <c r="M7" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="N7" s="29" t="s">
+      <c r="N7" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="O7" s="29"/>
-      <c r="P7" s="29"/>
-      <c r="Q7" s="32" t="s">
+      <c r="O7" s="30"/>
+      <c r="P7" s="30"/>
+      <c r="Q7" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="R7" s="33" t="s">
+      <c r="R7" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="S7" s="34"/>
+      <c r="S7" s="35"/>
     </row>
     <row r="8" s="3" customFormat="1" ht="15" customHeight="1" spans="1:19">
-      <c r="A8" s="29">
+      <c r="A8" s="30">
         <v>30010004</v>
       </c>
-      <c r="B8" s="30">
+      <c r="B8" s="31">
         <v>100100</v>
       </c>
-      <c r="C8" s="30" t="s">
+      <c r="C8" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="30">
         <v>31004</v>
       </c>
-      <c r="E8" s="29" t="s">
+      <c r="E8" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="F8" s="29" t="s">
+      <c r="F8" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="G8" s="29"/>
-      <c r="H8" s="29"/>
-      <c r="I8" s="29" t="s">
+      <c r="G8" s="30"/>
+      <c r="H8" s="30"/>
+      <c r="I8" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="J8" s="29"/>
-      <c r="K8" s="31"/>
-      <c r="L8" s="15" t="s">
+      <c r="J8" s="30"/>
+      <c r="K8" s="32"/>
+      <c r="L8" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="M8" s="29" t="s">
+      <c r="M8" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="N8" s="29" t="s">
+      <c r="N8" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="O8" s="29"/>
-      <c r="P8" s="29"/>
-      <c r="Q8" s="32" t="s">
+      <c r="O8" s="30"/>
+      <c r="P8" s="30"/>
+      <c r="Q8" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="R8" s="33" t="s">
+      <c r="R8" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="S8" s="34"/>
+      <c r="S8" s="35"/>
     </row>
     <row r="9" s="3" customFormat="1" ht="15" customHeight="1" spans="1:19">
-      <c r="A9" s="15">
+      <c r="A9" s="16">
         <v>30010005</v>
       </c>
-      <c r="B9" s="27">
+      <c r="B9" s="28">
         <v>100100</v>
       </c>
-      <c r="C9" s="30" t="s">
+      <c r="C9" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="15">
+      <c r="D9" s="16">
         <v>31101</v>
       </c>
-      <c r="E9" s="15" t="s">
+      <c r="E9" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="F9" s="15" t="s">
+      <c r="F9" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="G9" s="15"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="15" t="s">
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="J9" s="15"/>
-      <c r="K9" s="17"/>
-      <c r="L9" s="15" t="s">
+      <c r="J9" s="16"/>
+      <c r="K9" s="18"/>
+      <c r="L9" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="M9" s="15" t="s">
+      <c r="M9" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="N9" s="15"/>
-      <c r="O9" s="15" t="s">
+      <c r="N9" s="16"/>
+      <c r="O9" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="P9" s="15"/>
-      <c r="Q9" s="18"/>
-      <c r="R9" s="18"/>
-      <c r="S9" s="34"/>
+      <c r="P9" s="16"/>
+      <c r="Q9" s="19"/>
+      <c r="R9" s="19"/>
+      <c r="S9" s="35"/>
     </row>
     <row r="10" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A10" s="35">
+      <c r="A10" s="36">
         <v>30010006</v>
       </c>
-      <c r="B10" s="36">
+      <c r="B10" s="37">
         <v>100100</v>
       </c>
-      <c r="C10" s="30" t="s">
+      <c r="C10" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="D10" s="35">
+      <c r="D10" s="36">
         <v>31102</v>
       </c>
-      <c r="E10" s="35" t="s">
+      <c r="E10" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="F10" s="35" t="s">
+      <c r="F10" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="G10" s="35"/>
-      <c r="H10" s="35"/>
-      <c r="I10" s="35" t="s">
+      <c r="G10" s="36"/>
+      <c r="H10" s="36"/>
+      <c r="I10" s="36" t="s">
         <v>56</v>
       </c>
-      <c r="J10" s="35"/>
-      <c r="K10" s="37"/>
-      <c r="L10" s="35" t="s">
+      <c r="J10" s="36"/>
+      <c r="K10" s="38"/>
+      <c r="L10" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="M10" s="35" t="s">
+      <c r="M10" s="36" t="s">
         <v>57</v>
       </c>
-      <c r="N10" s="35" t="s">
+      <c r="N10" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="O10" s="35" t="s">
+      <c r="O10" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="P10" s="35"/>
-      <c r="Q10" s="35"/>
-      <c r="R10" s="15"/>
-      <c r="S10" s="34"/>
+      <c r="P10" s="36"/>
+      <c r="Q10" s="36"/>
+      <c r="R10" s="16"/>
+      <c r="S10" s="35"/>
     </row>
     <row r="11" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A11" s="38">
+      <c r="A11" s="39">
         <v>30010007</v>
       </c>
-      <c r="B11" s="39">
+      <c r="B11" s="40">
         <v>100100</v>
       </c>
-      <c r="C11" s="30" t="s">
+      <c r="C11" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="40">
+      <c r="D11" s="41">
         <v>31201</v>
       </c>
-      <c r="E11" s="40" t="s">
+      <c r="E11" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="F11" s="38" t="s">
+      <c r="F11" s="39" t="s">
         <v>59</v>
       </c>
-      <c r="G11" s="38">
+      <c r="G11" s="39">
         <v>2001001</v>
       </c>
-      <c r="H11" s="38" t="s">
+      <c r="H11" s="39" t="s">
         <v>60</v>
       </c>
-      <c r="I11" s="38" t="s">
+      <c r="I11" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="J11" s="38"/>
-      <c r="K11" s="41">
+      <c r="J11" s="39"/>
+      <c r="K11" s="42">
         <v>10010091</v>
       </c>
-      <c r="L11" s="38"/>
-      <c r="M11" s="38"/>
-      <c r="N11" s="38"/>
-      <c r="O11" s="38"/>
-      <c r="P11" s="38"/>
-      <c r="Q11" s="38"/>
-      <c r="R11" s="15"/>
-      <c r="S11" s="34"/>
+      <c r="L11" s="39"/>
+      <c r="M11" s="39"/>
+      <c r="N11" s="39"/>
+      <c r="O11" s="39"/>
+      <c r="P11" s="39"/>
+      <c r="Q11" s="39"/>
+      <c r="R11" s="16"/>
+      <c r="S11" s="35"/>
     </row>
     <row r="12" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A12" s="42">
+      <c r="A12" s="43">
         <v>30010008</v>
       </c>
-      <c r="B12" s="43">
+      <c r="B12" s="44">
         <v>100100</v>
       </c>
-      <c r="C12" s="30" t="s">
+      <c r="C12" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="40">
+      <c r="D12" s="41">
         <v>31202</v>
       </c>
-      <c r="E12" s="40" t="s">
+      <c r="E12" s="41" t="s">
         <v>62</v>
       </c>
-      <c r="F12" s="42" t="s">
+      <c r="F12" s="43" t="s">
         <v>53</v>
       </c>
-      <c r="G12" s="42">
+      <c r="G12" s="43">
         <v>2001001</v>
       </c>
-      <c r="H12" s="42" t="s">
+      <c r="H12" s="43" t="s">
         <v>60</v>
       </c>
-      <c r="I12" s="42" t="s">
+      <c r="I12" s="43" t="s">
         <v>63</v>
       </c>
-      <c r="J12" s="42"/>
-      <c r="K12" s="44" t="s">
+      <c r="J12" s="43"/>
+      <c r="K12" s="45" t="s">
         <v>64</v>
       </c>
-      <c r="L12" s="42"/>
-      <c r="M12" s="42"/>
-      <c r="N12" s="42"/>
-      <c r="O12" s="42"/>
-      <c r="P12" s="42"/>
-      <c r="Q12" s="42"/>
-      <c r="R12" s="15"/>
-      <c r="S12" s="34"/>
+      <c r="L12" s="43"/>
+      <c r="M12" s="43"/>
+      <c r="N12" s="43"/>
+      <c r="O12" s="43"/>
+      <c r="P12" s="43"/>
+      <c r="Q12" s="43"/>
+      <c r="R12" s="16"/>
+      <c r="S12" s="35"/>
     </row>
     <row r="13" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A13" s="45">
+      <c r="A13" s="46">
         <v>30010009</v>
       </c>
-      <c r="B13" s="46">
+      <c r="B13" s="47">
         <v>100100</v>
       </c>
-      <c r="C13" s="30" t="s">
+      <c r="C13" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="D13" s="40">
+      <c r="D13" s="41">
         <v>31203</v>
       </c>
-      <c r="E13" s="40" t="s">
+      <c r="E13" s="41" t="s">
         <v>65</v>
       </c>
-      <c r="F13" s="45" t="s">
+      <c r="F13" s="46" t="s">
         <v>53</v>
       </c>
-      <c r="G13" s="45">
+      <c r="G13" s="46">
         <v>2001001</v>
       </c>
-      <c r="H13" s="45" t="s">
+      <c r="H13" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="I13" s="45" t="s">
+      <c r="I13" s="46" t="s">
         <v>66</v>
       </c>
-      <c r="J13" s="45"/>
-      <c r="K13" s="47" t="s">
+      <c r="J13" s="46"/>
+      <c r="K13" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="L13" s="45"/>
-      <c r="M13" s="45"/>
-      <c r="N13" s="45"/>
-      <c r="O13" s="45"/>
-      <c r="P13" s="45"/>
-      <c r="Q13" s="45"/>
-      <c r="R13" s="15"/>
-      <c r="S13" s="34"/>
+      <c r="L13" s="46"/>
+      <c r="M13" s="46"/>
+      <c r="N13" s="46"/>
+      <c r="O13" s="46"/>
+      <c r="P13" s="46"/>
+      <c r="Q13" s="46"/>
+      <c r="R13" s="16"/>
+      <c r="S13" s="35"/>
     </row>
     <row r="14" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A14" s="40">
+      <c r="A14" s="41">
         <v>30010010</v>
       </c>
-      <c r="B14" s="48">
+      <c r="B14" s="49">
         <v>100100</v>
       </c>
-      <c r="C14" s="30" t="s">
+      <c r="C14" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="D14" s="49">
+      <c r="D14" s="50">
         <v>31301</v>
       </c>
-      <c r="E14" s="49" t="s">
+      <c r="E14" s="50" t="s">
         <v>68</v>
       </c>
-      <c r="F14" s="40" t="s">
+      <c r="F14" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="G14" s="40"/>
-      <c r="H14" s="40"/>
-      <c r="I14" s="40" t="s">
+      <c r="G14" s="41"/>
+      <c r="H14" s="41"/>
+      <c r="I14" s="41" t="s">
         <v>69</v>
       </c>
-      <c r="J14" s="40"/>
-      <c r="K14" s="50"/>
-      <c r="L14" s="40" t="s">
+      <c r="J14" s="41"/>
+      <c r="K14" s="51"/>
+      <c r="L14" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="M14" s="40" t="s">
+      <c r="M14" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="N14" s="40"/>
-      <c r="O14" s="40"/>
-      <c r="P14" s="40"/>
-      <c r="Q14" s="51" t="s">
+      <c r="N14" s="41"/>
+      <c r="O14" s="41"/>
+      <c r="P14" s="41"/>
+      <c r="Q14" s="52" t="s">
         <v>71</v>
       </c>
-      <c r="R14" s="52" t="s">
+      <c r="R14" s="53" t="s">
         <v>72</v>
       </c>
-      <c r="S14" s="18" t="s">
+      <c r="S14" s="19" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="15" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A15" s="45">
+      <c r="A15" s="46">
         <v>30010011</v>
       </c>
-      <c r="B15" s="46">
+      <c r="B15" s="47">
         <v>100100</v>
       </c>
-      <c r="C15" s="30" t="s">
+      <c r="C15" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="D15" s="49">
+      <c r="D15" s="50">
         <v>31302</v>
       </c>
-      <c r="E15" s="49" t="s">
+      <c r="E15" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F15" s="45" t="s">
+      <c r="F15" s="46" t="s">
         <v>34</v>
       </c>
-      <c r="G15" s="45"/>
-      <c r="H15" s="45"/>
-      <c r="I15" s="45" t="s">
+      <c r="G15" s="46"/>
+      <c r="H15" s="46"/>
+      <c r="I15" s="46" t="s">
         <v>75</v>
       </c>
-      <c r="J15" s="45"/>
-      <c r="K15" s="47"/>
-      <c r="L15" s="45" t="s">
+      <c r="J15" s="46"/>
+      <c r="K15" s="48"/>
+      <c r="L15" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="M15" s="45" t="s">
+      <c r="M15" s="46" t="s">
         <v>57</v>
       </c>
-      <c r="N15" s="45"/>
-      <c r="O15" s="45"/>
-      <c r="P15" s="45"/>
-      <c r="Q15" s="45"/>
-      <c r="R15" s="15"/>
-      <c r="S15" s="34"/>
+      <c r="N15" s="46"/>
+      <c r="O15" s="46"/>
+      <c r="P15" s="46"/>
+      <c r="Q15" s="46"/>
+      <c r="R15" s="16"/>
+      <c r="S15" s="35"/>
     </row>
     <row r="16" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A16" s="45">
+      <c r="A16" s="46">
         <v>30010012</v>
       </c>
-      <c r="B16" s="46">
+      <c r="B16" s="47">
         <v>100100</v>
       </c>
-      <c r="C16" s="30" t="s">
+      <c r="C16" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="D16" s="49">
+      <c r="D16" s="50">
         <v>31303</v>
       </c>
-      <c r="E16" s="49" t="s">
+      <c r="E16" s="50" t="s">
         <v>76</v>
       </c>
-      <c r="F16" s="45" t="s">
+      <c r="F16" s="46" t="s">
         <v>53</v>
       </c>
-      <c r="G16" s="45">
+      <c r="G16" s="46">
         <v>2001001</v>
       </c>
-      <c r="H16" s="45" t="s">
+      <c r="H16" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="I16" s="45" t="s">
+      <c r="I16" s="46" t="s">
         <v>66</v>
       </c>
-      <c r="J16" s="45"/>
-      <c r="K16" s="47" t="s">
+      <c r="J16" s="46"/>
+      <c r="K16" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="L16" s="45"/>
-      <c r="M16" s="45"/>
-      <c r="N16" s="45"/>
-      <c r="O16" s="45"/>
-      <c r="P16" s="45"/>
-      <c r="Q16" s="45"/>
-      <c r="R16" s="15"/>
-      <c r="S16" s="34"/>
+      <c r="L16" s="46"/>
+      <c r="M16" s="46"/>
+      <c r="N16" s="46"/>
+      <c r="O16" s="46"/>
+      <c r="P16" s="46"/>
+      <c r="Q16" s="46"/>
+      <c r="R16" s="16"/>
+      <c r="S16" s="35"/>
     </row>
     <row r="17" s="3" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A17" s="15">
+      <c r="A17" s="16">
         <v>30070001</v>
       </c>
       <c r="B17" s="3">
@@ -2908,30 +2950,30 @@
       <c r="C17" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D17" s="38">
+      <c r="D17" s="39">
         <v>34001</v>
       </c>
-      <c r="E17" s="38" t="s">
+      <c r="E17" s="39" t="s">
         <v>78</v>
       </c>
-      <c r="F17" s="38" t="s">
+      <c r="F17" s="39" t="s">
         <v>79</v>
       </c>
-      <c r="G17" s="27">
+      <c r="G17" s="28">
         <v>2007001</v>
       </c>
-      <c r="H17" s="15" t="s">
+      <c r="H17" s="16" t="s">
         <v>60</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="K17" s="53" t="s">
+      <c r="K17" s="54" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="18" s="3" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A18" s="15">
+      <c r="A18" s="16">
         <v>30070002</v>
       </c>
       <c r="B18" s="3">
@@ -2940,30 +2982,30 @@
       <c r="C18" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D18" s="38">
+      <c r="D18" s="39">
         <v>34002</v>
       </c>
-      <c r="E18" s="38" t="s">
+      <c r="E18" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="F18" s="38" t="s">
+      <c r="F18" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="G18" s="27">
+      <c r="G18" s="28">
         <v>2007001</v>
       </c>
-      <c r="H18" s="15" t="s">
+      <c r="H18" s="16" t="s">
         <v>60</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="K18" s="53" t="s">
+      <c r="K18" s="54" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="19" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A19" s="40">
+      <c r="A19" s="41">
         <v>30120001</v>
       </c>
       <c r="B19" s="4">
@@ -2972,33 +3014,33 @@
       <c r="C19" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D19" s="40">
+      <c r="D19" s="41">
         <v>32001</v>
       </c>
-      <c r="E19" s="40" t="s">
+      <c r="E19" s="41" t="s">
         <v>85</v>
       </c>
-      <c r="F19" s="40" t="s">
+      <c r="F19" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="G19" s="48">
+      <c r="G19" s="49">
         <v>2012001</v>
       </c>
-      <c r="H19" s="40" t="s">
+      <c r="H19" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="I19" s="40" t="s">
+      <c r="I19" s="41" t="s">
         <v>85</v>
       </c>
-      <c r="J19" s="40" t="s">
+      <c r="J19" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="K19" s="54">
+      <c r="K19" s="55">
         <v>10120041</v>
       </c>
     </row>
     <row r="20" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A20" s="40">
+      <c r="A20" s="41">
         <v>30120002</v>
       </c>
       <c r="B20" s="4">
@@ -3007,33 +3049,33 @@
       <c r="C20" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D20" s="40">
+      <c r="D20" s="41">
         <v>32002</v>
       </c>
-      <c r="E20" s="40" t="s">
+      <c r="E20" s="41" t="s">
         <v>87</v>
       </c>
-      <c r="F20" s="40" t="s">
+      <c r="F20" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="G20" s="48">
+      <c r="G20" s="49">
         <v>2012001</v>
       </c>
-      <c r="H20" s="40" t="s">
+      <c r="H20" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="I20" s="40" t="s">
+      <c r="I20" s="41" t="s">
         <v>87</v>
       </c>
-      <c r="J20" s="40" t="s">
+      <c r="J20" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="K20" s="54">
+      <c r="K20" s="55">
         <v>10120042</v>
       </c>
     </row>
     <row r="21" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A21" s="40">
+      <c r="A21" s="41">
         <v>30120003</v>
       </c>
       <c r="B21" s="4">
@@ -3042,33 +3084,33 @@
       <c r="C21" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D21" s="40">
+      <c r="D21" s="41">
         <v>32003</v>
       </c>
-      <c r="E21" s="40" t="s">
+      <c r="E21" s="41" t="s">
         <v>88</v>
       </c>
-      <c r="F21" s="40" t="s">
+      <c r="F21" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="G21" s="48">
+      <c r="G21" s="49">
         <v>2012001</v>
       </c>
-      <c r="H21" s="40" t="s">
+      <c r="H21" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="I21" s="40" t="s">
+      <c r="I21" s="41" t="s">
         <v>88</v>
       </c>
-      <c r="J21" s="40" t="s">
+      <c r="J21" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="K21" s="54">
+      <c r="K21" s="55">
         <v>10120043</v>
       </c>
     </row>
     <row r="22" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A22" s="40">
+      <c r="A22" s="41">
         <v>30120004</v>
       </c>
       <c r="B22" s="4">
@@ -3077,33 +3119,33 @@
       <c r="C22" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D22" s="40">
+      <c r="D22" s="41">
         <v>32004</v>
       </c>
-      <c r="E22" s="40" t="s">
+      <c r="E22" s="41" t="s">
         <v>89</v>
       </c>
-      <c r="F22" s="40" t="s">
+      <c r="F22" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="G22" s="48">
+      <c r="G22" s="49">
         <v>2012001</v>
       </c>
-      <c r="H22" s="40" t="s">
+      <c r="H22" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="I22" s="40" t="s">
+      <c r="I22" s="41" t="s">
         <v>89</v>
       </c>
-      <c r="J22" s="40" t="s">
+      <c r="J22" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="K22" s="54">
+      <c r="K22" s="55">
         <v>10120044</v>
       </c>
     </row>
     <row r="23" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A23" s="40">
+      <c r="A23" s="41">
         <v>30120005</v>
       </c>
       <c r="B23" s="4">
@@ -3112,33 +3154,33 @@
       <c r="C23" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D23" s="40">
+      <c r="D23" s="41">
         <v>32005</v>
       </c>
-      <c r="E23" s="40" t="s">
+      <c r="E23" s="41" t="s">
         <v>89</v>
       </c>
-      <c r="F23" s="40" t="s">
+      <c r="F23" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="G23" s="48">
+      <c r="G23" s="49">
         <v>2012001</v>
       </c>
-      <c r="H23" s="40" t="s">
+      <c r="H23" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="I23" s="40" t="s">
+      <c r="I23" s="41" t="s">
         <v>89</v>
       </c>
-      <c r="J23" s="40" t="s">
+      <c r="J23" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="K23" s="54">
+      <c r="K23" s="55">
         <v>10120045</v>
       </c>
     </row>
     <row r="24" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A24" s="40">
+      <c r="A24" s="41">
         <v>30120006</v>
       </c>
       <c r="B24" s="4">
@@ -3147,33 +3189,33 @@
       <c r="C24" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D24" s="40">
+      <c r="D24" s="41">
         <v>32006</v>
       </c>
-      <c r="E24" s="40" t="s">
+      <c r="E24" s="41" t="s">
         <v>89</v>
       </c>
-      <c r="F24" s="40" t="s">
+      <c r="F24" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="G24" s="48">
+      <c r="G24" s="49">
         <v>2012001</v>
       </c>
-      <c r="H24" s="40" t="s">
+      <c r="H24" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="I24" s="40" t="s">
+      <c r="I24" s="41" t="s">
         <v>89</v>
       </c>
-      <c r="J24" s="40" t="s">
+      <c r="J24" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="K24" s="54">
+      <c r="K24" s="55">
         <v>10120046</v>
       </c>
     </row>
     <row r="25" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A25" s="55">
+      <c r="A25" s="56">
         <v>30120011</v>
       </c>
       <c r="B25" s="5">
@@ -3182,33 +3224,33 @@
       <c r="C25" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="D25" s="40">
+      <c r="D25" s="41">
         <v>32101</v>
       </c>
-      <c r="E25" s="55" t="s">
+      <c r="E25" s="56" t="s">
         <v>85</v>
       </c>
-      <c r="F25" s="55" t="s">
+      <c r="F25" s="56" t="s">
         <v>53</v>
       </c>
-      <c r="G25" s="56">
+      <c r="G25" s="57">
         <v>2012001</v>
       </c>
-      <c r="H25" s="55" t="s">
+      <c r="H25" s="56" t="s">
         <v>60</v>
       </c>
-      <c r="I25" s="55" t="s">
+      <c r="I25" s="56" t="s">
         <v>85</v>
       </c>
-      <c r="J25" s="55" t="s">
+      <c r="J25" s="56" t="s">
         <v>91</v>
       </c>
-      <c r="K25" s="57">
+      <c r="K25" s="58">
         <v>10120041</v>
       </c>
     </row>
     <row r="26" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A26" s="55">
+      <c r="A26" s="56">
         <v>30120012</v>
       </c>
       <c r="B26" s="5">
@@ -3217,33 +3259,33 @@
       <c r="C26" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="D26" s="40">
+      <c r="D26" s="41">
         <v>32102</v>
       </c>
-      <c r="E26" s="55" t="s">
+      <c r="E26" s="56" t="s">
         <v>87</v>
       </c>
-      <c r="F26" s="55" t="s">
+      <c r="F26" s="56" t="s">
         <v>53</v>
       </c>
-      <c r="G26" s="56">
+      <c r="G26" s="57">
         <v>2012001</v>
       </c>
-      <c r="H26" s="55" t="s">
+      <c r="H26" s="56" t="s">
         <v>60</v>
       </c>
-      <c r="I26" s="55" t="s">
+      <c r="I26" s="56" t="s">
         <v>87</v>
       </c>
-      <c r="J26" s="55" t="s">
+      <c r="J26" s="56" t="s">
         <v>91</v>
       </c>
-      <c r="K26" s="57">
+      <c r="K26" s="58">
         <v>10120042</v>
       </c>
     </row>
     <row r="27" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A27" s="55">
+      <c r="A27" s="56">
         <v>30120013</v>
       </c>
       <c r="B27" s="5">
@@ -3252,33 +3294,33 @@
       <c r="C27" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="D27" s="40">
+      <c r="D27" s="41">
         <v>32103</v>
       </c>
-      <c r="E27" s="55" t="s">
+      <c r="E27" s="56" t="s">
         <v>88</v>
       </c>
-      <c r="F27" s="55" t="s">
+      <c r="F27" s="56" t="s">
         <v>53</v>
       </c>
-      <c r="G27" s="56">
+      <c r="G27" s="57">
         <v>2012001</v>
       </c>
-      <c r="H27" s="55" t="s">
+      <c r="H27" s="56" t="s">
         <v>60</v>
       </c>
-      <c r="I27" s="55" t="s">
+      <c r="I27" s="56" t="s">
         <v>88</v>
       </c>
-      <c r="J27" s="55" t="s">
+      <c r="J27" s="56" t="s">
         <v>91</v>
       </c>
-      <c r="K27" s="57">
+      <c r="K27" s="58">
         <v>10120043</v>
       </c>
     </row>
     <row r="28" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A28" s="55">
+      <c r="A28" s="56">
         <v>30120014</v>
       </c>
       <c r="B28" s="5">
@@ -3287,33 +3329,33 @@
       <c r="C28" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="D28" s="40">
+      <c r="D28" s="41">
         <v>32104</v>
       </c>
-      <c r="E28" s="55" t="s">
+      <c r="E28" s="56" t="s">
         <v>89</v>
       </c>
-      <c r="F28" s="55" t="s">
+      <c r="F28" s="56" t="s">
         <v>53</v>
       </c>
-      <c r="G28" s="56">
+      <c r="G28" s="57">
         <v>2012001</v>
       </c>
-      <c r="H28" s="55" t="s">
+      <c r="H28" s="56" t="s">
         <v>60</v>
       </c>
-      <c r="I28" s="55" t="s">
+      <c r="I28" s="56" t="s">
         <v>89</v>
       </c>
-      <c r="J28" s="55" t="s">
+      <c r="J28" s="56" t="s">
         <v>91</v>
       </c>
-      <c r="K28" s="57">
+      <c r="K28" s="58">
         <v>10120044</v>
       </c>
     </row>
     <row r="29" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A29" s="55">
+      <c r="A29" s="56">
         <v>30120015</v>
       </c>
       <c r="B29" s="5">
@@ -3322,33 +3364,33 @@
       <c r="C29" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="D29" s="40">
+      <c r="D29" s="41">
         <v>32105</v>
       </c>
-      <c r="E29" s="55" t="s">
+      <c r="E29" s="56" t="s">
         <v>89</v>
       </c>
-      <c r="F29" s="55" t="s">
+      <c r="F29" s="56" t="s">
         <v>53</v>
       </c>
-      <c r="G29" s="56">
+      <c r="G29" s="57">
         <v>2012001</v>
       </c>
-      <c r="H29" s="55" t="s">
+      <c r="H29" s="56" t="s">
         <v>60</v>
       </c>
-      <c r="I29" s="55" t="s">
+      <c r="I29" s="56" t="s">
         <v>89</v>
       </c>
-      <c r="J29" s="55" t="s">
+      <c r="J29" s="56" t="s">
         <v>91</v>
       </c>
-      <c r="K29" s="57">
+      <c r="K29" s="58">
         <v>10120045</v>
       </c>
     </row>
     <row r="30" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A30" s="55">
+      <c r="A30" s="56">
         <v>30120016</v>
       </c>
       <c r="B30" s="5">
@@ -3357,33 +3399,33 @@
       <c r="C30" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="D30" s="40">
+      <c r="D30" s="41">
         <v>32106</v>
       </c>
-      <c r="E30" s="55" t="s">
+      <c r="E30" s="56" t="s">
         <v>89</v>
       </c>
-      <c r="F30" s="55" t="s">
+      <c r="F30" s="56" t="s">
         <v>53</v>
       </c>
-      <c r="G30" s="56">
+      <c r="G30" s="57">
         <v>2012001</v>
       </c>
-      <c r="H30" s="55" t="s">
+      <c r="H30" s="56" t="s">
         <v>60</v>
       </c>
-      <c r="I30" s="55" t="s">
+      <c r="I30" s="56" t="s">
         <v>89</v>
       </c>
-      <c r="J30" s="55" t="s">
+      <c r="J30" s="56" t="s">
         <v>91</v>
       </c>
-      <c r="K30" s="57">
+      <c r="K30" s="58">
         <v>10120046</v>
       </c>
     </row>
     <row r="31" s="6" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A31" s="49">
+      <c r="A31" s="50">
         <v>30120021</v>
       </c>
       <c r="B31" s="6">
@@ -3392,31 +3434,31 @@
       <c r="C31" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D31" s="49">
+      <c r="D31" s="50">
         <v>32201</v>
       </c>
-      <c r="E31" s="49" t="s">
+      <c r="E31" s="50" t="s">
         <v>85</v>
       </c>
-      <c r="F31" s="49" t="s">
+      <c r="F31" s="50" t="s">
         <v>53</v>
       </c>
-      <c r="G31" s="58">
+      <c r="G31" s="59">
         <v>2012001</v>
       </c>
-      <c r="H31" s="49" t="s">
+      <c r="H31" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="I31" s="49" t="s">
+      <c r="I31" s="50" t="s">
         <v>85</v>
       </c>
-      <c r="J31" s="49"/>
-      <c r="K31" s="59">
+      <c r="J31" s="50"/>
+      <c r="K31" s="60">
         <v>10120041</v>
       </c>
     </row>
     <row r="32" s="6" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A32" s="49">
+      <c r="A32" s="50">
         <v>30120022</v>
       </c>
       <c r="B32" s="6">
@@ -3425,31 +3467,31 @@
       <c r="C32" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D32" s="49">
+      <c r="D32" s="50">
         <v>32202</v>
       </c>
-      <c r="E32" s="49" t="s">
+      <c r="E32" s="50" t="s">
         <v>87</v>
       </c>
-      <c r="F32" s="49" t="s">
+      <c r="F32" s="50" t="s">
         <v>53</v>
       </c>
-      <c r="G32" s="58">
+      <c r="G32" s="59">
         <v>2012001</v>
       </c>
-      <c r="H32" s="49" t="s">
+      <c r="H32" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="I32" s="49" t="s">
+      <c r="I32" s="50" t="s">
         <v>87</v>
       </c>
-      <c r="J32" s="49"/>
-      <c r="K32" s="59">
+      <c r="J32" s="50"/>
+      <c r="K32" s="60">
         <v>10120042</v>
       </c>
     </row>
     <row r="33" s="6" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A33" s="49">
+      <c r="A33" s="50">
         <v>30120023</v>
       </c>
       <c r="B33" s="6">
@@ -3458,31 +3500,31 @@
       <c r="C33" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D33" s="49">
+      <c r="D33" s="50">
         <v>32203</v>
       </c>
-      <c r="E33" s="49" t="s">
+      <c r="E33" s="50" t="s">
         <v>88</v>
       </c>
-      <c r="F33" s="49" t="s">
+      <c r="F33" s="50" t="s">
         <v>53</v>
       </c>
-      <c r="G33" s="58">
+      <c r="G33" s="59">
         <v>2012001</v>
       </c>
-      <c r="H33" s="49" t="s">
+      <c r="H33" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="I33" s="49" t="s">
+      <c r="I33" s="50" t="s">
         <v>88</v>
       </c>
-      <c r="J33" s="49"/>
-      <c r="K33" s="59">
+      <c r="J33" s="50"/>
+      <c r="K33" s="60">
         <v>10120043</v>
       </c>
     </row>
     <row r="34" s="6" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A34" s="49">
+      <c r="A34" s="50">
         <v>30120024</v>
       </c>
       <c r="B34" s="6">
@@ -3491,31 +3533,31 @@
       <c r="C34" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D34" s="49">
+      <c r="D34" s="50">
         <v>32204</v>
       </c>
-      <c r="E34" s="49" t="s">
+      <c r="E34" s="50" t="s">
         <v>89</v>
       </c>
-      <c r="F34" s="49" t="s">
+      <c r="F34" s="50" t="s">
         <v>53</v>
       </c>
-      <c r="G34" s="58">
+      <c r="G34" s="59">
         <v>2012001</v>
       </c>
-      <c r="H34" s="49" t="s">
+      <c r="H34" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="I34" s="49" t="s">
+      <c r="I34" s="50" t="s">
         <v>89</v>
       </c>
-      <c r="J34" s="49"/>
-      <c r="K34" s="59">
+      <c r="J34" s="50"/>
+      <c r="K34" s="60">
         <v>10120044</v>
       </c>
     </row>
     <row r="35" s="6" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A35" s="49">
+      <c r="A35" s="50">
         <v>30120025</v>
       </c>
       <c r="B35" s="6">
@@ -3524,31 +3566,31 @@
       <c r="C35" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D35" s="49">
+      <c r="D35" s="50">
         <v>32205</v>
       </c>
-      <c r="E35" s="49" t="s">
+      <c r="E35" s="50" t="s">
         <v>89</v>
       </c>
-      <c r="F35" s="49" t="s">
+      <c r="F35" s="50" t="s">
         <v>53</v>
       </c>
-      <c r="G35" s="58">
+      <c r="G35" s="59">
         <v>2012001</v>
       </c>
-      <c r="H35" s="49" t="s">
+      <c r="H35" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="I35" s="49" t="s">
+      <c r="I35" s="50" t="s">
         <v>89</v>
       </c>
-      <c r="J35" s="49"/>
-      <c r="K35" s="59">
+      <c r="J35" s="50"/>
+      <c r="K35" s="60">
         <v>10120045</v>
       </c>
     </row>
     <row r="36" s="6" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A36" s="49">
+      <c r="A36" s="50">
         <v>30120026</v>
       </c>
       <c r="B36" s="6">
@@ -3557,1077 +3599,1249 @@
       <c r="C36" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D36" s="49">
+      <c r="D36" s="50">
         <v>32206</v>
       </c>
-      <c r="E36" s="49" t="s">
+      <c r="E36" s="50" t="s">
         <v>89</v>
       </c>
-      <c r="F36" s="49" t="s">
+      <c r="F36" s="50" t="s">
         <v>53</v>
       </c>
-      <c r="G36" s="58">
+      <c r="G36" s="59">
         <v>2012001</v>
       </c>
-      <c r="H36" s="49" t="s">
+      <c r="H36" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="I36" s="49" t="s">
+      <c r="I36" s="50" t="s">
         <v>89</v>
       </c>
-      <c r="J36" s="49"/>
-      <c r="K36" s="59">
+      <c r="J36" s="50"/>
+      <c r="K36" s="60">
         <v>10120046</v>
       </c>
     </row>
     <row r="37" s="7" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A37" s="60">
+      <c r="A37" s="61">
         <v>30240001</v>
       </c>
-      <c r="B37" s="61">
+      <c r="B37" s="62">
         <v>102400</v>
       </c>
-      <c r="C37" s="61" t="s">
+      <c r="C37" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="D37" s="60">
+      <c r="D37" s="61">
         <v>32401</v>
       </c>
-      <c r="E37" s="60" t="s">
+      <c r="E37" s="61" t="s">
         <v>33</v>
       </c>
-      <c r="F37" s="60" t="s">
+      <c r="F37" s="61" t="s">
         <v>34</v>
       </c>
-      <c r="G37" s="60"/>
-      <c r="H37" s="60"/>
-      <c r="I37" s="60" t="s">
+      <c r="G37" s="61"/>
+      <c r="H37" s="61"/>
+      <c r="I37" s="61" t="s">
         <v>35</v>
       </c>
-      <c r="J37" s="60"/>
-      <c r="K37" s="62"/>
-      <c r="L37" s="60" t="s">
+      <c r="J37" s="61"/>
+      <c r="K37" s="63"/>
+      <c r="L37" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="M37" s="60" t="s">
+      <c r="M37" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="N37" s="60" t="s">
+      <c r="N37" s="61" t="s">
         <v>38</v>
       </c>
-      <c r="O37" s="60"/>
-      <c r="P37" s="60"/>
-      <c r="Q37" s="63" t="s">
+      <c r="O37" s="61"/>
+      <c r="P37" s="61"/>
+      <c r="Q37" s="64" t="s">
         <v>39</v>
       </c>
-      <c r="R37" s="64" t="s">
+      <c r="R37" s="65" t="s">
         <v>40</v>
       </c>
-      <c r="S37" s="65" t="s">
+      <c r="S37" s="66" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="38" s="7" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A38" s="60">
+      <c r="A38" s="61">
         <v>30240002</v>
       </c>
-      <c r="B38" s="61">
+      <c r="B38" s="62">
         <v>102400</v>
       </c>
-      <c r="C38" s="61" t="s">
+      <c r="C38" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="D38" s="60">
+      <c r="D38" s="61">
         <v>32402</v>
       </c>
-      <c r="E38" s="60" t="s">
+      <c r="E38" s="61" t="s">
         <v>42</v>
       </c>
-      <c r="F38" s="60" t="s">
+      <c r="F38" s="61" t="s">
         <v>34</v>
       </c>
-      <c r="G38" s="60"/>
-      <c r="H38" s="60"/>
-      <c r="I38" s="60" t="s">
+      <c r="G38" s="61"/>
+      <c r="H38" s="61"/>
+      <c r="I38" s="61" t="s">
         <v>43</v>
       </c>
-      <c r="J38" s="60"/>
-      <c r="K38" s="62"/>
-      <c r="L38" s="60" t="s">
+      <c r="J38" s="61"/>
+      <c r="K38" s="63"/>
+      <c r="L38" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="M38" s="60" t="s">
+      <c r="M38" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="N38" s="60" t="s">
+      <c r="N38" s="61" t="s">
         <v>38</v>
       </c>
-      <c r="O38" s="60"/>
-      <c r="P38" s="60"/>
-      <c r="Q38" s="63" t="s">
+      <c r="O38" s="61"/>
+      <c r="P38" s="61"/>
+      <c r="Q38" s="64" t="s">
         <v>44</v>
       </c>
-      <c r="R38" s="64" t="s">
+      <c r="R38" s="65" t="s">
         <v>40</v>
       </c>
-      <c r="S38" s="65"/>
+      <c r="S38" s="66"/>
     </row>
     <row r="39" s="7" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A39" s="60">
+      <c r="A39" s="61">
         <v>30240003</v>
       </c>
-      <c r="B39" s="61">
+      <c r="B39" s="62">
         <v>102400</v>
       </c>
-      <c r="C39" s="61" t="s">
+      <c r="C39" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="D39" s="60">
+      <c r="D39" s="61">
         <v>32403</v>
       </c>
-      <c r="E39" s="60" t="s">
+      <c r="E39" s="61" t="s">
         <v>45</v>
       </c>
-      <c r="F39" s="60" t="s">
+      <c r="F39" s="61" t="s">
         <v>34</v>
       </c>
-      <c r="G39" s="60"/>
-      <c r="H39" s="60"/>
-      <c r="I39" s="60" t="s">
+      <c r="G39" s="61"/>
+      <c r="H39" s="61"/>
+      <c r="I39" s="61" t="s">
         <v>46</v>
       </c>
-      <c r="J39" s="60"/>
-      <c r="K39" s="62"/>
-      <c r="L39" s="60" t="s">
+      <c r="J39" s="61"/>
+      <c r="K39" s="63"/>
+      <c r="L39" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="M39" s="60" t="s">
+      <c r="M39" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="N39" s="60" t="s">
+      <c r="N39" s="61" t="s">
         <v>38</v>
       </c>
-      <c r="O39" s="60"/>
-      <c r="P39" s="60"/>
-      <c r="Q39" s="63" t="s">
+      <c r="O39" s="61"/>
+      <c r="P39" s="61"/>
+      <c r="Q39" s="64" t="s">
         <v>47</v>
       </c>
-      <c r="R39" s="64" t="s">
+      <c r="R39" s="65" t="s">
         <v>40</v>
       </c>
-      <c r="S39" s="65"/>
+      <c r="S39" s="66"/>
     </row>
     <row r="40" s="7" customFormat="1" ht="15" customHeight="1" spans="1:19">
-      <c r="A40" s="60">
+      <c r="A40" s="61">
         <v>30240004</v>
       </c>
-      <c r="B40" s="61">
+      <c r="B40" s="62">
         <v>102400</v>
       </c>
-      <c r="C40" s="61" t="s">
+      <c r="C40" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="D40" s="60">
+      <c r="D40" s="61">
         <v>32404</v>
       </c>
-      <c r="E40" s="60" t="s">
+      <c r="E40" s="61" t="s">
         <v>48</v>
       </c>
-      <c r="F40" s="60" t="s">
+      <c r="F40" s="61" t="s">
         <v>34</v>
       </c>
-      <c r="G40" s="60"/>
-      <c r="H40" s="60"/>
-      <c r="I40" s="60" t="s">
+      <c r="G40" s="61"/>
+      <c r="H40" s="61"/>
+      <c r="I40" s="61" t="s">
         <v>49</v>
       </c>
-      <c r="J40" s="60"/>
-      <c r="K40" s="62"/>
-      <c r="L40" s="60" t="s">
+      <c r="J40" s="61"/>
+      <c r="K40" s="63"/>
+      <c r="L40" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="M40" s="60" t="s">
+      <c r="M40" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="N40" s="60" t="s">
+      <c r="N40" s="61" t="s">
         <v>38</v>
       </c>
-      <c r="O40" s="60"/>
-      <c r="P40" s="60"/>
-      <c r="Q40" s="63" t="s">
+      <c r="O40" s="61"/>
+      <c r="P40" s="61"/>
+      <c r="Q40" s="64" t="s">
         <v>50</v>
       </c>
-      <c r="R40" s="64" t="s">
+      <c r="R40" s="65" t="s">
         <v>40</v>
       </c>
-      <c r="S40" s="65"/>
+      <c r="S40" s="66"/>
     </row>
     <row r="41" s="7" customFormat="1" ht="15" customHeight="1" spans="1:19">
-      <c r="A41" s="60">
+      <c r="A41" s="61">
         <v>30240005</v>
       </c>
-      <c r="B41" s="61">
+      <c r="B41" s="62">
         <v>102400</v>
       </c>
-      <c r="C41" s="61" t="s">
+      <c r="C41" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="D41" s="60">
+      <c r="D41" s="61">
         <v>32411</v>
       </c>
-      <c r="E41" s="60" t="s">
+      <c r="E41" s="61" t="s">
         <v>51</v>
       </c>
-      <c r="F41" s="60" t="s">
+      <c r="F41" s="61" t="s">
         <v>34</v>
       </c>
-      <c r="G41" s="60"/>
-      <c r="H41" s="60"/>
-      <c r="I41" s="60" t="s">
+      <c r="G41" s="61"/>
+      <c r="H41" s="61"/>
+      <c r="I41" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="J41" s="60"/>
-      <c r="K41" s="62"/>
-      <c r="L41" s="60" t="s">
+      <c r="J41" s="61"/>
+      <c r="K41" s="63"/>
+      <c r="L41" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="M41" s="60" t="s">
+      <c r="M41" s="61" t="s">
         <v>53</v>
       </c>
-      <c r="N41" s="60"/>
-      <c r="O41" s="60" t="s">
+      <c r="N41" s="61"/>
+      <c r="O41" s="61" t="s">
         <v>54</v>
       </c>
-      <c r="P41" s="60"/>
-      <c r="Q41" s="63"/>
-      <c r="R41" s="63"/>
-      <c r="S41" s="65"/>
+      <c r="P41" s="61"/>
+      <c r="Q41" s="64"/>
+      <c r="R41" s="64"/>
+      <c r="S41" s="66"/>
     </row>
     <row r="42" s="7" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A42" s="60">
+      <c r="A42" s="61">
         <v>30240006</v>
       </c>
-      <c r="B42" s="61">
+      <c r="B42" s="62">
         <v>102400</v>
       </c>
-      <c r="C42" s="61" t="s">
+      <c r="C42" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="D42" s="60">
+      <c r="D42" s="61">
         <v>32421</v>
       </c>
-      <c r="E42" s="60" t="s">
+      <c r="E42" s="61" t="s">
         <v>55</v>
       </c>
-      <c r="F42" s="60" t="s">
+      <c r="F42" s="61" t="s">
         <v>34</v>
       </c>
-      <c r="G42" s="60"/>
-      <c r="H42" s="60"/>
-      <c r="I42" s="60" t="s">
+      <c r="G42" s="61"/>
+      <c r="H42" s="61"/>
+      <c r="I42" s="61" t="s">
         <v>56</v>
       </c>
-      <c r="J42" s="60"/>
-      <c r="K42" s="62"/>
-      <c r="L42" s="60" t="s">
+      <c r="J42" s="61"/>
+      <c r="K42" s="63"/>
+      <c r="L42" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="M42" s="60" t="s">
+      <c r="M42" s="61" t="s">
         <v>57</v>
       </c>
-      <c r="N42" s="60" t="s">
+      <c r="N42" s="61" t="s">
         <v>38</v>
       </c>
-      <c r="O42" s="60" t="s">
+      <c r="O42" s="61" t="s">
         <v>54</v>
       </c>
-      <c r="P42" s="60"/>
-      <c r="Q42" s="60"/>
-      <c r="R42" s="60"/>
-      <c r="S42" s="65"/>
+      <c r="P42" s="61"/>
+      <c r="Q42" s="61"/>
+      <c r="R42" s="61"/>
+      <c r="S42" s="66"/>
     </row>
     <row r="43" s="7" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A43" s="60">
+      <c r="A43" s="61">
         <v>30240007</v>
       </c>
-      <c r="B43" s="61">
+      <c r="B43" s="62">
         <v>102400</v>
       </c>
-      <c r="C43" s="61" t="s">
+      <c r="C43" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="D43" s="60">
+      <c r="D43" s="61">
         <v>32431</v>
       </c>
-      <c r="E43" s="60" t="s">
+      <c r="E43" s="61" t="s">
         <v>58</v>
       </c>
-      <c r="F43" s="60" t="s">
+      <c r="F43" s="61" t="s">
         <v>59</v>
       </c>
-      <c r="G43" s="60">
+      <c r="G43" s="61">
         <v>2024001</v>
       </c>
-      <c r="H43" s="60" t="s">
+      <c r="H43" s="61" t="s">
         <v>60</v>
       </c>
-      <c r="I43" s="60" t="s">
+      <c r="I43" s="61" t="s">
         <v>61</v>
       </c>
-      <c r="J43" s="60"/>
-      <c r="K43" s="62">
+      <c r="J43" s="61"/>
+      <c r="K43" s="63">
         <v>10240091</v>
       </c>
-      <c r="L43" s="60"/>
-      <c r="M43" s="60"/>
-      <c r="N43" s="60"/>
-      <c r="O43" s="60"/>
-      <c r="P43" s="60"/>
-      <c r="Q43" s="60"/>
-      <c r="R43" s="60"/>
-      <c r="S43" s="65"/>
+      <c r="L43" s="61"/>
+      <c r="M43" s="61"/>
+      <c r="N43" s="61"/>
+      <c r="O43" s="61"/>
+      <c r="P43" s="61"/>
+      <c r="Q43" s="61"/>
+      <c r="R43" s="61"/>
+      <c r="S43" s="66"/>
     </row>
     <row r="44" s="7" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A44" s="60">
+      <c r="A44" s="61">
         <v>30240008</v>
       </c>
-      <c r="B44" s="61">
+      <c r="B44" s="62">
         <v>102400</v>
       </c>
-      <c r="C44" s="61" t="s">
+      <c r="C44" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="D44" s="60">
+      <c r="D44" s="61">
         <v>32432</v>
       </c>
-      <c r="E44" s="60" t="s">
+      <c r="E44" s="61" t="s">
         <v>62</v>
       </c>
-      <c r="F44" s="60" t="s">
+      <c r="F44" s="61" t="s">
         <v>53</v>
       </c>
-      <c r="G44" s="60">
+      <c r="G44" s="61">
         <v>2024001</v>
       </c>
-      <c r="H44" s="60" t="s">
+      <c r="H44" s="61" t="s">
         <v>60</v>
       </c>
-      <c r="I44" s="60" t="s">
+      <c r="I44" s="61" t="s">
         <v>63</v>
       </c>
-      <c r="J44" s="60"/>
-      <c r="K44" s="66" t="s">
+      <c r="J44" s="61"/>
+      <c r="K44" s="67" t="s">
         <v>93</v>
       </c>
-      <c r="L44" s="60"/>
-      <c r="M44" s="60"/>
-      <c r="N44" s="60"/>
-      <c r="O44" s="60"/>
-      <c r="P44" s="60"/>
-      <c r="Q44" s="60"/>
-      <c r="R44" s="60"/>
-      <c r="S44" s="65"/>
+      <c r="L44" s="61"/>
+      <c r="M44" s="61"/>
+      <c r="N44" s="61"/>
+      <c r="O44" s="61"/>
+      <c r="P44" s="61"/>
+      <c r="Q44" s="61"/>
+      <c r="R44" s="61"/>
+      <c r="S44" s="66"/>
     </row>
     <row r="45" s="7" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A45" s="60">
+      <c r="A45" s="61">
         <v>30240009</v>
       </c>
-      <c r="B45" s="61">
+      <c r="B45" s="62">
         <v>102400</v>
       </c>
-      <c r="C45" s="61" t="s">
+      <c r="C45" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="D45" s="60">
+      <c r="D45" s="61">
         <v>32433</v>
       </c>
-      <c r="E45" s="60" t="s">
+      <c r="E45" s="61" t="s">
         <v>65</v>
       </c>
-      <c r="F45" s="60" t="s">
+      <c r="F45" s="61" t="s">
         <v>53</v>
       </c>
-      <c r="G45" s="60">
+      <c r="G45" s="61">
         <v>2024001</v>
       </c>
-      <c r="H45" s="60" t="s">
+      <c r="H45" s="61" t="s">
         <v>60</v>
       </c>
-      <c r="I45" s="60" t="s">
+      <c r="I45" s="61" t="s">
         <v>66</v>
       </c>
-      <c r="J45" s="60"/>
-      <c r="K45" s="62" t="s">
+      <c r="J45" s="61"/>
+      <c r="K45" s="63" t="s">
         <v>94</v>
       </c>
-      <c r="L45" s="60"/>
-      <c r="M45" s="60"/>
-      <c r="N45" s="60"/>
-      <c r="O45" s="60"/>
-      <c r="P45" s="60"/>
-      <c r="Q45" s="60"/>
-      <c r="R45" s="60"/>
-      <c r="S45" s="65"/>
+      <c r="L45" s="61"/>
+      <c r="M45" s="61"/>
+      <c r="N45" s="61"/>
+      <c r="O45" s="61"/>
+      <c r="P45" s="61"/>
+      <c r="Q45" s="61"/>
+      <c r="R45" s="61"/>
+      <c r="S45" s="66"/>
     </row>
     <row r="46" s="7" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A46" s="60">
+      <c r="A46" s="61">
         <v>30240010</v>
       </c>
-      <c r="B46" s="61">
+      <c r="B46" s="62">
         <v>102400</v>
       </c>
-      <c r="C46" s="61" t="s">
+      <c r="C46" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="D46" s="60">
+      <c r="D46" s="61">
         <v>32441</v>
       </c>
-      <c r="E46" s="60" t="s">
+      <c r="E46" s="61" t="s">
         <v>68</v>
       </c>
-      <c r="F46" s="60" t="s">
+      <c r="F46" s="61" t="s">
         <v>34</v>
       </c>
-      <c r="G46" s="60"/>
-      <c r="H46" s="60"/>
-      <c r="I46" s="60" t="s">
+      <c r="G46" s="61"/>
+      <c r="H46" s="61"/>
+      <c r="I46" s="61" t="s">
         <v>69</v>
       </c>
-      <c r="J46" s="60"/>
-      <c r="K46" s="66"/>
-      <c r="L46" s="60" t="s">
+      <c r="J46" s="61"/>
+      <c r="K46" s="67"/>
+      <c r="L46" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="M46" s="60" t="s">
+      <c r="M46" s="61" t="s">
         <v>70</v>
       </c>
-      <c r="N46" s="60"/>
-      <c r="O46" s="60"/>
-      <c r="P46" s="60"/>
-      <c r="Q46" s="63" t="s">
+      <c r="N46" s="61"/>
+      <c r="O46" s="61"/>
+      <c r="P46" s="61"/>
+      <c r="Q46" s="64" t="s">
         <v>71</v>
       </c>
-      <c r="R46" s="67" t="s">
+      <c r="R46" s="68" t="s">
         <v>72</v>
       </c>
-      <c r="S46" s="63" t="s">
+      <c r="S46" s="64" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="47" s="7" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A47" s="60">
+      <c r="A47" s="61">
         <v>30240011</v>
       </c>
-      <c r="B47" s="61">
+      <c r="B47" s="62">
         <v>102400</v>
       </c>
-      <c r="C47" s="61" t="s">
+      <c r="C47" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="D47" s="60">
+      <c r="D47" s="61">
         <v>32442</v>
       </c>
-      <c r="E47" s="60" t="s">
+      <c r="E47" s="61" t="s">
         <v>74</v>
       </c>
-      <c r="F47" s="60" t="s">
+      <c r="F47" s="61" t="s">
         <v>34</v>
       </c>
-      <c r="G47" s="60"/>
-      <c r="H47" s="60"/>
-      <c r="I47" s="60" t="s">
+      <c r="G47" s="61"/>
+      <c r="H47" s="61"/>
+      <c r="I47" s="61" t="s">
         <v>75</v>
       </c>
-      <c r="J47" s="60"/>
-      <c r="K47" s="62"/>
-      <c r="L47" s="60" t="s">
+      <c r="J47" s="61"/>
+      <c r="K47" s="63"/>
+      <c r="L47" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="M47" s="60" t="s">
+      <c r="M47" s="61" t="s">
         <v>57</v>
       </c>
-      <c r="N47" s="60"/>
-      <c r="O47" s="60"/>
-      <c r="P47" s="60"/>
-      <c r="Q47" s="60"/>
-      <c r="R47" s="60"/>
-      <c r="S47" s="65"/>
+      <c r="N47" s="61"/>
+      <c r="O47" s="61"/>
+      <c r="P47" s="61"/>
+      <c r="Q47" s="61"/>
+      <c r="R47" s="61"/>
+      <c r="S47" s="66"/>
     </row>
     <row r="48" s="7" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A48" s="60">
+      <c r="A48" s="61">
         <v>30240012</v>
       </c>
-      <c r="B48" s="61">
+      <c r="B48" s="62">
         <v>102400</v>
       </c>
-      <c r="C48" s="61" t="s">
+      <c r="C48" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="D48" s="60">
+      <c r="D48" s="61">
         <v>32443</v>
       </c>
-      <c r="E48" s="60" t="s">
+      <c r="E48" s="61" t="s">
         <v>76</v>
       </c>
-      <c r="F48" s="60" t="s">
+      <c r="F48" s="61" t="s">
         <v>53</v>
       </c>
-      <c r="G48" s="60">
+      <c r="G48" s="61">
         <v>2024001</v>
       </c>
-      <c r="H48" s="60" t="s">
+      <c r="H48" s="61" t="s">
         <v>60</v>
       </c>
-      <c r="I48" s="60" t="s">
+      <c r="I48" s="61" t="s">
         <v>66</v>
       </c>
-      <c r="J48" s="60"/>
-      <c r="K48" s="62" t="s">
+      <c r="J48" s="61"/>
+      <c r="K48" s="63" t="s">
         <v>94</v>
       </c>
-      <c r="L48" s="60"/>
-      <c r="M48" s="60"/>
-      <c r="N48" s="60"/>
-      <c r="O48" s="60"/>
-      <c r="P48" s="60"/>
-      <c r="Q48" s="60"/>
-      <c r="R48" s="60"/>
-      <c r="S48" s="65"/>
+      <c r="L48" s="61"/>
+      <c r="M48" s="61"/>
+      <c r="N48" s="61"/>
+      <c r="O48" s="61"/>
+      <c r="P48" s="61"/>
+      <c r="Q48" s="61"/>
+      <c r="R48" s="61"/>
+      <c r="S48" s="66"/>
     </row>
     <row r="49" s="8" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A49" s="68">
+      <c r="A49" s="69">
         <v>30170001</v>
       </c>
-      <c r="B49" s="69">
+      <c r="B49" s="70">
         <v>101700</v>
       </c>
-      <c r="C49" s="69" t="s">
+      <c r="C49" s="70" t="s">
         <v>95</v>
       </c>
-      <c r="D49" s="68">
+      <c r="D49" s="69">
         <v>301701</v>
       </c>
-      <c r="E49" s="68" t="s">
+      <c r="E49" s="69" t="s">
         <v>96</v>
       </c>
-      <c r="F49" s="68" t="s">
+      <c r="F49" s="69" t="s">
         <v>79</v>
       </c>
-      <c r="G49" s="68">
+      <c r="G49" s="69">
         <v>2017001</v>
       </c>
-      <c r="H49" s="68" t="s">
+      <c r="H49" s="69" t="s">
         <v>60</v>
       </c>
-      <c r="I49" s="68" t="s">
+      <c r="I49" s="69" t="s">
         <v>80</v>
       </c>
-      <c r="J49" s="68"/>
-      <c r="K49" s="70" t="s">
+      <c r="J49" s="69"/>
+      <c r="K49" s="71" t="s">
         <v>97</v>
       </c>
-      <c r="L49" s="68"/>
-      <c r="M49" s="68"/>
-      <c r="N49" s="68"/>
-      <c r="O49" s="68"/>
-      <c r="P49" s="68"/>
-      <c r="Q49" s="68"/>
-      <c r="R49" s="68"/>
-      <c r="S49" s="71"/>
+      <c r="L49" s="69"/>
+      <c r="M49" s="69"/>
+      <c r="N49" s="69"/>
+      <c r="O49" s="69"/>
+      <c r="P49" s="69"/>
+      <c r="Q49" s="69"/>
+      <c r="R49" s="69"/>
+      <c r="S49" s="72"/>
     </row>
     <row r="50" s="8" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A50" s="68">
+      <c r="A50" s="69">
         <v>30170002</v>
       </c>
-      <c r="B50" s="69">
+      <c r="B50" s="70">
         <v>101700</v>
       </c>
-      <c r="C50" s="69" t="s">
+      <c r="C50" s="70" t="s">
         <v>95</v>
       </c>
-      <c r="D50" s="68">
+      <c r="D50" s="69">
         <v>301702</v>
       </c>
-      <c r="E50" s="68" t="s">
+      <c r="E50" s="69" t="s">
         <v>98</v>
       </c>
-      <c r="F50" s="68" t="s">
+      <c r="F50" s="69" t="s">
         <v>83</v>
       </c>
-      <c r="G50" s="68">
+      <c r="G50" s="69">
         <v>2017001</v>
       </c>
-      <c r="H50" s="68" t="s">
+      <c r="H50" s="69" t="s">
         <v>60</v>
       </c>
-      <c r="I50" s="68" t="s">
+      <c r="I50" s="69" t="s">
         <v>80</v>
       </c>
-      <c r="J50" s="68"/>
-      <c r="K50" s="70" t="s">
+      <c r="J50" s="69"/>
+      <c r="K50" s="71" t="s">
         <v>97</v>
       </c>
-      <c r="L50" s="68"/>
-      <c r="M50" s="68"/>
-      <c r="N50" s="68"/>
-      <c r="O50" s="68"/>
-      <c r="P50" s="68"/>
-      <c r="Q50" s="68"/>
-      <c r="R50" s="68"/>
-      <c r="S50" s="71"/>
+      <c r="L50" s="69"/>
+      <c r="M50" s="69"/>
+      <c r="N50" s="69"/>
+      <c r="O50" s="69"/>
+      <c r="P50" s="69"/>
+      <c r="Q50" s="69"/>
+      <c r="R50" s="69"/>
+      <c r="S50" s="72"/>
     </row>
     <row r="51" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A51" s="55">
+      <c r="A51" s="56">
         <v>30220001</v>
       </c>
-      <c r="B51" s="56">
+      <c r="B51" s="57">
         <v>102200</v>
       </c>
-      <c r="C51" s="56" t="s">
+      <c r="C51" s="57" t="s">
         <v>99</v>
       </c>
-      <c r="D51" s="55">
+      <c r="D51" s="56">
         <v>302201</v>
       </c>
-      <c r="E51" s="55" t="s">
+      <c r="E51" s="56" t="s">
         <v>100</v>
       </c>
-      <c r="F51" s="55" t="s">
+      <c r="F51" s="56" t="s">
         <v>101</v>
       </c>
-      <c r="G51" s="55">
+      <c r="G51" s="56">
         <v>2022001</v>
       </c>
-      <c r="H51" s="55" t="s">
+      <c r="H51" s="56" t="s">
         <v>60</v>
       </c>
-      <c r="I51" s="55"/>
-      <c r="J51" s="55"/>
-      <c r="K51" s="72" t="s">
+      <c r="I51" s="56"/>
+      <c r="J51" s="56"/>
+      <c r="K51" s="73" t="s">
         <v>102</v>
       </c>
-      <c r="L51" s="55" t="s">
+      <c r="L51" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="M51" s="55"/>
-      <c r="N51" s="55"/>
-      <c r="O51" s="55"/>
-      <c r="P51" s="55"/>
-      <c r="Q51" s="55"/>
-      <c r="R51" s="55"/>
-      <c r="S51" s="73"/>
+      <c r="M51" s="56"/>
+      <c r="N51" s="56"/>
+      <c r="O51" s="56"/>
+      <c r="P51" s="56"/>
+      <c r="Q51" s="56"/>
+      <c r="R51" s="56"/>
+      <c r="S51" s="74"/>
     </row>
     <row r="52" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A52" s="55">
+      <c r="A52" s="56">
         <v>30220002</v>
       </c>
-      <c r="B52" s="56">
+      <c r="B52" s="57">
         <v>102200</v>
       </c>
-      <c r="C52" s="56" t="s">
+      <c r="C52" s="57" t="s">
         <v>99</v>
       </c>
-      <c r="D52" s="55">
+      <c r="D52" s="56">
         <v>302202</v>
       </c>
-      <c r="E52" s="55" t="s">
+      <c r="E52" s="56" t="s">
         <v>104</v>
       </c>
-      <c r="F52" s="55" t="s">
+      <c r="F52" s="56" t="s">
         <v>101</v>
       </c>
-      <c r="G52" s="55">
+      <c r="G52" s="56">
         <v>2022001</v>
       </c>
-      <c r="H52" s="55" t="s">
+      <c r="H52" s="56" t="s">
         <v>60</v>
       </c>
-      <c r="I52" s="55"/>
-      <c r="J52" s="55"/>
-      <c r="K52" s="72" t="s">
+      <c r="I52" s="56"/>
+      <c r="J52" s="56"/>
+      <c r="K52" s="73" t="s">
         <v>105</v>
       </c>
-      <c r="L52" s="55" t="s">
+      <c r="L52" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="M52" s="55"/>
-      <c r="N52" s="55"/>
-      <c r="O52" s="55"/>
-      <c r="P52" s="55"/>
-      <c r="Q52" s="55"/>
-      <c r="R52" s="55"/>
-      <c r="S52" s="73"/>
+      <c r="M52" s="56"/>
+      <c r="N52" s="56"/>
+      <c r="O52" s="56"/>
+      <c r="P52" s="56"/>
+      <c r="Q52" s="56"/>
+      <c r="R52" s="56"/>
+      <c r="S52" s="74"/>
     </row>
     <row r="53" s="9" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A53" s="74">
+      <c r="A53" s="75">
         <v>30210001</v>
       </c>
-      <c r="B53" s="75">
+      <c r="B53" s="76">
         <v>102100</v>
       </c>
-      <c r="C53" s="75" t="s">
+      <c r="C53" s="76" t="s">
         <v>106</v>
       </c>
-      <c r="D53" s="74">
+      <c r="D53" s="75">
         <v>302101</v>
       </c>
-      <c r="E53" s="74" t="s">
+      <c r="E53" s="75" t="s">
         <v>107</v>
       </c>
-      <c r="F53" s="74" t="s">
+      <c r="F53" s="75" t="s">
         <v>108</v>
       </c>
-      <c r="G53" s="74">
+      <c r="G53" s="75">
         <v>2021001</v>
       </c>
-      <c r="H53" s="74" t="s">
+      <c r="H53" s="75" t="s">
         <v>60</v>
       </c>
-      <c r="I53" s="74" t="s">
+      <c r="I53" s="75" t="s">
         <v>80</v>
       </c>
-      <c r="J53" s="74"/>
-      <c r="K53" s="76" t="s">
+      <c r="J53" s="75"/>
+      <c r="K53" s="77" t="s">
         <v>109</v>
       </c>
-      <c r="L53" s="74" t="s">
+      <c r="L53" s="75" t="s">
         <v>110</v>
       </c>
-      <c r="M53" s="74"/>
-      <c r="N53" s="74"/>
-      <c r="O53" s="74"/>
-      <c r="P53" s="74"/>
-      <c r="Q53" s="74"/>
-      <c r="R53" s="74"/>
-      <c r="S53" s="77"/>
+      <c r="M53" s="75"/>
+      <c r="N53" s="75"/>
+      <c r="O53" s="75"/>
+      <c r="P53" s="75"/>
+      <c r="Q53" s="75"/>
+      <c r="R53" s="75"/>
+      <c r="S53" s="78"/>
     </row>
     <row r="54" s="9" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A54" s="74">
+      <c r="A54" s="75">
         <v>30210002</v>
       </c>
-      <c r="B54" s="75">
+      <c r="B54" s="76">
         <v>102100</v>
       </c>
-      <c r="C54" s="75" t="s">
+      <c r="C54" s="76" t="s">
         <v>106</v>
       </c>
-      <c r="D54" s="74">
+      <c r="D54" s="75">
         <v>302102</v>
       </c>
-      <c r="E54" s="74" t="s">
+      <c r="E54" s="75" t="s">
         <v>111</v>
       </c>
-      <c r="F54" s="74" t="s">
+      <c r="F54" s="75" t="s">
         <v>34</v>
       </c>
-      <c r="G54" s="74"/>
-      <c r="H54" s="74"/>
-      <c r="I54" s="74" t="s">
+      <c r="G54" s="75"/>
+      <c r="H54" s="75"/>
+      <c r="I54" s="75" t="s">
         <v>112</v>
       </c>
-      <c r="J54" s="74"/>
-      <c r="K54" s="76"/>
-      <c r="L54" s="74"/>
-      <c r="M54" s="74" t="s">
+      <c r="J54" s="75"/>
+      <c r="K54" s="77"/>
+      <c r="L54" s="75"/>
+      <c r="M54" s="75" t="s">
         <v>37</v>
       </c>
-      <c r="N54" s="74" t="s">
+      <c r="N54" s="75" t="s">
         <v>113</v>
       </c>
-      <c r="O54" s="74"/>
-      <c r="P54" s="74"/>
-      <c r="Q54" s="74" t="s">
+      <c r="O54" s="75"/>
+      <c r="P54" s="75"/>
+      <c r="Q54" s="75" t="s">
         <v>114</v>
       </c>
-      <c r="R54" s="74"/>
-      <c r="S54" s="77"/>
+      <c r="R54" s="75"/>
+      <c r="S54" s="78"/>
     </row>
     <row r="55" s="10" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A55" s="78">
+      <c r="A55" s="79">
         <v>30180001</v>
       </c>
-      <c r="B55" s="79">
+      <c r="B55" s="80">
         <v>101800</v>
       </c>
-      <c r="C55" s="79" t="s">
+      <c r="C55" s="80" t="s">
         <v>115</v>
       </c>
-      <c r="D55" s="78">
+      <c r="D55" s="79">
         <v>301801</v>
       </c>
-      <c r="E55" s="78" t="s">
+      <c r="E55" s="79" t="s">
         <v>80</v>
       </c>
-      <c r="F55" s="78" t="s">
+      <c r="F55" s="79" t="s">
         <v>116</v>
       </c>
-      <c r="G55" s="78">
+      <c r="G55" s="79">
         <v>2018001</v>
       </c>
-      <c r="H55" s="78" t="s">
+      <c r="H55" s="79" t="s">
         <v>60</v>
       </c>
-      <c r="I55" s="78" t="s">
+      <c r="I55" s="79" t="s">
         <v>80</v>
       </c>
-      <c r="J55" s="78"/>
-      <c r="K55" s="80">
+      <c r="J55" s="79"/>
+      <c r="K55" s="81">
         <v>10180041</v>
       </c>
-      <c r="L55" s="78"/>
-      <c r="M55" s="78"/>
-      <c r="N55" s="78"/>
-      <c r="O55" s="78"/>
-      <c r="P55" s="78"/>
-      <c r="Q55" s="78"/>
-      <c r="R55" s="78"/>
-      <c r="S55" s="81"/>
+      <c r="L55" s="79"/>
+      <c r="M55" s="79"/>
+      <c r="N55" s="79"/>
+      <c r="O55" s="79"/>
+      <c r="P55" s="79"/>
+      <c r="Q55" s="79"/>
+      <c r="R55" s="79"/>
+      <c r="S55" s="82"/>
     </row>
     <row r="56" s="11" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A56" s="82">
+      <c r="A56" s="83">
         <v>30250001</v>
       </c>
-      <c r="B56" s="83">
+      <c r="B56" s="84">
         <v>102500</v>
       </c>
-      <c r="C56" s="83" t="s">
+      <c r="C56" s="84" t="s">
         <v>117</v>
       </c>
-      <c r="D56" s="82">
+      <c r="D56" s="83">
         <v>302501</v>
       </c>
-      <c r="E56" s="82" t="s">
+      <c r="E56" s="83" t="s">
         <v>107</v>
       </c>
-      <c r="F56" s="82" t="s">
+      <c r="F56" s="83" t="s">
         <v>108</v>
       </c>
-      <c r="G56" s="82">
+      <c r="G56" s="83">
         <v>2025001</v>
       </c>
-      <c r="H56" s="82" t="s">
+      <c r="H56" s="83" t="s">
         <v>60</v>
       </c>
-      <c r="I56" s="82" t="s">
+      <c r="I56" s="83" t="s">
         <v>80</v>
       </c>
-      <c r="J56" s="82"/>
-      <c r="K56" s="84" t="s">
+      <c r="J56" s="83"/>
+      <c r="K56" s="85" t="s">
         <v>118</v>
       </c>
-      <c r="L56" s="82" t="s">
+      <c r="L56" s="83" t="s">
         <v>119</v>
       </c>
-      <c r="M56" s="82"/>
-      <c r="N56" s="82"/>
-      <c r="O56" s="82"/>
-      <c r="P56" s="82"/>
-      <c r="Q56" s="82"/>
-      <c r="R56" s="82"/>
-      <c r="S56" s="85"/>
+      <c r="M56" s="83"/>
+      <c r="N56" s="83"/>
+      <c r="O56" s="83"/>
+      <c r="P56" s="83"/>
+      <c r="Q56" s="83"/>
+      <c r="R56" s="83"/>
+      <c r="S56" s="86"/>
     </row>
     <row r="57" s="11" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A57" s="82">
+      <c r="A57" s="83">
         <v>30250002</v>
       </c>
-      <c r="B57" s="83">
+      <c r="B57" s="84">
         <v>102500</v>
       </c>
-      <c r="C57" s="83" t="s">
+      <c r="C57" s="84" t="s">
         <v>117</v>
       </c>
-      <c r="D57" s="82">
+      <c r="D57" s="83">
         <v>302502</v>
       </c>
-      <c r="E57" s="82" t="s">
+      <c r="E57" s="83" t="s">
         <v>120</v>
       </c>
-      <c r="F57" s="82" t="s">
+      <c r="F57" s="83" t="s">
         <v>121</v>
       </c>
-      <c r="G57" s="82">
+      <c r="G57" s="83">
         <v>2025001</v>
       </c>
-      <c r="H57" s="82" t="s">
+      <c r="H57" s="83" t="s">
         <v>60</v>
       </c>
-      <c r="I57" s="82" t="s">
+      <c r="I57" s="83" t="s">
         <v>80</v>
       </c>
-      <c r="J57" s="82"/>
-      <c r="K57" s="84" t="s">
+      <c r="J57" s="83"/>
+      <c r="K57" s="85" t="s">
         <v>118</v>
       </c>
-      <c r="L57" s="82" t="s">
+      <c r="L57" s="83" t="s">
         <v>119</v>
       </c>
-      <c r="M57" s="82"/>
-      <c r="N57" s="82"/>
-      <c r="O57" s="82"/>
-      <c r="P57" s="82"/>
-      <c r="Q57" s="82"/>
-      <c r="R57" s="82"/>
-      <c r="S57" s="85"/>
+      <c r="M57" s="83"/>
+      <c r="N57" s="83"/>
+      <c r="O57" s="83"/>
+      <c r="P57" s="83"/>
+      <c r="Q57" s="83"/>
+      <c r="R57" s="83"/>
+      <c r="S57" s="86"/>
     </row>
     <row r="58" s="11" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A58" s="82">
+      <c r="A58" s="83">
         <v>30250003</v>
       </c>
-      <c r="B58" s="83">
+      <c r="B58" s="84">
         <v>102500</v>
       </c>
-      <c r="C58" s="83" t="s">
+      <c r="C58" s="84" t="s">
         <v>117</v>
       </c>
-      <c r="D58" s="82">
+      <c r="D58" s="83">
         <v>302503</v>
       </c>
-      <c r="E58" s="82" t="s">
+      <c r="E58" s="83" t="s">
         <v>122</v>
       </c>
-      <c r="F58" s="82" t="s">
+      <c r="F58" s="83" t="s">
         <v>123</v>
       </c>
-      <c r="G58" s="82">
+      <c r="G58" s="83">
         <v>2025001</v>
       </c>
-      <c r="H58" s="82" t="s">
+      <c r="H58" s="83" t="s">
         <v>60</v>
       </c>
-      <c r="I58" s="82" t="s">
+      <c r="I58" s="83" t="s">
         <v>80</v>
       </c>
-      <c r="J58" s="82"/>
-      <c r="K58" s="84" t="s">
+      <c r="J58" s="83"/>
+      <c r="K58" s="85" t="s">
         <v>118</v>
       </c>
-      <c r="L58" s="82" t="s">
+      <c r="L58" s="83" t="s">
         <v>119</v>
       </c>
-      <c r="M58" s="82"/>
-      <c r="N58" s="82"/>
-      <c r="O58" s="82"/>
-      <c r="P58" s="82"/>
-      <c r="Q58" s="82"/>
-      <c r="R58" s="82"/>
-      <c r="S58" s="85"/>
+      <c r="M58" s="83"/>
+      <c r="N58" s="83"/>
+      <c r="O58" s="83"/>
+      <c r="P58" s="83"/>
+      <c r="Q58" s="83"/>
+      <c r="R58" s="83"/>
+      <c r="S58" s="86"/>
     </row>
     <row r="59" s="12" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A59" s="86">
+      <c r="A59" s="87">
         <v>30230001</v>
       </c>
-      <c r="B59" s="87">
+      <c r="B59" s="88">
         <v>102300</v>
       </c>
-      <c r="C59" s="87" t="s">
+      <c r="C59" s="88" t="s">
         <v>124</v>
       </c>
-      <c r="D59" s="86">
+      <c r="D59" s="87">
         <v>302301</v>
       </c>
-      <c r="E59" s="86" t="s">
+      <c r="E59" s="87" t="s">
         <v>107</v>
       </c>
-      <c r="F59" s="86" t="s">
+      <c r="F59" s="87" t="s">
         <v>108</v>
       </c>
-      <c r="G59" s="86">
+      <c r="G59" s="87">
         <v>2023001</v>
       </c>
-      <c r="H59" s="86" t="s">
+      <c r="H59" s="87" t="s">
         <v>60</v>
       </c>
-      <c r="I59" s="86" t="s">
+      <c r="I59" s="87" t="s">
         <v>80</v>
       </c>
-      <c r="J59" s="86"/>
-      <c r="K59" s="88"/>
-      <c r="L59" s="86"/>
-      <c r="M59" s="86"/>
-      <c r="N59" s="86"/>
-      <c r="O59" s="86"/>
-      <c r="P59" s="86"/>
-      <c r="Q59" s="86"/>
-      <c r="R59" s="86"/>
-      <c r="S59" s="89"/>
+      <c r="J59" s="87"/>
+      <c r="K59" s="89" t="s">
+        <v>125</v>
+      </c>
+      <c r="L59" s="87" t="s">
+        <v>126</v>
+      </c>
+      <c r="M59" s="87"/>
+      <c r="N59" s="87"/>
+      <c r="O59" s="87"/>
+      <c r="P59" s="87"/>
+      <c r="Q59" s="87"/>
+      <c r="R59" s="87"/>
+      <c r="S59" s="90"/>
     </row>
     <row r="60" s="12" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A60" s="86">
+      <c r="A60" s="87">
         <v>30230002</v>
       </c>
-      <c r="B60" s="87">
+      <c r="B60" s="88">
         <v>102300</v>
       </c>
-      <c r="C60" s="87" t="s">
+      <c r="C60" s="88" t="s">
         <v>124</v>
       </c>
-      <c r="D60" s="86">
+      <c r="D60" s="87">
         <v>302302</v>
       </c>
-      <c r="E60" s="86" t="s">
+      <c r="E60" s="87" t="s">
+        <v>127</v>
+      </c>
+      <c r="F60" s="87" t="s">
+        <v>79</v>
+      </c>
+      <c r="G60" s="87">
+        <v>2023001</v>
+      </c>
+      <c r="H60" s="87" t="s">
+        <v>60</v>
+      </c>
+      <c r="I60" s="87" t="s">
+        <v>80</v>
+      </c>
+      <c r="J60" s="87"/>
+      <c r="K60" s="89" t="s">
         <v>125</v>
       </c>
-      <c r="F60" s="86" t="s">
-        <v>79</v>
-      </c>
-      <c r="G60" s="86">
+      <c r="L60" s="87" t="s">
+        <v>126</v>
+      </c>
+      <c r="M60" s="87"/>
+      <c r="N60" s="87"/>
+      <c r="O60" s="87"/>
+      <c r="P60" s="87"/>
+      <c r="Q60" s="87"/>
+      <c r="R60" s="87"/>
+      <c r="S60" s="90"/>
+    </row>
+    <row r="61" s="12" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A61" s="87">
+        <v>30230003</v>
+      </c>
+      <c r="B61" s="88">
+        <v>102300</v>
+      </c>
+      <c r="C61" s="88" t="s">
+        <v>124</v>
+      </c>
+      <c r="D61" s="87">
+        <v>302303</v>
+      </c>
+      <c r="E61" s="87" t="s">
+        <v>128</v>
+      </c>
+      <c r="F61" s="87" t="s">
+        <v>83</v>
+      </c>
+      <c r="G61" s="87">
         <v>2023001</v>
       </c>
-      <c r="H60" s="86" t="s">
+      <c r="H61" s="87" t="s">
         <v>60</v>
       </c>
-      <c r="I60" s="86" t="s">
+      <c r="I61" s="87" t="s">
         <v>80</v>
       </c>
-      <c r="J60" s="86"/>
-      <c r="K60" s="88"/>
-      <c r="L60" s="86"/>
-      <c r="M60" s="86"/>
-      <c r="N60" s="86"/>
-      <c r="O60" s="86"/>
-      <c r="P60" s="86"/>
-      <c r="Q60" s="86"/>
-      <c r="R60" s="86"/>
-      <c r="S60" s="89"/>
-    </row>
-    <row r="61" s="12" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A61" s="86">
-        <v>30230003</v>
-      </c>
-      <c r="B61" s="87">
-        <v>102300</v>
-      </c>
-      <c r="C61" s="87" t="s">
-        <v>124</v>
-      </c>
-      <c r="D61" s="86">
-        <v>302303</v>
-      </c>
-      <c r="E61" s="86" t="s">
+      <c r="J61" s="87"/>
+      <c r="K61" s="89" t="s">
+        <v>125</v>
+      </c>
+      <c r="L61" s="87" t="s">
         <v>126</v>
       </c>
-      <c r="F61" s="86" t="s">
-        <v>83</v>
-      </c>
-      <c r="G61" s="86">
-        <v>2023001</v>
-      </c>
-      <c r="H61" s="86" t="s">
+      <c r="M61" s="87"/>
+      <c r="N61" s="87"/>
+      <c r="O61" s="87"/>
+      <c r="P61" s="87"/>
+      <c r="Q61" s="87"/>
+      <c r="R61" s="87"/>
+      <c r="S61" s="90"/>
+    </row>
+    <row r="62" s="13" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A62" s="91">
+        <v>30350001</v>
+      </c>
+      <c r="B62" s="92">
+        <v>103500</v>
+      </c>
+      <c r="C62" s="92" t="s">
+        <v>129</v>
+      </c>
+      <c r="D62" s="91">
+        <v>303501</v>
+      </c>
+      <c r="E62" s="91" t="s">
+        <v>130</v>
+      </c>
+      <c r="F62" s="91" t="s">
+        <v>59</v>
+      </c>
+      <c r="G62" s="91">
+        <v>2035001</v>
+      </c>
+      <c r="H62" s="91" t="s">
         <v>60</v>
       </c>
-      <c r="I61" s="86" t="s">
-        <v>80</v>
-      </c>
-      <c r="J61" s="86"/>
-      <c r="K61" s="88"/>
-      <c r="L61" s="86"/>
-      <c r="M61" s="86"/>
-      <c r="N61" s="86"/>
-      <c r="O61" s="86"/>
-      <c r="P61" s="86"/>
-      <c r="Q61" s="86"/>
-      <c r="R61" s="86"/>
-      <c r="S61" s="89"/>
+      <c r="I62" s="91" t="s">
+        <v>131</v>
+      </c>
+      <c r="J62" s="91"/>
+      <c r="K62" s="93">
+        <v>10350002</v>
+      </c>
+      <c r="L62" s="91" t="s">
+        <v>132</v>
+      </c>
+      <c r="M62" s="91"/>
+      <c r="N62" s="91"/>
+      <c r="O62" s="91"/>
+      <c r="P62" s="91"/>
+      <c r="Q62" s="91"/>
+      <c r="R62" s="91"/>
+      <c r="S62" s="94"/>
+    </row>
+    <row r="63" s="13" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A63" s="91">
+        <v>30350002</v>
+      </c>
+      <c r="B63" s="92">
+        <v>103500</v>
+      </c>
+      <c r="C63" s="92" t="s">
+        <v>129</v>
+      </c>
+      <c r="D63" s="91">
+        <v>303502</v>
+      </c>
+      <c r="E63" s="91" t="s">
+        <v>133</v>
+      </c>
+      <c r="F63" s="91" t="s">
+        <v>34</v>
+      </c>
+      <c r="G63" s="91"/>
+      <c r="H63" s="91"/>
+      <c r="I63" s="91"/>
+      <c r="J63" s="91"/>
+      <c r="K63" s="93"/>
+      <c r="L63" s="91"/>
+      <c r="M63" s="91" t="s">
+        <v>53</v>
+      </c>
+      <c r="N63" s="91"/>
+      <c r="O63" s="91" t="s">
+        <v>134</v>
+      </c>
+      <c r="P63" s="91"/>
+      <c r="Q63" s="91"/>
+      <c r="R63" s="91"/>
+      <c r="S63" s="94"/>
+    </row>
+    <row r="64" s="13" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A64" s="91">
+        <v>30350101</v>
+      </c>
+      <c r="B64" s="92">
+        <v>103501</v>
+      </c>
+      <c r="C64" s="92" t="s">
+        <v>135</v>
+      </c>
+      <c r="D64" s="91">
+        <v>303503</v>
+      </c>
+      <c r="E64" s="91" t="s">
+        <v>130</v>
+      </c>
+      <c r="F64" s="91" t="s">
+        <v>59</v>
+      </c>
+      <c r="G64" s="91">
+        <v>2035011</v>
+      </c>
+      <c r="H64" s="91" t="s">
+        <v>60</v>
+      </c>
+      <c r="I64" s="91" t="s">
+        <v>131</v>
+      </c>
+      <c r="J64" s="91"/>
+      <c r="K64" s="93">
+        <v>10350102</v>
+      </c>
+      <c r="L64" s="91" t="s">
+        <v>132</v>
+      </c>
+      <c r="M64" s="91"/>
+      <c r="N64" s="91"/>
+      <c r="O64" s="91"/>
+      <c r="P64" s="91"/>
+      <c r="Q64" s="91"/>
+      <c r="R64" s="91"/>
+      <c r="S64" s="94"/>
+    </row>
+    <row r="65" s="13" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A65" s="91">
+        <v>30350102</v>
+      </c>
+      <c r="B65" s="92">
+        <v>103501</v>
+      </c>
+      <c r="C65" s="92" t="s">
+        <v>135</v>
+      </c>
+      <c r="D65" s="91">
+        <v>303504</v>
+      </c>
+      <c r="E65" s="91" t="s">
+        <v>133</v>
+      </c>
+      <c r="F65" s="91" t="s">
+        <v>34</v>
+      </c>
+      <c r="G65" s="91"/>
+      <c r="H65" s="91"/>
+      <c r="I65" s="91"/>
+      <c r="J65" s="91"/>
+      <c r="K65" s="93"/>
+      <c r="L65" s="91"/>
+      <c r="M65" s="91" t="s">
+        <v>53</v>
+      </c>
+      <c r="N65" s="91"/>
+      <c r="O65" s="91" t="s">
+        <v>134</v>
+      </c>
+      <c r="P65" s="91"/>
+      <c r="Q65" s="91"/>
+      <c r="R65" s="91"/>
+      <c r="S65" s="94"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2">
@@ -4689,10 +4903,10 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="B1" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -4700,7 +4914,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -4708,7 +4922,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:8">
@@ -4716,16 +4930,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:8">
@@ -4733,16 +4947,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:8">
@@ -4750,16 +4964,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:8">
@@ -4767,16 +4981,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="F7" s="1">
         <v>2</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:8">
@@ -4784,16 +4998,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="F8" s="1">
         <v>3</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:8">
@@ -4801,16 +5015,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="F9" s="1">
         <v>4</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:8">
@@ -4818,16 +5032,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="F10" s="1">
         <v>5</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:8">
@@ -4835,16 +5049,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="F11" s="1">
         <v>6</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:8">
@@ -4852,16 +5066,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="F12" s="1">
         <v>7</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:8">
@@ -4869,16 +5083,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="F13" s="1">
         <v>8</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:8">
@@ -4886,16 +5100,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="F14" s="1">
         <v>9</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:8">
@@ -4903,16 +5117,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="F15" s="1">
         <v>10</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:8">
@@ -4920,16 +5134,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="F16" s="1">
         <v>11</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:8">
@@ -4937,16 +5151,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="F17" s="1">
         <v>12</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:8">
@@ -4954,16 +5168,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="F18" s="1">
         <v>13</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:8">
@@ -4971,16 +5185,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="F19" s="1">
         <v>14</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:8">
@@ -4988,16 +5202,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="F20" s="1">
         <v>15</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:8">
@@ -5005,16 +5219,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="F21" s="1">
         <v>16</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:8">
@@ -5022,16 +5236,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="F22" s="1">
         <v>17</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:8">
@@ -5039,16 +5253,16 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="F23" s="1">
         <v>18</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:8">
@@ -5056,16 +5270,16 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="F24" s="1">
         <v>19</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -5073,7 +5287,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -5081,7 +5295,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -5089,7 +5303,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -5097,7 +5311,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -5105,7 +5319,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -5113,7 +5327,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -5121,7 +5335,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -5129,7 +5343,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -5137,7 +5351,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -5145,7 +5359,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -5153,7 +5367,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -5161,7 +5375,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -5169,7 +5383,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -5177,7 +5391,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -5185,7 +5399,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -5193,7 +5407,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -5201,7 +5415,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -5209,7 +5423,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -5217,7 +5431,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -5225,7 +5439,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -5233,7 +5447,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -5241,7 +5455,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -5249,7 +5463,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialAuxiliary.xlsx
+++ b/slots/resources/sample/SpecialAuxiliary.xlsx
@@ -268,7 +268,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="225">
   <si>
     <t>小游戏模式ID</t>
   </si>
@@ -655,6 +655,27 @@
   </si>
   <si>
     <t>免费游戏-免费旋转-14次</t>
+  </si>
+  <si>
+    <t>金蛇招财</t>
+  </si>
+  <si>
+    <t>金钱兔模式-免费旋转-8次</t>
+  </si>
+  <si>
+    <t>金钱兔模式</t>
+  </si>
+  <si>
+    <t>改出奖金符号</t>
+  </si>
+  <si>
+    <t>奖金符号收集奖励</t>
+  </si>
+  <si>
+    <t>8_10000</t>
+  </si>
+  <si>
+    <t>金钱兔</t>
   </si>
   <si>
     <t>typeID</t>
@@ -1129,7 +1150,14 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1142,20 +1170,13 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="48">
+  <fills count="49">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1213,6 +1234,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.25"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1569,7 +1596,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1593,16 +1620,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1611,92 +1638,92 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1712,12 +1739,13 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1738,7 +1766,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1747,19 +1775,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="176" fontId="1" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
@@ -1767,11 +1783,15 @@
     <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="176" fontId="1" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="1" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1779,14 +1799,22 @@
     <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1881,6 +1909,14 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="52">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2212,7 +2248,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S61"/>
+  <dimension ref="A1:S65"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14.125" customWidth="1"/>
@@ -2224,15 +2260,15 @@
     <col min="8" max="8" width="16.25" customWidth="1"/>
     <col min="9" max="9" width="29.375" customWidth="1"/>
     <col min="10" max="10" width="42.5" customWidth="1"/>
-    <col min="11" max="11" width="41.25" style="13" customWidth="1"/>
-    <col min="12" max="12" width="11.75" style="3" customWidth="1"/>
+    <col min="11" max="11" width="41.25" style="14" customWidth="1"/>
+    <col min="12" max="12" width="36.0333333333333" style="3" customWidth="1"/>
     <col min="13" max="13" width="34.4083333333333" style="3" customWidth="1"/>
     <col min="14" max="14" width="7.93333333333333" style="3" customWidth="1"/>
     <col min="15" max="15" width="11.325" customWidth="1"/>
     <col min="16" max="16" width="8.96666666666667" customWidth="1"/>
     <col min="17" max="17" width="93.375" customWidth="1"/>
     <col min="18" max="18" width="10.625" customWidth="1"/>
-    <col min="19" max="19" width="23.75" style="14" customWidth="1"/>
+    <col min="19" max="19" width="23.75" style="15" customWidth="1"/>
     <col min="20" max="20" width="60.875" customWidth="1"/>
     <col min="21" max="22" width="11.5"/>
   </cols>
@@ -2241,671 +2277,671 @@
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15" t="s">
+      <c r="C1" s="16"/>
+      <c r="D1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15" t="s">
+      <c r="E1" s="16"/>
+      <c r="F1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15" t="s">
+      <c r="H1" s="16"/>
+      <c r="I1" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="J1" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="17" t="s">
+      <c r="K1" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15" t="s">
+      <c r="L1" s="16"/>
+      <c r="M1" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="15"/>
-      <c r="O1" s="18" t="s">
+      <c r="N1" s="16"/>
+      <c r="O1" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="18" t="s">
+      <c r="P1" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="Q1" s="18" t="s">
+      <c r="Q1" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="R1" s="19" t="s">
+      <c r="R1" s="20" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="2" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15" t="s">
+      <c r="C2" s="16"/>
+      <c r="D2" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="15"/>
-      <c r="F2" s="18" t="s">
+      <c r="E2" s="16"/>
+      <c r="F2" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="15" t="s">
+      <c r="G2" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="21" t="s">
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="22" t="s">
+      <c r="K2" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="L2" s="18"/>
-      <c r="M2" s="21" t="s">
+      <c r="L2" s="19"/>
+      <c r="M2" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="N2" s="15"/>
-      <c r="O2" s="18" t="s">
+      <c r="N2" s="16"/>
+      <c r="O2" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="P2" s="18" t="s">
+      <c r="P2" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="Q2" s="21" t="s">
+      <c r="Q2" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="R2" s="19" t="s">
+      <c r="R2" s="20" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="3" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="23" t="s">
+      <c r="B3" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23" t="s">
+      <c r="C3" s="24"/>
+      <c r="D3" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="23"/>
-      <c r="F3" s="23" t="s">
+      <c r="E3" s="24"/>
+      <c r="F3" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="24" t="s">
+      <c r="G3" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
-      <c r="J3" s="25" t="s">
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="26" t="s">
+      <c r="K3" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="L3" s="23"/>
-      <c r="M3" s="23" t="s">
+      <c r="L3" s="24"/>
+      <c r="M3" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="N3" s="23"/>
-      <c r="O3" s="18" t="s">
+      <c r="N3" s="24"/>
+      <c r="O3" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="P3" s="18" t="s">
+      <c r="P3" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="Q3" s="18" t="s">
+      <c r="Q3" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="R3" s="27" t="s">
+      <c r="R3" s="28" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="4" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="15"/>
-      <c r="J4" s="28"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="15"/>
-      <c r="O4" s="15"/>
-      <c r="P4" s="15"/>
-      <c r="Q4" s="15"/>
-      <c r="R4" s="15"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="29"/>
+      <c r="K4" s="18"/>
+      <c r="L4" s="16"/>
+      <c r="M4" s="16"/>
+      <c r="N4" s="16"/>
+      <c r="O4" s="16"/>
+      <c r="P4" s="16"/>
+      <c r="Q4" s="16"/>
+      <c r="R4" s="16"/>
     </row>
     <row r="5" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A5" s="29">
+      <c r="A5" s="30">
         <v>30010001</v>
       </c>
-      <c r="B5" s="30">
+      <c r="B5" s="31">
         <v>100100</v>
       </c>
-      <c r="C5" s="30" t="s">
+      <c r="C5" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="30">
         <v>31001</v>
       </c>
-      <c r="E5" s="29" t="s">
+      <c r="E5" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="29" t="s">
+      <c r="F5" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29" t="s">
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="J5" s="29"/>
-      <c r="K5" s="31"/>
-      <c r="L5" s="15" t="s">
+      <c r="J5" s="30"/>
+      <c r="K5" s="32"/>
+      <c r="L5" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="M5" s="29" t="s">
+      <c r="M5" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="N5" s="29" t="s">
+      <c r="N5" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="O5" s="29"/>
-      <c r="P5" s="29"/>
-      <c r="Q5" s="32" t="s">
+      <c r="O5" s="30"/>
+      <c r="P5" s="30"/>
+      <c r="Q5" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="R5" s="33" t="s">
+      <c r="R5" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="S5" s="34" t="s">
+      <c r="S5" s="35" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="6" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A6" s="29">
+      <c r="A6" s="30">
         <v>30010002</v>
       </c>
-      <c r="B6" s="30">
+      <c r="B6" s="31">
         <v>100100</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="C6" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="29">
+      <c r="D6" s="30">
         <v>31002</v>
       </c>
-      <c r="E6" s="29" t="s">
+      <c r="E6" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="F6" s="29" t="s">
+      <c r="F6" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="G6" s="29"/>
-      <c r="H6" s="29"/>
-      <c r="I6" s="29" t="s">
+      <c r="G6" s="30"/>
+      <c r="H6" s="30"/>
+      <c r="I6" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="J6" s="29"/>
-      <c r="K6" s="31"/>
-      <c r="L6" s="15" t="s">
+      <c r="J6" s="30"/>
+      <c r="K6" s="32"/>
+      <c r="L6" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="M6" s="29" t="s">
+      <c r="M6" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="N6" s="29" t="s">
+      <c r="N6" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="O6" s="29"/>
-      <c r="P6" s="29"/>
-      <c r="Q6" s="32" t="s">
+      <c r="O6" s="30"/>
+      <c r="P6" s="30"/>
+      <c r="Q6" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="R6" s="33" t="s">
+      <c r="R6" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="S6" s="34"/>
+      <c r="S6" s="35"/>
     </row>
     <row r="7" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A7" s="29">
+      <c r="A7" s="30">
         <v>30010003</v>
       </c>
-      <c r="B7" s="30">
+      <c r="B7" s="31">
         <v>100100</v>
       </c>
-      <c r="C7" s="30" t="s">
+      <c r="C7" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="30">
         <v>31003</v>
       </c>
-      <c r="E7" s="29" t="s">
+      <c r="E7" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="29" t="s">
+      <c r="F7" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="G7" s="29"/>
-      <c r="H7" s="29"/>
-      <c r="I7" s="29" t="s">
+      <c r="G7" s="30"/>
+      <c r="H7" s="30"/>
+      <c r="I7" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="J7" s="29"/>
-      <c r="K7" s="31"/>
-      <c r="L7" s="15" t="s">
+      <c r="J7" s="30"/>
+      <c r="K7" s="32"/>
+      <c r="L7" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="M7" s="29" t="s">
+      <c r="M7" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="N7" s="29" t="s">
+      <c r="N7" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="O7" s="29"/>
-      <c r="P7" s="29"/>
-      <c r="Q7" s="32" t="s">
+      <c r="O7" s="30"/>
+      <c r="P7" s="30"/>
+      <c r="Q7" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="R7" s="33" t="s">
+      <c r="R7" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="S7" s="34"/>
+      <c r="S7" s="35"/>
     </row>
     <row r="8" s="3" customFormat="1" ht="15" customHeight="1" spans="1:19">
-      <c r="A8" s="29">
+      <c r="A8" s="30">
         <v>30010004</v>
       </c>
-      <c r="B8" s="30">
+      <c r="B8" s="31">
         <v>100100</v>
       </c>
-      <c r="C8" s="30" t="s">
+      <c r="C8" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="30">
         <v>31004</v>
       </c>
-      <c r="E8" s="29" t="s">
+      <c r="E8" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="F8" s="29" t="s">
+      <c r="F8" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="G8" s="29"/>
-      <c r="H8" s="29"/>
-      <c r="I8" s="29" t="s">
+      <c r="G8" s="30"/>
+      <c r="H8" s="30"/>
+      <c r="I8" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="J8" s="29"/>
-      <c r="K8" s="31"/>
-      <c r="L8" s="15" t="s">
+      <c r="J8" s="30"/>
+      <c r="K8" s="32"/>
+      <c r="L8" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="M8" s="29" t="s">
+      <c r="M8" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="N8" s="29" t="s">
+      <c r="N8" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="O8" s="29"/>
-      <c r="P8" s="29"/>
-      <c r="Q8" s="32" t="s">
+      <c r="O8" s="30"/>
+      <c r="P8" s="30"/>
+      <c r="Q8" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="R8" s="33" t="s">
+      <c r="R8" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="S8" s="34"/>
+      <c r="S8" s="35"/>
     </row>
     <row r="9" s="3" customFormat="1" ht="15" customHeight="1" spans="1:19">
-      <c r="A9" s="15">
+      <c r="A9" s="16">
         <v>30010005</v>
       </c>
-      <c r="B9" s="27">
+      <c r="B9" s="28">
         <v>100100</v>
       </c>
-      <c r="C9" s="30" t="s">
+      <c r="C9" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="15">
+      <c r="D9" s="16">
         <v>31101</v>
       </c>
-      <c r="E9" s="15" t="s">
+      <c r="E9" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="F9" s="15" t="s">
+      <c r="F9" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="G9" s="15"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="15" t="s">
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="J9" s="15"/>
-      <c r="K9" s="17"/>
-      <c r="L9" s="15" t="s">
+      <c r="J9" s="16"/>
+      <c r="K9" s="18"/>
+      <c r="L9" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="M9" s="15" t="s">
+      <c r="M9" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="N9" s="15"/>
-      <c r="O9" s="15" t="s">
+      <c r="N9" s="16"/>
+      <c r="O9" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="P9" s="15"/>
-      <c r="Q9" s="18"/>
-      <c r="R9" s="18"/>
-      <c r="S9" s="34"/>
+      <c r="P9" s="16"/>
+      <c r="Q9" s="19"/>
+      <c r="R9" s="19"/>
+      <c r="S9" s="35"/>
     </row>
     <row r="10" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A10" s="35">
+      <c r="A10" s="36">
         <v>30010006</v>
       </c>
-      <c r="B10" s="36">
+      <c r="B10" s="37">
         <v>100100</v>
       </c>
-      <c r="C10" s="30" t="s">
+      <c r="C10" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="D10" s="35">
+      <c r="D10" s="36">
         <v>31102</v>
       </c>
-      <c r="E10" s="35" t="s">
+      <c r="E10" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="F10" s="35" t="s">
+      <c r="F10" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="G10" s="35"/>
-      <c r="H10" s="35"/>
-      <c r="I10" s="35" t="s">
+      <c r="G10" s="36"/>
+      <c r="H10" s="36"/>
+      <c r="I10" s="36" t="s">
         <v>56</v>
       </c>
-      <c r="J10" s="35"/>
-      <c r="K10" s="37"/>
-      <c r="L10" s="35" t="s">
+      <c r="J10" s="36"/>
+      <c r="K10" s="38"/>
+      <c r="L10" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="M10" s="35" t="s">
+      <c r="M10" s="36" t="s">
         <v>57</v>
       </c>
-      <c r="N10" s="35" t="s">
+      <c r="N10" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="O10" s="35" t="s">
+      <c r="O10" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="P10" s="35"/>
-      <c r="Q10" s="35"/>
-      <c r="R10" s="15"/>
-      <c r="S10" s="34"/>
+      <c r="P10" s="36"/>
+      <c r="Q10" s="36"/>
+      <c r="R10" s="16"/>
+      <c r="S10" s="35"/>
     </row>
     <row r="11" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A11" s="38">
+      <c r="A11" s="39">
         <v>30010007</v>
       </c>
-      <c r="B11" s="39">
+      <c r="B11" s="40">
         <v>100100</v>
       </c>
-      <c r="C11" s="30" t="s">
+      <c r="C11" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="40">
+      <c r="D11" s="41">
         <v>31201</v>
       </c>
-      <c r="E11" s="40" t="s">
+      <c r="E11" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="F11" s="38" t="s">
+      <c r="F11" s="39" t="s">
         <v>59</v>
       </c>
-      <c r="G11" s="38">
+      <c r="G11" s="39">
         <v>2001001</v>
       </c>
-      <c r="H11" s="38" t="s">
+      <c r="H11" s="39" t="s">
         <v>60</v>
       </c>
-      <c r="I11" s="38" t="s">
+      <c r="I11" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="J11" s="38"/>
-      <c r="K11" s="41">
+      <c r="J11" s="39"/>
+      <c r="K11" s="42">
         <v>10010091</v>
       </c>
-      <c r="L11" s="38"/>
-      <c r="M11" s="38"/>
-      <c r="N11" s="38"/>
-      <c r="O11" s="38"/>
-      <c r="P11" s="38"/>
-      <c r="Q11" s="38"/>
-      <c r="R11" s="15"/>
-      <c r="S11" s="34"/>
+      <c r="L11" s="39"/>
+      <c r="M11" s="39"/>
+      <c r="N11" s="39"/>
+      <c r="O11" s="39"/>
+      <c r="P11" s="39"/>
+      <c r="Q11" s="39"/>
+      <c r="R11" s="16"/>
+      <c r="S11" s="35"/>
     </row>
     <row r="12" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A12" s="42">
+      <c r="A12" s="43">
         <v>30010008</v>
       </c>
-      <c r="B12" s="43">
+      <c r="B12" s="44">
         <v>100100</v>
       </c>
-      <c r="C12" s="30" t="s">
+      <c r="C12" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="40">
+      <c r="D12" s="41">
         <v>31202</v>
       </c>
-      <c r="E12" s="40" t="s">
+      <c r="E12" s="41" t="s">
         <v>62</v>
       </c>
-      <c r="F12" s="42" t="s">
+      <c r="F12" s="43" t="s">
         <v>53</v>
       </c>
-      <c r="G12" s="42">
+      <c r="G12" s="43">
         <v>2001001</v>
       </c>
-      <c r="H12" s="42" t="s">
+      <c r="H12" s="43" t="s">
         <v>60</v>
       </c>
-      <c r="I12" s="42" t="s">
+      <c r="I12" s="43" t="s">
         <v>63</v>
       </c>
-      <c r="J12" s="42"/>
-      <c r="K12" s="44" t="s">
+      <c r="J12" s="43"/>
+      <c r="K12" s="45" t="s">
         <v>64</v>
       </c>
-      <c r="L12" s="42"/>
-      <c r="M12" s="42"/>
-      <c r="N12" s="42"/>
-      <c r="O12" s="42"/>
-      <c r="P12" s="42"/>
-      <c r="Q12" s="42"/>
-      <c r="R12" s="15"/>
-      <c r="S12" s="34"/>
+      <c r="L12" s="43"/>
+      <c r="M12" s="43"/>
+      <c r="N12" s="43"/>
+      <c r="O12" s="43"/>
+      <c r="P12" s="43"/>
+      <c r="Q12" s="43"/>
+      <c r="R12" s="16"/>
+      <c r="S12" s="35"/>
     </row>
     <row r="13" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A13" s="45">
+      <c r="A13" s="46">
         <v>30010009</v>
       </c>
-      <c r="B13" s="46">
+      <c r="B13" s="47">
         <v>100100</v>
       </c>
-      <c r="C13" s="30" t="s">
+      <c r="C13" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="D13" s="40">
+      <c r="D13" s="41">
         <v>31203</v>
       </c>
-      <c r="E13" s="40" t="s">
+      <c r="E13" s="41" t="s">
         <v>65</v>
       </c>
-      <c r="F13" s="45" t="s">
+      <c r="F13" s="46" t="s">
         <v>53</v>
       </c>
-      <c r="G13" s="45">
+      <c r="G13" s="46">
         <v>2001001</v>
       </c>
-      <c r="H13" s="45" t="s">
+      <c r="H13" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="I13" s="45" t="s">
+      <c r="I13" s="46" t="s">
         <v>66</v>
       </c>
-      <c r="J13" s="45"/>
-      <c r="K13" s="47" t="s">
+      <c r="J13" s="46"/>
+      <c r="K13" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="L13" s="45"/>
-      <c r="M13" s="45"/>
-      <c r="N13" s="45"/>
-      <c r="O13" s="45"/>
-      <c r="P13" s="45"/>
-      <c r="Q13" s="45"/>
-      <c r="R13" s="15"/>
-      <c r="S13" s="34"/>
+      <c r="L13" s="46"/>
+      <c r="M13" s="46"/>
+      <c r="N13" s="46"/>
+      <c r="O13" s="46"/>
+      <c r="P13" s="46"/>
+      <c r="Q13" s="46"/>
+      <c r="R13" s="16"/>
+      <c r="S13" s="35"/>
     </row>
     <row r="14" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A14" s="40">
+      <c r="A14" s="41">
         <v>30010010</v>
       </c>
-      <c r="B14" s="48">
+      <c r="B14" s="49">
         <v>100100</v>
       </c>
-      <c r="C14" s="30" t="s">
+      <c r="C14" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="D14" s="49">
+      <c r="D14" s="50">
         <v>31301</v>
       </c>
-      <c r="E14" s="49" t="s">
+      <c r="E14" s="50" t="s">
         <v>68</v>
       </c>
-      <c r="F14" s="40" t="s">
+      <c r="F14" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="G14" s="40"/>
-      <c r="H14" s="40"/>
-      <c r="I14" s="40" t="s">
+      <c r="G14" s="41"/>
+      <c r="H14" s="41"/>
+      <c r="I14" s="41" t="s">
         <v>69</v>
       </c>
-      <c r="J14" s="40"/>
-      <c r="K14" s="50"/>
-      <c r="L14" s="40" t="s">
+      <c r="J14" s="41"/>
+      <c r="K14" s="51"/>
+      <c r="L14" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="M14" s="40" t="s">
+      <c r="M14" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="N14" s="40"/>
-      <c r="O14" s="40"/>
-      <c r="P14" s="40"/>
-      <c r="Q14" s="51" t="s">
+      <c r="N14" s="41"/>
+      <c r="O14" s="41"/>
+      <c r="P14" s="41"/>
+      <c r="Q14" s="52" t="s">
         <v>71</v>
       </c>
-      <c r="R14" s="52" t="s">
+      <c r="R14" s="53" t="s">
         <v>72</v>
       </c>
-      <c r="S14" s="18" t="s">
+      <c r="S14" s="19" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="15" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A15" s="45">
+      <c r="A15" s="46">
         <v>30010011</v>
       </c>
-      <c r="B15" s="46">
+      <c r="B15" s="47">
         <v>100100</v>
       </c>
-      <c r="C15" s="30" t="s">
+      <c r="C15" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="D15" s="49">
+      <c r="D15" s="50">
         <v>31302</v>
       </c>
-      <c r="E15" s="49" t="s">
+      <c r="E15" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F15" s="45" t="s">
+      <c r="F15" s="46" t="s">
         <v>34</v>
       </c>
-      <c r="G15" s="45"/>
-      <c r="H15" s="45"/>
-      <c r="I15" s="45" t="s">
+      <c r="G15" s="46"/>
+      <c r="H15" s="46"/>
+      <c r="I15" s="46" t="s">
         <v>75</v>
       </c>
-      <c r="J15" s="45"/>
-      <c r="K15" s="47"/>
-      <c r="L15" s="45" t="s">
+      <c r="J15" s="46"/>
+      <c r="K15" s="48"/>
+      <c r="L15" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="M15" s="45" t="s">
+      <c r="M15" s="46" t="s">
         <v>57</v>
       </c>
-      <c r="N15" s="45"/>
-      <c r="O15" s="45"/>
-      <c r="P15" s="45"/>
-      <c r="Q15" s="45"/>
-      <c r="R15" s="15"/>
-      <c r="S15" s="34"/>
+      <c r="N15" s="46"/>
+      <c r="O15" s="46"/>
+      <c r="P15" s="46"/>
+      <c r="Q15" s="46"/>
+      <c r="R15" s="16"/>
+      <c r="S15" s="35"/>
     </row>
     <row r="16" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A16" s="45">
+      <c r="A16" s="46">
         <v>30010012</v>
       </c>
-      <c r="B16" s="46">
+      <c r="B16" s="47">
         <v>100100</v>
       </c>
-      <c r="C16" s="30" t="s">
+      <c r="C16" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="D16" s="49">
+      <c r="D16" s="50">
         <v>31303</v>
       </c>
-      <c r="E16" s="49" t="s">
+      <c r="E16" s="50" t="s">
         <v>76</v>
       </c>
-      <c r="F16" s="45" t="s">
+      <c r="F16" s="46" t="s">
         <v>53</v>
       </c>
-      <c r="G16" s="45">
+      <c r="G16" s="46">
         <v>2001001</v>
       </c>
-      <c r="H16" s="45" t="s">
+      <c r="H16" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="I16" s="45" t="s">
+      <c r="I16" s="46" t="s">
         <v>66</v>
       </c>
-      <c r="J16" s="45"/>
-      <c r="K16" s="47" t="s">
+      <c r="J16" s="46"/>
+      <c r="K16" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="L16" s="45"/>
-      <c r="M16" s="45"/>
-      <c r="N16" s="45"/>
-      <c r="O16" s="45"/>
-      <c r="P16" s="45"/>
-      <c r="Q16" s="45"/>
-      <c r="R16" s="15"/>
-      <c r="S16" s="34"/>
+      <c r="L16" s="46"/>
+      <c r="M16" s="46"/>
+      <c r="N16" s="46"/>
+      <c r="O16" s="46"/>
+      <c r="P16" s="46"/>
+      <c r="Q16" s="46"/>
+      <c r="R16" s="16"/>
+      <c r="S16" s="35"/>
     </row>
     <row r="17" s="3" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A17" s="15">
+      <c r="A17" s="16">
         <v>30070001</v>
       </c>
       <c r="B17" s="3">
@@ -2914,30 +2950,30 @@
       <c r="C17" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D17" s="38">
+      <c r="D17" s="39">
         <v>34001</v>
       </c>
-      <c r="E17" s="38" t="s">
+      <c r="E17" s="39" t="s">
         <v>78</v>
       </c>
-      <c r="F17" s="38" t="s">
+      <c r="F17" s="39" t="s">
         <v>79</v>
       </c>
-      <c r="G17" s="27">
+      <c r="G17" s="28">
         <v>2007001</v>
       </c>
-      <c r="H17" s="15" t="s">
+      <c r="H17" s="16" t="s">
         <v>60</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="K17" s="53" t="s">
+      <c r="K17" s="54" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="18" s="3" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A18" s="15">
+      <c r="A18" s="16">
         <v>30070002</v>
       </c>
       <c r="B18" s="3">
@@ -2946,30 +2982,30 @@
       <c r="C18" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D18" s="38">
+      <c r="D18" s="39">
         <v>34002</v>
       </c>
-      <c r="E18" s="38" t="s">
+      <c r="E18" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="F18" s="38" t="s">
+      <c r="F18" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="G18" s="27">
+      <c r="G18" s="28">
         <v>2007001</v>
       </c>
-      <c r="H18" s="15" t="s">
+      <c r="H18" s="16" t="s">
         <v>60</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="K18" s="53" t="s">
+      <c r="K18" s="54" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="19" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A19" s="40">
+      <c r="A19" s="41">
         <v>30120001</v>
       </c>
       <c r="B19" s="4">
@@ -2978,33 +3014,33 @@
       <c r="C19" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D19" s="40">
+      <c r="D19" s="41">
         <v>32001</v>
       </c>
-      <c r="E19" s="40" t="s">
+      <c r="E19" s="41" t="s">
         <v>85</v>
       </c>
-      <c r="F19" s="40" t="s">
+      <c r="F19" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="G19" s="48">
+      <c r="G19" s="49">
         <v>2012001</v>
       </c>
-      <c r="H19" s="40" t="s">
+      <c r="H19" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="I19" s="40" t="s">
+      <c r="I19" s="41" t="s">
         <v>85</v>
       </c>
-      <c r="J19" s="40" t="s">
+      <c r="J19" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="K19" s="54">
+      <c r="K19" s="55">
         <v>10120041</v>
       </c>
     </row>
     <row r="20" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A20" s="40">
+      <c r="A20" s="41">
         <v>30120002</v>
       </c>
       <c r="B20" s="4">
@@ -3013,33 +3049,33 @@
       <c r="C20" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D20" s="40">
+      <c r="D20" s="41">
         <v>32002</v>
       </c>
-      <c r="E20" s="40" t="s">
+      <c r="E20" s="41" t="s">
         <v>87</v>
       </c>
-      <c r="F20" s="40" t="s">
+      <c r="F20" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="G20" s="48">
+      <c r="G20" s="49">
         <v>2012001</v>
       </c>
-      <c r="H20" s="40" t="s">
+      <c r="H20" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="I20" s="40" t="s">
+      <c r="I20" s="41" t="s">
         <v>87</v>
       </c>
-      <c r="J20" s="40" t="s">
+      <c r="J20" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="K20" s="54">
+      <c r="K20" s="55">
         <v>10120042</v>
       </c>
     </row>
     <row r="21" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A21" s="40">
+      <c r="A21" s="41">
         <v>30120003</v>
       </c>
       <c r="B21" s="4">
@@ -3048,33 +3084,33 @@
       <c r="C21" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D21" s="40">
+      <c r="D21" s="41">
         <v>32003</v>
       </c>
-      <c r="E21" s="40" t="s">
+      <c r="E21" s="41" t="s">
         <v>88</v>
       </c>
-      <c r="F21" s="40" t="s">
+      <c r="F21" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="G21" s="48">
+      <c r="G21" s="49">
         <v>2012001</v>
       </c>
-      <c r="H21" s="40" t="s">
+      <c r="H21" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="I21" s="40" t="s">
+      <c r="I21" s="41" t="s">
         <v>88</v>
       </c>
-      <c r="J21" s="40" t="s">
+      <c r="J21" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="K21" s="54">
+      <c r="K21" s="55">
         <v>10120043</v>
       </c>
     </row>
     <row r="22" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A22" s="40">
+      <c r="A22" s="41">
         <v>30120004</v>
       </c>
       <c r="B22" s="4">
@@ -3083,33 +3119,33 @@
       <c r="C22" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D22" s="40">
+      <c r="D22" s="41">
         <v>32004</v>
       </c>
-      <c r="E22" s="40" t="s">
+      <c r="E22" s="41" t="s">
         <v>89</v>
       </c>
-      <c r="F22" s="40" t="s">
+      <c r="F22" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="G22" s="48">
+      <c r="G22" s="49">
         <v>2012001</v>
       </c>
-      <c r="H22" s="40" t="s">
+      <c r="H22" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="I22" s="40" t="s">
+      <c r="I22" s="41" t="s">
         <v>89</v>
       </c>
-      <c r="J22" s="40" t="s">
+      <c r="J22" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="K22" s="54">
+      <c r="K22" s="55">
         <v>10120044</v>
       </c>
     </row>
     <row r="23" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A23" s="40">
+      <c r="A23" s="41">
         <v>30120005</v>
       </c>
       <c r="B23" s="4">
@@ -3118,33 +3154,33 @@
       <c r="C23" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D23" s="40">
+      <c r="D23" s="41">
         <v>32005</v>
       </c>
-      <c r="E23" s="40" t="s">
+      <c r="E23" s="41" t="s">
         <v>89</v>
       </c>
-      <c r="F23" s="40" t="s">
+      <c r="F23" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="G23" s="48">
+      <c r="G23" s="49">
         <v>2012001</v>
       </c>
-      <c r="H23" s="40" t="s">
+      <c r="H23" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="I23" s="40" t="s">
+      <c r="I23" s="41" t="s">
         <v>89</v>
       </c>
-      <c r="J23" s="40" t="s">
+      <c r="J23" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="K23" s="54">
+      <c r="K23" s="55">
         <v>10120045</v>
       </c>
     </row>
     <row r="24" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A24" s="40">
+      <c r="A24" s="41">
         <v>30120006</v>
       </c>
       <c r="B24" s="4">
@@ -3153,33 +3189,33 @@
       <c r="C24" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D24" s="40">
+      <c r="D24" s="41">
         <v>32006</v>
       </c>
-      <c r="E24" s="40" t="s">
+      <c r="E24" s="41" t="s">
         <v>89</v>
       </c>
-      <c r="F24" s="40" t="s">
+      <c r="F24" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="G24" s="48">
+      <c r="G24" s="49">
         <v>2012001</v>
       </c>
-      <c r="H24" s="40" t="s">
+      <c r="H24" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="I24" s="40" t="s">
+      <c r="I24" s="41" t="s">
         <v>89</v>
       </c>
-      <c r="J24" s="40" t="s">
+      <c r="J24" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="K24" s="54">
+      <c r="K24" s="55">
         <v>10120046</v>
       </c>
     </row>
     <row r="25" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A25" s="55">
+      <c r="A25" s="56">
         <v>30120011</v>
       </c>
       <c r="B25" s="5">
@@ -3188,33 +3224,33 @@
       <c r="C25" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="D25" s="40">
+      <c r="D25" s="41">
         <v>32101</v>
       </c>
-      <c r="E25" s="55" t="s">
+      <c r="E25" s="56" t="s">
         <v>85</v>
       </c>
-      <c r="F25" s="55" t="s">
+      <c r="F25" s="56" t="s">
         <v>53</v>
       </c>
-      <c r="G25" s="56">
+      <c r="G25" s="57">
         <v>2012001</v>
       </c>
-      <c r="H25" s="55" t="s">
+      <c r="H25" s="56" t="s">
         <v>60</v>
       </c>
-      <c r="I25" s="55" t="s">
+      <c r="I25" s="56" t="s">
         <v>85</v>
       </c>
-      <c r="J25" s="55" t="s">
+      <c r="J25" s="56" t="s">
         <v>91</v>
       </c>
-      <c r="K25" s="57">
+      <c r="K25" s="58">
         <v>10120041</v>
       </c>
     </row>
     <row r="26" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A26" s="55">
+      <c r="A26" s="56">
         <v>30120012</v>
       </c>
       <c r="B26" s="5">
@@ -3223,33 +3259,33 @@
       <c r="C26" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="D26" s="40">
+      <c r="D26" s="41">
         <v>32102</v>
       </c>
-      <c r="E26" s="55" t="s">
+      <c r="E26" s="56" t="s">
         <v>87</v>
       </c>
-      <c r="F26" s="55" t="s">
+      <c r="F26" s="56" t="s">
         <v>53</v>
       </c>
-      <c r="G26" s="56">
+      <c r="G26" s="57">
         <v>2012001</v>
       </c>
-      <c r="H26" s="55" t="s">
+      <c r="H26" s="56" t="s">
         <v>60</v>
       </c>
-      <c r="I26" s="55" t="s">
+      <c r="I26" s="56" t="s">
         <v>87</v>
       </c>
-      <c r="J26" s="55" t="s">
+      <c r="J26" s="56" t="s">
         <v>91</v>
       </c>
-      <c r="K26" s="57">
+      <c r="K26" s="58">
         <v>10120042</v>
       </c>
     </row>
     <row r="27" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A27" s="55">
+      <c r="A27" s="56">
         <v>30120013</v>
       </c>
       <c r="B27" s="5">
@@ -3258,33 +3294,33 @@
       <c r="C27" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="D27" s="40">
+      <c r="D27" s="41">
         <v>32103</v>
       </c>
-      <c r="E27" s="55" t="s">
+      <c r="E27" s="56" t="s">
         <v>88</v>
       </c>
-      <c r="F27" s="55" t="s">
+      <c r="F27" s="56" t="s">
         <v>53</v>
       </c>
-      <c r="G27" s="56">
+      <c r="G27" s="57">
         <v>2012001</v>
       </c>
-      <c r="H27" s="55" t="s">
+      <c r="H27" s="56" t="s">
         <v>60</v>
       </c>
-      <c r="I27" s="55" t="s">
+      <c r="I27" s="56" t="s">
         <v>88</v>
       </c>
-      <c r="J27" s="55" t="s">
+      <c r="J27" s="56" t="s">
         <v>91</v>
       </c>
-      <c r="K27" s="57">
+      <c r="K27" s="58">
         <v>10120043</v>
       </c>
     </row>
     <row r="28" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A28" s="55">
+      <c r="A28" s="56">
         <v>30120014</v>
       </c>
       <c r="B28" s="5">
@@ -3293,33 +3329,33 @@
       <c r="C28" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="D28" s="40">
+      <c r="D28" s="41">
         <v>32104</v>
       </c>
-      <c r="E28" s="55" t="s">
+      <c r="E28" s="56" t="s">
         <v>89</v>
       </c>
-      <c r="F28" s="55" t="s">
+      <c r="F28" s="56" t="s">
         <v>53</v>
       </c>
-      <c r="G28" s="56">
+      <c r="G28" s="57">
         <v>2012001</v>
       </c>
-      <c r="H28" s="55" t="s">
+      <c r="H28" s="56" t="s">
         <v>60</v>
       </c>
-      <c r="I28" s="55" t="s">
+      <c r="I28" s="56" t="s">
         <v>89</v>
       </c>
-      <c r="J28" s="55" t="s">
+      <c r="J28" s="56" t="s">
         <v>91</v>
       </c>
-      <c r="K28" s="57">
+      <c r="K28" s="58">
         <v>10120044</v>
       </c>
     </row>
     <row r="29" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A29" s="55">
+      <c r="A29" s="56">
         <v>30120015</v>
       </c>
       <c r="B29" s="5">
@@ -3328,33 +3364,33 @@
       <c r="C29" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="D29" s="40">
+      <c r="D29" s="41">
         <v>32105</v>
       </c>
-      <c r="E29" s="55" t="s">
+      <c r="E29" s="56" t="s">
         <v>89</v>
       </c>
-      <c r="F29" s="55" t="s">
+      <c r="F29" s="56" t="s">
         <v>53</v>
       </c>
-      <c r="G29" s="56">
+      <c r="G29" s="57">
         <v>2012001</v>
       </c>
-      <c r="H29" s="55" t="s">
+      <c r="H29" s="56" t="s">
         <v>60</v>
       </c>
-      <c r="I29" s="55" t="s">
+      <c r="I29" s="56" t="s">
         <v>89</v>
       </c>
-      <c r="J29" s="55" t="s">
+      <c r="J29" s="56" t="s">
         <v>91</v>
       </c>
-      <c r="K29" s="57">
+      <c r="K29" s="58">
         <v>10120045</v>
       </c>
     </row>
     <row r="30" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A30" s="55">
+      <c r="A30" s="56">
         <v>30120016</v>
       </c>
       <c r="B30" s="5">
@@ -3363,33 +3399,33 @@
       <c r="C30" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="D30" s="40">
+      <c r="D30" s="41">
         <v>32106</v>
       </c>
-      <c r="E30" s="55" t="s">
+      <c r="E30" s="56" t="s">
         <v>89</v>
       </c>
-      <c r="F30" s="55" t="s">
+      <c r="F30" s="56" t="s">
         <v>53</v>
       </c>
-      <c r="G30" s="56">
+      <c r="G30" s="57">
         <v>2012001</v>
       </c>
-      <c r="H30" s="55" t="s">
+      <c r="H30" s="56" t="s">
         <v>60</v>
       </c>
-      <c r="I30" s="55" t="s">
+      <c r="I30" s="56" t="s">
         <v>89</v>
       </c>
-      <c r="J30" s="55" t="s">
+      <c r="J30" s="56" t="s">
         <v>91</v>
       </c>
-      <c r="K30" s="57">
+      <c r="K30" s="58">
         <v>10120046</v>
       </c>
     </row>
     <row r="31" s="6" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A31" s="49">
+      <c r="A31" s="50">
         <v>30120021</v>
       </c>
       <c r="B31" s="6">
@@ -3398,31 +3434,31 @@
       <c r="C31" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D31" s="49">
+      <c r="D31" s="50">
         <v>32201</v>
       </c>
-      <c r="E31" s="49" t="s">
+      <c r="E31" s="50" t="s">
         <v>85</v>
       </c>
-      <c r="F31" s="49" t="s">
+      <c r="F31" s="50" t="s">
         <v>53</v>
       </c>
-      <c r="G31" s="58">
+      <c r="G31" s="59">
         <v>2012001</v>
       </c>
-      <c r="H31" s="49" t="s">
+      <c r="H31" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="I31" s="49" t="s">
+      <c r="I31" s="50" t="s">
         <v>85</v>
       </c>
-      <c r="J31" s="49"/>
-      <c r="K31" s="59">
+      <c r="J31" s="50"/>
+      <c r="K31" s="60">
         <v>10120041</v>
       </c>
     </row>
     <row r="32" s="6" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A32" s="49">
+      <c r="A32" s="50">
         <v>30120022</v>
       </c>
       <c r="B32" s="6">
@@ -3431,31 +3467,31 @@
       <c r="C32" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D32" s="49">
+      <c r="D32" s="50">
         <v>32202</v>
       </c>
-      <c r="E32" s="49" t="s">
+      <c r="E32" s="50" t="s">
         <v>87</v>
       </c>
-      <c r="F32" s="49" t="s">
+      <c r="F32" s="50" t="s">
         <v>53</v>
       </c>
-      <c r="G32" s="58">
+      <c r="G32" s="59">
         <v>2012001</v>
       </c>
-      <c r="H32" s="49" t="s">
+      <c r="H32" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="I32" s="49" t="s">
+      <c r="I32" s="50" t="s">
         <v>87</v>
       </c>
-      <c r="J32" s="49"/>
-      <c r="K32" s="59">
+      <c r="J32" s="50"/>
+      <c r="K32" s="60">
         <v>10120042</v>
       </c>
     </row>
     <row r="33" s="6" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A33" s="49">
+      <c r="A33" s="50">
         <v>30120023</v>
       </c>
       <c r="B33" s="6">
@@ -3464,31 +3500,31 @@
       <c r="C33" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D33" s="49">
+      <c r="D33" s="50">
         <v>32203</v>
       </c>
-      <c r="E33" s="49" t="s">
+      <c r="E33" s="50" t="s">
         <v>88</v>
       </c>
-      <c r="F33" s="49" t="s">
+      <c r="F33" s="50" t="s">
         <v>53</v>
       </c>
-      <c r="G33" s="58">
+      <c r="G33" s="59">
         <v>2012001</v>
       </c>
-      <c r="H33" s="49" t="s">
+      <c r="H33" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="I33" s="49" t="s">
+      <c r="I33" s="50" t="s">
         <v>88</v>
       </c>
-      <c r="J33" s="49"/>
-      <c r="K33" s="59">
+      <c r="J33" s="50"/>
+      <c r="K33" s="60">
         <v>10120043</v>
       </c>
     </row>
     <row r="34" s="6" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A34" s="49">
+      <c r="A34" s="50">
         <v>30120024</v>
       </c>
       <c r="B34" s="6">
@@ -3497,31 +3533,31 @@
       <c r="C34" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D34" s="49">
+      <c r="D34" s="50">
         <v>32204</v>
       </c>
-      <c r="E34" s="49" t="s">
+      <c r="E34" s="50" t="s">
         <v>89</v>
       </c>
-      <c r="F34" s="49" t="s">
+      <c r="F34" s="50" t="s">
         <v>53</v>
       </c>
-      <c r="G34" s="58">
+      <c r="G34" s="59">
         <v>2012001</v>
       </c>
-      <c r="H34" s="49" t="s">
+      <c r="H34" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="I34" s="49" t="s">
+      <c r="I34" s="50" t="s">
         <v>89</v>
       </c>
-      <c r="J34" s="49"/>
-      <c r="K34" s="59">
+      <c r="J34" s="50"/>
+      <c r="K34" s="60">
         <v>10120044</v>
       </c>
     </row>
     <row r="35" s="6" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A35" s="49">
+      <c r="A35" s="50">
         <v>30120025</v>
       </c>
       <c r="B35" s="6">
@@ -3530,31 +3566,31 @@
       <c r="C35" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D35" s="49">
+      <c r="D35" s="50">
         <v>32205</v>
       </c>
-      <c r="E35" s="49" t="s">
+      <c r="E35" s="50" t="s">
         <v>89</v>
       </c>
-      <c r="F35" s="49" t="s">
+      <c r="F35" s="50" t="s">
         <v>53</v>
       </c>
-      <c r="G35" s="58">
+      <c r="G35" s="59">
         <v>2012001</v>
       </c>
-      <c r="H35" s="49" t="s">
+      <c r="H35" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="I35" s="49" t="s">
+      <c r="I35" s="50" t="s">
         <v>89</v>
       </c>
-      <c r="J35" s="49"/>
-      <c r="K35" s="59">
+      <c r="J35" s="50"/>
+      <c r="K35" s="60">
         <v>10120045</v>
       </c>
     </row>
     <row r="36" s="6" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A36" s="49">
+      <c r="A36" s="50">
         <v>30120026</v>
       </c>
       <c r="B36" s="6">
@@ -3563,1089 +3599,1249 @@
       <c r="C36" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D36" s="49">
+      <c r="D36" s="50">
         <v>32206</v>
       </c>
-      <c r="E36" s="49" t="s">
+      <c r="E36" s="50" t="s">
         <v>89</v>
       </c>
-      <c r="F36" s="49" t="s">
+      <c r="F36" s="50" t="s">
         <v>53</v>
       </c>
-      <c r="G36" s="58">
+      <c r="G36" s="59">
         <v>2012001</v>
       </c>
-      <c r="H36" s="49" t="s">
+      <c r="H36" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="I36" s="49" t="s">
+      <c r="I36" s="50" t="s">
         <v>89</v>
       </c>
-      <c r="J36" s="49"/>
-      <c r="K36" s="59">
+      <c r="J36" s="50"/>
+      <c r="K36" s="60">
         <v>10120046</v>
       </c>
     </row>
     <row r="37" s="7" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A37" s="60">
+      <c r="A37" s="61">
         <v>30240001</v>
       </c>
-      <c r="B37" s="61">
+      <c r="B37" s="62">
         <v>102400</v>
       </c>
-      <c r="C37" s="61" t="s">
+      <c r="C37" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="D37" s="60">
+      <c r="D37" s="61">
         <v>32401</v>
       </c>
-      <c r="E37" s="60" t="s">
+      <c r="E37" s="61" t="s">
         <v>33</v>
       </c>
-      <c r="F37" s="60" t="s">
+      <c r="F37" s="61" t="s">
         <v>34</v>
       </c>
-      <c r="G37" s="60"/>
-      <c r="H37" s="60"/>
-      <c r="I37" s="60" t="s">
+      <c r="G37" s="61"/>
+      <c r="H37" s="61"/>
+      <c r="I37" s="61" t="s">
         <v>35</v>
       </c>
-      <c r="J37" s="60"/>
-      <c r="K37" s="62"/>
-      <c r="L37" s="60" t="s">
+      <c r="J37" s="61"/>
+      <c r="K37" s="63"/>
+      <c r="L37" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="M37" s="60" t="s">
+      <c r="M37" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="N37" s="60" t="s">
+      <c r="N37" s="61" t="s">
         <v>38</v>
       </c>
-      <c r="O37" s="60"/>
-      <c r="P37" s="60"/>
-      <c r="Q37" s="63" t="s">
+      <c r="O37" s="61"/>
+      <c r="P37" s="61"/>
+      <c r="Q37" s="64" t="s">
         <v>39</v>
       </c>
-      <c r="R37" s="64" t="s">
+      <c r="R37" s="65" t="s">
         <v>40</v>
       </c>
-      <c r="S37" s="65" t="s">
+      <c r="S37" s="66" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="38" s="7" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A38" s="60">
+      <c r="A38" s="61">
         <v>30240002</v>
       </c>
-      <c r="B38" s="61">
+      <c r="B38" s="62">
         <v>102400</v>
       </c>
-      <c r="C38" s="61" t="s">
+      <c r="C38" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="D38" s="60">
+      <c r="D38" s="61">
         <v>32402</v>
       </c>
-      <c r="E38" s="60" t="s">
+      <c r="E38" s="61" t="s">
         <v>42</v>
       </c>
-      <c r="F38" s="60" t="s">
+      <c r="F38" s="61" t="s">
         <v>34</v>
       </c>
-      <c r="G38" s="60"/>
-      <c r="H38" s="60"/>
-      <c r="I38" s="60" t="s">
+      <c r="G38" s="61"/>
+      <c r="H38" s="61"/>
+      <c r="I38" s="61" t="s">
         <v>43</v>
       </c>
-      <c r="J38" s="60"/>
-      <c r="K38" s="62"/>
-      <c r="L38" s="60" t="s">
+      <c r="J38" s="61"/>
+      <c r="K38" s="63"/>
+      <c r="L38" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="M38" s="60" t="s">
+      <c r="M38" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="N38" s="60" t="s">
+      <c r="N38" s="61" t="s">
         <v>38</v>
       </c>
-      <c r="O38" s="60"/>
-      <c r="P38" s="60"/>
-      <c r="Q38" s="63" t="s">
+      <c r="O38" s="61"/>
+      <c r="P38" s="61"/>
+      <c r="Q38" s="64" t="s">
         <v>44</v>
       </c>
-      <c r="R38" s="64" t="s">
+      <c r="R38" s="65" t="s">
         <v>40</v>
       </c>
-      <c r="S38" s="65"/>
+      <c r="S38" s="66"/>
     </row>
     <row r="39" s="7" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A39" s="60">
+      <c r="A39" s="61">
         <v>30240003</v>
       </c>
-      <c r="B39" s="61">
+      <c r="B39" s="62">
         <v>102400</v>
       </c>
-      <c r="C39" s="61" t="s">
+      <c r="C39" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="D39" s="60">
+      <c r="D39" s="61">
         <v>32403</v>
       </c>
-      <c r="E39" s="60" t="s">
+      <c r="E39" s="61" t="s">
         <v>45</v>
       </c>
-      <c r="F39" s="60" t="s">
+      <c r="F39" s="61" t="s">
         <v>34</v>
       </c>
-      <c r="G39" s="60"/>
-      <c r="H39" s="60"/>
-      <c r="I39" s="60" t="s">
+      <c r="G39" s="61"/>
+      <c r="H39" s="61"/>
+      <c r="I39" s="61" t="s">
         <v>46</v>
       </c>
-      <c r="J39" s="60"/>
-      <c r="K39" s="62"/>
-      <c r="L39" s="60" t="s">
+      <c r="J39" s="61"/>
+      <c r="K39" s="63"/>
+      <c r="L39" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="M39" s="60" t="s">
+      <c r="M39" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="N39" s="60" t="s">
+      <c r="N39" s="61" t="s">
         <v>38</v>
       </c>
-      <c r="O39" s="60"/>
-      <c r="P39" s="60"/>
-      <c r="Q39" s="63" t="s">
+      <c r="O39" s="61"/>
+      <c r="P39" s="61"/>
+      <c r="Q39" s="64" t="s">
         <v>47</v>
       </c>
-      <c r="R39" s="64" t="s">
+      <c r="R39" s="65" t="s">
         <v>40</v>
       </c>
-      <c r="S39" s="65"/>
+      <c r="S39" s="66"/>
     </row>
     <row r="40" s="7" customFormat="1" ht="15" customHeight="1" spans="1:19">
-      <c r="A40" s="60">
+      <c r="A40" s="61">
         <v>30240004</v>
       </c>
-      <c r="B40" s="61">
+      <c r="B40" s="62">
         <v>102400</v>
       </c>
-      <c r="C40" s="61" t="s">
+      <c r="C40" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="D40" s="60">
+      <c r="D40" s="61">
         <v>32404</v>
       </c>
-      <c r="E40" s="60" t="s">
+      <c r="E40" s="61" t="s">
         <v>48</v>
       </c>
-      <c r="F40" s="60" t="s">
+      <c r="F40" s="61" t="s">
         <v>34</v>
       </c>
-      <c r="G40" s="60"/>
-      <c r="H40" s="60"/>
-      <c r="I40" s="60" t="s">
+      <c r="G40" s="61"/>
+      <c r="H40" s="61"/>
+      <c r="I40" s="61" t="s">
         <v>49</v>
       </c>
-      <c r="J40" s="60"/>
-      <c r="K40" s="62"/>
-      <c r="L40" s="60" t="s">
+      <c r="J40" s="61"/>
+      <c r="K40" s="63"/>
+      <c r="L40" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="M40" s="60" t="s">
+      <c r="M40" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="N40" s="60" t="s">
+      <c r="N40" s="61" t="s">
         <v>38</v>
       </c>
-      <c r="O40" s="60"/>
-      <c r="P40" s="60"/>
-      <c r="Q40" s="63" t="s">
+      <c r="O40" s="61"/>
+      <c r="P40" s="61"/>
+      <c r="Q40" s="64" t="s">
         <v>50</v>
       </c>
-      <c r="R40" s="64" t="s">
+      <c r="R40" s="65" t="s">
         <v>40</v>
       </c>
-      <c r="S40" s="65"/>
+      <c r="S40" s="66"/>
     </row>
     <row r="41" s="7" customFormat="1" ht="15" customHeight="1" spans="1:19">
-      <c r="A41" s="60">
+      <c r="A41" s="61">
         <v>30240005</v>
       </c>
-      <c r="B41" s="61">
+      <c r="B41" s="62">
         <v>102400</v>
       </c>
-      <c r="C41" s="61" t="s">
+      <c r="C41" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="D41" s="60">
+      <c r="D41" s="61">
         <v>32411</v>
       </c>
-      <c r="E41" s="60" t="s">
+      <c r="E41" s="61" t="s">
         <v>51</v>
       </c>
-      <c r="F41" s="60" t="s">
+      <c r="F41" s="61" t="s">
         <v>34</v>
       </c>
-      <c r="G41" s="60"/>
-      <c r="H41" s="60"/>
-      <c r="I41" s="60" t="s">
+      <c r="G41" s="61"/>
+      <c r="H41" s="61"/>
+      <c r="I41" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="J41" s="60"/>
-      <c r="K41" s="62"/>
-      <c r="L41" s="60" t="s">
+      <c r="J41" s="61"/>
+      <c r="K41" s="63"/>
+      <c r="L41" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="M41" s="60" t="s">
+      <c r="M41" s="61" t="s">
         <v>53</v>
       </c>
-      <c r="N41" s="60"/>
-      <c r="O41" s="60" t="s">
+      <c r="N41" s="61"/>
+      <c r="O41" s="61" t="s">
         <v>54</v>
       </c>
-      <c r="P41" s="60"/>
-      <c r="Q41" s="63"/>
-      <c r="R41" s="63"/>
-      <c r="S41" s="65"/>
+      <c r="P41" s="61"/>
+      <c r="Q41" s="64"/>
+      <c r="R41" s="64"/>
+      <c r="S41" s="66"/>
     </row>
     <row r="42" s="7" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A42" s="60">
+      <c r="A42" s="61">
         <v>30240006</v>
       </c>
-      <c r="B42" s="61">
+      <c r="B42" s="62">
         <v>102400</v>
       </c>
-      <c r="C42" s="61" t="s">
+      <c r="C42" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="D42" s="60">
+      <c r="D42" s="61">
         <v>32421</v>
       </c>
-      <c r="E42" s="60" t="s">
+      <c r="E42" s="61" t="s">
         <v>55</v>
       </c>
-      <c r="F42" s="60" t="s">
+      <c r="F42" s="61" t="s">
         <v>34</v>
       </c>
-      <c r="G42" s="60"/>
-      <c r="H42" s="60"/>
-      <c r="I42" s="60" t="s">
+      <c r="G42" s="61"/>
+      <c r="H42" s="61"/>
+      <c r="I42" s="61" t="s">
         <v>56</v>
       </c>
-      <c r="J42" s="60"/>
-      <c r="K42" s="62"/>
-      <c r="L42" s="60" t="s">
+      <c r="J42" s="61"/>
+      <c r="K42" s="63"/>
+      <c r="L42" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="M42" s="60" t="s">
+      <c r="M42" s="61" t="s">
         <v>57</v>
       </c>
-      <c r="N42" s="60" t="s">
+      <c r="N42" s="61" t="s">
         <v>38</v>
       </c>
-      <c r="O42" s="60" t="s">
+      <c r="O42" s="61" t="s">
         <v>54</v>
       </c>
-      <c r="P42" s="60"/>
-      <c r="Q42" s="60"/>
-      <c r="R42" s="60"/>
-      <c r="S42" s="65"/>
+      <c r="P42" s="61"/>
+      <c r="Q42" s="61"/>
+      <c r="R42" s="61"/>
+      <c r="S42" s="66"/>
     </row>
     <row r="43" s="7" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A43" s="60">
+      <c r="A43" s="61">
         <v>30240007</v>
       </c>
-      <c r="B43" s="61">
+      <c r="B43" s="62">
         <v>102400</v>
       </c>
-      <c r="C43" s="61" t="s">
+      <c r="C43" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="D43" s="60">
+      <c r="D43" s="61">
         <v>32431</v>
       </c>
-      <c r="E43" s="60" t="s">
+      <c r="E43" s="61" t="s">
         <v>58</v>
       </c>
-      <c r="F43" s="60" t="s">
+      <c r="F43" s="61" t="s">
         <v>59</v>
       </c>
-      <c r="G43" s="60">
+      <c r="G43" s="61">
         <v>2024001</v>
       </c>
-      <c r="H43" s="60" t="s">
+      <c r="H43" s="61" t="s">
         <v>60</v>
       </c>
-      <c r="I43" s="60" t="s">
+      <c r="I43" s="61" t="s">
         <v>61</v>
       </c>
-      <c r="J43" s="60"/>
-      <c r="K43" s="62">
+      <c r="J43" s="61"/>
+      <c r="K43" s="63">
         <v>10240091</v>
       </c>
-      <c r="L43" s="60"/>
-      <c r="M43" s="60"/>
-      <c r="N43" s="60"/>
-      <c r="O43" s="60"/>
-      <c r="P43" s="60"/>
-      <c r="Q43" s="60"/>
-      <c r="R43" s="60"/>
-      <c r="S43" s="65"/>
+      <c r="L43" s="61"/>
+      <c r="M43" s="61"/>
+      <c r="N43" s="61"/>
+      <c r="O43" s="61"/>
+      <c r="P43" s="61"/>
+      <c r="Q43" s="61"/>
+      <c r="R43" s="61"/>
+      <c r="S43" s="66"/>
     </row>
     <row r="44" s="7" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A44" s="60">
+      <c r="A44" s="61">
         <v>30240008</v>
       </c>
-      <c r="B44" s="61">
+      <c r="B44" s="62">
         <v>102400</v>
       </c>
-      <c r="C44" s="61" t="s">
+      <c r="C44" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="D44" s="60">
+      <c r="D44" s="61">
         <v>32432</v>
       </c>
-      <c r="E44" s="60" t="s">
+      <c r="E44" s="61" t="s">
         <v>62</v>
       </c>
-      <c r="F44" s="60" t="s">
+      <c r="F44" s="61" t="s">
         <v>53</v>
       </c>
-      <c r="G44" s="60">
+      <c r="G44" s="61">
         <v>2024001</v>
       </c>
-      <c r="H44" s="60" t="s">
+      <c r="H44" s="61" t="s">
         <v>60</v>
       </c>
-      <c r="I44" s="60" t="s">
+      <c r="I44" s="61" t="s">
         <v>63</v>
       </c>
-      <c r="J44" s="60"/>
-      <c r="K44" s="66" t="s">
+      <c r="J44" s="61"/>
+      <c r="K44" s="67" t="s">
         <v>93</v>
       </c>
-      <c r="L44" s="60"/>
-      <c r="M44" s="60"/>
-      <c r="N44" s="60"/>
-      <c r="O44" s="60"/>
-      <c r="P44" s="60"/>
-      <c r="Q44" s="60"/>
-      <c r="R44" s="60"/>
-      <c r="S44" s="65"/>
+      <c r="L44" s="61"/>
+      <c r="M44" s="61"/>
+      <c r="N44" s="61"/>
+      <c r="O44" s="61"/>
+      <c r="P44" s="61"/>
+      <c r="Q44" s="61"/>
+      <c r="R44" s="61"/>
+      <c r="S44" s="66"/>
     </row>
     <row r="45" s="7" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A45" s="60">
+      <c r="A45" s="61">
         <v>30240009</v>
       </c>
-      <c r="B45" s="61">
+      <c r="B45" s="62">
         <v>102400</v>
       </c>
-      <c r="C45" s="61" t="s">
+      <c r="C45" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="D45" s="60">
+      <c r="D45" s="61">
         <v>32433</v>
       </c>
-      <c r="E45" s="60" t="s">
+      <c r="E45" s="61" t="s">
         <v>65</v>
       </c>
-      <c r="F45" s="60" t="s">
+      <c r="F45" s="61" t="s">
         <v>53</v>
       </c>
-      <c r="G45" s="60">
+      <c r="G45" s="61">
         <v>2024001</v>
       </c>
-      <c r="H45" s="60" t="s">
+      <c r="H45" s="61" t="s">
         <v>60</v>
       </c>
-      <c r="I45" s="60" t="s">
+      <c r="I45" s="61" t="s">
         <v>66</v>
       </c>
-      <c r="J45" s="60"/>
-      <c r="K45" s="62" t="s">
+      <c r="J45" s="61"/>
+      <c r="K45" s="63" t="s">
         <v>94</v>
       </c>
-      <c r="L45" s="60"/>
-      <c r="M45" s="60"/>
-      <c r="N45" s="60"/>
-      <c r="O45" s="60"/>
-      <c r="P45" s="60"/>
-      <c r="Q45" s="60"/>
-      <c r="R45" s="60"/>
-      <c r="S45" s="65"/>
+      <c r="L45" s="61"/>
+      <c r="M45" s="61"/>
+      <c r="N45" s="61"/>
+      <c r="O45" s="61"/>
+      <c r="P45" s="61"/>
+      <c r="Q45" s="61"/>
+      <c r="R45" s="61"/>
+      <c r="S45" s="66"/>
     </row>
     <row r="46" s="7" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A46" s="60">
+      <c r="A46" s="61">
         <v>30240010</v>
       </c>
-      <c r="B46" s="61">
+      <c r="B46" s="62">
         <v>102400</v>
       </c>
-      <c r="C46" s="61" t="s">
+      <c r="C46" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="D46" s="60">
+      <c r="D46" s="61">
         <v>32441</v>
       </c>
-      <c r="E46" s="60" t="s">
+      <c r="E46" s="61" t="s">
         <v>68</v>
       </c>
-      <c r="F46" s="60" t="s">
+      <c r="F46" s="61" t="s">
         <v>34</v>
       </c>
-      <c r="G46" s="60"/>
-      <c r="H46" s="60"/>
-      <c r="I46" s="60" t="s">
+      <c r="G46" s="61"/>
+      <c r="H46" s="61"/>
+      <c r="I46" s="61" t="s">
         <v>69</v>
       </c>
-      <c r="J46" s="60"/>
-      <c r="K46" s="66"/>
-      <c r="L46" s="60" t="s">
+      <c r="J46" s="61"/>
+      <c r="K46" s="67"/>
+      <c r="L46" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="M46" s="60" t="s">
+      <c r="M46" s="61" t="s">
         <v>70</v>
       </c>
-      <c r="N46" s="60"/>
-      <c r="O46" s="60"/>
-      <c r="P46" s="60"/>
-      <c r="Q46" s="63" t="s">
+      <c r="N46" s="61"/>
+      <c r="O46" s="61"/>
+      <c r="P46" s="61"/>
+      <c r="Q46" s="64" t="s">
         <v>71</v>
       </c>
-      <c r="R46" s="67" t="s">
+      <c r="R46" s="68" t="s">
         <v>72</v>
       </c>
-      <c r="S46" s="63" t="s">
+      <c r="S46" s="64" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="47" s="7" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A47" s="60">
+      <c r="A47" s="61">
         <v>30240011</v>
       </c>
-      <c r="B47" s="61">
+      <c r="B47" s="62">
         <v>102400</v>
       </c>
-      <c r="C47" s="61" t="s">
+      <c r="C47" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="D47" s="60">
+      <c r="D47" s="61">
         <v>32442</v>
       </c>
-      <c r="E47" s="60" t="s">
+      <c r="E47" s="61" t="s">
         <v>74</v>
       </c>
-      <c r="F47" s="60" t="s">
+      <c r="F47" s="61" t="s">
         <v>34</v>
       </c>
-      <c r="G47" s="60"/>
-      <c r="H47" s="60"/>
-      <c r="I47" s="60" t="s">
+      <c r="G47" s="61"/>
+      <c r="H47" s="61"/>
+      <c r="I47" s="61" t="s">
         <v>75</v>
       </c>
-      <c r="J47" s="60"/>
-      <c r="K47" s="62"/>
-      <c r="L47" s="60" t="s">
+      <c r="J47" s="61"/>
+      <c r="K47" s="63"/>
+      <c r="L47" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="M47" s="60" t="s">
+      <c r="M47" s="61" t="s">
         <v>57</v>
       </c>
-      <c r="N47" s="60"/>
-      <c r="O47" s="60"/>
-      <c r="P47" s="60"/>
-      <c r="Q47" s="60"/>
-      <c r="R47" s="60"/>
-      <c r="S47" s="65"/>
+      <c r="N47" s="61"/>
+      <c r="O47" s="61"/>
+      <c r="P47" s="61"/>
+      <c r="Q47" s="61"/>
+      <c r="R47" s="61"/>
+      <c r="S47" s="66"/>
     </row>
     <row r="48" s="7" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A48" s="60">
+      <c r="A48" s="61">
         <v>30240012</v>
       </c>
-      <c r="B48" s="61">
+      <c r="B48" s="62">
         <v>102400</v>
       </c>
-      <c r="C48" s="61" t="s">
+      <c r="C48" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="D48" s="60">
+      <c r="D48" s="61">
         <v>32443</v>
       </c>
-      <c r="E48" s="60" t="s">
+      <c r="E48" s="61" t="s">
         <v>76</v>
       </c>
-      <c r="F48" s="60" t="s">
+      <c r="F48" s="61" t="s">
         <v>53</v>
       </c>
-      <c r="G48" s="60">
+      <c r="G48" s="61">
         <v>2024001</v>
       </c>
-      <c r="H48" s="60" t="s">
+      <c r="H48" s="61" t="s">
         <v>60</v>
       </c>
-      <c r="I48" s="60" t="s">
+      <c r="I48" s="61" t="s">
         <v>66</v>
       </c>
-      <c r="J48" s="60"/>
-      <c r="K48" s="62" t="s">
+      <c r="J48" s="61"/>
+      <c r="K48" s="63" t="s">
         <v>94</v>
       </c>
-      <c r="L48" s="60"/>
-      <c r="M48" s="60"/>
-      <c r="N48" s="60"/>
-      <c r="O48" s="60"/>
-      <c r="P48" s="60"/>
-      <c r="Q48" s="60"/>
-      <c r="R48" s="60"/>
-      <c r="S48" s="65"/>
+      <c r="L48" s="61"/>
+      <c r="M48" s="61"/>
+      <c r="N48" s="61"/>
+      <c r="O48" s="61"/>
+      <c r="P48" s="61"/>
+      <c r="Q48" s="61"/>
+      <c r="R48" s="61"/>
+      <c r="S48" s="66"/>
     </row>
     <row r="49" s="8" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A49" s="68">
+      <c r="A49" s="69">
         <v>30170001</v>
       </c>
-      <c r="B49" s="69">
+      <c r="B49" s="70">
         <v>101700</v>
       </c>
-      <c r="C49" s="69" t="s">
+      <c r="C49" s="70" t="s">
         <v>95</v>
       </c>
-      <c r="D49" s="68">
+      <c r="D49" s="69">
         <v>301701</v>
       </c>
-      <c r="E49" s="68" t="s">
+      <c r="E49" s="69" t="s">
         <v>96</v>
       </c>
-      <c r="F49" s="68" t="s">
+      <c r="F49" s="69" t="s">
         <v>79</v>
       </c>
-      <c r="G49" s="68">
+      <c r="G49" s="69">
         <v>2017001</v>
       </c>
-      <c r="H49" s="68" t="s">
+      <c r="H49" s="69" t="s">
         <v>60</v>
       </c>
-      <c r="I49" s="68" t="s">
+      <c r="I49" s="69" t="s">
         <v>80</v>
       </c>
-      <c r="J49" s="68"/>
-      <c r="K49" s="70" t="s">
+      <c r="J49" s="69"/>
+      <c r="K49" s="71" t="s">
         <v>97</v>
       </c>
-      <c r="L49" s="68"/>
-      <c r="M49" s="68"/>
-      <c r="N49" s="68"/>
-      <c r="O49" s="68"/>
-      <c r="P49" s="68"/>
-      <c r="Q49" s="68"/>
-      <c r="R49" s="68"/>
-      <c r="S49" s="71"/>
+      <c r="L49" s="69"/>
+      <c r="M49" s="69"/>
+      <c r="N49" s="69"/>
+      <c r="O49" s="69"/>
+      <c r="P49" s="69"/>
+      <c r="Q49" s="69"/>
+      <c r="R49" s="69"/>
+      <c r="S49" s="72"/>
     </row>
     <row r="50" s="8" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A50" s="68">
+      <c r="A50" s="69">
         <v>30170002</v>
       </c>
-      <c r="B50" s="69">
+      <c r="B50" s="70">
         <v>101700</v>
       </c>
-      <c r="C50" s="69" t="s">
+      <c r="C50" s="70" t="s">
         <v>95</v>
       </c>
-      <c r="D50" s="68">
+      <c r="D50" s="69">
         <v>301702</v>
       </c>
-      <c r="E50" s="68" t="s">
+      <c r="E50" s="69" t="s">
         <v>98</v>
       </c>
-      <c r="F50" s="68" t="s">
+      <c r="F50" s="69" t="s">
         <v>83</v>
       </c>
-      <c r="G50" s="68">
+      <c r="G50" s="69">
         <v>2017001</v>
       </c>
-      <c r="H50" s="68" t="s">
+      <c r="H50" s="69" t="s">
         <v>60</v>
       </c>
-      <c r="I50" s="68" t="s">
+      <c r="I50" s="69" t="s">
         <v>80</v>
       </c>
-      <c r="J50" s="68"/>
-      <c r="K50" s="70" t="s">
+      <c r="J50" s="69"/>
+      <c r="K50" s="71" t="s">
         <v>97</v>
       </c>
-      <c r="L50" s="68"/>
-      <c r="M50" s="68"/>
-      <c r="N50" s="68"/>
-      <c r="O50" s="68"/>
-      <c r="P50" s="68"/>
-      <c r="Q50" s="68"/>
-      <c r="R50" s="68"/>
-      <c r="S50" s="71"/>
+      <c r="L50" s="69"/>
+      <c r="M50" s="69"/>
+      <c r="N50" s="69"/>
+      <c r="O50" s="69"/>
+      <c r="P50" s="69"/>
+      <c r="Q50" s="69"/>
+      <c r="R50" s="69"/>
+      <c r="S50" s="72"/>
     </row>
     <row r="51" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A51" s="55">
+      <c r="A51" s="56">
         <v>30220001</v>
       </c>
-      <c r="B51" s="56">
+      <c r="B51" s="57">
         <v>102200</v>
       </c>
-      <c r="C51" s="56" t="s">
+      <c r="C51" s="57" t="s">
         <v>99</v>
       </c>
-      <c r="D51" s="55">
+      <c r="D51" s="56">
         <v>302201</v>
       </c>
-      <c r="E51" s="55" t="s">
+      <c r="E51" s="56" t="s">
         <v>100</v>
       </c>
-      <c r="F51" s="55" t="s">
+      <c r="F51" s="56" t="s">
         <v>101</v>
       </c>
-      <c r="G51" s="55">
+      <c r="G51" s="56">
         <v>2022001</v>
       </c>
-      <c r="H51" s="55" t="s">
+      <c r="H51" s="56" t="s">
         <v>60</v>
       </c>
-      <c r="I51" s="55"/>
-      <c r="J51" s="55"/>
-      <c r="K51" s="72" t="s">
+      <c r="I51" s="56"/>
+      <c r="J51" s="56"/>
+      <c r="K51" s="73" t="s">
         <v>102</v>
       </c>
-      <c r="L51" s="55" t="s">
+      <c r="L51" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="M51" s="55"/>
-      <c r="N51" s="55"/>
-      <c r="O51" s="55"/>
-      <c r="P51" s="55"/>
-      <c r="Q51" s="55"/>
-      <c r="R51" s="55"/>
-      <c r="S51" s="73"/>
+      <c r="M51" s="56"/>
+      <c r="N51" s="56"/>
+      <c r="O51" s="56"/>
+      <c r="P51" s="56"/>
+      <c r="Q51" s="56"/>
+      <c r="R51" s="56"/>
+      <c r="S51" s="74"/>
     </row>
     <row r="52" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A52" s="55">
+      <c r="A52" s="56">
         <v>30220002</v>
       </c>
-      <c r="B52" s="56">
+      <c r="B52" s="57">
         <v>102200</v>
       </c>
-      <c r="C52" s="56" t="s">
+      <c r="C52" s="57" t="s">
         <v>99</v>
       </c>
-      <c r="D52" s="55">
+      <c r="D52" s="56">
         <v>302202</v>
       </c>
-      <c r="E52" s="55" t="s">
+      <c r="E52" s="56" t="s">
         <v>104</v>
       </c>
-      <c r="F52" s="55" t="s">
+      <c r="F52" s="56" t="s">
         <v>101</v>
       </c>
-      <c r="G52" s="55">
+      <c r="G52" s="56">
         <v>2022001</v>
       </c>
-      <c r="H52" s="55" t="s">
+      <c r="H52" s="56" t="s">
         <v>60</v>
       </c>
-      <c r="I52" s="55"/>
-      <c r="J52" s="55"/>
-      <c r="K52" s="72" t="s">
+      <c r="I52" s="56"/>
+      <c r="J52" s="56"/>
+      <c r="K52" s="73" t="s">
         <v>105</v>
       </c>
-      <c r="L52" s="55" t="s">
+      <c r="L52" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="M52" s="55"/>
-      <c r="N52" s="55"/>
-      <c r="O52" s="55"/>
-      <c r="P52" s="55"/>
-      <c r="Q52" s="55"/>
-      <c r="R52" s="55"/>
-      <c r="S52" s="73"/>
+      <c r="M52" s="56"/>
+      <c r="N52" s="56"/>
+      <c r="O52" s="56"/>
+      <c r="P52" s="56"/>
+      <c r="Q52" s="56"/>
+      <c r="R52" s="56"/>
+      <c r="S52" s="74"/>
     </row>
     <row r="53" s="9" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A53" s="74">
+      <c r="A53" s="75">
         <v>30210001</v>
       </c>
-      <c r="B53" s="75">
+      <c r="B53" s="76">
         <v>102100</v>
       </c>
-      <c r="C53" s="75" t="s">
+      <c r="C53" s="76" t="s">
         <v>106</v>
       </c>
-      <c r="D53" s="74">
+      <c r="D53" s="75">
         <v>302101</v>
       </c>
-      <c r="E53" s="74" t="s">
+      <c r="E53" s="75" t="s">
         <v>107</v>
       </c>
-      <c r="F53" s="74" t="s">
+      <c r="F53" s="75" t="s">
         <v>108</v>
       </c>
-      <c r="G53" s="74">
+      <c r="G53" s="75">
         <v>2021001</v>
       </c>
-      <c r="H53" s="74" t="s">
+      <c r="H53" s="75" t="s">
         <v>60</v>
       </c>
-      <c r="I53" s="74" t="s">
+      <c r="I53" s="75" t="s">
         <v>80</v>
       </c>
-      <c r="J53" s="74"/>
-      <c r="K53" s="76" t="s">
+      <c r="J53" s="75"/>
+      <c r="K53" s="77" t="s">
         <v>109</v>
       </c>
-      <c r="L53" s="74" t="s">
+      <c r="L53" s="75" t="s">
         <v>110</v>
       </c>
-      <c r="M53" s="74"/>
-      <c r="N53" s="74"/>
-      <c r="O53" s="74"/>
-      <c r="P53" s="74"/>
-      <c r="Q53" s="74"/>
-      <c r="R53" s="74"/>
-      <c r="S53" s="77"/>
+      <c r="M53" s="75"/>
+      <c r="N53" s="75"/>
+      <c r="O53" s="75"/>
+      <c r="P53" s="75"/>
+      <c r="Q53" s="75"/>
+      <c r="R53" s="75"/>
+      <c r="S53" s="78"/>
     </row>
     <row r="54" s="9" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A54" s="74">
+      <c r="A54" s="75">
         <v>30210002</v>
       </c>
-      <c r="B54" s="75">
+      <c r="B54" s="76">
         <v>102100</v>
       </c>
-      <c r="C54" s="75" t="s">
+      <c r="C54" s="76" t="s">
         <v>106</v>
       </c>
-      <c r="D54" s="74">
+      <c r="D54" s="75">
         <v>302102</v>
       </c>
-      <c r="E54" s="74" t="s">
+      <c r="E54" s="75" t="s">
         <v>111</v>
       </c>
-      <c r="F54" s="74" t="s">
+      <c r="F54" s="75" t="s">
         <v>34</v>
       </c>
-      <c r="G54" s="74"/>
-      <c r="H54" s="74"/>
-      <c r="I54" s="74" t="s">
+      <c r="G54" s="75"/>
+      <c r="H54" s="75"/>
+      <c r="I54" s="75" t="s">
         <v>112</v>
       </c>
-      <c r="J54" s="74"/>
-      <c r="K54" s="76"/>
-      <c r="L54" s="74"/>
-      <c r="M54" s="74" t="s">
+      <c r="J54" s="75"/>
+      <c r="K54" s="77"/>
+      <c r="L54" s="75"/>
+      <c r="M54" s="75" t="s">
         <v>37</v>
       </c>
-      <c r="N54" s="74" t="s">
+      <c r="N54" s="75" t="s">
         <v>113</v>
       </c>
-      <c r="O54" s="74"/>
-      <c r="P54" s="74"/>
-      <c r="Q54" s="74" t="s">
+      <c r="O54" s="75"/>
+      <c r="P54" s="75"/>
+      <c r="Q54" s="75" t="s">
         <v>114</v>
       </c>
-      <c r="R54" s="74"/>
-      <c r="S54" s="77"/>
+      <c r="R54" s="75"/>
+      <c r="S54" s="78"/>
     </row>
     <row r="55" s="10" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A55" s="78">
+      <c r="A55" s="79">
         <v>30180001</v>
       </c>
-      <c r="B55" s="79">
+      <c r="B55" s="80">
         <v>101800</v>
       </c>
-      <c r="C55" s="79" t="s">
+      <c r="C55" s="80" t="s">
         <v>115</v>
       </c>
-      <c r="D55" s="78">
+      <c r="D55" s="79">
         <v>301801</v>
       </c>
-      <c r="E55" s="78" t="s">
+      <c r="E55" s="79" t="s">
         <v>80</v>
       </c>
-      <c r="F55" s="78" t="s">
+      <c r="F55" s="79" t="s">
         <v>116</v>
       </c>
-      <c r="G55" s="78">
+      <c r="G55" s="79">
         <v>2018001</v>
       </c>
-      <c r="H55" s="78" t="s">
+      <c r="H55" s="79" t="s">
         <v>60</v>
       </c>
-      <c r="I55" s="78" t="s">
+      <c r="I55" s="79" t="s">
         <v>80</v>
       </c>
-      <c r="J55" s="78"/>
-      <c r="K55" s="80">
+      <c r="J55" s="79"/>
+      <c r="K55" s="81">
         <v>10180041</v>
       </c>
-      <c r="L55" s="78"/>
-      <c r="M55" s="78"/>
-      <c r="N55" s="78"/>
-      <c r="O55" s="78"/>
-      <c r="P55" s="78"/>
-      <c r="Q55" s="78"/>
-      <c r="R55" s="78"/>
-      <c r="S55" s="81"/>
+      <c r="L55" s="79"/>
+      <c r="M55" s="79"/>
+      <c r="N55" s="79"/>
+      <c r="O55" s="79"/>
+      <c r="P55" s="79"/>
+      <c r="Q55" s="79"/>
+      <c r="R55" s="79"/>
+      <c r="S55" s="82"/>
     </row>
     <row r="56" s="11" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A56" s="82">
+      <c r="A56" s="83">
         <v>30250001</v>
       </c>
-      <c r="B56" s="83">
+      <c r="B56" s="84">
         <v>102500</v>
       </c>
-      <c r="C56" s="83" t="s">
+      <c r="C56" s="84" t="s">
         <v>117</v>
       </c>
-      <c r="D56" s="82">
+      <c r="D56" s="83">
         <v>302501</v>
       </c>
-      <c r="E56" s="82" t="s">
+      <c r="E56" s="83" t="s">
         <v>107</v>
       </c>
-      <c r="F56" s="82" t="s">
+      <c r="F56" s="83" t="s">
         <v>108</v>
       </c>
-      <c r="G56" s="82">
+      <c r="G56" s="83">
         <v>2025001</v>
       </c>
-      <c r="H56" s="82" t="s">
+      <c r="H56" s="83" t="s">
         <v>60</v>
       </c>
-      <c r="I56" s="82" t="s">
+      <c r="I56" s="83" t="s">
         <v>80</v>
       </c>
-      <c r="J56" s="82"/>
-      <c r="K56" s="84" t="s">
+      <c r="J56" s="83"/>
+      <c r="K56" s="85" t="s">
         <v>118</v>
       </c>
-      <c r="L56" s="82" t="s">
+      <c r="L56" s="83" t="s">
         <v>119</v>
       </c>
-      <c r="M56" s="82"/>
-      <c r="N56" s="82"/>
-      <c r="O56" s="82"/>
-      <c r="P56" s="82"/>
-      <c r="Q56" s="82"/>
-      <c r="R56" s="82"/>
-      <c r="S56" s="85"/>
+      <c r="M56" s="83"/>
+      <c r="N56" s="83"/>
+      <c r="O56" s="83"/>
+      <c r="P56" s="83"/>
+      <c r="Q56" s="83"/>
+      <c r="R56" s="83"/>
+      <c r="S56" s="86"/>
     </row>
     <row r="57" s="11" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A57" s="82">
+      <c r="A57" s="83">
         <v>30250002</v>
       </c>
-      <c r="B57" s="83">
+      <c r="B57" s="84">
         <v>102500</v>
       </c>
-      <c r="C57" s="83" t="s">
+      <c r="C57" s="84" t="s">
         <v>117</v>
       </c>
-      <c r="D57" s="82">
+      <c r="D57" s="83">
         <v>302502</v>
       </c>
-      <c r="E57" s="82" t="s">
+      <c r="E57" s="83" t="s">
         <v>120</v>
       </c>
-      <c r="F57" s="82" t="s">
+      <c r="F57" s="83" t="s">
         <v>121</v>
       </c>
-      <c r="G57" s="82">
+      <c r="G57" s="83">
         <v>2025001</v>
       </c>
-      <c r="H57" s="82" t="s">
+      <c r="H57" s="83" t="s">
         <v>60</v>
       </c>
-      <c r="I57" s="82" t="s">
+      <c r="I57" s="83" t="s">
         <v>80</v>
       </c>
-      <c r="J57" s="82"/>
-      <c r="K57" s="84" t="s">
+      <c r="J57" s="83"/>
+      <c r="K57" s="85" t="s">
         <v>118</v>
       </c>
-      <c r="L57" s="82" t="s">
+      <c r="L57" s="83" t="s">
         <v>119</v>
       </c>
-      <c r="M57" s="82"/>
-      <c r="N57" s="82"/>
-      <c r="O57" s="82"/>
-      <c r="P57" s="82"/>
-      <c r="Q57" s="82"/>
-      <c r="R57" s="82"/>
-      <c r="S57" s="85"/>
+      <c r="M57" s="83"/>
+      <c r="N57" s="83"/>
+      <c r="O57" s="83"/>
+      <c r="P57" s="83"/>
+      <c r="Q57" s="83"/>
+      <c r="R57" s="83"/>
+      <c r="S57" s="86"/>
     </row>
     <row r="58" s="11" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A58" s="82">
+      <c r="A58" s="83">
         <v>30250003</v>
       </c>
-      <c r="B58" s="83">
+      <c r="B58" s="84">
         <v>102500</v>
       </c>
-      <c r="C58" s="83" t="s">
+      <c r="C58" s="84" t="s">
         <v>117</v>
       </c>
-      <c r="D58" s="82">
+      <c r="D58" s="83">
         <v>302503</v>
       </c>
-      <c r="E58" s="82" t="s">
+      <c r="E58" s="83" t="s">
         <v>122</v>
       </c>
-      <c r="F58" s="82" t="s">
+      <c r="F58" s="83" t="s">
         <v>123</v>
       </c>
-      <c r="G58" s="82">
+      <c r="G58" s="83">
         <v>2025001</v>
       </c>
-      <c r="H58" s="82" t="s">
+      <c r="H58" s="83" t="s">
         <v>60</v>
       </c>
-      <c r="I58" s="82" t="s">
+      <c r="I58" s="83" t="s">
         <v>80</v>
       </c>
-      <c r="J58" s="82"/>
-      <c r="K58" s="84" t="s">
+      <c r="J58" s="83"/>
+      <c r="K58" s="85" t="s">
         <v>118</v>
       </c>
-      <c r="L58" s="82" t="s">
+      <c r="L58" s="83" t="s">
         <v>119</v>
       </c>
-      <c r="M58" s="82"/>
-      <c r="N58" s="82"/>
-      <c r="O58" s="82"/>
-      <c r="P58" s="82"/>
-      <c r="Q58" s="82"/>
-      <c r="R58" s="82"/>
-      <c r="S58" s="85"/>
+      <c r="M58" s="83"/>
+      <c r="N58" s="83"/>
+      <c r="O58" s="83"/>
+      <c r="P58" s="83"/>
+      <c r="Q58" s="83"/>
+      <c r="R58" s="83"/>
+      <c r="S58" s="86"/>
     </row>
     <row r="59" s="12" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A59" s="86">
+      <c r="A59" s="87">
         <v>30230001</v>
       </c>
-      <c r="B59" s="87">
+      <c r="B59" s="88">
         <v>102300</v>
       </c>
-      <c r="C59" s="87" t="s">
+      <c r="C59" s="88" t="s">
         <v>124</v>
       </c>
-      <c r="D59" s="86">
+      <c r="D59" s="87">
         <v>302301</v>
       </c>
-      <c r="E59" s="86" t="s">
+      <c r="E59" s="87" t="s">
         <v>107</v>
       </c>
-      <c r="F59" s="86" t="s">
+      <c r="F59" s="87" t="s">
         <v>108</v>
       </c>
-      <c r="G59" s="86">
+      <c r="G59" s="87">
         <v>2023001</v>
       </c>
-      <c r="H59" s="86" t="s">
+      <c r="H59" s="87" t="s">
         <v>60</v>
       </c>
-      <c r="I59" s="86" t="s">
+      <c r="I59" s="87" t="s">
         <v>80</v>
       </c>
-      <c r="J59" s="86"/>
-      <c r="K59" s="88" t="s">
+      <c r="J59" s="87"/>
+      <c r="K59" s="89" t="s">
         <v>125</v>
       </c>
-      <c r="L59" s="86" t="s">
+      <c r="L59" s="87" t="s">
         <v>126</v>
       </c>
-      <c r="M59" s="86"/>
-      <c r="N59" s="86"/>
-      <c r="O59" s="86"/>
-      <c r="P59" s="86"/>
-      <c r="Q59" s="86"/>
-      <c r="R59" s="86"/>
-      <c r="S59" s="89"/>
+      <c r="M59" s="87"/>
+      <c r="N59" s="87"/>
+      <c r="O59" s="87"/>
+      <c r="P59" s="87"/>
+      <c r="Q59" s="87"/>
+      <c r="R59" s="87"/>
+      <c r="S59" s="90"/>
     </row>
     <row r="60" s="12" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A60" s="86">
+      <c r="A60" s="87">
         <v>30230002</v>
       </c>
-      <c r="B60" s="87">
+      <c r="B60" s="88">
         <v>102300</v>
       </c>
-      <c r="C60" s="87" t="s">
+      <c r="C60" s="88" t="s">
         <v>124</v>
       </c>
-      <c r="D60" s="86">
+      <c r="D60" s="87">
         <v>302302</v>
       </c>
-      <c r="E60" s="86" t="s">
+      <c r="E60" s="87" t="s">
         <v>127</v>
       </c>
-      <c r="F60" s="86" t="s">
+      <c r="F60" s="87" t="s">
         <v>79</v>
       </c>
-      <c r="G60" s="86">
+      <c r="G60" s="87">
         <v>2023001</v>
       </c>
-      <c r="H60" s="86" t="s">
+      <c r="H60" s="87" t="s">
         <v>60</v>
       </c>
-      <c r="I60" s="86" t="s">
+      <c r="I60" s="87" t="s">
         <v>80</v>
       </c>
-      <c r="J60" s="86"/>
-      <c r="K60" s="88" t="s">
+      <c r="J60" s="87"/>
+      <c r="K60" s="89" t="s">
         <v>125</v>
       </c>
-      <c r="L60" s="86" t="s">
+      <c r="L60" s="87" t="s">
         <v>126</v>
       </c>
-      <c r="M60" s="86"/>
-      <c r="N60" s="86"/>
-      <c r="O60" s="86"/>
-      <c r="P60" s="86"/>
-      <c r="Q60" s="86"/>
-      <c r="R60" s="86"/>
-      <c r="S60" s="89"/>
+      <c r="M60" s="87"/>
+      <c r="N60" s="87"/>
+      <c r="O60" s="87"/>
+      <c r="P60" s="87"/>
+      <c r="Q60" s="87"/>
+      <c r="R60" s="87"/>
+      <c r="S60" s="90"/>
     </row>
     <row r="61" s="12" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A61" s="86">
+      <c r="A61" s="87">
         <v>30230003</v>
       </c>
-      <c r="B61" s="87">
+      <c r="B61" s="88">
         <v>102300</v>
       </c>
-      <c r="C61" s="87" t="s">
+      <c r="C61" s="88" t="s">
         <v>124</v>
       </c>
-      <c r="D61" s="86">
+      <c r="D61" s="87">
         <v>302303</v>
       </c>
-      <c r="E61" s="86" t="s">
+      <c r="E61" s="87" t="s">
         <v>128</v>
       </c>
-      <c r="F61" s="86" t="s">
+      <c r="F61" s="87" t="s">
         <v>83</v>
       </c>
-      <c r="G61" s="86">
+      <c r="G61" s="87">
         <v>2023001</v>
       </c>
-      <c r="H61" s="86" t="s">
+      <c r="H61" s="87" t="s">
         <v>60</v>
       </c>
-      <c r="I61" s="86" t="s">
+      <c r="I61" s="87" t="s">
         <v>80</v>
       </c>
-      <c r="J61" s="86"/>
-      <c r="K61" s="88" t="s">
+      <c r="J61" s="87"/>
+      <c r="K61" s="89" t="s">
         <v>125</v>
       </c>
-      <c r="L61" s="86" t="s">
+      <c r="L61" s="87" t="s">
         <v>126</v>
       </c>
-      <c r="M61" s="86"/>
-      <c r="N61" s="86"/>
-      <c r="O61" s="86"/>
-      <c r="P61" s="86"/>
-      <c r="Q61" s="86"/>
-      <c r="R61" s="86"/>
-      <c r="S61" s="89"/>
+      <c r="M61" s="87"/>
+      <c r="N61" s="87"/>
+      <c r="O61" s="87"/>
+      <c r="P61" s="87"/>
+      <c r="Q61" s="87"/>
+      <c r="R61" s="87"/>
+      <c r="S61" s="90"/>
+    </row>
+    <row r="62" s="13" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A62" s="91">
+        <v>30350001</v>
+      </c>
+      <c r="B62" s="92">
+        <v>103500</v>
+      </c>
+      <c r="C62" s="92" t="s">
+        <v>129</v>
+      </c>
+      <c r="D62" s="91">
+        <v>303501</v>
+      </c>
+      <c r="E62" s="91" t="s">
+        <v>130</v>
+      </c>
+      <c r="F62" s="91" t="s">
+        <v>59</v>
+      </c>
+      <c r="G62" s="91">
+        <v>2035001</v>
+      </c>
+      <c r="H62" s="91" t="s">
+        <v>60</v>
+      </c>
+      <c r="I62" s="91" t="s">
+        <v>131</v>
+      </c>
+      <c r="J62" s="91"/>
+      <c r="K62" s="93">
+        <v>10350002</v>
+      </c>
+      <c r="L62" s="91" t="s">
+        <v>132</v>
+      </c>
+      <c r="M62" s="91"/>
+      <c r="N62" s="91"/>
+      <c r="O62" s="91"/>
+      <c r="P62" s="91"/>
+      <c r="Q62" s="91"/>
+      <c r="R62" s="91"/>
+      <c r="S62" s="94"/>
+    </row>
+    <row r="63" s="13" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A63" s="91">
+        <v>30350002</v>
+      </c>
+      <c r="B63" s="92">
+        <v>103500</v>
+      </c>
+      <c r="C63" s="92" t="s">
+        <v>129</v>
+      </c>
+      <c r="D63" s="91">
+        <v>303502</v>
+      </c>
+      <c r="E63" s="91" t="s">
+        <v>133</v>
+      </c>
+      <c r="F63" s="91" t="s">
+        <v>34</v>
+      </c>
+      <c r="G63" s="91"/>
+      <c r="H63" s="91"/>
+      <c r="I63" s="91"/>
+      <c r="J63" s="91"/>
+      <c r="K63" s="93"/>
+      <c r="L63" s="91"/>
+      <c r="M63" s="91" t="s">
+        <v>53</v>
+      </c>
+      <c r="N63" s="91"/>
+      <c r="O63" s="91" t="s">
+        <v>134</v>
+      </c>
+      <c r="P63" s="91"/>
+      <c r="Q63" s="91"/>
+      <c r="R63" s="91"/>
+      <c r="S63" s="94"/>
+    </row>
+    <row r="64" s="13" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A64" s="91">
+        <v>30350101</v>
+      </c>
+      <c r="B64" s="92">
+        <v>103501</v>
+      </c>
+      <c r="C64" s="92" t="s">
+        <v>135</v>
+      </c>
+      <c r="D64" s="91">
+        <v>303503</v>
+      </c>
+      <c r="E64" s="91" t="s">
+        <v>130</v>
+      </c>
+      <c r="F64" s="91" t="s">
+        <v>59</v>
+      </c>
+      <c r="G64" s="91">
+        <v>2035011</v>
+      </c>
+      <c r="H64" s="91" t="s">
+        <v>60</v>
+      </c>
+      <c r="I64" s="91" t="s">
+        <v>131</v>
+      </c>
+      <c r="J64" s="91"/>
+      <c r="K64" s="93">
+        <v>10350102</v>
+      </c>
+      <c r="L64" s="91" t="s">
+        <v>132</v>
+      </c>
+      <c r="M64" s="91"/>
+      <c r="N64" s="91"/>
+      <c r="O64" s="91"/>
+      <c r="P64" s="91"/>
+      <c r="Q64" s="91"/>
+      <c r="R64" s="91"/>
+      <c r="S64" s="94"/>
+    </row>
+    <row r="65" s="13" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A65" s="91">
+        <v>30350102</v>
+      </c>
+      <c r="B65" s="92">
+        <v>103501</v>
+      </c>
+      <c r="C65" s="92" t="s">
+        <v>135</v>
+      </c>
+      <c r="D65" s="91">
+        <v>303504</v>
+      </c>
+      <c r="E65" s="91" t="s">
+        <v>133</v>
+      </c>
+      <c r="F65" s="91" t="s">
+        <v>34</v>
+      </c>
+      <c r="G65" s="91"/>
+      <c r="H65" s="91"/>
+      <c r="I65" s="91"/>
+      <c r="J65" s="91"/>
+      <c r="K65" s="93"/>
+      <c r="L65" s="91"/>
+      <c r="M65" s="91" t="s">
+        <v>53</v>
+      </c>
+      <c r="N65" s="91"/>
+      <c r="O65" s="91" t="s">
+        <v>134</v>
+      </c>
+      <c r="P65" s="91"/>
+      <c r="Q65" s="91"/>
+      <c r="R65" s="91"/>
+      <c r="S65" s="94"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2">
@@ -4707,10 +4903,10 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="B1" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -4718,7 +4914,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -4726,7 +4922,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:8">
@@ -4734,16 +4930,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:8">
@@ -4751,16 +4947,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:8">
@@ -4768,16 +4964,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:8">
@@ -4785,16 +4981,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F7" s="1">
         <v>2</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:8">
@@ -4802,16 +4998,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="F8" s="1">
         <v>3</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:8">
@@ -4819,16 +5015,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="F9" s="1">
         <v>4</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:8">
@@ -4836,16 +5032,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="F10" s="1">
         <v>5</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:8">
@@ -4853,16 +5049,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="F11" s="1">
         <v>6</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:8">
@@ -4870,16 +5066,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="F12" s="1">
         <v>7</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:8">
@@ -4887,16 +5083,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="F13" s="1">
         <v>8</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:8">
@@ -4904,16 +5100,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="F14" s="1">
         <v>9</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:8">
@@ -4921,16 +5117,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="F15" s="1">
         <v>10</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:8">
@@ -4938,16 +5134,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="F16" s="1">
         <v>11</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:8">
@@ -4955,16 +5151,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="F17" s="1">
         <v>12</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:8">
@@ -4972,16 +5168,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="F18" s="1">
         <v>13</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:8">
@@ -4989,16 +5185,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="F19" s="1">
         <v>14</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:8">
@@ -5006,16 +5202,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="F20" s="1">
         <v>15</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:8">
@@ -5023,16 +5219,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="F21" s="1">
         <v>16</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:8">
@@ -5040,16 +5236,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="F22" s="1">
         <v>17</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:8">
@@ -5057,16 +5253,16 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="F23" s="1">
         <v>18</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:8">
@@ -5074,16 +5270,16 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="F24" s="1">
         <v>19</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -5091,7 +5287,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -5099,7 +5295,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -5107,7 +5303,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -5115,7 +5311,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -5123,7 +5319,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -5131,7 +5327,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -5139,7 +5335,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -5147,7 +5343,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -5155,7 +5351,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -5163,7 +5359,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -5171,7 +5367,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -5179,7 +5375,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -5187,7 +5383,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -5195,7 +5391,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -5203,7 +5399,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -5211,7 +5407,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -5219,7 +5415,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -5227,7 +5423,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -5235,7 +5431,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -5243,7 +5439,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -5251,7 +5447,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -5259,7 +5455,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -5267,7 +5463,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialAuxiliary.xlsx
+++ b/slots/resources/sample/SpecialAuxiliary.xlsx
@@ -268,7 +268,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="227">
   <si>
     <t>小游戏模式ID</t>
   </si>
@@ -666,7 +666,10 @@
     <t>金钱兔模式</t>
   </si>
   <si>
-    <t>改出奖金符号</t>
+    <t>10350014|10350002</t>
+  </si>
+  <si>
+    <t>异形位置改为不中奖符号+改出奖金符号</t>
   </si>
   <si>
     <t>奖金符号收集奖励</t>
@@ -676,6 +679,9 @@
   </si>
   <si>
     <t>金钱兔</t>
+  </si>
+  <si>
+    <t>10350114|10350102</t>
   </si>
   <si>
     <t>typeID</t>
@@ -1133,13 +1139,6 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1150,7 +1149,14 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1163,14 +1169,14 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <b/>
+      <sz val="18"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -4703,7 +4709,7 @@
         <v>59</v>
       </c>
       <c r="G62" s="91">
-        <v>2035001</v>
+        <v>2035002</v>
       </c>
       <c r="H62" s="91" t="s">
         <v>60</v>
@@ -4712,11 +4718,11 @@
         <v>131</v>
       </c>
       <c r="J62" s="91"/>
-      <c r="K62" s="93">
-        <v>10350002</v>
+      <c r="K62" s="93" t="s">
+        <v>132</v>
       </c>
       <c r="L62" s="91" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M62" s="91"/>
       <c r="N62" s="91"/>
@@ -4740,7 +4746,7 @@
         <v>303502</v>
       </c>
       <c r="E63" s="91" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F63" s="91" t="s">
         <v>34</v>
@@ -4756,7 +4762,7 @@
       </c>
       <c r="N63" s="91"/>
       <c r="O63" s="91" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P63" s="91"/>
       <c r="Q63" s="91"/>
@@ -4771,7 +4777,7 @@
         <v>103501</v>
       </c>
       <c r="C64" s="92" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D64" s="91">
         <v>303503</v>
@@ -4783,7 +4789,7 @@
         <v>59</v>
       </c>
       <c r="G64" s="91">
-        <v>2035011</v>
+        <v>2035012</v>
       </c>
       <c r="H64" s="91" t="s">
         <v>60</v>
@@ -4792,11 +4798,11 @@
         <v>131</v>
       </c>
       <c r="J64" s="91"/>
-      <c r="K64" s="93">
-        <v>10350102</v>
+      <c r="K64" s="93" t="s">
+        <v>137</v>
       </c>
       <c r="L64" s="91" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M64" s="91"/>
       <c r="N64" s="91"/>
@@ -4814,13 +4820,13 @@
         <v>103501</v>
       </c>
       <c r="C65" s="92" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D65" s="91">
         <v>303504</v>
       </c>
       <c r="E65" s="91" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F65" s="91" t="s">
         <v>34</v>
@@ -4836,7 +4842,7 @@
       </c>
       <c r="N65" s="91"/>
       <c r="O65" s="91" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P65" s="91"/>
       <c r="Q65" s="91"/>
@@ -4903,10 +4909,10 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -4914,7 +4920,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -4922,7 +4928,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:8">
@@ -4930,16 +4936,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:8">
@@ -4947,16 +4953,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:8">
@@ -4964,16 +4970,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:8">
@@ -4981,16 +4987,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F7" s="1">
         <v>2</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:8">
@@ -4998,16 +5004,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F8" s="1">
         <v>3</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:8">
@@ -5015,16 +5021,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F9" s="1">
         <v>4</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:8">
@@ -5032,16 +5038,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F10" s="1">
         <v>5</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:8">
@@ -5049,16 +5055,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F11" s="1">
         <v>6</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:8">
@@ -5066,16 +5072,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F12" s="1">
         <v>7</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:8">
@@ -5083,16 +5089,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F13" s="1">
         <v>8</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:8">
@@ -5100,16 +5106,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F14" s="1">
         <v>9</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:8">
@@ -5117,16 +5123,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F15" s="1">
         <v>10</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:8">
@@ -5134,16 +5140,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F16" s="1">
         <v>11</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:8">
@@ -5151,16 +5157,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F17" s="1">
         <v>12</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:8">
@@ -5168,16 +5174,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F18" s="1">
         <v>13</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:8">
@@ -5185,16 +5191,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F19" s="1">
         <v>14</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:8">
@@ -5202,16 +5208,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F20" s="1">
         <v>15</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:8">
@@ -5219,16 +5225,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F21" s="1">
         <v>16</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:8">
@@ -5236,16 +5242,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F22" s="1">
         <v>17</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:8">
@@ -5253,16 +5259,16 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F23" s="1">
         <v>18</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:8">
@@ -5270,16 +5276,16 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F24" s="1">
         <v>19</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -5287,7 +5293,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -5295,7 +5301,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -5303,7 +5309,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -5311,7 +5317,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -5319,7 +5325,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -5327,7 +5333,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -5335,7 +5341,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -5343,7 +5349,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -5351,7 +5357,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -5359,7 +5365,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -5367,7 +5373,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -5375,7 +5381,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -5383,7 +5389,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -5391,7 +5397,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -5399,7 +5405,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -5407,7 +5413,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -5415,7 +5421,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -5423,7 +5429,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -5431,7 +5437,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -5439,7 +5445,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -5447,7 +5453,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -5455,7 +5461,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -5463,7 +5469,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialAuxiliary.xlsx
+++ b/slots/resources/sample/SpecialAuxiliary.xlsx
@@ -1145,11 +1145,25 @@
     </font>
     <font>
       <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1162,21 +1176,7 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -4410,7 +4410,7 @@
         <v>116</v>
       </c>
       <c r="G55" s="79">
-        <v>2018001</v>
+        <v>2018002</v>
       </c>
       <c r="H55" s="79" t="s">
         <v>60</v>

--- a/slots/resources/sample/SpecialAuxiliary.xlsx
+++ b/slots/resources/sample/SpecialAuxiliary.xlsx
@@ -597,7 +597,7 @@
     <t>10_1</t>
   </si>
   <si>
-    <t>10210021|10210042|10210032</t>
+    <t>10210022|10210042|10210032</t>
   </si>
   <si>
     <t>概率改出wild、scatter、bonus</t>
@@ -1138,20 +1138,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1163,7 +1150,13 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1176,7 +1169,14 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/slots/resources/sample/SpecialAuxiliary.xlsx
+++ b/slots/resources/sample/SpecialAuxiliary.xlsx
@@ -268,7 +268,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="231">
   <si>
     <t>小游戏模式ID</t>
   </si>
@@ -645,7 +645,7 @@
     <t>蒸汽时代</t>
   </si>
   <si>
-    <t>10230021|10230031</t>
+    <t>10230022|10230031</t>
   </si>
   <si>
     <t>概率改出百搭+概率改出免费+1</t>
@@ -682,6 +682,18 @@
   </si>
   <si>
     <t>10350114|10350102</t>
+  </si>
+  <si>
+    <t>鼠鼠福福</t>
+  </si>
+  <si>
+    <t>福鼠模式</t>
+  </si>
+  <si>
+    <t>99999_1</t>
+  </si>
+  <si>
+    <t>第二轴改出三个wild符号</t>
   </si>
   <si>
     <t>typeID</t>
@@ -1138,13 +1150,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
+      <b/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1156,15 +1164,13 @@
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="18"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1176,7 +1182,13 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1729,7 +1741,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1746,6 +1758,7 @@
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1923,6 +1936,14 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="52">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2254,7 +2275,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S65"/>
+  <dimension ref="A1:S66"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14.125" customWidth="1"/>
@@ -2266,7 +2287,7 @@
     <col min="8" max="8" width="16.25" customWidth="1"/>
     <col min="9" max="9" width="29.375" customWidth="1"/>
     <col min="10" max="10" width="42.5" customWidth="1"/>
-    <col min="11" max="11" width="41.25" style="14" customWidth="1"/>
+    <col min="11" max="11" width="41.25" style="15" customWidth="1"/>
     <col min="12" max="12" width="36.0333333333333" style="3" customWidth="1"/>
     <col min="13" max="13" width="34.4083333333333" style="3" customWidth="1"/>
     <col min="14" max="14" width="7.93333333333333" style="3" customWidth="1"/>
@@ -2274,7 +2295,7 @@
     <col min="16" max="16" width="8.96666666666667" customWidth="1"/>
     <col min="17" max="17" width="93.375" customWidth="1"/>
     <col min="18" max="18" width="10.625" customWidth="1"/>
-    <col min="19" max="19" width="23.75" style="15" customWidth="1"/>
+    <col min="19" max="19" width="23.75" style="16" customWidth="1"/>
     <col min="20" max="20" width="60.875" customWidth="1"/>
     <col min="21" max="22" width="11.5"/>
   </cols>
@@ -2283,671 +2304,671 @@
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16" t="s">
+      <c r="C1" s="17"/>
+      <c r="D1" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16" t="s">
+      <c r="E1" s="17"/>
+      <c r="F1" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="G1" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16" t="s">
+      <c r="H1" s="17"/>
+      <c r="I1" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="17" t="s">
+      <c r="J1" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="18" t="s">
+      <c r="K1" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16" t="s">
+      <c r="L1" s="17"/>
+      <c r="M1" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="16"/>
-      <c r="O1" s="19" t="s">
+      <c r="N1" s="17"/>
+      <c r="O1" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="19" t="s">
+      <c r="P1" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="Q1" s="19" t="s">
+      <c r="Q1" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="R1" s="20" t="s">
+      <c r="R1" s="21" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="2" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16" t="s">
+      <c r="C2" s="17"/>
+      <c r="D2" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="16"/>
-      <c r="F2" s="19" t="s">
+      <c r="E2" s="17"/>
+      <c r="F2" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="16" t="s">
+      <c r="G2" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="22" t="s">
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="23" t="s">
+      <c r="K2" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="L2" s="19"/>
-      <c r="M2" s="22" t="s">
+      <c r="L2" s="20"/>
+      <c r="M2" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="N2" s="16"/>
-      <c r="O2" s="19" t="s">
+      <c r="N2" s="17"/>
+      <c r="O2" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="P2" s="19" t="s">
+      <c r="P2" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="Q2" s="22" t="s">
+      <c r="Q2" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="R2" s="20" t="s">
+      <c r="R2" s="21" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="3" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24" t="s">
+      <c r="C3" s="25"/>
+      <c r="D3" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24" t="s">
+      <c r="E3" s="25"/>
+      <c r="F3" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="25" t="s">
+      <c r="G3" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="26" t="s">
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
+      <c r="J3" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="27" t="s">
+      <c r="K3" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="L3" s="24"/>
-      <c r="M3" s="24" t="s">
+      <c r="L3" s="25"/>
+      <c r="M3" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="N3" s="24"/>
-      <c r="O3" s="19" t="s">
+      <c r="N3" s="25"/>
+      <c r="O3" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="P3" s="19" t="s">
+      <c r="P3" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="Q3" s="19" t="s">
+      <c r="Q3" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="R3" s="28" t="s">
+      <c r="R3" s="29" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="4" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="B4" s="16"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="29"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="16"/>
-      <c r="M4" s="16"/>
-      <c r="N4" s="16"/>
-      <c r="O4" s="16"/>
-      <c r="P4" s="16"/>
-      <c r="Q4" s="16"/>
-      <c r="R4" s="16"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="30"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="17"/>
+      <c r="R4" s="17"/>
     </row>
     <row r="5" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A5" s="30">
+      <c r="A5" s="31">
         <v>30010001</v>
       </c>
-      <c r="B5" s="31">
+      <c r="B5" s="32">
         <v>100100</v>
       </c>
-      <c r="C5" s="31" t="s">
+      <c r="C5" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="31">
         <v>31001</v>
       </c>
-      <c r="E5" s="30" t="s">
+      <c r="E5" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="30" t="s">
+      <c r="F5" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="G5" s="30"/>
-      <c r="H5" s="30"/>
-      <c r="I5" s="30" t="s">
+      <c r="G5" s="31"/>
+      <c r="H5" s="31"/>
+      <c r="I5" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="J5" s="30"/>
-      <c r="K5" s="32"/>
-      <c r="L5" s="16" t="s">
+      <c r="J5" s="31"/>
+      <c r="K5" s="33"/>
+      <c r="L5" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="M5" s="30" t="s">
+      <c r="M5" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="N5" s="30" t="s">
+      <c r="N5" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="O5" s="30"/>
-      <c r="P5" s="30"/>
-      <c r="Q5" s="33" t="s">
+      <c r="O5" s="31"/>
+      <c r="P5" s="31"/>
+      <c r="Q5" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="R5" s="34" t="s">
+      <c r="R5" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="S5" s="35" t="s">
+      <c r="S5" s="36" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="6" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A6" s="30">
+      <c r="A6" s="31">
         <v>30010002</v>
       </c>
-      <c r="B6" s="31">
+      <c r="B6" s="32">
         <v>100100</v>
       </c>
-      <c r="C6" s="31" t="s">
+      <c r="C6" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="31">
         <v>31002</v>
       </c>
-      <c r="E6" s="30" t="s">
+      <c r="E6" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="F6" s="30" t="s">
+      <c r="F6" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="G6" s="30"/>
-      <c r="H6" s="30"/>
-      <c r="I6" s="30" t="s">
+      <c r="G6" s="31"/>
+      <c r="H6" s="31"/>
+      <c r="I6" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="J6" s="30"/>
-      <c r="K6" s="32"/>
-      <c r="L6" s="16" t="s">
+      <c r="J6" s="31"/>
+      <c r="K6" s="33"/>
+      <c r="L6" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="M6" s="30" t="s">
+      <c r="M6" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="N6" s="30" t="s">
+      <c r="N6" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="O6" s="30"/>
-      <c r="P6" s="30"/>
-      <c r="Q6" s="33" t="s">
+      <c r="O6" s="31"/>
+      <c r="P6" s="31"/>
+      <c r="Q6" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="R6" s="34" t="s">
+      <c r="R6" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="S6" s="35"/>
+      <c r="S6" s="36"/>
     </row>
     <row r="7" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A7" s="30">
+      <c r="A7" s="31">
         <v>30010003</v>
       </c>
-      <c r="B7" s="31">
+      <c r="B7" s="32">
         <v>100100</v>
       </c>
-      <c r="C7" s="31" t="s">
+      <c r="C7" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="31">
         <v>31003</v>
       </c>
-      <c r="E7" s="30" t="s">
+      <c r="E7" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="30" t="s">
+      <c r="F7" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="G7" s="30"/>
-      <c r="H7" s="30"/>
-      <c r="I7" s="30" t="s">
+      <c r="G7" s="31"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="J7" s="30"/>
-      <c r="K7" s="32"/>
-      <c r="L7" s="16" t="s">
+      <c r="J7" s="31"/>
+      <c r="K7" s="33"/>
+      <c r="L7" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="M7" s="30" t="s">
+      <c r="M7" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="N7" s="30" t="s">
+      <c r="N7" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="O7" s="30"/>
-      <c r="P7" s="30"/>
-      <c r="Q7" s="33" t="s">
+      <c r="O7" s="31"/>
+      <c r="P7" s="31"/>
+      <c r="Q7" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="R7" s="34" t="s">
+      <c r="R7" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="S7" s="35"/>
+      <c r="S7" s="36"/>
     </row>
     <row r="8" s="3" customFormat="1" ht="15" customHeight="1" spans="1:19">
-      <c r="A8" s="30">
+      <c r="A8" s="31">
         <v>30010004</v>
       </c>
-      <c r="B8" s="31">
+      <c r="B8" s="32">
         <v>100100</v>
       </c>
-      <c r="C8" s="31" t="s">
+      <c r="C8" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="31">
         <v>31004</v>
       </c>
-      <c r="E8" s="30" t="s">
+      <c r="E8" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="F8" s="30" t="s">
+      <c r="F8" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="G8" s="30"/>
-      <c r="H8" s="30"/>
-      <c r="I8" s="30" t="s">
+      <c r="G8" s="31"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="J8" s="30"/>
-      <c r="K8" s="32"/>
-      <c r="L8" s="16" t="s">
+      <c r="J8" s="31"/>
+      <c r="K8" s="33"/>
+      <c r="L8" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="M8" s="30" t="s">
+      <c r="M8" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="N8" s="30" t="s">
+      <c r="N8" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="O8" s="30"/>
-      <c r="P8" s="30"/>
-      <c r="Q8" s="33" t="s">
+      <c r="O8" s="31"/>
+      <c r="P8" s="31"/>
+      <c r="Q8" s="34" t="s">
         <v>50</v>
       </c>
-      <c r="R8" s="34" t="s">
+      <c r="R8" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="S8" s="35"/>
+      <c r="S8" s="36"/>
     </row>
     <row r="9" s="3" customFormat="1" ht="15" customHeight="1" spans="1:19">
-      <c r="A9" s="16">
+      <c r="A9" s="17">
         <v>30010005</v>
       </c>
-      <c r="B9" s="28">
+      <c r="B9" s="29">
         <v>100100</v>
       </c>
-      <c r="C9" s="31" t="s">
+      <c r="C9" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="16">
+      <c r="D9" s="17">
         <v>31101</v>
       </c>
-      <c r="E9" s="16" t="s">
+      <c r="E9" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="F9" s="16" t="s">
+      <c r="F9" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="16" t="s">
+      <c r="G9" s="17"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="J9" s="16"/>
-      <c r="K9" s="18"/>
-      <c r="L9" s="16" t="s">
+      <c r="J9" s="17"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="M9" s="16" t="s">
+      <c r="M9" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="N9" s="16"/>
-      <c r="O9" s="16" t="s">
+      <c r="N9" s="17"/>
+      <c r="O9" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="P9" s="16"/>
-      <c r="Q9" s="19"/>
-      <c r="R9" s="19"/>
-      <c r="S9" s="35"/>
+      <c r="P9" s="17"/>
+      <c r="Q9" s="20"/>
+      <c r="R9" s="20"/>
+      <c r="S9" s="36"/>
     </row>
     <row r="10" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A10" s="36">
+      <c r="A10" s="37">
         <v>30010006</v>
       </c>
-      <c r="B10" s="37">
+      <c r="B10" s="38">
         <v>100100</v>
       </c>
-      <c r="C10" s="31" t="s">
+      <c r="C10" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="D10" s="36">
+      <c r="D10" s="37">
         <v>31102</v>
       </c>
-      <c r="E10" s="36" t="s">
+      <c r="E10" s="37" t="s">
         <v>55</v>
       </c>
-      <c r="F10" s="36" t="s">
+      <c r="F10" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="G10" s="36"/>
-      <c r="H10" s="36"/>
-      <c r="I10" s="36" t="s">
+      <c r="G10" s="37"/>
+      <c r="H10" s="37"/>
+      <c r="I10" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="J10" s="36"/>
-      <c r="K10" s="38"/>
-      <c r="L10" s="36" t="s">
+      <c r="J10" s="37"/>
+      <c r="K10" s="39"/>
+      <c r="L10" s="37" t="s">
         <v>36</v>
       </c>
-      <c r="M10" s="36" t="s">
+      <c r="M10" s="37" t="s">
         <v>57</v>
       </c>
-      <c r="N10" s="36" t="s">
+      <c r="N10" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="O10" s="36" t="s">
+      <c r="O10" s="37" t="s">
         <v>54</v>
       </c>
-      <c r="P10" s="36"/>
-      <c r="Q10" s="36"/>
-      <c r="R10" s="16"/>
-      <c r="S10" s="35"/>
+      <c r="P10" s="37"/>
+      <c r="Q10" s="37"/>
+      <c r="R10" s="17"/>
+      <c r="S10" s="36"/>
     </row>
     <row r="11" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A11" s="39">
+      <c r="A11" s="40">
         <v>30010007</v>
       </c>
-      <c r="B11" s="40">
+      <c r="B11" s="41">
         <v>100100</v>
       </c>
-      <c r="C11" s="31" t="s">
+      <c r="C11" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="41">
+      <c r="D11" s="42">
         <v>31201</v>
       </c>
-      <c r="E11" s="41" t="s">
+      <c r="E11" s="42" t="s">
         <v>58</v>
       </c>
-      <c r="F11" s="39" t="s">
+      <c r="F11" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="G11" s="39">
+      <c r="G11" s="40">
         <v>2001001</v>
       </c>
-      <c r="H11" s="39" t="s">
+      <c r="H11" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="I11" s="39" t="s">
+      <c r="I11" s="40" t="s">
         <v>61</v>
       </c>
-      <c r="J11" s="39"/>
-      <c r="K11" s="42">
+      <c r="J11" s="40"/>
+      <c r="K11" s="43">
         <v>10010091</v>
       </c>
-      <c r="L11" s="39"/>
-      <c r="M11" s="39"/>
-      <c r="N11" s="39"/>
-      <c r="O11" s="39"/>
-      <c r="P11" s="39"/>
-      <c r="Q11" s="39"/>
-      <c r="R11" s="16"/>
-      <c r="S11" s="35"/>
+      <c r="L11" s="40"/>
+      <c r="M11" s="40"/>
+      <c r="N11" s="40"/>
+      <c r="O11" s="40"/>
+      <c r="P11" s="40"/>
+      <c r="Q11" s="40"/>
+      <c r="R11" s="17"/>
+      <c r="S11" s="36"/>
     </row>
     <row r="12" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A12" s="43">
+      <c r="A12" s="44">
         <v>30010008</v>
       </c>
-      <c r="B12" s="44">
+      <c r="B12" s="45">
         <v>100100</v>
       </c>
-      <c r="C12" s="31" t="s">
+      <c r="C12" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="41">
+      <c r="D12" s="42">
         <v>31202</v>
       </c>
-      <c r="E12" s="41" t="s">
+      <c r="E12" s="42" t="s">
         <v>62</v>
       </c>
-      <c r="F12" s="43" t="s">
+      <c r="F12" s="44" t="s">
         <v>53</v>
       </c>
-      <c r="G12" s="43">
+      <c r="G12" s="44">
         <v>2001001</v>
       </c>
-      <c r="H12" s="43" t="s">
+      <c r="H12" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="I12" s="43" t="s">
+      <c r="I12" s="44" t="s">
         <v>63</v>
       </c>
-      <c r="J12" s="43"/>
-      <c r="K12" s="45" t="s">
+      <c r="J12" s="44"/>
+      <c r="K12" s="46" t="s">
         <v>64</v>
       </c>
-      <c r="L12" s="43"/>
-      <c r="M12" s="43"/>
-      <c r="N12" s="43"/>
-      <c r="O12" s="43"/>
-      <c r="P12" s="43"/>
-      <c r="Q12" s="43"/>
-      <c r="R12" s="16"/>
-      <c r="S12" s="35"/>
+      <c r="L12" s="44"/>
+      <c r="M12" s="44"/>
+      <c r="N12" s="44"/>
+      <c r="O12" s="44"/>
+      <c r="P12" s="44"/>
+      <c r="Q12" s="44"/>
+      <c r="R12" s="17"/>
+      <c r="S12" s="36"/>
     </row>
     <row r="13" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A13" s="46">
+      <c r="A13" s="47">
         <v>30010009</v>
       </c>
-      <c r="B13" s="47">
+      <c r="B13" s="48">
         <v>100100</v>
       </c>
-      <c r="C13" s="31" t="s">
+      <c r="C13" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="D13" s="41">
+      <c r="D13" s="42">
         <v>31203</v>
       </c>
-      <c r="E13" s="41" t="s">
+      <c r="E13" s="42" t="s">
         <v>65</v>
       </c>
-      <c r="F13" s="46" t="s">
+      <c r="F13" s="47" t="s">
         <v>53</v>
       </c>
-      <c r="G13" s="46">
+      <c r="G13" s="47">
         <v>2001001</v>
       </c>
-      <c r="H13" s="46" t="s">
+      <c r="H13" s="47" t="s">
         <v>60</v>
       </c>
-      <c r="I13" s="46" t="s">
+      <c r="I13" s="47" t="s">
         <v>66</v>
       </c>
-      <c r="J13" s="46"/>
-      <c r="K13" s="48" t="s">
+      <c r="J13" s="47"/>
+      <c r="K13" s="49" t="s">
         <v>67</v>
       </c>
-      <c r="L13" s="46"/>
-      <c r="M13" s="46"/>
-      <c r="N13" s="46"/>
-      <c r="O13" s="46"/>
-      <c r="P13" s="46"/>
-      <c r="Q13" s="46"/>
-      <c r="R13" s="16"/>
-      <c r="S13" s="35"/>
+      <c r="L13" s="47"/>
+      <c r="M13" s="47"/>
+      <c r="N13" s="47"/>
+      <c r="O13" s="47"/>
+      <c r="P13" s="47"/>
+      <c r="Q13" s="47"/>
+      <c r="R13" s="17"/>
+      <c r="S13" s="36"/>
     </row>
     <row r="14" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A14" s="41">
+      <c r="A14" s="42">
         <v>30010010</v>
       </c>
-      <c r="B14" s="49">
+      <c r="B14" s="50">
         <v>100100</v>
       </c>
-      <c r="C14" s="31" t="s">
+      <c r="C14" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="D14" s="50">
+      <c r="D14" s="51">
         <v>31301</v>
       </c>
-      <c r="E14" s="50" t="s">
+      <c r="E14" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="F14" s="41" t="s">
+      <c r="F14" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="G14" s="41"/>
-      <c r="H14" s="41"/>
-      <c r="I14" s="41" t="s">
+      <c r="G14" s="42"/>
+      <c r="H14" s="42"/>
+      <c r="I14" s="42" t="s">
         <v>69</v>
       </c>
-      <c r="J14" s="41"/>
-      <c r="K14" s="51"/>
-      <c r="L14" s="41" t="s">
+      <c r="J14" s="42"/>
+      <c r="K14" s="52"/>
+      <c r="L14" s="42" t="s">
         <v>36</v>
       </c>
-      <c r="M14" s="41" t="s">
+      <c r="M14" s="42" t="s">
         <v>70</v>
       </c>
-      <c r="N14" s="41"/>
-      <c r="O14" s="41"/>
-      <c r="P14" s="41"/>
-      <c r="Q14" s="52" t="s">
+      <c r="N14" s="42"/>
+      <c r="O14" s="42"/>
+      <c r="P14" s="42"/>
+      <c r="Q14" s="53" t="s">
         <v>71</v>
       </c>
-      <c r="R14" s="53" t="s">
+      <c r="R14" s="54" t="s">
         <v>72</v>
       </c>
-      <c r="S14" s="19" t="s">
+      <c r="S14" s="20" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="15" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A15" s="46">
+      <c r="A15" s="47">
         <v>30010011</v>
       </c>
-      <c r="B15" s="47">
+      <c r="B15" s="48">
         <v>100100</v>
       </c>
-      <c r="C15" s="31" t="s">
+      <c r="C15" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="D15" s="50">
+      <c r="D15" s="51">
         <v>31302</v>
       </c>
-      <c r="E15" s="50" t="s">
+      <c r="E15" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F15" s="46" t="s">
+      <c r="F15" s="47" t="s">
         <v>34</v>
       </c>
-      <c r="G15" s="46"/>
-      <c r="H15" s="46"/>
-      <c r="I15" s="46" t="s">
+      <c r="G15" s="47"/>
+      <c r="H15" s="47"/>
+      <c r="I15" s="47" t="s">
         <v>75</v>
       </c>
-      <c r="J15" s="46"/>
-      <c r="K15" s="48"/>
-      <c r="L15" s="46" t="s">
+      <c r="J15" s="47"/>
+      <c r="K15" s="49"/>
+      <c r="L15" s="47" t="s">
         <v>36</v>
       </c>
-      <c r="M15" s="46" t="s">
+      <c r="M15" s="47" t="s">
         <v>57</v>
       </c>
-      <c r="N15" s="46"/>
-      <c r="O15" s="46"/>
-      <c r="P15" s="46"/>
-      <c r="Q15" s="46"/>
-      <c r="R15" s="16"/>
-      <c r="S15" s="35"/>
+      <c r="N15" s="47"/>
+      <c r="O15" s="47"/>
+      <c r="P15" s="47"/>
+      <c r="Q15" s="47"/>
+      <c r="R15" s="17"/>
+      <c r="S15" s="36"/>
     </row>
     <row r="16" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A16" s="46">
+      <c r="A16" s="47">
         <v>30010012</v>
       </c>
-      <c r="B16" s="47">
+      <c r="B16" s="48">
         <v>100100</v>
       </c>
-      <c r="C16" s="31" t="s">
+      <c r="C16" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="D16" s="50">
+      <c r="D16" s="51">
         <v>31303</v>
       </c>
-      <c r="E16" s="50" t="s">
+      <c r="E16" s="51" t="s">
         <v>76</v>
       </c>
-      <c r="F16" s="46" t="s">
+      <c r="F16" s="47" t="s">
         <v>53</v>
       </c>
-      <c r="G16" s="46">
+      <c r="G16" s="47">
         <v>2001001</v>
       </c>
-      <c r="H16" s="46" t="s">
+      <c r="H16" s="47" t="s">
         <v>60</v>
       </c>
-      <c r="I16" s="46" t="s">
+      <c r="I16" s="47" t="s">
         <v>66</v>
       </c>
-      <c r="J16" s="46"/>
-      <c r="K16" s="48" t="s">
+      <c r="J16" s="47"/>
+      <c r="K16" s="49" t="s">
         <v>67</v>
       </c>
-      <c r="L16" s="46"/>
-      <c r="M16" s="46"/>
-      <c r="N16" s="46"/>
-      <c r="O16" s="46"/>
-      <c r="P16" s="46"/>
-      <c r="Q16" s="46"/>
-      <c r="R16" s="16"/>
-      <c r="S16" s="35"/>
+      <c r="L16" s="47"/>
+      <c r="M16" s="47"/>
+      <c r="N16" s="47"/>
+      <c r="O16" s="47"/>
+      <c r="P16" s="47"/>
+      <c r="Q16" s="47"/>
+      <c r="R16" s="17"/>
+      <c r="S16" s="36"/>
     </row>
     <row r="17" s="3" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A17" s="16">
+      <c r="A17" s="17">
         <v>30070001</v>
       </c>
       <c r="B17" s="3">
@@ -2956,30 +2977,30 @@
       <c r="C17" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D17" s="39">
+      <c r="D17" s="40">
         <v>34001</v>
       </c>
-      <c r="E17" s="39" t="s">
+      <c r="E17" s="40" t="s">
         <v>78</v>
       </c>
-      <c r="F17" s="39" t="s">
+      <c r="F17" s="40" t="s">
         <v>79</v>
       </c>
-      <c r="G17" s="28">
+      <c r="G17" s="29">
         <v>2007001</v>
       </c>
-      <c r="H17" s="16" t="s">
+      <c r="H17" s="17" t="s">
         <v>60</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="K17" s="54" t="s">
+      <c r="K17" s="55" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="18" s="3" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A18" s="16">
+      <c r="A18" s="17">
         <v>30070002</v>
       </c>
       <c r="B18" s="3">
@@ -2988,30 +3009,30 @@
       <c r="C18" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D18" s="39">
+      <c r="D18" s="40">
         <v>34002</v>
       </c>
-      <c r="E18" s="39" t="s">
+      <c r="E18" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="F18" s="39" t="s">
+      <c r="F18" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="G18" s="28">
+      <c r="G18" s="29">
         <v>2007001</v>
       </c>
-      <c r="H18" s="16" t="s">
+      <c r="H18" s="17" t="s">
         <v>60</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="K18" s="54" t="s">
+      <c r="K18" s="55" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="19" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A19" s="41">
+      <c r="A19" s="42">
         <v>30120001</v>
       </c>
       <c r="B19" s="4">
@@ -3020,33 +3041,33 @@
       <c r="C19" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D19" s="41">
+      <c r="D19" s="42">
         <v>32001</v>
       </c>
-      <c r="E19" s="41" t="s">
+      <c r="E19" s="42" t="s">
         <v>85</v>
       </c>
-      <c r="F19" s="41" t="s">
+      <c r="F19" s="42" t="s">
         <v>53</v>
       </c>
-      <c r="G19" s="49">
+      <c r="G19" s="50">
         <v>2012001</v>
       </c>
-      <c r="H19" s="41" t="s">
+      <c r="H19" s="42" t="s">
         <v>60</v>
       </c>
-      <c r="I19" s="41" t="s">
+      <c r="I19" s="42" t="s">
         <v>85</v>
       </c>
-      <c r="J19" s="41" t="s">
+      <c r="J19" s="42" t="s">
         <v>86</v>
       </c>
-      <c r="K19" s="55">
+      <c r="K19" s="56">
         <v>10120041</v>
       </c>
     </row>
     <row r="20" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A20" s="41">
+      <c r="A20" s="42">
         <v>30120002</v>
       </c>
       <c r="B20" s="4">
@@ -3055,33 +3076,33 @@
       <c r="C20" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D20" s="41">
+      <c r="D20" s="42">
         <v>32002</v>
       </c>
-      <c r="E20" s="41" t="s">
+      <c r="E20" s="42" t="s">
         <v>87</v>
       </c>
-      <c r="F20" s="41" t="s">
+      <c r="F20" s="42" t="s">
         <v>53</v>
       </c>
-      <c r="G20" s="49">
+      <c r="G20" s="50">
         <v>2012001</v>
       </c>
-      <c r="H20" s="41" t="s">
+      <c r="H20" s="42" t="s">
         <v>60</v>
       </c>
-      <c r="I20" s="41" t="s">
+      <c r="I20" s="42" t="s">
         <v>87</v>
       </c>
-      <c r="J20" s="41" t="s">
+      <c r="J20" s="42" t="s">
         <v>86</v>
       </c>
-      <c r="K20" s="55">
+      <c r="K20" s="56">
         <v>10120042</v>
       </c>
     </row>
     <row r="21" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A21" s="41">
+      <c r="A21" s="42">
         <v>30120003</v>
       </c>
       <c r="B21" s="4">
@@ -3090,33 +3111,33 @@
       <c r="C21" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D21" s="41">
+      <c r="D21" s="42">
         <v>32003</v>
       </c>
-      <c r="E21" s="41" t="s">
+      <c r="E21" s="42" t="s">
         <v>88</v>
       </c>
-      <c r="F21" s="41" t="s">
+      <c r="F21" s="42" t="s">
         <v>53</v>
       </c>
-      <c r="G21" s="49">
+      <c r="G21" s="50">
         <v>2012001</v>
       </c>
-      <c r="H21" s="41" t="s">
+      <c r="H21" s="42" t="s">
         <v>60</v>
       </c>
-      <c r="I21" s="41" t="s">
+      <c r="I21" s="42" t="s">
         <v>88</v>
       </c>
-      <c r="J21" s="41" t="s">
+      <c r="J21" s="42" t="s">
         <v>86</v>
       </c>
-      <c r="K21" s="55">
+      <c r="K21" s="56">
         <v>10120043</v>
       </c>
     </row>
     <row r="22" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A22" s="41">
+      <c r="A22" s="42">
         <v>30120004</v>
       </c>
       <c r="B22" s="4">
@@ -3125,33 +3146,33 @@
       <c r="C22" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D22" s="41">
+      <c r="D22" s="42">
         <v>32004</v>
       </c>
-      <c r="E22" s="41" t="s">
+      <c r="E22" s="42" t="s">
         <v>89</v>
       </c>
-      <c r="F22" s="41" t="s">
+      <c r="F22" s="42" t="s">
         <v>53</v>
       </c>
-      <c r="G22" s="49">
+      <c r="G22" s="50">
         <v>2012001</v>
       </c>
-      <c r="H22" s="41" t="s">
+      <c r="H22" s="42" t="s">
         <v>60</v>
       </c>
-      <c r="I22" s="41" t="s">
+      <c r="I22" s="42" t="s">
         <v>89</v>
       </c>
-      <c r="J22" s="41" t="s">
+      <c r="J22" s="42" t="s">
         <v>86</v>
       </c>
-      <c r="K22" s="55">
+      <c r="K22" s="56">
         <v>10120044</v>
       </c>
     </row>
     <row r="23" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A23" s="41">
+      <c r="A23" s="42">
         <v>30120005</v>
       </c>
       <c r="B23" s="4">
@@ -3160,33 +3181,33 @@
       <c r="C23" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D23" s="41">
+      <c r="D23" s="42">
         <v>32005</v>
       </c>
-      <c r="E23" s="41" t="s">
+      <c r="E23" s="42" t="s">
         <v>89</v>
       </c>
-      <c r="F23" s="41" t="s">
+      <c r="F23" s="42" t="s">
         <v>53</v>
       </c>
-      <c r="G23" s="49">
+      <c r="G23" s="50">
         <v>2012001</v>
       </c>
-      <c r="H23" s="41" t="s">
+      <c r="H23" s="42" t="s">
         <v>60</v>
       </c>
-      <c r="I23" s="41" t="s">
+      <c r="I23" s="42" t="s">
         <v>89</v>
       </c>
-      <c r="J23" s="41" t="s">
+      <c r="J23" s="42" t="s">
         <v>86</v>
       </c>
-      <c r="K23" s="55">
+      <c r="K23" s="56">
         <v>10120045</v>
       </c>
     </row>
     <row r="24" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A24" s="41">
+      <c r="A24" s="42">
         <v>30120006</v>
       </c>
       <c r="B24" s="4">
@@ -3195,33 +3216,33 @@
       <c r="C24" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D24" s="41">
+      <c r="D24" s="42">
         <v>32006</v>
       </c>
-      <c r="E24" s="41" t="s">
+      <c r="E24" s="42" t="s">
         <v>89</v>
       </c>
-      <c r="F24" s="41" t="s">
+      <c r="F24" s="42" t="s">
         <v>53</v>
       </c>
-      <c r="G24" s="49">
+      <c r="G24" s="50">
         <v>2012001</v>
       </c>
-      <c r="H24" s="41" t="s">
+      <c r="H24" s="42" t="s">
         <v>60</v>
       </c>
-      <c r="I24" s="41" t="s">
+      <c r="I24" s="42" t="s">
         <v>89</v>
       </c>
-      <c r="J24" s="41" t="s">
+      <c r="J24" s="42" t="s">
         <v>86</v>
       </c>
-      <c r="K24" s="55">
+      <c r="K24" s="56">
         <v>10120046</v>
       </c>
     </row>
     <row r="25" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A25" s="56">
+      <c r="A25" s="57">
         <v>30120011</v>
       </c>
       <c r="B25" s="5">
@@ -3230,33 +3251,33 @@
       <c r="C25" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="D25" s="41">
+      <c r="D25" s="42">
         <v>32101</v>
       </c>
-      <c r="E25" s="56" t="s">
+      <c r="E25" s="57" t="s">
         <v>85</v>
       </c>
-      <c r="F25" s="56" t="s">
+      <c r="F25" s="57" t="s">
         <v>53</v>
       </c>
-      <c r="G25" s="57">
+      <c r="G25" s="58">
         <v>2012001</v>
       </c>
-      <c r="H25" s="56" t="s">
+      <c r="H25" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="I25" s="56" t="s">
+      <c r="I25" s="57" t="s">
         <v>85</v>
       </c>
-      <c r="J25" s="56" t="s">
+      <c r="J25" s="57" t="s">
         <v>91</v>
       </c>
-      <c r="K25" s="58">
+      <c r="K25" s="59">
         <v>10120041</v>
       </c>
     </row>
     <row r="26" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A26" s="56">
+      <c r="A26" s="57">
         <v>30120012</v>
       </c>
       <c r="B26" s="5">
@@ -3265,33 +3286,33 @@
       <c r="C26" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="D26" s="41">
+      <c r="D26" s="42">
         <v>32102</v>
       </c>
-      <c r="E26" s="56" t="s">
+      <c r="E26" s="57" t="s">
         <v>87</v>
       </c>
-      <c r="F26" s="56" t="s">
+      <c r="F26" s="57" t="s">
         <v>53</v>
       </c>
-      <c r="G26" s="57">
+      <c r="G26" s="58">
         <v>2012001</v>
       </c>
-      <c r="H26" s="56" t="s">
+      <c r="H26" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="I26" s="56" t="s">
+      <c r="I26" s="57" t="s">
         <v>87</v>
       </c>
-      <c r="J26" s="56" t="s">
+      <c r="J26" s="57" t="s">
         <v>91</v>
       </c>
-      <c r="K26" s="58">
+      <c r="K26" s="59">
         <v>10120042</v>
       </c>
     </row>
     <row r="27" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A27" s="56">
+      <c r="A27" s="57">
         <v>30120013</v>
       </c>
       <c r="B27" s="5">
@@ -3300,33 +3321,33 @@
       <c r="C27" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="D27" s="41">
+      <c r="D27" s="42">
         <v>32103</v>
       </c>
-      <c r="E27" s="56" t="s">
+      <c r="E27" s="57" t="s">
         <v>88</v>
       </c>
-      <c r="F27" s="56" t="s">
+      <c r="F27" s="57" t="s">
         <v>53</v>
       </c>
-      <c r="G27" s="57">
+      <c r="G27" s="58">
         <v>2012001</v>
       </c>
-      <c r="H27" s="56" t="s">
+      <c r="H27" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="I27" s="56" t="s">
+      <c r="I27" s="57" t="s">
         <v>88</v>
       </c>
-      <c r="J27" s="56" t="s">
+      <c r="J27" s="57" t="s">
         <v>91</v>
       </c>
-      <c r="K27" s="58">
+      <c r="K27" s="59">
         <v>10120043</v>
       </c>
     </row>
     <row r="28" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A28" s="56">
+      <c r="A28" s="57">
         <v>30120014</v>
       </c>
       <c r="B28" s="5">
@@ -3335,33 +3356,33 @@
       <c r="C28" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="D28" s="41">
+      <c r="D28" s="42">
         <v>32104</v>
       </c>
-      <c r="E28" s="56" t="s">
+      <c r="E28" s="57" t="s">
         <v>89</v>
       </c>
-      <c r="F28" s="56" t="s">
+      <c r="F28" s="57" t="s">
         <v>53</v>
       </c>
-      <c r="G28" s="57">
+      <c r="G28" s="58">
         <v>2012001</v>
       </c>
-      <c r="H28" s="56" t="s">
+      <c r="H28" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="I28" s="56" t="s">
+      <c r="I28" s="57" t="s">
         <v>89</v>
       </c>
-      <c r="J28" s="56" t="s">
+      <c r="J28" s="57" t="s">
         <v>91</v>
       </c>
-      <c r="K28" s="58">
+      <c r="K28" s="59">
         <v>10120044</v>
       </c>
     </row>
     <row r="29" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A29" s="56">
+      <c r="A29" s="57">
         <v>30120015</v>
       </c>
       <c r="B29" s="5">
@@ -3370,33 +3391,33 @@
       <c r="C29" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="D29" s="41">
+      <c r="D29" s="42">
         <v>32105</v>
       </c>
-      <c r="E29" s="56" t="s">
+      <c r="E29" s="57" t="s">
         <v>89</v>
       </c>
-      <c r="F29" s="56" t="s">
+      <c r="F29" s="57" t="s">
         <v>53</v>
       </c>
-      <c r="G29" s="57">
+      <c r="G29" s="58">
         <v>2012001</v>
       </c>
-      <c r="H29" s="56" t="s">
+      <c r="H29" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="I29" s="56" t="s">
+      <c r="I29" s="57" t="s">
         <v>89</v>
       </c>
-      <c r="J29" s="56" t="s">
+      <c r="J29" s="57" t="s">
         <v>91</v>
       </c>
-      <c r="K29" s="58">
+      <c r="K29" s="59">
         <v>10120045</v>
       </c>
     </row>
     <row r="30" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A30" s="56">
+      <c r="A30" s="57">
         <v>30120016</v>
       </c>
       <c r="B30" s="5">
@@ -3405,33 +3426,33 @@
       <c r="C30" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="D30" s="41">
+      <c r="D30" s="42">
         <v>32106</v>
       </c>
-      <c r="E30" s="56" t="s">
+      <c r="E30" s="57" t="s">
         <v>89</v>
       </c>
-      <c r="F30" s="56" t="s">
+      <c r="F30" s="57" t="s">
         <v>53</v>
       </c>
-      <c r="G30" s="57">
+      <c r="G30" s="58">
         <v>2012001</v>
       </c>
-      <c r="H30" s="56" t="s">
+      <c r="H30" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="I30" s="56" t="s">
+      <c r="I30" s="57" t="s">
         <v>89</v>
       </c>
-      <c r="J30" s="56" t="s">
+      <c r="J30" s="57" t="s">
         <v>91</v>
       </c>
-      <c r="K30" s="58">
+      <c r="K30" s="59">
         <v>10120046</v>
       </c>
     </row>
     <row r="31" s="6" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A31" s="50">
+      <c r="A31" s="51">
         <v>30120021</v>
       </c>
       <c r="B31" s="6">
@@ -3440,31 +3461,31 @@
       <c r="C31" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D31" s="50">
+      <c r="D31" s="51">
         <v>32201</v>
       </c>
-      <c r="E31" s="50" t="s">
+      <c r="E31" s="51" t="s">
         <v>85</v>
       </c>
-      <c r="F31" s="50" t="s">
+      <c r="F31" s="51" t="s">
         <v>53</v>
       </c>
-      <c r="G31" s="59">
+      <c r="G31" s="60">
         <v>2012001</v>
       </c>
-      <c r="H31" s="50" t="s">
+      <c r="H31" s="51" t="s">
         <v>60</v>
       </c>
-      <c r="I31" s="50" t="s">
+      <c r="I31" s="51" t="s">
         <v>85</v>
       </c>
-      <c r="J31" s="50"/>
-      <c r="K31" s="60">
+      <c r="J31" s="51"/>
+      <c r="K31" s="61">
         <v>10120041</v>
       </c>
     </row>
     <row r="32" s="6" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A32" s="50">
+      <c r="A32" s="51">
         <v>30120022</v>
       </c>
       <c r="B32" s="6">
@@ -3473,31 +3494,31 @@
       <c r="C32" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D32" s="50">
+      <c r="D32" s="51">
         <v>32202</v>
       </c>
-      <c r="E32" s="50" t="s">
+      <c r="E32" s="51" t="s">
         <v>87</v>
       </c>
-      <c r="F32" s="50" t="s">
+      <c r="F32" s="51" t="s">
         <v>53</v>
       </c>
-      <c r="G32" s="59">
+      <c r="G32" s="60">
         <v>2012001</v>
       </c>
-      <c r="H32" s="50" t="s">
+      <c r="H32" s="51" t="s">
         <v>60</v>
       </c>
-      <c r="I32" s="50" t="s">
+      <c r="I32" s="51" t="s">
         <v>87</v>
       </c>
-      <c r="J32" s="50"/>
-      <c r="K32" s="60">
+      <c r="J32" s="51"/>
+      <c r="K32" s="61">
         <v>10120042</v>
       </c>
     </row>
     <row r="33" s="6" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A33" s="50">
+      <c r="A33" s="51">
         <v>30120023</v>
       </c>
       <c r="B33" s="6">
@@ -3506,31 +3527,31 @@
       <c r="C33" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D33" s="50">
+      <c r="D33" s="51">
         <v>32203</v>
       </c>
-      <c r="E33" s="50" t="s">
+      <c r="E33" s="51" t="s">
         <v>88</v>
       </c>
-      <c r="F33" s="50" t="s">
+      <c r="F33" s="51" t="s">
         <v>53</v>
       </c>
-      <c r="G33" s="59">
+      <c r="G33" s="60">
         <v>2012001</v>
       </c>
-      <c r="H33" s="50" t="s">
+      <c r="H33" s="51" t="s">
         <v>60</v>
       </c>
-      <c r="I33" s="50" t="s">
+      <c r="I33" s="51" t="s">
         <v>88</v>
       </c>
-      <c r="J33" s="50"/>
-      <c r="K33" s="60">
+      <c r="J33" s="51"/>
+      <c r="K33" s="61">
         <v>10120043</v>
       </c>
     </row>
     <row r="34" s="6" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A34" s="50">
+      <c r="A34" s="51">
         <v>30120024</v>
       </c>
       <c r="B34" s="6">
@@ -3539,31 +3560,31 @@
       <c r="C34" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D34" s="50">
+      <c r="D34" s="51">
         <v>32204</v>
       </c>
-      <c r="E34" s="50" t="s">
+      <c r="E34" s="51" t="s">
         <v>89</v>
       </c>
-      <c r="F34" s="50" t="s">
+      <c r="F34" s="51" t="s">
         <v>53</v>
       </c>
-      <c r="G34" s="59">
+      <c r="G34" s="60">
         <v>2012001</v>
       </c>
-      <c r="H34" s="50" t="s">
+      <c r="H34" s="51" t="s">
         <v>60</v>
       </c>
-      <c r="I34" s="50" t="s">
+      <c r="I34" s="51" t="s">
         <v>89</v>
       </c>
-      <c r="J34" s="50"/>
-      <c r="K34" s="60">
+      <c r="J34" s="51"/>
+      <c r="K34" s="61">
         <v>10120044</v>
       </c>
     </row>
     <row r="35" s="6" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A35" s="50">
+      <c r="A35" s="51">
         <v>30120025</v>
       </c>
       <c r="B35" s="6">
@@ -3572,31 +3593,31 @@
       <c r="C35" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D35" s="50">
+      <c r="D35" s="51">
         <v>32205</v>
       </c>
-      <c r="E35" s="50" t="s">
+      <c r="E35" s="51" t="s">
         <v>89</v>
       </c>
-      <c r="F35" s="50" t="s">
+      <c r="F35" s="51" t="s">
         <v>53</v>
       </c>
-      <c r="G35" s="59">
+      <c r="G35" s="60">
         <v>2012001</v>
       </c>
-      <c r="H35" s="50" t="s">
+      <c r="H35" s="51" t="s">
         <v>60</v>
       </c>
-      <c r="I35" s="50" t="s">
+      <c r="I35" s="51" t="s">
         <v>89</v>
       </c>
-      <c r="J35" s="50"/>
-      <c r="K35" s="60">
+      <c r="J35" s="51"/>
+      <c r="K35" s="61">
         <v>10120045</v>
       </c>
     </row>
     <row r="36" s="6" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A36" s="50">
+      <c r="A36" s="51">
         <v>30120026</v>
       </c>
       <c r="B36" s="6">
@@ -3605,1249 +3626,1292 @@
       <c r="C36" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D36" s="50">
+      <c r="D36" s="51">
         <v>32206</v>
       </c>
-      <c r="E36" s="50" t="s">
+      <c r="E36" s="51" t="s">
         <v>89</v>
       </c>
-      <c r="F36" s="50" t="s">
+      <c r="F36" s="51" t="s">
         <v>53</v>
       </c>
-      <c r="G36" s="59">
+      <c r="G36" s="60">
         <v>2012001</v>
       </c>
-      <c r="H36" s="50" t="s">
+      <c r="H36" s="51" t="s">
         <v>60</v>
       </c>
-      <c r="I36" s="50" t="s">
+      <c r="I36" s="51" t="s">
         <v>89</v>
       </c>
-      <c r="J36" s="50"/>
-      <c r="K36" s="60">
+      <c r="J36" s="51"/>
+      <c r="K36" s="61">
         <v>10120046</v>
       </c>
     </row>
     <row r="37" s="7" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A37" s="61">
+      <c r="A37" s="62">
         <v>30240001</v>
       </c>
-      <c r="B37" s="62">
+      <c r="B37" s="63">
         <v>102400</v>
       </c>
-      <c r="C37" s="62" t="s">
+      <c r="C37" s="63" t="s">
         <v>32</v>
       </c>
-      <c r="D37" s="61">
+      <c r="D37" s="62">
         <v>32401</v>
       </c>
-      <c r="E37" s="61" t="s">
+      <c r="E37" s="62" t="s">
         <v>33</v>
       </c>
-      <c r="F37" s="61" t="s">
+      <c r="F37" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="G37" s="61"/>
-      <c r="H37" s="61"/>
-      <c r="I37" s="61" t="s">
+      <c r="G37" s="62"/>
+      <c r="H37" s="62"/>
+      <c r="I37" s="62" t="s">
         <v>35</v>
       </c>
-      <c r="J37" s="61"/>
-      <c r="K37" s="63"/>
-      <c r="L37" s="61" t="s">
+      <c r="J37" s="62"/>
+      <c r="K37" s="64"/>
+      <c r="L37" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="M37" s="61" t="s">
+      <c r="M37" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="N37" s="61" t="s">
+      <c r="N37" s="62" t="s">
         <v>38</v>
       </c>
-      <c r="O37" s="61"/>
-      <c r="P37" s="61"/>
-      <c r="Q37" s="64" t="s">
+      <c r="O37" s="62"/>
+      <c r="P37" s="62"/>
+      <c r="Q37" s="65" t="s">
         <v>39</v>
       </c>
-      <c r="R37" s="65" t="s">
+      <c r="R37" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="S37" s="66" t="s">
+      <c r="S37" s="67" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="38" s="7" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A38" s="61">
+      <c r="A38" s="62">
         <v>30240002</v>
       </c>
-      <c r="B38" s="62">
+      <c r="B38" s="63">
         <v>102400</v>
       </c>
-      <c r="C38" s="62" t="s">
+      <c r="C38" s="63" t="s">
         <v>32</v>
       </c>
-      <c r="D38" s="61">
+      <c r="D38" s="62">
         <v>32402</v>
       </c>
-      <c r="E38" s="61" t="s">
+      <c r="E38" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="F38" s="61" t="s">
+      <c r="F38" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="G38" s="61"/>
-      <c r="H38" s="61"/>
-      <c r="I38" s="61" t="s">
+      <c r="G38" s="62"/>
+      <c r="H38" s="62"/>
+      <c r="I38" s="62" t="s">
         <v>43</v>
       </c>
-      <c r="J38" s="61"/>
-      <c r="K38" s="63"/>
-      <c r="L38" s="61" t="s">
+      <c r="J38" s="62"/>
+      <c r="K38" s="64"/>
+      <c r="L38" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="M38" s="61" t="s">
+      <c r="M38" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="N38" s="61" t="s">
+      <c r="N38" s="62" t="s">
         <v>38</v>
       </c>
-      <c r="O38" s="61"/>
-      <c r="P38" s="61"/>
-      <c r="Q38" s="64" t="s">
+      <c r="O38" s="62"/>
+      <c r="P38" s="62"/>
+      <c r="Q38" s="65" t="s">
         <v>44</v>
       </c>
-      <c r="R38" s="65" t="s">
+      <c r="R38" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="S38" s="66"/>
+      <c r="S38" s="67"/>
     </row>
     <row r="39" s="7" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A39" s="61">
+      <c r="A39" s="62">
         <v>30240003</v>
       </c>
-      <c r="B39" s="62">
+      <c r="B39" s="63">
         <v>102400</v>
       </c>
-      <c r="C39" s="62" t="s">
+      <c r="C39" s="63" t="s">
         <v>32</v>
       </c>
-      <c r="D39" s="61">
+      <c r="D39" s="62">
         <v>32403</v>
       </c>
-      <c r="E39" s="61" t="s">
+      <c r="E39" s="62" t="s">
         <v>45</v>
       </c>
-      <c r="F39" s="61" t="s">
+      <c r="F39" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="G39" s="61"/>
-      <c r="H39" s="61"/>
-      <c r="I39" s="61" t="s">
+      <c r="G39" s="62"/>
+      <c r="H39" s="62"/>
+      <c r="I39" s="62" t="s">
         <v>46</v>
       </c>
-      <c r="J39" s="61"/>
-      <c r="K39" s="63"/>
-      <c r="L39" s="61" t="s">
+      <c r="J39" s="62"/>
+      <c r="K39" s="64"/>
+      <c r="L39" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="M39" s="61" t="s">
+      <c r="M39" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="N39" s="61" t="s">
+      <c r="N39" s="62" t="s">
         <v>38</v>
       </c>
-      <c r="O39" s="61"/>
-      <c r="P39" s="61"/>
-      <c r="Q39" s="64" t="s">
+      <c r="O39" s="62"/>
+      <c r="P39" s="62"/>
+      <c r="Q39" s="65" t="s">
         <v>47</v>
       </c>
-      <c r="R39" s="65" t="s">
+      <c r="R39" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="S39" s="66"/>
+      <c r="S39" s="67"/>
     </row>
     <row r="40" s="7" customFormat="1" ht="15" customHeight="1" spans="1:19">
-      <c r="A40" s="61">
+      <c r="A40" s="62">
         <v>30240004</v>
       </c>
-      <c r="B40" s="62">
+      <c r="B40" s="63">
         <v>102400</v>
       </c>
-      <c r="C40" s="62" t="s">
+      <c r="C40" s="63" t="s">
         <v>32</v>
       </c>
-      <c r="D40" s="61">
+      <c r="D40" s="62">
         <v>32404</v>
       </c>
-      <c r="E40" s="61" t="s">
+      <c r="E40" s="62" t="s">
         <v>48</v>
       </c>
-      <c r="F40" s="61" t="s">
+      <c r="F40" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="G40" s="61"/>
-      <c r="H40" s="61"/>
-      <c r="I40" s="61" t="s">
+      <c r="G40" s="62"/>
+      <c r="H40" s="62"/>
+      <c r="I40" s="62" t="s">
         <v>49</v>
       </c>
-      <c r="J40" s="61"/>
-      <c r="K40" s="63"/>
-      <c r="L40" s="61" t="s">
+      <c r="J40" s="62"/>
+      <c r="K40" s="64"/>
+      <c r="L40" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="M40" s="61" t="s">
+      <c r="M40" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="N40" s="61" t="s">
+      <c r="N40" s="62" t="s">
         <v>38</v>
       </c>
-      <c r="O40" s="61"/>
-      <c r="P40" s="61"/>
-      <c r="Q40" s="64" t="s">
+      <c r="O40" s="62"/>
+      <c r="P40" s="62"/>
+      <c r="Q40" s="65" t="s">
         <v>50</v>
       </c>
-      <c r="R40" s="65" t="s">
+      <c r="R40" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="S40" s="66"/>
+      <c r="S40" s="67"/>
     </row>
     <row r="41" s="7" customFormat="1" ht="15" customHeight="1" spans="1:19">
-      <c r="A41" s="61">
+      <c r="A41" s="62">
         <v>30240005</v>
       </c>
-      <c r="B41" s="62">
+      <c r="B41" s="63">
         <v>102400</v>
       </c>
-      <c r="C41" s="62" t="s">
+      <c r="C41" s="63" t="s">
         <v>32</v>
       </c>
-      <c r="D41" s="61">
+      <c r="D41" s="62">
         <v>32411</v>
       </c>
-      <c r="E41" s="61" t="s">
+      <c r="E41" s="62" t="s">
         <v>51</v>
       </c>
-      <c r="F41" s="61" t="s">
+      <c r="F41" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="G41" s="61"/>
-      <c r="H41" s="61"/>
-      <c r="I41" s="61" t="s">
+      <c r="G41" s="62"/>
+      <c r="H41" s="62"/>
+      <c r="I41" s="62" t="s">
         <v>52</v>
       </c>
-      <c r="J41" s="61"/>
-      <c r="K41" s="63"/>
-      <c r="L41" s="61" t="s">
+      <c r="J41" s="62"/>
+      <c r="K41" s="64"/>
+      <c r="L41" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="M41" s="61" t="s">
+      <c r="M41" s="62" t="s">
         <v>53</v>
       </c>
-      <c r="N41" s="61"/>
-      <c r="O41" s="61" t="s">
+      <c r="N41" s="62"/>
+      <c r="O41" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="P41" s="61"/>
-      <c r="Q41" s="64"/>
-      <c r="R41" s="64"/>
-      <c r="S41" s="66"/>
+      <c r="P41" s="62"/>
+      <c r="Q41" s="65"/>
+      <c r="R41" s="65"/>
+      <c r="S41" s="67"/>
     </row>
     <row r="42" s="7" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A42" s="61">
+      <c r="A42" s="62">
         <v>30240006</v>
       </c>
-      <c r="B42" s="62">
+      <c r="B42" s="63">
         <v>102400</v>
       </c>
-      <c r="C42" s="62" t="s">
+      <c r="C42" s="63" t="s">
         <v>32</v>
       </c>
-      <c r="D42" s="61">
+      <c r="D42" s="62">
         <v>32421</v>
       </c>
-      <c r="E42" s="61" t="s">
+      <c r="E42" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="F42" s="61" t="s">
+      <c r="F42" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="G42" s="61"/>
-      <c r="H42" s="61"/>
-      <c r="I42" s="61" t="s">
+      <c r="G42" s="62"/>
+      <c r="H42" s="62"/>
+      <c r="I42" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="J42" s="61"/>
-      <c r="K42" s="63"/>
-      <c r="L42" s="61" t="s">
+      <c r="J42" s="62"/>
+      <c r="K42" s="64"/>
+      <c r="L42" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="M42" s="61" t="s">
+      <c r="M42" s="62" t="s">
         <v>57</v>
       </c>
-      <c r="N42" s="61" t="s">
+      <c r="N42" s="62" t="s">
         <v>38</v>
       </c>
-      <c r="O42" s="61" t="s">
+      <c r="O42" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="P42" s="61"/>
-      <c r="Q42" s="61"/>
-      <c r="R42" s="61"/>
-      <c r="S42" s="66"/>
+      <c r="P42" s="62"/>
+      <c r="Q42" s="62"/>
+      <c r="R42" s="62"/>
+      <c r="S42" s="67"/>
     </row>
     <row r="43" s="7" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A43" s="61">
+      <c r="A43" s="62">
         <v>30240007</v>
       </c>
-      <c r="B43" s="62">
+      <c r="B43" s="63">
         <v>102400</v>
       </c>
-      <c r="C43" s="62" t="s">
+      <c r="C43" s="63" t="s">
         <v>32</v>
       </c>
-      <c r="D43" s="61">
+      <c r="D43" s="62">
         <v>32431</v>
       </c>
-      <c r="E43" s="61" t="s">
+      <c r="E43" s="62" t="s">
         <v>58</v>
       </c>
-      <c r="F43" s="61" t="s">
+      <c r="F43" s="62" t="s">
         <v>59</v>
       </c>
-      <c r="G43" s="61">
+      <c r="G43" s="62">
         <v>2024001</v>
       </c>
-      <c r="H43" s="61" t="s">
+      <c r="H43" s="62" t="s">
         <v>60</v>
       </c>
-      <c r="I43" s="61" t="s">
+      <c r="I43" s="62" t="s">
         <v>61</v>
       </c>
-      <c r="J43" s="61"/>
-      <c r="K43" s="63">
+      <c r="J43" s="62"/>
+      <c r="K43" s="64">
         <v>10240091</v>
       </c>
-      <c r="L43" s="61"/>
-      <c r="M43" s="61"/>
-      <c r="N43" s="61"/>
-      <c r="O43" s="61"/>
-      <c r="P43" s="61"/>
-      <c r="Q43" s="61"/>
-      <c r="R43" s="61"/>
-      <c r="S43" s="66"/>
+      <c r="L43" s="62"/>
+      <c r="M43" s="62"/>
+      <c r="N43" s="62"/>
+      <c r="O43" s="62"/>
+      <c r="P43" s="62"/>
+      <c r="Q43" s="62"/>
+      <c r="R43" s="62"/>
+      <c r="S43" s="67"/>
     </row>
     <row r="44" s="7" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A44" s="61">
+      <c r="A44" s="62">
         <v>30240008</v>
       </c>
-      <c r="B44" s="62">
+      <c r="B44" s="63">
         <v>102400</v>
       </c>
-      <c r="C44" s="62" t="s">
+      <c r="C44" s="63" t="s">
         <v>32</v>
       </c>
-      <c r="D44" s="61">
+      <c r="D44" s="62">
         <v>32432</v>
       </c>
-      <c r="E44" s="61" t="s">
+      <c r="E44" s="62" t="s">
         <v>62</v>
       </c>
-      <c r="F44" s="61" t="s">
+      <c r="F44" s="62" t="s">
         <v>53</v>
       </c>
-      <c r="G44" s="61">
+      <c r="G44" s="62">
         <v>2024001</v>
       </c>
-      <c r="H44" s="61" t="s">
+      <c r="H44" s="62" t="s">
         <v>60</v>
       </c>
-      <c r="I44" s="61" t="s">
+      <c r="I44" s="62" t="s">
         <v>63</v>
       </c>
-      <c r="J44" s="61"/>
-      <c r="K44" s="67" t="s">
+      <c r="J44" s="62"/>
+      <c r="K44" s="68" t="s">
         <v>93</v>
       </c>
-      <c r="L44" s="61"/>
-      <c r="M44" s="61"/>
-      <c r="N44" s="61"/>
-      <c r="O44" s="61"/>
-      <c r="P44" s="61"/>
-      <c r="Q44" s="61"/>
-      <c r="R44" s="61"/>
-      <c r="S44" s="66"/>
+      <c r="L44" s="62"/>
+      <c r="M44" s="62"/>
+      <c r="N44" s="62"/>
+      <c r="O44" s="62"/>
+      <c r="P44" s="62"/>
+      <c r="Q44" s="62"/>
+      <c r="R44" s="62"/>
+      <c r="S44" s="67"/>
     </row>
     <row r="45" s="7" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A45" s="61">
+      <c r="A45" s="62">
         <v>30240009</v>
       </c>
-      <c r="B45" s="62">
+      <c r="B45" s="63">
         <v>102400</v>
       </c>
-      <c r="C45" s="62" t="s">
+      <c r="C45" s="63" t="s">
         <v>32</v>
       </c>
-      <c r="D45" s="61">
+      <c r="D45" s="62">
         <v>32433</v>
       </c>
-      <c r="E45" s="61" t="s">
+      <c r="E45" s="62" t="s">
         <v>65</v>
       </c>
-      <c r="F45" s="61" t="s">
+      <c r="F45" s="62" t="s">
         <v>53</v>
       </c>
-      <c r="G45" s="61">
+      <c r="G45" s="62">
         <v>2024001</v>
       </c>
-      <c r="H45" s="61" t="s">
+      <c r="H45" s="62" t="s">
         <v>60</v>
       </c>
-      <c r="I45" s="61" t="s">
+      <c r="I45" s="62" t="s">
         <v>66</v>
       </c>
-      <c r="J45" s="61"/>
-      <c r="K45" s="63" t="s">
+      <c r="J45" s="62"/>
+      <c r="K45" s="64" t="s">
         <v>94</v>
       </c>
-      <c r="L45" s="61"/>
-      <c r="M45" s="61"/>
-      <c r="N45" s="61"/>
-      <c r="O45" s="61"/>
-      <c r="P45" s="61"/>
-      <c r="Q45" s="61"/>
-      <c r="R45" s="61"/>
-      <c r="S45" s="66"/>
+      <c r="L45" s="62"/>
+      <c r="M45" s="62"/>
+      <c r="N45" s="62"/>
+      <c r="O45" s="62"/>
+      <c r="P45" s="62"/>
+      <c r="Q45" s="62"/>
+      <c r="R45" s="62"/>
+      <c r="S45" s="67"/>
     </row>
     <row r="46" s="7" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A46" s="61">
+      <c r="A46" s="62">
         <v>30240010</v>
       </c>
-      <c r="B46" s="62">
+      <c r="B46" s="63">
         <v>102400</v>
       </c>
-      <c r="C46" s="62" t="s">
+      <c r="C46" s="63" t="s">
         <v>32</v>
       </c>
-      <c r="D46" s="61">
+      <c r="D46" s="62">
         <v>32441</v>
       </c>
-      <c r="E46" s="61" t="s">
+      <c r="E46" s="62" t="s">
         <v>68</v>
       </c>
-      <c r="F46" s="61" t="s">
+      <c r="F46" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="G46" s="61"/>
-      <c r="H46" s="61"/>
-      <c r="I46" s="61" t="s">
+      <c r="G46" s="62"/>
+      <c r="H46" s="62"/>
+      <c r="I46" s="62" t="s">
         <v>69</v>
       </c>
-      <c r="J46" s="61"/>
-      <c r="K46" s="67"/>
-      <c r="L46" s="61" t="s">
+      <c r="J46" s="62"/>
+      <c r="K46" s="68"/>
+      <c r="L46" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="M46" s="61" t="s">
+      <c r="M46" s="62" t="s">
         <v>70</v>
       </c>
-      <c r="N46" s="61"/>
-      <c r="O46" s="61"/>
-      <c r="P46" s="61"/>
-      <c r="Q46" s="64" t="s">
+      <c r="N46" s="62"/>
+      <c r="O46" s="62"/>
+      <c r="P46" s="62"/>
+      <c r="Q46" s="65" t="s">
         <v>71</v>
       </c>
-      <c r="R46" s="68" t="s">
+      <c r="R46" s="69" t="s">
         <v>72</v>
       </c>
-      <c r="S46" s="64" t="s">
+      <c r="S46" s="65" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="47" s="7" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A47" s="61">
+      <c r="A47" s="62">
         <v>30240011</v>
       </c>
-      <c r="B47" s="62">
+      <c r="B47" s="63">
         <v>102400</v>
       </c>
-      <c r="C47" s="62" t="s">
+      <c r="C47" s="63" t="s">
         <v>32</v>
       </c>
-      <c r="D47" s="61">
+      <c r="D47" s="62">
         <v>32442</v>
       </c>
-      <c r="E47" s="61" t="s">
+      <c r="E47" s="62" t="s">
         <v>74</v>
       </c>
-      <c r="F47" s="61" t="s">
+      <c r="F47" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="G47" s="61"/>
-      <c r="H47" s="61"/>
-      <c r="I47" s="61" t="s">
+      <c r="G47" s="62"/>
+      <c r="H47" s="62"/>
+      <c r="I47" s="62" t="s">
         <v>75</v>
       </c>
-      <c r="J47" s="61"/>
-      <c r="K47" s="63"/>
-      <c r="L47" s="61" t="s">
+      <c r="J47" s="62"/>
+      <c r="K47" s="64"/>
+      <c r="L47" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="M47" s="61" t="s">
+      <c r="M47" s="62" t="s">
         <v>57</v>
       </c>
-      <c r="N47" s="61"/>
-      <c r="O47" s="61"/>
-      <c r="P47" s="61"/>
-      <c r="Q47" s="61"/>
-      <c r="R47" s="61"/>
-      <c r="S47" s="66"/>
+      <c r="N47" s="62"/>
+      <c r="O47" s="62"/>
+      <c r="P47" s="62"/>
+      <c r="Q47" s="62"/>
+      <c r="R47" s="62"/>
+      <c r="S47" s="67"/>
     </row>
     <row r="48" s="7" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A48" s="61">
+      <c r="A48" s="62">
         <v>30240012</v>
       </c>
-      <c r="B48" s="62">
+      <c r="B48" s="63">
         <v>102400</v>
       </c>
-      <c r="C48" s="62" t="s">
+      <c r="C48" s="63" t="s">
         <v>32</v>
       </c>
-      <c r="D48" s="61">
+      <c r="D48" s="62">
         <v>32443</v>
       </c>
-      <c r="E48" s="61" t="s">
+      <c r="E48" s="62" t="s">
         <v>76</v>
       </c>
-      <c r="F48" s="61" t="s">
+      <c r="F48" s="62" t="s">
         <v>53</v>
       </c>
-      <c r="G48" s="61">
+      <c r="G48" s="62">
         <v>2024001</v>
       </c>
-      <c r="H48" s="61" t="s">
+      <c r="H48" s="62" t="s">
         <v>60</v>
       </c>
-      <c r="I48" s="61" t="s">
+      <c r="I48" s="62" t="s">
         <v>66</v>
       </c>
-      <c r="J48" s="61"/>
-      <c r="K48" s="63" t="s">
+      <c r="J48" s="62"/>
+      <c r="K48" s="64" t="s">
         <v>94</v>
       </c>
-      <c r="L48" s="61"/>
-      <c r="M48" s="61"/>
-      <c r="N48" s="61"/>
-      <c r="O48" s="61"/>
-      <c r="P48" s="61"/>
-      <c r="Q48" s="61"/>
-      <c r="R48" s="61"/>
-      <c r="S48" s="66"/>
+      <c r="L48" s="62"/>
+      <c r="M48" s="62"/>
+      <c r="N48" s="62"/>
+      <c r="O48" s="62"/>
+      <c r="P48" s="62"/>
+      <c r="Q48" s="62"/>
+      <c r="R48" s="62"/>
+      <c r="S48" s="67"/>
     </row>
     <row r="49" s="8" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A49" s="69">
+      <c r="A49" s="70">
         <v>30170001</v>
       </c>
-      <c r="B49" s="70">
+      <c r="B49" s="71">
         <v>101700</v>
       </c>
-      <c r="C49" s="70" t="s">
+      <c r="C49" s="71" t="s">
         <v>95</v>
       </c>
-      <c r="D49" s="69">
+      <c r="D49" s="70">
         <v>301701</v>
       </c>
-      <c r="E49" s="69" t="s">
+      <c r="E49" s="70" t="s">
         <v>96</v>
       </c>
-      <c r="F49" s="69" t="s">
+      <c r="F49" s="70" t="s">
         <v>79</v>
       </c>
-      <c r="G49" s="69">
+      <c r="G49" s="70">
         <v>2017001</v>
       </c>
-      <c r="H49" s="69" t="s">
+      <c r="H49" s="70" t="s">
         <v>60</v>
       </c>
-      <c r="I49" s="69" t="s">
+      <c r="I49" s="70" t="s">
         <v>80</v>
       </c>
-      <c r="J49" s="69"/>
-      <c r="K49" s="71" t="s">
+      <c r="J49" s="70"/>
+      <c r="K49" s="72" t="s">
         <v>97</v>
       </c>
-      <c r="L49" s="69"/>
-      <c r="M49" s="69"/>
-      <c r="N49" s="69"/>
-      <c r="O49" s="69"/>
-      <c r="P49" s="69"/>
-      <c r="Q49" s="69"/>
-      <c r="R49" s="69"/>
-      <c r="S49" s="72"/>
+      <c r="L49" s="70"/>
+      <c r="M49" s="70"/>
+      <c r="N49" s="70"/>
+      <c r="O49" s="70"/>
+      <c r="P49" s="70"/>
+      <c r="Q49" s="70"/>
+      <c r="R49" s="70"/>
+      <c r="S49" s="73"/>
     </row>
     <row r="50" s="8" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A50" s="69">
+      <c r="A50" s="70">
         <v>30170002</v>
       </c>
-      <c r="B50" s="70">
+      <c r="B50" s="71">
         <v>101700</v>
       </c>
-      <c r="C50" s="70" t="s">
+      <c r="C50" s="71" t="s">
         <v>95</v>
       </c>
-      <c r="D50" s="69">
+      <c r="D50" s="70">
         <v>301702</v>
       </c>
-      <c r="E50" s="69" t="s">
+      <c r="E50" s="70" t="s">
         <v>98</v>
       </c>
-      <c r="F50" s="69" t="s">
+      <c r="F50" s="70" t="s">
         <v>83</v>
       </c>
-      <c r="G50" s="69">
+      <c r="G50" s="70">
         <v>2017001</v>
       </c>
-      <c r="H50" s="69" t="s">
+      <c r="H50" s="70" t="s">
         <v>60</v>
       </c>
-      <c r="I50" s="69" t="s">
+      <c r="I50" s="70" t="s">
         <v>80</v>
       </c>
-      <c r="J50" s="69"/>
-      <c r="K50" s="71" t="s">
+      <c r="J50" s="70"/>
+      <c r="K50" s="72" t="s">
         <v>97</v>
       </c>
-      <c r="L50" s="69"/>
-      <c r="M50" s="69"/>
-      <c r="N50" s="69"/>
-      <c r="O50" s="69"/>
-      <c r="P50" s="69"/>
-      <c r="Q50" s="69"/>
-      <c r="R50" s="69"/>
-      <c r="S50" s="72"/>
+      <c r="L50" s="70"/>
+      <c r="M50" s="70"/>
+      <c r="N50" s="70"/>
+      <c r="O50" s="70"/>
+      <c r="P50" s="70"/>
+      <c r="Q50" s="70"/>
+      <c r="R50" s="70"/>
+      <c r="S50" s="73"/>
     </row>
     <row r="51" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A51" s="56">
+      <c r="A51" s="57">
         <v>30220001</v>
       </c>
-      <c r="B51" s="57">
+      <c r="B51" s="58">
         <v>102200</v>
       </c>
-      <c r="C51" s="57" t="s">
+      <c r="C51" s="58" t="s">
         <v>99</v>
       </c>
-      <c r="D51" s="56">
+      <c r="D51" s="57">
         <v>302201</v>
       </c>
-      <c r="E51" s="56" t="s">
+      <c r="E51" s="57" t="s">
         <v>100</v>
       </c>
-      <c r="F51" s="56" t="s">
+      <c r="F51" s="57" t="s">
         <v>101</v>
       </c>
-      <c r="G51" s="56">
+      <c r="G51" s="57">
         <v>2022001</v>
       </c>
-      <c r="H51" s="56" t="s">
+      <c r="H51" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="I51" s="56"/>
-      <c r="J51" s="56"/>
-      <c r="K51" s="73" t="s">
+      <c r="I51" s="57"/>
+      <c r="J51" s="57"/>
+      <c r="K51" s="74" t="s">
         <v>102</v>
       </c>
-      <c r="L51" s="56" t="s">
+      <c r="L51" s="57" t="s">
         <v>103</v>
       </c>
-      <c r="M51" s="56"/>
-      <c r="N51" s="56"/>
-      <c r="O51" s="56"/>
-      <c r="P51" s="56"/>
-      <c r="Q51" s="56"/>
-      <c r="R51" s="56"/>
-      <c r="S51" s="74"/>
+      <c r="M51" s="57"/>
+      <c r="N51" s="57"/>
+      <c r="O51" s="57"/>
+      <c r="P51" s="57"/>
+      <c r="Q51" s="57"/>
+      <c r="R51" s="57"/>
+      <c r="S51" s="75"/>
     </row>
     <row r="52" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A52" s="56">
+      <c r="A52" s="57">
         <v>30220002</v>
       </c>
-      <c r="B52" s="57">
+      <c r="B52" s="58">
         <v>102200</v>
       </c>
-      <c r="C52" s="57" t="s">
+      <c r="C52" s="58" t="s">
         <v>99</v>
       </c>
-      <c r="D52" s="56">
+      <c r="D52" s="57">
         <v>302202</v>
       </c>
-      <c r="E52" s="56" t="s">
+      <c r="E52" s="57" t="s">
         <v>104</v>
       </c>
-      <c r="F52" s="56" t="s">
+      <c r="F52" s="57" t="s">
         <v>101</v>
       </c>
-      <c r="G52" s="56">
+      <c r="G52" s="57">
         <v>2022001</v>
       </c>
-      <c r="H52" s="56" t="s">
+      <c r="H52" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="I52" s="56"/>
-      <c r="J52" s="56"/>
-      <c r="K52" s="73" t="s">
+      <c r="I52" s="57"/>
+      <c r="J52" s="57"/>
+      <c r="K52" s="74" t="s">
         <v>105</v>
       </c>
-      <c r="L52" s="56" t="s">
+      <c r="L52" s="57" t="s">
         <v>103</v>
       </c>
-      <c r="M52" s="56"/>
-      <c r="N52" s="56"/>
-      <c r="O52" s="56"/>
-      <c r="P52" s="56"/>
-      <c r="Q52" s="56"/>
-      <c r="R52" s="56"/>
-      <c r="S52" s="74"/>
+      <c r="M52" s="57"/>
+      <c r="N52" s="57"/>
+      <c r="O52" s="57"/>
+      <c r="P52" s="57"/>
+      <c r="Q52" s="57"/>
+      <c r="R52" s="57"/>
+      <c r="S52" s="75"/>
     </row>
     <row r="53" s="9" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A53" s="75">
+      <c r="A53" s="76">
         <v>30210001</v>
       </c>
-      <c r="B53" s="76">
+      <c r="B53" s="77">
         <v>102100</v>
       </c>
-      <c r="C53" s="76" t="s">
+      <c r="C53" s="77" t="s">
         <v>106</v>
       </c>
-      <c r="D53" s="75">
+      <c r="D53" s="76">
         <v>302101</v>
       </c>
-      <c r="E53" s="75" t="s">
+      <c r="E53" s="76" t="s">
         <v>107</v>
       </c>
-      <c r="F53" s="75" t="s">
+      <c r="F53" s="76" t="s">
         <v>108</v>
       </c>
-      <c r="G53" s="75">
+      <c r="G53" s="76">
         <v>2021001</v>
       </c>
-      <c r="H53" s="75" t="s">
+      <c r="H53" s="76" t="s">
         <v>60</v>
       </c>
-      <c r="I53" s="75" t="s">
+      <c r="I53" s="76" t="s">
         <v>80</v>
       </c>
-      <c r="J53" s="75"/>
-      <c r="K53" s="77" t="s">
+      <c r="J53" s="76"/>
+      <c r="K53" s="78" t="s">
         <v>109</v>
       </c>
-      <c r="L53" s="75" t="s">
+      <c r="L53" s="76" t="s">
         <v>110</v>
       </c>
-      <c r="M53" s="75"/>
-      <c r="N53" s="75"/>
-      <c r="O53" s="75"/>
-      <c r="P53" s="75"/>
-      <c r="Q53" s="75"/>
-      <c r="R53" s="75"/>
-      <c r="S53" s="78"/>
+      <c r="M53" s="76"/>
+      <c r="N53" s="76"/>
+      <c r="O53" s="76"/>
+      <c r="P53" s="76"/>
+      <c r="Q53" s="76"/>
+      <c r="R53" s="76"/>
+      <c r="S53" s="79"/>
     </row>
     <row r="54" s="9" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A54" s="75">
+      <c r="A54" s="76">
         <v>30210002</v>
       </c>
-      <c r="B54" s="76">
+      <c r="B54" s="77">
         <v>102100</v>
       </c>
-      <c r="C54" s="76" t="s">
+      <c r="C54" s="77" t="s">
         <v>106</v>
       </c>
-      <c r="D54" s="75">
+      <c r="D54" s="76">
         <v>302102</v>
       </c>
-      <c r="E54" s="75" t="s">
+      <c r="E54" s="76" t="s">
         <v>111</v>
       </c>
-      <c r="F54" s="75" t="s">
+      <c r="F54" s="76" t="s">
         <v>34</v>
       </c>
-      <c r="G54" s="75"/>
-      <c r="H54" s="75"/>
-      <c r="I54" s="75" t="s">
+      <c r="G54" s="76"/>
+      <c r="H54" s="76"/>
+      <c r="I54" s="76" t="s">
         <v>112</v>
       </c>
-      <c r="J54" s="75"/>
-      <c r="K54" s="77"/>
-      <c r="L54" s="75"/>
-      <c r="M54" s="75" t="s">
+      <c r="J54" s="76"/>
+      <c r="K54" s="78"/>
+      <c r="L54" s="76"/>
+      <c r="M54" s="76" t="s">
         <v>37</v>
       </c>
-      <c r="N54" s="75" t="s">
+      <c r="N54" s="76" t="s">
         <v>113</v>
       </c>
-      <c r="O54" s="75"/>
-      <c r="P54" s="75"/>
-      <c r="Q54" s="75" t="s">
+      <c r="O54" s="76"/>
+      <c r="P54" s="76"/>
+      <c r="Q54" s="76" t="s">
         <v>114</v>
       </c>
-      <c r="R54" s="75"/>
-      <c r="S54" s="78"/>
+      <c r="R54" s="76"/>
+      <c r="S54" s="79"/>
     </row>
     <row r="55" s="10" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A55" s="79">
+      <c r="A55" s="80">
         <v>30180001</v>
       </c>
-      <c r="B55" s="80">
+      <c r="B55" s="81">
         <v>101800</v>
       </c>
-      <c r="C55" s="80" t="s">
+      <c r="C55" s="81" t="s">
         <v>115</v>
       </c>
-      <c r="D55" s="79">
+      <c r="D55" s="80">
         <v>301801</v>
       </c>
-      <c r="E55" s="79" t="s">
+      <c r="E55" s="80" t="s">
         <v>80</v>
       </c>
-      <c r="F55" s="79" t="s">
+      <c r="F55" s="80" t="s">
         <v>116</v>
       </c>
-      <c r="G55" s="79">
+      <c r="G55" s="80">
         <v>2018002</v>
       </c>
-      <c r="H55" s="79" t="s">
+      <c r="H55" s="80" t="s">
         <v>60</v>
       </c>
-      <c r="I55" s="79" t="s">
+      <c r="I55" s="80" t="s">
         <v>80</v>
       </c>
-      <c r="J55" s="79"/>
-      <c r="K55" s="81">
+      <c r="J55" s="80"/>
+      <c r="K55" s="82">
         <v>10180041</v>
       </c>
-      <c r="L55" s="79"/>
-      <c r="M55" s="79"/>
-      <c r="N55" s="79"/>
-      <c r="O55" s="79"/>
-      <c r="P55" s="79"/>
-      <c r="Q55" s="79"/>
-      <c r="R55" s="79"/>
-      <c r="S55" s="82"/>
+      <c r="L55" s="80"/>
+      <c r="M55" s="80"/>
+      <c r="N55" s="80"/>
+      <c r="O55" s="80"/>
+      <c r="P55" s="80"/>
+      <c r="Q55" s="80"/>
+      <c r="R55" s="80"/>
+      <c r="S55" s="83"/>
     </row>
     <row r="56" s="11" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A56" s="83">
+      <c r="A56" s="84">
         <v>30250001</v>
       </c>
-      <c r="B56" s="84">
+      <c r="B56" s="85">
         <v>102500</v>
       </c>
-      <c r="C56" s="84" t="s">
+      <c r="C56" s="85" t="s">
         <v>117</v>
       </c>
-      <c r="D56" s="83">
+      <c r="D56" s="84">
         <v>302501</v>
       </c>
-      <c r="E56" s="83" t="s">
+      <c r="E56" s="84" t="s">
         <v>107</v>
       </c>
-      <c r="F56" s="83" t="s">
+      <c r="F56" s="84" t="s">
         <v>108</v>
       </c>
-      <c r="G56" s="83">
+      <c r="G56" s="84">
         <v>2025001</v>
       </c>
-      <c r="H56" s="83" t="s">
+      <c r="H56" s="84" t="s">
         <v>60</v>
       </c>
-      <c r="I56" s="83" t="s">
+      <c r="I56" s="84" t="s">
         <v>80</v>
       </c>
-      <c r="J56" s="83"/>
-      <c r="K56" s="85" t="s">
+      <c r="J56" s="84"/>
+      <c r="K56" s="86" t="s">
         <v>118</v>
       </c>
-      <c r="L56" s="83" t="s">
+      <c r="L56" s="84" t="s">
         <v>119</v>
       </c>
-      <c r="M56" s="83"/>
-      <c r="N56" s="83"/>
-      <c r="O56" s="83"/>
-      <c r="P56" s="83"/>
-      <c r="Q56" s="83"/>
-      <c r="R56" s="83"/>
-      <c r="S56" s="86"/>
+      <c r="M56" s="84"/>
+      <c r="N56" s="84"/>
+      <c r="O56" s="84"/>
+      <c r="P56" s="84"/>
+      <c r="Q56" s="84"/>
+      <c r="R56" s="84"/>
+      <c r="S56" s="87"/>
     </row>
     <row r="57" s="11" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A57" s="83">
+      <c r="A57" s="84">
         <v>30250002</v>
       </c>
-      <c r="B57" s="84">
+      <c r="B57" s="85">
         <v>102500</v>
       </c>
-      <c r="C57" s="84" t="s">
+      <c r="C57" s="85" t="s">
         <v>117</v>
       </c>
-      <c r="D57" s="83">
+      <c r="D57" s="84">
         <v>302502</v>
       </c>
-      <c r="E57" s="83" t="s">
+      <c r="E57" s="84" t="s">
         <v>120</v>
       </c>
-      <c r="F57" s="83" t="s">
+      <c r="F57" s="84" t="s">
         <v>121</v>
       </c>
-      <c r="G57" s="83">
+      <c r="G57" s="84">
         <v>2025001</v>
       </c>
-      <c r="H57" s="83" t="s">
+      <c r="H57" s="84" t="s">
         <v>60</v>
       </c>
-      <c r="I57" s="83" t="s">
+      <c r="I57" s="84" t="s">
         <v>80</v>
       </c>
-      <c r="J57" s="83"/>
-      <c r="K57" s="85" t="s">
+      <c r="J57" s="84"/>
+      <c r="K57" s="86" t="s">
         <v>118</v>
       </c>
-      <c r="L57" s="83" t="s">
+      <c r="L57" s="84" t="s">
         <v>119</v>
       </c>
-      <c r="M57" s="83"/>
-      <c r="N57" s="83"/>
-      <c r="O57" s="83"/>
-      <c r="P57" s="83"/>
-      <c r="Q57" s="83"/>
-      <c r="R57" s="83"/>
-      <c r="S57" s="86"/>
+      <c r="M57" s="84"/>
+      <c r="N57" s="84"/>
+      <c r="O57" s="84"/>
+      <c r="P57" s="84"/>
+      <c r="Q57" s="84"/>
+      <c r="R57" s="84"/>
+      <c r="S57" s="87"/>
     </row>
     <row r="58" s="11" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A58" s="83">
+      <c r="A58" s="84">
         <v>30250003</v>
       </c>
-      <c r="B58" s="84">
+      <c r="B58" s="85">
         <v>102500</v>
       </c>
-      <c r="C58" s="84" t="s">
+      <c r="C58" s="85" t="s">
         <v>117</v>
       </c>
-      <c r="D58" s="83">
+      <c r="D58" s="84">
         <v>302503</v>
       </c>
-      <c r="E58" s="83" t="s">
+      <c r="E58" s="84" t="s">
         <v>122</v>
       </c>
-      <c r="F58" s="83" t="s">
+      <c r="F58" s="84" t="s">
         <v>123</v>
       </c>
-      <c r="G58" s="83">
+      <c r="G58" s="84">
         <v>2025001</v>
       </c>
-      <c r="H58" s="83" t="s">
+      <c r="H58" s="84" t="s">
         <v>60</v>
       </c>
-      <c r="I58" s="83" t="s">
+      <c r="I58" s="84" t="s">
         <v>80</v>
       </c>
-      <c r="J58" s="83"/>
-      <c r="K58" s="85" t="s">
+      <c r="J58" s="84"/>
+      <c r="K58" s="86" t="s">
         <v>118</v>
       </c>
-      <c r="L58" s="83" t="s">
+      <c r="L58" s="84" t="s">
         <v>119</v>
       </c>
-      <c r="M58" s="83"/>
-      <c r="N58" s="83"/>
-      <c r="O58" s="83"/>
-      <c r="P58" s="83"/>
-      <c r="Q58" s="83"/>
-      <c r="R58" s="83"/>
-      <c r="S58" s="86"/>
+      <c r="M58" s="84"/>
+      <c r="N58" s="84"/>
+      <c r="O58" s="84"/>
+      <c r="P58" s="84"/>
+      <c r="Q58" s="84"/>
+      <c r="R58" s="84"/>
+      <c r="S58" s="87"/>
     </row>
     <row r="59" s="12" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A59" s="87">
+      <c r="A59" s="88">
         <v>30230001</v>
       </c>
-      <c r="B59" s="88">
+      <c r="B59" s="89">
         <v>102300</v>
       </c>
-      <c r="C59" s="88" t="s">
+      <c r="C59" s="89" t="s">
         <v>124</v>
       </c>
-      <c r="D59" s="87">
+      <c r="D59" s="88">
         <v>302301</v>
       </c>
-      <c r="E59" s="87" t="s">
+      <c r="E59" s="88" t="s">
         <v>107</v>
       </c>
-      <c r="F59" s="87" t="s">
+      <c r="F59" s="88" t="s">
         <v>108</v>
       </c>
-      <c r="G59" s="87">
+      <c r="G59" s="88">
         <v>2023001</v>
       </c>
-      <c r="H59" s="87" t="s">
+      <c r="H59" s="88" t="s">
         <v>60</v>
       </c>
-      <c r="I59" s="87" t="s">
+      <c r="I59" s="88" t="s">
         <v>80</v>
       </c>
-      <c r="J59" s="87"/>
-      <c r="K59" s="89" t="s">
+      <c r="J59" s="88"/>
+      <c r="K59" s="90" t="s">
         <v>125</v>
       </c>
-      <c r="L59" s="87" t="s">
+      <c r="L59" s="88" t="s">
         <v>126</v>
       </c>
-      <c r="M59" s="87"/>
-      <c r="N59" s="87"/>
-      <c r="O59" s="87"/>
-      <c r="P59" s="87"/>
-      <c r="Q59" s="87"/>
-      <c r="R59" s="87"/>
-      <c r="S59" s="90"/>
+      <c r="M59" s="88"/>
+      <c r="N59" s="88"/>
+      <c r="O59" s="88"/>
+      <c r="P59" s="88"/>
+      <c r="Q59" s="88"/>
+      <c r="R59" s="88"/>
+      <c r="S59" s="91"/>
     </row>
     <row r="60" s="12" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A60" s="87">
+      <c r="A60" s="88">
         <v>30230002</v>
       </c>
-      <c r="B60" s="88">
+      <c r="B60" s="89">
         <v>102300</v>
       </c>
-      <c r="C60" s="88" t="s">
+      <c r="C60" s="89" t="s">
         <v>124</v>
       </c>
-      <c r="D60" s="87">
+      <c r="D60" s="88">
         <v>302302</v>
       </c>
-      <c r="E60" s="87" t="s">
+      <c r="E60" s="88" t="s">
         <v>127</v>
       </c>
-      <c r="F60" s="87" t="s">
+      <c r="F60" s="88" t="s">
         <v>79</v>
       </c>
-      <c r="G60" s="87">
+      <c r="G60" s="88">
         <v>2023001</v>
       </c>
-      <c r="H60" s="87" t="s">
+      <c r="H60" s="88" t="s">
         <v>60</v>
       </c>
-      <c r="I60" s="87" t="s">
+      <c r="I60" s="88" t="s">
         <v>80</v>
       </c>
-      <c r="J60" s="87"/>
-      <c r="K60" s="89" t="s">
+      <c r="J60" s="88"/>
+      <c r="K60" s="90" t="s">
         <v>125</v>
       </c>
-      <c r="L60" s="87" t="s">
+      <c r="L60" s="88" t="s">
         <v>126</v>
       </c>
-      <c r="M60" s="87"/>
-      <c r="N60" s="87"/>
-      <c r="O60" s="87"/>
-      <c r="P60" s="87"/>
-      <c r="Q60" s="87"/>
-      <c r="R60" s="87"/>
-      <c r="S60" s="90"/>
+      <c r="M60" s="88"/>
+      <c r="N60" s="88"/>
+      <c r="O60" s="88"/>
+      <c r="P60" s="88"/>
+      <c r="Q60" s="88"/>
+      <c r="R60" s="88"/>
+      <c r="S60" s="91"/>
     </row>
     <row r="61" s="12" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A61" s="87">
+      <c r="A61" s="88">
         <v>30230003</v>
       </c>
-      <c r="B61" s="88">
+      <c r="B61" s="89">
         <v>102300</v>
       </c>
-      <c r="C61" s="88" t="s">
+      <c r="C61" s="89" t="s">
         <v>124</v>
       </c>
-      <c r="D61" s="87">
+      <c r="D61" s="88">
         <v>302303</v>
       </c>
-      <c r="E61" s="87" t="s">
+      <c r="E61" s="88" t="s">
         <v>128</v>
       </c>
-      <c r="F61" s="87" t="s">
+      <c r="F61" s="88" t="s">
         <v>83</v>
       </c>
-      <c r="G61" s="87">
+      <c r="G61" s="88">
         <v>2023001</v>
       </c>
-      <c r="H61" s="87" t="s">
+      <c r="H61" s="88" t="s">
         <v>60</v>
       </c>
-      <c r="I61" s="87" t="s">
+      <c r="I61" s="88" t="s">
         <v>80</v>
       </c>
-      <c r="J61" s="87"/>
-      <c r="K61" s="89" t="s">
+      <c r="J61" s="88"/>
+      <c r="K61" s="90" t="s">
         <v>125</v>
       </c>
-      <c r="L61" s="87" t="s">
+      <c r="L61" s="88" t="s">
         <v>126</v>
       </c>
-      <c r="M61" s="87"/>
-      <c r="N61" s="87"/>
-      <c r="O61" s="87"/>
-      <c r="P61" s="87"/>
-      <c r="Q61" s="87"/>
-      <c r="R61" s="87"/>
-      <c r="S61" s="90"/>
+      <c r="M61" s="88"/>
+      <c r="N61" s="88"/>
+      <c r="O61" s="88"/>
+      <c r="P61" s="88"/>
+      <c r="Q61" s="88"/>
+      <c r="R61" s="88"/>
+      <c r="S61" s="91"/>
     </row>
     <row r="62" s="13" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A62" s="91">
+      <c r="A62" s="92">
         <v>30350001</v>
       </c>
-      <c r="B62" s="92">
+      <c r="B62" s="93">
         <v>103500</v>
       </c>
-      <c r="C62" s="92" t="s">
+      <c r="C62" s="93" t="s">
         <v>129</v>
       </c>
-      <c r="D62" s="91">
+      <c r="D62" s="92">
         <v>303501</v>
       </c>
-      <c r="E62" s="91" t="s">
+      <c r="E62" s="92" t="s">
         <v>130</v>
       </c>
-      <c r="F62" s="91" t="s">
+      <c r="F62" s="92" t="s">
         <v>59</v>
       </c>
-      <c r="G62" s="91">
+      <c r="G62" s="92">
         <v>2035002</v>
       </c>
-      <c r="H62" s="91" t="s">
+      <c r="H62" s="92" t="s">
         <v>60</v>
       </c>
-      <c r="I62" s="91" t="s">
+      <c r="I62" s="92" t="s">
         <v>131</v>
       </c>
-      <c r="J62" s="91"/>
-      <c r="K62" s="93" t="s">
+      <c r="J62" s="92"/>
+      <c r="K62" s="94" t="s">
         <v>132</v>
       </c>
-      <c r="L62" s="91" t="s">
+      <c r="L62" s="92" t="s">
         <v>133</v>
       </c>
-      <c r="M62" s="91"/>
-      <c r="N62" s="91"/>
-      <c r="O62" s="91"/>
-      <c r="P62" s="91"/>
-      <c r="Q62" s="91"/>
-      <c r="R62" s="91"/>
-      <c r="S62" s="94"/>
+      <c r="M62" s="92"/>
+      <c r="N62" s="92"/>
+      <c r="O62" s="92"/>
+      <c r="P62" s="92"/>
+      <c r="Q62" s="92"/>
+      <c r="R62" s="92"/>
+      <c r="S62" s="95"/>
     </row>
     <row r="63" s="13" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A63" s="91">
+      <c r="A63" s="92">
         <v>30350002</v>
       </c>
-      <c r="B63" s="92">
+      <c r="B63" s="93">
         <v>103500</v>
       </c>
-      <c r="C63" s="92" t="s">
+      <c r="C63" s="93" t="s">
         <v>129</v>
       </c>
-      <c r="D63" s="91">
+      <c r="D63" s="92">
         <v>303502</v>
       </c>
-      <c r="E63" s="91" t="s">
+      <c r="E63" s="92" t="s">
         <v>134</v>
       </c>
-      <c r="F63" s="91" t="s">
+      <c r="F63" s="92" t="s">
         <v>34</v>
       </c>
-      <c r="G63" s="91"/>
-      <c r="H63" s="91"/>
-      <c r="I63" s="91"/>
-      <c r="J63" s="91"/>
-      <c r="K63" s="93"/>
-      <c r="L63" s="91"/>
-      <c r="M63" s="91" t="s">
+      <c r="G63" s="92"/>
+      <c r="H63" s="92"/>
+      <c r="I63" s="92"/>
+      <c r="J63" s="92"/>
+      <c r="K63" s="94"/>
+      <c r="L63" s="92"/>
+      <c r="M63" s="92" t="s">
         <v>53</v>
       </c>
-      <c r="N63" s="91"/>
-      <c r="O63" s="91" t="s">
+      <c r="N63" s="92"/>
+      <c r="O63" s="92" t="s">
         <v>135</v>
       </c>
-      <c r="P63" s="91"/>
-      <c r="Q63" s="91"/>
-      <c r="R63" s="91"/>
-      <c r="S63" s="94"/>
+      <c r="P63" s="92"/>
+      <c r="Q63" s="92"/>
+      <c r="R63" s="92"/>
+      <c r="S63" s="95"/>
     </row>
     <row r="64" s="13" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A64" s="91">
+      <c r="A64" s="92">
         <v>30350101</v>
       </c>
-      <c r="B64" s="92">
+      <c r="B64" s="93">
         <v>103501</v>
       </c>
-      <c r="C64" s="92" t="s">
+      <c r="C64" s="93" t="s">
         <v>136</v>
       </c>
-      <c r="D64" s="91">
+      <c r="D64" s="92">
         <v>303503</v>
       </c>
-      <c r="E64" s="91" t="s">
+      <c r="E64" s="92" t="s">
         <v>130</v>
       </c>
-      <c r="F64" s="91" t="s">
+      <c r="F64" s="92" t="s">
         <v>59</v>
       </c>
-      <c r="G64" s="91">
+      <c r="G64" s="92">
         <v>2035012</v>
       </c>
-      <c r="H64" s="91" t="s">
+      <c r="H64" s="92" t="s">
         <v>60</v>
       </c>
-      <c r="I64" s="91" t="s">
+      <c r="I64" s="92" t="s">
         <v>131</v>
       </c>
-      <c r="J64" s="91"/>
-      <c r="K64" s="93" t="s">
+      <c r="J64" s="92"/>
+      <c r="K64" s="94" t="s">
         <v>137</v>
       </c>
-      <c r="L64" s="91" t="s">
+      <c r="L64" s="92" t="s">
         <v>133</v>
       </c>
-      <c r="M64" s="91"/>
-      <c r="N64" s="91"/>
-      <c r="O64" s="91"/>
-      <c r="P64" s="91"/>
-      <c r="Q64" s="91"/>
-      <c r="R64" s="91"/>
-      <c r="S64" s="94"/>
+      <c r="M64" s="92"/>
+      <c r="N64" s="92"/>
+      <c r="O64" s="92"/>
+      <c r="P64" s="92"/>
+      <c r="Q64" s="92"/>
+      <c r="R64" s="92"/>
+      <c r="S64" s="95"/>
     </row>
     <row r="65" s="13" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A65" s="91">
+      <c r="A65" s="92">
         <v>30350102</v>
       </c>
-      <c r="B65" s="92">
+      <c r="B65" s="93">
         <v>103501</v>
       </c>
-      <c r="C65" s="92" t="s">
+      <c r="C65" s="93" t="s">
         <v>136</v>
       </c>
-      <c r="D65" s="91">
+      <c r="D65" s="92">
         <v>303504</v>
       </c>
-      <c r="E65" s="91" t="s">
+      <c r="E65" s="92" t="s">
         <v>134</v>
       </c>
-      <c r="F65" s="91" t="s">
+      <c r="F65" s="92" t="s">
         <v>34</v>
       </c>
-      <c r="G65" s="91"/>
-      <c r="H65" s="91"/>
-      <c r="I65" s="91"/>
-      <c r="J65" s="91"/>
-      <c r="K65" s="93"/>
-      <c r="L65" s="91"/>
-      <c r="M65" s="91" t="s">
+      <c r="G65" s="92"/>
+      <c r="H65" s="92"/>
+      <c r="I65" s="92"/>
+      <c r="J65" s="92"/>
+      <c r="K65" s="94"/>
+      <c r="L65" s="92"/>
+      <c r="M65" s="92" t="s">
         <v>53</v>
       </c>
-      <c r="N65" s="91"/>
-      <c r="O65" s="91" t="s">
+      <c r="N65" s="92"/>
+      <c r="O65" s="92" t="s">
         <v>135</v>
       </c>
-      <c r="P65" s="91"/>
-      <c r="Q65" s="91"/>
-      <c r="R65" s="91"/>
-      <c r="S65" s="94"/>
+      <c r="P65" s="92"/>
+      <c r="Q65" s="92"/>
+      <c r="R65" s="92"/>
+      <c r="S65" s="95"/>
+    </row>
+    <row r="66" s="14" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A66" s="96">
+        <v>30360001</v>
+      </c>
+      <c r="B66" s="97">
+        <v>103600</v>
+      </c>
+      <c r="C66" s="97" t="s">
+        <v>138</v>
+      </c>
+      <c r="D66" s="96">
+        <v>303601</v>
+      </c>
+      <c r="E66" s="96" t="s">
+        <v>139</v>
+      </c>
+      <c r="F66" s="96" t="s">
+        <v>140</v>
+      </c>
+      <c r="G66" s="96">
+        <v>2036002</v>
+      </c>
+      <c r="H66" s="96" t="s">
+        <v>60</v>
+      </c>
+      <c r="I66" s="96" t="s">
+        <v>139</v>
+      </c>
+      <c r="J66" s="96"/>
+      <c r="K66" s="98">
+        <v>10360005</v>
+      </c>
+      <c r="L66" s="96" t="s">
+        <v>141</v>
+      </c>
+      <c r="M66" s="96"/>
+      <c r="N66" s="96"/>
+      <c r="O66" s="96"/>
+      <c r="P66" s="96"/>
+      <c r="Q66" s="96"/>
+      <c r="R66" s="96"/>
+      <c r="S66" s="99"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2">
@@ -4909,10 +4973,10 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -4920,7 +4984,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -4928,7 +4992,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:8">
@@ -4936,16 +5000,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
+        <v>146</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>138</v>
-      </c>
       <c r="G4" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:8">
@@ -4953,16 +5017,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:8">
@@ -4970,16 +5034,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:8">
@@ -4987,16 +5051,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="F7" s="1">
         <v>2</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:8">
@@ -5004,16 +5068,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="F8" s="1">
         <v>3</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:8">
@@ -5021,16 +5085,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="F9" s="1">
         <v>4</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:8">
@@ -5038,16 +5102,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="F10" s="1">
         <v>5</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:8">
@@ -5055,16 +5119,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="F11" s="1">
         <v>6</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:8">
@@ -5072,16 +5136,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="F12" s="1">
         <v>7</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:8">
@@ -5089,16 +5153,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="F13" s="1">
         <v>8</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:8">
@@ -5106,16 +5170,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="F14" s="1">
         <v>9</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:8">
@@ -5123,16 +5187,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="F15" s="1">
         <v>10</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:8">
@@ -5140,16 +5204,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="F16" s="1">
         <v>11</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:8">
@@ -5157,16 +5221,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="F17" s="1">
         <v>12</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:8">
@@ -5174,16 +5238,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="F18" s="1">
         <v>13</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:8">
@@ -5191,16 +5255,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="F19" s="1">
         <v>14</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:8">
@@ -5208,16 +5272,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="F20" s="1">
         <v>15</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:8">
@@ -5225,16 +5289,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="F21" s="1">
         <v>16</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:8">
@@ -5242,16 +5306,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="F22" s="1">
         <v>17</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:8">
@@ -5259,16 +5323,16 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="F23" s="1">
         <v>18</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:8">
@@ -5276,16 +5340,16 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F24" s="1">
         <v>19</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -5293,7 +5357,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -5301,7 +5365,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -5309,7 +5373,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -5317,7 +5381,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -5325,7 +5389,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -5333,7 +5397,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -5341,7 +5405,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -5349,7 +5413,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -5357,7 +5421,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -5365,7 +5429,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -5373,7 +5437,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -5381,7 +5445,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -5389,7 +5453,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -5397,7 +5461,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -5405,7 +5469,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -5413,7 +5477,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -5421,7 +5485,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -5429,7 +5493,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -5437,7 +5501,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -5445,7 +5509,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -5453,7 +5517,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -5461,7 +5525,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -5469,7 +5533,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialAuxiliary.xlsx
+++ b/slots/resources/sample/SpecialAuxiliary.xlsx
@@ -268,7 +268,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="230">
   <si>
     <t>小游戏模式ID</t>
   </si>
@@ -688,9 +688,6 @@
   </si>
   <si>
     <t>福鼠模式</t>
-  </si>
-  <si>
-    <t>99999_1</t>
   </si>
   <si>
     <t>第二轴改出三个wild符号</t>
@@ -1152,6 +1149,17 @@
     <font>
       <b/>
       <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1159,18 +1167,13 @@
     <font>
       <b/>
       <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1182,13 +1185,7 @@
     </font>
     <font>
       <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
+      <sz val="18"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -4887,7 +4884,7 @@
         <v>139</v>
       </c>
       <c r="F66" s="96" t="s">
-        <v>140</v>
+        <v>108</v>
       </c>
       <c r="G66" s="96">
         <v>2036002</v>
@@ -4903,7 +4900,7 @@
         <v>10360005</v>
       </c>
       <c r="L66" s="96" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="M66" s="96"/>
       <c r="N66" s="96"/>
@@ -4973,10 +4970,10 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B1" t="s">
         <v>142</v>
-      </c>
-      <c r="B1" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -4984,7 +4981,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -4992,7 +4989,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:8">
@@ -5000,16 +4997,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
+        <v>145</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>146</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:8">
@@ -5017,16 +5014,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>149</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:8">
@@ -5034,16 +5031,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
       </c>
       <c r="G6" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:8">
@@ -5051,16 +5048,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F7" s="1">
         <v>2</v>
       </c>
       <c r="G7" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="H7" s="1" t="s">
         <v>155</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:8">
@@ -5068,16 +5065,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F8" s="1">
         <v>3</v>
       </c>
       <c r="G8" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="H8" s="1" t="s">
         <v>158</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:8">
@@ -5085,16 +5082,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F9" s="1">
         <v>4</v>
       </c>
       <c r="G9" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="H9" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:8">
@@ -5102,16 +5099,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F10" s="1">
         <v>5</v>
       </c>
       <c r="G10" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="H10" s="1" t="s">
         <v>164</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:8">
@@ -5119,16 +5116,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F11" s="1">
         <v>6</v>
       </c>
       <c r="G11" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="H11" s="1" t="s">
         <v>167</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:8">
@@ -5136,16 +5133,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F12" s="1">
         <v>7</v>
       </c>
       <c r="G12" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="H12" s="1" t="s">
         <v>170</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:8">
@@ -5153,16 +5150,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F13" s="1">
         <v>8</v>
       </c>
       <c r="G13" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="H13" s="1" t="s">
         <v>173</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:8">
@@ -5170,16 +5167,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F14" s="1">
         <v>9</v>
       </c>
       <c r="G14" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="H14" s="1" t="s">
         <v>176</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:8">
@@ -5187,16 +5184,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F15" s="1">
         <v>10</v>
       </c>
       <c r="G15" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="H15" s="1" t="s">
         <v>179</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:8">
@@ -5204,16 +5201,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F16" s="1">
         <v>11</v>
       </c>
       <c r="G16" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="H16" s="1" t="s">
         <v>182</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:8">
@@ -5221,16 +5218,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F17" s="1">
         <v>12</v>
       </c>
       <c r="G17" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="H17" s="1" t="s">
         <v>185</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:8">
@@ -5238,16 +5235,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F18" s="1">
         <v>13</v>
       </c>
       <c r="G18" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="H18" s="1" t="s">
         <v>188</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:8">
@@ -5255,16 +5252,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F19" s="1">
         <v>14</v>
       </c>
       <c r="G19" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="H19" s="1" t="s">
         <v>191</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:8">
@@ -5272,16 +5269,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F20" s="1">
         <v>15</v>
       </c>
       <c r="G20" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="H20" s="1" t="s">
         <v>194</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:8">
@@ -5289,16 +5286,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F21" s="1">
         <v>16</v>
       </c>
       <c r="G21" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="H21" s="1" t="s">
         <v>197</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:8">
@@ -5306,16 +5303,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F22" s="1">
         <v>17</v>
       </c>
       <c r="G22" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="H22" s="1" t="s">
         <v>200</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:8">
@@ -5323,16 +5320,16 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F23" s="1">
         <v>18</v>
       </c>
       <c r="G23" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="H23" s="1" t="s">
         <v>203</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:8">
@@ -5340,16 +5337,16 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F24" s="1">
         <v>19</v>
       </c>
       <c r="G24" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="H24" s="1" t="s">
         <v>206</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -5357,7 +5354,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -5365,7 +5362,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -5373,7 +5370,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -5381,7 +5378,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -5389,7 +5386,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -5397,7 +5394,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -5405,7 +5402,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -5413,7 +5410,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -5421,7 +5418,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -5429,7 +5426,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -5437,7 +5434,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -5445,7 +5442,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -5453,7 +5450,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -5461,7 +5458,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -5469,7 +5466,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -5477,7 +5474,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -5485,7 +5482,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -5493,7 +5490,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -5501,7 +5498,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -5509,7 +5506,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -5517,7 +5514,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -5525,7 +5522,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -5533,7 +5530,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialAuxiliary.xlsx
+++ b/slots/resources/sample/SpecialAuxiliary.xlsx
@@ -268,7 +268,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="236">
   <si>
     <t>小游戏模式ID</t>
   </si>
@@ -691,6 +691,24 @@
   </si>
   <si>
     <t>第二轴改出三个wild符号</t>
+  </si>
+  <si>
+    <t>王牌dj</t>
+  </si>
+  <si>
+    <t>10280001|10280005|10280006|10280007|10280008</t>
+  </si>
+  <si>
+    <t>概率改出wild、概率改出scatter符号、概率改出占据2、3、4个格子符号</t>
+  </si>
+  <si>
+    <t>宙斯vs哈迪斯</t>
+  </si>
+  <si>
+    <t>免费游戏-宙斯玩法</t>
+  </si>
+  <si>
+    <t>免费游戏-哈迪斯玩法</t>
   </si>
   <si>
     <t>typeID</t>
@@ -1147,6 +1165,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
@@ -1154,6 +1184,13 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1171,27 +1208,8 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="49">
+  <fills count="51">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1261,6 +1279,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCFE09A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE42EF0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1611,7 +1641,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1635,16 +1665,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1653,92 +1683,92 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="110">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1756,6 +1786,8 @@
     <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1792,45 +1824,45 @@
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="176" fontId="1" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="176" fontId="1" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="1" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1941,6 +1973,22 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="52">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2006,6 +2054,14 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="00ECB112"/>
+      <color rgb="00B0D08D"/>
+      <color rgb="00CFE09A"/>
+      <color rgb="00E42EF0"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2272,7 +2328,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S66"/>
+  <dimension ref="A1:S72"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14.125" customWidth="1"/>
@@ -2284,7 +2340,7 @@
     <col min="8" max="8" width="16.25" customWidth="1"/>
     <col min="9" max="9" width="29.375" customWidth="1"/>
     <col min="10" max="10" width="42.5" customWidth="1"/>
-    <col min="11" max="11" width="41.25" style="15" customWidth="1"/>
+    <col min="11" max="11" width="41.25" style="17" customWidth="1"/>
     <col min="12" max="12" width="36.0333333333333" style="3" customWidth="1"/>
     <col min="13" max="13" width="34.4083333333333" style="3" customWidth="1"/>
     <col min="14" max="14" width="7.93333333333333" style="3" customWidth="1"/>
@@ -2292,7 +2348,7 @@
     <col min="16" max="16" width="8.96666666666667" customWidth="1"/>
     <col min="17" max="17" width="93.375" customWidth="1"/>
     <col min="18" max="18" width="10.625" customWidth="1"/>
-    <col min="19" max="19" width="23.75" style="16" customWidth="1"/>
+    <col min="19" max="19" width="23.75" style="18" customWidth="1"/>
     <col min="20" max="20" width="60.875" customWidth="1"/>
     <col min="21" max="22" width="11.5"/>
   </cols>
@@ -2301,671 +2357,671 @@
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17" t="s">
+      <c r="C1" s="19"/>
+      <c r="D1" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17" t="s">
+      <c r="E1" s="19"/>
+      <c r="F1" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="G1" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17" t="s">
+      <c r="H1" s="19"/>
+      <c r="I1" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="18" t="s">
+      <c r="J1" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="19" t="s">
+      <c r="K1" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17" t="s">
+      <c r="L1" s="19"/>
+      <c r="M1" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="17"/>
-      <c r="O1" s="20" t="s">
+      <c r="N1" s="19"/>
+      <c r="O1" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="20" t="s">
+      <c r="P1" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="Q1" s="20" t="s">
+      <c r="Q1" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="R1" s="21" t="s">
+      <c r="R1" s="23" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="2" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17" t="s">
+      <c r="C2" s="19"/>
+      <c r="D2" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="17"/>
-      <c r="F2" s="20" t="s">
+      <c r="E2" s="19"/>
+      <c r="F2" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="G2" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="23" t="s">
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="24" t="s">
+      <c r="K2" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="L2" s="20"/>
-      <c r="M2" s="23" t="s">
+      <c r="L2" s="22"/>
+      <c r="M2" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="N2" s="17"/>
-      <c r="O2" s="20" t="s">
+      <c r="N2" s="19"/>
+      <c r="O2" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="P2" s="20" t="s">
+      <c r="P2" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="Q2" s="23" t="s">
+      <c r="Q2" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="R2" s="21" t="s">
+      <c r="R2" s="23" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="3" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="25" t="s">
+      <c r="B3" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25" t="s">
+      <c r="C3" s="27"/>
+      <c r="D3" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25" t="s">
+      <c r="E3" s="27"/>
+      <c r="F3" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="26" t="s">
+      <c r="G3" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
-      <c r="J3" s="27" t="s">
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
+      <c r="J3" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="28" t="s">
+      <c r="K3" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="L3" s="25"/>
-      <c r="M3" s="25" t="s">
+      <c r="L3" s="27"/>
+      <c r="M3" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="N3" s="25"/>
-      <c r="O3" s="20" t="s">
+      <c r="N3" s="27"/>
+      <c r="O3" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="P3" s="20" t="s">
+      <c r="P3" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="Q3" s="20" t="s">
+      <c r="Q3" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="R3" s="29" t="s">
+      <c r="R3" s="31" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="4" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="30"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="17"/>
-      <c r="M4" s="17"/>
-      <c r="N4" s="17"/>
-      <c r="O4" s="17"/>
-      <c r="P4" s="17"/>
-      <c r="Q4" s="17"/>
-      <c r="R4" s="17"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="32"/>
+      <c r="K4" s="21"/>
+      <c r="L4" s="19"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="19"/>
+      <c r="O4" s="19"/>
+      <c r="P4" s="19"/>
+      <c r="Q4" s="19"/>
+      <c r="R4" s="19"/>
     </row>
     <row r="5" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A5" s="31">
+      <c r="A5" s="33">
         <v>30010001</v>
       </c>
-      <c r="B5" s="32">
+      <c r="B5" s="34">
         <v>100100</v>
       </c>
-      <c r="C5" s="32" t="s">
+      <c r="C5" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="31">
+      <c r="D5" s="33">
         <v>31001</v>
       </c>
-      <c r="E5" s="31" t="s">
+      <c r="E5" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="31" t="s">
+      <c r="F5" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="G5" s="31"/>
-      <c r="H5" s="31"/>
-      <c r="I5" s="31" t="s">
+      <c r="G5" s="33"/>
+      <c r="H5" s="33"/>
+      <c r="I5" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="J5" s="31"/>
-      <c r="K5" s="33"/>
-      <c r="L5" s="17" t="s">
+      <c r="J5" s="33"/>
+      <c r="K5" s="35"/>
+      <c r="L5" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="M5" s="31" t="s">
+      <c r="M5" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="N5" s="31" t="s">
+      <c r="N5" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="O5" s="31"/>
-      <c r="P5" s="31"/>
-      <c r="Q5" s="34" t="s">
+      <c r="O5" s="33"/>
+      <c r="P5" s="33"/>
+      <c r="Q5" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="R5" s="35" t="s">
+      <c r="R5" s="37" t="s">
         <v>40</v>
       </c>
-      <c r="S5" s="36" t="s">
+      <c r="S5" s="38" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="6" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A6" s="31">
+      <c r="A6" s="33">
         <v>30010002</v>
       </c>
-      <c r="B6" s="32">
+      <c r="B6" s="34">
         <v>100100</v>
       </c>
-      <c r="C6" s="32" t="s">
+      <c r="C6" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="31">
+      <c r="D6" s="33">
         <v>31002</v>
       </c>
-      <c r="E6" s="31" t="s">
+      <c r="E6" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="F6" s="31" t="s">
+      <c r="F6" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="G6" s="31"/>
-      <c r="H6" s="31"/>
-      <c r="I6" s="31" t="s">
+      <c r="G6" s="33"/>
+      <c r="H6" s="33"/>
+      <c r="I6" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="J6" s="31"/>
-      <c r="K6" s="33"/>
-      <c r="L6" s="17" t="s">
+      <c r="J6" s="33"/>
+      <c r="K6" s="35"/>
+      <c r="L6" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="M6" s="31" t="s">
+      <c r="M6" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="N6" s="31" t="s">
+      <c r="N6" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="O6" s="31"/>
-      <c r="P6" s="31"/>
-      <c r="Q6" s="34" t="s">
+      <c r="O6" s="33"/>
+      <c r="P6" s="33"/>
+      <c r="Q6" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="R6" s="35" t="s">
+      <c r="R6" s="37" t="s">
         <v>40</v>
       </c>
-      <c r="S6" s="36"/>
+      <c r="S6" s="38"/>
     </row>
     <row r="7" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A7" s="31">
+      <c r="A7" s="33">
         <v>30010003</v>
       </c>
-      <c r="B7" s="32">
+      <c r="B7" s="34">
         <v>100100</v>
       </c>
-      <c r="C7" s="32" t="s">
+      <c r="C7" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="31">
+      <c r="D7" s="33">
         <v>31003</v>
       </c>
-      <c r="E7" s="31" t="s">
+      <c r="E7" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="31" t="s">
+      <c r="F7" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="G7" s="31"/>
-      <c r="H7" s="31"/>
-      <c r="I7" s="31" t="s">
+      <c r="G7" s="33"/>
+      <c r="H7" s="33"/>
+      <c r="I7" s="33" t="s">
         <v>46</v>
       </c>
-      <c r="J7" s="31"/>
-      <c r="K7" s="33"/>
-      <c r="L7" s="17" t="s">
+      <c r="J7" s="33"/>
+      <c r="K7" s="35"/>
+      <c r="L7" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="M7" s="31" t="s">
+      <c r="M7" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="N7" s="31" t="s">
+      <c r="N7" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="O7" s="31"/>
-      <c r="P7" s="31"/>
-      <c r="Q7" s="34" t="s">
+      <c r="O7" s="33"/>
+      <c r="P7" s="33"/>
+      <c r="Q7" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="R7" s="35" t="s">
+      <c r="R7" s="37" t="s">
         <v>40</v>
       </c>
-      <c r="S7" s="36"/>
+      <c r="S7" s="38"/>
     </row>
     <row r="8" s="3" customFormat="1" ht="15" customHeight="1" spans="1:19">
-      <c r="A8" s="31">
+      <c r="A8" s="33">
         <v>30010004</v>
       </c>
-      <c r="B8" s="32">
+      <c r="B8" s="34">
         <v>100100</v>
       </c>
-      <c r="C8" s="32" t="s">
+      <c r="C8" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="31">
+      <c r="D8" s="33">
         <v>31004</v>
       </c>
-      <c r="E8" s="31" t="s">
+      <c r="E8" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="F8" s="31" t="s">
+      <c r="F8" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="G8" s="31"/>
-      <c r="H8" s="31"/>
-      <c r="I8" s="31" t="s">
+      <c r="G8" s="33"/>
+      <c r="H8" s="33"/>
+      <c r="I8" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="J8" s="31"/>
-      <c r="K8" s="33"/>
-      <c r="L8" s="17" t="s">
+      <c r="J8" s="33"/>
+      <c r="K8" s="35"/>
+      <c r="L8" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="M8" s="31" t="s">
+      <c r="M8" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="N8" s="31" t="s">
+      <c r="N8" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="O8" s="31"/>
-      <c r="P8" s="31"/>
-      <c r="Q8" s="34" t="s">
+      <c r="O8" s="33"/>
+      <c r="P8" s="33"/>
+      <c r="Q8" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="R8" s="35" t="s">
+      <c r="R8" s="37" t="s">
         <v>40</v>
       </c>
-      <c r="S8" s="36"/>
+      <c r="S8" s="38"/>
     </row>
     <row r="9" s="3" customFormat="1" ht="15" customHeight="1" spans="1:19">
-      <c r="A9" s="17">
+      <c r="A9" s="19">
         <v>30010005</v>
       </c>
-      <c r="B9" s="29">
+      <c r="B9" s="31">
         <v>100100</v>
       </c>
-      <c r="C9" s="32" t="s">
+      <c r="C9" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="17">
+      <c r="D9" s="19">
         <v>31101</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="E9" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="F9" s="17" t="s">
+      <c r="F9" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="G9" s="17"/>
-      <c r="H9" s="17"/>
-      <c r="I9" s="17" t="s">
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="J9" s="17"/>
-      <c r="K9" s="19"/>
-      <c r="L9" s="17" t="s">
+      <c r="J9" s="19"/>
+      <c r="K9" s="21"/>
+      <c r="L9" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="M9" s="17" t="s">
+      <c r="M9" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="N9" s="17"/>
-      <c r="O9" s="17" t="s">
+      <c r="N9" s="19"/>
+      <c r="O9" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="P9" s="17"/>
-      <c r="Q9" s="20"/>
-      <c r="R9" s="20"/>
-      <c r="S9" s="36"/>
+      <c r="P9" s="19"/>
+      <c r="Q9" s="22"/>
+      <c r="R9" s="22"/>
+      <c r="S9" s="38"/>
     </row>
     <row r="10" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A10" s="37">
+      <c r="A10" s="39">
         <v>30010006</v>
       </c>
-      <c r="B10" s="38">
+      <c r="B10" s="40">
         <v>100100</v>
       </c>
-      <c r="C10" s="32" t="s">
+      <c r="C10" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="D10" s="37">
+      <c r="D10" s="39">
         <v>31102</v>
       </c>
-      <c r="E10" s="37" t="s">
+      <c r="E10" s="39" t="s">
         <v>55</v>
       </c>
-      <c r="F10" s="37" t="s">
+      <c r="F10" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="G10" s="37"/>
-      <c r="H10" s="37"/>
-      <c r="I10" s="37" t="s">
+      <c r="G10" s="39"/>
+      <c r="H10" s="39"/>
+      <c r="I10" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="J10" s="37"/>
-      <c r="K10" s="39"/>
-      <c r="L10" s="37" t="s">
+      <c r="J10" s="39"/>
+      <c r="K10" s="41"/>
+      <c r="L10" s="39" t="s">
         <v>36</v>
       </c>
-      <c r="M10" s="37" t="s">
+      <c r="M10" s="39" t="s">
         <v>57</v>
       </c>
-      <c r="N10" s="37" t="s">
+      <c r="N10" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="O10" s="37" t="s">
+      <c r="O10" s="39" t="s">
         <v>54</v>
       </c>
-      <c r="P10" s="37"/>
-      <c r="Q10" s="37"/>
-      <c r="R10" s="17"/>
-      <c r="S10" s="36"/>
+      <c r="P10" s="39"/>
+      <c r="Q10" s="39"/>
+      <c r="R10" s="19"/>
+      <c r="S10" s="38"/>
     </row>
     <row r="11" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A11" s="40">
+      <c r="A11" s="42">
         <v>30010007</v>
       </c>
-      <c r="B11" s="41">
+      <c r="B11" s="43">
         <v>100100</v>
       </c>
-      <c r="C11" s="32" t="s">
+      <c r="C11" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="42">
+      <c r="D11" s="44">
         <v>31201</v>
       </c>
-      <c r="E11" s="42" t="s">
+      <c r="E11" s="44" t="s">
         <v>58</v>
       </c>
-      <c r="F11" s="40" t="s">
+      <c r="F11" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="G11" s="40">
+      <c r="G11" s="42">
         <v>2001001</v>
       </c>
-      <c r="H11" s="40" t="s">
+      <c r="H11" s="42" t="s">
         <v>60</v>
       </c>
-      <c r="I11" s="40" t="s">
+      <c r="I11" s="42" t="s">
         <v>61</v>
       </c>
-      <c r="J11" s="40"/>
-      <c r="K11" s="43">
+      <c r="J11" s="42"/>
+      <c r="K11" s="45">
         <v>10010091</v>
       </c>
-      <c r="L11" s="40"/>
-      <c r="M11" s="40"/>
-      <c r="N11" s="40"/>
-      <c r="O11" s="40"/>
-      <c r="P11" s="40"/>
-      <c r="Q11" s="40"/>
-      <c r="R11" s="17"/>
-      <c r="S11" s="36"/>
+      <c r="L11" s="42"/>
+      <c r="M11" s="42"/>
+      <c r="N11" s="42"/>
+      <c r="O11" s="42"/>
+      <c r="P11" s="42"/>
+      <c r="Q11" s="42"/>
+      <c r="R11" s="19"/>
+      <c r="S11" s="38"/>
     </row>
     <row r="12" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A12" s="44">
+      <c r="A12" s="46">
         <v>30010008</v>
       </c>
-      <c r="B12" s="45">
+      <c r="B12" s="47">
         <v>100100</v>
       </c>
-      <c r="C12" s="32" t="s">
+      <c r="C12" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="42">
+      <c r="D12" s="44">
         <v>31202</v>
       </c>
-      <c r="E12" s="42" t="s">
+      <c r="E12" s="44" t="s">
         <v>62</v>
       </c>
-      <c r="F12" s="44" t="s">
+      <c r="F12" s="46" t="s">
         <v>53</v>
       </c>
-      <c r="G12" s="44">
+      <c r="G12" s="46">
         <v>2001001</v>
       </c>
-      <c r="H12" s="44" t="s">
+      <c r="H12" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="I12" s="44" t="s">
+      <c r="I12" s="46" t="s">
         <v>63</v>
       </c>
-      <c r="J12" s="44"/>
-      <c r="K12" s="46" t="s">
+      <c r="J12" s="46"/>
+      <c r="K12" s="48" t="s">
         <v>64</v>
       </c>
-      <c r="L12" s="44"/>
-      <c r="M12" s="44"/>
-      <c r="N12" s="44"/>
-      <c r="O12" s="44"/>
-      <c r="P12" s="44"/>
-      <c r="Q12" s="44"/>
-      <c r="R12" s="17"/>
-      <c r="S12" s="36"/>
+      <c r="L12" s="46"/>
+      <c r="M12" s="46"/>
+      <c r="N12" s="46"/>
+      <c r="O12" s="46"/>
+      <c r="P12" s="46"/>
+      <c r="Q12" s="46"/>
+      <c r="R12" s="19"/>
+      <c r="S12" s="38"/>
     </row>
     <row r="13" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A13" s="47">
+      <c r="A13" s="49">
         <v>30010009</v>
       </c>
-      <c r="B13" s="48">
+      <c r="B13" s="50">
         <v>100100</v>
       </c>
-      <c r="C13" s="32" t="s">
+      <c r="C13" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="D13" s="42">
+      <c r="D13" s="44">
         <v>31203</v>
       </c>
-      <c r="E13" s="42" t="s">
+      <c r="E13" s="44" t="s">
         <v>65</v>
       </c>
-      <c r="F13" s="47" t="s">
+      <c r="F13" s="49" t="s">
         <v>53</v>
       </c>
-      <c r="G13" s="47">
+      <c r="G13" s="49">
         <v>2001001</v>
       </c>
-      <c r="H13" s="47" t="s">
+      <c r="H13" s="49" t="s">
         <v>60</v>
       </c>
-      <c r="I13" s="47" t="s">
+      <c r="I13" s="49" t="s">
         <v>66</v>
       </c>
-      <c r="J13" s="47"/>
-      <c r="K13" s="49" t="s">
+      <c r="J13" s="49"/>
+      <c r="K13" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="L13" s="47"/>
-      <c r="M13" s="47"/>
-      <c r="N13" s="47"/>
-      <c r="O13" s="47"/>
-      <c r="P13" s="47"/>
-      <c r="Q13" s="47"/>
-      <c r="R13" s="17"/>
-      <c r="S13" s="36"/>
+      <c r="L13" s="49"/>
+      <c r="M13" s="49"/>
+      <c r="N13" s="49"/>
+      <c r="O13" s="49"/>
+      <c r="P13" s="49"/>
+      <c r="Q13" s="49"/>
+      <c r="R13" s="19"/>
+      <c r="S13" s="38"/>
     </row>
     <row r="14" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A14" s="42">
+      <c r="A14" s="44">
         <v>30010010</v>
       </c>
-      <c r="B14" s="50">
+      <c r="B14" s="52">
         <v>100100</v>
       </c>
-      <c r="C14" s="32" t="s">
+      <c r="C14" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="D14" s="51">
+      <c r="D14" s="53">
         <v>31301</v>
       </c>
-      <c r="E14" s="51" t="s">
+      <c r="E14" s="53" t="s">
         <v>68</v>
       </c>
-      <c r="F14" s="42" t="s">
+      <c r="F14" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="G14" s="42"/>
-      <c r="H14" s="42"/>
-      <c r="I14" s="42" t="s">
+      <c r="G14" s="44"/>
+      <c r="H14" s="44"/>
+      <c r="I14" s="44" t="s">
         <v>69</v>
       </c>
-      <c r="J14" s="42"/>
-      <c r="K14" s="52"/>
-      <c r="L14" s="42" t="s">
+      <c r="J14" s="44"/>
+      <c r="K14" s="54"/>
+      <c r="L14" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="M14" s="42" t="s">
+      <c r="M14" s="44" t="s">
         <v>70</v>
       </c>
-      <c r="N14" s="42"/>
-      <c r="O14" s="42"/>
-      <c r="P14" s="42"/>
-      <c r="Q14" s="53" t="s">
+      <c r="N14" s="44"/>
+      <c r="O14" s="44"/>
+      <c r="P14" s="44"/>
+      <c r="Q14" s="55" t="s">
         <v>71</v>
       </c>
-      <c r="R14" s="54" t="s">
+      <c r="R14" s="56" t="s">
         <v>72</v>
       </c>
-      <c r="S14" s="20" t="s">
+      <c r="S14" s="22" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="15" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A15" s="47">
+      <c r="A15" s="49">
         <v>30010011</v>
       </c>
-      <c r="B15" s="48">
+      <c r="B15" s="50">
         <v>100100</v>
       </c>
-      <c r="C15" s="32" t="s">
+      <c r="C15" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="D15" s="51">
+      <c r="D15" s="53">
         <v>31302</v>
       </c>
-      <c r="E15" s="51" t="s">
+      <c r="E15" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="F15" s="47" t="s">
+      <c r="F15" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="G15" s="47"/>
-      <c r="H15" s="47"/>
-      <c r="I15" s="47" t="s">
+      <c r="G15" s="49"/>
+      <c r="H15" s="49"/>
+      <c r="I15" s="49" t="s">
         <v>75</v>
       </c>
-      <c r="J15" s="47"/>
-      <c r="K15" s="49"/>
-      <c r="L15" s="47" t="s">
+      <c r="J15" s="49"/>
+      <c r="K15" s="51"/>
+      <c r="L15" s="49" t="s">
         <v>36</v>
       </c>
-      <c r="M15" s="47" t="s">
+      <c r="M15" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="N15" s="47"/>
-      <c r="O15" s="47"/>
-      <c r="P15" s="47"/>
-      <c r="Q15" s="47"/>
-      <c r="R15" s="17"/>
-      <c r="S15" s="36"/>
+      <c r="N15" s="49"/>
+      <c r="O15" s="49"/>
+      <c r="P15" s="49"/>
+      <c r="Q15" s="49"/>
+      <c r="R15" s="19"/>
+      <c r="S15" s="38"/>
     </row>
     <row r="16" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A16" s="47">
+      <c r="A16" s="49">
         <v>30010012</v>
       </c>
-      <c r="B16" s="48">
+      <c r="B16" s="50">
         <v>100100</v>
       </c>
-      <c r="C16" s="32" t="s">
+      <c r="C16" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="D16" s="51">
+      <c r="D16" s="53">
         <v>31303</v>
       </c>
-      <c r="E16" s="51" t="s">
+      <c r="E16" s="53" t="s">
         <v>76</v>
       </c>
-      <c r="F16" s="47" t="s">
+      <c r="F16" s="49" t="s">
         <v>53</v>
       </c>
-      <c r="G16" s="47">
+      <c r="G16" s="49">
         <v>2001001</v>
       </c>
-      <c r="H16" s="47" t="s">
+      <c r="H16" s="49" t="s">
         <v>60</v>
       </c>
-      <c r="I16" s="47" t="s">
+      <c r="I16" s="49" t="s">
         <v>66</v>
       </c>
-      <c r="J16" s="47"/>
-      <c r="K16" s="49" t="s">
+      <c r="J16" s="49"/>
+      <c r="K16" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="L16" s="47"/>
-      <c r="M16" s="47"/>
-      <c r="N16" s="47"/>
-      <c r="O16" s="47"/>
-      <c r="P16" s="47"/>
-      <c r="Q16" s="47"/>
-      <c r="R16" s="17"/>
-      <c r="S16" s="36"/>
+      <c r="L16" s="49"/>
+      <c r="M16" s="49"/>
+      <c r="N16" s="49"/>
+      <c r="O16" s="49"/>
+      <c r="P16" s="49"/>
+      <c r="Q16" s="49"/>
+      <c r="R16" s="19"/>
+      <c r="S16" s="38"/>
     </row>
     <row r="17" s="3" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A17" s="17">
+      <c r="A17" s="19">
         <v>30070001</v>
       </c>
       <c r="B17" s="3">
@@ -2974,30 +3030,30 @@
       <c r="C17" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D17" s="40">
+      <c r="D17" s="42">
         <v>34001</v>
       </c>
-      <c r="E17" s="40" t="s">
+      <c r="E17" s="42" t="s">
         <v>78</v>
       </c>
-      <c r="F17" s="40" t="s">
+      <c r="F17" s="42" t="s">
         <v>79</v>
       </c>
-      <c r="G17" s="29">
+      <c r="G17" s="31">
         <v>2007001</v>
       </c>
-      <c r="H17" s="17" t="s">
+      <c r="H17" s="19" t="s">
         <v>60</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="K17" s="55" t="s">
+      <c r="K17" s="57" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="18" s="3" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A18" s="17">
+      <c r="A18" s="19">
         <v>30070002</v>
       </c>
       <c r="B18" s="3">
@@ -3006,30 +3062,30 @@
       <c r="C18" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D18" s="40">
+      <c r="D18" s="42">
         <v>34002</v>
       </c>
-      <c r="E18" s="40" t="s">
+      <c r="E18" s="42" t="s">
         <v>82</v>
       </c>
-      <c r="F18" s="40" t="s">
+      <c r="F18" s="42" t="s">
         <v>83</v>
       </c>
-      <c r="G18" s="29">
+      <c r="G18" s="31">
         <v>2007001</v>
       </c>
-      <c r="H18" s="17" t="s">
+      <c r="H18" s="19" t="s">
         <v>60</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="K18" s="55" t="s">
+      <c r="K18" s="57" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="19" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A19" s="42">
+      <c r="A19" s="44">
         <v>30120001</v>
       </c>
       <c r="B19" s="4">
@@ -3038,33 +3094,33 @@
       <c r="C19" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D19" s="42">
+      <c r="D19" s="44">
         <v>32001</v>
       </c>
-      <c r="E19" s="42" t="s">
+      <c r="E19" s="44" t="s">
         <v>85</v>
       </c>
-      <c r="F19" s="42" t="s">
+      <c r="F19" s="44" t="s">
         <v>53</v>
       </c>
-      <c r="G19" s="50">
+      <c r="G19" s="52">
         <v>2012001</v>
       </c>
-      <c r="H19" s="42" t="s">
+      <c r="H19" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="I19" s="42" t="s">
+      <c r="I19" s="44" t="s">
         <v>85</v>
       </c>
-      <c r="J19" s="42" t="s">
+      <c r="J19" s="44" t="s">
         <v>86</v>
       </c>
-      <c r="K19" s="56">
+      <c r="K19" s="58">
         <v>10120041</v>
       </c>
     </row>
     <row r="20" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A20" s="42">
+      <c r="A20" s="44">
         <v>30120002</v>
       </c>
       <c r="B20" s="4">
@@ -3073,33 +3129,33 @@
       <c r="C20" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D20" s="42">
+      <c r="D20" s="44">
         <v>32002</v>
       </c>
-      <c r="E20" s="42" t="s">
+      <c r="E20" s="44" t="s">
         <v>87</v>
       </c>
-      <c r="F20" s="42" t="s">
+      <c r="F20" s="44" t="s">
         <v>53</v>
       </c>
-      <c r="G20" s="50">
+      <c r="G20" s="52">
         <v>2012001</v>
       </c>
-      <c r="H20" s="42" t="s">
+      <c r="H20" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="I20" s="42" t="s">
+      <c r="I20" s="44" t="s">
         <v>87</v>
       </c>
-      <c r="J20" s="42" t="s">
+      <c r="J20" s="44" t="s">
         <v>86</v>
       </c>
-      <c r="K20" s="56">
+      <c r="K20" s="58">
         <v>10120042</v>
       </c>
     </row>
     <row r="21" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A21" s="42">
+      <c r="A21" s="44">
         <v>30120003</v>
       </c>
       <c r="B21" s="4">
@@ -3108,33 +3164,33 @@
       <c r="C21" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D21" s="42">
+      <c r="D21" s="44">
         <v>32003</v>
       </c>
-      <c r="E21" s="42" t="s">
+      <c r="E21" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="F21" s="42" t="s">
+      <c r="F21" s="44" t="s">
         <v>53</v>
       </c>
-      <c r="G21" s="50">
+      <c r="G21" s="52">
         <v>2012001</v>
       </c>
-      <c r="H21" s="42" t="s">
+      <c r="H21" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="I21" s="42" t="s">
+      <c r="I21" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="J21" s="42" t="s">
+      <c r="J21" s="44" t="s">
         <v>86</v>
       </c>
-      <c r="K21" s="56">
+      <c r="K21" s="58">
         <v>10120043</v>
       </c>
     </row>
     <row r="22" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A22" s="42">
+      <c r="A22" s="44">
         <v>30120004</v>
       </c>
       <c r="B22" s="4">
@@ -3143,33 +3199,33 @@
       <c r="C22" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D22" s="42">
+      <c r="D22" s="44">
         <v>32004</v>
       </c>
-      <c r="E22" s="42" t="s">
+      <c r="E22" s="44" t="s">
         <v>89</v>
       </c>
-      <c r="F22" s="42" t="s">
+      <c r="F22" s="44" t="s">
         <v>53</v>
       </c>
-      <c r="G22" s="50">
+      <c r="G22" s="52">
         <v>2012001</v>
       </c>
-      <c r="H22" s="42" t="s">
+      <c r="H22" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="I22" s="42" t="s">
+      <c r="I22" s="44" t="s">
         <v>89</v>
       </c>
-      <c r="J22" s="42" t="s">
+      <c r="J22" s="44" t="s">
         <v>86</v>
       </c>
-      <c r="K22" s="56">
+      <c r="K22" s="58">
         <v>10120044</v>
       </c>
     </row>
     <row r="23" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A23" s="42">
+      <c r="A23" s="44">
         <v>30120005</v>
       </c>
       <c r="B23" s="4">
@@ -3178,33 +3234,33 @@
       <c r="C23" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D23" s="42">
+      <c r="D23" s="44">
         <v>32005</v>
       </c>
-      <c r="E23" s="42" t="s">
+      <c r="E23" s="44" t="s">
         <v>89</v>
       </c>
-      <c r="F23" s="42" t="s">
+      <c r="F23" s="44" t="s">
         <v>53</v>
       </c>
-      <c r="G23" s="50">
+      <c r="G23" s="52">
         <v>2012001</v>
       </c>
-      <c r="H23" s="42" t="s">
+      <c r="H23" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="I23" s="42" t="s">
+      <c r="I23" s="44" t="s">
         <v>89</v>
       </c>
-      <c r="J23" s="42" t="s">
+      <c r="J23" s="44" t="s">
         <v>86</v>
       </c>
-      <c r="K23" s="56">
+      <c r="K23" s="58">
         <v>10120045</v>
       </c>
     </row>
     <row r="24" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A24" s="42">
+      <c r="A24" s="44">
         <v>30120006</v>
       </c>
       <c r="B24" s="4">
@@ -3213,33 +3269,33 @@
       <c r="C24" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D24" s="42">
+      <c r="D24" s="44">
         <v>32006</v>
       </c>
-      <c r="E24" s="42" t="s">
+      <c r="E24" s="44" t="s">
         <v>89</v>
       </c>
-      <c r="F24" s="42" t="s">
+      <c r="F24" s="44" t="s">
         <v>53</v>
       </c>
-      <c r="G24" s="50">
+      <c r="G24" s="52">
         <v>2012001</v>
       </c>
-      <c r="H24" s="42" t="s">
+      <c r="H24" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="I24" s="42" t="s">
+      <c r="I24" s="44" t="s">
         <v>89</v>
       </c>
-      <c r="J24" s="42" t="s">
+      <c r="J24" s="44" t="s">
         <v>86</v>
       </c>
-      <c r="K24" s="56">
+      <c r="K24" s="58">
         <v>10120046</v>
       </c>
     </row>
     <row r="25" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A25" s="57">
+      <c r="A25" s="59">
         <v>30120011</v>
       </c>
       <c r="B25" s="5">
@@ -3248,33 +3304,33 @@
       <c r="C25" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="D25" s="42">
+      <c r="D25" s="44">
         <v>32101</v>
       </c>
-      <c r="E25" s="57" t="s">
+      <c r="E25" s="59" t="s">
         <v>85</v>
       </c>
-      <c r="F25" s="57" t="s">
+      <c r="F25" s="59" t="s">
         <v>53</v>
       </c>
-      <c r="G25" s="58">
+      <c r="G25" s="60">
         <v>2012001</v>
       </c>
-      <c r="H25" s="57" t="s">
+      <c r="H25" s="59" t="s">
         <v>60</v>
       </c>
-      <c r="I25" s="57" t="s">
+      <c r="I25" s="59" t="s">
         <v>85</v>
       </c>
-      <c r="J25" s="57" t="s">
+      <c r="J25" s="59" t="s">
         <v>91</v>
       </c>
-      <c r="K25" s="59">
+      <c r="K25" s="61">
         <v>10120041</v>
       </c>
     </row>
     <row r="26" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A26" s="57">
+      <c r="A26" s="59">
         <v>30120012</v>
       </c>
       <c r="B26" s="5">
@@ -3283,33 +3339,33 @@
       <c r="C26" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="D26" s="42">
+      <c r="D26" s="44">
         <v>32102</v>
       </c>
-      <c r="E26" s="57" t="s">
+      <c r="E26" s="59" t="s">
         <v>87</v>
       </c>
-      <c r="F26" s="57" t="s">
+      <c r="F26" s="59" t="s">
         <v>53</v>
       </c>
-      <c r="G26" s="58">
+      <c r="G26" s="60">
         <v>2012001</v>
       </c>
-      <c r="H26" s="57" t="s">
+      <c r="H26" s="59" t="s">
         <v>60</v>
       </c>
-      <c r="I26" s="57" t="s">
+      <c r="I26" s="59" t="s">
         <v>87</v>
       </c>
-      <c r="J26" s="57" t="s">
+      <c r="J26" s="59" t="s">
         <v>91</v>
       </c>
-      <c r="K26" s="59">
+      <c r="K26" s="61">
         <v>10120042</v>
       </c>
     </row>
     <row r="27" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A27" s="57">
+      <c r="A27" s="59">
         <v>30120013</v>
       </c>
       <c r="B27" s="5">
@@ -3318,33 +3374,33 @@
       <c r="C27" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="D27" s="42">
+      <c r="D27" s="44">
         <v>32103</v>
       </c>
-      <c r="E27" s="57" t="s">
+      <c r="E27" s="59" t="s">
         <v>88</v>
       </c>
-      <c r="F27" s="57" t="s">
+      <c r="F27" s="59" t="s">
         <v>53</v>
       </c>
-      <c r="G27" s="58">
+      <c r="G27" s="60">
         <v>2012001</v>
       </c>
-      <c r="H27" s="57" t="s">
+      <c r="H27" s="59" t="s">
         <v>60</v>
       </c>
-      <c r="I27" s="57" t="s">
+      <c r="I27" s="59" t="s">
         <v>88</v>
       </c>
-      <c r="J27" s="57" t="s">
+      <c r="J27" s="59" t="s">
         <v>91</v>
       </c>
-      <c r="K27" s="59">
+      <c r="K27" s="61">
         <v>10120043</v>
       </c>
     </row>
     <row r="28" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A28" s="57">
+      <c r="A28" s="59">
         <v>30120014</v>
       </c>
       <c r="B28" s="5">
@@ -3353,33 +3409,33 @@
       <c r="C28" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="D28" s="42">
+      <c r="D28" s="44">
         <v>32104</v>
       </c>
-      <c r="E28" s="57" t="s">
+      <c r="E28" s="59" t="s">
         <v>89</v>
       </c>
-      <c r="F28" s="57" t="s">
+      <c r="F28" s="59" t="s">
         <v>53</v>
       </c>
-      <c r="G28" s="58">
+      <c r="G28" s="60">
         <v>2012001</v>
       </c>
-      <c r="H28" s="57" t="s">
+      <c r="H28" s="59" t="s">
         <v>60</v>
       </c>
-      <c r="I28" s="57" t="s">
+      <c r="I28" s="59" t="s">
         <v>89</v>
       </c>
-      <c r="J28" s="57" t="s">
+      <c r="J28" s="59" t="s">
         <v>91</v>
       </c>
-      <c r="K28" s="59">
+      <c r="K28" s="61">
         <v>10120044</v>
       </c>
     </row>
     <row r="29" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A29" s="57">
+      <c r="A29" s="59">
         <v>30120015</v>
       </c>
       <c r="B29" s="5">
@@ -3388,33 +3444,33 @@
       <c r="C29" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="D29" s="42">
+      <c r="D29" s="44">
         <v>32105</v>
       </c>
-      <c r="E29" s="57" t="s">
+      <c r="E29" s="59" t="s">
         <v>89</v>
       </c>
-      <c r="F29" s="57" t="s">
+      <c r="F29" s="59" t="s">
         <v>53</v>
       </c>
-      <c r="G29" s="58">
+      <c r="G29" s="60">
         <v>2012001</v>
       </c>
-      <c r="H29" s="57" t="s">
+      <c r="H29" s="59" t="s">
         <v>60</v>
       </c>
-      <c r="I29" s="57" t="s">
+      <c r="I29" s="59" t="s">
         <v>89</v>
       </c>
-      <c r="J29" s="57" t="s">
+      <c r="J29" s="59" t="s">
         <v>91</v>
       </c>
-      <c r="K29" s="59">
+      <c r="K29" s="61">
         <v>10120045</v>
       </c>
     </row>
     <row r="30" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A30" s="57">
+      <c r="A30" s="59">
         <v>30120016</v>
       </c>
       <c r="B30" s="5">
@@ -3423,33 +3479,33 @@
       <c r="C30" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="D30" s="42">
+      <c r="D30" s="44">
         <v>32106</v>
       </c>
-      <c r="E30" s="57" t="s">
+      <c r="E30" s="59" t="s">
         <v>89</v>
       </c>
-      <c r="F30" s="57" t="s">
+      <c r="F30" s="59" t="s">
         <v>53</v>
       </c>
-      <c r="G30" s="58">
+      <c r="G30" s="60">
         <v>2012001</v>
       </c>
-      <c r="H30" s="57" t="s">
+      <c r="H30" s="59" t="s">
         <v>60</v>
       </c>
-      <c r="I30" s="57" t="s">
+      <c r="I30" s="59" t="s">
         <v>89</v>
       </c>
-      <c r="J30" s="57" t="s">
+      <c r="J30" s="59" t="s">
         <v>91</v>
       </c>
-      <c r="K30" s="59">
+      <c r="K30" s="61">
         <v>10120046</v>
       </c>
     </row>
     <row r="31" s="6" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A31" s="51">
+      <c r="A31" s="53">
         <v>30120021</v>
       </c>
       <c r="B31" s="6">
@@ -3458,31 +3514,31 @@
       <c r="C31" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D31" s="51">
+      <c r="D31" s="53">
         <v>32201</v>
       </c>
-      <c r="E31" s="51" t="s">
+      <c r="E31" s="53" t="s">
         <v>85</v>
       </c>
-      <c r="F31" s="51" t="s">
+      <c r="F31" s="53" t="s">
         <v>53</v>
       </c>
-      <c r="G31" s="60">
+      <c r="G31" s="62">
         <v>2012001</v>
       </c>
-      <c r="H31" s="51" t="s">
+      <c r="H31" s="53" t="s">
         <v>60</v>
       </c>
-      <c r="I31" s="51" t="s">
+      <c r="I31" s="53" t="s">
         <v>85</v>
       </c>
-      <c r="J31" s="51"/>
-      <c r="K31" s="61">
+      <c r="J31" s="53"/>
+      <c r="K31" s="63">
         <v>10120041</v>
       </c>
     </row>
     <row r="32" s="6" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A32" s="51">
+      <c r="A32" s="53">
         <v>30120022</v>
       </c>
       <c r="B32" s="6">
@@ -3491,31 +3547,31 @@
       <c r="C32" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D32" s="51">
+      <c r="D32" s="53">
         <v>32202</v>
       </c>
-      <c r="E32" s="51" t="s">
+      <c r="E32" s="53" t="s">
         <v>87</v>
       </c>
-      <c r="F32" s="51" t="s">
+      <c r="F32" s="53" t="s">
         <v>53</v>
       </c>
-      <c r="G32" s="60">
+      <c r="G32" s="62">
         <v>2012001</v>
       </c>
-      <c r="H32" s="51" t="s">
+      <c r="H32" s="53" t="s">
         <v>60</v>
       </c>
-      <c r="I32" s="51" t="s">
+      <c r="I32" s="53" t="s">
         <v>87</v>
       </c>
-      <c r="J32" s="51"/>
-      <c r="K32" s="61">
+      <c r="J32" s="53"/>
+      <c r="K32" s="63">
         <v>10120042</v>
       </c>
     </row>
     <row r="33" s="6" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A33" s="51">
+      <c r="A33" s="53">
         <v>30120023</v>
       </c>
       <c r="B33" s="6">
@@ -3524,31 +3580,31 @@
       <c r="C33" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D33" s="51">
+      <c r="D33" s="53">
         <v>32203</v>
       </c>
-      <c r="E33" s="51" t="s">
+      <c r="E33" s="53" t="s">
         <v>88</v>
       </c>
-      <c r="F33" s="51" t="s">
+      <c r="F33" s="53" t="s">
         <v>53</v>
       </c>
-      <c r="G33" s="60">
+      <c r="G33" s="62">
         <v>2012001</v>
       </c>
-      <c r="H33" s="51" t="s">
+      <c r="H33" s="53" t="s">
         <v>60</v>
       </c>
-      <c r="I33" s="51" t="s">
+      <c r="I33" s="53" t="s">
         <v>88</v>
       </c>
-      <c r="J33" s="51"/>
-      <c r="K33" s="61">
+      <c r="J33" s="53"/>
+      <c r="K33" s="63">
         <v>10120043</v>
       </c>
     </row>
     <row r="34" s="6" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A34" s="51">
+      <c r="A34" s="53">
         <v>30120024</v>
       </c>
       <c r="B34" s="6">
@@ -3557,31 +3613,31 @@
       <c r="C34" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D34" s="51">
+      <c r="D34" s="53">
         <v>32204</v>
       </c>
-      <c r="E34" s="51" t="s">
+      <c r="E34" s="53" t="s">
         <v>89</v>
       </c>
-      <c r="F34" s="51" t="s">
+      <c r="F34" s="53" t="s">
         <v>53</v>
       </c>
-      <c r="G34" s="60">
+      <c r="G34" s="62">
         <v>2012001</v>
       </c>
-      <c r="H34" s="51" t="s">
+      <c r="H34" s="53" t="s">
         <v>60</v>
       </c>
-      <c r="I34" s="51" t="s">
+      <c r="I34" s="53" t="s">
         <v>89</v>
       </c>
-      <c r="J34" s="51"/>
-      <c r="K34" s="61">
+      <c r="J34" s="53"/>
+      <c r="K34" s="63">
         <v>10120044</v>
       </c>
     </row>
     <row r="35" s="6" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A35" s="51">
+      <c r="A35" s="53">
         <v>30120025</v>
       </c>
       <c r="B35" s="6">
@@ -3590,31 +3646,31 @@
       <c r="C35" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D35" s="51">
+      <c r="D35" s="53">
         <v>32205</v>
       </c>
-      <c r="E35" s="51" t="s">
+      <c r="E35" s="53" t="s">
         <v>89</v>
       </c>
-      <c r="F35" s="51" t="s">
+      <c r="F35" s="53" t="s">
         <v>53</v>
       </c>
-      <c r="G35" s="60">
+      <c r="G35" s="62">
         <v>2012001</v>
       </c>
-      <c r="H35" s="51" t="s">
+      <c r="H35" s="53" t="s">
         <v>60</v>
       </c>
-      <c r="I35" s="51" t="s">
+      <c r="I35" s="53" t="s">
         <v>89</v>
       </c>
-      <c r="J35" s="51"/>
-      <c r="K35" s="61">
+      <c r="J35" s="53"/>
+      <c r="K35" s="63">
         <v>10120045</v>
       </c>
     </row>
     <row r="36" s="6" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A36" s="51">
+      <c r="A36" s="53">
         <v>30120026</v>
       </c>
       <c r="B36" s="6">
@@ -3623,1292 +3679,1502 @@
       <c r="C36" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D36" s="51">
+      <c r="D36" s="53">
         <v>32206</v>
       </c>
-      <c r="E36" s="51" t="s">
+      <c r="E36" s="53" t="s">
         <v>89</v>
       </c>
-      <c r="F36" s="51" t="s">
+      <c r="F36" s="53" t="s">
         <v>53</v>
       </c>
-      <c r="G36" s="60">
+      <c r="G36" s="62">
         <v>2012001</v>
       </c>
-      <c r="H36" s="51" t="s">
+      <c r="H36" s="53" t="s">
         <v>60</v>
       </c>
-      <c r="I36" s="51" t="s">
+      <c r="I36" s="53" t="s">
         <v>89</v>
       </c>
-      <c r="J36" s="51"/>
-      <c r="K36" s="61">
+      <c r="J36" s="53"/>
+      <c r="K36" s="63">
         <v>10120046</v>
       </c>
     </row>
     <row r="37" s="7" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A37" s="62">
+      <c r="A37" s="64">
         <v>30240001</v>
       </c>
-      <c r="B37" s="63">
+      <c r="B37" s="65">
         <v>102400</v>
       </c>
-      <c r="C37" s="63" t="s">
+      <c r="C37" s="65" t="s">
         <v>32</v>
       </c>
-      <c r="D37" s="62">
+      <c r="D37" s="64">
         <v>32401</v>
       </c>
-      <c r="E37" s="62" t="s">
+      <c r="E37" s="64" t="s">
         <v>33</v>
       </c>
-      <c r="F37" s="62" t="s">
+      <c r="F37" s="64" t="s">
         <v>34</v>
       </c>
-      <c r="G37" s="62"/>
-      <c r="H37" s="62"/>
-      <c r="I37" s="62" t="s">
+      <c r="G37" s="64"/>
+      <c r="H37" s="64"/>
+      <c r="I37" s="64" t="s">
         <v>35</v>
       </c>
-      <c r="J37" s="62"/>
-      <c r="K37" s="64"/>
-      <c r="L37" s="62" t="s">
+      <c r="J37" s="64"/>
+      <c r="K37" s="66"/>
+      <c r="L37" s="64" t="s">
         <v>36</v>
       </c>
-      <c r="M37" s="62" t="s">
+      <c r="M37" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="N37" s="62" t="s">
+      <c r="N37" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="O37" s="62"/>
-      <c r="P37" s="62"/>
-      <c r="Q37" s="65" t="s">
+      <c r="O37" s="64"/>
+      <c r="P37" s="64"/>
+      <c r="Q37" s="67" t="s">
         <v>39</v>
       </c>
-      <c r="R37" s="66" t="s">
+      <c r="R37" s="68" t="s">
         <v>40</v>
       </c>
-      <c r="S37" s="67" t="s">
+      <c r="S37" s="69" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="38" s="7" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A38" s="62">
+      <c r="A38" s="64">
         <v>30240002</v>
       </c>
-      <c r="B38" s="63">
+      <c r="B38" s="65">
         <v>102400</v>
       </c>
-      <c r="C38" s="63" t="s">
+      <c r="C38" s="65" t="s">
         <v>32</v>
       </c>
-      <c r="D38" s="62">
+      <c r="D38" s="64">
         <v>32402</v>
       </c>
-      <c r="E38" s="62" t="s">
+      <c r="E38" s="64" t="s">
         <v>42</v>
       </c>
-      <c r="F38" s="62" t="s">
+      <c r="F38" s="64" t="s">
         <v>34</v>
       </c>
-      <c r="G38" s="62"/>
-      <c r="H38" s="62"/>
-      <c r="I38" s="62" t="s">
+      <c r="G38" s="64"/>
+      <c r="H38" s="64"/>
+      <c r="I38" s="64" t="s">
         <v>43</v>
       </c>
-      <c r="J38" s="62"/>
-      <c r="K38" s="64"/>
-      <c r="L38" s="62" t="s">
+      <c r="J38" s="64"/>
+      <c r="K38" s="66"/>
+      <c r="L38" s="64" t="s">
         <v>36</v>
       </c>
-      <c r="M38" s="62" t="s">
+      <c r="M38" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="N38" s="62" t="s">
+      <c r="N38" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="O38" s="62"/>
-      <c r="P38" s="62"/>
-      <c r="Q38" s="65" t="s">
+      <c r="O38" s="64"/>
+      <c r="P38" s="64"/>
+      <c r="Q38" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="R38" s="66" t="s">
+      <c r="R38" s="68" t="s">
         <v>40</v>
       </c>
-      <c r="S38" s="67"/>
+      <c r="S38" s="69"/>
     </row>
     <row r="39" s="7" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A39" s="62">
+      <c r="A39" s="64">
         <v>30240003</v>
       </c>
-      <c r="B39" s="63">
+      <c r="B39" s="65">
         <v>102400</v>
       </c>
-      <c r="C39" s="63" t="s">
+      <c r="C39" s="65" t="s">
         <v>32</v>
       </c>
-      <c r="D39" s="62">
+      <c r="D39" s="64">
         <v>32403</v>
       </c>
-      <c r="E39" s="62" t="s">
+      <c r="E39" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="F39" s="62" t="s">
+      <c r="F39" s="64" t="s">
         <v>34</v>
       </c>
-      <c r="G39" s="62"/>
-      <c r="H39" s="62"/>
-      <c r="I39" s="62" t="s">
+      <c r="G39" s="64"/>
+      <c r="H39" s="64"/>
+      <c r="I39" s="64" t="s">
         <v>46</v>
       </c>
-      <c r="J39" s="62"/>
-      <c r="K39" s="64"/>
-      <c r="L39" s="62" t="s">
+      <c r="J39" s="64"/>
+      <c r="K39" s="66"/>
+      <c r="L39" s="64" t="s">
         <v>36</v>
       </c>
-      <c r="M39" s="62" t="s">
+      <c r="M39" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="N39" s="62" t="s">
+      <c r="N39" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="O39" s="62"/>
-      <c r="P39" s="62"/>
-      <c r="Q39" s="65" t="s">
+      <c r="O39" s="64"/>
+      <c r="P39" s="64"/>
+      <c r="Q39" s="67" t="s">
         <v>47</v>
       </c>
-      <c r="R39" s="66" t="s">
+      <c r="R39" s="68" t="s">
         <v>40</v>
       </c>
-      <c r="S39" s="67"/>
+      <c r="S39" s="69"/>
     </row>
     <row r="40" s="7" customFormat="1" ht="15" customHeight="1" spans="1:19">
-      <c r="A40" s="62">
+      <c r="A40" s="64">
         <v>30240004</v>
       </c>
-      <c r="B40" s="63">
+      <c r="B40" s="65">
         <v>102400</v>
       </c>
-      <c r="C40" s="63" t="s">
+      <c r="C40" s="65" t="s">
         <v>32</v>
       </c>
-      <c r="D40" s="62">
+      <c r="D40" s="64">
         <v>32404</v>
       </c>
-      <c r="E40" s="62" t="s">
+      <c r="E40" s="64" t="s">
         <v>48</v>
       </c>
-      <c r="F40" s="62" t="s">
+      <c r="F40" s="64" t="s">
         <v>34</v>
       </c>
-      <c r="G40" s="62"/>
-      <c r="H40" s="62"/>
-      <c r="I40" s="62" t="s">
+      <c r="G40" s="64"/>
+      <c r="H40" s="64"/>
+      <c r="I40" s="64" t="s">
         <v>49</v>
       </c>
-      <c r="J40" s="62"/>
-      <c r="K40" s="64"/>
-      <c r="L40" s="62" t="s">
+      <c r="J40" s="64"/>
+      <c r="K40" s="66"/>
+      <c r="L40" s="64" t="s">
         <v>36</v>
       </c>
-      <c r="M40" s="62" t="s">
+      <c r="M40" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="N40" s="62" t="s">
+      <c r="N40" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="O40" s="62"/>
-      <c r="P40" s="62"/>
-      <c r="Q40" s="65" t="s">
+      <c r="O40" s="64"/>
+      <c r="P40" s="64"/>
+      <c r="Q40" s="67" t="s">
         <v>50</v>
       </c>
-      <c r="R40" s="66" t="s">
+      <c r="R40" s="68" t="s">
         <v>40</v>
       </c>
-      <c r="S40" s="67"/>
+      <c r="S40" s="69"/>
     </row>
     <row r="41" s="7" customFormat="1" ht="15" customHeight="1" spans="1:19">
-      <c r="A41" s="62">
+      <c r="A41" s="64">
         <v>30240005</v>
       </c>
-      <c r="B41" s="63">
+      <c r="B41" s="65">
         <v>102400</v>
       </c>
-      <c r="C41" s="63" t="s">
+      <c r="C41" s="65" t="s">
         <v>32</v>
       </c>
-      <c r="D41" s="62">
+      <c r="D41" s="64">
         <v>32411</v>
       </c>
-      <c r="E41" s="62" t="s">
+      <c r="E41" s="64" t="s">
         <v>51</v>
       </c>
-      <c r="F41" s="62" t="s">
+      <c r="F41" s="64" t="s">
         <v>34</v>
       </c>
-      <c r="G41" s="62"/>
-      <c r="H41" s="62"/>
-      <c r="I41" s="62" t="s">
+      <c r="G41" s="64"/>
+      <c r="H41" s="64"/>
+      <c r="I41" s="64" t="s">
         <v>52</v>
       </c>
-      <c r="J41" s="62"/>
-      <c r="K41" s="64"/>
-      <c r="L41" s="62" t="s">
+      <c r="J41" s="64"/>
+      <c r="K41" s="66"/>
+      <c r="L41" s="64" t="s">
         <v>36</v>
       </c>
-      <c r="M41" s="62" t="s">
+      <c r="M41" s="64" t="s">
         <v>53</v>
       </c>
-      <c r="N41" s="62"/>
-      <c r="O41" s="62" t="s">
+      <c r="N41" s="64"/>
+      <c r="O41" s="64" t="s">
         <v>54</v>
       </c>
-      <c r="P41" s="62"/>
-      <c r="Q41" s="65"/>
-      <c r="R41" s="65"/>
-      <c r="S41" s="67"/>
+      <c r="P41" s="64"/>
+      <c r="Q41" s="67"/>
+      <c r="R41" s="67"/>
+      <c r="S41" s="69"/>
     </row>
     <row r="42" s="7" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A42" s="62">
+      <c r="A42" s="64">
         <v>30240006</v>
       </c>
-      <c r="B42" s="63">
+      <c r="B42" s="65">
         <v>102400</v>
       </c>
-      <c r="C42" s="63" t="s">
+      <c r="C42" s="65" t="s">
         <v>32</v>
       </c>
-      <c r="D42" s="62">
+      <c r="D42" s="64">
         <v>32421</v>
       </c>
-      <c r="E42" s="62" t="s">
+      <c r="E42" s="64" t="s">
         <v>55</v>
       </c>
-      <c r="F42" s="62" t="s">
+      <c r="F42" s="64" t="s">
         <v>34</v>
       </c>
-      <c r="G42" s="62"/>
-      <c r="H42" s="62"/>
-      <c r="I42" s="62" t="s">
+      <c r="G42" s="64"/>
+      <c r="H42" s="64"/>
+      <c r="I42" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="J42" s="62"/>
-      <c r="K42" s="64"/>
-      <c r="L42" s="62" t="s">
+      <c r="J42" s="64"/>
+      <c r="K42" s="66"/>
+      <c r="L42" s="64" t="s">
         <v>36</v>
       </c>
-      <c r="M42" s="62" t="s">
+      <c r="M42" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="N42" s="62" t="s">
+      <c r="N42" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="O42" s="62" t="s">
+      <c r="O42" s="64" t="s">
         <v>54</v>
       </c>
-      <c r="P42" s="62"/>
-      <c r="Q42" s="62"/>
-      <c r="R42" s="62"/>
-      <c r="S42" s="67"/>
+      <c r="P42" s="64"/>
+      <c r="Q42" s="64"/>
+      <c r="R42" s="64"/>
+      <c r="S42" s="69"/>
     </row>
     <row r="43" s="7" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A43" s="62">
+      <c r="A43" s="64">
         <v>30240007</v>
       </c>
-      <c r="B43" s="63">
+      <c r="B43" s="65">
         <v>102400</v>
       </c>
-      <c r="C43" s="63" t="s">
+      <c r="C43" s="65" t="s">
         <v>32</v>
       </c>
-      <c r="D43" s="62">
+      <c r="D43" s="64">
         <v>32431</v>
       </c>
-      <c r="E43" s="62" t="s">
+      <c r="E43" s="64" t="s">
         <v>58</v>
       </c>
-      <c r="F43" s="62" t="s">
+      <c r="F43" s="64" t="s">
         <v>59</v>
       </c>
-      <c r="G43" s="62">
+      <c r="G43" s="64">
         <v>2024001</v>
       </c>
-      <c r="H43" s="62" t="s">
+      <c r="H43" s="64" t="s">
         <v>60</v>
       </c>
-      <c r="I43" s="62" t="s">
+      <c r="I43" s="64" t="s">
         <v>61</v>
       </c>
-      <c r="J43" s="62"/>
-      <c r="K43" s="64">
+      <c r="J43" s="64"/>
+      <c r="K43" s="66">
         <v>10240091</v>
       </c>
-      <c r="L43" s="62"/>
-      <c r="M43" s="62"/>
-      <c r="N43" s="62"/>
-      <c r="O43" s="62"/>
-      <c r="P43" s="62"/>
-      <c r="Q43" s="62"/>
-      <c r="R43" s="62"/>
-      <c r="S43" s="67"/>
+      <c r="L43" s="64"/>
+      <c r="M43" s="64"/>
+      <c r="N43" s="64"/>
+      <c r="O43" s="64"/>
+      <c r="P43" s="64"/>
+      <c r="Q43" s="64"/>
+      <c r="R43" s="64"/>
+      <c r="S43" s="69"/>
     </row>
     <row r="44" s="7" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A44" s="62">
+      <c r="A44" s="64">
         <v>30240008</v>
       </c>
-      <c r="B44" s="63">
+      <c r="B44" s="65">
         <v>102400</v>
       </c>
-      <c r="C44" s="63" t="s">
+      <c r="C44" s="65" t="s">
         <v>32</v>
       </c>
-      <c r="D44" s="62">
+      <c r="D44" s="64">
         <v>32432</v>
       </c>
-      <c r="E44" s="62" t="s">
+      <c r="E44" s="64" t="s">
         <v>62</v>
       </c>
-      <c r="F44" s="62" t="s">
+      <c r="F44" s="64" t="s">
         <v>53</v>
       </c>
-      <c r="G44" s="62">
+      <c r="G44" s="64">
         <v>2024001</v>
       </c>
-      <c r="H44" s="62" t="s">
+      <c r="H44" s="64" t="s">
         <v>60</v>
       </c>
-      <c r="I44" s="62" t="s">
+      <c r="I44" s="64" t="s">
         <v>63</v>
       </c>
-      <c r="J44" s="62"/>
-      <c r="K44" s="68" t="s">
+      <c r="J44" s="64"/>
+      <c r="K44" s="70" t="s">
         <v>93</v>
       </c>
-      <c r="L44" s="62"/>
-      <c r="M44" s="62"/>
-      <c r="N44" s="62"/>
-      <c r="O44" s="62"/>
-      <c r="P44" s="62"/>
-      <c r="Q44" s="62"/>
-      <c r="R44" s="62"/>
-      <c r="S44" s="67"/>
+      <c r="L44" s="64"/>
+      <c r="M44" s="64"/>
+      <c r="N44" s="64"/>
+      <c r="O44" s="64"/>
+      <c r="P44" s="64"/>
+      <c r="Q44" s="64"/>
+      <c r="R44" s="64"/>
+      <c r="S44" s="69"/>
     </row>
     <row r="45" s="7" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A45" s="62">
+      <c r="A45" s="64">
         <v>30240009</v>
       </c>
-      <c r="B45" s="63">
+      <c r="B45" s="65">
         <v>102400</v>
       </c>
-      <c r="C45" s="63" t="s">
+      <c r="C45" s="65" t="s">
         <v>32</v>
       </c>
-      <c r="D45" s="62">
+      <c r="D45" s="64">
         <v>32433</v>
       </c>
-      <c r="E45" s="62" t="s">
+      <c r="E45" s="64" t="s">
         <v>65</v>
       </c>
-      <c r="F45" s="62" t="s">
+      <c r="F45" s="64" t="s">
         <v>53</v>
       </c>
-      <c r="G45" s="62">
+      <c r="G45" s="64">
         <v>2024001</v>
       </c>
-      <c r="H45" s="62" t="s">
+      <c r="H45" s="64" t="s">
         <v>60</v>
       </c>
-      <c r="I45" s="62" t="s">
+      <c r="I45" s="64" t="s">
         <v>66</v>
       </c>
-      <c r="J45" s="62"/>
-      <c r="K45" s="64" t="s">
+      <c r="J45" s="64"/>
+      <c r="K45" s="66" t="s">
         <v>94</v>
       </c>
-      <c r="L45" s="62"/>
-      <c r="M45" s="62"/>
-      <c r="N45" s="62"/>
-      <c r="O45" s="62"/>
-      <c r="P45" s="62"/>
-      <c r="Q45" s="62"/>
-      <c r="R45" s="62"/>
-      <c r="S45" s="67"/>
+      <c r="L45" s="64"/>
+      <c r="M45" s="64"/>
+      <c r="N45" s="64"/>
+      <c r="O45" s="64"/>
+      <c r="P45" s="64"/>
+      <c r="Q45" s="64"/>
+      <c r="R45" s="64"/>
+      <c r="S45" s="69"/>
     </row>
     <row r="46" s="7" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A46" s="62">
+      <c r="A46" s="64">
         <v>30240010</v>
       </c>
-      <c r="B46" s="63">
+      <c r="B46" s="65">
         <v>102400</v>
       </c>
-      <c r="C46" s="63" t="s">
+      <c r="C46" s="65" t="s">
         <v>32</v>
       </c>
-      <c r="D46" s="62">
+      <c r="D46" s="64">
         <v>32441</v>
       </c>
-      <c r="E46" s="62" t="s">
+      <c r="E46" s="64" t="s">
         <v>68</v>
       </c>
-      <c r="F46" s="62" t="s">
+      <c r="F46" s="64" t="s">
         <v>34</v>
       </c>
-      <c r="G46" s="62"/>
-      <c r="H46" s="62"/>
-      <c r="I46" s="62" t="s">
+      <c r="G46" s="64"/>
+      <c r="H46" s="64"/>
+      <c r="I46" s="64" t="s">
         <v>69</v>
       </c>
-      <c r="J46" s="62"/>
-      <c r="K46" s="68"/>
-      <c r="L46" s="62" t="s">
+      <c r="J46" s="64"/>
+      <c r="K46" s="70"/>
+      <c r="L46" s="64" t="s">
         <v>36</v>
       </c>
-      <c r="M46" s="62" t="s">
+      <c r="M46" s="64" t="s">
         <v>70</v>
       </c>
-      <c r="N46" s="62"/>
-      <c r="O46" s="62"/>
-      <c r="P46" s="62"/>
-      <c r="Q46" s="65" t="s">
+      <c r="N46" s="64"/>
+      <c r="O46" s="64"/>
+      <c r="P46" s="64"/>
+      <c r="Q46" s="67" t="s">
         <v>71</v>
       </c>
-      <c r="R46" s="69" t="s">
+      <c r="R46" s="71" t="s">
         <v>72</v>
       </c>
-      <c r="S46" s="65" t="s">
+      <c r="S46" s="67" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="47" s="7" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A47" s="62">
+      <c r="A47" s="64">
         <v>30240011</v>
       </c>
-      <c r="B47" s="63">
+      <c r="B47" s="65">
         <v>102400</v>
       </c>
-      <c r="C47" s="63" t="s">
+      <c r="C47" s="65" t="s">
         <v>32</v>
       </c>
-      <c r="D47" s="62">
+      <c r="D47" s="64">
         <v>32442</v>
       </c>
-      <c r="E47" s="62" t="s">
+      <c r="E47" s="64" t="s">
         <v>74</v>
       </c>
-      <c r="F47" s="62" t="s">
+      <c r="F47" s="64" t="s">
         <v>34</v>
       </c>
-      <c r="G47" s="62"/>
-      <c r="H47" s="62"/>
-      <c r="I47" s="62" t="s">
+      <c r="G47" s="64"/>
+      <c r="H47" s="64"/>
+      <c r="I47" s="64" t="s">
         <v>75</v>
       </c>
-      <c r="J47" s="62"/>
-      <c r="K47" s="64"/>
-      <c r="L47" s="62" t="s">
+      <c r="J47" s="64"/>
+      <c r="K47" s="66"/>
+      <c r="L47" s="64" t="s">
         <v>36</v>
       </c>
-      <c r="M47" s="62" t="s">
+      <c r="M47" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="N47" s="62"/>
-      <c r="O47" s="62"/>
-      <c r="P47" s="62"/>
-      <c r="Q47" s="62"/>
-      <c r="R47" s="62"/>
-      <c r="S47" s="67"/>
+      <c r="N47" s="64"/>
+      <c r="O47" s="64"/>
+      <c r="P47" s="64"/>
+      <c r="Q47" s="64"/>
+      <c r="R47" s="64"/>
+      <c r="S47" s="69"/>
     </row>
     <row r="48" s="7" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A48" s="62">
+      <c r="A48" s="64">
         <v>30240012</v>
       </c>
-      <c r="B48" s="63">
+      <c r="B48" s="65">
         <v>102400</v>
       </c>
-      <c r="C48" s="63" t="s">
+      <c r="C48" s="65" t="s">
         <v>32</v>
       </c>
-      <c r="D48" s="62">
+      <c r="D48" s="64">
         <v>32443</v>
       </c>
-      <c r="E48" s="62" t="s">
+      <c r="E48" s="64" t="s">
         <v>76</v>
       </c>
-      <c r="F48" s="62" t="s">
+      <c r="F48" s="64" t="s">
         <v>53</v>
       </c>
-      <c r="G48" s="62">
+      <c r="G48" s="64">
         <v>2024001</v>
       </c>
-      <c r="H48" s="62" t="s">
+      <c r="H48" s="64" t="s">
         <v>60</v>
       </c>
-      <c r="I48" s="62" t="s">
+      <c r="I48" s="64" t="s">
         <v>66</v>
       </c>
-      <c r="J48" s="62"/>
-      <c r="K48" s="64" t="s">
+      <c r="J48" s="64"/>
+      <c r="K48" s="66" t="s">
         <v>94</v>
       </c>
-      <c r="L48" s="62"/>
-      <c r="M48" s="62"/>
-      <c r="N48" s="62"/>
-      <c r="O48" s="62"/>
-      <c r="P48" s="62"/>
-      <c r="Q48" s="62"/>
-      <c r="R48" s="62"/>
-      <c r="S48" s="67"/>
+      <c r="L48" s="64"/>
+      <c r="M48" s="64"/>
+      <c r="N48" s="64"/>
+      <c r="O48" s="64"/>
+      <c r="P48" s="64"/>
+      <c r="Q48" s="64"/>
+      <c r="R48" s="64"/>
+      <c r="S48" s="69"/>
     </row>
     <row r="49" s="8" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A49" s="70">
+      <c r="A49" s="72">
         <v>30170001</v>
       </c>
-      <c r="B49" s="71">
+      <c r="B49" s="73">
         <v>101700</v>
       </c>
-      <c r="C49" s="71" t="s">
+      <c r="C49" s="73" t="s">
         <v>95</v>
       </c>
-      <c r="D49" s="70">
+      <c r="D49" s="72">
         <v>301701</v>
       </c>
-      <c r="E49" s="70" t="s">
+      <c r="E49" s="72" t="s">
         <v>96</v>
       </c>
-      <c r="F49" s="70" t="s">
+      <c r="F49" s="72" t="s">
         <v>79</v>
       </c>
-      <c r="G49" s="70">
+      <c r="G49" s="72">
         <v>2017001</v>
       </c>
-      <c r="H49" s="70" t="s">
+      <c r="H49" s="72" t="s">
         <v>60</v>
       </c>
-      <c r="I49" s="70" t="s">
+      <c r="I49" s="72" t="s">
         <v>80</v>
       </c>
-      <c r="J49" s="70"/>
-      <c r="K49" s="72" t="s">
+      <c r="J49" s="72"/>
+      <c r="K49" s="74" t="s">
         <v>97</v>
       </c>
-      <c r="L49" s="70"/>
-      <c r="M49" s="70"/>
-      <c r="N49" s="70"/>
-      <c r="O49" s="70"/>
-      <c r="P49" s="70"/>
-      <c r="Q49" s="70"/>
-      <c r="R49" s="70"/>
-      <c r="S49" s="73"/>
+      <c r="L49" s="72"/>
+      <c r="M49" s="72"/>
+      <c r="N49" s="72"/>
+      <c r="O49" s="72"/>
+      <c r="P49" s="72"/>
+      <c r="Q49" s="72"/>
+      <c r="R49" s="72"/>
+      <c r="S49" s="75"/>
     </row>
     <row r="50" s="8" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A50" s="70">
+      <c r="A50" s="72">
         <v>30170002</v>
       </c>
-      <c r="B50" s="71">
+      <c r="B50" s="73">
         <v>101700</v>
       </c>
-      <c r="C50" s="71" t="s">
+      <c r="C50" s="73" t="s">
         <v>95</v>
       </c>
-      <c r="D50" s="70">
+      <c r="D50" s="72">
         <v>301702</v>
       </c>
-      <c r="E50" s="70" t="s">
+      <c r="E50" s="72" t="s">
         <v>98</v>
       </c>
-      <c r="F50" s="70" t="s">
+      <c r="F50" s="72" t="s">
         <v>83</v>
       </c>
-      <c r="G50" s="70">
+      <c r="G50" s="72">
         <v>2017001</v>
       </c>
-      <c r="H50" s="70" t="s">
+      <c r="H50" s="72" t="s">
         <v>60</v>
       </c>
-      <c r="I50" s="70" t="s">
+      <c r="I50" s="72" t="s">
         <v>80</v>
       </c>
-      <c r="J50" s="70"/>
-      <c r="K50" s="72" t="s">
+      <c r="J50" s="72"/>
+      <c r="K50" s="74" t="s">
         <v>97</v>
       </c>
-      <c r="L50" s="70"/>
-      <c r="M50" s="70"/>
-      <c r="N50" s="70"/>
-      <c r="O50" s="70"/>
-      <c r="P50" s="70"/>
-      <c r="Q50" s="70"/>
-      <c r="R50" s="70"/>
-      <c r="S50" s="73"/>
+      <c r="L50" s="72"/>
+      <c r="M50" s="72"/>
+      <c r="N50" s="72"/>
+      <c r="O50" s="72"/>
+      <c r="P50" s="72"/>
+      <c r="Q50" s="72"/>
+      <c r="R50" s="72"/>
+      <c r="S50" s="75"/>
     </row>
     <row r="51" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A51" s="57">
+      <c r="A51" s="59">
         <v>30220001</v>
       </c>
-      <c r="B51" s="58">
+      <c r="B51" s="60">
         <v>102200</v>
       </c>
-      <c r="C51" s="58" t="s">
+      <c r="C51" s="60" t="s">
         <v>99</v>
       </c>
-      <c r="D51" s="57">
+      <c r="D51" s="59">
         <v>302201</v>
       </c>
-      <c r="E51" s="57" t="s">
+      <c r="E51" s="59" t="s">
         <v>100</v>
       </c>
-      <c r="F51" s="57" t="s">
+      <c r="F51" s="59" t="s">
         <v>101</v>
       </c>
-      <c r="G51" s="57">
+      <c r="G51" s="59">
         <v>2022001</v>
       </c>
-      <c r="H51" s="57" t="s">
+      <c r="H51" s="59" t="s">
         <v>60</v>
       </c>
-      <c r="I51" s="57"/>
-      <c r="J51" s="57"/>
-      <c r="K51" s="74" t="s">
+      <c r="I51" s="59"/>
+      <c r="J51" s="59"/>
+      <c r="K51" s="76" t="s">
         <v>102</v>
       </c>
-      <c r="L51" s="57" t="s">
+      <c r="L51" s="59" t="s">
         <v>103</v>
       </c>
-      <c r="M51" s="57"/>
-      <c r="N51" s="57"/>
-      <c r="O51" s="57"/>
-      <c r="P51" s="57"/>
-      <c r="Q51" s="57"/>
-      <c r="R51" s="57"/>
-      <c r="S51" s="75"/>
+      <c r="M51" s="59"/>
+      <c r="N51" s="59"/>
+      <c r="O51" s="59"/>
+      <c r="P51" s="59"/>
+      <c r="Q51" s="59"/>
+      <c r="R51" s="59"/>
+      <c r="S51" s="77"/>
     </row>
     <row r="52" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A52" s="57">
+      <c r="A52" s="59">
         <v>30220002</v>
       </c>
-      <c r="B52" s="58">
+      <c r="B52" s="60">
         <v>102200</v>
       </c>
-      <c r="C52" s="58" t="s">
+      <c r="C52" s="60" t="s">
         <v>99</v>
       </c>
-      <c r="D52" s="57">
+      <c r="D52" s="59">
         <v>302202</v>
       </c>
-      <c r="E52" s="57" t="s">
+      <c r="E52" s="59" t="s">
         <v>104</v>
       </c>
-      <c r="F52" s="57" t="s">
+      <c r="F52" s="59" t="s">
         <v>101</v>
       </c>
-      <c r="G52" s="57">
+      <c r="G52" s="59">
         <v>2022001</v>
       </c>
-      <c r="H52" s="57" t="s">
+      <c r="H52" s="59" t="s">
         <v>60</v>
       </c>
-      <c r="I52" s="57"/>
-      <c r="J52" s="57"/>
-      <c r="K52" s="74" t="s">
+      <c r="I52" s="59"/>
+      <c r="J52" s="59"/>
+      <c r="K52" s="76" t="s">
         <v>105</v>
       </c>
-      <c r="L52" s="57" t="s">
+      <c r="L52" s="59" t="s">
         <v>103</v>
       </c>
-      <c r="M52" s="57"/>
-      <c r="N52" s="57"/>
-      <c r="O52" s="57"/>
-      <c r="P52" s="57"/>
-      <c r="Q52" s="57"/>
-      <c r="R52" s="57"/>
-      <c r="S52" s="75"/>
+      <c r="M52" s="59"/>
+      <c r="N52" s="59"/>
+      <c r="O52" s="59"/>
+      <c r="P52" s="59"/>
+      <c r="Q52" s="59"/>
+      <c r="R52" s="59"/>
+      <c r="S52" s="77"/>
     </row>
     <row r="53" s="9" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A53" s="76">
+      <c r="A53" s="78">
         <v>30210001</v>
       </c>
-      <c r="B53" s="77">
+      <c r="B53" s="79">
         <v>102100</v>
       </c>
-      <c r="C53" s="77" t="s">
+      <c r="C53" s="79" t="s">
         <v>106</v>
       </c>
-      <c r="D53" s="76">
+      <c r="D53" s="78">
         <v>302101</v>
       </c>
-      <c r="E53" s="76" t="s">
+      <c r="E53" s="78" t="s">
         <v>107</v>
       </c>
-      <c r="F53" s="76" t="s">
+      <c r="F53" s="78" t="s">
         <v>108</v>
       </c>
-      <c r="G53" s="76">
+      <c r="G53" s="78">
         <v>2021001</v>
       </c>
-      <c r="H53" s="76" t="s">
+      <c r="H53" s="78" t="s">
         <v>60</v>
       </c>
-      <c r="I53" s="76" t="s">
+      <c r="I53" s="78" t="s">
         <v>80</v>
       </c>
-      <c r="J53" s="76"/>
-      <c r="K53" s="78" t="s">
+      <c r="J53" s="78"/>
+      <c r="K53" s="80" t="s">
         <v>109</v>
       </c>
-      <c r="L53" s="76" t="s">
+      <c r="L53" s="78" t="s">
         <v>110</v>
       </c>
-      <c r="M53" s="76"/>
-      <c r="N53" s="76"/>
-      <c r="O53" s="76"/>
-      <c r="P53" s="76"/>
-      <c r="Q53" s="76"/>
-      <c r="R53" s="76"/>
-      <c r="S53" s="79"/>
+      <c r="M53" s="78"/>
+      <c r="N53" s="78"/>
+      <c r="O53" s="78"/>
+      <c r="P53" s="78"/>
+      <c r="Q53" s="78"/>
+      <c r="R53" s="78"/>
+      <c r="S53" s="81"/>
     </row>
     <row r="54" s="9" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A54" s="76">
+      <c r="A54" s="78">
         <v>30210002</v>
       </c>
-      <c r="B54" s="77">
+      <c r="B54" s="79">
         <v>102100</v>
       </c>
-      <c r="C54" s="77" t="s">
+      <c r="C54" s="79" t="s">
         <v>106</v>
       </c>
-      <c r="D54" s="76">
+      <c r="D54" s="78">
         <v>302102</v>
       </c>
-      <c r="E54" s="76" t="s">
+      <c r="E54" s="78" t="s">
         <v>111</v>
       </c>
-      <c r="F54" s="76" t="s">
+      <c r="F54" s="78" t="s">
         <v>34</v>
       </c>
-      <c r="G54" s="76"/>
-      <c r="H54" s="76"/>
-      <c r="I54" s="76" t="s">
+      <c r="G54" s="78"/>
+      <c r="H54" s="78"/>
+      <c r="I54" s="78" t="s">
         <v>112</v>
       </c>
-      <c r="J54" s="76"/>
-      <c r="K54" s="78"/>
-      <c r="L54" s="76"/>
-      <c r="M54" s="76" t="s">
+      <c r="J54" s="78"/>
+      <c r="K54" s="80"/>
+      <c r="L54" s="78"/>
+      <c r="M54" s="78" t="s">
         <v>37</v>
       </c>
-      <c r="N54" s="76" t="s">
+      <c r="N54" s="78" t="s">
         <v>113</v>
       </c>
-      <c r="O54" s="76"/>
-      <c r="P54" s="76"/>
-      <c r="Q54" s="76" t="s">
+      <c r="O54" s="78"/>
+      <c r="P54" s="78"/>
+      <c r="Q54" s="78" t="s">
         <v>114</v>
       </c>
-      <c r="R54" s="76"/>
-      <c r="S54" s="79"/>
+      <c r="R54" s="78"/>
+      <c r="S54" s="81"/>
     </row>
     <row r="55" s="10" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A55" s="80">
+      <c r="A55" s="82">
         <v>30180001</v>
       </c>
-      <c r="B55" s="81">
+      <c r="B55" s="83">
         <v>101800</v>
       </c>
-      <c r="C55" s="81" t="s">
+      <c r="C55" s="83" t="s">
         <v>115</v>
       </c>
-      <c r="D55" s="80">
+      <c r="D55" s="82">
         <v>301801</v>
       </c>
-      <c r="E55" s="80" t="s">
+      <c r="E55" s="82" t="s">
         <v>80</v>
       </c>
-      <c r="F55" s="80" t="s">
+      <c r="F55" s="82" t="s">
         <v>116</v>
       </c>
-      <c r="G55" s="80">
+      <c r="G55" s="82">
         <v>2018002</v>
       </c>
-      <c r="H55" s="80" t="s">
+      <c r="H55" s="82" t="s">
         <v>60</v>
       </c>
-      <c r="I55" s="80" t="s">
+      <c r="I55" s="82" t="s">
         <v>80</v>
       </c>
-      <c r="J55" s="80"/>
-      <c r="K55" s="82">
+      <c r="J55" s="82"/>
+      <c r="K55" s="84">
         <v>10180041</v>
       </c>
-      <c r="L55" s="80"/>
-      <c r="M55" s="80"/>
-      <c r="N55" s="80"/>
-      <c r="O55" s="80"/>
-      <c r="P55" s="80"/>
-      <c r="Q55" s="80"/>
-      <c r="R55" s="80"/>
-      <c r="S55" s="83"/>
+      <c r="L55" s="82"/>
+      <c r="M55" s="82"/>
+      <c r="N55" s="82"/>
+      <c r="O55" s="82"/>
+      <c r="P55" s="82"/>
+      <c r="Q55" s="82"/>
+      <c r="R55" s="82"/>
+      <c r="S55" s="85"/>
     </row>
     <row r="56" s="11" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A56" s="84">
+      <c r="A56" s="86">
         <v>30250001</v>
       </c>
-      <c r="B56" s="85">
+      <c r="B56" s="87">
         <v>102500</v>
       </c>
-      <c r="C56" s="85" t="s">
+      <c r="C56" s="87" t="s">
         <v>117</v>
       </c>
-      <c r="D56" s="84">
+      <c r="D56" s="86">
         <v>302501</v>
       </c>
-      <c r="E56" s="84" t="s">
+      <c r="E56" s="86" t="s">
         <v>107</v>
       </c>
-      <c r="F56" s="84" t="s">
+      <c r="F56" s="86" t="s">
         <v>108</v>
       </c>
-      <c r="G56" s="84">
+      <c r="G56" s="86">
         <v>2025001</v>
       </c>
-      <c r="H56" s="84" t="s">
+      <c r="H56" s="86" t="s">
         <v>60</v>
       </c>
-      <c r="I56" s="84" t="s">
+      <c r="I56" s="86" t="s">
         <v>80</v>
       </c>
-      <c r="J56" s="84"/>
-      <c r="K56" s="86" t="s">
+      <c r="J56" s="86"/>
+      <c r="K56" s="88" t="s">
         <v>118</v>
       </c>
-      <c r="L56" s="84" t="s">
+      <c r="L56" s="86" t="s">
         <v>119</v>
       </c>
-      <c r="M56" s="84"/>
-      <c r="N56" s="84"/>
-      <c r="O56" s="84"/>
-      <c r="P56" s="84"/>
-      <c r="Q56" s="84"/>
-      <c r="R56" s="84"/>
-      <c r="S56" s="87"/>
+      <c r="M56" s="86"/>
+      <c r="N56" s="86"/>
+      <c r="O56" s="86"/>
+      <c r="P56" s="86"/>
+      <c r="Q56" s="86"/>
+      <c r="R56" s="86"/>
+      <c r="S56" s="89"/>
     </row>
     <row r="57" s="11" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A57" s="84">
+      <c r="A57" s="86">
         <v>30250002</v>
       </c>
-      <c r="B57" s="85">
+      <c r="B57" s="87">
         <v>102500</v>
       </c>
-      <c r="C57" s="85" t="s">
+      <c r="C57" s="87" t="s">
         <v>117</v>
       </c>
-      <c r="D57" s="84">
+      <c r="D57" s="86">
         <v>302502</v>
       </c>
-      <c r="E57" s="84" t="s">
+      <c r="E57" s="86" t="s">
         <v>120</v>
       </c>
-      <c r="F57" s="84" t="s">
+      <c r="F57" s="86" t="s">
         <v>121</v>
       </c>
-      <c r="G57" s="84">
+      <c r="G57" s="86">
         <v>2025001</v>
       </c>
-      <c r="H57" s="84" t="s">
+      <c r="H57" s="86" t="s">
         <v>60</v>
       </c>
-      <c r="I57" s="84" t="s">
+      <c r="I57" s="86" t="s">
         <v>80</v>
       </c>
-      <c r="J57" s="84"/>
-      <c r="K57" s="86" t="s">
+      <c r="J57" s="86"/>
+      <c r="K57" s="88" t="s">
         <v>118</v>
       </c>
-      <c r="L57" s="84" t="s">
+      <c r="L57" s="86" t="s">
         <v>119</v>
       </c>
-      <c r="M57" s="84"/>
-      <c r="N57" s="84"/>
-      <c r="O57" s="84"/>
-      <c r="P57" s="84"/>
-      <c r="Q57" s="84"/>
-      <c r="R57" s="84"/>
-      <c r="S57" s="87"/>
+      <c r="M57" s="86"/>
+      <c r="N57" s="86"/>
+      <c r="O57" s="86"/>
+      <c r="P57" s="86"/>
+      <c r="Q57" s="86"/>
+      <c r="R57" s="86"/>
+      <c r="S57" s="89"/>
     </row>
     <row r="58" s="11" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A58" s="84">
+      <c r="A58" s="86">
         <v>30250003</v>
       </c>
-      <c r="B58" s="85">
+      <c r="B58" s="87">
         <v>102500</v>
       </c>
-      <c r="C58" s="85" t="s">
+      <c r="C58" s="87" t="s">
         <v>117</v>
       </c>
-      <c r="D58" s="84">
+      <c r="D58" s="86">
         <v>302503</v>
       </c>
-      <c r="E58" s="84" t="s">
+      <c r="E58" s="86" t="s">
         <v>122</v>
       </c>
-      <c r="F58" s="84" t="s">
+      <c r="F58" s="86" t="s">
         <v>123</v>
       </c>
-      <c r="G58" s="84">
+      <c r="G58" s="86">
         <v>2025001</v>
       </c>
-      <c r="H58" s="84" t="s">
+      <c r="H58" s="86" t="s">
         <v>60</v>
       </c>
-      <c r="I58" s="84" t="s">
+      <c r="I58" s="86" t="s">
         <v>80</v>
       </c>
-      <c r="J58" s="84"/>
-      <c r="K58" s="86" t="s">
+      <c r="J58" s="86"/>
+      <c r="K58" s="88" t="s">
         <v>118</v>
       </c>
-      <c r="L58" s="84" t="s">
+      <c r="L58" s="86" t="s">
         <v>119</v>
       </c>
-      <c r="M58" s="84"/>
-      <c r="N58" s="84"/>
-      <c r="O58" s="84"/>
-      <c r="P58" s="84"/>
-      <c r="Q58" s="84"/>
-      <c r="R58" s="84"/>
-      <c r="S58" s="87"/>
+      <c r="M58" s="86"/>
+      <c r="N58" s="86"/>
+      <c r="O58" s="86"/>
+      <c r="P58" s="86"/>
+      <c r="Q58" s="86"/>
+      <c r="R58" s="86"/>
+      <c r="S58" s="89"/>
     </row>
     <row r="59" s="12" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A59" s="88">
+      <c r="A59" s="90">
         <v>30230001</v>
       </c>
-      <c r="B59" s="89">
+      <c r="B59" s="91">
         <v>102300</v>
       </c>
-      <c r="C59" s="89" t="s">
+      <c r="C59" s="91" t="s">
         <v>124</v>
       </c>
-      <c r="D59" s="88">
+      <c r="D59" s="90">
         <v>302301</v>
       </c>
-      <c r="E59" s="88" t="s">
+      <c r="E59" s="90" t="s">
         <v>107</v>
       </c>
-      <c r="F59" s="88" t="s">
+      <c r="F59" s="90" t="s">
         <v>108</v>
       </c>
-      <c r="G59" s="88">
+      <c r="G59" s="90">
         <v>2023001</v>
       </c>
-      <c r="H59" s="88" t="s">
+      <c r="H59" s="90" t="s">
         <v>60</v>
       </c>
-      <c r="I59" s="88" t="s">
+      <c r="I59" s="90" t="s">
         <v>80</v>
       </c>
-      <c r="J59" s="88"/>
-      <c r="K59" s="90" t="s">
+      <c r="J59" s="90"/>
+      <c r="K59" s="92" t="s">
         <v>125</v>
       </c>
-      <c r="L59" s="88" t="s">
+      <c r="L59" s="90" t="s">
         <v>126</v>
       </c>
-      <c r="M59" s="88"/>
-      <c r="N59" s="88"/>
-      <c r="O59" s="88"/>
-      <c r="P59" s="88"/>
-      <c r="Q59" s="88"/>
-      <c r="R59" s="88"/>
-      <c r="S59" s="91"/>
+      <c r="M59" s="90"/>
+      <c r="N59" s="90"/>
+      <c r="O59" s="90"/>
+      <c r="P59" s="90"/>
+      <c r="Q59" s="90"/>
+      <c r="R59" s="90"/>
+      <c r="S59" s="93"/>
     </row>
     <row r="60" s="12" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A60" s="88">
+      <c r="A60" s="90">
         <v>30230002</v>
       </c>
-      <c r="B60" s="89">
+      <c r="B60" s="91">
         <v>102300</v>
       </c>
-      <c r="C60" s="89" t="s">
+      <c r="C60" s="91" t="s">
         <v>124</v>
       </c>
-      <c r="D60" s="88">
+      <c r="D60" s="90">
         <v>302302</v>
       </c>
-      <c r="E60" s="88" t="s">
+      <c r="E60" s="90" t="s">
         <v>127</v>
       </c>
-      <c r="F60" s="88" t="s">
+      <c r="F60" s="90" t="s">
         <v>79</v>
       </c>
-      <c r="G60" s="88">
+      <c r="G60" s="90">
         <v>2023001</v>
       </c>
-      <c r="H60" s="88" t="s">
+      <c r="H60" s="90" t="s">
         <v>60</v>
       </c>
-      <c r="I60" s="88" t="s">
+      <c r="I60" s="90" t="s">
         <v>80</v>
       </c>
-      <c r="J60" s="88"/>
-      <c r="K60" s="90" t="s">
+      <c r="J60" s="90"/>
+      <c r="K60" s="92" t="s">
         <v>125</v>
       </c>
-      <c r="L60" s="88" t="s">
+      <c r="L60" s="90" t="s">
         <v>126</v>
       </c>
-      <c r="M60" s="88"/>
-      <c r="N60" s="88"/>
-      <c r="O60" s="88"/>
-      <c r="P60" s="88"/>
-      <c r="Q60" s="88"/>
-      <c r="R60" s="88"/>
-      <c r="S60" s="91"/>
+      <c r="M60" s="90"/>
+      <c r="N60" s="90"/>
+      <c r="O60" s="90"/>
+      <c r="P60" s="90"/>
+      <c r="Q60" s="90"/>
+      <c r="R60" s="90"/>
+      <c r="S60" s="93"/>
     </row>
     <row r="61" s="12" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A61" s="88">
+      <c r="A61" s="90">
         <v>30230003</v>
       </c>
-      <c r="B61" s="89">
+      <c r="B61" s="91">
         <v>102300</v>
       </c>
-      <c r="C61" s="89" t="s">
+      <c r="C61" s="91" t="s">
         <v>124</v>
       </c>
-      <c r="D61" s="88">
+      <c r="D61" s="90">
         <v>302303</v>
       </c>
-      <c r="E61" s="88" t="s">
+      <c r="E61" s="90" t="s">
         <v>128</v>
       </c>
-      <c r="F61" s="88" t="s">
+      <c r="F61" s="90" t="s">
         <v>83</v>
       </c>
-      <c r="G61" s="88">
+      <c r="G61" s="90">
         <v>2023001</v>
       </c>
-      <c r="H61" s="88" t="s">
+      <c r="H61" s="90" t="s">
         <v>60</v>
       </c>
-      <c r="I61" s="88" t="s">
+      <c r="I61" s="90" t="s">
         <v>80</v>
       </c>
-      <c r="J61" s="88"/>
-      <c r="K61" s="90" t="s">
+      <c r="J61" s="90"/>
+      <c r="K61" s="92" t="s">
         <v>125</v>
       </c>
-      <c r="L61" s="88" t="s">
+      <c r="L61" s="90" t="s">
         <v>126</v>
       </c>
-      <c r="M61" s="88"/>
-      <c r="N61" s="88"/>
-      <c r="O61" s="88"/>
-      <c r="P61" s="88"/>
-      <c r="Q61" s="88"/>
-      <c r="R61" s="88"/>
-      <c r="S61" s="91"/>
+      <c r="M61" s="90"/>
+      <c r="N61" s="90"/>
+      <c r="O61" s="90"/>
+      <c r="P61" s="90"/>
+      <c r="Q61" s="90"/>
+      <c r="R61" s="90"/>
+      <c r="S61" s="93"/>
     </row>
     <row r="62" s="13" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A62" s="92">
+      <c r="A62" s="94">
         <v>30350001</v>
       </c>
-      <c r="B62" s="93">
+      <c r="B62" s="95">
         <v>103500</v>
       </c>
-      <c r="C62" s="93" t="s">
+      <c r="C62" s="95" t="s">
         <v>129</v>
       </c>
-      <c r="D62" s="92">
+      <c r="D62" s="94">
         <v>303501</v>
       </c>
-      <c r="E62" s="92" t="s">
+      <c r="E62" s="94" t="s">
         <v>130</v>
       </c>
-      <c r="F62" s="92" t="s">
+      <c r="F62" s="94" t="s">
         <v>59</v>
       </c>
-      <c r="G62" s="92">
+      <c r="G62" s="94">
         <v>2035002</v>
       </c>
-      <c r="H62" s="92" t="s">
+      <c r="H62" s="94" t="s">
         <v>60</v>
       </c>
-      <c r="I62" s="92" t="s">
+      <c r="I62" s="94" t="s">
         <v>131</v>
       </c>
-      <c r="J62" s="92"/>
-      <c r="K62" s="94" t="s">
+      <c r="J62" s="94"/>
+      <c r="K62" s="96" t="s">
         <v>132</v>
       </c>
-      <c r="L62" s="92" t="s">
+      <c r="L62" s="94" t="s">
         <v>133</v>
       </c>
-      <c r="M62" s="92"/>
-      <c r="N62" s="92"/>
-      <c r="O62" s="92"/>
-      <c r="P62" s="92"/>
-      <c r="Q62" s="92"/>
-      <c r="R62" s="92"/>
-      <c r="S62" s="95"/>
+      <c r="M62" s="94"/>
+      <c r="N62" s="94"/>
+      <c r="O62" s="94"/>
+      <c r="P62" s="94"/>
+      <c r="Q62" s="94"/>
+      <c r="R62" s="94"/>
+      <c r="S62" s="97"/>
     </row>
     <row r="63" s="13" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A63" s="92">
+      <c r="A63" s="94">
         <v>30350002</v>
       </c>
-      <c r="B63" s="93">
+      <c r="B63" s="95">
         <v>103500</v>
       </c>
-      <c r="C63" s="93" t="s">
+      <c r="C63" s="95" t="s">
         <v>129</v>
       </c>
-      <c r="D63" s="92">
+      <c r="D63" s="94">
         <v>303502</v>
       </c>
-      <c r="E63" s="92" t="s">
+      <c r="E63" s="94" t="s">
         <v>134</v>
       </c>
-      <c r="F63" s="92" t="s">
+      <c r="F63" s="94" t="s">
         <v>34</v>
       </c>
-      <c r="G63" s="92"/>
-      <c r="H63" s="92"/>
-      <c r="I63" s="92"/>
-      <c r="J63" s="92"/>
-      <c r="K63" s="94"/>
-      <c r="L63" s="92"/>
-      <c r="M63" s="92" t="s">
+      <c r="G63" s="94"/>
+      <c r="H63" s="94"/>
+      <c r="I63" s="94"/>
+      <c r="J63" s="94"/>
+      <c r="K63" s="96"/>
+      <c r="L63" s="94"/>
+      <c r="M63" s="94" t="s">
         <v>53</v>
       </c>
-      <c r="N63" s="92"/>
-      <c r="O63" s="92" t="s">
+      <c r="N63" s="94"/>
+      <c r="O63" s="94" t="s">
         <v>135</v>
       </c>
-      <c r="P63" s="92"/>
-      <c r="Q63" s="92"/>
-      <c r="R63" s="92"/>
-      <c r="S63" s="95"/>
+      <c r="P63" s="94"/>
+      <c r="Q63" s="94"/>
+      <c r="R63" s="94"/>
+      <c r="S63" s="97"/>
     </row>
     <row r="64" s="13" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A64" s="92">
+      <c r="A64" s="94">
         <v>30350101</v>
       </c>
-      <c r="B64" s="93">
+      <c r="B64" s="95">
         <v>103501</v>
       </c>
-      <c r="C64" s="93" t="s">
+      <c r="C64" s="95" t="s">
         <v>136</v>
       </c>
-      <c r="D64" s="92">
+      <c r="D64" s="94">
         <v>303503</v>
       </c>
-      <c r="E64" s="92" t="s">
+      <c r="E64" s="94" t="s">
         <v>130</v>
       </c>
-      <c r="F64" s="92" t="s">
+      <c r="F64" s="94" t="s">
         <v>59</v>
       </c>
-      <c r="G64" s="92">
+      <c r="G64" s="94">
         <v>2035012</v>
       </c>
-      <c r="H64" s="92" t="s">
+      <c r="H64" s="94" t="s">
         <v>60</v>
       </c>
-      <c r="I64" s="92" t="s">
+      <c r="I64" s="94" t="s">
         <v>131</v>
       </c>
-      <c r="J64" s="92"/>
-      <c r="K64" s="94" t="s">
+      <c r="J64" s="94"/>
+      <c r="K64" s="96" t="s">
         <v>137</v>
       </c>
-      <c r="L64" s="92" t="s">
+      <c r="L64" s="94" t="s">
         <v>133</v>
       </c>
-      <c r="M64" s="92"/>
-      <c r="N64" s="92"/>
-      <c r="O64" s="92"/>
-      <c r="P64" s="92"/>
-      <c r="Q64" s="92"/>
-      <c r="R64" s="92"/>
-      <c r="S64" s="95"/>
+      <c r="M64" s="94"/>
+      <c r="N64" s="94"/>
+      <c r="O64" s="94"/>
+      <c r="P64" s="94"/>
+      <c r="Q64" s="94"/>
+      <c r="R64" s="94"/>
+      <c r="S64" s="97"/>
     </row>
     <row r="65" s="13" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A65" s="92">
+      <c r="A65" s="94">
         <v>30350102</v>
       </c>
-      <c r="B65" s="93">
+      <c r="B65" s="95">
         <v>103501</v>
       </c>
-      <c r="C65" s="93" t="s">
+      <c r="C65" s="95" t="s">
         <v>136</v>
       </c>
-      <c r="D65" s="92">
+      <c r="D65" s="94">
         <v>303504</v>
       </c>
-      <c r="E65" s="92" t="s">
+      <c r="E65" s="94" t="s">
         <v>134</v>
       </c>
-      <c r="F65" s="92" t="s">
+      <c r="F65" s="94" t="s">
         <v>34</v>
       </c>
-      <c r="G65" s="92"/>
-      <c r="H65" s="92"/>
-      <c r="I65" s="92"/>
-      <c r="J65" s="92"/>
-      <c r="K65" s="94"/>
-      <c r="L65" s="92"/>
-      <c r="M65" s="92" t="s">
+      <c r="G65" s="94"/>
+      <c r="H65" s="94"/>
+      <c r="I65" s="94"/>
+      <c r="J65" s="94"/>
+      <c r="K65" s="96"/>
+      <c r="L65" s="94"/>
+      <c r="M65" s="94" t="s">
         <v>53</v>
       </c>
-      <c r="N65" s="92"/>
-      <c r="O65" s="92" t="s">
+      <c r="N65" s="94"/>
+      <c r="O65" s="94" t="s">
         <v>135</v>
       </c>
-      <c r="P65" s="92"/>
-      <c r="Q65" s="92"/>
-      <c r="R65" s="92"/>
-      <c r="S65" s="95"/>
+      <c r="P65" s="94"/>
+      <c r="Q65" s="94"/>
+      <c r="R65" s="94"/>
+      <c r="S65" s="97"/>
     </row>
     <row r="66" s="14" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A66" s="96">
+      <c r="A66" s="98">
         <v>30360001</v>
       </c>
-      <c r="B66" s="97">
+      <c r="B66" s="99">
         <v>103600</v>
       </c>
-      <c r="C66" s="97" t="s">
+      <c r="C66" s="99" t="s">
         <v>138</v>
       </c>
-      <c r="D66" s="96">
+      <c r="D66" s="98">
         <v>303601</v>
       </c>
-      <c r="E66" s="96" t="s">
+      <c r="E66" s="98" t="s">
         <v>139</v>
       </c>
-      <c r="F66" s="96" t="s">
+      <c r="F66" s="98" t="s">
         <v>108</v>
       </c>
-      <c r="G66" s="96">
+      <c r="G66" s="98">
         <v>2036002</v>
       </c>
-      <c r="H66" s="96" t="s">
+      <c r="H66" s="98" t="s">
         <v>60</v>
       </c>
-      <c r="I66" s="96" t="s">
+      <c r="I66" s="98" t="s">
         <v>139</v>
       </c>
-      <c r="J66" s="96"/>
-      <c r="K66" s="98">
+      <c r="J66" s="98"/>
+      <c r="K66" s="100">
         <v>10360005</v>
       </c>
-      <c r="L66" s="96" t="s">
+      <c r="L66" s="98" t="s">
         <v>140</v>
       </c>
-      <c r="M66" s="96"/>
-      <c r="N66" s="96"/>
-      <c r="O66" s="96"/>
-      <c r="P66" s="96"/>
-      <c r="Q66" s="96"/>
-      <c r="R66" s="96"/>
-      <c r="S66" s="99"/>
+      <c r="M66" s="98"/>
+      <c r="N66" s="98"/>
+      <c r="O66" s="98"/>
+      <c r="P66" s="98"/>
+      <c r="Q66" s="98"/>
+      <c r="R66" s="98"/>
+      <c r="S66" s="101"/>
+    </row>
+    <row r="67" s="15" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A67" s="102">
+        <v>30280001</v>
+      </c>
+      <c r="B67" s="103">
+        <v>102800</v>
+      </c>
+      <c r="C67" s="103" t="s">
+        <v>141</v>
+      </c>
+      <c r="D67" s="102">
+        <v>302801</v>
+      </c>
+      <c r="E67" s="102" t="s">
+        <v>107</v>
+      </c>
+      <c r="F67" s="102" t="s">
+        <v>108</v>
+      </c>
+      <c r="G67" s="102">
+        <v>2028001</v>
+      </c>
+      <c r="H67" s="102" t="s">
+        <v>60</v>
+      </c>
+      <c r="I67" s="102" t="s">
+        <v>80</v>
+      </c>
+      <c r="J67" s="102"/>
+      <c r="K67" s="104" t="s">
+        <v>142</v>
+      </c>
+      <c r="L67" s="102" t="s">
+        <v>143</v>
+      </c>
+      <c r="M67" s="102"/>
+      <c r="N67" s="102"/>
+      <c r="O67" s="102"/>
+      <c r="P67" s="102"/>
+      <c r="Q67" s="102"/>
+      <c r="R67" s="102"/>
+      <c r="S67" s="105"/>
+    </row>
+    <row r="68" s="15" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A68" s="102">
+        <v>30280002</v>
+      </c>
+      <c r="B68" s="103">
+        <v>102800</v>
+      </c>
+      <c r="C68" s="103" t="s">
+        <v>141</v>
+      </c>
+      <c r="D68" s="102">
+        <v>302802</v>
+      </c>
+      <c r="E68" s="102" t="s">
+        <v>127</v>
+      </c>
+      <c r="F68" s="102" t="s">
+        <v>79</v>
+      </c>
+      <c r="G68" s="102">
+        <v>2028001</v>
+      </c>
+      <c r="H68" s="102" t="s">
+        <v>60</v>
+      </c>
+      <c r="I68" s="102" t="s">
+        <v>80</v>
+      </c>
+      <c r="J68" s="102"/>
+      <c r="K68" s="104" t="s">
+        <v>142</v>
+      </c>
+      <c r="L68" s="102" t="s">
+        <v>143</v>
+      </c>
+      <c r="M68" s="102"/>
+      <c r="N68" s="102"/>
+      <c r="O68" s="102"/>
+      <c r="P68" s="102"/>
+      <c r="Q68" s="102"/>
+      <c r="R68" s="102"/>
+      <c r="S68" s="105"/>
+    </row>
+    <row r="69" s="15" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A69" s="102">
+        <v>30280003</v>
+      </c>
+      <c r="B69" s="103">
+        <v>102800</v>
+      </c>
+      <c r="C69" s="103" t="s">
+        <v>141</v>
+      </c>
+      <c r="D69" s="102">
+        <v>302803</v>
+      </c>
+      <c r="E69" s="102" t="s">
+        <v>128</v>
+      </c>
+      <c r="F69" s="102" t="s">
+        <v>83</v>
+      </c>
+      <c r="G69" s="102">
+        <v>2028001</v>
+      </c>
+      <c r="H69" s="102" t="s">
+        <v>60</v>
+      </c>
+      <c r="I69" s="102" t="s">
+        <v>80</v>
+      </c>
+      <c r="J69" s="102"/>
+      <c r="K69" s="104" t="s">
+        <v>142</v>
+      </c>
+      <c r="L69" s="102" t="s">
+        <v>143</v>
+      </c>
+      <c r="M69" s="102"/>
+      <c r="N69" s="102"/>
+      <c r="O69" s="102"/>
+      <c r="P69" s="102"/>
+      <c r="Q69" s="102"/>
+      <c r="R69" s="102"/>
+      <c r="S69" s="105"/>
+    </row>
+    <row r="70" s="16" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A70" s="106">
+        <v>30200001</v>
+      </c>
+      <c r="B70" s="107">
+        <v>102000</v>
+      </c>
+      <c r="C70" s="107" t="s">
+        <v>144</v>
+      </c>
+      <c r="D70" s="106">
+        <v>302001</v>
+      </c>
+      <c r="E70" s="106" t="s">
+        <v>145</v>
+      </c>
+      <c r="F70" s="106" t="s">
+        <v>108</v>
+      </c>
+      <c r="G70" s="106">
+        <v>2020002</v>
+      </c>
+      <c r="H70" s="106" t="s">
+        <v>60</v>
+      </c>
+      <c r="I70" s="106" t="s">
+        <v>80</v>
+      </c>
+      <c r="J70" s="106"/>
+      <c r="K70" s="108"/>
+      <c r="L70" s="106"/>
+      <c r="M70" s="106"/>
+      <c r="N70" s="106"/>
+      <c r="O70" s="106"/>
+      <c r="P70" s="106"/>
+      <c r="Q70" s="106"/>
+      <c r="R70" s="106"/>
+      <c r="S70" s="109"/>
+    </row>
+    <row r="71" s="16" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A71" s="106">
+        <v>30200002</v>
+      </c>
+      <c r="B71" s="107">
+        <v>102000</v>
+      </c>
+      <c r="C71" s="107" t="s">
+        <v>144</v>
+      </c>
+      <c r="D71" s="106">
+        <v>302002</v>
+      </c>
+      <c r="E71" s="106" t="s">
+        <v>146</v>
+      </c>
+      <c r="F71" s="106" t="s">
+        <v>108</v>
+      </c>
+      <c r="G71" s="106">
+        <v>2020003</v>
+      </c>
+      <c r="H71" s="106" t="s">
+        <v>60</v>
+      </c>
+      <c r="I71" s="106" t="s">
+        <v>80</v>
+      </c>
+      <c r="J71" s="106"/>
+      <c r="K71" s="108"/>
+      <c r="L71" s="106"/>
+      <c r="M71" s="106"/>
+      <c r="N71" s="106"/>
+      <c r="O71" s="106"/>
+      <c r="P71" s="106"/>
+      <c r="Q71" s="106"/>
+      <c r="R71" s="106"/>
+      <c r="S71" s="109"/>
+    </row>
+    <row r="72" spans="1:19">
+      <c r="F72" s="3"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2">
@@ -4970,10 +5236,10 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="B1" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -4981,7 +5247,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -4989,7 +5255,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:8">
@@ -4997,16 +5263,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:8">
@@ -5014,16 +5280,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:8">
@@ -5031,16 +5297,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:8">
@@ -5048,16 +5314,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="F7" s="1">
         <v>2</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:8">
@@ -5065,16 +5331,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="F8" s="1">
         <v>3</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:8">
@@ -5082,16 +5348,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="F9" s="1">
         <v>4</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:8">
@@ -5099,16 +5365,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="F10" s="1">
         <v>5</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:8">
@@ -5116,16 +5382,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="F11" s="1">
         <v>6</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:8">
@@ -5133,16 +5399,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="F12" s="1">
         <v>7</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:8">
@@ -5150,16 +5416,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="F13" s="1">
         <v>8</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:8">
@@ -5167,16 +5433,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="F14" s="1">
         <v>9</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:8">
@@ -5184,16 +5450,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="F15" s="1">
         <v>10</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:8">
@@ -5201,16 +5467,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="F16" s="1">
         <v>11</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:8">
@@ -5218,16 +5484,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="F17" s="1">
         <v>12</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:8">
@@ -5235,16 +5501,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="F18" s="1">
         <v>13</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:8">
@@ -5252,16 +5518,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="F19" s="1">
         <v>14</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:8">
@@ -5269,16 +5535,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="F20" s="1">
         <v>15</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:8">
@@ -5286,16 +5552,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="F21" s="1">
         <v>16</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:8">
@@ -5303,16 +5569,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="F22" s="1">
         <v>17</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:8">
@@ -5320,16 +5586,16 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="F23" s="1">
         <v>18</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:8">
@@ -5337,16 +5603,16 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="F24" s="1">
         <v>19</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -5354,7 +5620,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -5362,7 +5628,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -5370,7 +5636,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -5378,7 +5644,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -5386,7 +5652,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -5394,7 +5660,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -5402,7 +5668,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -5410,7 +5676,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -5418,7 +5684,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -5426,7 +5692,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -5434,7 +5700,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -5442,7 +5708,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -5450,7 +5716,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -5458,7 +5724,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -5466,7 +5732,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -5474,7 +5740,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -5482,7 +5748,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -5490,7 +5756,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -5498,7 +5764,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -5506,7 +5772,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -5514,7 +5780,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -5522,7 +5788,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -5530,7 +5796,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialAuxiliary.xlsx
+++ b/slots/resources/sample/SpecialAuxiliary.xlsx
@@ -268,7 +268,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="669" uniqueCount="275">
   <si>
     <t>小游戏模式ID</t>
   </si>
@@ -303,7 +303,7 @@
     <t>奖励类型B</t>
   </si>
   <si>
-    <t>单线押分倍数，中奖权重，最大出现次数，根据配置额外增加</t>
+    <t>奖励类型C:  单线押分倍数，中奖权重，最大出现次数，根据配置额外增加</t>
   </si>
   <si>
     <t>赋予值类型</t>
@@ -378,30 +378,33 @@
     <t>拉火车绿火车MINI，随几次为几节车厢</t>
   </si>
   <si>
+    <t>总奖励 = 次数×(TypeC + TypeA + TypeB) * 赋予值类型押分</t>
+  </si>
+  <si>
+    <t>5_0|6_8|7_18|8_12|9_6|10_3|11_2|12_1</t>
+  </si>
+  <si>
+    <t>车厢数量</t>
+  </si>
+  <si>
+    <t>40_200_1|50_500_2|60_1300_3|70_1500_4|80_1500_4|90_1500_4|100_1500_4|110_1000_4|120_1000_4|130_0_0|150_0_0|200_0_0</t>
+  </si>
+  <si>
+    <t>1_0</t>
+  </si>
+  <si>
+    <t>单线押分倍数*单线押分 = 奖励金额</t>
+  </si>
+  <si>
+    <t>拉火车-蓝火车</t>
+  </si>
+  <si>
+    <t>拉火车蓝火车MINOR</t>
+  </si>
+  <si>
     <t>总奖励 = 次数×(TypeC + TypeA + TypeB)</t>
   </si>
   <si>
-    <t>5_0|6_8|7_18|8_12|9_6|10_3|11_2|12_1</t>
-  </si>
-  <si>
-    <t>车厢数量</t>
-  </si>
-  <si>
-    <t>40_200_1|50_500_2|60_1300_3|70_1500_4|80_1500_4|90_1500_4|100_1500_4|110_1000_4|120_1000_4|130_0_0|150_0_0|200_0_0</t>
-  </si>
-  <si>
-    <t>1_0</t>
-  </si>
-  <si>
-    <t>单线押分倍数*单线押分 = 奖励金额</t>
-  </si>
-  <si>
-    <t>拉火车-蓝火车</t>
-  </si>
-  <si>
-    <t>拉火车蓝火车MINOR</t>
-  </si>
-  <si>
     <t>40_0_0|50_0_0|60_1000_3|70_1500_4|80_2000_4|90_2000_4|100_1500_4|110_1000_4|120_1000_4|130_0_0|150_0_0|200_0_0</t>
   </si>
   <si>
@@ -636,10 +639,10 @@
     <t>15_1</t>
   </si>
   <si>
-    <t>免费游戏-免费旋转-20次</t>
-  </si>
-  <si>
-    <t>20_1</t>
+    <t>免费游戏-免费旋转-25次</t>
+  </si>
+  <si>
+    <t>25_1</t>
   </si>
   <si>
     <t>蒸汽时代</t>
@@ -705,10 +708,124 @@
     <t>宙斯vs哈迪斯</t>
   </si>
   <si>
+    <t>普通模式vs1改出宙斯或哈迪斯大图标-第1轴</t>
+  </si>
+  <si>
+    <t>普通模式</t>
+  </si>
+  <si>
+    <t>第1轴改出宙斯、哈迪斯大图标</t>
+  </si>
+  <si>
+    <t>普通模式vs1改出宙斯或哈迪斯大图标-第2轴</t>
+  </si>
+  <si>
+    <t>第2轴改出宙斯、哈迪斯大图标</t>
+  </si>
+  <si>
+    <t>普通模式vs1改出宙斯或哈迪斯大图标-第3轴</t>
+  </si>
+  <si>
+    <t>第3轴改出宙斯、哈迪斯大图标</t>
+  </si>
+  <si>
+    <t>普通模式vs1改出宙斯或哈迪斯大图标-第4轴</t>
+  </si>
+  <si>
+    <t>第4轴改出宙斯、哈迪斯大图标</t>
+  </si>
+  <si>
+    <t>宙斯大图标玩法 - 普通</t>
+  </si>
+  <si>
+    <t>2_500_1|3_200_1|4_100_1|5_50_1|6_30_1|7_15_1|8_10_1</t>
+  </si>
+  <si>
+    <t>哈迪斯大图标玩法 - 普通</t>
+  </si>
+  <si>
+    <t>随机修改两个wild</t>
+  </si>
+  <si>
     <t>免费游戏-宙斯玩法</t>
   </si>
   <si>
+    <t>10200001|10200017|10200018|10200019|10200020</t>
+  </si>
+  <si>
+    <t>概率出现wild+概率在12345轴上改出vs -免费宙斯</t>
+  </si>
+  <si>
+    <t>免费模式  把 vs1变成 宙斯 大图标-第1轴</t>
+  </si>
+  <si>
+    <t>第1轴改出宙斯</t>
+  </si>
+  <si>
+    <t>4_500_1|6_200_1|8_100_1|10_50_1|12_30_1|14_15_1|16_10_1</t>
+  </si>
+  <si>
+    <t>免费模式  把 vs1变成 宙斯 大图标-第2轴</t>
+  </si>
+  <si>
+    <t>第2轴改出宙斯</t>
+  </si>
+  <si>
+    <t>免费模式  把 vs1变成 宙斯 大图标-第3轴</t>
+  </si>
+  <si>
+    <t>第3轴改出宙斯</t>
+  </si>
+  <si>
+    <t>免费模式  把 vs1变成 宙斯 大图标-第4轴</t>
+  </si>
+  <si>
+    <t>第4轴改出宙斯</t>
+  </si>
+  <si>
     <t>免费游戏-哈迪斯玩法</t>
+  </si>
+  <si>
+    <t>10200001|10200022|10200023|10200024|10200025</t>
+  </si>
+  <si>
+    <t>概率出现wild+概率在12345轴上改出vs</t>
+  </si>
+  <si>
+    <t>免费模式 VS1-哈迪斯 大图标第1轴</t>
+  </si>
+  <si>
+    <t>10200125|10200026</t>
+  </si>
+  <si>
+    <t>第1轴改出哈迪斯+随机修改两个wild</t>
+  </si>
+  <si>
+    <t>免费模式 VS1-哈迪斯 大图标第2轴</t>
+  </si>
+  <si>
+    <t>10200225|10200026</t>
+  </si>
+  <si>
+    <t>第2轴改出哈迪斯+随机修改两个wild</t>
+  </si>
+  <si>
+    <t>免费模式 VS1-哈迪斯 大图标第3轴</t>
+  </si>
+  <si>
+    <t>10200325|10200026</t>
+  </si>
+  <si>
+    <t>第3轴改出哈迪斯+随机修改两个wild</t>
+  </si>
+  <si>
+    <t>免费模式 VS1-哈迪斯 大图标第4轴</t>
+  </si>
+  <si>
+    <t>10200425|10200026</t>
+  </si>
+  <si>
+    <t>第4轴改出哈迪斯+随机修改两个wild</t>
   </si>
   <si>
     <t>typeID</t>
@@ -1171,8 +1288,14 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1183,7 +1306,15 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1194,22 +1325,8 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="51">
+  <fills count="50">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1285,12 +1402,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFCFE09A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE42EF0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1641,7 +1752,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1665,16 +1776,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1683,92 +1794,92 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="110">
+  <cellXfs count="121">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1787,6 +1898,7 @@
     <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1824,6 +1936,18 @@
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="1" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
@@ -1831,15 +1955,11 @@
     <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="176" fontId="1" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1847,22 +1967,14 @@
     <xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1981,6 +2093,14 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
@@ -1989,6 +2109,16 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="176" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="52">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2328,7 +2458,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S72"/>
+  <dimension ref="A1:S92"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14.125" customWidth="1"/>
@@ -2340,15 +2470,15 @@
     <col min="8" max="8" width="16.25" customWidth="1"/>
     <col min="9" max="9" width="29.375" customWidth="1"/>
     <col min="10" max="10" width="42.5" customWidth="1"/>
-    <col min="11" max="11" width="41.25" style="17" customWidth="1"/>
-    <col min="12" max="12" width="36.0333333333333" style="3" customWidth="1"/>
+    <col min="11" max="11" width="41.25" style="18" customWidth="1"/>
+    <col min="12" max="12" width="45.2916666666667" style="3" customWidth="1"/>
     <col min="13" max="13" width="34.4083333333333" style="3" customWidth="1"/>
     <col min="14" max="14" width="7.93333333333333" style="3" customWidth="1"/>
     <col min="15" max="15" width="11.325" customWidth="1"/>
     <col min="16" max="16" width="8.96666666666667" customWidth="1"/>
     <col min="17" max="17" width="93.375" customWidth="1"/>
     <col min="18" max="18" width="10.625" customWidth="1"/>
-    <col min="19" max="19" width="23.75" style="18" customWidth="1"/>
+    <col min="19" max="19" width="23.75" style="19" customWidth="1"/>
     <col min="20" max="20" width="60.875" customWidth="1"/>
     <col min="21" max="22" width="11.5"/>
   </cols>
@@ -2357,2824 +2487,3462 @@
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19" t="s">
+      <c r="C1" s="20"/>
+      <c r="D1" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19" t="s">
+      <c r="E1" s="20"/>
+      <c r="F1" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="G1" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19" t="s">
+      <c r="H1" s="20"/>
+      <c r="I1" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="20" t="s">
+      <c r="J1" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="21" t="s">
+      <c r="K1" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19" t="s">
+      <c r="L1" s="20"/>
+      <c r="M1" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="19"/>
-      <c r="O1" s="22" t="s">
+      <c r="N1" s="20"/>
+      <c r="O1" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="22" t="s">
+      <c r="P1" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="Q1" s="22" t="s">
+      <c r="Q1" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="R1" s="23" t="s">
+      <c r="R1" s="24" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="2" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19" t="s">
+      <c r="C2" s="20"/>
+      <c r="D2" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="19"/>
-      <c r="F2" s="22" t="s">
+      <c r="E2" s="20"/>
+      <c r="F2" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="19" t="s">
+      <c r="G2" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="25" t="s">
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="26" t="s">
+      <c r="K2" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="L2" s="22"/>
-      <c r="M2" s="25" t="s">
+      <c r="L2" s="23"/>
+      <c r="M2" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="N2" s="19"/>
-      <c r="O2" s="22" t="s">
+      <c r="N2" s="20"/>
+      <c r="O2" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="P2" s="22" t="s">
+      <c r="P2" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="Q2" s="25" t="s">
+      <c r="Q2" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="R2" s="23" t="s">
+      <c r="R2" s="24" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="3" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="27" t="s">
+      <c r="B3" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27" t="s">
+      <c r="C3" s="28"/>
+      <c r="D3" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="27"/>
-      <c r="F3" s="27" t="s">
+      <c r="E3" s="28"/>
+      <c r="F3" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="28" t="s">
+      <c r="G3" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="27"/>
-      <c r="I3" s="27"/>
-      <c r="J3" s="29" t="s">
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="30" t="s">
+      <c r="K3" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="L3" s="27"/>
-      <c r="M3" s="27" t="s">
+      <c r="L3" s="28"/>
+      <c r="M3" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="N3" s="27"/>
-      <c r="O3" s="22" t="s">
+      <c r="N3" s="28"/>
+      <c r="O3" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="P3" s="22" t="s">
+      <c r="P3" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="Q3" s="22" t="s">
+      <c r="Q3" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="R3" s="31" t="s">
+      <c r="R3" s="32" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="4" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="19"/>
-      <c r="I4" s="19"/>
-      <c r="J4" s="32"/>
-      <c r="K4" s="21"/>
-      <c r="L4" s="19"/>
-      <c r="M4" s="19"/>
-      <c r="N4" s="19"/>
-      <c r="O4" s="19"/>
-      <c r="P4" s="19"/>
-      <c r="Q4" s="19"/>
-      <c r="R4" s="19"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="33"/>
+      <c r="K4" s="22"/>
+      <c r="L4" s="20"/>
+      <c r="M4" s="20"/>
+      <c r="N4" s="20"/>
+      <c r="O4" s="20"/>
+      <c r="P4" s="20"/>
+      <c r="Q4" s="20"/>
+      <c r="R4" s="20"/>
     </row>
     <row r="5" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A5" s="33">
+      <c r="A5" s="34">
         <v>30010001</v>
       </c>
-      <c r="B5" s="34">
+      <c r="B5" s="35">
         <v>100100</v>
       </c>
-      <c r="C5" s="34" t="s">
+      <c r="C5" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="33">
+      <c r="D5" s="34">
         <v>31001</v>
       </c>
-      <c r="E5" s="33" t="s">
+      <c r="E5" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="33" t="s">
+      <c r="F5" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="G5" s="33"/>
-      <c r="H5" s="33"/>
-      <c r="I5" s="33" t="s">
+      <c r="G5" s="34"/>
+      <c r="H5" s="34"/>
+      <c r="I5" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="J5" s="33"/>
-      <c r="K5" s="35"/>
-      <c r="L5" s="19" t="s">
+      <c r="J5" s="34"/>
+      <c r="K5" s="36"/>
+      <c r="L5" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="M5" s="33" t="s">
+      <c r="M5" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="N5" s="33" t="s">
+      <c r="N5" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="O5" s="33"/>
-      <c r="P5" s="33"/>
-      <c r="Q5" s="36" t="s">
+      <c r="O5" s="34"/>
+      <c r="P5" s="34"/>
+      <c r="Q5" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="R5" s="37" t="s">
+      <c r="R5" s="38" t="s">
         <v>40</v>
       </c>
-      <c r="S5" s="38" t="s">
+      <c r="S5" s="39" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="6" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A6" s="33">
+      <c r="A6" s="34">
         <v>30010002</v>
       </c>
-      <c r="B6" s="34">
+      <c r="B6" s="35">
         <v>100100</v>
       </c>
-      <c r="C6" s="34" t="s">
+      <c r="C6" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="33">
+      <c r="D6" s="34">
         <v>31002</v>
       </c>
-      <c r="E6" s="33" t="s">
+      <c r="E6" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="F6" s="33" t="s">
+      <c r="F6" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="G6" s="33"/>
-      <c r="H6" s="33"/>
-      <c r="I6" s="33" t="s">
+      <c r="G6" s="34"/>
+      <c r="H6" s="34"/>
+      <c r="I6" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="J6" s="33"/>
-      <c r="K6" s="35"/>
-      <c r="L6" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="M6" s="33" t="s">
+      <c r="J6" s="34"/>
+      <c r="K6" s="36"/>
+      <c r="L6" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="M6" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="N6" s="33" t="s">
+      <c r="N6" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="O6" s="33"/>
-      <c r="P6" s="33"/>
-      <c r="Q6" s="36" t="s">
+      <c r="O6" s="34"/>
+      <c r="P6" s="34"/>
+      <c r="Q6" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="R6" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="S6" s="39"/>
+    </row>
+    <row r="7" s="3" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A7" s="34">
+        <v>30010003</v>
+      </c>
+      <c r="B7" s="35">
+        <v>100100</v>
+      </c>
+      <c r="C7" s="35" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="34">
+        <v>31003</v>
+      </c>
+      <c r="E7" s="34" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" s="34"/>
+      <c r="H7" s="34"/>
+      <c r="I7" s="34" t="s">
+        <v>47</v>
+      </c>
+      <c r="J7" s="34"/>
+      <c r="K7" s="36"/>
+      <c r="L7" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="R6" s="37" t="s">
+      <c r="M7" s="34" t="s">
+        <v>37</v>
+      </c>
+      <c r="N7" s="34" t="s">
+        <v>38</v>
+      </c>
+      <c r="O7" s="34"/>
+      <c r="P7" s="34"/>
+      <c r="Q7" s="37" t="s">
+        <v>48</v>
+      </c>
+      <c r="R7" s="38" t="s">
         <v>40</v>
       </c>
-      <c r="S6" s="38"/>
-    </row>
-    <row r="7" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A7" s="33">
-        <v>30010003</v>
-      </c>
-      <c r="B7" s="34">
+      <c r="S7" s="39"/>
+    </row>
+    <row r="8" s="3" customFormat="1" ht="15" customHeight="1" spans="1:19">
+      <c r="A8" s="34">
+        <v>30010004</v>
+      </c>
+      <c r="B8" s="35">
         <v>100100</v>
       </c>
-      <c r="C7" s="34" t="s">
+      <c r="C8" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="33">
-        <v>31003</v>
-      </c>
-      <c r="E7" s="33" t="s">
-        <v>45</v>
-      </c>
-      <c r="F7" s="33" t="s">
+      <c r="D8" s="34">
+        <v>31004</v>
+      </c>
+      <c r="E8" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="F8" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="G7" s="33"/>
-      <c r="H7" s="33"/>
-      <c r="I7" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="J7" s="33"/>
-      <c r="K7" s="35"/>
-      <c r="L7" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="M7" s="33" t="s">
+      <c r="G8" s="34"/>
+      <c r="H8" s="34"/>
+      <c r="I8" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="J8" s="34"/>
+      <c r="K8" s="36"/>
+      <c r="L8" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="M8" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="N7" s="33" t="s">
+      <c r="N8" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="O7" s="33"/>
-      <c r="P7" s="33"/>
-      <c r="Q7" s="36" t="s">
-        <v>47</v>
-      </c>
-      <c r="R7" s="37" t="s">
+      <c r="O8" s="34"/>
+      <c r="P8" s="34"/>
+      <c r="Q8" s="37" t="s">
+        <v>51</v>
+      </c>
+      <c r="R8" s="38" t="s">
         <v>40</v>
       </c>
-      <c r="S7" s="38"/>
-    </row>
-    <row r="8" s="3" customFormat="1" ht="15" customHeight="1" spans="1:19">
-      <c r="A8" s="33">
-        <v>30010004</v>
-      </c>
-      <c r="B8" s="34">
+      <c r="S8" s="39"/>
+    </row>
+    <row r="9" s="3" customFormat="1" ht="15" customHeight="1" spans="1:19">
+      <c r="A9" s="20">
+        <v>30010005</v>
+      </c>
+      <c r="B9" s="32">
         <v>100100</v>
       </c>
-      <c r="C8" s="34" t="s">
+      <c r="C9" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="33">
-        <v>31004</v>
-      </c>
-      <c r="E8" s="33" t="s">
-        <v>48</v>
-      </c>
-      <c r="F8" s="33" t="s">
+      <c r="D9" s="20">
+        <v>31101</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="G8" s="33"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="33" t="s">
-        <v>49</v>
-      </c>
-      <c r="J8" s="33"/>
-      <c r="K8" s="35"/>
-      <c r="L8" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="M8" s="33" t="s">
-        <v>37</v>
-      </c>
-      <c r="N8" s="33" t="s">
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="J9" s="20"/>
+      <c r="K9" s="22"/>
+      <c r="L9" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="M9" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="N9" s="20"/>
+      <c r="O9" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="P9" s="20"/>
+      <c r="Q9" s="23"/>
+      <c r="R9" s="23"/>
+      <c r="S9" s="39"/>
+    </row>
+    <row r="10" s="3" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A10" s="40">
+        <v>30010006</v>
+      </c>
+      <c r="B10" s="41">
+        <v>100100</v>
+      </c>
+      <c r="C10" s="35" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" s="40">
+        <v>31102</v>
+      </c>
+      <c r="E10" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10" s="40" t="s">
+        <v>34</v>
+      </c>
+      <c r="G10" s="40"/>
+      <c r="H10" s="40"/>
+      <c r="I10" s="40" t="s">
+        <v>57</v>
+      </c>
+      <c r="J10" s="40"/>
+      <c r="K10" s="42"/>
+      <c r="L10" s="40" t="s">
+        <v>44</v>
+      </c>
+      <c r="M10" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="N10" s="40" t="s">
         <v>38</v>
       </c>
-      <c r="O8" s="33"/>
-      <c r="P8" s="33"/>
-      <c r="Q8" s="36" t="s">
-        <v>50</v>
-      </c>
-      <c r="R8" s="37" t="s">
-        <v>40</v>
-      </c>
-      <c r="S8" s="38"/>
-    </row>
-    <row r="9" s="3" customFormat="1" ht="15" customHeight="1" spans="1:19">
-      <c r="A9" s="19">
-        <v>30010005</v>
-      </c>
-      <c r="B9" s="31">
+      <c r="O10" s="40" t="s">
+        <v>55</v>
+      </c>
+      <c r="P10" s="40"/>
+      <c r="Q10" s="40"/>
+      <c r="R10" s="20"/>
+      <c r="S10" s="39"/>
+    </row>
+    <row r="11" s="3" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A11" s="43">
+        <v>30010007</v>
+      </c>
+      <c r="B11" s="44">
         <v>100100</v>
       </c>
-      <c r="C9" s="34" t="s">
+      <c r="C11" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="19">
-        <v>31101</v>
-      </c>
-      <c r="E9" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="F9" s="19" t="s">
+      <c r="D11" s="45">
+        <v>31201</v>
+      </c>
+      <c r="E11" s="45" t="s">
+        <v>59</v>
+      </c>
+      <c r="F11" s="43" t="s">
+        <v>60</v>
+      </c>
+      <c r="G11" s="43">
+        <v>2001001</v>
+      </c>
+      <c r="H11" s="43" t="s">
+        <v>61</v>
+      </c>
+      <c r="I11" s="43" t="s">
+        <v>62</v>
+      </c>
+      <c r="J11" s="43"/>
+      <c r="K11" s="46">
+        <v>10010091</v>
+      </c>
+      <c r="L11" s="43"/>
+      <c r="M11" s="43"/>
+      <c r="N11" s="43"/>
+      <c r="O11" s="43"/>
+      <c r="P11" s="43"/>
+      <c r="Q11" s="43"/>
+      <c r="R11" s="20"/>
+      <c r="S11" s="39"/>
+    </row>
+    <row r="12" s="3" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A12" s="47">
+        <v>30010008</v>
+      </c>
+      <c r="B12" s="48">
+        <v>100100</v>
+      </c>
+      <c r="C12" s="35" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="45">
+        <v>31202</v>
+      </c>
+      <c r="E12" s="45" t="s">
+        <v>63</v>
+      </c>
+      <c r="F12" s="47" t="s">
+        <v>54</v>
+      </c>
+      <c r="G12" s="47">
+        <v>2001001</v>
+      </c>
+      <c r="H12" s="47" t="s">
+        <v>61</v>
+      </c>
+      <c r="I12" s="47" t="s">
+        <v>64</v>
+      </c>
+      <c r="J12" s="47"/>
+      <c r="K12" s="49" t="s">
+        <v>65</v>
+      </c>
+      <c r="L12" s="47"/>
+      <c r="M12" s="47"/>
+      <c r="N12" s="47"/>
+      <c r="O12" s="47"/>
+      <c r="P12" s="47"/>
+      <c r="Q12" s="47"/>
+      <c r="R12" s="20"/>
+      <c r="S12" s="39"/>
+    </row>
+    <row r="13" s="3" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A13" s="50">
+        <v>30010009</v>
+      </c>
+      <c r="B13" s="51">
+        <v>100100</v>
+      </c>
+      <c r="C13" s="35" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" s="45">
+        <v>31203</v>
+      </c>
+      <c r="E13" s="45" t="s">
+        <v>66</v>
+      </c>
+      <c r="F13" s="50" t="s">
+        <v>54</v>
+      </c>
+      <c r="G13" s="50">
+        <v>2001001</v>
+      </c>
+      <c r="H13" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="I13" s="50" t="s">
+        <v>67</v>
+      </c>
+      <c r="J13" s="50"/>
+      <c r="K13" s="52" t="s">
+        <v>68</v>
+      </c>
+      <c r="L13" s="50"/>
+      <c r="M13" s="50"/>
+      <c r="N13" s="50"/>
+      <c r="O13" s="50"/>
+      <c r="P13" s="50"/>
+      <c r="Q13" s="50"/>
+      <c r="R13" s="20"/>
+      <c r="S13" s="39"/>
+    </row>
+    <row r="14" s="3" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A14" s="45">
+        <v>30010010</v>
+      </c>
+      <c r="B14" s="53">
+        <v>100100</v>
+      </c>
+      <c r="C14" s="35" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" s="54">
+        <v>31301</v>
+      </c>
+      <c r="E14" s="54" t="s">
+        <v>69</v>
+      </c>
+      <c r="F14" s="45" t="s">
         <v>34</v>
       </c>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="J9" s="19"/>
-      <c r="K9" s="21"/>
-      <c r="L9" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="M9" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="N9" s="19"/>
-      <c r="O9" s="19" t="s">
+      <c r="G14" s="45"/>
+      <c r="H14" s="45"/>
+      <c r="I14" s="45" t="s">
+        <v>70</v>
+      </c>
+      <c r="J14" s="45"/>
+      <c r="K14" s="55"/>
+      <c r="L14" s="45" t="s">
+        <v>44</v>
+      </c>
+      <c r="M14" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="N14" s="45"/>
+      <c r="O14" s="45"/>
+      <c r="P14" s="45"/>
+      <c r="Q14" s="56" t="s">
+        <v>72</v>
+      </c>
+      <c r="R14" s="57" t="s">
+        <v>73</v>
+      </c>
+      <c r="S14" s="23" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="15" s="3" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A15" s="50">
+        <v>30010011</v>
+      </c>
+      <c r="B15" s="51">
+        <v>100100</v>
+      </c>
+      <c r="C15" s="35" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" s="54">
+        <v>31302</v>
+      </c>
+      <c r="E15" s="54" t="s">
+        <v>75</v>
+      </c>
+      <c r="F15" s="50" t="s">
+        <v>34</v>
+      </c>
+      <c r="G15" s="50"/>
+      <c r="H15" s="50"/>
+      <c r="I15" s="50" t="s">
+        <v>76</v>
+      </c>
+      <c r="J15" s="50"/>
+      <c r="K15" s="52"/>
+      <c r="L15" s="50" t="s">
+        <v>44</v>
+      </c>
+      <c r="M15" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="N15" s="50"/>
+      <c r="O15" s="50"/>
+      <c r="P15" s="50"/>
+      <c r="Q15" s="50"/>
+      <c r="R15" s="20"/>
+      <c r="S15" s="39"/>
+    </row>
+    <row r="16" s="3" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A16" s="50">
+        <v>30010012</v>
+      </c>
+      <c r="B16" s="51">
+        <v>100100</v>
+      </c>
+      <c r="C16" s="35" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" s="54">
+        <v>31303</v>
+      </c>
+      <c r="E16" s="54" t="s">
+        <v>77</v>
+      </c>
+      <c r="F16" s="50" t="s">
         <v>54</v>
       </c>
-      <c r="P9" s="19"/>
-      <c r="Q9" s="22"/>
-      <c r="R9" s="22"/>
-      <c r="S9" s="38"/>
-    </row>
-    <row r="10" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A10" s="39">
-        <v>30010006</v>
-      </c>
-      <c r="B10" s="40">
-        <v>100100</v>
-      </c>
-      <c r="C10" s="34" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" s="39">
-        <v>31102</v>
-      </c>
-      <c r="E10" s="39" t="s">
-        <v>55</v>
-      </c>
-      <c r="F10" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="G10" s="39"/>
-      <c r="H10" s="39"/>
-      <c r="I10" s="39" t="s">
-        <v>56</v>
-      </c>
-      <c r="J10" s="39"/>
-      <c r="K10" s="41"/>
-      <c r="L10" s="39" t="s">
-        <v>36</v>
-      </c>
-      <c r="M10" s="39" t="s">
-        <v>57</v>
-      </c>
-      <c r="N10" s="39" t="s">
-        <v>38</v>
-      </c>
-      <c r="O10" s="39" t="s">
-        <v>54</v>
-      </c>
-      <c r="P10" s="39"/>
-      <c r="Q10" s="39"/>
-      <c r="R10" s="19"/>
-      <c r="S10" s="38"/>
-    </row>
-    <row r="11" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A11" s="42">
-        <v>30010007</v>
-      </c>
-      <c r="B11" s="43">
-        <v>100100</v>
-      </c>
-      <c r="C11" s="34" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11" s="44">
-        <v>31201</v>
-      </c>
-      <c r="E11" s="44" t="s">
-        <v>58</v>
-      </c>
-      <c r="F11" s="42" t="s">
-        <v>59</v>
-      </c>
-      <c r="G11" s="42">
+      <c r="G16" s="50">
         <v>2001001</v>
       </c>
-      <c r="H11" s="42" t="s">
-        <v>60</v>
-      </c>
-      <c r="I11" s="42" t="s">
+      <c r="H16" s="50" t="s">
         <v>61</v>
       </c>
-      <c r="J11" s="42"/>
-      <c r="K11" s="45">
-        <v>10010091</v>
-      </c>
-      <c r="L11" s="42"/>
-      <c r="M11" s="42"/>
-      <c r="N11" s="42"/>
-      <c r="O11" s="42"/>
-      <c r="P11" s="42"/>
-      <c r="Q11" s="42"/>
-      <c r="R11" s="19"/>
-      <c r="S11" s="38"/>
-    </row>
-    <row r="12" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A12" s="46">
-        <v>30010008</v>
-      </c>
-      <c r="B12" s="47">
-        <v>100100</v>
-      </c>
-      <c r="C12" s="34" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" s="44">
-        <v>31202</v>
-      </c>
-      <c r="E12" s="44" t="s">
-        <v>62</v>
-      </c>
-      <c r="F12" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="G12" s="46">
-        <v>2001001</v>
-      </c>
-      <c r="H12" s="46" t="s">
-        <v>60</v>
-      </c>
-      <c r="I12" s="46" t="s">
-        <v>63</v>
-      </c>
-      <c r="J12" s="46"/>
-      <c r="K12" s="48" t="s">
-        <v>64</v>
-      </c>
-      <c r="L12" s="46"/>
-      <c r="M12" s="46"/>
-      <c r="N12" s="46"/>
-      <c r="O12" s="46"/>
-      <c r="P12" s="46"/>
-      <c r="Q12" s="46"/>
-      <c r="R12" s="19"/>
-      <c r="S12" s="38"/>
-    </row>
-    <row r="13" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A13" s="49">
-        <v>30010009</v>
-      </c>
-      <c r="B13" s="50">
-        <v>100100</v>
-      </c>
-      <c r="C13" s="34" t="s">
-        <v>32</v>
-      </c>
-      <c r="D13" s="44">
-        <v>31203</v>
-      </c>
-      <c r="E13" s="44" t="s">
-        <v>65</v>
-      </c>
-      <c r="F13" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="G13" s="49">
-        <v>2001001</v>
-      </c>
-      <c r="H13" s="49" t="s">
-        <v>60</v>
-      </c>
-      <c r="I13" s="49" t="s">
-        <v>66</v>
-      </c>
-      <c r="J13" s="49"/>
-      <c r="K13" s="51" t="s">
+      <c r="I16" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="L13" s="49"/>
-      <c r="M13" s="49"/>
-      <c r="N13" s="49"/>
-      <c r="O13" s="49"/>
-      <c r="P13" s="49"/>
-      <c r="Q13" s="49"/>
-      <c r="R13" s="19"/>
-      <c r="S13" s="38"/>
-    </row>
-    <row r="14" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A14" s="44">
-        <v>30010010</v>
-      </c>
-      <c r="B14" s="52">
-        <v>100100</v>
-      </c>
-      <c r="C14" s="34" t="s">
-        <v>32</v>
-      </c>
-      <c r="D14" s="53">
-        <v>31301</v>
-      </c>
-      <c r="E14" s="53" t="s">
+      <c r="J16" s="50"/>
+      <c r="K16" s="52" t="s">
         <v>68</v>
       </c>
-      <c r="F14" s="44" t="s">
-        <v>34</v>
-      </c>
-      <c r="G14" s="44"/>
-      <c r="H14" s="44"/>
-      <c r="I14" s="44" t="s">
-        <v>69</v>
-      </c>
-      <c r="J14" s="44"/>
-      <c r="K14" s="54"/>
-      <c r="L14" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="M14" s="44" t="s">
-        <v>70</v>
-      </c>
-      <c r="N14" s="44"/>
-      <c r="O14" s="44"/>
-      <c r="P14" s="44"/>
-      <c r="Q14" s="55" t="s">
-        <v>71</v>
-      </c>
-      <c r="R14" s="56" t="s">
-        <v>72</v>
-      </c>
-      <c r="S14" s="22" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="15" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A15" s="49">
-        <v>30010011</v>
-      </c>
-      <c r="B15" s="50">
-        <v>100100</v>
-      </c>
-      <c r="C15" s="34" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" s="53">
-        <v>31302</v>
-      </c>
-      <c r="E15" s="53" t="s">
-        <v>74</v>
-      </c>
-      <c r="F15" s="49" t="s">
-        <v>34</v>
-      </c>
-      <c r="G15" s="49"/>
-      <c r="H15" s="49"/>
-      <c r="I15" s="49" t="s">
-        <v>75</v>
-      </c>
-      <c r="J15" s="49"/>
-      <c r="K15" s="51"/>
-      <c r="L15" s="49" t="s">
-        <v>36</v>
-      </c>
-      <c r="M15" s="49" t="s">
-        <v>57</v>
-      </c>
-      <c r="N15" s="49"/>
-      <c r="O15" s="49"/>
-      <c r="P15" s="49"/>
-      <c r="Q15" s="49"/>
-      <c r="R15" s="19"/>
-      <c r="S15" s="38"/>
-    </row>
-    <row r="16" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A16" s="49">
-        <v>30010012</v>
-      </c>
-      <c r="B16" s="50">
-        <v>100100</v>
-      </c>
-      <c r="C16" s="34" t="s">
-        <v>32</v>
-      </c>
-      <c r="D16" s="53">
-        <v>31303</v>
-      </c>
-      <c r="E16" s="53" t="s">
-        <v>76</v>
-      </c>
-      <c r="F16" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="G16" s="49">
-        <v>2001001</v>
-      </c>
-      <c r="H16" s="49" t="s">
-        <v>60</v>
-      </c>
-      <c r="I16" s="49" t="s">
-        <v>66</v>
-      </c>
-      <c r="J16" s="49"/>
-      <c r="K16" s="51" t="s">
-        <v>67</v>
-      </c>
-      <c r="L16" s="49"/>
-      <c r="M16" s="49"/>
-      <c r="N16" s="49"/>
-      <c r="O16" s="49"/>
-      <c r="P16" s="49"/>
-      <c r="Q16" s="49"/>
-      <c r="R16" s="19"/>
-      <c r="S16" s="38"/>
+      <c r="L16" s="50"/>
+      <c r="M16" s="50"/>
+      <c r="N16" s="50"/>
+      <c r="O16" s="50"/>
+      <c r="P16" s="50"/>
+      <c r="Q16" s="50"/>
+      <c r="R16" s="20"/>
+      <c r="S16" s="39"/>
     </row>
     <row r="17" s="3" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A17" s="19">
+      <c r="A17" s="20">
         <v>30070001</v>
       </c>
       <c r="B17" s="3">
         <v>100700</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D17" s="42">
+        <v>78</v>
+      </c>
+      <c r="D17" s="43">
         <v>34001</v>
       </c>
-      <c r="E17" s="42" t="s">
-        <v>78</v>
-      </c>
-      <c r="F17" s="42" t="s">
+      <c r="E17" s="43" t="s">
         <v>79</v>
       </c>
-      <c r="G17" s="31">
+      <c r="F17" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="G17" s="32">
         <v>2007001</v>
       </c>
-      <c r="H17" s="19" t="s">
-        <v>60</v>
+      <c r="H17" s="20" t="s">
+        <v>61</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="K17" s="57" t="s">
         <v>81</v>
       </c>
+      <c r="K17" s="58" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="18" s="3" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A18" s="19">
+      <c r="A18" s="20">
         <v>30070002</v>
       </c>
       <c r="B18" s="3">
         <v>100700</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D18" s="42">
+        <v>78</v>
+      </c>
+      <c r="D18" s="43">
         <v>34002</v>
       </c>
-      <c r="E18" s="42" t="s">
+      <c r="E18" s="43" t="s">
+        <v>83</v>
+      </c>
+      <c r="F18" s="43" t="s">
+        <v>84</v>
+      </c>
+      <c r="G18" s="32">
+        <v>2007001</v>
+      </c>
+      <c r="H18" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="K18" s="58" t="s">
         <v>82</v>
       </c>
-      <c r="F18" s="42" t="s">
-        <v>83</v>
-      </c>
-      <c r="G18" s="31">
-        <v>2007001</v>
-      </c>
-      <c r="H18" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="K18" s="57" t="s">
-        <v>81</v>
-      </c>
     </row>
     <row r="19" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A19" s="44">
+      <c r="A19" s="45">
         <v>30120001</v>
       </c>
       <c r="B19" s="4">
         <v>101200</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="D19" s="44">
+        <v>85</v>
+      </c>
+      <c r="D19" s="45">
         <v>32001</v>
       </c>
-      <c r="E19" s="44" t="s">
-        <v>85</v>
-      </c>
-      <c r="F19" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="G19" s="52">
+      <c r="E19" s="45" t="s">
+        <v>86</v>
+      </c>
+      <c r="F19" s="45" t="s">
+        <v>54</v>
+      </c>
+      <c r="G19" s="53">
         <v>2012001</v>
       </c>
-      <c r="H19" s="44" t="s">
-        <v>60</v>
-      </c>
-      <c r="I19" s="44" t="s">
-        <v>85</v>
-      </c>
-      <c r="J19" s="44" t="s">
+      <c r="H19" s="45" t="s">
+        <v>61</v>
+      </c>
+      <c r="I19" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="K19" s="58">
+      <c r="J19" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="K19" s="59">
         <v>10120041</v>
       </c>
     </row>
     <row r="20" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A20" s="44">
+      <c r="A20" s="45">
         <v>30120002</v>
       </c>
       <c r="B20" s="4">
         <v>101200</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="D20" s="44">
+        <v>85</v>
+      </c>
+      <c r="D20" s="45">
         <v>32002</v>
       </c>
-      <c r="E20" s="44" t="s">
+      <c r="E20" s="45" t="s">
+        <v>88</v>
+      </c>
+      <c r="F20" s="45" t="s">
+        <v>54</v>
+      </c>
+      <c r="G20" s="53">
+        <v>2012001</v>
+      </c>
+      <c r="H20" s="45" t="s">
+        <v>61</v>
+      </c>
+      <c r="I20" s="45" t="s">
+        <v>88</v>
+      </c>
+      <c r="J20" s="45" t="s">
         <v>87</v>
       </c>
-      <c r="F20" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="G20" s="52">
-        <v>2012001</v>
-      </c>
-      <c r="H20" s="44" t="s">
-        <v>60</v>
-      </c>
-      <c r="I20" s="44" t="s">
-        <v>87</v>
-      </c>
-      <c r="J20" s="44" t="s">
-        <v>86</v>
-      </c>
-      <c r="K20" s="58">
+      <c r="K20" s="59">
         <v>10120042</v>
       </c>
     </row>
     <row r="21" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A21" s="44">
+      <c r="A21" s="45">
         <v>30120003</v>
       </c>
       <c r="B21" s="4">
         <v>101200</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="D21" s="44">
+        <v>85</v>
+      </c>
+      <c r="D21" s="45">
         <v>32003</v>
       </c>
-      <c r="E21" s="44" t="s">
-        <v>88</v>
-      </c>
-      <c r="F21" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="G21" s="52">
+      <c r="E21" s="45" t="s">
+        <v>89</v>
+      </c>
+      <c r="F21" s="45" t="s">
+        <v>54</v>
+      </c>
+      <c r="G21" s="53">
         <v>2012001</v>
       </c>
-      <c r="H21" s="44" t="s">
-        <v>60</v>
-      </c>
-      <c r="I21" s="44" t="s">
-        <v>88</v>
-      </c>
-      <c r="J21" s="44" t="s">
-        <v>86</v>
-      </c>
-      <c r="K21" s="58">
+      <c r="H21" s="45" t="s">
+        <v>61</v>
+      </c>
+      <c r="I21" s="45" t="s">
+        <v>89</v>
+      </c>
+      <c r="J21" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="K21" s="59">
         <v>10120043</v>
       </c>
     </row>
     <row r="22" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A22" s="44">
+      <c r="A22" s="45">
         <v>30120004</v>
       </c>
       <c r="B22" s="4">
         <v>101200</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="D22" s="44">
+        <v>85</v>
+      </c>
+      <c r="D22" s="45">
         <v>32004</v>
       </c>
-      <c r="E22" s="44" t="s">
-        <v>89</v>
-      </c>
-      <c r="F22" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="G22" s="52">
+      <c r="E22" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="F22" s="45" t="s">
+        <v>54</v>
+      </c>
+      <c r="G22" s="53">
         <v>2012001</v>
       </c>
-      <c r="H22" s="44" t="s">
-        <v>60</v>
-      </c>
-      <c r="I22" s="44" t="s">
-        <v>89</v>
-      </c>
-      <c r="J22" s="44" t="s">
-        <v>86</v>
-      </c>
-      <c r="K22" s="58">
+      <c r="H22" s="45" t="s">
+        <v>61</v>
+      </c>
+      <c r="I22" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="J22" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="K22" s="59">
         <v>10120044</v>
       </c>
     </row>
     <row r="23" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A23" s="44">
+      <c r="A23" s="45">
         <v>30120005</v>
       </c>
       <c r="B23" s="4">
         <v>101200</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="D23" s="44">
+        <v>85</v>
+      </c>
+      <c r="D23" s="45">
         <v>32005</v>
       </c>
-      <c r="E23" s="44" t="s">
-        <v>89</v>
-      </c>
-      <c r="F23" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="G23" s="52">
+      <c r="E23" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="F23" s="45" t="s">
+        <v>54</v>
+      </c>
+      <c r="G23" s="53">
         <v>2012001</v>
       </c>
-      <c r="H23" s="44" t="s">
-        <v>60</v>
-      </c>
-      <c r="I23" s="44" t="s">
-        <v>89</v>
-      </c>
-      <c r="J23" s="44" t="s">
-        <v>86</v>
-      </c>
-      <c r="K23" s="58">
+      <c r="H23" s="45" t="s">
+        <v>61</v>
+      </c>
+      <c r="I23" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="J23" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="K23" s="59">
         <v>10120045</v>
       </c>
     </row>
     <row r="24" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A24" s="44">
+      <c r="A24" s="45">
         <v>30120006</v>
       </c>
       <c r="B24" s="4">
         <v>101200</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="D24" s="44">
+        <v>85</v>
+      </c>
+      <c r="D24" s="45">
         <v>32006</v>
       </c>
-      <c r="E24" s="44" t="s">
-        <v>89</v>
-      </c>
-      <c r="F24" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="G24" s="52">
+      <c r="E24" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="F24" s="45" t="s">
+        <v>54</v>
+      </c>
+      <c r="G24" s="53">
         <v>2012001</v>
       </c>
-      <c r="H24" s="44" t="s">
-        <v>60</v>
-      </c>
-      <c r="I24" s="44" t="s">
-        <v>89</v>
-      </c>
-      <c r="J24" s="44" t="s">
-        <v>86</v>
-      </c>
-      <c r="K24" s="58">
+      <c r="H24" s="45" t="s">
+        <v>61</v>
+      </c>
+      <c r="I24" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="J24" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="K24" s="59">
         <v>10120046</v>
       </c>
     </row>
     <row r="25" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A25" s="59">
+      <c r="A25" s="60">
         <v>30120011</v>
       </c>
       <c r="B25" s="5">
         <v>101200</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="D25" s="44">
+        <v>91</v>
+      </c>
+      <c r="D25" s="45">
         <v>32101</v>
       </c>
-      <c r="E25" s="59" t="s">
-        <v>85</v>
-      </c>
-      <c r="F25" s="59" t="s">
-        <v>53</v>
-      </c>
-      <c r="G25" s="60">
+      <c r="E25" s="60" t="s">
+        <v>86</v>
+      </c>
+      <c r="F25" s="60" t="s">
+        <v>54</v>
+      </c>
+      <c r="G25" s="61">
         <v>2012001</v>
       </c>
-      <c r="H25" s="59" t="s">
-        <v>60</v>
-      </c>
-      <c r="I25" s="59" t="s">
-        <v>85</v>
-      </c>
-      <c r="J25" s="59" t="s">
-        <v>91</v>
-      </c>
-      <c r="K25" s="61">
+      <c r="H25" s="60" t="s">
+        <v>61</v>
+      </c>
+      <c r="I25" s="60" t="s">
+        <v>86</v>
+      </c>
+      <c r="J25" s="60" t="s">
+        <v>92</v>
+      </c>
+      <c r="K25" s="62">
         <v>10120041</v>
       </c>
     </row>
     <row r="26" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A26" s="59">
+      <c r="A26" s="60">
         <v>30120012</v>
       </c>
       <c r="B26" s="5">
         <v>101200</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="D26" s="44">
+        <v>91</v>
+      </c>
+      <c r="D26" s="45">
         <v>32102</v>
       </c>
-      <c r="E26" s="59" t="s">
-        <v>87</v>
-      </c>
-      <c r="F26" s="59" t="s">
-        <v>53</v>
-      </c>
-      <c r="G26" s="60">
+      <c r="E26" s="60" t="s">
+        <v>88</v>
+      </c>
+      <c r="F26" s="60" t="s">
+        <v>54</v>
+      </c>
+      <c r="G26" s="61">
         <v>2012001</v>
       </c>
-      <c r="H26" s="59" t="s">
-        <v>60</v>
-      </c>
-      <c r="I26" s="59" t="s">
-        <v>87</v>
-      </c>
-      <c r="J26" s="59" t="s">
-        <v>91</v>
-      </c>
-      <c r="K26" s="61">
+      <c r="H26" s="60" t="s">
+        <v>61</v>
+      </c>
+      <c r="I26" s="60" t="s">
+        <v>88</v>
+      </c>
+      <c r="J26" s="60" t="s">
+        <v>92</v>
+      </c>
+      <c r="K26" s="62">
         <v>10120042</v>
       </c>
     </row>
     <row r="27" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A27" s="59">
+      <c r="A27" s="60">
         <v>30120013</v>
       </c>
       <c r="B27" s="5">
         <v>101200</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="D27" s="44">
+        <v>91</v>
+      </c>
+      <c r="D27" s="45">
         <v>32103</v>
       </c>
-      <c r="E27" s="59" t="s">
-        <v>88</v>
-      </c>
-      <c r="F27" s="59" t="s">
-        <v>53</v>
-      </c>
-      <c r="G27" s="60">
+      <c r="E27" s="60" t="s">
+        <v>89</v>
+      </c>
+      <c r="F27" s="60" t="s">
+        <v>54</v>
+      </c>
+      <c r="G27" s="61">
         <v>2012001</v>
       </c>
-      <c r="H27" s="59" t="s">
-        <v>60</v>
-      </c>
-      <c r="I27" s="59" t="s">
-        <v>88</v>
-      </c>
-      <c r="J27" s="59" t="s">
-        <v>91</v>
-      </c>
-      <c r="K27" s="61">
+      <c r="H27" s="60" t="s">
+        <v>61</v>
+      </c>
+      <c r="I27" s="60" t="s">
+        <v>89</v>
+      </c>
+      <c r="J27" s="60" t="s">
+        <v>92</v>
+      </c>
+      <c r="K27" s="62">
         <v>10120043</v>
       </c>
     </row>
     <row r="28" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A28" s="59">
+      <c r="A28" s="60">
         <v>30120014</v>
       </c>
       <c r="B28" s="5">
         <v>101200</v>
       </c>
       <c r="C28" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D28" s="45">
+        <v>32104</v>
+      </c>
+      <c r="E28" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="D28" s="44">
-        <v>32104</v>
-      </c>
-      <c r="E28" s="59" t="s">
-        <v>89</v>
-      </c>
-      <c r="F28" s="59" t="s">
-        <v>53</v>
-      </c>
-      <c r="G28" s="60">
+      <c r="F28" s="60" t="s">
+        <v>54</v>
+      </c>
+      <c r="G28" s="61">
         <v>2012001</v>
       </c>
-      <c r="H28" s="59" t="s">
-        <v>60</v>
-      </c>
-      <c r="I28" s="59" t="s">
-        <v>89</v>
-      </c>
-      <c r="J28" s="59" t="s">
-        <v>91</v>
-      </c>
-      <c r="K28" s="61">
+      <c r="H28" s="60" t="s">
+        <v>61</v>
+      </c>
+      <c r="I28" s="60" t="s">
+        <v>90</v>
+      </c>
+      <c r="J28" s="60" t="s">
+        <v>92</v>
+      </c>
+      <c r="K28" s="62">
         <v>10120044</v>
       </c>
     </row>
     <row r="29" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A29" s="59">
+      <c r="A29" s="60">
         <v>30120015</v>
       </c>
       <c r="B29" s="5">
         <v>101200</v>
       </c>
       <c r="C29" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D29" s="45">
+        <v>32105</v>
+      </c>
+      <c r="E29" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="D29" s="44">
-        <v>32105</v>
-      </c>
-      <c r="E29" s="59" t="s">
-        <v>89</v>
-      </c>
-      <c r="F29" s="59" t="s">
-        <v>53</v>
-      </c>
-      <c r="G29" s="60">
+      <c r="F29" s="60" t="s">
+        <v>54</v>
+      </c>
+      <c r="G29" s="61">
         <v>2012001</v>
       </c>
-      <c r="H29" s="59" t="s">
-        <v>60</v>
-      </c>
-      <c r="I29" s="59" t="s">
-        <v>89</v>
-      </c>
-      <c r="J29" s="59" t="s">
-        <v>91</v>
-      </c>
-      <c r="K29" s="61">
+      <c r="H29" s="60" t="s">
+        <v>61</v>
+      </c>
+      <c r="I29" s="60" t="s">
+        <v>90</v>
+      </c>
+      <c r="J29" s="60" t="s">
+        <v>92</v>
+      </c>
+      <c r="K29" s="62">
         <v>10120045</v>
       </c>
     </row>
     <row r="30" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A30" s="59">
+      <c r="A30" s="60">
         <v>30120016</v>
       </c>
       <c r="B30" s="5">
         <v>101200</v>
       </c>
       <c r="C30" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D30" s="45">
+        <v>32106</v>
+      </c>
+      <c r="E30" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="D30" s="44">
-        <v>32106</v>
-      </c>
-      <c r="E30" s="59" t="s">
-        <v>89</v>
-      </c>
-      <c r="F30" s="59" t="s">
-        <v>53</v>
-      </c>
-      <c r="G30" s="60">
+      <c r="F30" s="60" t="s">
+        <v>54</v>
+      </c>
+      <c r="G30" s="61">
         <v>2012001</v>
       </c>
-      <c r="H30" s="59" t="s">
-        <v>60</v>
-      </c>
-      <c r="I30" s="59" t="s">
-        <v>89</v>
-      </c>
-      <c r="J30" s="59" t="s">
-        <v>91</v>
-      </c>
-      <c r="K30" s="61">
+      <c r="H30" s="60" t="s">
+        <v>61</v>
+      </c>
+      <c r="I30" s="60" t="s">
+        <v>90</v>
+      </c>
+      <c r="J30" s="60" t="s">
+        <v>92</v>
+      </c>
+      <c r="K30" s="62">
         <v>10120046</v>
       </c>
     </row>
     <row r="31" s="6" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A31" s="53">
+      <c r="A31" s="54">
         <v>30120021</v>
       </c>
       <c r="B31" s="6">
         <v>101200</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="D31" s="53">
+        <v>93</v>
+      </c>
+      <c r="D31" s="54">
         <v>32201</v>
       </c>
-      <c r="E31" s="53" t="s">
-        <v>85</v>
-      </c>
-      <c r="F31" s="53" t="s">
-        <v>53</v>
-      </c>
-      <c r="G31" s="62">
+      <c r="E31" s="54" t="s">
+        <v>86</v>
+      </c>
+      <c r="F31" s="54" t="s">
+        <v>54</v>
+      </c>
+      <c r="G31" s="63">
         <v>2012001</v>
       </c>
-      <c r="H31" s="53" t="s">
-        <v>60</v>
-      </c>
-      <c r="I31" s="53" t="s">
-        <v>85</v>
-      </c>
-      <c r="J31" s="53"/>
-      <c r="K31" s="63">
+      <c r="H31" s="54" t="s">
+        <v>61</v>
+      </c>
+      <c r="I31" s="54" t="s">
+        <v>86</v>
+      </c>
+      <c r="J31" s="54"/>
+      <c r="K31" s="64">
         <v>10120041</v>
       </c>
     </row>
     <row r="32" s="6" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A32" s="53">
+      <c r="A32" s="54">
         <v>30120022</v>
       </c>
       <c r="B32" s="6">
         <v>101200</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="D32" s="53">
+        <v>93</v>
+      </c>
+      <c r="D32" s="54">
         <v>32202</v>
       </c>
-      <c r="E32" s="53" t="s">
-        <v>87</v>
-      </c>
-      <c r="F32" s="53" t="s">
-        <v>53</v>
-      </c>
-      <c r="G32" s="62">
+      <c r="E32" s="54" t="s">
+        <v>88</v>
+      </c>
+      <c r="F32" s="54" t="s">
+        <v>54</v>
+      </c>
+      <c r="G32" s="63">
         <v>2012001</v>
       </c>
-      <c r="H32" s="53" t="s">
-        <v>60</v>
-      </c>
-      <c r="I32" s="53" t="s">
-        <v>87</v>
-      </c>
-      <c r="J32" s="53"/>
-      <c r="K32" s="63">
+      <c r="H32" s="54" t="s">
+        <v>61</v>
+      </c>
+      <c r="I32" s="54" t="s">
+        <v>88</v>
+      </c>
+      <c r="J32" s="54"/>
+      <c r="K32" s="64">
         <v>10120042</v>
       </c>
     </row>
     <row r="33" s="6" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A33" s="53">
+      <c r="A33" s="54">
         <v>30120023</v>
       </c>
       <c r="B33" s="6">
         <v>101200</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="D33" s="53">
+        <v>93</v>
+      </c>
+      <c r="D33" s="54">
         <v>32203</v>
       </c>
-      <c r="E33" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="F33" s="53" t="s">
-        <v>53</v>
-      </c>
-      <c r="G33" s="62">
+      <c r="E33" s="54" t="s">
+        <v>89</v>
+      </c>
+      <c r="F33" s="54" t="s">
+        <v>54</v>
+      </c>
+      <c r="G33" s="63">
         <v>2012001</v>
       </c>
-      <c r="H33" s="53" t="s">
-        <v>60</v>
-      </c>
-      <c r="I33" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="J33" s="53"/>
-      <c r="K33" s="63">
+      <c r="H33" s="54" t="s">
+        <v>61</v>
+      </c>
+      <c r="I33" s="54" t="s">
+        <v>89</v>
+      </c>
+      <c r="J33" s="54"/>
+      <c r="K33" s="64">
         <v>10120043</v>
       </c>
     </row>
     <row r="34" s="6" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A34" s="53">
+      <c r="A34" s="54">
         <v>30120024</v>
       </c>
       <c r="B34" s="6">
         <v>101200</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="D34" s="53">
+        <v>93</v>
+      </c>
+      <c r="D34" s="54">
         <v>32204</v>
       </c>
-      <c r="E34" s="53" t="s">
-        <v>89</v>
-      </c>
-      <c r="F34" s="53" t="s">
-        <v>53</v>
-      </c>
-      <c r="G34" s="62">
+      <c r="E34" s="54" t="s">
+        <v>90</v>
+      </c>
+      <c r="F34" s="54" t="s">
+        <v>54</v>
+      </c>
+      <c r="G34" s="63">
         <v>2012001</v>
       </c>
-      <c r="H34" s="53" t="s">
-        <v>60</v>
-      </c>
-      <c r="I34" s="53" t="s">
-        <v>89</v>
-      </c>
-      <c r="J34" s="53"/>
-      <c r="K34" s="63">
+      <c r="H34" s="54" t="s">
+        <v>61</v>
+      </c>
+      <c r="I34" s="54" t="s">
+        <v>90</v>
+      </c>
+      <c r="J34" s="54"/>
+      <c r="K34" s="64">
         <v>10120044</v>
       </c>
     </row>
     <row r="35" s="6" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A35" s="53">
+      <c r="A35" s="54">
         <v>30120025</v>
       </c>
       <c r="B35" s="6">
         <v>101200</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="D35" s="53">
+        <v>93</v>
+      </c>
+      <c r="D35" s="54">
         <v>32205</v>
       </c>
-      <c r="E35" s="53" t="s">
-        <v>89</v>
-      </c>
-      <c r="F35" s="53" t="s">
-        <v>53</v>
-      </c>
-      <c r="G35" s="62">
+      <c r="E35" s="54" t="s">
+        <v>90</v>
+      </c>
+      <c r="F35" s="54" t="s">
+        <v>54</v>
+      </c>
+      <c r="G35" s="63">
         <v>2012001</v>
       </c>
-      <c r="H35" s="53" t="s">
-        <v>60</v>
-      </c>
-      <c r="I35" s="53" t="s">
-        <v>89</v>
-      </c>
-      <c r="J35" s="53"/>
-      <c r="K35" s="63">
+      <c r="H35" s="54" t="s">
+        <v>61</v>
+      </c>
+      <c r="I35" s="54" t="s">
+        <v>90</v>
+      </c>
+      <c r="J35" s="54"/>
+      <c r="K35" s="64">
         <v>10120045</v>
       </c>
     </row>
     <row r="36" s="6" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A36" s="53">
+      <c r="A36" s="54">
         <v>30120026</v>
       </c>
       <c r="B36" s="6">
         <v>101200</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="D36" s="53">
+        <v>93</v>
+      </c>
+      <c r="D36" s="54">
         <v>32206</v>
       </c>
-      <c r="E36" s="53" t="s">
-        <v>89</v>
-      </c>
-      <c r="F36" s="53" t="s">
+      <c r="E36" s="54" t="s">
+        <v>90</v>
+      </c>
+      <c r="F36" s="54" t="s">
+        <v>54</v>
+      </c>
+      <c r="G36" s="63">
+        <v>2012001</v>
+      </c>
+      <c r="H36" s="54" t="s">
+        <v>61</v>
+      </c>
+      <c r="I36" s="54" t="s">
+        <v>90</v>
+      </c>
+      <c r="J36" s="54"/>
+      <c r="K36" s="64">
+        <v>10120046</v>
+      </c>
+    </row>
+    <row r="37" s="7" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A37" s="65">
+        <v>30240001</v>
+      </c>
+      <c r="B37" s="66">
+        <v>102400</v>
+      </c>
+      <c r="C37" s="66" t="s">
+        <v>32</v>
+      </c>
+      <c r="D37" s="65">
+        <v>32401</v>
+      </c>
+      <c r="E37" s="65" t="s">
+        <v>33</v>
+      </c>
+      <c r="F37" s="65" t="s">
+        <v>34</v>
+      </c>
+      <c r="G37" s="65"/>
+      <c r="H37" s="65"/>
+      <c r="I37" s="65" t="s">
+        <v>35</v>
+      </c>
+      <c r="J37" s="65"/>
+      <c r="K37" s="67"/>
+      <c r="L37" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="M37" s="65" t="s">
+        <v>37</v>
+      </c>
+      <c r="N37" s="65" t="s">
+        <v>38</v>
+      </c>
+      <c r="O37" s="65"/>
+      <c r="P37" s="65"/>
+      <c r="Q37" s="68" t="s">
+        <v>39</v>
+      </c>
+      <c r="R37" s="69" t="s">
+        <v>40</v>
+      </c>
+      <c r="S37" s="70" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="38" s="7" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A38" s="65">
+        <v>30240002</v>
+      </c>
+      <c r="B38" s="66">
+        <v>102400</v>
+      </c>
+      <c r="C38" s="66" t="s">
+        <v>32</v>
+      </c>
+      <c r="D38" s="65">
+        <v>32402</v>
+      </c>
+      <c r="E38" s="65" t="s">
+        <v>42</v>
+      </c>
+      <c r="F38" s="65" t="s">
+        <v>34</v>
+      </c>
+      <c r="G38" s="65"/>
+      <c r="H38" s="65"/>
+      <c r="I38" s="65" t="s">
+        <v>43</v>
+      </c>
+      <c r="J38" s="65"/>
+      <c r="K38" s="67"/>
+      <c r="L38" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="M38" s="65" t="s">
+        <v>37</v>
+      </c>
+      <c r="N38" s="65" t="s">
+        <v>38</v>
+      </c>
+      <c r="O38" s="65"/>
+      <c r="P38" s="65"/>
+      <c r="Q38" s="68" t="s">
+        <v>45</v>
+      </c>
+      <c r="R38" s="69" t="s">
+        <v>40</v>
+      </c>
+      <c r="S38" s="70"/>
+    </row>
+    <row r="39" s="7" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A39" s="65">
+        <v>30240003</v>
+      </c>
+      <c r="B39" s="66">
+        <v>102400</v>
+      </c>
+      <c r="C39" s="66" t="s">
+        <v>32</v>
+      </c>
+      <c r="D39" s="65">
+        <v>32403</v>
+      </c>
+      <c r="E39" s="65" t="s">
+        <v>46</v>
+      </c>
+      <c r="F39" s="65" t="s">
+        <v>34</v>
+      </c>
+      <c r="G39" s="65"/>
+      <c r="H39" s="65"/>
+      <c r="I39" s="65" t="s">
+        <v>47</v>
+      </c>
+      <c r="J39" s="65"/>
+      <c r="K39" s="67"/>
+      <c r="L39" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="M39" s="65" t="s">
+        <v>37</v>
+      </c>
+      <c r="N39" s="65" t="s">
+        <v>38</v>
+      </c>
+      <c r="O39" s="65"/>
+      <c r="P39" s="65"/>
+      <c r="Q39" s="68" t="s">
+        <v>48</v>
+      </c>
+      <c r="R39" s="69" t="s">
+        <v>40</v>
+      </c>
+      <c r="S39" s="70"/>
+    </row>
+    <row r="40" s="7" customFormat="1" ht="15" customHeight="1" spans="1:19">
+      <c r="A40" s="65">
+        <v>30240004</v>
+      </c>
+      <c r="B40" s="66">
+        <v>102400</v>
+      </c>
+      <c r="C40" s="66" t="s">
+        <v>32</v>
+      </c>
+      <c r="D40" s="65">
+        <v>32404</v>
+      </c>
+      <c r="E40" s="65" t="s">
+        <v>49</v>
+      </c>
+      <c r="F40" s="65" t="s">
+        <v>34</v>
+      </c>
+      <c r="G40" s="65"/>
+      <c r="H40" s="65"/>
+      <c r="I40" s="65" t="s">
+        <v>50</v>
+      </c>
+      <c r="J40" s="65"/>
+      <c r="K40" s="67"/>
+      <c r="L40" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="M40" s="65" t="s">
+        <v>37</v>
+      </c>
+      <c r="N40" s="65" t="s">
+        <v>38</v>
+      </c>
+      <c r="O40" s="65"/>
+      <c r="P40" s="65"/>
+      <c r="Q40" s="68" t="s">
+        <v>51</v>
+      </c>
+      <c r="R40" s="69" t="s">
+        <v>40</v>
+      </c>
+      <c r="S40" s="70"/>
+    </row>
+    <row r="41" s="7" customFormat="1" ht="15" customHeight="1" spans="1:19">
+      <c r="A41" s="65">
+        <v>30240005</v>
+      </c>
+      <c r="B41" s="66">
+        <v>102400</v>
+      </c>
+      <c r="C41" s="66" t="s">
+        <v>32</v>
+      </c>
+      <c r="D41" s="65">
+        <v>32411</v>
+      </c>
+      <c r="E41" s="65" t="s">
+        <v>52</v>
+      </c>
+      <c r="F41" s="65" t="s">
+        <v>34</v>
+      </c>
+      <c r="G41" s="65"/>
+      <c r="H41" s="65"/>
+      <c r="I41" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="G36" s="62">
-        <v>2012001</v>
-      </c>
-      <c r="H36" s="53" t="s">
+      <c r="J41" s="65"/>
+      <c r="K41" s="67"/>
+      <c r="L41" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="M41" s="65" t="s">
+        <v>54</v>
+      </c>
+      <c r="N41" s="65"/>
+      <c r="O41" s="65" t="s">
+        <v>55</v>
+      </c>
+      <c r="P41" s="65"/>
+      <c r="Q41" s="68"/>
+      <c r="R41" s="68"/>
+      <c r="S41" s="70"/>
+    </row>
+    <row r="42" s="7" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A42" s="65">
+        <v>30240006</v>
+      </c>
+      <c r="B42" s="66">
+        <v>102400</v>
+      </c>
+      <c r="C42" s="66" t="s">
+        <v>32</v>
+      </c>
+      <c r="D42" s="65">
+        <v>32421</v>
+      </c>
+      <c r="E42" s="65" t="s">
+        <v>56</v>
+      </c>
+      <c r="F42" s="65" t="s">
+        <v>34</v>
+      </c>
+      <c r="G42" s="65"/>
+      <c r="H42" s="65"/>
+      <c r="I42" s="65" t="s">
+        <v>57</v>
+      </c>
+      <c r="J42" s="65"/>
+      <c r="K42" s="67"/>
+      <c r="L42" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="M42" s="65" t="s">
+        <v>58</v>
+      </c>
+      <c r="N42" s="65" t="s">
+        <v>38</v>
+      </c>
+      <c r="O42" s="65" t="s">
+        <v>55</v>
+      </c>
+      <c r="P42" s="65"/>
+      <c r="Q42" s="65"/>
+      <c r="R42" s="65"/>
+      <c r="S42" s="70"/>
+    </row>
+    <row r="43" s="7" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A43" s="65">
+        <v>30240007</v>
+      </c>
+      <c r="B43" s="66">
+        <v>102400</v>
+      </c>
+      <c r="C43" s="66" t="s">
+        <v>32</v>
+      </c>
+      <c r="D43" s="65">
+        <v>32431</v>
+      </c>
+      <c r="E43" s="65" t="s">
+        <v>59</v>
+      </c>
+      <c r="F43" s="65" t="s">
         <v>60</v>
       </c>
-      <c r="I36" s="53" t="s">
-        <v>89</v>
-      </c>
-      <c r="J36" s="53"/>
-      <c r="K36" s="63">
-        <v>10120046</v>
-      </c>
-    </row>
-    <row r="37" s="7" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A37" s="64">
-        <v>30240001</v>
-      </c>
-      <c r="B37" s="65">
+      <c r="G43" s="65">
+        <v>2024001</v>
+      </c>
+      <c r="H43" s="65" t="s">
+        <v>61</v>
+      </c>
+      <c r="I43" s="65" t="s">
+        <v>62</v>
+      </c>
+      <c r="J43" s="65"/>
+      <c r="K43" s="67">
+        <v>10240091</v>
+      </c>
+      <c r="L43" s="65"/>
+      <c r="M43" s="65"/>
+      <c r="N43" s="65"/>
+      <c r="O43" s="65"/>
+      <c r="P43" s="65"/>
+      <c r="Q43" s="65"/>
+      <c r="R43" s="65"/>
+      <c r="S43" s="70"/>
+    </row>
+    <row r="44" s="7" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A44" s="65">
+        <v>30240008</v>
+      </c>
+      <c r="B44" s="66">
         <v>102400</v>
       </c>
-      <c r="C37" s="65" t="s">
+      <c r="C44" s="66" t="s">
         <v>32</v>
       </c>
-      <c r="D37" s="64">
-        <v>32401</v>
-      </c>
-      <c r="E37" s="64" t="s">
-        <v>33</v>
-      </c>
-      <c r="F37" s="64" t="s">
+      <c r="D44" s="65">
+        <v>32432</v>
+      </c>
+      <c r="E44" s="65" t="s">
+        <v>63</v>
+      </c>
+      <c r="F44" s="65" t="s">
+        <v>54</v>
+      </c>
+      <c r="G44" s="65">
+        <v>2024001</v>
+      </c>
+      <c r="H44" s="65" t="s">
+        <v>61</v>
+      </c>
+      <c r="I44" s="65" t="s">
+        <v>64</v>
+      </c>
+      <c r="J44" s="65"/>
+      <c r="K44" s="71" t="s">
+        <v>94</v>
+      </c>
+      <c r="L44" s="65"/>
+      <c r="M44" s="65"/>
+      <c r="N44" s="65"/>
+      <c r="O44" s="65"/>
+      <c r="P44" s="65"/>
+      <c r="Q44" s="65"/>
+      <c r="R44" s="65"/>
+      <c r="S44" s="70"/>
+    </row>
+    <row r="45" s="7" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A45" s="65">
+        <v>30240009</v>
+      </c>
+      <c r="B45" s="66">
+        <v>102400</v>
+      </c>
+      <c r="C45" s="66" t="s">
+        <v>32</v>
+      </c>
+      <c r="D45" s="65">
+        <v>32433</v>
+      </c>
+      <c r="E45" s="65" t="s">
+        <v>66</v>
+      </c>
+      <c r="F45" s="65" t="s">
+        <v>54</v>
+      </c>
+      <c r="G45" s="65">
+        <v>2024001</v>
+      </c>
+      <c r="H45" s="65" t="s">
+        <v>61</v>
+      </c>
+      <c r="I45" s="65" t="s">
+        <v>67</v>
+      </c>
+      <c r="J45" s="65"/>
+      <c r="K45" s="67" t="s">
+        <v>95</v>
+      </c>
+      <c r="L45" s="65"/>
+      <c r="M45" s="65"/>
+      <c r="N45" s="65"/>
+      <c r="O45" s="65"/>
+      <c r="P45" s="65"/>
+      <c r="Q45" s="65"/>
+      <c r="R45" s="65"/>
+      <c r="S45" s="70"/>
+    </row>
+    <row r="46" s="7" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A46" s="65">
+        <v>30240010</v>
+      </c>
+      <c r="B46" s="66">
+        <v>102400</v>
+      </c>
+      <c r="C46" s="66" t="s">
+        <v>32</v>
+      </c>
+      <c r="D46" s="65">
+        <v>32441</v>
+      </c>
+      <c r="E46" s="65" t="s">
+        <v>69</v>
+      </c>
+      <c r="F46" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="G37" s="64"/>
-      <c r="H37" s="64"/>
-      <c r="I37" s="64" t="s">
-        <v>35</v>
-      </c>
-      <c r="J37" s="64"/>
-      <c r="K37" s="66"/>
-      <c r="L37" s="64" t="s">
-        <v>36</v>
-      </c>
-      <c r="M37" s="64" t="s">
+      <c r="G46" s="65"/>
+      <c r="H46" s="65"/>
+      <c r="I46" s="65" t="s">
+        <v>70</v>
+      </c>
+      <c r="J46" s="65"/>
+      <c r="K46" s="71"/>
+      <c r="L46" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="M46" s="65" t="s">
+        <v>71</v>
+      </c>
+      <c r="N46" s="65"/>
+      <c r="O46" s="65"/>
+      <c r="P46" s="65"/>
+      <c r="Q46" s="68" t="s">
+        <v>72</v>
+      </c>
+      <c r="R46" s="72" t="s">
+        <v>73</v>
+      </c>
+      <c r="S46" s="68" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="47" s="7" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A47" s="65">
+        <v>30240011</v>
+      </c>
+      <c r="B47" s="66">
+        <v>102400</v>
+      </c>
+      <c r="C47" s="66" t="s">
+        <v>32</v>
+      </c>
+      <c r="D47" s="65">
+        <v>32442</v>
+      </c>
+      <c r="E47" s="65" t="s">
+        <v>75</v>
+      </c>
+      <c r="F47" s="65" t="s">
+        <v>34</v>
+      </c>
+      <c r="G47" s="65"/>
+      <c r="H47" s="65"/>
+      <c r="I47" s="65" t="s">
+        <v>76</v>
+      </c>
+      <c r="J47" s="65"/>
+      <c r="K47" s="67"/>
+      <c r="L47" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="M47" s="65" t="s">
+        <v>58</v>
+      </c>
+      <c r="N47" s="65"/>
+      <c r="O47" s="65"/>
+      <c r="P47" s="65"/>
+      <c r="Q47" s="65"/>
+      <c r="R47" s="65"/>
+      <c r="S47" s="70"/>
+    </row>
+    <row r="48" s="7" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A48" s="65">
+        <v>30240012</v>
+      </c>
+      <c r="B48" s="66">
+        <v>102400</v>
+      </c>
+      <c r="C48" s="66" t="s">
+        <v>32</v>
+      </c>
+      <c r="D48" s="65">
+        <v>32443</v>
+      </c>
+      <c r="E48" s="65" t="s">
+        <v>77</v>
+      </c>
+      <c r="F48" s="65" t="s">
+        <v>54</v>
+      </c>
+      <c r="G48" s="65">
+        <v>2024001</v>
+      </c>
+      <c r="H48" s="65" t="s">
+        <v>61</v>
+      </c>
+      <c r="I48" s="65" t="s">
+        <v>67</v>
+      </c>
+      <c r="J48" s="65"/>
+      <c r="K48" s="67" t="s">
+        <v>95</v>
+      </c>
+      <c r="L48" s="65"/>
+      <c r="M48" s="65"/>
+      <c r="N48" s="65"/>
+      <c r="O48" s="65"/>
+      <c r="P48" s="65"/>
+      <c r="Q48" s="65"/>
+      <c r="R48" s="65"/>
+      <c r="S48" s="70"/>
+    </row>
+    <row r="49" s="8" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A49" s="73">
+        <v>30170001</v>
+      </c>
+      <c r="B49" s="74">
+        <v>101700</v>
+      </c>
+      <c r="C49" s="74" t="s">
+        <v>96</v>
+      </c>
+      <c r="D49" s="73">
+        <v>301701</v>
+      </c>
+      <c r="E49" s="73" t="s">
+        <v>97</v>
+      </c>
+      <c r="F49" s="73" t="s">
+        <v>80</v>
+      </c>
+      <c r="G49" s="73">
+        <v>2017001</v>
+      </c>
+      <c r="H49" s="73" t="s">
+        <v>61</v>
+      </c>
+      <c r="I49" s="73" t="s">
+        <v>81</v>
+      </c>
+      <c r="J49" s="73"/>
+      <c r="K49" s="75" t="s">
+        <v>98</v>
+      </c>
+      <c r="L49" s="73"/>
+      <c r="M49" s="73"/>
+      <c r="N49" s="73"/>
+      <c r="O49" s="73"/>
+      <c r="P49" s="73"/>
+      <c r="Q49" s="73"/>
+      <c r="R49" s="73"/>
+      <c r="S49" s="76"/>
+    </row>
+    <row r="50" s="8" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A50" s="73">
+        <v>30170002</v>
+      </c>
+      <c r="B50" s="74">
+        <v>101700</v>
+      </c>
+      <c r="C50" s="74" t="s">
+        <v>96</v>
+      </c>
+      <c r="D50" s="73">
+        <v>301702</v>
+      </c>
+      <c r="E50" s="73" t="s">
+        <v>99</v>
+      </c>
+      <c r="F50" s="73" t="s">
+        <v>84</v>
+      </c>
+      <c r="G50" s="73">
+        <v>2017001</v>
+      </c>
+      <c r="H50" s="73" t="s">
+        <v>61</v>
+      </c>
+      <c r="I50" s="73" t="s">
+        <v>81</v>
+      </c>
+      <c r="J50" s="73"/>
+      <c r="K50" s="75" t="s">
+        <v>98</v>
+      </c>
+      <c r="L50" s="73"/>
+      <c r="M50" s="73"/>
+      <c r="N50" s="73"/>
+      <c r="O50" s="73"/>
+      <c r="P50" s="73"/>
+      <c r="Q50" s="73"/>
+      <c r="R50" s="73"/>
+      <c r="S50" s="76"/>
+    </row>
+    <row r="51" s="5" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A51" s="60">
+        <v>30220001</v>
+      </c>
+      <c r="B51" s="61">
+        <v>102200</v>
+      </c>
+      <c r="C51" s="61" t="s">
+        <v>100</v>
+      </c>
+      <c r="D51" s="60">
+        <v>302201</v>
+      </c>
+      <c r="E51" s="60" t="s">
+        <v>101</v>
+      </c>
+      <c r="F51" s="60" t="s">
+        <v>102</v>
+      </c>
+      <c r="G51" s="60">
+        <v>2022001</v>
+      </c>
+      <c r="H51" s="60" t="s">
+        <v>61</v>
+      </c>
+      <c r="I51" s="60"/>
+      <c r="J51" s="60"/>
+      <c r="K51" s="77" t="s">
+        <v>103</v>
+      </c>
+      <c r="L51" s="60" t="s">
+        <v>104</v>
+      </c>
+      <c r="M51" s="60"/>
+      <c r="N51" s="60"/>
+      <c r="O51" s="60"/>
+      <c r="P51" s="60"/>
+      <c r="Q51" s="60"/>
+      <c r="R51" s="60"/>
+      <c r="S51" s="78"/>
+    </row>
+    <row r="52" s="5" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A52" s="60">
+        <v>30220002</v>
+      </c>
+      <c r="B52" s="61">
+        <v>102200</v>
+      </c>
+      <c r="C52" s="61" t="s">
+        <v>100</v>
+      </c>
+      <c r="D52" s="60">
+        <v>302202</v>
+      </c>
+      <c r="E52" s="60" t="s">
+        <v>105</v>
+      </c>
+      <c r="F52" s="60" t="s">
+        <v>102</v>
+      </c>
+      <c r="G52" s="60">
+        <v>2022001</v>
+      </c>
+      <c r="H52" s="60" t="s">
+        <v>61</v>
+      </c>
+      <c r="I52" s="60"/>
+      <c r="J52" s="60"/>
+      <c r="K52" s="77" t="s">
+        <v>106</v>
+      </c>
+      <c r="L52" s="60" t="s">
+        <v>104</v>
+      </c>
+      <c r="M52" s="60"/>
+      <c r="N52" s="60"/>
+      <c r="O52" s="60"/>
+      <c r="P52" s="60"/>
+      <c r="Q52" s="60"/>
+      <c r="R52" s="60"/>
+      <c r="S52" s="78"/>
+    </row>
+    <row r="53" s="9" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A53" s="79">
+        <v>30210001</v>
+      </c>
+      <c r="B53" s="80">
+        <v>102100</v>
+      </c>
+      <c r="C53" s="80" t="s">
+        <v>107</v>
+      </c>
+      <c r="D53" s="79">
+        <v>302101</v>
+      </c>
+      <c r="E53" s="79" t="s">
+        <v>108</v>
+      </c>
+      <c r="F53" s="79" t="s">
+        <v>109</v>
+      </c>
+      <c r="G53" s="79">
+        <v>2021001</v>
+      </c>
+      <c r="H53" s="79" t="s">
+        <v>61</v>
+      </c>
+      <c r="I53" s="79" t="s">
+        <v>81</v>
+      </c>
+      <c r="J53" s="79"/>
+      <c r="K53" s="81" t="s">
+        <v>110</v>
+      </c>
+      <c r="L53" s="79" t="s">
+        <v>111</v>
+      </c>
+      <c r="M53" s="79"/>
+      <c r="N53" s="79"/>
+      <c r="O53" s="79"/>
+      <c r="P53" s="79"/>
+      <c r="Q53" s="79"/>
+      <c r="R53" s="79"/>
+      <c r="S53" s="82"/>
+    </row>
+    <row r="54" s="9" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A54" s="79">
+        <v>30210002</v>
+      </c>
+      <c r="B54" s="80">
+        <v>102100</v>
+      </c>
+      <c r="C54" s="80" t="s">
+        <v>107</v>
+      </c>
+      <c r="D54" s="79">
+        <v>302102</v>
+      </c>
+      <c r="E54" s="79" t="s">
+        <v>112</v>
+      </c>
+      <c r="F54" s="79" t="s">
+        <v>34</v>
+      </c>
+      <c r="G54" s="79"/>
+      <c r="H54" s="79"/>
+      <c r="I54" s="79" t="s">
+        <v>113</v>
+      </c>
+      <c r="J54" s="79"/>
+      <c r="K54" s="81"/>
+      <c r="L54" s="79"/>
+      <c r="M54" s="79" t="s">
         <v>37</v>
       </c>
-      <c r="N37" s="64" t="s">
-        <v>38</v>
-      </c>
-      <c r="O37" s="64"/>
-      <c r="P37" s="64"/>
-      <c r="Q37" s="67" t="s">
-        <v>39</v>
-      </c>
-      <c r="R37" s="68" t="s">
+      <c r="N54" s="79" t="s">
+        <v>114</v>
+      </c>
+      <c r="O54" s="79"/>
+      <c r="P54" s="79"/>
+      <c r="Q54" s="79" t="s">
+        <v>115</v>
+      </c>
+      <c r="R54" s="79"/>
+      <c r="S54" s="82"/>
+    </row>
+    <row r="55" s="10" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A55" s="83">
+        <v>30180001</v>
+      </c>
+      <c r="B55" s="84">
+        <v>101800</v>
+      </c>
+      <c r="C55" s="84" t="s">
+        <v>116</v>
+      </c>
+      <c r="D55" s="83">
+        <v>301801</v>
+      </c>
+      <c r="E55" s="83" t="s">
+        <v>81</v>
+      </c>
+      <c r="F55" s="83" t="s">
+        <v>117</v>
+      </c>
+      <c r="G55" s="83">
+        <v>2018002</v>
+      </c>
+      <c r="H55" s="83" t="s">
+        <v>61</v>
+      </c>
+      <c r="I55" s="83" t="s">
+        <v>81</v>
+      </c>
+      <c r="J55" s="83"/>
+      <c r="K55" s="85">
+        <v>10180041</v>
+      </c>
+      <c r="L55" s="83"/>
+      <c r="M55" s="83"/>
+      <c r="N55" s="83"/>
+      <c r="O55" s="83"/>
+      <c r="P55" s="83"/>
+      <c r="Q55" s="83"/>
+      <c r="R55" s="83"/>
+      <c r="S55" s="86"/>
+    </row>
+    <row r="56" s="11" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A56" s="87">
+        <v>30250001</v>
+      </c>
+      <c r="B56" s="88">
+        <v>102500</v>
+      </c>
+      <c r="C56" s="88" t="s">
+        <v>118</v>
+      </c>
+      <c r="D56" s="87">
+        <v>302501</v>
+      </c>
+      <c r="E56" s="87" t="s">
+        <v>108</v>
+      </c>
+      <c r="F56" s="87" t="s">
+        <v>109</v>
+      </c>
+      <c r="G56" s="87">
+        <v>2025001</v>
+      </c>
+      <c r="H56" s="87" t="s">
+        <v>61</v>
+      </c>
+      <c r="I56" s="87" t="s">
+        <v>81</v>
+      </c>
+      <c r="J56" s="87"/>
+      <c r="K56" s="89" t="s">
+        <v>119</v>
+      </c>
+      <c r="L56" s="87" t="s">
+        <v>120</v>
+      </c>
+      <c r="M56" s="87"/>
+      <c r="N56" s="87"/>
+      <c r="O56" s="87"/>
+      <c r="P56" s="87"/>
+      <c r="Q56" s="87"/>
+      <c r="R56" s="87"/>
+      <c r="S56" s="90"/>
+    </row>
+    <row r="57" s="11" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A57" s="87">
+        <v>30250002</v>
+      </c>
+      <c r="B57" s="88">
+        <v>102500</v>
+      </c>
+      <c r="C57" s="88" t="s">
+        <v>118</v>
+      </c>
+      <c r="D57" s="87">
+        <v>302502</v>
+      </c>
+      <c r="E57" s="87" t="s">
+        <v>121</v>
+      </c>
+      <c r="F57" s="87" t="s">
+        <v>122</v>
+      </c>
+      <c r="G57" s="87">
+        <v>2025001</v>
+      </c>
+      <c r="H57" s="87" t="s">
+        <v>61</v>
+      </c>
+      <c r="I57" s="87" t="s">
+        <v>81</v>
+      </c>
+      <c r="J57" s="87"/>
+      <c r="K57" s="89" t="s">
+        <v>119</v>
+      </c>
+      <c r="L57" s="87" t="s">
+        <v>120</v>
+      </c>
+      <c r="M57" s="87"/>
+      <c r="N57" s="87"/>
+      <c r="O57" s="87"/>
+      <c r="P57" s="87"/>
+      <c r="Q57" s="87"/>
+      <c r="R57" s="87"/>
+      <c r="S57" s="90"/>
+    </row>
+    <row r="58" s="11" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A58" s="87">
+        <v>30250003</v>
+      </c>
+      <c r="B58" s="88">
+        <v>102500</v>
+      </c>
+      <c r="C58" s="88" t="s">
+        <v>118</v>
+      </c>
+      <c r="D58" s="87">
+        <v>302503</v>
+      </c>
+      <c r="E58" s="87" t="s">
+        <v>123</v>
+      </c>
+      <c r="F58" s="87" t="s">
+        <v>124</v>
+      </c>
+      <c r="G58" s="87">
+        <v>2025001</v>
+      </c>
+      <c r="H58" s="87" t="s">
+        <v>61</v>
+      </c>
+      <c r="I58" s="87" t="s">
+        <v>81</v>
+      </c>
+      <c r="J58" s="87"/>
+      <c r="K58" s="89" t="s">
+        <v>119</v>
+      </c>
+      <c r="L58" s="87" t="s">
+        <v>120</v>
+      </c>
+      <c r="M58" s="87"/>
+      <c r="N58" s="87"/>
+      <c r="O58" s="87"/>
+      <c r="P58" s="87"/>
+      <c r="Q58" s="87"/>
+      <c r="R58" s="87"/>
+      <c r="S58" s="90"/>
+    </row>
+    <row r="59" s="12" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A59" s="91">
+        <v>30230001</v>
+      </c>
+      <c r="B59" s="92">
+        <v>102300</v>
+      </c>
+      <c r="C59" s="92" t="s">
+        <v>125</v>
+      </c>
+      <c r="D59" s="91">
+        <v>302301</v>
+      </c>
+      <c r="E59" s="91" t="s">
+        <v>108</v>
+      </c>
+      <c r="F59" s="91" t="s">
+        <v>109</v>
+      </c>
+      <c r="G59" s="91">
+        <v>2023001</v>
+      </c>
+      <c r="H59" s="91" t="s">
+        <v>61</v>
+      </c>
+      <c r="I59" s="91" t="s">
+        <v>81</v>
+      </c>
+      <c r="J59" s="91"/>
+      <c r="K59" s="93" t="s">
+        <v>126</v>
+      </c>
+      <c r="L59" s="91" t="s">
+        <v>127</v>
+      </c>
+      <c r="M59" s="91"/>
+      <c r="N59" s="91"/>
+      <c r="O59" s="91"/>
+      <c r="P59" s="91"/>
+      <c r="Q59" s="91"/>
+      <c r="R59" s="91"/>
+      <c r="S59" s="94"/>
+    </row>
+    <row r="60" s="12" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A60" s="91">
+        <v>30230002</v>
+      </c>
+      <c r="B60" s="92">
+        <v>102300</v>
+      </c>
+      <c r="C60" s="92" t="s">
+        <v>125</v>
+      </c>
+      <c r="D60" s="91">
+        <v>302302</v>
+      </c>
+      <c r="E60" s="91" t="s">
+        <v>128</v>
+      </c>
+      <c r="F60" s="91" t="s">
+        <v>80</v>
+      </c>
+      <c r="G60" s="91">
+        <v>2023001</v>
+      </c>
+      <c r="H60" s="91" t="s">
+        <v>61</v>
+      </c>
+      <c r="I60" s="91" t="s">
+        <v>81</v>
+      </c>
+      <c r="J60" s="91"/>
+      <c r="K60" s="93" t="s">
+        <v>126</v>
+      </c>
+      <c r="L60" s="91" t="s">
+        <v>127</v>
+      </c>
+      <c r="M60" s="91"/>
+      <c r="N60" s="91"/>
+      <c r="O60" s="91"/>
+      <c r="P60" s="91"/>
+      <c r="Q60" s="91"/>
+      <c r="R60" s="91"/>
+      <c r="S60" s="94"/>
+    </row>
+    <row r="61" s="12" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A61" s="91">
+        <v>30230003</v>
+      </c>
+      <c r="B61" s="92">
+        <v>102300</v>
+      </c>
+      <c r="C61" s="92" t="s">
+        <v>125</v>
+      </c>
+      <c r="D61" s="91">
+        <v>302303</v>
+      </c>
+      <c r="E61" s="91" t="s">
+        <v>129</v>
+      </c>
+      <c r="F61" s="91" t="s">
+        <v>84</v>
+      </c>
+      <c r="G61" s="91">
+        <v>2023001</v>
+      </c>
+      <c r="H61" s="91" t="s">
+        <v>61</v>
+      </c>
+      <c r="I61" s="91" t="s">
+        <v>81</v>
+      </c>
+      <c r="J61" s="91"/>
+      <c r="K61" s="93" t="s">
+        <v>126</v>
+      </c>
+      <c r="L61" s="91" t="s">
+        <v>127</v>
+      </c>
+      <c r="M61" s="91"/>
+      <c r="N61" s="91"/>
+      <c r="O61" s="91"/>
+      <c r="P61" s="91"/>
+      <c r="Q61" s="91"/>
+      <c r="R61" s="91"/>
+      <c r="S61" s="94"/>
+    </row>
+    <row r="62" s="13" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A62" s="95">
+        <v>30350001</v>
+      </c>
+      <c r="B62" s="96">
+        <v>103500</v>
+      </c>
+      <c r="C62" s="96" t="s">
+        <v>130</v>
+      </c>
+      <c r="D62" s="95">
+        <v>303501</v>
+      </c>
+      <c r="E62" s="95" t="s">
+        <v>131</v>
+      </c>
+      <c r="F62" s="95" t="s">
+        <v>60</v>
+      </c>
+      <c r="G62" s="95">
+        <v>2035002</v>
+      </c>
+      <c r="H62" s="95" t="s">
+        <v>61</v>
+      </c>
+      <c r="I62" s="95" t="s">
+        <v>132</v>
+      </c>
+      <c r="J62" s="95"/>
+      <c r="K62" s="97" t="s">
+        <v>133</v>
+      </c>
+      <c r="L62" s="95" t="s">
+        <v>134</v>
+      </c>
+      <c r="M62" s="95"/>
+      <c r="N62" s="95"/>
+      <c r="O62" s="95"/>
+      <c r="P62" s="95"/>
+      <c r="Q62" s="95"/>
+      <c r="R62" s="95"/>
+      <c r="S62" s="98"/>
+    </row>
+    <row r="63" s="13" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A63" s="95">
+        <v>30350002</v>
+      </c>
+      <c r="B63" s="96">
+        <v>103500</v>
+      </c>
+      <c r="C63" s="96" t="s">
+        <v>130</v>
+      </c>
+      <c r="D63" s="95">
+        <v>303502</v>
+      </c>
+      <c r="E63" s="95" t="s">
+        <v>135</v>
+      </c>
+      <c r="F63" s="95" t="s">
+        <v>34</v>
+      </c>
+      <c r="G63" s="95"/>
+      <c r="H63" s="95"/>
+      <c r="I63" s="95"/>
+      <c r="J63" s="95"/>
+      <c r="K63" s="97"/>
+      <c r="L63" s="95"/>
+      <c r="M63" s="95" t="s">
+        <v>54</v>
+      </c>
+      <c r="N63" s="95"/>
+      <c r="O63" s="95" t="s">
+        <v>136</v>
+      </c>
+      <c r="P63" s="95"/>
+      <c r="Q63" s="95"/>
+      <c r="R63" s="95"/>
+      <c r="S63" s="98"/>
+    </row>
+    <row r="64" s="13" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A64" s="95">
+        <v>30350101</v>
+      </c>
+      <c r="B64" s="96">
+        <v>103501</v>
+      </c>
+      <c r="C64" s="96" t="s">
+        <v>137</v>
+      </c>
+      <c r="D64" s="95">
+        <v>303503</v>
+      </c>
+      <c r="E64" s="95" t="s">
+        <v>131</v>
+      </c>
+      <c r="F64" s="95" t="s">
+        <v>60</v>
+      </c>
+      <c r="G64" s="95">
+        <v>2035012</v>
+      </c>
+      <c r="H64" s="95" t="s">
+        <v>61</v>
+      </c>
+      <c r="I64" s="95" t="s">
+        <v>132</v>
+      </c>
+      <c r="J64" s="95"/>
+      <c r="K64" s="97" t="s">
+        <v>138</v>
+      </c>
+      <c r="L64" s="95" t="s">
+        <v>134</v>
+      </c>
+      <c r="M64" s="95"/>
+      <c r="N64" s="95"/>
+      <c r="O64" s="95"/>
+      <c r="P64" s="95"/>
+      <c r="Q64" s="95"/>
+      <c r="R64" s="95"/>
+      <c r="S64" s="98"/>
+    </row>
+    <row r="65" s="13" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A65" s="95">
+        <v>30350102</v>
+      </c>
+      <c r="B65" s="96">
+        <v>103501</v>
+      </c>
+      <c r="C65" s="96" t="s">
+        <v>137</v>
+      </c>
+      <c r="D65" s="95">
+        <v>303504</v>
+      </c>
+      <c r="E65" s="95" t="s">
+        <v>135</v>
+      </c>
+      <c r="F65" s="95" t="s">
+        <v>34</v>
+      </c>
+      <c r="G65" s="95"/>
+      <c r="H65" s="95"/>
+      <c r="I65" s="95"/>
+      <c r="J65" s="95"/>
+      <c r="K65" s="97"/>
+      <c r="L65" s="95"/>
+      <c r="M65" s="95" t="s">
+        <v>54</v>
+      </c>
+      <c r="N65" s="95"/>
+      <c r="O65" s="95" t="s">
+        <v>136</v>
+      </c>
+      <c r="P65" s="95"/>
+      <c r="Q65" s="95"/>
+      <c r="R65" s="95"/>
+      <c r="S65" s="98"/>
+    </row>
+    <row r="66" s="14" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A66" s="99">
+        <v>30360001</v>
+      </c>
+      <c r="B66" s="100">
+        <v>103600</v>
+      </c>
+      <c r="C66" s="100" t="s">
+        <v>139</v>
+      </c>
+      <c r="D66" s="99">
+        <v>303601</v>
+      </c>
+      <c r="E66" s="99" t="s">
+        <v>140</v>
+      </c>
+      <c r="F66" s="99" t="s">
+        <v>109</v>
+      </c>
+      <c r="G66" s="99">
+        <v>2036002</v>
+      </c>
+      <c r="H66" s="99" t="s">
+        <v>61</v>
+      </c>
+      <c r="I66" s="99" t="s">
+        <v>140</v>
+      </c>
+      <c r="J66" s="99"/>
+      <c r="K66" s="101">
+        <v>10360005</v>
+      </c>
+      <c r="L66" s="99" t="s">
+        <v>141</v>
+      </c>
+      <c r="M66" s="99"/>
+      <c r="N66" s="99"/>
+      <c r="O66" s="99"/>
+      <c r="P66" s="99"/>
+      <c r="Q66" s="99"/>
+      <c r="R66" s="99"/>
+      <c r="S66" s="102"/>
+    </row>
+    <row r="67" s="15" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A67" s="103">
+        <v>30280001</v>
+      </c>
+      <c r="B67" s="104">
+        <v>102800</v>
+      </c>
+      <c r="C67" s="104" t="s">
+        <v>142</v>
+      </c>
+      <c r="D67" s="103">
+        <v>302801</v>
+      </c>
+      <c r="E67" s="103" t="s">
+        <v>108</v>
+      </c>
+      <c r="F67" s="103" t="s">
+        <v>109</v>
+      </c>
+      <c r="G67" s="103">
+        <v>2028001</v>
+      </c>
+      <c r="H67" s="103" t="s">
+        <v>61</v>
+      </c>
+      <c r="I67" s="103" t="s">
+        <v>81</v>
+      </c>
+      <c r="J67" s="103"/>
+      <c r="K67" s="105" t="s">
+        <v>143</v>
+      </c>
+      <c r="L67" s="103" t="s">
+        <v>144</v>
+      </c>
+      <c r="M67" s="103"/>
+      <c r="N67" s="103"/>
+      <c r="O67" s="103"/>
+      <c r="P67" s="103"/>
+      <c r="Q67" s="103"/>
+      <c r="R67" s="103"/>
+      <c r="S67" s="106"/>
+    </row>
+    <row r="68" s="15" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A68" s="103">
+        <v>30280002</v>
+      </c>
+      <c r="B68" s="104">
+        <v>102800</v>
+      </c>
+      <c r="C68" s="104" t="s">
+        <v>142</v>
+      </c>
+      <c r="D68" s="103">
+        <v>302802</v>
+      </c>
+      <c r="E68" s="103" t="s">
+        <v>128</v>
+      </c>
+      <c r="F68" s="103" t="s">
+        <v>80</v>
+      </c>
+      <c r="G68" s="103">
+        <v>2028001</v>
+      </c>
+      <c r="H68" s="103" t="s">
+        <v>61</v>
+      </c>
+      <c r="I68" s="103" t="s">
+        <v>81</v>
+      </c>
+      <c r="J68" s="103"/>
+      <c r="K68" s="105" t="s">
+        <v>143</v>
+      </c>
+      <c r="L68" s="103" t="s">
+        <v>144</v>
+      </c>
+      <c r="M68" s="103"/>
+      <c r="N68" s="103"/>
+      <c r="O68" s="103"/>
+      <c r="P68" s="103"/>
+      <c r="Q68" s="103"/>
+      <c r="R68" s="103"/>
+      <c r="S68" s="106"/>
+    </row>
+    <row r="69" s="15" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A69" s="103">
+        <v>30280003</v>
+      </c>
+      <c r="B69" s="104">
+        <v>102800</v>
+      </c>
+      <c r="C69" s="104" t="s">
+        <v>142</v>
+      </c>
+      <c r="D69" s="103">
+        <v>302803</v>
+      </c>
+      <c r="E69" s="103" t="s">
+        <v>129</v>
+      </c>
+      <c r="F69" s="103" t="s">
+        <v>84</v>
+      </c>
+      <c r="G69" s="103">
+        <v>2028001</v>
+      </c>
+      <c r="H69" s="103" t="s">
+        <v>61</v>
+      </c>
+      <c r="I69" s="103" t="s">
+        <v>81</v>
+      </c>
+      <c r="J69" s="103"/>
+      <c r="K69" s="105" t="s">
+        <v>143</v>
+      </c>
+      <c r="L69" s="103" t="s">
+        <v>144</v>
+      </c>
+      <c r="M69" s="103"/>
+      <c r="N69" s="103"/>
+      <c r="O69" s="103"/>
+      <c r="P69" s="103"/>
+      <c r="Q69" s="103"/>
+      <c r="R69" s="103"/>
+      <c r="S69" s="106"/>
+    </row>
+    <row r="70" s="16" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A70" s="107">
+        <v>30200003</v>
+      </c>
+      <c r="B70" s="108">
+        <v>102000</v>
+      </c>
+      <c r="C70" s="108" t="s">
+        <v>145</v>
+      </c>
+      <c r="D70" s="107">
+        <v>302003</v>
+      </c>
+      <c r="E70" s="107" t="s">
+        <v>146</v>
+      </c>
+      <c r="F70" s="107" t="s">
+        <v>34</v>
+      </c>
+      <c r="G70" s="107">
+        <v>2020001</v>
+      </c>
+      <c r="H70" s="107" t="s">
+        <v>61</v>
+      </c>
+      <c r="I70" s="107" t="s">
+        <v>147</v>
+      </c>
+      <c r="J70" s="107"/>
+      <c r="K70" s="109">
+        <v>10200011</v>
+      </c>
+      <c r="L70" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="M70" s="107"/>
+      <c r="N70" s="107"/>
+      <c r="O70" s="107"/>
+      <c r="P70" s="107"/>
+      <c r="Q70" s="107"/>
+      <c r="R70" s="107"/>
+      <c r="S70" s="110"/>
+    </row>
+    <row r="71" s="16" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A71" s="107">
+        <v>30200004</v>
+      </c>
+      <c r="B71" s="108">
+        <v>102000</v>
+      </c>
+      <c r="C71" s="108" t="s">
+        <v>145</v>
+      </c>
+      <c r="D71" s="107">
+        <v>302004</v>
+      </c>
+      <c r="E71" s="107" t="s">
+        <v>149</v>
+      </c>
+      <c r="F71" s="107" t="s">
+        <v>34</v>
+      </c>
+      <c r="G71" s="107">
+        <v>2020001</v>
+      </c>
+      <c r="H71" s="107" t="s">
+        <v>61</v>
+      </c>
+      <c r="I71" s="107" t="s">
+        <v>147</v>
+      </c>
+      <c r="J71" s="107"/>
+      <c r="K71" s="109">
+        <v>10200012</v>
+      </c>
+      <c r="L71" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="M71" s="107"/>
+      <c r="N71" s="107"/>
+      <c r="O71" s="107"/>
+      <c r="P71" s="107"/>
+      <c r="Q71" s="107"/>
+      <c r="R71" s="107"/>
+      <c r="S71" s="110"/>
+    </row>
+    <row r="72" s="16" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A72" s="107">
+        <v>30200005</v>
+      </c>
+      <c r="B72" s="108">
+        <v>102000</v>
+      </c>
+      <c r="C72" s="108" t="s">
+        <v>145</v>
+      </c>
+      <c r="D72" s="107">
+        <v>302005</v>
+      </c>
+      <c r="E72" s="107" t="s">
+        <v>151</v>
+      </c>
+      <c r="F72" s="107" t="s">
+        <v>34</v>
+      </c>
+      <c r="G72" s="107">
+        <v>2020001</v>
+      </c>
+      <c r="H72" s="107" t="s">
+        <v>61</v>
+      </c>
+      <c r="I72" s="107" t="s">
+        <v>147</v>
+      </c>
+      <c r="J72" s="107"/>
+      <c r="K72" s="109">
+        <v>10200013</v>
+      </c>
+      <c r="L72" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="M72" s="107"/>
+      <c r="N72" s="107"/>
+      <c r="O72" s="107"/>
+      <c r="P72" s="107"/>
+      <c r="Q72" s="107"/>
+      <c r="R72" s="107"/>
+      <c r="S72" s="110"/>
+    </row>
+    <row r="73" s="16" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A73" s="107">
+        <v>30200006</v>
+      </c>
+      <c r="B73" s="108">
+        <v>102000</v>
+      </c>
+      <c r="C73" s="108" t="s">
+        <v>145</v>
+      </c>
+      <c r="D73" s="107">
+        <v>302006</v>
+      </c>
+      <c r="E73" s="107" t="s">
+        <v>153</v>
+      </c>
+      <c r="F73" s="107" t="s">
+        <v>34</v>
+      </c>
+      <c r="G73" s="107">
+        <v>2020001</v>
+      </c>
+      <c r="H73" s="107" t="s">
+        <v>61</v>
+      </c>
+      <c r="I73" s="107" t="s">
+        <v>147</v>
+      </c>
+      <c r="J73" s="107"/>
+      <c r="K73" s="109">
+        <v>10200014</v>
+      </c>
+      <c r="L73" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="M73" s="107"/>
+      <c r="N73" s="107"/>
+      <c r="O73" s="107"/>
+      <c r="P73" s="107"/>
+      <c r="Q73" s="107"/>
+      <c r="R73" s="107"/>
+      <c r="S73" s="110"/>
+    </row>
+    <row r="74" s="16" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A74" s="107">
+        <v>30200007</v>
+      </c>
+      <c r="B74" s="108">
+        <v>102000</v>
+      </c>
+      <c r="C74" s="108" t="s">
+        <v>145</v>
+      </c>
+      <c r="D74" s="107">
+        <v>302007</v>
+      </c>
+      <c r="E74" s="107" t="s">
+        <v>155</v>
+      </c>
+      <c r="F74" s="107" t="s">
+        <v>54</v>
+      </c>
+      <c r="G74" s="107">
+        <v>2020001</v>
+      </c>
+      <c r="H74" s="107" t="s">
+        <v>61</v>
+      </c>
+      <c r="I74" s="107"/>
+      <c r="J74" s="107"/>
+      <c r="K74" s="109"/>
+      <c r="L74" s="5"/>
+      <c r="M74" s="107"/>
+      <c r="N74" s="107"/>
+      <c r="O74" s="107"/>
+      <c r="P74" s="107"/>
+      <c r="Q74" s="107" t="s">
+        <v>156</v>
+      </c>
+      <c r="R74" s="107" t="s">
         <v>40</v>
       </c>
-      <c r="S37" s="69" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="38" s="7" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A38" s="64">
-        <v>30240002</v>
-      </c>
-      <c r="B38" s="65">
-        <v>102400</v>
-      </c>
-      <c r="C38" s="65" t="s">
-        <v>32</v>
-      </c>
-      <c r="D38" s="64">
-        <v>32402</v>
-      </c>
-      <c r="E38" s="64" t="s">
-        <v>42</v>
-      </c>
-      <c r="F38" s="64" t="s">
+      <c r="S74" s="110"/>
+    </row>
+    <row r="75" s="16" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A75" s="107">
+        <v>30200008</v>
+      </c>
+      <c r="B75" s="108">
+        <v>102000</v>
+      </c>
+      <c r="C75" s="108" t="s">
+        <v>145</v>
+      </c>
+      <c r="D75" s="107">
+        <v>302008</v>
+      </c>
+      <c r="E75" s="107" t="s">
+        <v>157</v>
+      </c>
+      <c r="F75" s="107" t="s">
         <v>34</v>
       </c>
-      <c r="G38" s="64"/>
-      <c r="H38" s="64"/>
-      <c r="I38" s="64" t="s">
-        <v>43</v>
-      </c>
-      <c r="J38" s="64"/>
-      <c r="K38" s="66"/>
-      <c r="L38" s="64" t="s">
-        <v>36</v>
-      </c>
-      <c r="M38" s="64" t="s">
-        <v>37</v>
-      </c>
-      <c r="N38" s="64" t="s">
-        <v>38</v>
-      </c>
-      <c r="O38" s="64"/>
-      <c r="P38" s="64"/>
-      <c r="Q38" s="67" t="s">
-        <v>44</v>
-      </c>
-      <c r="R38" s="68" t="s">
+      <c r="G75" s="107">
+        <v>2020001</v>
+      </c>
+      <c r="H75" s="107" t="s">
+        <v>61</v>
+      </c>
+      <c r="I75" s="107"/>
+      <c r="J75" s="107"/>
+      <c r="K75" s="109">
+        <v>10200026</v>
+      </c>
+      <c r="L75" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="M75" s="107"/>
+      <c r="N75" s="107"/>
+      <c r="O75" s="107"/>
+      <c r="P75" s="107"/>
+      <c r="Q75" s="107" t="s">
+        <v>156</v>
+      </c>
+      <c r="R75" s="107" t="s">
         <v>40</v>
       </c>
-      <c r="S38" s="69"/>
-    </row>
-    <row r="39" s="7" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A39" s="64">
-        <v>30240003</v>
-      </c>
-      <c r="B39" s="65">
-        <v>102400</v>
-      </c>
-      <c r="C39" s="65" t="s">
-        <v>32</v>
-      </c>
-      <c r="D39" s="64">
-        <v>32403</v>
-      </c>
-      <c r="E39" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="F39" s="64" t="s">
+      <c r="S75" s="110"/>
+    </row>
+    <row r="76" s="17" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A76" s="111">
+        <v>30200009</v>
+      </c>
+      <c r="B76" s="112">
+        <v>102000</v>
+      </c>
+      <c r="C76" s="112" t="s">
+        <v>145</v>
+      </c>
+      <c r="D76" s="111">
+        <v>302009</v>
+      </c>
+      <c r="E76" s="111" t="s">
+        <v>159</v>
+      </c>
+      <c r="F76" s="111" t="s">
+        <v>109</v>
+      </c>
+      <c r="G76" s="111">
+        <v>2020002</v>
+      </c>
+      <c r="H76" s="111" t="s">
+        <v>61</v>
+      </c>
+      <c r="I76" s="111" t="s">
+        <v>81</v>
+      </c>
+      <c r="J76" s="111"/>
+      <c r="K76" s="113" t="s">
+        <v>160</v>
+      </c>
+      <c r="L76" s="111" t="s">
+        <v>161</v>
+      </c>
+      <c r="M76" s="111"/>
+      <c r="N76" s="111"/>
+      <c r="O76" s="111"/>
+      <c r="P76" s="111"/>
+      <c r="Q76" s="37"/>
+      <c r="R76" s="38"/>
+      <c r="S76" s="114"/>
+    </row>
+    <row r="77" s="17" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A77" s="111">
+        <v>30200010</v>
+      </c>
+      <c r="B77" s="112">
+        <v>102000</v>
+      </c>
+      <c r="C77" s="112" t="s">
+        <v>145</v>
+      </c>
+      <c r="D77" s="111">
+        <v>302010</v>
+      </c>
+      <c r="E77" s="111" t="s">
+        <v>162</v>
+      </c>
+      <c r="F77" s="111" t="s">
+        <v>54</v>
+      </c>
+      <c r="G77" s="111">
+        <v>2020002</v>
+      </c>
+      <c r="H77" s="111" t="s">
+        <v>61</v>
+      </c>
+      <c r="I77" s="111"/>
+      <c r="J77" s="111"/>
+      <c r="K77" s="115">
+        <v>10200120</v>
+      </c>
+      <c r="L77" s="116" t="s">
+        <v>163</v>
+      </c>
+      <c r="M77" s="111"/>
+      <c r="N77" s="111"/>
+      <c r="O77" s="111"/>
+      <c r="P77" s="111"/>
+      <c r="Q77" s="37" t="s">
+        <v>164</v>
+      </c>
+      <c r="R77" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="S77" s="114"/>
+    </row>
+    <row r="78" s="17" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A78" s="111">
+        <v>30200011</v>
+      </c>
+      <c r="B78" s="112">
+        <v>102000</v>
+      </c>
+      <c r="C78" s="112" t="s">
+        <v>145</v>
+      </c>
+      <c r="D78" s="111">
+        <v>302011</v>
+      </c>
+      <c r="E78" s="111" t="s">
+        <v>165</v>
+      </c>
+      <c r="F78" s="111" t="s">
+        <v>54</v>
+      </c>
+      <c r="G78" s="111">
+        <v>2020002</v>
+      </c>
+      <c r="H78" s="111" t="s">
+        <v>61</v>
+      </c>
+      <c r="I78" s="111"/>
+      <c r="J78" s="111"/>
+      <c r="K78" s="115">
+        <v>10200220</v>
+      </c>
+      <c r="L78" s="116" t="s">
+        <v>166</v>
+      </c>
+      <c r="M78" s="111"/>
+      <c r="N78" s="111"/>
+      <c r="O78" s="111"/>
+      <c r="P78" s="111"/>
+      <c r="Q78" s="37" t="s">
+        <v>164</v>
+      </c>
+      <c r="R78" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="S78" s="114"/>
+    </row>
+    <row r="79" s="17" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A79" s="111">
+        <v>30200012</v>
+      </c>
+      <c r="B79" s="112">
+        <v>102000</v>
+      </c>
+      <c r="C79" s="112" t="s">
+        <v>145</v>
+      </c>
+      <c r="D79" s="111">
+        <v>302012</v>
+      </c>
+      <c r="E79" s="111" t="s">
+        <v>167</v>
+      </c>
+      <c r="F79" s="111" t="s">
+        <v>54</v>
+      </c>
+      <c r="G79" s="111">
+        <v>2020002</v>
+      </c>
+      <c r="H79" s="111" t="s">
+        <v>61</v>
+      </c>
+      <c r="I79" s="111"/>
+      <c r="J79" s="111"/>
+      <c r="K79" s="115">
+        <v>10200320</v>
+      </c>
+      <c r="L79" s="116" t="s">
+        <v>168</v>
+      </c>
+      <c r="M79" s="111"/>
+      <c r="N79" s="111"/>
+      <c r="O79" s="111"/>
+      <c r="P79" s="111"/>
+      <c r="Q79" s="37" t="s">
+        <v>164</v>
+      </c>
+      <c r="R79" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="S79" s="114"/>
+    </row>
+    <row r="80" s="17" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A80" s="111">
+        <v>30200013</v>
+      </c>
+      <c r="B80" s="112">
+        <v>102000</v>
+      </c>
+      <c r="C80" s="112" t="s">
+        <v>145</v>
+      </c>
+      <c r="D80" s="111">
+        <v>302013</v>
+      </c>
+      <c r="E80" s="111" t="s">
+        <v>169</v>
+      </c>
+      <c r="F80" s="111" t="s">
+        <v>54</v>
+      </c>
+      <c r="G80" s="111">
+        <v>2020002</v>
+      </c>
+      <c r="H80" s="111" t="s">
+        <v>61</v>
+      </c>
+      <c r="I80" s="111"/>
+      <c r="J80" s="111"/>
+      <c r="K80" s="115">
+        <v>10200420</v>
+      </c>
+      <c r="L80" s="116" t="s">
+        <v>170</v>
+      </c>
+      <c r="M80" s="111"/>
+      <c r="N80" s="111"/>
+      <c r="O80" s="111"/>
+      <c r="P80" s="111"/>
+      <c r="Q80" s="37" t="s">
+        <v>164</v>
+      </c>
+      <c r="R80" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="S80" s="114"/>
+    </row>
+    <row r="81" s="11" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A81" s="87">
+        <v>30200014</v>
+      </c>
+      <c r="B81" s="88">
+        <v>102000</v>
+      </c>
+      <c r="C81" s="88" t="s">
+        <v>145</v>
+      </c>
+      <c r="D81" s="87">
+        <v>302014</v>
+      </c>
+      <c r="E81" s="87" t="s">
+        <v>171</v>
+      </c>
+      <c r="F81" s="87" t="s">
+        <v>109</v>
+      </c>
+      <c r="G81" s="87">
+        <v>2020003</v>
+      </c>
+      <c r="H81" s="87" t="s">
+        <v>61</v>
+      </c>
+      <c r="I81" s="87" t="s">
+        <v>81</v>
+      </c>
+      <c r="J81" s="87"/>
+      <c r="K81" s="89" t="s">
+        <v>172</v>
+      </c>
+      <c r="L81" s="87" t="s">
+        <v>173</v>
+      </c>
+      <c r="M81" s="87"/>
+      <c r="N81" s="87"/>
+      <c r="O81" s="87"/>
+      <c r="P81" s="87"/>
+      <c r="Q81" s="87"/>
+      <c r="R81" s="87"/>
+      <c r="S81" s="90"/>
+    </row>
+    <row r="82" s="11" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A82" s="87">
+        <v>30200015</v>
+      </c>
+      <c r="B82" s="88">
+        <v>102000</v>
+      </c>
+      <c r="C82" s="88" t="s">
+        <v>145</v>
+      </c>
+      <c r="D82" s="87">
+        <v>302015</v>
+      </c>
+      <c r="E82" s="87" t="s">
+        <v>174</v>
+      </c>
+      <c r="F82" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="G39" s="64"/>
-      <c r="H39" s="64"/>
-      <c r="I39" s="64" t="s">
-        <v>46</v>
-      </c>
-      <c r="J39" s="64"/>
-      <c r="K39" s="66"/>
-      <c r="L39" s="64" t="s">
-        <v>36</v>
-      </c>
-      <c r="M39" s="64" t="s">
-        <v>37</v>
-      </c>
-      <c r="N39" s="64" t="s">
-        <v>38</v>
-      </c>
-      <c r="O39" s="64"/>
-      <c r="P39" s="64"/>
-      <c r="Q39" s="67" t="s">
-        <v>47</v>
-      </c>
-      <c r="R39" s="68" t="s">
+      <c r="G82" s="87">
+        <v>2020003</v>
+      </c>
+      <c r="H82" s="87" t="s">
+        <v>61</v>
+      </c>
+      <c r="I82" s="87"/>
+      <c r="J82" s="87"/>
+      <c r="K82" s="89" t="s">
+        <v>175</v>
+      </c>
+      <c r="L82" s="87" t="s">
+        <v>176</v>
+      </c>
+      <c r="M82" s="87"/>
+      <c r="N82" s="87"/>
+      <c r="O82" s="87"/>
+      <c r="P82" s="87"/>
+      <c r="Q82" s="117" t="s">
+        <v>164</v>
+      </c>
+      <c r="R82" s="118" t="s">
         <v>40</v>
       </c>
-      <c r="S39" s="69"/>
-    </row>
-    <row r="40" s="7" customFormat="1" ht="15" customHeight="1" spans="1:19">
-      <c r="A40" s="64">
-        <v>30240004</v>
-      </c>
-      <c r="B40" s="65">
-        <v>102400</v>
-      </c>
-      <c r="C40" s="65" t="s">
-        <v>32</v>
-      </c>
-      <c r="D40" s="64">
-        <v>32404</v>
-      </c>
-      <c r="E40" s="64" t="s">
-        <v>48</v>
-      </c>
-      <c r="F40" s="64" t="s">
+      <c r="S82" s="90"/>
+    </row>
+    <row r="83" s="11" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A83" s="87">
+        <v>30200016</v>
+      </c>
+      <c r="B83" s="88">
+        <v>102000</v>
+      </c>
+      <c r="C83" s="88" t="s">
+        <v>145</v>
+      </c>
+      <c r="D83" s="87">
+        <v>302016</v>
+      </c>
+      <c r="E83" s="87" t="s">
+        <v>177</v>
+      </c>
+      <c r="F83" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="G40" s="64"/>
-      <c r="H40" s="64"/>
-      <c r="I40" s="64" t="s">
-        <v>49</v>
-      </c>
-      <c r="J40" s="64"/>
-      <c r="K40" s="66"/>
-      <c r="L40" s="64" t="s">
-        <v>36</v>
-      </c>
-      <c r="M40" s="64" t="s">
-        <v>37</v>
-      </c>
-      <c r="N40" s="64" t="s">
-        <v>38</v>
-      </c>
-      <c r="O40" s="64"/>
-      <c r="P40" s="64"/>
-      <c r="Q40" s="67" t="s">
-        <v>50</v>
-      </c>
-      <c r="R40" s="68" t="s">
+      <c r="G83" s="87">
+        <v>2020003</v>
+      </c>
+      <c r="H83" s="87" t="s">
+        <v>61</v>
+      </c>
+      <c r="I83" s="87"/>
+      <c r="J83" s="87"/>
+      <c r="K83" s="89" t="s">
+        <v>178</v>
+      </c>
+      <c r="L83" s="87" t="s">
+        <v>179</v>
+      </c>
+      <c r="M83" s="87"/>
+      <c r="N83" s="87"/>
+      <c r="O83" s="87"/>
+      <c r="P83" s="87"/>
+      <c r="Q83" s="117" t="s">
+        <v>164</v>
+      </c>
+      <c r="R83" s="118" t="s">
         <v>40</v>
       </c>
-      <c r="S40" s="69"/>
-    </row>
-    <row r="41" s="7" customFormat="1" ht="15" customHeight="1" spans="1:19">
-      <c r="A41" s="64">
-        <v>30240005</v>
-      </c>
-      <c r="B41" s="65">
-        <v>102400</v>
-      </c>
-      <c r="C41" s="65" t="s">
-        <v>32</v>
-      </c>
-      <c r="D41" s="64">
-        <v>32411</v>
-      </c>
-      <c r="E41" s="64" t="s">
-        <v>51</v>
-      </c>
-      <c r="F41" s="64" t="s">
+      <c r="S83" s="90"/>
+    </row>
+    <row r="84" s="11" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A84" s="87">
+        <v>30200017</v>
+      </c>
+      <c r="B84" s="88">
+        <v>102000</v>
+      </c>
+      <c r="C84" s="88" t="s">
+        <v>145</v>
+      </c>
+      <c r="D84" s="87">
+        <v>302017</v>
+      </c>
+      <c r="E84" s="87" t="s">
+        <v>180</v>
+      </c>
+      <c r="F84" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="G41" s="64"/>
-      <c r="H41" s="64"/>
-      <c r="I41" s="64" t="s">
-        <v>52</v>
-      </c>
-      <c r="J41" s="64"/>
-      <c r="K41" s="66"/>
-      <c r="L41" s="64" t="s">
-        <v>36</v>
-      </c>
-      <c r="M41" s="64" t="s">
-        <v>53</v>
-      </c>
-      <c r="N41" s="64"/>
-      <c r="O41" s="64" t="s">
-        <v>54</v>
-      </c>
-      <c r="P41" s="64"/>
-      <c r="Q41" s="67"/>
-      <c r="R41" s="67"/>
-      <c r="S41" s="69"/>
-    </row>
-    <row r="42" s="7" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A42" s="64">
-        <v>30240006</v>
-      </c>
-      <c r="B42" s="65">
-        <v>102400</v>
-      </c>
-      <c r="C42" s="65" t="s">
-        <v>32</v>
-      </c>
-      <c r="D42" s="64">
-        <v>32421</v>
-      </c>
-      <c r="E42" s="64" t="s">
-        <v>55</v>
-      </c>
-      <c r="F42" s="64" t="s">
+      <c r="G84" s="87">
+        <v>2020003</v>
+      </c>
+      <c r="H84" s="87" t="s">
+        <v>61</v>
+      </c>
+      <c r="I84" s="87"/>
+      <c r="J84" s="87"/>
+      <c r="K84" s="89" t="s">
+        <v>181</v>
+      </c>
+      <c r="L84" s="87" t="s">
+        <v>182</v>
+      </c>
+      <c r="M84" s="87"/>
+      <c r="N84" s="87"/>
+      <c r="O84" s="87"/>
+      <c r="P84" s="87"/>
+      <c r="Q84" s="117" t="s">
+        <v>164</v>
+      </c>
+      <c r="R84" s="118" t="s">
+        <v>40</v>
+      </c>
+      <c r="S84" s="90"/>
+    </row>
+    <row r="85" s="11" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A85" s="87">
+        <v>30200018</v>
+      </c>
+      <c r="B85" s="88">
+        <v>102000</v>
+      </c>
+      <c r="C85" s="88" t="s">
+        <v>145</v>
+      </c>
+      <c r="D85" s="87">
+        <v>302018</v>
+      </c>
+      <c r="E85" s="87" t="s">
+        <v>183</v>
+      </c>
+      <c r="F85" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="G42" s="64"/>
-      <c r="H42" s="64"/>
-      <c r="I42" s="64" t="s">
-        <v>56</v>
-      </c>
-      <c r="J42" s="64"/>
-      <c r="K42" s="66"/>
-      <c r="L42" s="64" t="s">
-        <v>36</v>
-      </c>
-      <c r="M42" s="64" t="s">
-        <v>57</v>
-      </c>
-      <c r="N42" s="64" t="s">
-        <v>38</v>
-      </c>
-      <c r="O42" s="64" t="s">
-        <v>54</v>
-      </c>
-      <c r="P42" s="64"/>
-      <c r="Q42" s="64"/>
-      <c r="R42" s="64"/>
-      <c r="S42" s="69"/>
-    </row>
-    <row r="43" s="7" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A43" s="64">
-        <v>30240007</v>
-      </c>
-      <c r="B43" s="65">
-        <v>102400</v>
-      </c>
-      <c r="C43" s="65" t="s">
-        <v>32</v>
-      </c>
-      <c r="D43" s="64">
-        <v>32431</v>
-      </c>
-      <c r="E43" s="64" t="s">
-        <v>58</v>
-      </c>
-      <c r="F43" s="64" t="s">
-        <v>59</v>
-      </c>
-      <c r="G43" s="64">
-        <v>2024001</v>
-      </c>
-      <c r="H43" s="64" t="s">
-        <v>60</v>
-      </c>
-      <c r="I43" s="64" t="s">
+      <c r="G85" s="87">
+        <v>2020003</v>
+      </c>
+      <c r="H85" s="87" t="s">
         <v>61</v>
       </c>
-      <c r="J43" s="64"/>
-      <c r="K43" s="66">
-        <v>10240091</v>
-      </c>
-      <c r="L43" s="64"/>
-      <c r="M43" s="64"/>
-      <c r="N43" s="64"/>
-      <c r="O43" s="64"/>
-      <c r="P43" s="64"/>
-      <c r="Q43" s="64"/>
-      <c r="R43" s="64"/>
-      <c r="S43" s="69"/>
-    </row>
-    <row r="44" s="7" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A44" s="64">
-        <v>30240008</v>
-      </c>
-      <c r="B44" s="65">
-        <v>102400</v>
-      </c>
-      <c r="C44" s="65" t="s">
-        <v>32</v>
-      </c>
-      <c r="D44" s="64">
-        <v>32432</v>
-      </c>
-      <c r="E44" s="64" t="s">
-        <v>62</v>
-      </c>
-      <c r="F44" s="64" t="s">
-        <v>53</v>
-      </c>
-      <c r="G44" s="64">
-        <v>2024001</v>
-      </c>
-      <c r="H44" s="64" t="s">
-        <v>60</v>
-      </c>
-      <c r="I44" s="64" t="s">
-        <v>63</v>
-      </c>
-      <c r="J44" s="64"/>
-      <c r="K44" s="70" t="s">
-        <v>93</v>
-      </c>
-      <c r="L44" s="64"/>
-      <c r="M44" s="64"/>
-      <c r="N44" s="64"/>
-      <c r="O44" s="64"/>
-      <c r="P44" s="64"/>
-      <c r="Q44" s="64"/>
-      <c r="R44" s="64"/>
-      <c r="S44" s="69"/>
-    </row>
-    <row r="45" s="7" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A45" s="64">
-        <v>30240009</v>
-      </c>
-      <c r="B45" s="65">
-        <v>102400</v>
-      </c>
-      <c r="C45" s="65" t="s">
-        <v>32</v>
-      </c>
-      <c r="D45" s="64">
-        <v>32433</v>
-      </c>
-      <c r="E45" s="64" t="s">
-        <v>65</v>
-      </c>
-      <c r="F45" s="64" t="s">
-        <v>53</v>
-      </c>
-      <c r="G45" s="64">
-        <v>2024001</v>
-      </c>
-      <c r="H45" s="64" t="s">
-        <v>60</v>
-      </c>
-      <c r="I45" s="64" t="s">
-        <v>66</v>
-      </c>
-      <c r="J45" s="64"/>
-      <c r="K45" s="66" t="s">
-        <v>94</v>
-      </c>
-      <c r="L45" s="64"/>
-      <c r="M45" s="64"/>
-      <c r="N45" s="64"/>
-      <c r="O45" s="64"/>
-      <c r="P45" s="64"/>
-      <c r="Q45" s="64"/>
-      <c r="R45" s="64"/>
-      <c r="S45" s="69"/>
-    </row>
-    <row r="46" s="7" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A46" s="64">
-        <v>30240010</v>
-      </c>
-      <c r="B46" s="65">
-        <v>102400</v>
-      </c>
-      <c r="C46" s="65" t="s">
-        <v>32</v>
-      </c>
-      <c r="D46" s="64">
-        <v>32441</v>
-      </c>
-      <c r="E46" s="64" t="s">
-        <v>68</v>
-      </c>
-      <c r="F46" s="64" t="s">
-        <v>34</v>
-      </c>
-      <c r="G46" s="64"/>
-      <c r="H46" s="64"/>
-      <c r="I46" s="64" t="s">
-        <v>69</v>
-      </c>
-      <c r="J46" s="64"/>
-      <c r="K46" s="70"/>
-      <c r="L46" s="64" t="s">
-        <v>36</v>
-      </c>
-      <c r="M46" s="64" t="s">
-        <v>70</v>
-      </c>
-      <c r="N46" s="64"/>
-      <c r="O46" s="64"/>
-      <c r="P46" s="64"/>
-      <c r="Q46" s="67" t="s">
-        <v>71</v>
-      </c>
-      <c r="R46" s="71" t="s">
-        <v>72</v>
-      </c>
-      <c r="S46" s="67" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="47" s="7" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A47" s="64">
-        <v>30240011</v>
-      </c>
-      <c r="B47" s="65">
-        <v>102400</v>
-      </c>
-      <c r="C47" s="65" t="s">
-        <v>32</v>
-      </c>
-      <c r="D47" s="64">
-        <v>32442</v>
-      </c>
-      <c r="E47" s="64" t="s">
-        <v>74</v>
-      </c>
-      <c r="F47" s="64" t="s">
-        <v>34</v>
-      </c>
-      <c r="G47" s="64"/>
-      <c r="H47" s="64"/>
-      <c r="I47" s="64" t="s">
-        <v>75</v>
-      </c>
-      <c r="J47" s="64"/>
-      <c r="K47" s="66"/>
-      <c r="L47" s="64" t="s">
-        <v>36</v>
-      </c>
-      <c r="M47" s="64" t="s">
-        <v>57</v>
-      </c>
-      <c r="N47" s="64"/>
-      <c r="O47" s="64"/>
-      <c r="P47" s="64"/>
-      <c r="Q47" s="64"/>
-      <c r="R47" s="64"/>
-      <c r="S47" s="69"/>
-    </row>
-    <row r="48" s="7" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A48" s="64">
-        <v>30240012</v>
-      </c>
-      <c r="B48" s="65">
-        <v>102400</v>
-      </c>
-      <c r="C48" s="65" t="s">
-        <v>32</v>
-      </c>
-      <c r="D48" s="64">
-        <v>32443</v>
-      </c>
-      <c r="E48" s="64" t="s">
-        <v>76</v>
-      </c>
-      <c r="F48" s="64" t="s">
-        <v>53</v>
-      </c>
-      <c r="G48" s="64">
-        <v>2024001</v>
-      </c>
-      <c r="H48" s="64" t="s">
-        <v>60</v>
-      </c>
-      <c r="I48" s="64" t="s">
-        <v>66</v>
-      </c>
-      <c r="J48" s="64"/>
-      <c r="K48" s="66" t="s">
-        <v>94</v>
-      </c>
-      <c r="L48" s="64"/>
-      <c r="M48" s="64"/>
-      <c r="N48" s="64"/>
-      <c r="O48" s="64"/>
-      <c r="P48" s="64"/>
-      <c r="Q48" s="64"/>
-      <c r="R48" s="64"/>
-      <c r="S48" s="69"/>
-    </row>
-    <row r="49" s="8" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A49" s="72">
-        <v>30170001</v>
-      </c>
-      <c r="B49" s="73">
-        <v>101700</v>
-      </c>
-      <c r="C49" s="73" t="s">
-        <v>95</v>
-      </c>
-      <c r="D49" s="72">
-        <v>301701</v>
-      </c>
-      <c r="E49" s="72" t="s">
-        <v>96</v>
-      </c>
-      <c r="F49" s="72" t="s">
-        <v>79</v>
-      </c>
-      <c r="G49" s="72">
-        <v>2017001</v>
-      </c>
-      <c r="H49" s="72" t="s">
-        <v>60</v>
-      </c>
-      <c r="I49" s="72" t="s">
-        <v>80</v>
-      </c>
-      <c r="J49" s="72"/>
-      <c r="K49" s="74" t="s">
-        <v>97</v>
-      </c>
-      <c r="L49" s="72"/>
-      <c r="M49" s="72"/>
-      <c r="N49" s="72"/>
-      <c r="O49" s="72"/>
-      <c r="P49" s="72"/>
-      <c r="Q49" s="72"/>
-      <c r="R49" s="72"/>
-      <c r="S49" s="75"/>
-    </row>
-    <row r="50" s="8" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A50" s="72">
-        <v>30170002</v>
-      </c>
-      <c r="B50" s="73">
-        <v>101700</v>
-      </c>
-      <c r="C50" s="73" t="s">
-        <v>95</v>
-      </c>
-      <c r="D50" s="72">
-        <v>301702</v>
-      </c>
-      <c r="E50" s="72" t="s">
-        <v>98</v>
-      </c>
-      <c r="F50" s="72" t="s">
-        <v>83</v>
-      </c>
-      <c r="G50" s="72">
-        <v>2017001</v>
-      </c>
-      <c r="H50" s="72" t="s">
-        <v>60</v>
-      </c>
-      <c r="I50" s="72" t="s">
-        <v>80</v>
-      </c>
-      <c r="J50" s="72"/>
-      <c r="K50" s="74" t="s">
-        <v>97</v>
-      </c>
-      <c r="L50" s="72"/>
-      <c r="M50" s="72"/>
-      <c r="N50" s="72"/>
-      <c r="O50" s="72"/>
-      <c r="P50" s="72"/>
-      <c r="Q50" s="72"/>
-      <c r="R50" s="72"/>
-      <c r="S50" s="75"/>
-    </row>
-    <row r="51" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A51" s="59">
-        <v>30220001</v>
-      </c>
-      <c r="B51" s="60">
-        <v>102200</v>
-      </c>
-      <c r="C51" s="60" t="s">
-        <v>99</v>
-      </c>
-      <c r="D51" s="59">
-        <v>302201</v>
-      </c>
-      <c r="E51" s="59" t="s">
-        <v>100</v>
-      </c>
-      <c r="F51" s="59" t="s">
-        <v>101</v>
-      </c>
-      <c r="G51" s="59">
-        <v>2022001</v>
-      </c>
-      <c r="H51" s="59" t="s">
-        <v>60</v>
-      </c>
-      <c r="I51" s="59"/>
-      <c r="J51" s="59"/>
-      <c r="K51" s="76" t="s">
-        <v>102</v>
-      </c>
-      <c r="L51" s="59" t="s">
-        <v>103</v>
-      </c>
-      <c r="M51" s="59"/>
-      <c r="N51" s="59"/>
-      <c r="O51" s="59"/>
-      <c r="P51" s="59"/>
-      <c r="Q51" s="59"/>
-      <c r="R51" s="59"/>
-      <c r="S51" s="77"/>
-    </row>
-    <row r="52" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A52" s="59">
-        <v>30220002</v>
-      </c>
-      <c r="B52" s="60">
-        <v>102200</v>
-      </c>
-      <c r="C52" s="60" t="s">
-        <v>99</v>
-      </c>
-      <c r="D52" s="59">
-        <v>302202</v>
-      </c>
-      <c r="E52" s="59" t="s">
-        <v>104</v>
-      </c>
-      <c r="F52" s="59" t="s">
-        <v>101</v>
-      </c>
-      <c r="G52" s="59">
-        <v>2022001</v>
-      </c>
-      <c r="H52" s="59" t="s">
-        <v>60</v>
-      </c>
-      <c r="I52" s="59"/>
-      <c r="J52" s="59"/>
-      <c r="K52" s="76" t="s">
-        <v>105</v>
-      </c>
-      <c r="L52" s="59" t="s">
-        <v>103</v>
-      </c>
-      <c r="M52" s="59"/>
-      <c r="N52" s="59"/>
-      <c r="O52" s="59"/>
-      <c r="P52" s="59"/>
-      <c r="Q52" s="59"/>
-      <c r="R52" s="59"/>
-      <c r="S52" s="77"/>
-    </row>
-    <row r="53" s="9" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A53" s="78">
-        <v>30210001</v>
-      </c>
-      <c r="B53" s="79">
-        <v>102100</v>
-      </c>
-      <c r="C53" s="79" t="s">
-        <v>106</v>
-      </c>
-      <c r="D53" s="78">
-        <v>302101</v>
-      </c>
-      <c r="E53" s="78" t="s">
-        <v>107</v>
-      </c>
-      <c r="F53" s="78" t="s">
-        <v>108</v>
-      </c>
-      <c r="G53" s="78">
-        <v>2021001</v>
-      </c>
-      <c r="H53" s="78" t="s">
-        <v>60</v>
-      </c>
-      <c r="I53" s="78" t="s">
-        <v>80</v>
-      </c>
-      <c r="J53" s="78"/>
-      <c r="K53" s="80" t="s">
-        <v>109</v>
-      </c>
-      <c r="L53" s="78" t="s">
-        <v>110</v>
-      </c>
-      <c r="M53" s="78"/>
-      <c r="N53" s="78"/>
-      <c r="O53" s="78"/>
-      <c r="P53" s="78"/>
-      <c r="Q53" s="78"/>
-      <c r="R53" s="78"/>
-      <c r="S53" s="81"/>
-    </row>
-    <row r="54" s="9" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A54" s="78">
-        <v>30210002</v>
-      </c>
-      <c r="B54" s="79">
-        <v>102100</v>
-      </c>
-      <c r="C54" s="79" t="s">
-        <v>106</v>
-      </c>
-      <c r="D54" s="78">
-        <v>302102</v>
-      </c>
-      <c r="E54" s="78" t="s">
-        <v>111</v>
-      </c>
-      <c r="F54" s="78" t="s">
-        <v>34</v>
-      </c>
-      <c r="G54" s="78"/>
-      <c r="H54" s="78"/>
-      <c r="I54" s="78" t="s">
-        <v>112</v>
-      </c>
-      <c r="J54" s="78"/>
-      <c r="K54" s="80"/>
-      <c r="L54" s="78"/>
-      <c r="M54" s="78" t="s">
-        <v>37</v>
-      </c>
-      <c r="N54" s="78" t="s">
-        <v>113</v>
-      </c>
-      <c r="O54" s="78"/>
-      <c r="P54" s="78"/>
-      <c r="Q54" s="78" t="s">
-        <v>114</v>
-      </c>
-      <c r="R54" s="78"/>
-      <c r="S54" s="81"/>
-    </row>
-    <row r="55" s="10" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A55" s="82">
-        <v>30180001</v>
-      </c>
-      <c r="B55" s="83">
-        <v>101800</v>
-      </c>
-      <c r="C55" s="83" t="s">
-        <v>115</v>
-      </c>
-      <c r="D55" s="82">
-        <v>301801</v>
-      </c>
-      <c r="E55" s="82" t="s">
-        <v>80</v>
-      </c>
-      <c r="F55" s="82" t="s">
-        <v>116</v>
-      </c>
-      <c r="G55" s="82">
-        <v>2018002</v>
-      </c>
-      <c r="H55" s="82" t="s">
-        <v>60</v>
-      </c>
-      <c r="I55" s="82" t="s">
-        <v>80</v>
-      </c>
-      <c r="J55" s="82"/>
-      <c r="K55" s="84">
-        <v>10180041</v>
-      </c>
-      <c r="L55" s="82"/>
-      <c r="M55" s="82"/>
-      <c r="N55" s="82"/>
-      <c r="O55" s="82"/>
-      <c r="P55" s="82"/>
-      <c r="Q55" s="82"/>
-      <c r="R55" s="82"/>
-      <c r="S55" s="85"/>
-    </row>
-    <row r="56" s="11" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A56" s="86">
-        <v>30250001</v>
-      </c>
-      <c r="B56" s="87">
-        <v>102500</v>
-      </c>
-      <c r="C56" s="87" t="s">
-        <v>117</v>
-      </c>
-      <c r="D56" s="86">
-        <v>302501</v>
-      </c>
-      <c r="E56" s="86" t="s">
-        <v>107</v>
-      </c>
-      <c r="F56" s="86" t="s">
-        <v>108</v>
-      </c>
-      <c r="G56" s="86">
-        <v>2025001</v>
-      </c>
-      <c r="H56" s="86" t="s">
-        <v>60</v>
-      </c>
-      <c r="I56" s="86" t="s">
-        <v>80</v>
-      </c>
-      <c r="J56" s="86"/>
-      <c r="K56" s="88" t="s">
-        <v>118</v>
-      </c>
-      <c r="L56" s="86" t="s">
-        <v>119</v>
-      </c>
-      <c r="M56" s="86"/>
-      <c r="N56" s="86"/>
-      <c r="O56" s="86"/>
-      <c r="P56" s="86"/>
-      <c r="Q56" s="86"/>
-      <c r="R56" s="86"/>
-      <c r="S56" s="89"/>
-    </row>
-    <row r="57" s="11" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A57" s="86">
-        <v>30250002</v>
-      </c>
-      <c r="B57" s="87">
-        <v>102500</v>
-      </c>
-      <c r="C57" s="87" t="s">
-        <v>117</v>
-      </c>
-      <c r="D57" s="86">
-        <v>302502</v>
-      </c>
-      <c r="E57" s="86" t="s">
-        <v>120</v>
-      </c>
-      <c r="F57" s="86" t="s">
-        <v>121</v>
-      </c>
-      <c r="G57" s="86">
-        <v>2025001</v>
-      </c>
-      <c r="H57" s="86" t="s">
-        <v>60</v>
-      </c>
-      <c r="I57" s="86" t="s">
-        <v>80</v>
-      </c>
-      <c r="J57" s="86"/>
-      <c r="K57" s="88" t="s">
-        <v>118</v>
-      </c>
-      <c r="L57" s="86" t="s">
-        <v>119</v>
-      </c>
-      <c r="M57" s="86"/>
-      <c r="N57" s="86"/>
-      <c r="O57" s="86"/>
-      <c r="P57" s="86"/>
-      <c r="Q57" s="86"/>
-      <c r="R57" s="86"/>
-      <c r="S57" s="89"/>
-    </row>
-    <row r="58" s="11" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A58" s="86">
-        <v>30250003</v>
-      </c>
-      <c r="B58" s="87">
-        <v>102500</v>
-      </c>
-      <c r="C58" s="87" t="s">
-        <v>117</v>
-      </c>
-      <c r="D58" s="86">
-        <v>302503</v>
-      </c>
-      <c r="E58" s="86" t="s">
-        <v>122</v>
-      </c>
-      <c r="F58" s="86" t="s">
-        <v>123</v>
-      </c>
-      <c r="G58" s="86">
-        <v>2025001</v>
-      </c>
-      <c r="H58" s="86" t="s">
-        <v>60</v>
-      </c>
-      <c r="I58" s="86" t="s">
-        <v>80</v>
-      </c>
-      <c r="J58" s="86"/>
-      <c r="K58" s="88" t="s">
-        <v>118</v>
-      </c>
-      <c r="L58" s="86" t="s">
-        <v>119</v>
-      </c>
-      <c r="M58" s="86"/>
-      <c r="N58" s="86"/>
-      <c r="O58" s="86"/>
-      <c r="P58" s="86"/>
-      <c r="Q58" s="86"/>
-      <c r="R58" s="86"/>
-      <c r="S58" s="89"/>
-    </row>
-    <row r="59" s="12" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A59" s="90">
-        <v>30230001</v>
-      </c>
-      <c r="B59" s="91">
-        <v>102300</v>
-      </c>
-      <c r="C59" s="91" t="s">
-        <v>124</v>
-      </c>
-      <c r="D59" s="90">
-        <v>302301</v>
-      </c>
-      <c r="E59" s="90" t="s">
-        <v>107</v>
-      </c>
-      <c r="F59" s="90" t="s">
-        <v>108</v>
-      </c>
-      <c r="G59" s="90">
-        <v>2023001</v>
-      </c>
-      <c r="H59" s="90" t="s">
-        <v>60</v>
-      </c>
-      <c r="I59" s="90" t="s">
-        <v>80</v>
-      </c>
-      <c r="J59" s="90"/>
-      <c r="K59" s="92" t="s">
-        <v>125</v>
-      </c>
-      <c r="L59" s="90" t="s">
-        <v>126</v>
-      </c>
-      <c r="M59" s="90"/>
-      <c r="N59" s="90"/>
-      <c r="O59" s="90"/>
-      <c r="P59" s="90"/>
-      <c r="Q59" s="90"/>
-      <c r="R59" s="90"/>
-      <c r="S59" s="93"/>
-    </row>
-    <row r="60" s="12" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A60" s="90">
-        <v>30230002</v>
-      </c>
-      <c r="B60" s="91">
-        <v>102300</v>
-      </c>
-      <c r="C60" s="91" t="s">
-        <v>124</v>
-      </c>
-      <c r="D60" s="90">
-        <v>302302</v>
-      </c>
-      <c r="E60" s="90" t="s">
-        <v>127</v>
-      </c>
-      <c r="F60" s="90" t="s">
-        <v>79</v>
-      </c>
-      <c r="G60" s="90">
-        <v>2023001</v>
-      </c>
-      <c r="H60" s="90" t="s">
-        <v>60</v>
-      </c>
-      <c r="I60" s="90" t="s">
-        <v>80</v>
-      </c>
-      <c r="J60" s="90"/>
-      <c r="K60" s="92" t="s">
-        <v>125</v>
-      </c>
-      <c r="L60" s="90" t="s">
-        <v>126</v>
-      </c>
-      <c r="M60" s="90"/>
-      <c r="N60" s="90"/>
-      <c r="O60" s="90"/>
-      <c r="P60" s="90"/>
-      <c r="Q60" s="90"/>
-      <c r="R60" s="90"/>
-      <c r="S60" s="93"/>
-    </row>
-    <row r="61" s="12" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A61" s="90">
-        <v>30230003</v>
-      </c>
-      <c r="B61" s="91">
-        <v>102300</v>
-      </c>
-      <c r="C61" s="91" t="s">
-        <v>124</v>
-      </c>
-      <c r="D61" s="90">
-        <v>302303</v>
-      </c>
-      <c r="E61" s="90" t="s">
-        <v>128</v>
-      </c>
-      <c r="F61" s="90" t="s">
-        <v>83</v>
-      </c>
-      <c r="G61" s="90">
-        <v>2023001</v>
-      </c>
-      <c r="H61" s="90" t="s">
-        <v>60</v>
-      </c>
-      <c r="I61" s="90" t="s">
-        <v>80</v>
-      </c>
-      <c r="J61" s="90"/>
-      <c r="K61" s="92" t="s">
-        <v>125</v>
-      </c>
-      <c r="L61" s="90" t="s">
-        <v>126</v>
-      </c>
-      <c r="M61" s="90"/>
-      <c r="N61" s="90"/>
-      <c r="O61" s="90"/>
-      <c r="P61" s="90"/>
-      <c r="Q61" s="90"/>
-      <c r="R61" s="90"/>
-      <c r="S61" s="93"/>
-    </row>
-    <row r="62" s="13" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A62" s="94">
-        <v>30350001</v>
-      </c>
-      <c r="B62" s="95">
-        <v>103500</v>
-      </c>
-      <c r="C62" s="95" t="s">
-        <v>129</v>
-      </c>
-      <c r="D62" s="94">
-        <v>303501</v>
-      </c>
-      <c r="E62" s="94" t="s">
-        <v>130</v>
-      </c>
-      <c r="F62" s="94" t="s">
-        <v>59</v>
-      </c>
-      <c r="G62" s="94">
-        <v>2035002</v>
-      </c>
-      <c r="H62" s="94" t="s">
-        <v>60</v>
-      </c>
-      <c r="I62" s="94" t="s">
-        <v>131</v>
-      </c>
-      <c r="J62" s="94"/>
-      <c r="K62" s="96" t="s">
-        <v>132</v>
-      </c>
-      <c r="L62" s="94" t="s">
-        <v>133</v>
-      </c>
-      <c r="M62" s="94"/>
-      <c r="N62" s="94"/>
-      <c r="O62" s="94"/>
-      <c r="P62" s="94"/>
-      <c r="Q62" s="94"/>
-      <c r="R62" s="94"/>
-      <c r="S62" s="97"/>
-    </row>
-    <row r="63" s="13" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A63" s="94">
-        <v>30350002</v>
-      </c>
-      <c r="B63" s="95">
-        <v>103500</v>
-      </c>
-      <c r="C63" s="95" t="s">
-        <v>129</v>
-      </c>
-      <c r="D63" s="94">
-        <v>303502</v>
-      </c>
-      <c r="E63" s="94" t="s">
-        <v>134</v>
-      </c>
-      <c r="F63" s="94" t="s">
-        <v>34</v>
-      </c>
-      <c r="G63" s="94"/>
-      <c r="H63" s="94"/>
-      <c r="I63" s="94"/>
-      <c r="J63" s="94"/>
-      <c r="K63" s="96"/>
-      <c r="L63" s="94"/>
-      <c r="M63" s="94" t="s">
-        <v>53</v>
-      </c>
-      <c r="N63" s="94"/>
-      <c r="O63" s="94" t="s">
-        <v>135</v>
-      </c>
-      <c r="P63" s="94"/>
-      <c r="Q63" s="94"/>
-      <c r="R63" s="94"/>
-      <c r="S63" s="97"/>
-    </row>
-    <row r="64" s="13" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A64" s="94">
-        <v>30350101</v>
-      </c>
-      <c r="B64" s="95">
-        <v>103501</v>
-      </c>
-      <c r="C64" s="95" t="s">
-        <v>136</v>
-      </c>
-      <c r="D64" s="94">
-        <v>303503</v>
-      </c>
-      <c r="E64" s="94" t="s">
-        <v>130</v>
-      </c>
-      <c r="F64" s="94" t="s">
-        <v>59</v>
-      </c>
-      <c r="G64" s="94">
-        <v>2035012</v>
-      </c>
-      <c r="H64" s="94" t="s">
-        <v>60</v>
-      </c>
-      <c r="I64" s="94" t="s">
-        <v>131</v>
-      </c>
-      <c r="J64" s="94"/>
-      <c r="K64" s="96" t="s">
-        <v>137</v>
-      </c>
-      <c r="L64" s="94" t="s">
-        <v>133</v>
-      </c>
-      <c r="M64" s="94"/>
-      <c r="N64" s="94"/>
-      <c r="O64" s="94"/>
-      <c r="P64" s="94"/>
-      <c r="Q64" s="94"/>
-      <c r="R64" s="94"/>
-      <c r="S64" s="97"/>
-    </row>
-    <row r="65" s="13" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A65" s="94">
-        <v>30350102</v>
-      </c>
-      <c r="B65" s="95">
-        <v>103501</v>
-      </c>
-      <c r="C65" s="95" t="s">
-        <v>136</v>
-      </c>
-      <c r="D65" s="94">
-        <v>303504</v>
-      </c>
-      <c r="E65" s="94" t="s">
-        <v>134</v>
-      </c>
-      <c r="F65" s="94" t="s">
-        <v>34</v>
-      </c>
-      <c r="G65" s="94"/>
-      <c r="H65" s="94"/>
-      <c r="I65" s="94"/>
-      <c r="J65" s="94"/>
-      <c r="K65" s="96"/>
-      <c r="L65" s="94"/>
-      <c r="M65" s="94" t="s">
-        <v>53</v>
-      </c>
-      <c r="N65" s="94"/>
-      <c r="O65" s="94" t="s">
-        <v>135</v>
-      </c>
-      <c r="P65" s="94"/>
-      <c r="Q65" s="94"/>
-      <c r="R65" s="94"/>
-      <c r="S65" s="97"/>
-    </row>
-    <row r="66" s="14" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A66" s="98">
-        <v>30360001</v>
-      </c>
-      <c r="B66" s="99">
-        <v>103600</v>
-      </c>
-      <c r="C66" s="99" t="s">
-        <v>138</v>
-      </c>
-      <c r="D66" s="98">
-        <v>303601</v>
-      </c>
-      <c r="E66" s="98" t="s">
-        <v>139</v>
-      </c>
-      <c r="F66" s="98" t="s">
-        <v>108</v>
-      </c>
-      <c r="G66" s="98">
-        <v>2036002</v>
-      </c>
-      <c r="H66" s="98" t="s">
-        <v>60</v>
-      </c>
-      <c r="I66" s="98" t="s">
-        <v>139</v>
-      </c>
-      <c r="J66" s="98"/>
-      <c r="K66" s="100">
-        <v>10360005</v>
-      </c>
-      <c r="L66" s="98" t="s">
-        <v>140</v>
-      </c>
-      <c r="M66" s="98"/>
-      <c r="N66" s="98"/>
-      <c r="O66" s="98"/>
-      <c r="P66" s="98"/>
-      <c r="Q66" s="98"/>
-      <c r="R66" s="98"/>
-      <c r="S66" s="101"/>
-    </row>
-    <row r="67" s="15" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A67" s="102">
-        <v>30280001</v>
-      </c>
-      <c r="B67" s="103">
-        <v>102800</v>
-      </c>
-      <c r="C67" s="103" t="s">
-        <v>141</v>
-      </c>
-      <c r="D67" s="102">
-        <v>302801</v>
-      </c>
-      <c r="E67" s="102" t="s">
-        <v>107</v>
-      </c>
-      <c r="F67" s="102" t="s">
-        <v>108</v>
-      </c>
-      <c r="G67" s="102">
-        <v>2028001</v>
-      </c>
-      <c r="H67" s="102" t="s">
-        <v>60</v>
-      </c>
-      <c r="I67" s="102" t="s">
-        <v>80</v>
-      </c>
-      <c r="J67" s="102"/>
-      <c r="K67" s="104" t="s">
-        <v>142</v>
-      </c>
-      <c r="L67" s="102" t="s">
-        <v>143</v>
-      </c>
-      <c r="M67" s="102"/>
-      <c r="N67" s="102"/>
-      <c r="O67" s="102"/>
-      <c r="P67" s="102"/>
-      <c r="Q67" s="102"/>
-      <c r="R67" s="102"/>
-      <c r="S67" s="105"/>
-    </row>
-    <row r="68" s="15" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A68" s="102">
-        <v>30280002</v>
-      </c>
-      <c r="B68" s="103">
-        <v>102800</v>
-      </c>
-      <c r="C68" s="103" t="s">
-        <v>141</v>
-      </c>
-      <c r="D68" s="102">
-        <v>302802</v>
-      </c>
-      <c r="E68" s="102" t="s">
-        <v>127</v>
-      </c>
-      <c r="F68" s="102" t="s">
-        <v>79</v>
-      </c>
-      <c r="G68" s="102">
-        <v>2028001</v>
-      </c>
-      <c r="H68" s="102" t="s">
-        <v>60</v>
-      </c>
-      <c r="I68" s="102" t="s">
-        <v>80</v>
-      </c>
-      <c r="J68" s="102"/>
-      <c r="K68" s="104" t="s">
-        <v>142</v>
-      </c>
-      <c r="L68" s="102" t="s">
-        <v>143</v>
-      </c>
-      <c r="M68" s="102"/>
-      <c r="N68" s="102"/>
-      <c r="O68" s="102"/>
-      <c r="P68" s="102"/>
-      <c r="Q68" s="102"/>
-      <c r="R68" s="102"/>
-      <c r="S68" s="105"/>
-    </row>
-    <row r="69" s="15" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A69" s="102">
-        <v>30280003</v>
-      </c>
-      <c r="B69" s="103">
-        <v>102800</v>
-      </c>
-      <c r="C69" s="103" t="s">
-        <v>141</v>
-      </c>
-      <c r="D69" s="102">
-        <v>302803</v>
-      </c>
-      <c r="E69" s="102" t="s">
-        <v>128</v>
-      </c>
-      <c r="F69" s="102" t="s">
-        <v>83</v>
-      </c>
-      <c r="G69" s="102">
-        <v>2028001</v>
-      </c>
-      <c r="H69" s="102" t="s">
-        <v>60</v>
-      </c>
-      <c r="I69" s="102" t="s">
-        <v>80</v>
-      </c>
-      <c r="J69" s="102"/>
-      <c r="K69" s="104" t="s">
-        <v>142</v>
-      </c>
-      <c r="L69" s="102" t="s">
-        <v>143</v>
-      </c>
-      <c r="M69" s="102"/>
-      <c r="N69" s="102"/>
-      <c r="O69" s="102"/>
-      <c r="P69" s="102"/>
-      <c r="Q69" s="102"/>
-      <c r="R69" s="102"/>
-      <c r="S69" s="105"/>
-    </row>
-    <row r="70" s="16" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A70" s="106">
-        <v>30200001</v>
-      </c>
-      <c r="B70" s="107">
-        <v>102000</v>
-      </c>
-      <c r="C70" s="107" t="s">
-        <v>144</v>
-      </c>
-      <c r="D70" s="106">
-        <v>302001</v>
-      </c>
-      <c r="E70" s="106" t="s">
-        <v>145</v>
-      </c>
-      <c r="F70" s="106" t="s">
-        <v>108</v>
-      </c>
-      <c r="G70" s="106">
-        <v>2020002</v>
-      </c>
-      <c r="H70" s="106" t="s">
-        <v>60</v>
-      </c>
-      <c r="I70" s="106" t="s">
-        <v>80</v>
-      </c>
-      <c r="J70" s="106"/>
-      <c r="K70" s="108"/>
-      <c r="L70" s="106"/>
-      <c r="M70" s="106"/>
-      <c r="N70" s="106"/>
-      <c r="O70" s="106"/>
-      <c r="P70" s="106"/>
-      <c r="Q70" s="106"/>
-      <c r="R70" s="106"/>
-      <c r="S70" s="109"/>
-    </row>
-    <row r="71" s="16" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A71" s="106">
-        <v>30200002</v>
-      </c>
-      <c r="B71" s="107">
-        <v>102000</v>
-      </c>
-      <c r="C71" s="107" t="s">
-        <v>144</v>
-      </c>
-      <c r="D71" s="106">
-        <v>302002</v>
-      </c>
-      <c r="E71" s="106" t="s">
-        <v>146</v>
-      </c>
-      <c r="F71" s="106" t="s">
-        <v>108</v>
-      </c>
-      <c r="G71" s="106">
-        <v>2020003</v>
-      </c>
-      <c r="H71" s="106" t="s">
-        <v>60</v>
-      </c>
-      <c r="I71" s="106" t="s">
-        <v>80</v>
-      </c>
-      <c r="J71" s="106"/>
-      <c r="K71" s="108"/>
-      <c r="L71" s="106"/>
-      <c r="M71" s="106"/>
-      <c r="N71" s="106"/>
-      <c r="O71" s="106"/>
-      <c r="P71" s="106"/>
-      <c r="Q71" s="106"/>
-      <c r="R71" s="106"/>
-      <c r="S71" s="109"/>
-    </row>
-    <row r="72" spans="1:19">
-      <c r="F72" s="3"/>
+      <c r="I85" s="87"/>
+      <c r="J85" s="87"/>
+      <c r="K85" s="89" t="s">
+        <v>184</v>
+      </c>
+      <c r="L85" s="87" t="s">
+        <v>185</v>
+      </c>
+      <c r="M85" s="87"/>
+      <c r="N85" s="87"/>
+      <c r="O85" s="87"/>
+      <c r="P85" s="87"/>
+      <c r="Q85" s="117" t="s">
+        <v>164</v>
+      </c>
+      <c r="R85" s="118" t="s">
+        <v>40</v>
+      </c>
+      <c r="S85" s="90"/>
+    </row>
+    <row r="88" ht="16.5" spans="1:19">
+      <c r="K88" s="119"/>
+    </row>
+    <row r="89" ht="16.5" spans="1:19">
+      <c r="K89" s="119"/>
+    </row>
+    <row r="90" ht="16.5" spans="1:19">
+      <c r="K90" s="119"/>
+    </row>
+    <row r="91" ht="16.5" spans="1:19">
+      <c r="K91" s="119"/>
+    </row>
+    <row r="92" ht="16.5" spans="1:19">
+      <c r="A92" s="120"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2">
@@ -5236,10 +6004,10 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>147</v>
+        <v>186</v>
       </c>
       <c r="B1" t="s">
-        <v>148</v>
+        <v>187</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -5247,7 +6015,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>149</v>
+        <v>188</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -5255,7 +6023,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>150</v>
+        <v>189</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:8">
@@ -5263,16 +6031,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>151</v>
+        <v>190</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>147</v>
+        <v>186</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>148</v>
+        <v>187</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>152</v>
+        <v>191</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:8">
@@ -5280,16 +6048,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>153</v>
+        <v>192</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>154</v>
+        <v>193</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>155</v>
+        <v>194</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:8">
@@ -5297,16 +6065,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>156</v>
+        <v>195</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>157</v>
+        <v>196</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>158</v>
+        <v>197</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:8">
@@ -5314,16 +6082,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>159</v>
+        <v>198</v>
       </c>
       <c r="F7" s="1">
         <v>2</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>160</v>
+        <v>199</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>161</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:8">
@@ -5331,16 +6099,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>162</v>
+        <v>201</v>
       </c>
       <c r="F8" s="1">
         <v>3</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>163</v>
+        <v>202</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>164</v>
+        <v>203</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:8">
@@ -5348,16 +6116,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>165</v>
+        <v>204</v>
       </c>
       <c r="F9" s="1">
         <v>4</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>166</v>
+        <v>205</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>167</v>
+        <v>206</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:8">
@@ -5365,16 +6133,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>168</v>
+        <v>207</v>
       </c>
       <c r="F10" s="1">
         <v>5</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>169</v>
+        <v>208</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>170</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:8">
@@ -5382,16 +6150,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>171</v>
+        <v>210</v>
       </c>
       <c r="F11" s="1">
         <v>6</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>172</v>
+        <v>211</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>173</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:8">
@@ -5399,16 +6167,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>174</v>
+        <v>213</v>
       </c>
       <c r="F12" s="1">
         <v>7</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>175</v>
+        <v>214</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>176</v>
+        <v>215</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:8">
@@ -5416,16 +6184,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>177</v>
+        <v>216</v>
       </c>
       <c r="F13" s="1">
         <v>8</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>178</v>
+        <v>217</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>179</v>
+        <v>218</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:8">
@@ -5433,16 +6201,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>180</v>
+        <v>219</v>
       </c>
       <c r="F14" s="1">
         <v>9</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>181</v>
+        <v>220</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>182</v>
+        <v>221</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:8">
@@ -5450,16 +6218,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>183</v>
+        <v>222</v>
       </c>
       <c r="F15" s="1">
         <v>10</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>184</v>
+        <v>223</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>185</v>
+        <v>224</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:8">
@@ -5467,16 +6235,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>186</v>
+        <v>225</v>
       </c>
       <c r="F16" s="1">
         <v>11</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>187</v>
+        <v>226</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>188</v>
+        <v>227</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:8">
@@ -5484,16 +6252,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>189</v>
+        <v>228</v>
       </c>
       <c r="F17" s="1">
         <v>12</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>190</v>
+        <v>229</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>191</v>
+        <v>230</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:8">
@@ -5501,16 +6269,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>192</v>
+        <v>231</v>
       </c>
       <c r="F18" s="1">
         <v>13</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>193</v>
+        <v>232</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>194</v>
+        <v>233</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:8">
@@ -5518,16 +6286,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>195</v>
+        <v>234</v>
       </c>
       <c r="F19" s="1">
         <v>14</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>196</v>
+        <v>235</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>197</v>
+        <v>236</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:8">
@@ -5535,16 +6303,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>198</v>
+        <v>237</v>
       </c>
       <c r="F20" s="1">
         <v>15</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>199</v>
+        <v>238</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>200</v>
+        <v>239</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:8">
@@ -5552,16 +6320,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>201</v>
+        <v>240</v>
       </c>
       <c r="F21" s="1">
         <v>16</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>202</v>
+        <v>241</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>203</v>
+        <v>242</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:8">
@@ -5569,16 +6337,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>204</v>
+        <v>243</v>
       </c>
       <c r="F22" s="1">
         <v>17</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>205</v>
+        <v>244</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>206</v>
+        <v>245</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:8">
@@ -5586,16 +6354,16 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>207</v>
+        <v>246</v>
       </c>
       <c r="F23" s="1">
         <v>18</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>208</v>
+        <v>247</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>209</v>
+        <v>248</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:8">
@@ -5603,16 +6371,16 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>210</v>
+        <v>249</v>
       </c>
       <c r="F24" s="1">
         <v>19</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>211</v>
+        <v>250</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>212</v>
+        <v>251</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -5620,7 +6388,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>213</v>
+        <v>252</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -5628,7 +6396,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>214</v>
+        <v>253</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -5636,7 +6404,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>215</v>
+        <v>254</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -5644,7 +6412,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>216</v>
+        <v>255</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -5652,7 +6420,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>217</v>
+        <v>256</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -5660,7 +6428,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>218</v>
+        <v>257</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -5668,7 +6436,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>219</v>
+        <v>258</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -5676,7 +6444,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>220</v>
+        <v>259</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -5684,7 +6452,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>221</v>
+        <v>260</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -5692,7 +6460,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>222</v>
+        <v>261</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -5700,7 +6468,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>223</v>
+        <v>262</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -5708,7 +6476,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>224</v>
+        <v>263</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -5716,7 +6484,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>225</v>
+        <v>264</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -5724,7 +6492,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>226</v>
+        <v>265</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -5732,7 +6500,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>227</v>
+        <v>266</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -5740,7 +6508,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>228</v>
+        <v>267</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -5748,7 +6516,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>229</v>
+        <v>268</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -5756,7 +6524,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>230</v>
+        <v>269</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -5764,7 +6532,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>231</v>
+        <v>270</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -5772,7 +6540,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>232</v>
+        <v>271</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -5780,7 +6548,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>233</v>
+        <v>272</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -5788,7 +6556,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>234</v>
+        <v>273</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -5796,7 +6564,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>235</v>
+        <v>274</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialAuxiliary.xlsx
+++ b/slots/resources/sample/SpecialAuxiliary.xlsx
@@ -268,7 +268,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="669" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="270">
   <si>
     <t>小游戏模式ID</t>
   </si>
@@ -744,9 +744,6 @@
     <t>哈迪斯大图标玩法 - 普通</t>
   </si>
   <si>
-    <t>随机修改两个wild</t>
-  </si>
-  <si>
     <t>免费游戏-宙斯玩法</t>
   </si>
   <si>
@@ -795,37 +792,25 @@
     <t>免费模式 VS1-哈迪斯 大图标第1轴</t>
   </si>
   <si>
-    <t>10200125|10200026</t>
-  </si>
-  <si>
-    <t>第1轴改出哈迪斯+随机修改两个wild</t>
+    <t>第1轴改出哈迪斯</t>
   </si>
   <si>
     <t>免费模式 VS1-哈迪斯 大图标第2轴</t>
   </si>
   <si>
-    <t>10200225|10200026</t>
-  </si>
-  <si>
-    <t>第2轴改出哈迪斯+随机修改两个wild</t>
+    <t>第2轴改出哈迪斯</t>
   </si>
   <si>
     <t>免费模式 VS1-哈迪斯 大图标第3轴</t>
   </si>
   <si>
-    <t>10200325|10200026</t>
-  </si>
-  <si>
-    <t>第3轴改出哈迪斯+随机修改两个wild</t>
+    <t>第3轴改出哈迪斯</t>
   </si>
   <si>
     <t>免费模式 VS1-哈迪斯 大图标第4轴</t>
   </si>
   <si>
-    <t>10200425|10200026</t>
-  </si>
-  <si>
-    <t>第4轴改出哈迪斯+随机修改两个wild</t>
+    <t>第4轴改出哈迪斯</t>
   </si>
   <si>
     <t>typeID</t>
@@ -1282,8 +1267,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1296,12 +1286,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1313,14 +1298,14 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <b/>
+      <sz val="18"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1879,7 +1864,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="121">
+  <cellXfs count="120">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2117,7 +2102,6 @@
     <xf numFmtId="176" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="52">
@@ -5465,12 +5449,8 @@
       </c>
       <c r="I75" s="107"/>
       <c r="J75" s="107"/>
-      <c r="K75" s="109">
-        <v>10200026</v>
-      </c>
-      <c r="L75" s="5" t="s">
-        <v>158</v>
-      </c>
+      <c r="K75" s="109"/>
+      <c r="L75" s="5"/>
       <c r="M75" s="107"/>
       <c r="N75" s="107"/>
       <c r="O75" s="107"/>
@@ -5497,7 +5477,7 @@
         <v>302009</v>
       </c>
       <c r="E76" s="111" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F76" s="111" t="s">
         <v>109</v>
@@ -5513,10 +5493,10 @@
       </c>
       <c r="J76" s="111"/>
       <c r="K76" s="113" t="s">
+        <v>159</v>
+      </c>
+      <c r="L76" s="111" t="s">
         <v>160</v>
-      </c>
-      <c r="L76" s="111" t="s">
-        <v>161</v>
       </c>
       <c r="M76" s="111"/>
       <c r="N76" s="111"/>
@@ -5540,7 +5520,7 @@
         <v>302010</v>
       </c>
       <c r="E77" s="111" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F77" s="111" t="s">
         <v>54</v>
@@ -5557,14 +5537,14 @@
         <v>10200120</v>
       </c>
       <c r="L77" s="116" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="M77" s="111"/>
       <c r="N77" s="111"/>
       <c r="O77" s="111"/>
       <c r="P77" s="111"/>
       <c r="Q77" s="37" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="R77" s="38" t="s">
         <v>40</v>
@@ -5585,7 +5565,7 @@
         <v>302011</v>
       </c>
       <c r="E78" s="111" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F78" s="111" t="s">
         <v>54</v>
@@ -5602,14 +5582,14 @@
         <v>10200220</v>
       </c>
       <c r="L78" s="116" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="M78" s="111"/>
       <c r="N78" s="111"/>
       <c r="O78" s="111"/>
       <c r="P78" s="111"/>
       <c r="Q78" s="37" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="R78" s="38" t="s">
         <v>40</v>
@@ -5630,7 +5610,7 @@
         <v>302012</v>
       </c>
       <c r="E79" s="111" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F79" s="111" t="s">
         <v>54</v>
@@ -5647,14 +5627,14 @@
         <v>10200320</v>
       </c>
       <c r="L79" s="116" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="M79" s="111"/>
       <c r="N79" s="111"/>
       <c r="O79" s="111"/>
       <c r="P79" s="111"/>
       <c r="Q79" s="37" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="R79" s="38" t="s">
         <v>40</v>
@@ -5675,7 +5655,7 @@
         <v>302013</v>
       </c>
       <c r="E80" s="111" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F80" s="111" t="s">
         <v>54</v>
@@ -5692,14 +5672,14 @@
         <v>10200420</v>
       </c>
       <c r="L80" s="116" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="M80" s="111"/>
       <c r="N80" s="111"/>
       <c r="O80" s="111"/>
       <c r="P80" s="111"/>
       <c r="Q80" s="37" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="R80" s="38" t="s">
         <v>40</v>
@@ -5720,7 +5700,7 @@
         <v>302014</v>
       </c>
       <c r="E81" s="87" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F81" s="87" t="s">
         <v>109</v>
@@ -5736,10 +5716,10 @@
       </c>
       <c r="J81" s="87"/>
       <c r="K81" s="89" t="s">
+        <v>171</v>
+      </c>
+      <c r="L81" s="87" t="s">
         <v>172</v>
-      </c>
-      <c r="L81" s="87" t="s">
-        <v>173</v>
       </c>
       <c r="M81" s="87"/>
       <c r="N81" s="87"/>
@@ -5763,7 +5743,7 @@
         <v>302015</v>
       </c>
       <c r="E82" s="87" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F82" s="87" t="s">
         <v>34</v>
@@ -5776,18 +5756,18 @@
       </c>
       <c r="I82" s="87"/>
       <c r="J82" s="87"/>
-      <c r="K82" s="89" t="s">
-        <v>175</v>
+      <c r="K82" s="89">
+        <v>10200125</v>
       </c>
       <c r="L82" s="87" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="M82" s="87"/>
       <c r="N82" s="87"/>
       <c r="O82" s="87"/>
       <c r="P82" s="87"/>
       <c r="Q82" s="117" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="R82" s="118" t="s">
         <v>40</v>
@@ -5808,7 +5788,7 @@
         <v>302016</v>
       </c>
       <c r="E83" s="87" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F83" s="87" t="s">
         <v>34</v>
@@ -5821,18 +5801,18 @@
       </c>
       <c r="I83" s="87"/>
       <c r="J83" s="87"/>
-      <c r="K83" s="89" t="s">
-        <v>178</v>
+      <c r="K83" s="89">
+        <v>10200225</v>
       </c>
       <c r="L83" s="87" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="M83" s="87"/>
       <c r="N83" s="87"/>
       <c r="O83" s="87"/>
       <c r="P83" s="87"/>
       <c r="Q83" s="117" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="R83" s="118" t="s">
         <v>40</v>
@@ -5853,7 +5833,7 @@
         <v>302017</v>
       </c>
       <c r="E84" s="87" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="F84" s="87" t="s">
         <v>34</v>
@@ -5866,18 +5846,18 @@
       </c>
       <c r="I84" s="87"/>
       <c r="J84" s="87"/>
-      <c r="K84" s="89" t="s">
-        <v>181</v>
+      <c r="K84" s="89">
+        <v>10200325</v>
       </c>
       <c r="L84" s="87" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="M84" s="87"/>
       <c r="N84" s="87"/>
       <c r="O84" s="87"/>
       <c r="P84" s="87"/>
       <c r="Q84" s="117" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="R84" s="118" t="s">
         <v>40</v>
@@ -5898,7 +5878,7 @@
         <v>302018</v>
       </c>
       <c r="E85" s="87" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="F85" s="87" t="s">
         <v>34</v>
@@ -5911,18 +5891,18 @@
       </c>
       <c r="I85" s="87"/>
       <c r="J85" s="87"/>
-      <c r="K85" s="89" t="s">
-        <v>184</v>
+      <c r="K85" s="89">
+        <v>10200425</v>
       </c>
       <c r="L85" s="87" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="M85" s="87"/>
       <c r="N85" s="87"/>
       <c r="O85" s="87"/>
       <c r="P85" s="87"/>
       <c r="Q85" s="117" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="R85" s="118" t="s">
         <v>40</v>
@@ -5942,7 +5922,7 @@
       <c r="K91" s="119"/>
     </row>
     <row r="92" ht="16.5" spans="1:19">
-      <c r="A92" s="120"/>
+      <c r="A92" s="119"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2">
@@ -6004,10 +5984,10 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="B1" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -6015,7 +5995,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -6023,7 +6003,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:8">
@@ -6031,16 +6011,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="F4" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:8">
@@ -6048,16 +6028,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:8">
@@ -6065,16 +6045,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:8">
@@ -6082,16 +6062,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="F7" s="1">
         <v>2</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:8">
@@ -6099,16 +6079,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="F8" s="1">
         <v>3</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:8">
@@ -6116,16 +6096,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="F9" s="1">
         <v>4</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:8">
@@ -6133,16 +6113,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="F10" s="1">
         <v>5</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:8">
@@ -6150,16 +6130,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="F11" s="1">
         <v>6</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:8">
@@ -6167,16 +6147,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="F12" s="1">
         <v>7</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:8">
@@ -6184,16 +6164,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="F13" s="1">
         <v>8</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:8">
@@ -6201,16 +6181,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="F14" s="1">
         <v>9</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:8">
@@ -6218,16 +6198,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="F15" s="1">
         <v>10</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:8">
@@ -6235,16 +6215,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="F16" s="1">
         <v>11</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:8">
@@ -6252,16 +6232,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="F17" s="1">
         <v>12</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:8">
@@ -6269,16 +6249,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="F18" s="1">
         <v>13</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:8">
@@ -6286,16 +6266,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="F19" s="1">
         <v>14</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:8">
@@ -6303,16 +6283,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="F20" s="1">
         <v>15</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:8">
@@ -6320,16 +6300,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="F21" s="1">
         <v>16</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:8">
@@ -6337,16 +6317,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="F22" s="1">
         <v>17</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:8">
@@ -6354,16 +6334,16 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F23" s="1">
         <v>18</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:8">
@@ -6371,16 +6351,16 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="F24" s="1">
         <v>19</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -6388,7 +6368,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -6396,7 +6376,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -6404,7 +6384,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -6412,7 +6392,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -6420,7 +6400,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -6428,7 +6408,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -6436,7 +6416,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -6444,7 +6424,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -6452,7 +6432,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -6460,7 +6440,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -6468,7 +6448,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -6476,7 +6456,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -6484,7 +6464,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -6492,7 +6472,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -6500,7 +6480,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -6508,7 +6488,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -6516,7 +6496,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -6524,7 +6504,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -6532,7 +6512,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -6540,7 +6520,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -6548,7 +6528,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -6556,7 +6536,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -6564,7 +6544,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialAuxiliary.xlsx
+++ b/slots/resources/sample/SpecialAuxiliary.xlsx
@@ -268,7 +268,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="276">
   <si>
     <t>小游戏模式ID</t>
   </si>
@@ -813,6 +813,27 @@
     <t>第4轴改出哈迪斯</t>
   </si>
   <si>
+    <t>恶魔之子</t>
+  </si>
+  <si>
+    <t>免费游戏-免费旋转6局&amp;12局</t>
+  </si>
+  <si>
+    <t>6_10|12_1</t>
+  </si>
+  <si>
+    <t>10380003|10380004</t>
+  </si>
+  <si>
+    <t>改出收集金币符号+概率改出金币符号</t>
+  </si>
+  <si>
+    <t>收集金币</t>
+  </si>
+  <si>
+    <t>18_10000</t>
+  </si>
+  <si>
     <t>typeID</t>
   </si>
   <si>
@@ -949,9 +970,6 @@
   </si>
   <si>
     <t>通用免费10</t>
-  </si>
-  <si>
-    <t>收集金币</t>
   </si>
   <si>
     <t>&lt;!-- 小游戏中选择中该事件后，结束小游戏并获得金币奖励--&gt;</t>
@@ -1273,6 +1291,13 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1291,8 +1316,7 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1300,12 +1324,6 @@
     <font>
       <b/>
       <sz val="18"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1864,7 +1882,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="120">
+  <cellXfs count="122">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2100,6 +2118,10 @@
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="176" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="176" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="1" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2442,7 +2464,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S92"/>
+  <dimension ref="A1:S90"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14.125" customWidth="1"/>
@@ -5909,20 +5931,96 @@
       </c>
       <c r="S85" s="90"/>
     </row>
+    <row r="86" s="14" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A86" s="99">
+        <v>30380001</v>
+      </c>
+      <c r="B86" s="100">
+        <v>103800</v>
+      </c>
+      <c r="C86" s="100" t="s">
+        <v>181</v>
+      </c>
+      <c r="D86" s="99">
+        <v>303801</v>
+      </c>
+      <c r="E86" s="99" t="s">
+        <v>182</v>
+      </c>
+      <c r="F86" s="99" t="s">
+        <v>183</v>
+      </c>
+      <c r="G86" s="99">
+        <v>2038001</v>
+      </c>
+      <c r="H86" s="99" t="s">
+        <v>61</v>
+      </c>
+      <c r="I86" s="99"/>
+      <c r="J86" s="99"/>
+      <c r="K86" s="101" t="s">
+        <v>184</v>
+      </c>
+      <c r="L86" s="99" t="s">
+        <v>185</v>
+      </c>
+      <c r="M86" s="99"/>
+      <c r="N86" s="99"/>
+      <c r="O86" s="99"/>
+      <c r="P86" s="99"/>
+      <c r="Q86" s="119"/>
+      <c r="R86" s="120"/>
+      <c r="S86" s="102"/>
+    </row>
+    <row r="87" s="14" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A87" s="99">
+        <v>30380002</v>
+      </c>
+      <c r="B87" s="100">
+        <v>103800</v>
+      </c>
+      <c r="C87" s="100" t="s">
+        <v>181</v>
+      </c>
+      <c r="D87" s="99">
+        <v>303802</v>
+      </c>
+      <c r="E87" s="99" t="s">
+        <v>186</v>
+      </c>
+      <c r="F87" s="99" t="s">
+        <v>34</v>
+      </c>
+      <c r="G87" s="99">
+        <v>2038001</v>
+      </c>
+      <c r="H87" s="99" t="s">
+        <v>61</v>
+      </c>
+      <c r="I87" s="99"/>
+      <c r="J87" s="99"/>
+      <c r="K87" s="101"/>
+      <c r="L87" s="99"/>
+      <c r="M87" s="99" t="s">
+        <v>54</v>
+      </c>
+      <c r="N87" s="99"/>
+      <c r="O87" s="99" t="s">
+        <v>187</v>
+      </c>
+      <c r="P87" s="99"/>
+      <c r="Q87" s="119"/>
+      <c r="R87" s="120"/>
+      <c r="S87" s="102"/>
+    </row>
     <row r="88" ht="16.5" spans="1:19">
-      <c r="K88" s="119"/>
+      <c r="K88" s="121"/>
     </row>
     <row r="89" ht="16.5" spans="1:19">
-      <c r="K89" s="119"/>
+      <c r="K89" s="121"/>
     </row>
     <row r="90" ht="16.5" spans="1:19">
-      <c r="K90" s="119"/>
-    </row>
-    <row r="91" ht="16.5" spans="1:19">
-      <c r="K91" s="119"/>
-    </row>
-    <row r="92" ht="16.5" spans="1:19">
-      <c r="A92" s="119"/>
+      <c r="A90" s="121"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2">
@@ -5984,10 +6082,10 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="B1" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -5995,7 +6093,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -6003,7 +6101,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:8">
@@ -6011,16 +6109,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:8">
@@ -6028,16 +6126,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:8">
@@ -6045,16 +6143,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:8">
@@ -6062,16 +6160,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="F7" s="1">
         <v>2</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:8">
@@ -6079,16 +6177,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="F8" s="1">
         <v>3</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:8">
@@ -6096,16 +6194,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="F9" s="1">
         <v>4</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:8">
@@ -6113,16 +6211,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="F10" s="1">
         <v>5</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:8">
@@ -6130,16 +6228,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="F11" s="1">
         <v>6</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:8">
@@ -6147,16 +6245,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="F12" s="1">
         <v>7</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:8">
@@ -6164,16 +6262,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="F13" s="1">
         <v>8</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:8">
@@ -6181,16 +6279,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="F14" s="1">
         <v>9</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:8">
@@ -6198,16 +6296,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="F15" s="1">
         <v>10</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:8">
@@ -6215,16 +6313,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="F16" s="1">
         <v>11</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:8">
@@ -6232,16 +6330,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="F17" s="1">
         <v>12</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:8">
@@ -6249,16 +6347,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="F18" s="1">
         <v>13</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>227</v>
+        <v>186</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:8">
@@ -6266,16 +6364,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="F19" s="1">
         <v>14</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:8">
@@ -6283,16 +6381,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="F20" s="1">
         <v>15</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:8">
@@ -6300,16 +6398,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="F21" s="1">
         <v>16</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:8">
@@ -6317,16 +6415,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="F22" s="1">
         <v>17</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:8">
@@ -6334,16 +6432,16 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="F23" s="1">
         <v>18</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:8">
@@ -6351,16 +6449,16 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="F24" s="1">
         <v>19</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -6368,7 +6466,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -6376,7 +6474,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -6384,7 +6482,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -6392,7 +6490,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -6400,7 +6498,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -6408,7 +6506,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -6416,7 +6514,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -6424,7 +6522,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -6432,7 +6530,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -6440,7 +6538,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -6448,7 +6546,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -6456,7 +6554,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -6464,7 +6562,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -6472,7 +6570,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -6480,7 +6578,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -6488,7 +6586,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -6496,7 +6594,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -6504,7 +6602,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -6512,7 +6610,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -6520,7 +6618,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -6528,7 +6626,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -6536,7 +6634,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -6544,7 +6642,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialAuxiliary.xlsx
+++ b/slots/resources/sample/SpecialAuxiliary.xlsx
@@ -268,7 +268,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="705" uniqueCount="283">
   <si>
     <t>小游戏模式ID</t>
   </si>
@@ -717,6 +717,9 @@
     <t>第1轴改出宙斯、哈迪斯大图标</t>
   </si>
   <si>
+    <t>2_500_1|3_200_1|4_100_1|5_50_1|6_30_1|7_15_1|8_10_1</t>
+  </si>
+  <si>
     <t>普通模式vs1改出宙斯或哈迪斯大图标-第2轴</t>
   </si>
   <si>
@@ -738,9 +741,6 @@
     <t>宙斯大图标玩法 - 普通</t>
   </si>
   <si>
-    <t>2_500_1|3_200_1|4_100_1|5_50_1|6_30_1|7_15_1|8_10_1</t>
-  </si>
-  <si>
     <t>哈迪斯大图标玩法 - 普通</t>
   </si>
   <si>
@@ -832,6 +832,27 @@
   </si>
   <si>
     <t>18_10000</t>
+  </si>
+  <si>
+    <t>象财神</t>
+  </si>
+  <si>
+    <t>免费游戏-免费旋转12局</t>
+  </si>
+  <si>
+    <t>10270001|10270004</t>
+  </si>
+  <si>
+    <t>概率改出百搭符号+概率改出scatter符号</t>
+  </si>
+  <si>
+    <t>免费游戏-免费旋转15局</t>
+  </si>
+  <si>
+    <t>免费游戏-免费旋转20局</t>
+  </si>
+  <si>
+    <t>20_1</t>
   </si>
   <si>
     <t>typeID</t>
@@ -1287,11 +1308,24 @@
     <font>
       <b/>
       <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
@@ -1310,20 +1344,7 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1416,6 +1437,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1429,12 +1456,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1882,7 +1903,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="122">
+  <cellXfs count="128">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1903,6 +1924,7 @@
     <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1951,33 +1973,33 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2124,7 +2146,18 @@
     <xf numFmtId="176" fontId="1" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="1" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="52">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2476,7 +2509,7 @@
     <col min="8" max="8" width="16.25" customWidth="1"/>
     <col min="9" max="9" width="29.375" customWidth="1"/>
     <col min="10" max="10" width="42.5" customWidth="1"/>
-    <col min="11" max="11" width="41.25" style="18" customWidth="1"/>
+    <col min="11" max="11" width="41.25" style="19" customWidth="1"/>
     <col min="12" max="12" width="45.2916666666667" style="3" customWidth="1"/>
     <col min="13" max="13" width="34.4083333333333" style="3" customWidth="1"/>
     <col min="14" max="14" width="7.93333333333333" style="3" customWidth="1"/>
@@ -2484,7 +2517,7 @@
     <col min="16" max="16" width="8.96666666666667" customWidth="1"/>
     <col min="17" max="17" width="93.375" customWidth="1"/>
     <col min="18" max="18" width="10.625" customWidth="1"/>
-    <col min="19" max="19" width="23.75" style="19" customWidth="1"/>
+    <col min="19" max="19" width="23.75" style="20" customWidth="1"/>
     <col min="20" max="20" width="60.875" customWidth="1"/>
     <col min="21" max="22" width="11.5"/>
   </cols>
@@ -2493,671 +2526,671 @@
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20" t="s">
+      <c r="C1" s="21"/>
+      <c r="D1" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20" t="s">
+      <c r="E1" s="21"/>
+      <c r="F1" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="20" t="s">
+      <c r="G1" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20" t="s">
+      <c r="H1" s="21"/>
+      <c r="I1" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="21" t="s">
+      <c r="J1" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="22" t="s">
+      <c r="K1" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20" t="s">
+      <c r="L1" s="21"/>
+      <c r="M1" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="20"/>
-      <c r="O1" s="23" t="s">
+      <c r="N1" s="21"/>
+      <c r="O1" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="23" t="s">
+      <c r="P1" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="Q1" s="23" t="s">
+      <c r="Q1" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="R1" s="24" t="s">
+      <c r="R1" s="25" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="2" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20" t="s">
+      <c r="C2" s="21"/>
+      <c r="D2" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="20"/>
-      <c r="F2" s="23" t="s">
+      <c r="E2" s="21"/>
+      <c r="F2" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="G2" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="26" t="s">
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="27" t="s">
+      <c r="K2" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="L2" s="23"/>
-      <c r="M2" s="26" t="s">
+      <c r="L2" s="24"/>
+      <c r="M2" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="N2" s="20"/>
-      <c r="O2" s="23" t="s">
+      <c r="N2" s="21"/>
+      <c r="O2" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="P2" s="23" t="s">
+      <c r="P2" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="Q2" s="26" t="s">
+      <c r="Q2" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="R2" s="24" t="s">
+      <c r="R2" s="25" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="3" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28" t="s">
+      <c r="C3" s="29"/>
+      <c r="D3" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28" t="s">
+      <c r="E3" s="29"/>
+      <c r="F3" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="29" t="s">
+      <c r="G3" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
-      <c r="J3" s="30" t="s">
+      <c r="H3" s="29"/>
+      <c r="I3" s="29"/>
+      <c r="J3" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="31" t="s">
+      <c r="K3" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="L3" s="28"/>
-      <c r="M3" s="28" t="s">
+      <c r="L3" s="29"/>
+      <c r="M3" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="N3" s="28"/>
-      <c r="O3" s="23" t="s">
+      <c r="N3" s="29"/>
+      <c r="O3" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="P3" s="23" t="s">
+      <c r="P3" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="Q3" s="23" t="s">
+      <c r="Q3" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="R3" s="32" t="s">
+      <c r="R3" s="33" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="4" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="20"/>
-      <c r="I4" s="20"/>
-      <c r="J4" s="33"/>
-      <c r="K4" s="22"/>
-      <c r="L4" s="20"/>
-      <c r="M4" s="20"/>
-      <c r="N4" s="20"/>
-      <c r="O4" s="20"/>
-      <c r="P4" s="20"/>
-      <c r="Q4" s="20"/>
-      <c r="R4" s="20"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="34"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="21"/>
+      <c r="M4" s="21"/>
+      <c r="N4" s="21"/>
+      <c r="O4" s="21"/>
+      <c r="P4" s="21"/>
+      <c r="Q4" s="21"/>
+      <c r="R4" s="21"/>
     </row>
     <row r="5" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A5" s="34">
+      <c r="A5" s="35">
         <v>30010001</v>
       </c>
-      <c r="B5" s="35">
+      <c r="B5" s="36">
         <v>100100</v>
       </c>
-      <c r="C5" s="35" t="s">
+      <c r="C5" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="34">
+      <c r="D5" s="35">
         <v>31001</v>
       </c>
-      <c r="E5" s="34" t="s">
+      <c r="E5" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="34" t="s">
+      <c r="F5" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="G5" s="34"/>
-      <c r="H5" s="34"/>
-      <c r="I5" s="34" t="s">
+      <c r="G5" s="35"/>
+      <c r="H5" s="35"/>
+      <c r="I5" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="J5" s="34"/>
-      <c r="K5" s="36"/>
-      <c r="L5" s="20" t="s">
+      <c r="J5" s="35"/>
+      <c r="K5" s="37"/>
+      <c r="L5" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="M5" s="34" t="s">
+      <c r="M5" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="N5" s="34" t="s">
+      <c r="N5" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="O5" s="34"/>
-      <c r="P5" s="34"/>
-      <c r="Q5" s="37" t="s">
+      <c r="O5" s="35"/>
+      <c r="P5" s="35"/>
+      <c r="Q5" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="R5" s="38" t="s">
+      <c r="R5" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="S5" s="39" t="s">
+      <c r="S5" s="40" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="6" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A6" s="34">
+      <c r="A6" s="35">
         <v>30010002</v>
       </c>
-      <c r="B6" s="35">
+      <c r="B6" s="36">
         <v>100100</v>
       </c>
-      <c r="C6" s="35" t="s">
+      <c r="C6" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="34">
+      <c r="D6" s="35">
         <v>31002</v>
       </c>
-      <c r="E6" s="34" t="s">
+      <c r="E6" s="35" t="s">
         <v>42</v>
       </c>
-      <c r="F6" s="34" t="s">
+      <c r="F6" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="G6" s="34"/>
-      <c r="H6" s="34"/>
-      <c r="I6" s="34" t="s">
+      <c r="G6" s="35"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="J6" s="34"/>
-      <c r="K6" s="36"/>
-      <c r="L6" s="20" t="s">
+      <c r="J6" s="35"/>
+      <c r="K6" s="37"/>
+      <c r="L6" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="M6" s="34" t="s">
+      <c r="M6" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="N6" s="34" t="s">
+      <c r="N6" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="O6" s="34"/>
-      <c r="P6" s="34"/>
-      <c r="Q6" s="37" t="s">
+      <c r="O6" s="35"/>
+      <c r="P6" s="35"/>
+      <c r="Q6" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="R6" s="38" t="s">
+      <c r="R6" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="S6" s="39"/>
+      <c r="S6" s="40"/>
     </row>
     <row r="7" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A7" s="34">
+      <c r="A7" s="35">
         <v>30010003</v>
       </c>
-      <c r="B7" s="35">
+      <c r="B7" s="36">
         <v>100100</v>
       </c>
-      <c r="C7" s="35" t="s">
+      <c r="C7" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="34">
+      <c r="D7" s="35">
         <v>31003</v>
       </c>
-      <c r="E7" s="34" t="s">
+      <c r="E7" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="F7" s="34" t="s">
+      <c r="F7" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="G7" s="34"/>
-      <c r="H7" s="34"/>
-      <c r="I7" s="34" t="s">
+      <c r="G7" s="35"/>
+      <c r="H7" s="35"/>
+      <c r="I7" s="35" t="s">
         <v>47</v>
       </c>
-      <c r="J7" s="34"/>
-      <c r="K7" s="36"/>
-      <c r="L7" s="20" t="s">
+      <c r="J7" s="35"/>
+      <c r="K7" s="37"/>
+      <c r="L7" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="M7" s="34" t="s">
+      <c r="M7" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="N7" s="34" t="s">
+      <c r="N7" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="O7" s="34"/>
-      <c r="P7" s="34"/>
-      <c r="Q7" s="37" t="s">
+      <c r="O7" s="35"/>
+      <c r="P7" s="35"/>
+      <c r="Q7" s="38" t="s">
         <v>48</v>
       </c>
-      <c r="R7" s="38" t="s">
+      <c r="R7" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="S7" s="39"/>
+      <c r="S7" s="40"/>
     </row>
     <row r="8" s="3" customFormat="1" ht="15" customHeight="1" spans="1:19">
-      <c r="A8" s="34">
+      <c r="A8" s="35">
         <v>30010004</v>
       </c>
-      <c r="B8" s="35">
+      <c r="B8" s="36">
         <v>100100</v>
       </c>
-      <c r="C8" s="35" t="s">
+      <c r="C8" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="34">
+      <c r="D8" s="35">
         <v>31004</v>
       </c>
-      <c r="E8" s="34" t="s">
+      <c r="E8" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="F8" s="34" t="s">
+      <c r="F8" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="G8" s="34"/>
-      <c r="H8" s="34"/>
-      <c r="I8" s="34" t="s">
+      <c r="G8" s="35"/>
+      <c r="H8" s="35"/>
+      <c r="I8" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="J8" s="34"/>
-      <c r="K8" s="36"/>
-      <c r="L8" s="20" t="s">
+      <c r="J8" s="35"/>
+      <c r="K8" s="37"/>
+      <c r="L8" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="M8" s="34" t="s">
+      <c r="M8" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="N8" s="34" t="s">
+      <c r="N8" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="O8" s="34"/>
-      <c r="P8" s="34"/>
-      <c r="Q8" s="37" t="s">
+      <c r="O8" s="35"/>
+      <c r="P8" s="35"/>
+      <c r="Q8" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="R8" s="38" t="s">
+      <c r="R8" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="S8" s="39"/>
+      <c r="S8" s="40"/>
     </row>
     <row r="9" s="3" customFormat="1" ht="15" customHeight="1" spans="1:19">
-      <c r="A9" s="20">
+      <c r="A9" s="21">
         <v>30010005</v>
       </c>
-      <c r="B9" s="32">
+      <c r="B9" s="33">
         <v>100100</v>
       </c>
-      <c r="C9" s="35" t="s">
+      <c r="C9" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="20">
+      <c r="D9" s="21">
         <v>31101</v>
       </c>
-      <c r="E9" s="20" t="s">
+      <c r="E9" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="F9" s="20" t="s">
+      <c r="F9" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="G9" s="20"/>
-      <c r="H9" s="20"/>
-      <c r="I9" s="20" t="s">
+      <c r="G9" s="21"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="J9" s="20"/>
-      <c r="K9" s="22"/>
-      <c r="L9" s="20" t="s">
+      <c r="J9" s="21"/>
+      <c r="K9" s="23"/>
+      <c r="L9" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="M9" s="20" t="s">
+      <c r="M9" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="N9" s="20"/>
-      <c r="O9" s="20" t="s">
+      <c r="N9" s="21"/>
+      <c r="O9" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="P9" s="20"/>
-      <c r="Q9" s="23"/>
-      <c r="R9" s="23"/>
-      <c r="S9" s="39"/>
+      <c r="P9" s="21"/>
+      <c r="Q9" s="24"/>
+      <c r="R9" s="24"/>
+      <c r="S9" s="40"/>
     </row>
     <row r="10" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A10" s="40">
+      <c r="A10" s="41">
         <v>30010006</v>
       </c>
-      <c r="B10" s="41">
+      <c r="B10" s="42">
         <v>100100</v>
       </c>
-      <c r="C10" s="35" t="s">
+      <c r="C10" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="D10" s="40">
+      <c r="D10" s="41">
         <v>31102</v>
       </c>
-      <c r="E10" s="40" t="s">
+      <c r="E10" s="41" t="s">
         <v>56</v>
       </c>
-      <c r="F10" s="40" t="s">
+      <c r="F10" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="G10" s="40"/>
-      <c r="H10" s="40"/>
-      <c r="I10" s="40" t="s">
+      <c r="G10" s="41"/>
+      <c r="H10" s="41"/>
+      <c r="I10" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="J10" s="40"/>
-      <c r="K10" s="42"/>
-      <c r="L10" s="40" t="s">
+      <c r="J10" s="41"/>
+      <c r="K10" s="43"/>
+      <c r="L10" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="M10" s="40" t="s">
+      <c r="M10" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="N10" s="40" t="s">
+      <c r="N10" s="41" t="s">
         <v>38</v>
       </c>
-      <c r="O10" s="40" t="s">
+      <c r="O10" s="41" t="s">
         <v>55</v>
       </c>
-      <c r="P10" s="40"/>
-      <c r="Q10" s="40"/>
-      <c r="R10" s="20"/>
-      <c r="S10" s="39"/>
+      <c r="P10" s="41"/>
+      <c r="Q10" s="41"/>
+      <c r="R10" s="21"/>
+      <c r="S10" s="40"/>
     </row>
     <row r="11" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A11" s="43">
+      <c r="A11" s="44">
         <v>30010007</v>
       </c>
-      <c r="B11" s="44">
+      <c r="B11" s="45">
         <v>100100</v>
       </c>
-      <c r="C11" s="35" t="s">
+      <c r="C11" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="45">
+      <c r="D11" s="46">
         <v>31201</v>
       </c>
-      <c r="E11" s="45" t="s">
+      <c r="E11" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="F11" s="43" t="s">
+      <c r="F11" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="43">
+      <c r="G11" s="44">
         <v>2001001</v>
       </c>
-      <c r="H11" s="43" t="s">
+      <c r="H11" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="I11" s="43" t="s">
+      <c r="I11" s="44" t="s">
         <v>62</v>
       </c>
-      <c r="J11" s="43"/>
-      <c r="K11" s="46">
+      <c r="J11" s="44"/>
+      <c r="K11" s="47">
         <v>10010091</v>
       </c>
-      <c r="L11" s="43"/>
-      <c r="M11" s="43"/>
-      <c r="N11" s="43"/>
-      <c r="O11" s="43"/>
-      <c r="P11" s="43"/>
-      <c r="Q11" s="43"/>
-      <c r="R11" s="20"/>
-      <c r="S11" s="39"/>
+      <c r="L11" s="44"/>
+      <c r="M11" s="44"/>
+      <c r="N11" s="44"/>
+      <c r="O11" s="44"/>
+      <c r="P11" s="44"/>
+      <c r="Q11" s="44"/>
+      <c r="R11" s="21"/>
+      <c r="S11" s="40"/>
     </row>
     <row r="12" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A12" s="47">
+      <c r="A12" s="48">
         <v>30010008</v>
       </c>
-      <c r="B12" s="48">
+      <c r="B12" s="49">
         <v>100100</v>
       </c>
-      <c r="C12" s="35" t="s">
+      <c r="C12" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="45">
+      <c r="D12" s="46">
         <v>31202</v>
       </c>
-      <c r="E12" s="45" t="s">
+      <c r="E12" s="46" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="47" t="s">
+      <c r="F12" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="G12" s="47">
+      <c r="G12" s="48">
         <v>2001001</v>
       </c>
-      <c r="H12" s="47" t="s">
+      <c r="H12" s="48" t="s">
         <v>61</v>
       </c>
-      <c r="I12" s="47" t="s">
+      <c r="I12" s="48" t="s">
         <v>64</v>
       </c>
-      <c r="J12" s="47"/>
-      <c r="K12" s="49" t="s">
+      <c r="J12" s="48"/>
+      <c r="K12" s="50" t="s">
         <v>65</v>
       </c>
-      <c r="L12" s="47"/>
-      <c r="M12" s="47"/>
-      <c r="N12" s="47"/>
-      <c r="O12" s="47"/>
-      <c r="P12" s="47"/>
-      <c r="Q12" s="47"/>
-      <c r="R12" s="20"/>
-      <c r="S12" s="39"/>
+      <c r="L12" s="48"/>
+      <c r="M12" s="48"/>
+      <c r="N12" s="48"/>
+      <c r="O12" s="48"/>
+      <c r="P12" s="48"/>
+      <c r="Q12" s="48"/>
+      <c r="R12" s="21"/>
+      <c r="S12" s="40"/>
     </row>
     <row r="13" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A13" s="50">
+      <c r="A13" s="51">
         <v>30010009</v>
       </c>
-      <c r="B13" s="51">
+      <c r="B13" s="52">
         <v>100100</v>
       </c>
-      <c r="C13" s="35" t="s">
+      <c r="C13" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="D13" s="45">
+      <c r="D13" s="46">
         <v>31203</v>
       </c>
-      <c r="E13" s="45" t="s">
+      <c r="E13" s="46" t="s">
         <v>66</v>
       </c>
-      <c r="F13" s="50" t="s">
+      <c r="F13" s="51" t="s">
         <v>54</v>
       </c>
-      <c r="G13" s="50">
+      <c r="G13" s="51">
         <v>2001001</v>
       </c>
-      <c r="H13" s="50" t="s">
+      <c r="H13" s="51" t="s">
         <v>61</v>
       </c>
-      <c r="I13" s="50" t="s">
+      <c r="I13" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="J13" s="50"/>
-      <c r="K13" s="52" t="s">
+      <c r="J13" s="51"/>
+      <c r="K13" s="53" t="s">
         <v>68</v>
       </c>
-      <c r="L13" s="50"/>
-      <c r="M13" s="50"/>
-      <c r="N13" s="50"/>
-      <c r="O13" s="50"/>
-      <c r="P13" s="50"/>
-      <c r="Q13" s="50"/>
-      <c r="R13" s="20"/>
-      <c r="S13" s="39"/>
+      <c r="L13" s="51"/>
+      <c r="M13" s="51"/>
+      <c r="N13" s="51"/>
+      <c r="O13" s="51"/>
+      <c r="P13" s="51"/>
+      <c r="Q13" s="51"/>
+      <c r="R13" s="21"/>
+      <c r="S13" s="40"/>
     </row>
     <row r="14" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A14" s="45">
+      <c r="A14" s="46">
         <v>30010010</v>
       </c>
-      <c r="B14" s="53">
+      <c r="B14" s="54">
         <v>100100</v>
       </c>
-      <c r="C14" s="35" t="s">
+      <c r="C14" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="D14" s="54">
+      <c r="D14" s="55">
         <v>31301</v>
       </c>
-      <c r="E14" s="54" t="s">
+      <c r="E14" s="55" t="s">
         <v>69</v>
       </c>
-      <c r="F14" s="45" t="s">
+      <c r="F14" s="46" t="s">
         <v>34</v>
       </c>
-      <c r="G14" s="45"/>
-      <c r="H14" s="45"/>
-      <c r="I14" s="45" t="s">
+      <c r="G14" s="46"/>
+      <c r="H14" s="46"/>
+      <c r="I14" s="46" t="s">
         <v>70</v>
       </c>
-      <c r="J14" s="45"/>
-      <c r="K14" s="55"/>
-      <c r="L14" s="45" t="s">
+      <c r="J14" s="46"/>
+      <c r="K14" s="56"/>
+      <c r="L14" s="46" t="s">
         <v>44</v>
       </c>
-      <c r="M14" s="45" t="s">
+      <c r="M14" s="46" t="s">
         <v>71</v>
       </c>
-      <c r="N14" s="45"/>
-      <c r="O14" s="45"/>
-      <c r="P14" s="45"/>
-      <c r="Q14" s="56" t="s">
+      <c r="N14" s="46"/>
+      <c r="O14" s="46"/>
+      <c r="P14" s="46"/>
+      <c r="Q14" s="57" t="s">
         <v>72</v>
       </c>
-      <c r="R14" s="57" t="s">
+      <c r="R14" s="58" t="s">
         <v>73</v>
       </c>
-      <c r="S14" s="23" t="s">
+      <c r="S14" s="24" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="15" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A15" s="50">
+      <c r="A15" s="51">
         <v>30010011</v>
       </c>
-      <c r="B15" s="51">
+      <c r="B15" s="52">
         <v>100100</v>
       </c>
-      <c r="C15" s="35" t="s">
+      <c r="C15" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="D15" s="54">
+      <c r="D15" s="55">
         <v>31302</v>
       </c>
-      <c r="E15" s="54" t="s">
+      <c r="E15" s="55" t="s">
         <v>75</v>
       </c>
-      <c r="F15" s="50" t="s">
+      <c r="F15" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="G15" s="50"/>
-      <c r="H15" s="50"/>
-      <c r="I15" s="50" t="s">
+      <c r="G15" s="51"/>
+      <c r="H15" s="51"/>
+      <c r="I15" s="51" t="s">
         <v>76</v>
       </c>
-      <c r="J15" s="50"/>
-      <c r="K15" s="52"/>
-      <c r="L15" s="50" t="s">
+      <c r="J15" s="51"/>
+      <c r="K15" s="53"/>
+      <c r="L15" s="51" t="s">
         <v>44</v>
       </c>
-      <c r="M15" s="50" t="s">
+      <c r="M15" s="51" t="s">
         <v>58</v>
       </c>
-      <c r="N15" s="50"/>
-      <c r="O15" s="50"/>
-      <c r="P15" s="50"/>
-      <c r="Q15" s="50"/>
-      <c r="R15" s="20"/>
-      <c r="S15" s="39"/>
+      <c r="N15" s="51"/>
+      <c r="O15" s="51"/>
+      <c r="P15" s="51"/>
+      <c r="Q15" s="51"/>
+      <c r="R15" s="21"/>
+      <c r="S15" s="40"/>
     </row>
     <row r="16" s="3" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A16" s="50">
+      <c r="A16" s="51">
         <v>30010012</v>
       </c>
-      <c r="B16" s="51">
+      <c r="B16" s="52">
         <v>100100</v>
       </c>
-      <c r="C16" s="35" t="s">
+      <c r="C16" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="D16" s="54">
+      <c r="D16" s="55">
         <v>31303</v>
       </c>
-      <c r="E16" s="54" t="s">
+      <c r="E16" s="55" t="s">
         <v>77</v>
       </c>
-      <c r="F16" s="50" t="s">
+      <c r="F16" s="51" t="s">
         <v>54</v>
       </c>
-      <c r="G16" s="50">
+      <c r="G16" s="51">
         <v>2001001</v>
       </c>
-      <c r="H16" s="50" t="s">
+      <c r="H16" s="51" t="s">
         <v>61</v>
       </c>
-      <c r="I16" s="50" t="s">
+      <c r="I16" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="J16" s="50"/>
-      <c r="K16" s="52" t="s">
+      <c r="J16" s="51"/>
+      <c r="K16" s="53" t="s">
         <v>68</v>
       </c>
-      <c r="L16" s="50"/>
-      <c r="M16" s="50"/>
-      <c r="N16" s="50"/>
-      <c r="O16" s="50"/>
-      <c r="P16" s="50"/>
-      <c r="Q16" s="50"/>
-      <c r="R16" s="20"/>
-      <c r="S16" s="39"/>
+      <c r="L16" s="51"/>
+      <c r="M16" s="51"/>
+      <c r="N16" s="51"/>
+      <c r="O16" s="51"/>
+      <c r="P16" s="51"/>
+      <c r="Q16" s="51"/>
+      <c r="R16" s="21"/>
+      <c r="S16" s="40"/>
     </row>
     <row r="17" s="3" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A17" s="20">
+      <c r="A17" s="21">
         <v>30070001</v>
       </c>
       <c r="B17" s="3">
@@ -3166,30 +3199,30 @@
       <c r="C17" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D17" s="43">
+      <c r="D17" s="44">
         <v>34001</v>
       </c>
-      <c r="E17" s="43" t="s">
+      <c r="E17" s="44" t="s">
         <v>79</v>
       </c>
-      <c r="F17" s="43" t="s">
+      <c r="F17" s="44" t="s">
         <v>80</v>
       </c>
-      <c r="G17" s="32">
+      <c r="G17" s="33">
         <v>2007001</v>
       </c>
-      <c r="H17" s="20" t="s">
+      <c r="H17" s="21" t="s">
         <v>61</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="K17" s="58" t="s">
+      <c r="K17" s="59" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="18" s="3" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A18" s="20">
+      <c r="A18" s="21">
         <v>30070002</v>
       </c>
       <c r="B18" s="3">
@@ -3198,30 +3231,30 @@
       <c r="C18" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D18" s="43">
+      <c r="D18" s="44">
         <v>34002</v>
       </c>
-      <c r="E18" s="43" t="s">
+      <c r="E18" s="44" t="s">
         <v>83</v>
       </c>
-      <c r="F18" s="43" t="s">
+      <c r="F18" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="G18" s="32">
+      <c r="G18" s="33">
         <v>2007001</v>
       </c>
-      <c r="H18" s="20" t="s">
+      <c r="H18" s="21" t="s">
         <v>61</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="K18" s="58" t="s">
+      <c r="K18" s="59" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="19" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A19" s="45">
+      <c r="A19" s="46">
         <v>30120001</v>
       </c>
       <c r="B19" s="4">
@@ -3230,33 +3263,33 @@
       <c r="C19" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="D19" s="45">
+      <c r="D19" s="46">
         <v>32001</v>
       </c>
-      <c r="E19" s="45" t="s">
+      <c r="E19" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="F19" s="45" t="s">
+      <c r="F19" s="46" t="s">
         <v>54</v>
       </c>
-      <c r="G19" s="53">
+      <c r="G19" s="54">
         <v>2012001</v>
       </c>
-      <c r="H19" s="45" t="s">
+      <c r="H19" s="46" t="s">
         <v>61</v>
       </c>
-      <c r="I19" s="45" t="s">
+      <c r="I19" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="J19" s="45" t="s">
+      <c r="J19" s="46" t="s">
         <v>87</v>
       </c>
-      <c r="K19" s="59">
+      <c r="K19" s="60">
         <v>10120041</v>
       </c>
     </row>
     <row r="20" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A20" s="45">
+      <c r="A20" s="46">
         <v>30120002</v>
       </c>
       <c r="B20" s="4">
@@ -3265,33 +3298,33 @@
       <c r="C20" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="D20" s="45">
+      <c r="D20" s="46">
         <v>32002</v>
       </c>
-      <c r="E20" s="45" t="s">
+      <c r="E20" s="46" t="s">
         <v>88</v>
       </c>
-      <c r="F20" s="45" t="s">
+      <c r="F20" s="46" t="s">
         <v>54</v>
       </c>
-      <c r="G20" s="53">
+      <c r="G20" s="54">
         <v>2012001</v>
       </c>
-      <c r="H20" s="45" t="s">
+      <c r="H20" s="46" t="s">
         <v>61</v>
       </c>
-      <c r="I20" s="45" t="s">
+      <c r="I20" s="46" t="s">
         <v>88</v>
       </c>
-      <c r="J20" s="45" t="s">
+      <c r="J20" s="46" t="s">
         <v>87</v>
       </c>
-      <c r="K20" s="59">
+      <c r="K20" s="60">
         <v>10120042</v>
       </c>
     </row>
     <row r="21" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A21" s="45">
+      <c r="A21" s="46">
         <v>30120003</v>
       </c>
       <c r="B21" s="4">
@@ -3300,33 +3333,33 @@
       <c r="C21" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="D21" s="45">
+      <c r="D21" s="46">
         <v>32003</v>
       </c>
-      <c r="E21" s="45" t="s">
+      <c r="E21" s="46" t="s">
         <v>89</v>
       </c>
-      <c r="F21" s="45" t="s">
+      <c r="F21" s="46" t="s">
         <v>54</v>
       </c>
-      <c r="G21" s="53">
+      <c r="G21" s="54">
         <v>2012001</v>
       </c>
-      <c r="H21" s="45" t="s">
+      <c r="H21" s="46" t="s">
         <v>61</v>
       </c>
-      <c r="I21" s="45" t="s">
+      <c r="I21" s="46" t="s">
         <v>89</v>
       </c>
-      <c r="J21" s="45" t="s">
+      <c r="J21" s="46" t="s">
         <v>87</v>
       </c>
-      <c r="K21" s="59">
+      <c r="K21" s="60">
         <v>10120043</v>
       </c>
     </row>
     <row r="22" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A22" s="45">
+      <c r="A22" s="46">
         <v>30120004</v>
       </c>
       <c r="B22" s="4">
@@ -3335,33 +3368,33 @@
       <c r="C22" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="D22" s="45">
+      <c r="D22" s="46">
         <v>32004</v>
       </c>
-      <c r="E22" s="45" t="s">
+      <c r="E22" s="46" t="s">
         <v>90</v>
       </c>
-      <c r="F22" s="45" t="s">
+      <c r="F22" s="46" t="s">
         <v>54</v>
       </c>
-      <c r="G22" s="53">
+      <c r="G22" s="54">
         <v>2012001</v>
       </c>
-      <c r="H22" s="45" t="s">
+      <c r="H22" s="46" t="s">
         <v>61</v>
       </c>
-      <c r="I22" s="45" t="s">
+      <c r="I22" s="46" t="s">
         <v>90</v>
       </c>
-      <c r="J22" s="45" t="s">
+      <c r="J22" s="46" t="s">
         <v>87</v>
       </c>
-      <c r="K22" s="59">
+      <c r="K22" s="60">
         <v>10120044</v>
       </c>
     </row>
     <row r="23" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A23" s="45">
+      <c r="A23" s="46">
         <v>30120005</v>
       </c>
       <c r="B23" s="4">
@@ -3370,33 +3403,33 @@
       <c r="C23" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="D23" s="45">
+      <c r="D23" s="46">
         <v>32005</v>
       </c>
-      <c r="E23" s="45" t="s">
+      <c r="E23" s="46" t="s">
         <v>90</v>
       </c>
-      <c r="F23" s="45" t="s">
+      <c r="F23" s="46" t="s">
         <v>54</v>
       </c>
-      <c r="G23" s="53">
+      <c r="G23" s="54">
         <v>2012001</v>
       </c>
-      <c r="H23" s="45" t="s">
+      <c r="H23" s="46" t="s">
         <v>61</v>
       </c>
-      <c r="I23" s="45" t="s">
+      <c r="I23" s="46" t="s">
         <v>90</v>
       </c>
-      <c r="J23" s="45" t="s">
+      <c r="J23" s="46" t="s">
         <v>87</v>
       </c>
-      <c r="K23" s="59">
+      <c r="K23" s="60">
         <v>10120045</v>
       </c>
     </row>
     <row r="24" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A24" s="45">
+      <c r="A24" s="46">
         <v>30120006</v>
       </c>
       <c r="B24" s="4">
@@ -3405,33 +3438,33 @@
       <c r="C24" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="D24" s="45">
+      <c r="D24" s="46">
         <v>32006</v>
       </c>
-      <c r="E24" s="45" t="s">
+      <c r="E24" s="46" t="s">
         <v>90</v>
       </c>
-      <c r="F24" s="45" t="s">
+      <c r="F24" s="46" t="s">
         <v>54</v>
       </c>
-      <c r="G24" s="53">
+      <c r="G24" s="54">
         <v>2012001</v>
       </c>
-      <c r="H24" s="45" t="s">
+      <c r="H24" s="46" t="s">
         <v>61</v>
       </c>
-      <c r="I24" s="45" t="s">
+      <c r="I24" s="46" t="s">
         <v>90</v>
       </c>
-      <c r="J24" s="45" t="s">
+      <c r="J24" s="46" t="s">
         <v>87</v>
       </c>
-      <c r="K24" s="59">
+      <c r="K24" s="60">
         <v>10120046</v>
       </c>
     </row>
     <row r="25" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A25" s="60">
+      <c r="A25" s="61">
         <v>30120011</v>
       </c>
       <c r="B25" s="5">
@@ -3440,33 +3473,33 @@
       <c r="C25" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="D25" s="45">
+      <c r="D25" s="46">
         <v>32101</v>
       </c>
-      <c r="E25" s="60" t="s">
+      <c r="E25" s="61" t="s">
         <v>86</v>
       </c>
-      <c r="F25" s="60" t="s">
+      <c r="F25" s="61" t="s">
         <v>54</v>
       </c>
-      <c r="G25" s="61">
+      <c r="G25" s="62">
         <v>2012001</v>
       </c>
-      <c r="H25" s="60" t="s">
+      <c r="H25" s="61" t="s">
         <v>61</v>
       </c>
-      <c r="I25" s="60" t="s">
+      <c r="I25" s="61" t="s">
         <v>86</v>
       </c>
-      <c r="J25" s="60" t="s">
+      <c r="J25" s="61" t="s">
         <v>92</v>
       </c>
-      <c r="K25" s="62">
+      <c r="K25" s="63">
         <v>10120041</v>
       </c>
     </row>
     <row r="26" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A26" s="60">
+      <c r="A26" s="61">
         <v>30120012</v>
       </c>
       <c r="B26" s="5">
@@ -3475,33 +3508,33 @@
       <c r="C26" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="D26" s="45">
+      <c r="D26" s="46">
         <v>32102</v>
       </c>
-      <c r="E26" s="60" t="s">
+      <c r="E26" s="61" t="s">
         <v>88</v>
       </c>
-      <c r="F26" s="60" t="s">
+      <c r="F26" s="61" t="s">
         <v>54</v>
       </c>
-      <c r="G26" s="61">
+      <c r="G26" s="62">
         <v>2012001</v>
       </c>
-      <c r="H26" s="60" t="s">
+      <c r="H26" s="61" t="s">
         <v>61</v>
       </c>
-      <c r="I26" s="60" t="s">
+      <c r="I26" s="61" t="s">
         <v>88</v>
       </c>
-      <c r="J26" s="60" t="s">
+      <c r="J26" s="61" t="s">
         <v>92</v>
       </c>
-      <c r="K26" s="62">
+      <c r="K26" s="63">
         <v>10120042</v>
       </c>
     </row>
     <row r="27" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A27" s="60">
+      <c r="A27" s="61">
         <v>30120013</v>
       </c>
       <c r="B27" s="5">
@@ -3510,33 +3543,33 @@
       <c r="C27" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="D27" s="45">
+      <c r="D27" s="46">
         <v>32103</v>
       </c>
-      <c r="E27" s="60" t="s">
+      <c r="E27" s="61" t="s">
         <v>89</v>
       </c>
-      <c r="F27" s="60" t="s">
+      <c r="F27" s="61" t="s">
         <v>54</v>
       </c>
-      <c r="G27" s="61">
+      <c r="G27" s="62">
         <v>2012001</v>
       </c>
-      <c r="H27" s="60" t="s">
+      <c r="H27" s="61" t="s">
         <v>61</v>
       </c>
-      <c r="I27" s="60" t="s">
+      <c r="I27" s="61" t="s">
         <v>89</v>
       </c>
-      <c r="J27" s="60" t="s">
+      <c r="J27" s="61" t="s">
         <v>92</v>
       </c>
-      <c r="K27" s="62">
+      <c r="K27" s="63">
         <v>10120043</v>
       </c>
     </row>
     <row r="28" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A28" s="60">
+      <c r="A28" s="61">
         <v>30120014</v>
       </c>
       <c r="B28" s="5">
@@ -3545,33 +3578,33 @@
       <c r="C28" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="D28" s="45">
+      <c r="D28" s="46">
         <v>32104</v>
       </c>
-      <c r="E28" s="60" t="s">
+      <c r="E28" s="61" t="s">
         <v>90</v>
       </c>
-      <c r="F28" s="60" t="s">
+      <c r="F28" s="61" t="s">
         <v>54</v>
       </c>
-      <c r="G28" s="61">
+      <c r="G28" s="62">
         <v>2012001</v>
       </c>
-      <c r="H28" s="60" t="s">
+      <c r="H28" s="61" t="s">
         <v>61</v>
       </c>
-      <c r="I28" s="60" t="s">
+      <c r="I28" s="61" t="s">
         <v>90</v>
       </c>
-      <c r="J28" s="60" t="s">
+      <c r="J28" s="61" t="s">
         <v>92</v>
       </c>
-      <c r="K28" s="62">
+      <c r="K28" s="63">
         <v>10120044</v>
       </c>
     </row>
     <row r="29" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A29" s="60">
+      <c r="A29" s="61">
         <v>30120015</v>
       </c>
       <c r="B29" s="5">
@@ -3580,33 +3613,33 @@
       <c r="C29" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="D29" s="45">
+      <c r="D29" s="46">
         <v>32105</v>
       </c>
-      <c r="E29" s="60" t="s">
+      <c r="E29" s="61" t="s">
         <v>90</v>
       </c>
-      <c r="F29" s="60" t="s">
+      <c r="F29" s="61" t="s">
         <v>54</v>
       </c>
-      <c r="G29" s="61">
+      <c r="G29" s="62">
         <v>2012001</v>
       </c>
-      <c r="H29" s="60" t="s">
+      <c r="H29" s="61" t="s">
         <v>61</v>
       </c>
-      <c r="I29" s="60" t="s">
+      <c r="I29" s="61" t="s">
         <v>90</v>
       </c>
-      <c r="J29" s="60" t="s">
+      <c r="J29" s="61" t="s">
         <v>92</v>
       </c>
-      <c r="K29" s="62">
+      <c r="K29" s="63">
         <v>10120045</v>
       </c>
     </row>
     <row r="30" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A30" s="60">
+      <c r="A30" s="61">
         <v>30120016</v>
       </c>
       <c r="B30" s="5">
@@ -3615,33 +3648,33 @@
       <c r="C30" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="D30" s="45">
+      <c r="D30" s="46">
         <v>32106</v>
       </c>
-      <c r="E30" s="60" t="s">
+      <c r="E30" s="61" t="s">
         <v>90</v>
       </c>
-      <c r="F30" s="60" t="s">
+      <c r="F30" s="61" t="s">
         <v>54</v>
       </c>
-      <c r="G30" s="61">
+      <c r="G30" s="62">
         <v>2012001</v>
       </c>
-      <c r="H30" s="60" t="s">
+      <c r="H30" s="61" t="s">
         <v>61</v>
       </c>
-      <c r="I30" s="60" t="s">
+      <c r="I30" s="61" t="s">
         <v>90</v>
       </c>
-      <c r="J30" s="60" t="s">
+      <c r="J30" s="61" t="s">
         <v>92</v>
       </c>
-      <c r="K30" s="62">
+      <c r="K30" s="63">
         <v>10120046</v>
       </c>
     </row>
     <row r="31" s="6" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A31" s="54">
+      <c r="A31" s="55">
         <v>30120021</v>
       </c>
       <c r="B31" s="6">
@@ -3650,31 +3683,31 @@
       <c r="C31" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D31" s="54">
+      <c r="D31" s="55">
         <v>32201</v>
       </c>
-      <c r="E31" s="54" t="s">
+      <c r="E31" s="55" t="s">
         <v>86</v>
       </c>
-      <c r="F31" s="54" t="s">
+      <c r="F31" s="55" t="s">
         <v>54</v>
       </c>
-      <c r="G31" s="63">
+      <c r="G31" s="64">
         <v>2012001</v>
       </c>
-      <c r="H31" s="54" t="s">
+      <c r="H31" s="55" t="s">
         <v>61</v>
       </c>
-      <c r="I31" s="54" t="s">
+      <c r="I31" s="55" t="s">
         <v>86</v>
       </c>
-      <c r="J31" s="54"/>
-      <c r="K31" s="64">
+      <c r="J31" s="55"/>
+      <c r="K31" s="65">
         <v>10120041</v>
       </c>
     </row>
     <row r="32" s="6" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A32" s="54">
+      <c r="A32" s="55">
         <v>30120022</v>
       </c>
       <c r="B32" s="6">
@@ -3683,31 +3716,31 @@
       <c r="C32" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D32" s="54">
+      <c r="D32" s="55">
         <v>32202</v>
       </c>
-      <c r="E32" s="54" t="s">
+      <c r="E32" s="55" t="s">
         <v>88</v>
       </c>
-      <c r="F32" s="54" t="s">
+      <c r="F32" s="55" t="s">
         <v>54</v>
       </c>
-      <c r="G32" s="63">
+      <c r="G32" s="64">
         <v>2012001</v>
       </c>
-      <c r="H32" s="54" t="s">
+      <c r="H32" s="55" t="s">
         <v>61</v>
       </c>
-      <c r="I32" s="54" t="s">
+      <c r="I32" s="55" t="s">
         <v>88</v>
       </c>
-      <c r="J32" s="54"/>
-      <c r="K32" s="64">
+      <c r="J32" s="55"/>
+      <c r="K32" s="65">
         <v>10120042</v>
       </c>
     </row>
     <row r="33" s="6" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A33" s="54">
+      <c r="A33" s="55">
         <v>30120023</v>
       </c>
       <c r="B33" s="6">
@@ -3716,31 +3749,31 @@
       <c r="C33" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D33" s="54">
+      <c r="D33" s="55">
         <v>32203</v>
       </c>
-      <c r="E33" s="54" t="s">
+      <c r="E33" s="55" t="s">
         <v>89</v>
       </c>
-      <c r="F33" s="54" t="s">
+      <c r="F33" s="55" t="s">
         <v>54</v>
       </c>
-      <c r="G33" s="63">
+      <c r="G33" s="64">
         <v>2012001</v>
       </c>
-      <c r="H33" s="54" t="s">
+      <c r="H33" s="55" t="s">
         <v>61</v>
       </c>
-      <c r="I33" s="54" t="s">
+      <c r="I33" s="55" t="s">
         <v>89</v>
       </c>
-      <c r="J33" s="54"/>
-      <c r="K33" s="64">
+      <c r="J33" s="55"/>
+      <c r="K33" s="65">
         <v>10120043</v>
       </c>
     </row>
     <row r="34" s="6" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A34" s="54">
+      <c r="A34" s="55">
         <v>30120024</v>
       </c>
       <c r="B34" s="6">
@@ -3749,31 +3782,31 @@
       <c r="C34" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D34" s="54">
+      <c r="D34" s="55">
         <v>32204</v>
       </c>
-      <c r="E34" s="54" t="s">
+      <c r="E34" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="F34" s="54" t="s">
+      <c r="F34" s="55" t="s">
         <v>54</v>
       </c>
-      <c r="G34" s="63">
+      <c r="G34" s="64">
         <v>2012001</v>
       </c>
-      <c r="H34" s="54" t="s">
+      <c r="H34" s="55" t="s">
         <v>61</v>
       </c>
-      <c r="I34" s="54" t="s">
+      <c r="I34" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="J34" s="54"/>
-      <c r="K34" s="64">
+      <c r="J34" s="55"/>
+      <c r="K34" s="65">
         <v>10120044</v>
       </c>
     </row>
     <row r="35" s="6" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A35" s="54">
+      <c r="A35" s="55">
         <v>30120025</v>
       </c>
       <c r="B35" s="6">
@@ -3782,31 +3815,31 @@
       <c r="C35" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D35" s="54">
+      <c r="D35" s="55">
         <v>32205</v>
       </c>
-      <c r="E35" s="54" t="s">
+      <c r="E35" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="F35" s="54" t="s">
+      <c r="F35" s="55" t="s">
         <v>54</v>
       </c>
-      <c r="G35" s="63">
+      <c r="G35" s="64">
         <v>2012001</v>
       </c>
-      <c r="H35" s="54" t="s">
+      <c r="H35" s="55" t="s">
         <v>61</v>
       </c>
-      <c r="I35" s="54" t="s">
+      <c r="I35" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="J35" s="54"/>
-      <c r="K35" s="64">
+      <c r="J35" s="55"/>
+      <c r="K35" s="65">
         <v>10120045</v>
       </c>
     </row>
     <row r="36" s="6" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A36" s="54">
+      <c r="A36" s="55">
         <v>30120026</v>
       </c>
       <c r="B36" s="6">
@@ -3815,2212 +3848,2348 @@
       <c r="C36" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D36" s="54">
+      <c r="D36" s="55">
         <v>32206</v>
       </c>
-      <c r="E36" s="54" t="s">
+      <c r="E36" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="F36" s="54" t="s">
+      <c r="F36" s="55" t="s">
         <v>54</v>
       </c>
-      <c r="G36" s="63">
+      <c r="G36" s="64">
         <v>2012001</v>
       </c>
-      <c r="H36" s="54" t="s">
+      <c r="H36" s="55" t="s">
         <v>61</v>
       </c>
-      <c r="I36" s="54" t="s">
+      <c r="I36" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="J36" s="54"/>
-      <c r="K36" s="64">
+      <c r="J36" s="55"/>
+      <c r="K36" s="65">
         <v>10120046</v>
       </c>
     </row>
     <row r="37" s="7" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A37" s="65">
+      <c r="A37" s="66">
         <v>30240001</v>
       </c>
-      <c r="B37" s="66">
+      <c r="B37" s="67">
         <v>102400</v>
       </c>
-      <c r="C37" s="66" t="s">
+      <c r="C37" s="67" t="s">
         <v>32</v>
       </c>
-      <c r="D37" s="65">
+      <c r="D37" s="66">
         <v>32401</v>
       </c>
-      <c r="E37" s="65" t="s">
+      <c r="E37" s="66" t="s">
         <v>33</v>
       </c>
-      <c r="F37" s="65" t="s">
+      <c r="F37" s="66" t="s">
         <v>34</v>
       </c>
-      <c r="G37" s="65"/>
-      <c r="H37" s="65"/>
-      <c r="I37" s="65" t="s">
+      <c r="G37" s="66"/>
+      <c r="H37" s="66"/>
+      <c r="I37" s="66" t="s">
         <v>35</v>
       </c>
-      <c r="J37" s="65"/>
-      <c r="K37" s="67"/>
-      <c r="L37" s="65" t="s">
+      <c r="J37" s="66"/>
+      <c r="K37" s="68"/>
+      <c r="L37" s="66" t="s">
         <v>44</v>
       </c>
-      <c r="M37" s="65" t="s">
+      <c r="M37" s="66" t="s">
         <v>37</v>
       </c>
-      <c r="N37" s="65" t="s">
+      <c r="N37" s="66" t="s">
         <v>38</v>
       </c>
-      <c r="O37" s="65"/>
-      <c r="P37" s="65"/>
-      <c r="Q37" s="68" t="s">
+      <c r="O37" s="66"/>
+      <c r="P37" s="66"/>
+      <c r="Q37" s="69" t="s">
         <v>39</v>
       </c>
-      <c r="R37" s="69" t="s">
+      <c r="R37" s="70" t="s">
         <v>40</v>
       </c>
-      <c r="S37" s="70" t="s">
+      <c r="S37" s="71" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="38" s="7" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A38" s="65">
+      <c r="A38" s="66">
         <v>30240002</v>
       </c>
-      <c r="B38" s="66">
+      <c r="B38" s="67">
         <v>102400</v>
       </c>
-      <c r="C38" s="66" t="s">
+      <c r="C38" s="67" t="s">
         <v>32</v>
       </c>
-      <c r="D38" s="65">
+      <c r="D38" s="66">
         <v>32402</v>
       </c>
-      <c r="E38" s="65" t="s">
+      <c r="E38" s="66" t="s">
         <v>42</v>
       </c>
-      <c r="F38" s="65" t="s">
+      <c r="F38" s="66" t="s">
         <v>34</v>
       </c>
-      <c r="G38" s="65"/>
-      <c r="H38" s="65"/>
-      <c r="I38" s="65" t="s">
+      <c r="G38" s="66"/>
+      <c r="H38" s="66"/>
+      <c r="I38" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="J38" s="65"/>
-      <c r="K38" s="67"/>
-      <c r="L38" s="65" t="s">
+      <c r="J38" s="66"/>
+      <c r="K38" s="68"/>
+      <c r="L38" s="66" t="s">
         <v>44</v>
       </c>
-      <c r="M38" s="65" t="s">
+      <c r="M38" s="66" t="s">
         <v>37</v>
       </c>
-      <c r="N38" s="65" t="s">
+      <c r="N38" s="66" t="s">
         <v>38</v>
       </c>
-      <c r="O38" s="65"/>
-      <c r="P38" s="65"/>
-      <c r="Q38" s="68" t="s">
+      <c r="O38" s="66"/>
+      <c r="P38" s="66"/>
+      <c r="Q38" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="R38" s="69" t="s">
+      <c r="R38" s="70" t="s">
         <v>40</v>
       </c>
-      <c r="S38" s="70"/>
+      <c r="S38" s="71"/>
     </row>
     <row r="39" s="7" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A39" s="65">
+      <c r="A39" s="66">
         <v>30240003</v>
       </c>
-      <c r="B39" s="66">
+      <c r="B39" s="67">
         <v>102400</v>
       </c>
-      <c r="C39" s="66" t="s">
+      <c r="C39" s="67" t="s">
         <v>32</v>
       </c>
-      <c r="D39" s="65">
+      <c r="D39" s="66">
         <v>32403</v>
       </c>
-      <c r="E39" s="65" t="s">
+      <c r="E39" s="66" t="s">
         <v>46</v>
       </c>
-      <c r="F39" s="65" t="s">
+      <c r="F39" s="66" t="s">
         <v>34</v>
       </c>
-      <c r="G39" s="65"/>
-      <c r="H39" s="65"/>
-      <c r="I39" s="65" t="s">
+      <c r="G39" s="66"/>
+      <c r="H39" s="66"/>
+      <c r="I39" s="66" t="s">
         <v>47</v>
       </c>
-      <c r="J39" s="65"/>
-      <c r="K39" s="67"/>
-      <c r="L39" s="65" t="s">
+      <c r="J39" s="66"/>
+      <c r="K39" s="68"/>
+      <c r="L39" s="66" t="s">
         <v>44</v>
       </c>
-      <c r="M39" s="65" t="s">
+      <c r="M39" s="66" t="s">
         <v>37</v>
       </c>
-      <c r="N39" s="65" t="s">
+      <c r="N39" s="66" t="s">
         <v>38</v>
       </c>
-      <c r="O39" s="65"/>
-      <c r="P39" s="65"/>
-      <c r="Q39" s="68" t="s">
+      <c r="O39" s="66"/>
+      <c r="P39" s="66"/>
+      <c r="Q39" s="69" t="s">
         <v>48</v>
       </c>
-      <c r="R39" s="69" t="s">
+      <c r="R39" s="70" t="s">
         <v>40</v>
       </c>
-      <c r="S39" s="70"/>
+      <c r="S39" s="71"/>
     </row>
     <row r="40" s="7" customFormat="1" ht="15" customHeight="1" spans="1:19">
-      <c r="A40" s="65">
+      <c r="A40" s="66">
         <v>30240004</v>
       </c>
-      <c r="B40" s="66">
+      <c r="B40" s="67">
         <v>102400</v>
       </c>
-      <c r="C40" s="66" t="s">
+      <c r="C40" s="67" t="s">
         <v>32</v>
       </c>
-      <c r="D40" s="65">
+      <c r="D40" s="66">
         <v>32404</v>
       </c>
-      <c r="E40" s="65" t="s">
+      <c r="E40" s="66" t="s">
         <v>49</v>
       </c>
-      <c r="F40" s="65" t="s">
+      <c r="F40" s="66" t="s">
         <v>34</v>
       </c>
-      <c r="G40" s="65"/>
-      <c r="H40" s="65"/>
-      <c r="I40" s="65" t="s">
+      <c r="G40" s="66"/>
+      <c r="H40" s="66"/>
+      <c r="I40" s="66" t="s">
         <v>50</v>
       </c>
-      <c r="J40" s="65"/>
-      <c r="K40" s="67"/>
-      <c r="L40" s="65" t="s">
+      <c r="J40" s="66"/>
+      <c r="K40" s="68"/>
+      <c r="L40" s="66" t="s">
         <v>44</v>
       </c>
-      <c r="M40" s="65" t="s">
+      <c r="M40" s="66" t="s">
         <v>37</v>
       </c>
-      <c r="N40" s="65" t="s">
+      <c r="N40" s="66" t="s">
         <v>38</v>
       </c>
-      <c r="O40" s="65"/>
-      <c r="P40" s="65"/>
-      <c r="Q40" s="68" t="s">
+      <c r="O40" s="66"/>
+      <c r="P40" s="66"/>
+      <c r="Q40" s="69" t="s">
         <v>51</v>
       </c>
-      <c r="R40" s="69" t="s">
+      <c r="R40" s="70" t="s">
         <v>40</v>
       </c>
-      <c r="S40" s="70"/>
+      <c r="S40" s="71"/>
     </row>
     <row r="41" s="7" customFormat="1" ht="15" customHeight="1" spans="1:19">
-      <c r="A41" s="65">
+      <c r="A41" s="66">
         <v>30240005</v>
       </c>
-      <c r="B41" s="66">
+      <c r="B41" s="67">
         <v>102400</v>
       </c>
-      <c r="C41" s="66" t="s">
+      <c r="C41" s="67" t="s">
         <v>32</v>
       </c>
-      <c r="D41" s="65">
+      <c r="D41" s="66">
         <v>32411</v>
       </c>
-      <c r="E41" s="65" t="s">
+      <c r="E41" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="F41" s="65" t="s">
+      <c r="F41" s="66" t="s">
         <v>34</v>
       </c>
-      <c r="G41" s="65"/>
-      <c r="H41" s="65"/>
-      <c r="I41" s="65" t="s">
+      <c r="G41" s="66"/>
+      <c r="H41" s="66"/>
+      <c r="I41" s="66" t="s">
         <v>53</v>
       </c>
-      <c r="J41" s="65"/>
-      <c r="K41" s="67"/>
-      <c r="L41" s="65" t="s">
+      <c r="J41" s="66"/>
+      <c r="K41" s="68"/>
+      <c r="L41" s="66" t="s">
         <v>44</v>
       </c>
-      <c r="M41" s="65" t="s">
+      <c r="M41" s="66" t="s">
         <v>54</v>
       </c>
-      <c r="N41" s="65"/>
-      <c r="O41" s="65" t="s">
+      <c r="N41" s="66"/>
+      <c r="O41" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="P41" s="65"/>
-      <c r="Q41" s="68"/>
-      <c r="R41" s="68"/>
-      <c r="S41" s="70"/>
+      <c r="P41" s="66"/>
+      <c r="Q41" s="69"/>
+      <c r="R41" s="69"/>
+      <c r="S41" s="71"/>
     </row>
     <row r="42" s="7" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A42" s="65">
+      <c r="A42" s="66">
         <v>30240006</v>
       </c>
-      <c r="B42" s="66">
+      <c r="B42" s="67">
         <v>102400</v>
       </c>
-      <c r="C42" s="66" t="s">
+      <c r="C42" s="67" t="s">
         <v>32</v>
       </c>
-      <c r="D42" s="65">
+      <c r="D42" s="66">
         <v>32421</v>
       </c>
-      <c r="E42" s="65" t="s">
+      <c r="E42" s="66" t="s">
         <v>56</v>
       </c>
-      <c r="F42" s="65" t="s">
+      <c r="F42" s="66" t="s">
         <v>34</v>
       </c>
-      <c r="G42" s="65"/>
-      <c r="H42" s="65"/>
-      <c r="I42" s="65" t="s">
+      <c r="G42" s="66"/>
+      <c r="H42" s="66"/>
+      <c r="I42" s="66" t="s">
         <v>57</v>
       </c>
-      <c r="J42" s="65"/>
-      <c r="K42" s="67"/>
-      <c r="L42" s="65" t="s">
+      <c r="J42" s="66"/>
+      <c r="K42" s="68"/>
+      <c r="L42" s="66" t="s">
         <v>44</v>
       </c>
-      <c r="M42" s="65" t="s">
+      <c r="M42" s="66" t="s">
         <v>58</v>
       </c>
-      <c r="N42" s="65" t="s">
+      <c r="N42" s="66" t="s">
         <v>38</v>
       </c>
-      <c r="O42" s="65" t="s">
+      <c r="O42" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="P42" s="65"/>
-      <c r="Q42" s="65"/>
-      <c r="R42" s="65"/>
-      <c r="S42" s="70"/>
+      <c r="P42" s="66"/>
+      <c r="Q42" s="66"/>
+      <c r="R42" s="66"/>
+      <c r="S42" s="71"/>
     </row>
     <row r="43" s="7" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A43" s="65">
+      <c r="A43" s="66">
         <v>30240007</v>
       </c>
-      <c r="B43" s="66">
+      <c r="B43" s="67">
         <v>102400</v>
       </c>
-      <c r="C43" s="66" t="s">
+      <c r="C43" s="67" t="s">
         <v>32</v>
       </c>
-      <c r="D43" s="65">
+      <c r="D43" s="66">
         <v>32431</v>
       </c>
-      <c r="E43" s="65" t="s">
+      <c r="E43" s="66" t="s">
         <v>59</v>
       </c>
-      <c r="F43" s="65" t="s">
+      <c r="F43" s="66" t="s">
         <v>60</v>
       </c>
-      <c r="G43" s="65">
+      <c r="G43" s="66">
         <v>2024001</v>
       </c>
-      <c r="H43" s="65" t="s">
+      <c r="H43" s="66" t="s">
         <v>61</v>
       </c>
-      <c r="I43" s="65" t="s">
+      <c r="I43" s="66" t="s">
         <v>62</v>
       </c>
-      <c r="J43" s="65"/>
-      <c r="K43" s="67">
+      <c r="J43" s="66"/>
+      <c r="K43" s="68">
         <v>10240091</v>
       </c>
-      <c r="L43" s="65"/>
-      <c r="M43" s="65"/>
-      <c r="N43" s="65"/>
-      <c r="O43" s="65"/>
-      <c r="P43" s="65"/>
-      <c r="Q43" s="65"/>
-      <c r="R43" s="65"/>
-      <c r="S43" s="70"/>
+      <c r="L43" s="66"/>
+      <c r="M43" s="66"/>
+      <c r="N43" s="66"/>
+      <c r="O43" s="66"/>
+      <c r="P43" s="66"/>
+      <c r="Q43" s="66"/>
+      <c r="R43" s="66"/>
+      <c r="S43" s="71"/>
     </row>
     <row r="44" s="7" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A44" s="65">
+      <c r="A44" s="66">
         <v>30240008</v>
       </c>
-      <c r="B44" s="66">
+      <c r="B44" s="67">
         <v>102400</v>
       </c>
-      <c r="C44" s="66" t="s">
+      <c r="C44" s="67" t="s">
         <v>32</v>
       </c>
-      <c r="D44" s="65">
+      <c r="D44" s="66">
         <v>32432</v>
       </c>
-      <c r="E44" s="65" t="s">
+      <c r="E44" s="66" t="s">
         <v>63</v>
       </c>
-      <c r="F44" s="65" t="s">
+      <c r="F44" s="66" t="s">
         <v>54</v>
       </c>
-      <c r="G44" s="65">
+      <c r="G44" s="66">
         <v>2024001</v>
       </c>
-      <c r="H44" s="65" t="s">
+      <c r="H44" s="66" t="s">
         <v>61</v>
       </c>
-      <c r="I44" s="65" t="s">
+      <c r="I44" s="66" t="s">
         <v>64</v>
       </c>
-      <c r="J44" s="65"/>
-      <c r="K44" s="71" t="s">
+      <c r="J44" s="66"/>
+      <c r="K44" s="72" t="s">
         <v>94</v>
       </c>
-      <c r="L44" s="65"/>
-      <c r="M44" s="65"/>
-      <c r="N44" s="65"/>
-      <c r="O44" s="65"/>
-      <c r="P44" s="65"/>
-      <c r="Q44" s="65"/>
-      <c r="R44" s="65"/>
-      <c r="S44" s="70"/>
+      <c r="L44" s="66"/>
+      <c r="M44" s="66"/>
+      <c r="N44" s="66"/>
+      <c r="O44" s="66"/>
+      <c r="P44" s="66"/>
+      <c r="Q44" s="66"/>
+      <c r="R44" s="66"/>
+      <c r="S44" s="71"/>
     </row>
     <row r="45" s="7" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A45" s="65">
+      <c r="A45" s="66">
         <v>30240009</v>
       </c>
-      <c r="B45" s="66">
+      <c r="B45" s="67">
         <v>102400</v>
       </c>
-      <c r="C45" s="66" t="s">
+      <c r="C45" s="67" t="s">
         <v>32</v>
       </c>
-      <c r="D45" s="65">
+      <c r="D45" s="66">
         <v>32433</v>
       </c>
-      <c r="E45" s="65" t="s">
+      <c r="E45" s="66" t="s">
         <v>66</v>
       </c>
-      <c r="F45" s="65" t="s">
+      <c r="F45" s="66" t="s">
         <v>54</v>
       </c>
-      <c r="G45" s="65">
+      <c r="G45" s="66">
         <v>2024001</v>
       </c>
-      <c r="H45" s="65" t="s">
+      <c r="H45" s="66" t="s">
         <v>61</v>
       </c>
-      <c r="I45" s="65" t="s">
+      <c r="I45" s="66" t="s">
         <v>67</v>
       </c>
-      <c r="J45" s="65"/>
-      <c r="K45" s="67" t="s">
+      <c r="J45" s="66"/>
+      <c r="K45" s="68" t="s">
         <v>95</v>
       </c>
-      <c r="L45" s="65"/>
-      <c r="M45" s="65"/>
-      <c r="N45" s="65"/>
-      <c r="O45" s="65"/>
-      <c r="P45" s="65"/>
-      <c r="Q45" s="65"/>
-      <c r="R45" s="65"/>
-      <c r="S45" s="70"/>
+      <c r="L45" s="66"/>
+      <c r="M45" s="66"/>
+      <c r="N45" s="66"/>
+      <c r="O45" s="66"/>
+      <c r="P45" s="66"/>
+      <c r="Q45" s="66"/>
+      <c r="R45" s="66"/>
+      <c r="S45" s="71"/>
     </row>
     <row r="46" s="7" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A46" s="65">
+      <c r="A46" s="66">
         <v>30240010</v>
       </c>
-      <c r="B46" s="66">
+      <c r="B46" s="67">
         <v>102400</v>
       </c>
-      <c r="C46" s="66" t="s">
+      <c r="C46" s="67" t="s">
         <v>32</v>
       </c>
-      <c r="D46" s="65">
+      <c r="D46" s="66">
         <v>32441</v>
       </c>
-      <c r="E46" s="65" t="s">
+      <c r="E46" s="66" t="s">
         <v>69</v>
       </c>
-      <c r="F46" s="65" t="s">
+      <c r="F46" s="66" t="s">
         <v>34</v>
       </c>
-      <c r="G46" s="65"/>
-      <c r="H46" s="65"/>
-      <c r="I46" s="65" t="s">
+      <c r="G46" s="66"/>
+      <c r="H46" s="66"/>
+      <c r="I46" s="66" t="s">
         <v>70</v>
       </c>
-      <c r="J46" s="65"/>
-      <c r="K46" s="71"/>
-      <c r="L46" s="65" t="s">
+      <c r="J46" s="66"/>
+      <c r="K46" s="72"/>
+      <c r="L46" s="66" t="s">
         <v>44</v>
       </c>
-      <c r="M46" s="65" t="s">
+      <c r="M46" s="66" t="s">
         <v>71</v>
       </c>
-      <c r="N46" s="65"/>
-      <c r="O46" s="65"/>
-      <c r="P46" s="65"/>
-      <c r="Q46" s="68" t="s">
+      <c r="N46" s="66"/>
+      <c r="O46" s="66"/>
+      <c r="P46" s="66"/>
+      <c r="Q46" s="69" t="s">
         <v>72</v>
       </c>
-      <c r="R46" s="72" t="s">
+      <c r="R46" s="73" t="s">
         <v>73</v>
       </c>
-      <c r="S46" s="68" t="s">
+      <c r="S46" s="69" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="47" s="7" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A47" s="65">
+      <c r="A47" s="66">
         <v>30240011</v>
       </c>
-      <c r="B47" s="66">
+      <c r="B47" s="67">
         <v>102400</v>
       </c>
-      <c r="C47" s="66" t="s">
+      <c r="C47" s="67" t="s">
         <v>32</v>
       </c>
-      <c r="D47" s="65">
+      <c r="D47" s="66">
         <v>32442</v>
       </c>
-      <c r="E47" s="65" t="s">
+      <c r="E47" s="66" t="s">
         <v>75</v>
       </c>
-      <c r="F47" s="65" t="s">
+      <c r="F47" s="66" t="s">
         <v>34</v>
       </c>
-      <c r="G47" s="65"/>
-      <c r="H47" s="65"/>
-      <c r="I47" s="65" t="s">
+      <c r="G47" s="66"/>
+      <c r="H47" s="66"/>
+      <c r="I47" s="66" t="s">
         <v>76</v>
       </c>
-      <c r="J47" s="65"/>
-      <c r="K47" s="67"/>
-      <c r="L47" s="65" t="s">
+      <c r="J47" s="66"/>
+      <c r="K47" s="68"/>
+      <c r="L47" s="66" t="s">
         <v>44</v>
       </c>
-      <c r="M47" s="65" t="s">
+      <c r="M47" s="66" t="s">
         <v>58</v>
       </c>
-      <c r="N47" s="65"/>
-      <c r="O47" s="65"/>
-      <c r="P47" s="65"/>
-      <c r="Q47" s="65"/>
-      <c r="R47" s="65"/>
-      <c r="S47" s="70"/>
+      <c r="N47" s="66"/>
+      <c r="O47" s="66"/>
+      <c r="P47" s="66"/>
+      <c r="Q47" s="66"/>
+      <c r="R47" s="66"/>
+      <c r="S47" s="71"/>
     </row>
     <row r="48" s="7" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A48" s="65">
+      <c r="A48" s="66">
         <v>30240012</v>
       </c>
-      <c r="B48" s="66">
+      <c r="B48" s="67">
         <v>102400</v>
       </c>
-      <c r="C48" s="66" t="s">
+      <c r="C48" s="67" t="s">
         <v>32</v>
       </c>
-      <c r="D48" s="65">
+      <c r="D48" s="66">
         <v>32443</v>
       </c>
-      <c r="E48" s="65" t="s">
+      <c r="E48" s="66" t="s">
         <v>77</v>
       </c>
-      <c r="F48" s="65" t="s">
+      <c r="F48" s="66" t="s">
         <v>54</v>
       </c>
-      <c r="G48" s="65">
+      <c r="G48" s="66">
         <v>2024001</v>
       </c>
-      <c r="H48" s="65" t="s">
+      <c r="H48" s="66" t="s">
         <v>61</v>
       </c>
-      <c r="I48" s="65" t="s">
+      <c r="I48" s="66" t="s">
         <v>67</v>
       </c>
-      <c r="J48" s="65"/>
-      <c r="K48" s="67" t="s">
+      <c r="J48" s="66"/>
+      <c r="K48" s="68" t="s">
         <v>95</v>
       </c>
-      <c r="L48" s="65"/>
-      <c r="M48" s="65"/>
-      <c r="N48" s="65"/>
-      <c r="O48" s="65"/>
-      <c r="P48" s="65"/>
-      <c r="Q48" s="65"/>
-      <c r="R48" s="65"/>
-      <c r="S48" s="70"/>
+      <c r="L48" s="66"/>
+      <c r="M48" s="66"/>
+      <c r="N48" s="66"/>
+      <c r="O48" s="66"/>
+      <c r="P48" s="66"/>
+      <c r="Q48" s="66"/>
+      <c r="R48" s="66"/>
+      <c r="S48" s="71"/>
     </row>
     <row r="49" s="8" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A49" s="73">
+      <c r="A49" s="74">
         <v>30170001</v>
       </c>
-      <c r="B49" s="74">
+      <c r="B49" s="75">
         <v>101700</v>
       </c>
-      <c r="C49" s="74" t="s">
+      <c r="C49" s="75" t="s">
         <v>96</v>
       </c>
-      <c r="D49" s="73">
+      <c r="D49" s="74">
         <v>301701</v>
       </c>
-      <c r="E49" s="73" t="s">
+      <c r="E49" s="74" t="s">
         <v>97</v>
       </c>
-      <c r="F49" s="73" t="s">
+      <c r="F49" s="74" t="s">
         <v>80</v>
       </c>
-      <c r="G49" s="73">
+      <c r="G49" s="74">
         <v>2017001</v>
       </c>
-      <c r="H49" s="73" t="s">
+      <c r="H49" s="74" t="s">
         <v>61</v>
       </c>
-      <c r="I49" s="73" t="s">
+      <c r="I49" s="74" t="s">
         <v>81</v>
       </c>
-      <c r="J49" s="73"/>
-      <c r="K49" s="75" t="s">
+      <c r="J49" s="74"/>
+      <c r="K49" s="76" t="s">
         <v>98</v>
       </c>
-      <c r="L49" s="73"/>
-      <c r="M49" s="73"/>
-      <c r="N49" s="73"/>
-      <c r="O49" s="73"/>
-      <c r="P49" s="73"/>
-      <c r="Q49" s="73"/>
-      <c r="R49" s="73"/>
-      <c r="S49" s="76"/>
+      <c r="L49" s="74"/>
+      <c r="M49" s="74"/>
+      <c r="N49" s="74"/>
+      <c r="O49" s="74"/>
+      <c r="P49" s="74"/>
+      <c r="Q49" s="74"/>
+      <c r="R49" s="74"/>
+      <c r="S49" s="77"/>
     </row>
     <row r="50" s="8" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A50" s="73">
+      <c r="A50" s="74">
         <v>30170002</v>
       </c>
-      <c r="B50" s="74">
+      <c r="B50" s="75">
         <v>101700</v>
       </c>
-      <c r="C50" s="74" t="s">
+      <c r="C50" s="75" t="s">
         <v>96</v>
       </c>
-      <c r="D50" s="73">
+      <c r="D50" s="74">
         <v>301702</v>
       </c>
-      <c r="E50" s="73" t="s">
+      <c r="E50" s="74" t="s">
         <v>99</v>
       </c>
-      <c r="F50" s="73" t="s">
+      <c r="F50" s="74" t="s">
         <v>84</v>
       </c>
-      <c r="G50" s="73">
+      <c r="G50" s="74">
         <v>2017001</v>
       </c>
-      <c r="H50" s="73" t="s">
+      <c r="H50" s="74" t="s">
         <v>61</v>
       </c>
-      <c r="I50" s="73" t="s">
+      <c r="I50" s="74" t="s">
         <v>81</v>
       </c>
-      <c r="J50" s="73"/>
-      <c r="K50" s="75" t="s">
+      <c r="J50" s="74"/>
+      <c r="K50" s="76" t="s">
         <v>98</v>
       </c>
-      <c r="L50" s="73"/>
-      <c r="M50" s="73"/>
-      <c r="N50" s="73"/>
-      <c r="O50" s="73"/>
-      <c r="P50" s="73"/>
-      <c r="Q50" s="73"/>
-      <c r="R50" s="73"/>
-      <c r="S50" s="76"/>
+      <c r="L50" s="74"/>
+      <c r="M50" s="74"/>
+      <c r="N50" s="74"/>
+      <c r="O50" s="74"/>
+      <c r="P50" s="74"/>
+      <c r="Q50" s="74"/>
+      <c r="R50" s="74"/>
+      <c r="S50" s="77"/>
     </row>
     <row r="51" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A51" s="60">
+      <c r="A51" s="61">
         <v>30220001</v>
       </c>
-      <c r="B51" s="61">
+      <c r="B51" s="62">
         <v>102200</v>
       </c>
-      <c r="C51" s="61" t="s">
+      <c r="C51" s="62" t="s">
         <v>100</v>
       </c>
-      <c r="D51" s="60">
+      <c r="D51" s="61">
         <v>302201</v>
       </c>
-      <c r="E51" s="60" t="s">
+      <c r="E51" s="61" t="s">
         <v>101</v>
       </c>
-      <c r="F51" s="60" t="s">
+      <c r="F51" s="61" t="s">
         <v>102</v>
       </c>
-      <c r="G51" s="60">
+      <c r="G51" s="61">
         <v>2022001</v>
       </c>
-      <c r="H51" s="60" t="s">
+      <c r="H51" s="61" t="s">
         <v>61</v>
       </c>
-      <c r="I51" s="60"/>
-      <c r="J51" s="60"/>
-      <c r="K51" s="77" t="s">
+      <c r="I51" s="61"/>
+      <c r="J51" s="61"/>
+      <c r="K51" s="78" t="s">
         <v>103</v>
       </c>
-      <c r="L51" s="60" t="s">
+      <c r="L51" s="61" t="s">
         <v>104</v>
       </c>
-      <c r="M51" s="60"/>
-      <c r="N51" s="60"/>
-      <c r="O51" s="60"/>
-      <c r="P51" s="60"/>
-      <c r="Q51" s="60"/>
-      <c r="R51" s="60"/>
-      <c r="S51" s="78"/>
+      <c r="M51" s="61"/>
+      <c r="N51" s="61"/>
+      <c r="O51" s="61"/>
+      <c r="P51" s="61"/>
+      <c r="Q51" s="61"/>
+      <c r="R51" s="61"/>
+      <c r="S51" s="79"/>
     </row>
     <row r="52" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A52" s="60">
+      <c r="A52" s="61">
         <v>30220002</v>
       </c>
-      <c r="B52" s="61">
+      <c r="B52" s="62">
         <v>102200</v>
       </c>
-      <c r="C52" s="61" t="s">
+      <c r="C52" s="62" t="s">
         <v>100</v>
       </c>
-      <c r="D52" s="60">
+      <c r="D52" s="61">
         <v>302202</v>
       </c>
-      <c r="E52" s="60" t="s">
+      <c r="E52" s="61" t="s">
         <v>105</v>
       </c>
-      <c r="F52" s="60" t="s">
+      <c r="F52" s="61" t="s">
         <v>102</v>
       </c>
-      <c r="G52" s="60">
+      <c r="G52" s="61">
         <v>2022001</v>
       </c>
-      <c r="H52" s="60" t="s">
+      <c r="H52" s="61" t="s">
         <v>61</v>
       </c>
-      <c r="I52" s="60"/>
-      <c r="J52" s="60"/>
-      <c r="K52" s="77" t="s">
+      <c r="I52" s="61"/>
+      <c r="J52" s="61"/>
+      <c r="K52" s="78" t="s">
         <v>106</v>
       </c>
-      <c r="L52" s="60" t="s">
+      <c r="L52" s="61" t="s">
         <v>104</v>
       </c>
-      <c r="M52" s="60"/>
-      <c r="N52" s="60"/>
-      <c r="O52" s="60"/>
-      <c r="P52" s="60"/>
-      <c r="Q52" s="60"/>
-      <c r="R52" s="60"/>
-      <c r="S52" s="78"/>
+      <c r="M52" s="61"/>
+      <c r="N52" s="61"/>
+      <c r="O52" s="61"/>
+      <c r="P52" s="61"/>
+      <c r="Q52" s="61"/>
+      <c r="R52" s="61"/>
+      <c r="S52" s="79"/>
     </row>
     <row r="53" s="9" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A53" s="79">
+      <c r="A53" s="80">
         <v>30210001</v>
       </c>
-      <c r="B53" s="80">
+      <c r="B53" s="81">
         <v>102100</v>
       </c>
-      <c r="C53" s="80" t="s">
+      <c r="C53" s="81" t="s">
         <v>107</v>
       </c>
-      <c r="D53" s="79">
+      <c r="D53" s="80">
         <v>302101</v>
       </c>
-      <c r="E53" s="79" t="s">
+      <c r="E53" s="80" t="s">
         <v>108</v>
       </c>
-      <c r="F53" s="79" t="s">
+      <c r="F53" s="80" t="s">
         <v>109</v>
       </c>
-      <c r="G53" s="79">
+      <c r="G53" s="80">
         <v>2021001</v>
       </c>
-      <c r="H53" s="79" t="s">
+      <c r="H53" s="80" t="s">
         <v>61</v>
       </c>
-      <c r="I53" s="79" t="s">
+      <c r="I53" s="80" t="s">
         <v>81</v>
       </c>
-      <c r="J53" s="79"/>
-      <c r="K53" s="81" t="s">
+      <c r="J53" s="80"/>
+      <c r="K53" s="82" t="s">
         <v>110</v>
       </c>
-      <c r="L53" s="79" t="s">
+      <c r="L53" s="80" t="s">
         <v>111</v>
       </c>
-      <c r="M53" s="79"/>
-      <c r="N53" s="79"/>
-      <c r="O53" s="79"/>
-      <c r="P53" s="79"/>
-      <c r="Q53" s="79"/>
-      <c r="R53" s="79"/>
-      <c r="S53" s="82"/>
+      <c r="M53" s="80"/>
+      <c r="N53" s="80"/>
+      <c r="O53" s="80"/>
+      <c r="P53" s="80"/>
+      <c r="Q53" s="80"/>
+      <c r="R53" s="80"/>
+      <c r="S53" s="83"/>
     </row>
     <row r="54" s="9" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A54" s="79">
+      <c r="A54" s="80">
         <v>30210002</v>
       </c>
-      <c r="B54" s="80">
+      <c r="B54" s="81">
         <v>102100</v>
       </c>
-      <c r="C54" s="80" t="s">
+      <c r="C54" s="81" t="s">
         <v>107</v>
       </c>
-      <c r="D54" s="79">
+      <c r="D54" s="80">
         <v>302102</v>
       </c>
-      <c r="E54" s="79" t="s">
+      <c r="E54" s="80" t="s">
         <v>112</v>
       </c>
-      <c r="F54" s="79" t="s">
+      <c r="F54" s="80" t="s">
         <v>34</v>
       </c>
-      <c r="G54" s="79"/>
-      <c r="H54" s="79"/>
-      <c r="I54" s="79" t="s">
+      <c r="G54" s="80"/>
+      <c r="H54" s="80"/>
+      <c r="I54" s="80" t="s">
         <v>113</v>
       </c>
-      <c r="J54" s="79"/>
-      <c r="K54" s="81"/>
-      <c r="L54" s="79"/>
-      <c r="M54" s="79" t="s">
+      <c r="J54" s="80"/>
+      <c r="K54" s="82"/>
+      <c r="L54" s="80"/>
+      <c r="M54" s="80" t="s">
         <v>37</v>
       </c>
-      <c r="N54" s="79" t="s">
+      <c r="N54" s="80" t="s">
         <v>114</v>
       </c>
-      <c r="O54" s="79"/>
-      <c r="P54" s="79"/>
-      <c r="Q54" s="79" t="s">
+      <c r="O54" s="80"/>
+      <c r="P54" s="80"/>
+      <c r="Q54" s="80" t="s">
         <v>115</v>
       </c>
-      <c r="R54" s="79"/>
-      <c r="S54" s="82"/>
+      <c r="R54" s="80"/>
+      <c r="S54" s="83"/>
     </row>
     <row r="55" s="10" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A55" s="83">
+      <c r="A55" s="84">
         <v>30180001</v>
       </c>
-      <c r="B55" s="84">
+      <c r="B55" s="85">
         <v>101800</v>
       </c>
-      <c r="C55" s="84" t="s">
+      <c r="C55" s="85" t="s">
         <v>116</v>
       </c>
-      <c r="D55" s="83">
+      <c r="D55" s="84">
         <v>301801</v>
       </c>
-      <c r="E55" s="83" t="s">
+      <c r="E55" s="84" t="s">
         <v>81</v>
       </c>
-      <c r="F55" s="83" t="s">
+      <c r="F55" s="84" t="s">
         <v>117</v>
       </c>
-      <c r="G55" s="83">
+      <c r="G55" s="84">
         <v>2018002</v>
       </c>
-      <c r="H55" s="83" t="s">
+      <c r="H55" s="84" t="s">
         <v>61</v>
       </c>
-      <c r="I55" s="83" t="s">
+      <c r="I55" s="84" t="s">
         <v>81</v>
       </c>
-      <c r="J55" s="83"/>
-      <c r="K55" s="85">
+      <c r="J55" s="84"/>
+      <c r="K55" s="86">
         <v>10180041</v>
       </c>
-      <c r="L55" s="83"/>
-      <c r="M55" s="83"/>
-      <c r="N55" s="83"/>
-      <c r="O55" s="83"/>
-      <c r="P55" s="83"/>
-      <c r="Q55" s="83"/>
-      <c r="R55" s="83"/>
-      <c r="S55" s="86"/>
+      <c r="L55" s="84"/>
+      <c r="M55" s="84"/>
+      <c r="N55" s="84"/>
+      <c r="O55" s="84"/>
+      <c r="P55" s="84"/>
+      <c r="Q55" s="84"/>
+      <c r="R55" s="84"/>
+      <c r="S55" s="87"/>
     </row>
     <row r="56" s="11" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A56" s="87">
+      <c r="A56" s="88">
         <v>30250001</v>
       </c>
-      <c r="B56" s="88">
+      <c r="B56" s="89">
         <v>102500</v>
       </c>
-      <c r="C56" s="88" t="s">
+      <c r="C56" s="89" t="s">
         <v>118</v>
       </c>
-      <c r="D56" s="87">
+      <c r="D56" s="88">
         <v>302501</v>
       </c>
-      <c r="E56" s="87" t="s">
+      <c r="E56" s="88" t="s">
         <v>108</v>
       </c>
-      <c r="F56" s="87" t="s">
+      <c r="F56" s="88" t="s">
         <v>109</v>
       </c>
-      <c r="G56" s="87">
+      <c r="G56" s="88">
         <v>2025001</v>
       </c>
-      <c r="H56" s="87" t="s">
+      <c r="H56" s="88" t="s">
         <v>61</v>
       </c>
-      <c r="I56" s="87" t="s">
+      <c r="I56" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="J56" s="87"/>
-      <c r="K56" s="89" t="s">
+      <c r="J56" s="88"/>
+      <c r="K56" s="90" t="s">
         <v>119</v>
       </c>
-      <c r="L56" s="87" t="s">
+      <c r="L56" s="88" t="s">
         <v>120</v>
       </c>
-      <c r="M56" s="87"/>
-      <c r="N56" s="87"/>
-      <c r="O56" s="87"/>
-      <c r="P56" s="87"/>
-      <c r="Q56" s="87"/>
-      <c r="R56" s="87"/>
-      <c r="S56" s="90"/>
+      <c r="M56" s="88"/>
+      <c r="N56" s="88"/>
+      <c r="O56" s="88"/>
+      <c r="P56" s="88"/>
+      <c r="Q56" s="88"/>
+      <c r="R56" s="88"/>
+      <c r="S56" s="91"/>
     </row>
     <row r="57" s="11" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A57" s="87">
+      <c r="A57" s="88">
         <v>30250002</v>
       </c>
-      <c r="B57" s="88">
+      <c r="B57" s="89">
         <v>102500</v>
       </c>
-      <c r="C57" s="88" t="s">
+      <c r="C57" s="89" t="s">
         <v>118</v>
       </c>
-      <c r="D57" s="87">
+      <c r="D57" s="88">
         <v>302502</v>
       </c>
-      <c r="E57" s="87" t="s">
+      <c r="E57" s="88" t="s">
         <v>121</v>
       </c>
-      <c r="F57" s="87" t="s">
+      <c r="F57" s="88" t="s">
         <v>122</v>
       </c>
-      <c r="G57" s="87">
+      <c r="G57" s="88">
         <v>2025001</v>
       </c>
-      <c r="H57" s="87" t="s">
+      <c r="H57" s="88" t="s">
         <v>61</v>
       </c>
-      <c r="I57" s="87" t="s">
+      <c r="I57" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="J57" s="87"/>
-      <c r="K57" s="89" t="s">
+      <c r="J57" s="88"/>
+      <c r="K57" s="90" t="s">
         <v>119</v>
       </c>
-      <c r="L57" s="87" t="s">
+      <c r="L57" s="88" t="s">
         <v>120</v>
       </c>
-      <c r="M57" s="87"/>
-      <c r="N57" s="87"/>
-      <c r="O57" s="87"/>
-      <c r="P57" s="87"/>
-      <c r="Q57" s="87"/>
-      <c r="R57" s="87"/>
-      <c r="S57" s="90"/>
+      <c r="M57" s="88"/>
+      <c r="N57" s="88"/>
+      <c r="O57" s="88"/>
+      <c r="P57" s="88"/>
+      <c r="Q57" s="88"/>
+      <c r="R57" s="88"/>
+      <c r="S57" s="91"/>
     </row>
     <row r="58" s="11" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A58" s="87">
+      <c r="A58" s="88">
         <v>30250003</v>
       </c>
-      <c r="B58" s="88">
+      <c r="B58" s="89">
         <v>102500</v>
       </c>
-      <c r="C58" s="88" t="s">
+      <c r="C58" s="89" t="s">
         <v>118</v>
       </c>
-      <c r="D58" s="87">
+      <c r="D58" s="88">
         <v>302503</v>
       </c>
-      <c r="E58" s="87" t="s">
+      <c r="E58" s="88" t="s">
         <v>123</v>
       </c>
-      <c r="F58" s="87" t="s">
+      <c r="F58" s="88" t="s">
         <v>124</v>
       </c>
-      <c r="G58" s="87">
+      <c r="G58" s="88">
         <v>2025001</v>
       </c>
-      <c r="H58" s="87" t="s">
+      <c r="H58" s="88" t="s">
         <v>61</v>
       </c>
-      <c r="I58" s="87" t="s">
+      <c r="I58" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="J58" s="87"/>
-      <c r="K58" s="89" t="s">
+      <c r="J58" s="88"/>
+      <c r="K58" s="90" t="s">
         <v>119</v>
       </c>
-      <c r="L58" s="87" t="s">
+      <c r="L58" s="88" t="s">
         <v>120</v>
       </c>
-      <c r="M58" s="87"/>
-      <c r="N58" s="87"/>
-      <c r="O58" s="87"/>
-      <c r="P58" s="87"/>
-      <c r="Q58" s="87"/>
-      <c r="R58" s="87"/>
-      <c r="S58" s="90"/>
+      <c r="M58" s="88"/>
+      <c r="N58" s="88"/>
+      <c r="O58" s="88"/>
+      <c r="P58" s="88"/>
+      <c r="Q58" s="88"/>
+      <c r="R58" s="88"/>
+      <c r="S58" s="91"/>
     </row>
     <row r="59" s="12" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A59" s="91">
+      <c r="A59" s="92">
         <v>30230001</v>
       </c>
-      <c r="B59" s="92">
+      <c r="B59" s="93">
         <v>102300</v>
       </c>
-      <c r="C59" s="92" t="s">
+      <c r="C59" s="93" t="s">
         <v>125</v>
       </c>
-      <c r="D59" s="91">
+      <c r="D59" s="92">
         <v>302301</v>
       </c>
-      <c r="E59" s="91" t="s">
+      <c r="E59" s="92" t="s">
         <v>108</v>
       </c>
-      <c r="F59" s="91" t="s">
+      <c r="F59" s="92" t="s">
         <v>109</v>
       </c>
-      <c r="G59" s="91">
+      <c r="G59" s="92">
         <v>2023001</v>
       </c>
-      <c r="H59" s="91" t="s">
+      <c r="H59" s="92" t="s">
         <v>61</v>
       </c>
-      <c r="I59" s="91" t="s">
+      <c r="I59" s="92" t="s">
         <v>81</v>
       </c>
-      <c r="J59" s="91"/>
-      <c r="K59" s="93" t="s">
+      <c r="J59" s="92"/>
+      <c r="K59" s="94" t="s">
         <v>126</v>
       </c>
-      <c r="L59" s="91" t="s">
+      <c r="L59" s="92" t="s">
         <v>127</v>
       </c>
-      <c r="M59" s="91"/>
-      <c r="N59" s="91"/>
-      <c r="O59" s="91"/>
-      <c r="P59" s="91"/>
-      <c r="Q59" s="91"/>
-      <c r="R59" s="91"/>
-      <c r="S59" s="94"/>
+      <c r="M59" s="92"/>
+      <c r="N59" s="92"/>
+      <c r="O59" s="92"/>
+      <c r="P59" s="92"/>
+      <c r="Q59" s="92"/>
+      <c r="R59" s="92"/>
+      <c r="S59" s="95"/>
     </row>
     <row r="60" s="12" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A60" s="91">
+      <c r="A60" s="92">
         <v>30230002</v>
       </c>
-      <c r="B60" s="92">
+      <c r="B60" s="93">
         <v>102300</v>
       </c>
-      <c r="C60" s="92" t="s">
+      <c r="C60" s="93" t="s">
         <v>125</v>
       </c>
-      <c r="D60" s="91">
+      <c r="D60" s="92">
         <v>302302</v>
       </c>
-      <c r="E60" s="91" t="s">
+      <c r="E60" s="92" t="s">
         <v>128</v>
       </c>
-      <c r="F60" s="91" t="s">
+      <c r="F60" s="92" t="s">
         <v>80</v>
       </c>
-      <c r="G60" s="91">
+      <c r="G60" s="92">
         <v>2023001</v>
       </c>
-      <c r="H60" s="91" t="s">
+      <c r="H60" s="92" t="s">
         <v>61</v>
       </c>
-      <c r="I60" s="91" t="s">
+      <c r="I60" s="92" t="s">
         <v>81</v>
       </c>
-      <c r="J60" s="91"/>
-      <c r="K60" s="93" t="s">
+      <c r="J60" s="92"/>
+      <c r="K60" s="94" t="s">
         <v>126</v>
       </c>
-      <c r="L60" s="91" t="s">
+      <c r="L60" s="92" t="s">
         <v>127</v>
       </c>
-      <c r="M60" s="91"/>
-      <c r="N60" s="91"/>
-      <c r="O60" s="91"/>
-      <c r="P60" s="91"/>
-      <c r="Q60" s="91"/>
-      <c r="R60" s="91"/>
-      <c r="S60" s="94"/>
+      <c r="M60" s="92"/>
+      <c r="N60" s="92"/>
+      <c r="O60" s="92"/>
+      <c r="P60" s="92"/>
+      <c r="Q60" s="92"/>
+      <c r="R60" s="92"/>
+      <c r="S60" s="95"/>
     </row>
     <row r="61" s="12" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A61" s="91">
+      <c r="A61" s="92">
         <v>30230003</v>
       </c>
-      <c r="B61" s="92">
+      <c r="B61" s="93">
         <v>102300</v>
       </c>
-      <c r="C61" s="92" t="s">
+      <c r="C61" s="93" t="s">
         <v>125</v>
       </c>
-      <c r="D61" s="91">
+      <c r="D61" s="92">
         <v>302303</v>
       </c>
-      <c r="E61" s="91" t="s">
+      <c r="E61" s="92" t="s">
         <v>129</v>
       </c>
-      <c r="F61" s="91" t="s">
+      <c r="F61" s="92" t="s">
         <v>84</v>
       </c>
-      <c r="G61" s="91">
+      <c r="G61" s="92">
         <v>2023001</v>
       </c>
-      <c r="H61" s="91" t="s">
+      <c r="H61" s="92" t="s">
         <v>61</v>
       </c>
-      <c r="I61" s="91" t="s">
+      <c r="I61" s="92" t="s">
         <v>81</v>
       </c>
-      <c r="J61" s="91"/>
-      <c r="K61" s="93" t="s">
+      <c r="J61" s="92"/>
+      <c r="K61" s="94" t="s">
         <v>126</v>
       </c>
-      <c r="L61" s="91" t="s">
+      <c r="L61" s="92" t="s">
         <v>127</v>
       </c>
-      <c r="M61" s="91"/>
-      <c r="N61" s="91"/>
-      <c r="O61" s="91"/>
-      <c r="P61" s="91"/>
-      <c r="Q61" s="91"/>
-      <c r="R61" s="91"/>
-      <c r="S61" s="94"/>
+      <c r="M61" s="92"/>
+      <c r="N61" s="92"/>
+      <c r="O61" s="92"/>
+      <c r="P61" s="92"/>
+      <c r="Q61" s="92"/>
+      <c r="R61" s="92"/>
+      <c r="S61" s="95"/>
     </row>
     <row r="62" s="13" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A62" s="95">
+      <c r="A62" s="96">
         <v>30350001</v>
       </c>
-      <c r="B62" s="96">
+      <c r="B62" s="97">
         <v>103500</v>
       </c>
-      <c r="C62" s="96" t="s">
+      <c r="C62" s="97" t="s">
         <v>130</v>
       </c>
-      <c r="D62" s="95">
+      <c r="D62" s="96">
         <v>303501</v>
       </c>
-      <c r="E62" s="95" t="s">
+      <c r="E62" s="96" t="s">
         <v>131</v>
       </c>
-      <c r="F62" s="95" t="s">
+      <c r="F62" s="96" t="s">
         <v>60</v>
       </c>
-      <c r="G62" s="95">
+      <c r="G62" s="96">
         <v>2035002</v>
       </c>
-      <c r="H62" s="95" t="s">
+      <c r="H62" s="96" t="s">
         <v>61</v>
       </c>
-      <c r="I62" s="95" t="s">
+      <c r="I62" s="96" t="s">
         <v>132</v>
       </c>
-      <c r="J62" s="95"/>
-      <c r="K62" s="97" t="s">
+      <c r="J62" s="96"/>
+      <c r="K62" s="98" t="s">
         <v>133</v>
       </c>
-      <c r="L62" s="95" t="s">
+      <c r="L62" s="96" t="s">
         <v>134</v>
       </c>
-      <c r="M62" s="95"/>
-      <c r="N62" s="95"/>
-      <c r="O62" s="95"/>
-      <c r="P62" s="95"/>
-      <c r="Q62" s="95"/>
-      <c r="R62" s="95"/>
-      <c r="S62" s="98"/>
+      <c r="M62" s="96"/>
+      <c r="N62" s="96"/>
+      <c r="O62" s="96"/>
+      <c r="P62" s="96"/>
+      <c r="Q62" s="96"/>
+      <c r="R62" s="96"/>
+      <c r="S62" s="99"/>
     </row>
     <row r="63" s="13" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A63" s="95">
+      <c r="A63" s="96">
         <v>30350002</v>
       </c>
-      <c r="B63" s="96">
+      <c r="B63" s="97">
         <v>103500</v>
       </c>
-      <c r="C63" s="96" t="s">
+      <c r="C63" s="97" t="s">
         <v>130</v>
       </c>
-      <c r="D63" s="95">
+      <c r="D63" s="96">
         <v>303502</v>
       </c>
-      <c r="E63" s="95" t="s">
+      <c r="E63" s="96" t="s">
         <v>135</v>
       </c>
-      <c r="F63" s="95" t="s">
+      <c r="F63" s="96" t="s">
         <v>34</v>
       </c>
-      <c r="G63" s="95"/>
-      <c r="H63" s="95"/>
-      <c r="I63" s="95"/>
-      <c r="J63" s="95"/>
-      <c r="K63" s="97"/>
-      <c r="L63" s="95"/>
-      <c r="M63" s="95" t="s">
+      <c r="G63" s="96"/>
+      <c r="H63" s="96"/>
+      <c r="I63" s="96"/>
+      <c r="J63" s="96"/>
+      <c r="K63" s="98"/>
+      <c r="L63" s="96"/>
+      <c r="M63" s="96" t="s">
         <v>54</v>
       </c>
-      <c r="N63" s="95"/>
-      <c r="O63" s="95" t="s">
+      <c r="N63" s="96"/>
+      <c r="O63" s="96" t="s">
         <v>136</v>
       </c>
-      <c r="P63" s="95"/>
-      <c r="Q63" s="95"/>
-      <c r="R63" s="95"/>
-      <c r="S63" s="98"/>
+      <c r="P63" s="96"/>
+      <c r="Q63" s="96"/>
+      <c r="R63" s="96"/>
+      <c r="S63" s="99"/>
     </row>
     <row r="64" s="13" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A64" s="95">
+      <c r="A64" s="96">
         <v>30350101</v>
       </c>
-      <c r="B64" s="96">
+      <c r="B64" s="97">
         <v>103501</v>
       </c>
-      <c r="C64" s="96" t="s">
+      <c r="C64" s="97" t="s">
         <v>137</v>
       </c>
-      <c r="D64" s="95">
+      <c r="D64" s="96">
         <v>303503</v>
       </c>
-      <c r="E64" s="95" t="s">
+      <c r="E64" s="96" t="s">
         <v>131</v>
       </c>
-      <c r="F64" s="95" t="s">
+      <c r="F64" s="96" t="s">
         <v>60</v>
       </c>
-      <c r="G64" s="95">
+      <c r="G64" s="96">
         <v>2035012</v>
       </c>
-      <c r="H64" s="95" t="s">
+      <c r="H64" s="96" t="s">
         <v>61</v>
       </c>
-      <c r="I64" s="95" t="s">
+      <c r="I64" s="96" t="s">
         <v>132</v>
       </c>
-      <c r="J64" s="95"/>
-      <c r="K64" s="97" t="s">
+      <c r="J64" s="96"/>
+      <c r="K64" s="98" t="s">
         <v>138</v>
       </c>
-      <c r="L64" s="95" t="s">
+      <c r="L64" s="96" t="s">
         <v>134</v>
       </c>
-      <c r="M64" s="95"/>
-      <c r="N64" s="95"/>
-      <c r="O64" s="95"/>
-      <c r="P64" s="95"/>
-      <c r="Q64" s="95"/>
-      <c r="R64" s="95"/>
-      <c r="S64" s="98"/>
+      <c r="M64" s="96"/>
+      <c r="N64" s="96"/>
+      <c r="O64" s="96"/>
+      <c r="P64" s="96"/>
+      <c r="Q64" s="96"/>
+      <c r="R64" s="96"/>
+      <c r="S64" s="99"/>
     </row>
     <row r="65" s="13" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A65" s="95">
+      <c r="A65" s="96">
         <v>30350102</v>
       </c>
-      <c r="B65" s="96">
+      <c r="B65" s="97">
         <v>103501</v>
       </c>
-      <c r="C65" s="96" t="s">
+      <c r="C65" s="97" t="s">
         <v>137</v>
       </c>
-      <c r="D65" s="95">
+      <c r="D65" s="96">
         <v>303504</v>
       </c>
-      <c r="E65" s="95" t="s">
+      <c r="E65" s="96" t="s">
         <v>135</v>
       </c>
-      <c r="F65" s="95" t="s">
+      <c r="F65" s="96" t="s">
         <v>34</v>
       </c>
-      <c r="G65" s="95"/>
-      <c r="H65" s="95"/>
-      <c r="I65" s="95"/>
-      <c r="J65" s="95"/>
-      <c r="K65" s="97"/>
-      <c r="L65" s="95"/>
-      <c r="M65" s="95" t="s">
+      <c r="G65" s="96"/>
+      <c r="H65" s="96"/>
+      <c r="I65" s="96"/>
+      <c r="J65" s="96"/>
+      <c r="K65" s="98"/>
+      <c r="L65" s="96"/>
+      <c r="M65" s="96" t="s">
         <v>54</v>
       </c>
-      <c r="N65" s="95"/>
-      <c r="O65" s="95" t="s">
+      <c r="N65" s="96"/>
+      <c r="O65" s="96" t="s">
         <v>136</v>
       </c>
-      <c r="P65" s="95"/>
-      <c r="Q65" s="95"/>
-      <c r="R65" s="95"/>
-      <c r="S65" s="98"/>
+      <c r="P65" s="96"/>
+      <c r="Q65" s="96"/>
+      <c r="R65" s="96"/>
+      <c r="S65" s="99"/>
     </row>
     <row r="66" s="14" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A66" s="99">
+      <c r="A66" s="100">
         <v>30360001</v>
       </c>
-      <c r="B66" s="100">
+      <c r="B66" s="101">
         <v>103600</v>
       </c>
-      <c r="C66" s="100" t="s">
+      <c r="C66" s="101" t="s">
         <v>139</v>
       </c>
-      <c r="D66" s="99">
+      <c r="D66" s="100">
         <v>303601</v>
       </c>
-      <c r="E66" s="99" t="s">
+      <c r="E66" s="100" t="s">
         <v>140</v>
       </c>
-      <c r="F66" s="99" t="s">
+      <c r="F66" s="100" t="s">
         <v>109</v>
       </c>
-      <c r="G66" s="99">
+      <c r="G66" s="100">
         <v>2036002</v>
       </c>
-      <c r="H66" s="99" t="s">
+      <c r="H66" s="100" t="s">
         <v>61</v>
       </c>
-      <c r="I66" s="99" t="s">
+      <c r="I66" s="100" t="s">
         <v>140</v>
       </c>
-      <c r="J66" s="99"/>
-      <c r="K66" s="101">
+      <c r="J66" s="100"/>
+      <c r="K66" s="102">
         <v>10360005</v>
       </c>
-      <c r="L66" s="99" t="s">
+      <c r="L66" s="100" t="s">
         <v>141</v>
       </c>
-      <c r="M66" s="99"/>
-      <c r="N66" s="99"/>
-      <c r="O66" s="99"/>
-      <c r="P66" s="99"/>
-      <c r="Q66" s="99"/>
-      <c r="R66" s="99"/>
-      <c r="S66" s="102"/>
+      <c r="M66" s="100"/>
+      <c r="N66" s="100"/>
+      <c r="O66" s="100"/>
+      <c r="P66" s="100"/>
+      <c r="Q66" s="100"/>
+      <c r="R66" s="100"/>
+      <c r="S66" s="103"/>
     </row>
     <row r="67" s="15" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A67" s="103">
+      <c r="A67" s="104">
         <v>30280001</v>
       </c>
-      <c r="B67" s="104">
+      <c r="B67" s="105">
         <v>102800</v>
       </c>
-      <c r="C67" s="104" t="s">
+      <c r="C67" s="105" t="s">
         <v>142</v>
       </c>
-      <c r="D67" s="103">
+      <c r="D67" s="104">
         <v>302801</v>
       </c>
-      <c r="E67" s="103" t="s">
+      <c r="E67" s="104" t="s">
         <v>108</v>
       </c>
-      <c r="F67" s="103" t="s">
+      <c r="F67" s="104" t="s">
         <v>109</v>
       </c>
-      <c r="G67" s="103">
+      <c r="G67" s="104">
         <v>2028001</v>
       </c>
-      <c r="H67" s="103" t="s">
+      <c r="H67" s="104" t="s">
         <v>61</v>
       </c>
-      <c r="I67" s="103" t="s">
+      <c r="I67" s="104" t="s">
         <v>81</v>
       </c>
-      <c r="J67" s="103"/>
-      <c r="K67" s="105" t="s">
+      <c r="J67" s="104"/>
+      <c r="K67" s="106" t="s">
         <v>143</v>
       </c>
-      <c r="L67" s="103" t="s">
+      <c r="L67" s="104" t="s">
         <v>144</v>
       </c>
-      <c r="M67" s="103"/>
-      <c r="N67" s="103"/>
-      <c r="O67" s="103"/>
-      <c r="P67" s="103"/>
-      <c r="Q67" s="103"/>
-      <c r="R67" s="103"/>
-      <c r="S67" s="106"/>
+      <c r="M67" s="104"/>
+      <c r="N67" s="104"/>
+      <c r="O67" s="104"/>
+      <c r="P67" s="104"/>
+      <c r="Q67" s="104"/>
+      <c r="R67" s="104"/>
+      <c r="S67" s="107"/>
     </row>
     <row r="68" s="15" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A68" s="103">
+      <c r="A68" s="104">
         <v>30280002</v>
       </c>
-      <c r="B68" s="104">
+      <c r="B68" s="105">
         <v>102800</v>
       </c>
-      <c r="C68" s="104" t="s">
+      <c r="C68" s="105" t="s">
         <v>142</v>
       </c>
-      <c r="D68" s="103">
+      <c r="D68" s="104">
         <v>302802</v>
       </c>
-      <c r="E68" s="103" t="s">
+      <c r="E68" s="104" t="s">
         <v>128</v>
       </c>
-      <c r="F68" s="103" t="s">
+      <c r="F68" s="104" t="s">
         <v>80</v>
       </c>
-      <c r="G68" s="103">
+      <c r="G68" s="104">
         <v>2028001</v>
       </c>
-      <c r="H68" s="103" t="s">
+      <c r="H68" s="104" t="s">
         <v>61</v>
       </c>
-      <c r="I68" s="103" t="s">
+      <c r="I68" s="104" t="s">
         <v>81</v>
       </c>
-      <c r="J68" s="103"/>
-      <c r="K68" s="105" t="s">
+      <c r="J68" s="104"/>
+      <c r="K68" s="106" t="s">
         <v>143</v>
       </c>
-      <c r="L68" s="103" t="s">
+      <c r="L68" s="104" t="s">
         <v>144</v>
       </c>
-      <c r="M68" s="103"/>
-      <c r="N68" s="103"/>
-      <c r="O68" s="103"/>
-      <c r="P68" s="103"/>
-      <c r="Q68" s="103"/>
-      <c r="R68" s="103"/>
-      <c r="S68" s="106"/>
+      <c r="M68" s="104"/>
+      <c r="N68" s="104"/>
+      <c r="O68" s="104"/>
+      <c r="P68" s="104"/>
+      <c r="Q68" s="104"/>
+      <c r="R68" s="104"/>
+      <c r="S68" s="107"/>
     </row>
     <row r="69" s="15" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A69" s="103">
+      <c r="A69" s="104">
         <v>30280003</v>
       </c>
-      <c r="B69" s="104">
+      <c r="B69" s="105">
         <v>102800</v>
       </c>
-      <c r="C69" s="104" t="s">
+      <c r="C69" s="105" t="s">
         <v>142</v>
       </c>
-      <c r="D69" s="103">
+      <c r="D69" s="104">
         <v>302803</v>
       </c>
-      <c r="E69" s="103" t="s">
+      <c r="E69" s="104" t="s">
         <v>129</v>
       </c>
-      <c r="F69" s="103" t="s">
+      <c r="F69" s="104" t="s">
         <v>84</v>
       </c>
-      <c r="G69" s="103">
+      <c r="G69" s="104">
         <v>2028001</v>
       </c>
-      <c r="H69" s="103" t="s">
+      <c r="H69" s="104" t="s">
         <v>61</v>
       </c>
-      <c r="I69" s="103" t="s">
+      <c r="I69" s="104" t="s">
         <v>81</v>
       </c>
-      <c r="J69" s="103"/>
-      <c r="K69" s="105" t="s">
+      <c r="J69" s="104"/>
+      <c r="K69" s="106" t="s">
         <v>143</v>
       </c>
-      <c r="L69" s="103" t="s">
+      <c r="L69" s="104" t="s">
         <v>144</v>
       </c>
-      <c r="M69" s="103"/>
-      <c r="N69" s="103"/>
-      <c r="O69" s="103"/>
-      <c r="P69" s="103"/>
-      <c r="Q69" s="103"/>
-      <c r="R69" s="103"/>
-      <c r="S69" s="106"/>
+      <c r="M69" s="104"/>
+      <c r="N69" s="104"/>
+      <c r="O69" s="104"/>
+      <c r="P69" s="104"/>
+      <c r="Q69" s="104"/>
+      <c r="R69" s="104"/>
+      <c r="S69" s="107"/>
     </row>
     <row r="70" s="16" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A70" s="107">
+      <c r="A70" s="108">
         <v>30200003</v>
       </c>
-      <c r="B70" s="108">
+      <c r="B70" s="109">
         <v>102000</v>
       </c>
-      <c r="C70" s="108" t="s">
+      <c r="C70" s="109" t="s">
         <v>145</v>
       </c>
-      <c r="D70" s="107">
+      <c r="D70" s="108">
         <v>302003</v>
       </c>
-      <c r="E70" s="107" t="s">
+      <c r="E70" s="108" t="s">
         <v>146</v>
       </c>
-      <c r="F70" s="107" t="s">
+      <c r="F70" s="108" t="s">
         <v>34</v>
       </c>
-      <c r="G70" s="107">
+      <c r="G70" s="108">
         <v>2020001</v>
       </c>
-      <c r="H70" s="107" t="s">
+      <c r="H70" s="108" t="s">
         <v>61</v>
       </c>
-      <c r="I70" s="107" t="s">
+      <c r="I70" s="108" t="s">
         <v>147</v>
       </c>
-      <c r="J70" s="107"/>
-      <c r="K70" s="109">
+      <c r="J70" s="108"/>
+      <c r="K70" s="110">
         <v>10200011</v>
       </c>
       <c r="L70" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="M70" s="107"/>
-      <c r="N70" s="107"/>
-      <c r="O70" s="107"/>
-      <c r="P70" s="107"/>
-      <c r="Q70" s="107"/>
-      <c r="R70" s="107"/>
-      <c r="S70" s="110"/>
+      <c r="M70" s="108"/>
+      <c r="N70" s="108"/>
+      <c r="O70" s="108"/>
+      <c r="P70" s="108"/>
+      <c r="Q70" s="108" t="s">
+        <v>149</v>
+      </c>
+      <c r="R70" s="39" t="s">
+        <v>40</v>
+      </c>
+      <c r="S70" s="111"/>
     </row>
     <row r="71" s="16" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A71" s="107">
+      <c r="A71" s="108">
         <v>30200004</v>
       </c>
-      <c r="B71" s="108">
+      <c r="B71" s="109">
         <v>102000</v>
       </c>
-      <c r="C71" s="108" t="s">
+      <c r="C71" s="109" t="s">
         <v>145</v>
       </c>
-      <c r="D71" s="107">
+      <c r="D71" s="108">
         <v>302004</v>
       </c>
-      <c r="E71" s="107" t="s">
+      <c r="E71" s="108" t="s">
+        <v>150</v>
+      </c>
+      <c r="F71" s="108" t="s">
+        <v>34</v>
+      </c>
+      <c r="G71" s="108">
+        <v>2020001</v>
+      </c>
+      <c r="H71" s="108" t="s">
+        <v>61</v>
+      </c>
+      <c r="I71" s="108" t="s">
+        <v>147</v>
+      </c>
+      <c r="J71" s="108"/>
+      <c r="K71" s="110">
+        <v>10200012</v>
+      </c>
+      <c r="L71" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="M71" s="108"/>
+      <c r="N71" s="108"/>
+      <c r="O71" s="108"/>
+      <c r="P71" s="108"/>
+      <c r="Q71" s="108" t="s">
         <v>149</v>
       </c>
-      <c r="F71" s="107" t="s">
+      <c r="R71" s="39" t="s">
+        <v>40</v>
+      </c>
+      <c r="S71" s="111"/>
+    </row>
+    <row r="72" s="16" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A72" s="108">
+        <v>30200005</v>
+      </c>
+      <c r="B72" s="109">
+        <v>102000</v>
+      </c>
+      <c r="C72" s="109" t="s">
+        <v>145</v>
+      </c>
+      <c r="D72" s="108">
+        <v>302005</v>
+      </c>
+      <c r="E72" s="108" t="s">
+        <v>152</v>
+      </c>
+      <c r="F72" s="108" t="s">
         <v>34</v>
       </c>
-      <c r="G71" s="107">
+      <c r="G72" s="108">
         <v>2020001</v>
       </c>
-      <c r="H71" s="107" t="s">
+      <c r="H72" s="108" t="s">
         <v>61</v>
       </c>
-      <c r="I71" s="107" t="s">
+      <c r="I72" s="108" t="s">
         <v>147</v>
       </c>
-      <c r="J71" s="107"/>
-      <c r="K71" s="109">
-        <v>10200012</v>
-      </c>
-      <c r="L71" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="M71" s="107"/>
-      <c r="N71" s="107"/>
-      <c r="O71" s="107"/>
-      <c r="P71" s="107"/>
-      <c r="Q71" s="107"/>
-      <c r="R71" s="107"/>
-      <c r="S71" s="110"/>
-    </row>
-    <row r="72" s="16" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A72" s="107">
-        <v>30200005</v>
-      </c>
-      <c r="B72" s="108">
+      <c r="J72" s="108"/>
+      <c r="K72" s="110">
+        <v>10200013</v>
+      </c>
+      <c r="L72" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="M72" s="108"/>
+      <c r="N72" s="108"/>
+      <c r="O72" s="108"/>
+      <c r="P72" s="108"/>
+      <c r="Q72" s="108" t="s">
+        <v>149</v>
+      </c>
+      <c r="R72" s="39" t="s">
+        <v>40</v>
+      </c>
+      <c r="S72" s="111"/>
+    </row>
+    <row r="73" s="16" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A73" s="108">
+        <v>30200006</v>
+      </c>
+      <c r="B73" s="109">
         <v>102000</v>
       </c>
-      <c r="C72" s="108" t="s">
+      <c r="C73" s="109" t="s">
         <v>145</v>
       </c>
-      <c r="D72" s="107">
-        <v>302005</v>
-      </c>
-      <c r="E72" s="107" t="s">
-        <v>151</v>
-      </c>
-      <c r="F72" s="107" t="s">
+      <c r="D73" s="108">
+        <v>302006</v>
+      </c>
+      <c r="E73" s="108" t="s">
+        <v>154</v>
+      </c>
+      <c r="F73" s="108" t="s">
         <v>34</v>
       </c>
-      <c r="G72" s="107">
+      <c r="G73" s="108">
         <v>2020001</v>
       </c>
-      <c r="H72" s="107" t="s">
+      <c r="H73" s="108" t="s">
         <v>61</v>
       </c>
-      <c r="I72" s="107" t="s">
+      <c r="I73" s="108" t="s">
         <v>147</v>
       </c>
-      <c r="J72" s="107"/>
-      <c r="K72" s="109">
-        <v>10200013</v>
-      </c>
-      <c r="L72" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="M72" s="107"/>
-      <c r="N72" s="107"/>
-      <c r="O72" s="107"/>
-      <c r="P72" s="107"/>
-      <c r="Q72" s="107"/>
-      <c r="R72" s="107"/>
-      <c r="S72" s="110"/>
-    </row>
-    <row r="73" s="16" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A73" s="107">
-        <v>30200006</v>
-      </c>
-      <c r="B73" s="108">
+      <c r="J73" s="108"/>
+      <c r="K73" s="110">
+        <v>10200014</v>
+      </c>
+      <c r="L73" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="M73" s="108"/>
+      <c r="N73" s="108"/>
+      <c r="O73" s="108"/>
+      <c r="P73" s="108"/>
+      <c r="Q73" s="108" t="s">
+        <v>149</v>
+      </c>
+      <c r="R73" s="39" t="s">
+        <v>40</v>
+      </c>
+      <c r="S73" s="111"/>
+    </row>
+    <row r="74" s="16" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A74" s="108">
+        <v>30200007</v>
+      </c>
+      <c r="B74" s="109">
         <v>102000</v>
       </c>
-      <c r="C73" s="108" t="s">
+      <c r="C74" s="109" t="s">
         <v>145</v>
       </c>
-      <c r="D73" s="107">
-        <v>302006</v>
-      </c>
-      <c r="E73" s="107" t="s">
-        <v>153</v>
-      </c>
-      <c r="F73" s="107" t="s">
+      <c r="D74" s="108">
+        <v>302007</v>
+      </c>
+      <c r="E74" s="108" t="s">
+        <v>156</v>
+      </c>
+      <c r="F74" s="108" t="s">
+        <v>54</v>
+      </c>
+      <c r="G74" s="108">
+        <v>2020001</v>
+      </c>
+      <c r="H74" s="108" t="s">
+        <v>61</v>
+      </c>
+      <c r="I74" s="108"/>
+      <c r="J74" s="108"/>
+      <c r="K74" s="110"/>
+      <c r="L74" s="5"/>
+      <c r="M74" s="108"/>
+      <c r="N74" s="108"/>
+      <c r="O74" s="108"/>
+      <c r="P74" s="108"/>
+      <c r="Q74" s="108" t="s">
+        <v>149</v>
+      </c>
+      <c r="R74" s="108" t="s">
+        <v>40</v>
+      </c>
+      <c r="S74" s="111"/>
+    </row>
+    <row r="75" s="16" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A75" s="108">
+        <v>30200008</v>
+      </c>
+      <c r="B75" s="109">
+        <v>102000</v>
+      </c>
+      <c r="C75" s="109" t="s">
+        <v>145</v>
+      </c>
+      <c r="D75" s="108">
+        <v>302008</v>
+      </c>
+      <c r="E75" s="108" t="s">
+        <v>157</v>
+      </c>
+      <c r="F75" s="108" t="s">
         <v>34</v>
       </c>
-      <c r="G73" s="107">
+      <c r="G75" s="108">
         <v>2020001</v>
       </c>
-      <c r="H73" s="107" t="s">
+      <c r="H75" s="108" t="s">
         <v>61</v>
       </c>
-      <c r="I73" s="107" t="s">
-        <v>147</v>
-      </c>
-      <c r="J73" s="107"/>
-      <c r="K73" s="109">
-        <v>10200014</v>
-      </c>
-      <c r="L73" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="M73" s="107"/>
-      <c r="N73" s="107"/>
-      <c r="O73" s="107"/>
-      <c r="P73" s="107"/>
-      <c r="Q73" s="107"/>
-      <c r="R73" s="107"/>
-      <c r="S73" s="110"/>
-    </row>
-    <row r="74" s="16" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A74" s="107">
-        <v>30200007</v>
-      </c>
-      <c r="B74" s="108">
+      <c r="I75" s="108"/>
+      <c r="J75" s="108"/>
+      <c r="K75" s="110"/>
+      <c r="L75" s="5"/>
+      <c r="M75" s="108"/>
+      <c r="N75" s="108"/>
+      <c r="O75" s="108"/>
+      <c r="P75" s="108"/>
+      <c r="Q75" s="108" t="s">
+        <v>149</v>
+      </c>
+      <c r="R75" s="108" t="s">
+        <v>40</v>
+      </c>
+      <c r="S75" s="111"/>
+    </row>
+    <row r="76" s="17" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A76" s="112">
+        <v>30200009</v>
+      </c>
+      <c r="B76" s="113">
         <v>102000</v>
       </c>
-      <c r="C74" s="108" t="s">
+      <c r="C76" s="113" t="s">
         <v>145</v>
       </c>
-      <c r="D74" s="107">
-        <v>302007</v>
-      </c>
-      <c r="E74" s="107" t="s">
-        <v>155</v>
-      </c>
-      <c r="F74" s="107" t="s">
+      <c r="D76" s="112">
+        <v>302009</v>
+      </c>
+      <c r="E76" s="112" t="s">
+        <v>158</v>
+      </c>
+      <c r="F76" s="112" t="s">
+        <v>109</v>
+      </c>
+      <c r="G76" s="112">
+        <v>2020002</v>
+      </c>
+      <c r="H76" s="112" t="s">
+        <v>61</v>
+      </c>
+      <c r="I76" s="112" t="s">
+        <v>81</v>
+      </c>
+      <c r="J76" s="112"/>
+      <c r="K76" s="114" t="s">
+        <v>159</v>
+      </c>
+      <c r="L76" s="112" t="s">
+        <v>160</v>
+      </c>
+      <c r="M76" s="112"/>
+      <c r="N76" s="112"/>
+      <c r="O76" s="112"/>
+      <c r="P76" s="112"/>
+      <c r="Q76" s="38"/>
+      <c r="R76" s="39"/>
+      <c r="S76" s="115"/>
+    </row>
+    <row r="77" s="17" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A77" s="112">
+        <v>30200010</v>
+      </c>
+      <c r="B77" s="113">
+        <v>102000</v>
+      </c>
+      <c r="C77" s="113" t="s">
+        <v>145</v>
+      </c>
+      <c r="D77" s="112">
+        <v>302010</v>
+      </c>
+      <c r="E77" s="112" t="s">
+        <v>161</v>
+      </c>
+      <c r="F77" s="112" t="s">
         <v>54</v>
       </c>
-      <c r="G74" s="107">
-        <v>2020001</v>
-      </c>
-      <c r="H74" s="107" t="s">
+      <c r="G77" s="112">
+        <v>2020002</v>
+      </c>
+      <c r="H77" s="112" t="s">
         <v>61</v>
       </c>
-      <c r="I74" s="107"/>
-      <c r="J74" s="107"/>
-      <c r="K74" s="109"/>
-      <c r="L74" s="5"/>
-      <c r="M74" s="107"/>
-      <c r="N74" s="107"/>
-      <c r="O74" s="107"/>
-      <c r="P74" s="107"/>
-      <c r="Q74" s="107" t="s">
-        <v>156</v>
-      </c>
-      <c r="R74" s="107" t="s">
+      <c r="I77" s="112"/>
+      <c r="J77" s="112"/>
+      <c r="K77" s="116">
+        <v>10200120</v>
+      </c>
+      <c r="L77" s="117" t="s">
+        <v>162</v>
+      </c>
+      <c r="M77" s="112"/>
+      <c r="N77" s="112"/>
+      <c r="O77" s="112"/>
+      <c r="P77" s="112"/>
+      <c r="Q77" s="38" t="s">
+        <v>163</v>
+      </c>
+      <c r="R77" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="S74" s="110"/>
-    </row>
-    <row r="75" s="16" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A75" s="107">
-        <v>30200008</v>
-      </c>
-      <c r="B75" s="108">
+      <c r="S77" s="115"/>
+    </row>
+    <row r="78" s="17" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A78" s="112">
+        <v>30200011</v>
+      </c>
+      <c r="B78" s="113">
         <v>102000</v>
       </c>
-      <c r="C75" s="108" t="s">
+      <c r="C78" s="113" t="s">
         <v>145</v>
       </c>
-      <c r="D75" s="107">
-        <v>302008</v>
-      </c>
-      <c r="E75" s="107" t="s">
-        <v>157</v>
-      </c>
-      <c r="F75" s="107" t="s">
+      <c r="D78" s="112">
+        <v>302011</v>
+      </c>
+      <c r="E78" s="112" t="s">
+        <v>164</v>
+      </c>
+      <c r="F78" s="112" t="s">
+        <v>54</v>
+      </c>
+      <c r="G78" s="112">
+        <v>2020002</v>
+      </c>
+      <c r="H78" s="112" t="s">
+        <v>61</v>
+      </c>
+      <c r="I78" s="112"/>
+      <c r="J78" s="112"/>
+      <c r="K78" s="116">
+        <v>10200220</v>
+      </c>
+      <c r="L78" s="117" t="s">
+        <v>165</v>
+      </c>
+      <c r="M78" s="112"/>
+      <c r="N78" s="112"/>
+      <c r="O78" s="112"/>
+      <c r="P78" s="112"/>
+      <c r="Q78" s="38" t="s">
+        <v>163</v>
+      </c>
+      <c r="R78" s="39" t="s">
+        <v>40</v>
+      </c>
+      <c r="S78" s="115"/>
+    </row>
+    <row r="79" s="17" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A79" s="112">
+        <v>30200012</v>
+      </c>
+      <c r="B79" s="113">
+        <v>102000</v>
+      </c>
+      <c r="C79" s="113" t="s">
+        <v>145</v>
+      </c>
+      <c r="D79" s="112">
+        <v>302012</v>
+      </c>
+      <c r="E79" s="112" t="s">
+        <v>166</v>
+      </c>
+      <c r="F79" s="112" t="s">
+        <v>54</v>
+      </c>
+      <c r="G79" s="112">
+        <v>2020002</v>
+      </c>
+      <c r="H79" s="112" t="s">
+        <v>61</v>
+      </c>
+      <c r="I79" s="112"/>
+      <c r="J79" s="112"/>
+      <c r="K79" s="116">
+        <v>10200320</v>
+      </c>
+      <c r="L79" s="117" t="s">
+        <v>167</v>
+      </c>
+      <c r="M79" s="112"/>
+      <c r="N79" s="112"/>
+      <c r="O79" s="112"/>
+      <c r="P79" s="112"/>
+      <c r="Q79" s="38" t="s">
+        <v>163</v>
+      </c>
+      <c r="R79" s="39" t="s">
+        <v>40</v>
+      </c>
+      <c r="S79" s="115"/>
+    </row>
+    <row r="80" s="17" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A80" s="112">
+        <v>30200013</v>
+      </c>
+      <c r="B80" s="113">
+        <v>102000</v>
+      </c>
+      <c r="C80" s="113" t="s">
+        <v>145</v>
+      </c>
+      <c r="D80" s="112">
+        <v>302013</v>
+      </c>
+      <c r="E80" s="112" t="s">
+        <v>168</v>
+      </c>
+      <c r="F80" s="112" t="s">
+        <v>54</v>
+      </c>
+      <c r="G80" s="112">
+        <v>2020002</v>
+      </c>
+      <c r="H80" s="112" t="s">
+        <v>61</v>
+      </c>
+      <c r="I80" s="112"/>
+      <c r="J80" s="112"/>
+      <c r="K80" s="116">
+        <v>10200420</v>
+      </c>
+      <c r="L80" s="117" t="s">
+        <v>169</v>
+      </c>
+      <c r="M80" s="112"/>
+      <c r="N80" s="112"/>
+      <c r="O80" s="112"/>
+      <c r="P80" s="112"/>
+      <c r="Q80" s="38" t="s">
+        <v>163</v>
+      </c>
+      <c r="R80" s="39" t="s">
+        <v>40</v>
+      </c>
+      <c r="S80" s="115"/>
+    </row>
+    <row r="81" s="11" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A81" s="88">
+        <v>30200014</v>
+      </c>
+      <c r="B81" s="89">
+        <v>102000</v>
+      </c>
+      <c r="C81" s="89" t="s">
+        <v>145</v>
+      </c>
+      <c r="D81" s="88">
+        <v>302014</v>
+      </c>
+      <c r="E81" s="88" t="s">
+        <v>170</v>
+      </c>
+      <c r="F81" s="88" t="s">
+        <v>109</v>
+      </c>
+      <c r="G81" s="88">
+        <v>2020003</v>
+      </c>
+      <c r="H81" s="88" t="s">
+        <v>61</v>
+      </c>
+      <c r="I81" s="88" t="s">
+        <v>81</v>
+      </c>
+      <c r="J81" s="88"/>
+      <c r="K81" s="90" t="s">
+        <v>171</v>
+      </c>
+      <c r="L81" s="88" t="s">
+        <v>172</v>
+      </c>
+      <c r="M81" s="88"/>
+      <c r="N81" s="88"/>
+      <c r="O81" s="88"/>
+      <c r="P81" s="88"/>
+      <c r="Q81" s="88"/>
+      <c r="R81" s="88"/>
+      <c r="S81" s="91"/>
+    </row>
+    <row r="82" s="11" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A82" s="88">
+        <v>30200015</v>
+      </c>
+      <c r="B82" s="89">
+        <v>102000</v>
+      </c>
+      <c r="C82" s="89" t="s">
+        <v>145</v>
+      </c>
+      <c r="D82" s="88">
+        <v>302015</v>
+      </c>
+      <c r="E82" s="88" t="s">
+        <v>173</v>
+      </c>
+      <c r="F82" s="88" t="s">
         <v>34</v>
       </c>
-      <c r="G75" s="107">
-        <v>2020001</v>
-      </c>
-      <c r="H75" s="107" t="s">
+      <c r="G82" s="88">
+        <v>2020003</v>
+      </c>
+      <c r="H82" s="88" t="s">
         <v>61</v>
       </c>
-      <c r="I75" s="107"/>
-      <c r="J75" s="107"/>
-      <c r="K75" s="109"/>
-      <c r="L75" s="5"/>
-      <c r="M75" s="107"/>
-      <c r="N75" s="107"/>
-      <c r="O75" s="107"/>
-      <c r="P75" s="107"/>
-      <c r="Q75" s="107" t="s">
-        <v>156</v>
-      </c>
-      <c r="R75" s="107" t="s">
+      <c r="I82" s="88"/>
+      <c r="J82" s="88"/>
+      <c r="K82" s="90">
+        <v>10200125</v>
+      </c>
+      <c r="L82" s="88" t="s">
+        <v>174</v>
+      </c>
+      <c r="M82" s="88"/>
+      <c r="N82" s="88"/>
+      <c r="O82" s="88"/>
+      <c r="P82" s="88"/>
+      <c r="Q82" s="118" t="s">
+        <v>163</v>
+      </c>
+      <c r="R82" s="119" t="s">
         <v>40</v>
       </c>
-      <c r="S75" s="110"/>
-    </row>
-    <row r="76" s="17" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A76" s="111">
-        <v>30200009</v>
-      </c>
-      <c r="B76" s="112">
+      <c r="S82" s="91"/>
+    </row>
+    <row r="83" s="11" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A83" s="88">
+        <v>30200016</v>
+      </c>
+      <c r="B83" s="89">
         <v>102000</v>
       </c>
-      <c r="C76" s="112" t="s">
+      <c r="C83" s="89" t="s">
         <v>145</v>
       </c>
-      <c r="D76" s="111">
-        <v>302009</v>
-      </c>
-      <c r="E76" s="111" t="s">
-        <v>158</v>
-      </c>
-      <c r="F76" s="111" t="s">
-        <v>109</v>
-      </c>
-      <c r="G76" s="111">
-        <v>2020002</v>
-      </c>
-      <c r="H76" s="111" t="s">
+      <c r="D83" s="88">
+        <v>302016</v>
+      </c>
+      <c r="E83" s="88" t="s">
+        <v>175</v>
+      </c>
+      <c r="F83" s="88" t="s">
+        <v>34</v>
+      </c>
+      <c r="G83" s="88">
+        <v>2020003</v>
+      </c>
+      <c r="H83" s="88" t="s">
         <v>61</v>
       </c>
-      <c r="I76" s="111" t="s">
+      <c r="I83" s="88"/>
+      <c r="J83" s="88"/>
+      <c r="K83" s="90">
+        <v>10200225</v>
+      </c>
+      <c r="L83" s="88" t="s">
+        <v>176</v>
+      </c>
+      <c r="M83" s="88"/>
+      <c r="N83" s="88"/>
+      <c r="O83" s="88"/>
+      <c r="P83" s="88"/>
+      <c r="Q83" s="118" t="s">
+        <v>163</v>
+      </c>
+      <c r="R83" s="119" t="s">
+        <v>40</v>
+      </c>
+      <c r="S83" s="91"/>
+    </row>
+    <row r="84" s="11" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A84" s="88">
+        <v>30200017</v>
+      </c>
+      <c r="B84" s="89">
+        <v>102000</v>
+      </c>
+      <c r="C84" s="89" t="s">
+        <v>145</v>
+      </c>
+      <c r="D84" s="88">
+        <v>302017</v>
+      </c>
+      <c r="E84" s="88" t="s">
+        <v>177</v>
+      </c>
+      <c r="F84" s="88" t="s">
+        <v>34</v>
+      </c>
+      <c r="G84" s="88">
+        <v>2020003</v>
+      </c>
+      <c r="H84" s="88" t="s">
+        <v>61</v>
+      </c>
+      <c r="I84" s="88"/>
+      <c r="J84" s="88"/>
+      <c r="K84" s="90">
+        <v>10200325</v>
+      </c>
+      <c r="L84" s="88" t="s">
+        <v>178</v>
+      </c>
+      <c r="M84" s="88"/>
+      <c r="N84" s="88"/>
+      <c r="O84" s="88"/>
+      <c r="P84" s="88"/>
+      <c r="Q84" s="118" t="s">
+        <v>163</v>
+      </c>
+      <c r="R84" s="119" t="s">
+        <v>40</v>
+      </c>
+      <c r="S84" s="91"/>
+    </row>
+    <row r="85" s="11" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A85" s="88">
+        <v>30200018</v>
+      </c>
+      <c r="B85" s="89">
+        <v>102000</v>
+      </c>
+      <c r="C85" s="89" t="s">
+        <v>145</v>
+      </c>
+      <c r="D85" s="88">
+        <v>302018</v>
+      </c>
+      <c r="E85" s="88" t="s">
+        <v>179</v>
+      </c>
+      <c r="F85" s="88" t="s">
+        <v>34</v>
+      </c>
+      <c r="G85" s="88">
+        <v>2020003</v>
+      </c>
+      <c r="H85" s="88" t="s">
+        <v>61</v>
+      </c>
+      <c r="I85" s="88"/>
+      <c r="J85" s="88"/>
+      <c r="K85" s="90">
+        <v>10200425</v>
+      </c>
+      <c r="L85" s="88" t="s">
+        <v>180</v>
+      </c>
+      <c r="M85" s="88"/>
+      <c r="N85" s="88"/>
+      <c r="O85" s="88"/>
+      <c r="P85" s="88"/>
+      <c r="Q85" s="118" t="s">
+        <v>163</v>
+      </c>
+      <c r="R85" s="119" t="s">
+        <v>40</v>
+      </c>
+      <c r="S85" s="91"/>
+    </row>
+    <row r="86" s="14" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A86" s="100">
+        <v>30380001</v>
+      </c>
+      <c r="B86" s="101">
+        <v>103800</v>
+      </c>
+      <c r="C86" s="101" t="s">
+        <v>181</v>
+      </c>
+      <c r="D86" s="100">
+        <v>303801</v>
+      </c>
+      <c r="E86" s="100" t="s">
+        <v>182</v>
+      </c>
+      <c r="F86" s="100" t="s">
+        <v>183</v>
+      </c>
+      <c r="G86" s="100">
+        <v>2038001</v>
+      </c>
+      <c r="H86" s="100" t="s">
+        <v>61</v>
+      </c>
+      <c r="I86" s="100"/>
+      <c r="J86" s="100"/>
+      <c r="K86" s="102" t="s">
+        <v>184</v>
+      </c>
+      <c r="L86" s="100" t="s">
+        <v>185</v>
+      </c>
+      <c r="M86" s="100"/>
+      <c r="N86" s="100"/>
+      <c r="O86" s="100"/>
+      <c r="P86" s="100"/>
+      <c r="Q86" s="120"/>
+      <c r="R86" s="121"/>
+      <c r="S86" s="103"/>
+    </row>
+    <row r="87" s="14" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A87" s="100">
+        <v>30380002</v>
+      </c>
+      <c r="B87" s="101">
+        <v>103800</v>
+      </c>
+      <c r="C87" s="101" t="s">
+        <v>181</v>
+      </c>
+      <c r="D87" s="100">
+        <v>303802</v>
+      </c>
+      <c r="E87" s="100" t="s">
+        <v>186</v>
+      </c>
+      <c r="F87" s="100" t="s">
+        <v>34</v>
+      </c>
+      <c r="G87" s="100">
+        <v>2038001</v>
+      </c>
+      <c r="H87" s="100" t="s">
+        <v>61</v>
+      </c>
+      <c r="I87" s="100"/>
+      <c r="J87" s="100"/>
+      <c r="K87" s="102"/>
+      <c r="L87" s="100"/>
+      <c r="M87" s="100" t="s">
+        <v>54</v>
+      </c>
+      <c r="N87" s="100"/>
+      <c r="O87" s="100" t="s">
+        <v>187</v>
+      </c>
+      <c r="P87" s="100"/>
+      <c r="Q87" s="120"/>
+      <c r="R87" s="121"/>
+      <c r="S87" s="103"/>
+    </row>
+    <row r="88" s="18" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A88" s="122">
+        <v>30270001</v>
+      </c>
+      <c r="B88" s="123">
+        <v>102700</v>
+      </c>
+      <c r="C88" s="123" t="s">
+        <v>188</v>
+      </c>
+      <c r="D88" s="122">
+        <v>302701</v>
+      </c>
+      <c r="E88" s="122" t="s">
+        <v>189</v>
+      </c>
+      <c r="F88" s="122" t="s">
+        <v>80</v>
+      </c>
+      <c r="G88" s="122">
+        <v>2027001</v>
+      </c>
+      <c r="H88" s="122" t="s">
+        <v>61</v>
+      </c>
+      <c r="I88" s="122" t="s">
         <v>81</v>
       </c>
-      <c r="J76" s="111"/>
-      <c r="K76" s="113" t="s">
-        <v>159</v>
-      </c>
-      <c r="L76" s="111" t="s">
-        <v>160</v>
-      </c>
-      <c r="M76" s="111"/>
-      <c r="N76" s="111"/>
-      <c r="O76" s="111"/>
-      <c r="P76" s="111"/>
-      <c r="Q76" s="37"/>
-      <c r="R76" s="38"/>
-      <c r="S76" s="114"/>
-    </row>
-    <row r="77" s="17" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A77" s="111">
-        <v>30200010</v>
-      </c>
-      <c r="B77" s="112">
-        <v>102000</v>
-      </c>
-      <c r="C77" s="112" t="s">
-        <v>145</v>
-      </c>
-      <c r="D77" s="111">
-        <v>302010</v>
-      </c>
-      <c r="E77" s="111" t="s">
-        <v>161</v>
-      </c>
-      <c r="F77" s="111" t="s">
-        <v>54</v>
-      </c>
-      <c r="G77" s="111">
-        <v>2020002</v>
-      </c>
-      <c r="H77" s="111" t="s">
+      <c r="J88" s="122"/>
+      <c r="K88" s="124" t="s">
+        <v>190</v>
+      </c>
+      <c r="L88" s="122" t="s">
+        <v>191</v>
+      </c>
+      <c r="M88" s="122"/>
+      <c r="N88" s="122"/>
+      <c r="O88" s="122"/>
+      <c r="P88" s="122"/>
+      <c r="Q88" s="125"/>
+      <c r="R88" s="126"/>
+      <c r="S88" s="127"/>
+    </row>
+    <row r="89" s="18" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A89" s="122">
+        <v>30270002</v>
+      </c>
+      <c r="B89" s="123">
+        <v>102700</v>
+      </c>
+      <c r="C89" s="123" t="s">
+        <v>188</v>
+      </c>
+      <c r="D89" s="122">
+        <v>302702</v>
+      </c>
+      <c r="E89" s="122" t="s">
+        <v>192</v>
+      </c>
+      <c r="F89" s="122" t="s">
+        <v>122</v>
+      </c>
+      <c r="G89" s="122">
+        <v>2027001</v>
+      </c>
+      <c r="H89" s="122" t="s">
         <v>61</v>
       </c>
-      <c r="I77" s="111"/>
-      <c r="J77" s="111"/>
-      <c r="K77" s="115">
-        <v>10200120</v>
-      </c>
-      <c r="L77" s="116" t="s">
-        <v>162</v>
-      </c>
-      <c r="M77" s="111"/>
-      <c r="N77" s="111"/>
-      <c r="O77" s="111"/>
-      <c r="P77" s="111"/>
-      <c r="Q77" s="37" t="s">
-        <v>163</v>
-      </c>
-      <c r="R77" s="38" t="s">
-        <v>40</v>
-      </c>
-      <c r="S77" s="114"/>
-    </row>
-    <row r="78" s="17" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A78" s="111">
-        <v>30200011</v>
-      </c>
-      <c r="B78" s="112">
-        <v>102000</v>
-      </c>
-      <c r="C78" s="112" t="s">
-        <v>145</v>
-      </c>
-      <c r="D78" s="111">
-        <v>302011</v>
-      </c>
-      <c r="E78" s="111" t="s">
-        <v>164</v>
-      </c>
-      <c r="F78" s="111" t="s">
-        <v>54</v>
-      </c>
-      <c r="G78" s="111">
-        <v>2020002</v>
-      </c>
-      <c r="H78" s="111" t="s">
+      <c r="I89" s="122" t="s">
+        <v>81</v>
+      </c>
+      <c r="J89" s="122"/>
+      <c r="K89" s="124" t="s">
+        <v>190</v>
+      </c>
+      <c r="L89" s="122" t="s">
+        <v>191</v>
+      </c>
+      <c r="M89" s="122"/>
+      <c r="N89" s="122"/>
+      <c r="O89" s="122"/>
+      <c r="P89" s="122"/>
+      <c r="Q89" s="125"/>
+      <c r="R89" s="126"/>
+      <c r="S89" s="127"/>
+    </row>
+    <row r="90" s="18" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A90" s="122">
+        <v>30270003</v>
+      </c>
+      <c r="B90" s="123">
+        <v>102700</v>
+      </c>
+      <c r="C90" s="123" t="s">
+        <v>188</v>
+      </c>
+      <c r="D90" s="122">
+        <v>302703</v>
+      </c>
+      <c r="E90" s="122" t="s">
+        <v>193</v>
+      </c>
+      <c r="F90" s="122" t="s">
+        <v>194</v>
+      </c>
+      <c r="G90" s="122">
+        <v>2027001</v>
+      </c>
+      <c r="H90" s="122" t="s">
         <v>61</v>
       </c>
-      <c r="I78" s="111"/>
-      <c r="J78" s="111"/>
-      <c r="K78" s="115">
-        <v>10200220</v>
-      </c>
-      <c r="L78" s="116" t="s">
-        <v>165</v>
-      </c>
-      <c r="M78" s="111"/>
-      <c r="N78" s="111"/>
-      <c r="O78" s="111"/>
-      <c r="P78" s="111"/>
-      <c r="Q78" s="37" t="s">
-        <v>163</v>
-      </c>
-      <c r="R78" s="38" t="s">
-        <v>40</v>
-      </c>
-      <c r="S78" s="114"/>
-    </row>
-    <row r="79" s="17" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A79" s="111">
-        <v>30200012</v>
-      </c>
-      <c r="B79" s="112">
-        <v>102000</v>
-      </c>
-      <c r="C79" s="112" t="s">
-        <v>145</v>
-      </c>
-      <c r="D79" s="111">
-        <v>302012</v>
-      </c>
-      <c r="E79" s="111" t="s">
-        <v>166</v>
-      </c>
-      <c r="F79" s="111" t="s">
-        <v>54</v>
-      </c>
-      <c r="G79" s="111">
-        <v>2020002</v>
-      </c>
-      <c r="H79" s="111" t="s">
-        <v>61</v>
-      </c>
-      <c r="I79" s="111"/>
-      <c r="J79" s="111"/>
-      <c r="K79" s="115">
-        <v>10200320</v>
-      </c>
-      <c r="L79" s="116" t="s">
-        <v>167</v>
-      </c>
-      <c r="M79" s="111"/>
-      <c r="N79" s="111"/>
-      <c r="O79" s="111"/>
-      <c r="P79" s="111"/>
-      <c r="Q79" s="37" t="s">
-        <v>163</v>
-      </c>
-      <c r="R79" s="38" t="s">
-        <v>40</v>
-      </c>
-      <c r="S79" s="114"/>
-    </row>
-    <row r="80" s="17" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A80" s="111">
-        <v>30200013</v>
-      </c>
-      <c r="B80" s="112">
-        <v>102000</v>
-      </c>
-      <c r="C80" s="112" t="s">
-        <v>145</v>
-      </c>
-      <c r="D80" s="111">
-        <v>302013</v>
-      </c>
-      <c r="E80" s="111" t="s">
-        <v>168</v>
-      </c>
-      <c r="F80" s="111" t="s">
-        <v>54</v>
-      </c>
-      <c r="G80" s="111">
-        <v>2020002</v>
-      </c>
-      <c r="H80" s="111" t="s">
-        <v>61</v>
-      </c>
-      <c r="I80" s="111"/>
-      <c r="J80" s="111"/>
-      <c r="K80" s="115">
-        <v>10200420</v>
-      </c>
-      <c r="L80" s="116" t="s">
-        <v>169</v>
-      </c>
-      <c r="M80" s="111"/>
-      <c r="N80" s="111"/>
-      <c r="O80" s="111"/>
-      <c r="P80" s="111"/>
-      <c r="Q80" s="37" t="s">
-        <v>163</v>
-      </c>
-      <c r="R80" s="38" t="s">
-        <v>40</v>
-      </c>
-      <c r="S80" s="114"/>
-    </row>
-    <row r="81" s="11" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A81" s="87">
-        <v>30200014</v>
-      </c>
-      <c r="B81" s="88">
-        <v>102000</v>
-      </c>
-      <c r="C81" s="88" t="s">
-        <v>145</v>
-      </c>
-      <c r="D81" s="87">
-        <v>302014</v>
-      </c>
-      <c r="E81" s="87" t="s">
-        <v>170</v>
-      </c>
-      <c r="F81" s="87" t="s">
-        <v>109</v>
-      </c>
-      <c r="G81" s="87">
-        <v>2020003</v>
-      </c>
-      <c r="H81" s="87" t="s">
-        <v>61</v>
-      </c>
-      <c r="I81" s="87" t="s">
+      <c r="I90" s="122" t="s">
         <v>81</v>
       </c>
-      <c r="J81" s="87"/>
-      <c r="K81" s="89" t="s">
-        <v>171</v>
-      </c>
-      <c r="L81" s="87" t="s">
-        <v>172</v>
-      </c>
-      <c r="M81" s="87"/>
-      <c r="N81" s="87"/>
-      <c r="O81" s="87"/>
-      <c r="P81" s="87"/>
-      <c r="Q81" s="87"/>
-      <c r="R81" s="87"/>
-      <c r="S81" s="90"/>
-    </row>
-    <row r="82" s="11" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A82" s="87">
-        <v>30200015</v>
-      </c>
-      <c r="B82" s="88">
-        <v>102000</v>
-      </c>
-      <c r="C82" s="88" t="s">
-        <v>145</v>
-      </c>
-      <c r="D82" s="87">
-        <v>302015</v>
-      </c>
-      <c r="E82" s="87" t="s">
-        <v>173</v>
-      </c>
-      <c r="F82" s="87" t="s">
-        <v>34</v>
-      </c>
-      <c r="G82" s="87">
-        <v>2020003</v>
-      </c>
-      <c r="H82" s="87" t="s">
-        <v>61</v>
-      </c>
-      <c r="I82" s="87"/>
-      <c r="J82" s="87"/>
-      <c r="K82" s="89">
-        <v>10200125</v>
-      </c>
-      <c r="L82" s="87" t="s">
-        <v>174</v>
-      </c>
-      <c r="M82" s="87"/>
-      <c r="N82" s="87"/>
-      <c r="O82" s="87"/>
-      <c r="P82" s="87"/>
-      <c r="Q82" s="117" t="s">
-        <v>163</v>
-      </c>
-      <c r="R82" s="118" t="s">
-        <v>40</v>
-      </c>
-      <c r="S82" s="90"/>
-    </row>
-    <row r="83" s="11" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A83" s="87">
-        <v>30200016</v>
-      </c>
-      <c r="B83" s="88">
-        <v>102000</v>
-      </c>
-      <c r="C83" s="88" t="s">
-        <v>145</v>
-      </c>
-      <c r="D83" s="87">
-        <v>302016</v>
-      </c>
-      <c r="E83" s="87" t="s">
-        <v>175</v>
-      </c>
-      <c r="F83" s="87" t="s">
-        <v>34</v>
-      </c>
-      <c r="G83" s="87">
-        <v>2020003</v>
-      </c>
-      <c r="H83" s="87" t="s">
-        <v>61</v>
-      </c>
-      <c r="I83" s="87"/>
-      <c r="J83" s="87"/>
-      <c r="K83" s="89">
-        <v>10200225</v>
-      </c>
-      <c r="L83" s="87" t="s">
-        <v>176</v>
-      </c>
-      <c r="M83" s="87"/>
-      <c r="N83" s="87"/>
-      <c r="O83" s="87"/>
-      <c r="P83" s="87"/>
-      <c r="Q83" s="117" t="s">
-        <v>163</v>
-      </c>
-      <c r="R83" s="118" t="s">
-        <v>40</v>
-      </c>
-      <c r="S83" s="90"/>
-    </row>
-    <row r="84" s="11" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A84" s="87">
-        <v>30200017</v>
-      </c>
-      <c r="B84" s="88">
-        <v>102000</v>
-      </c>
-      <c r="C84" s="88" t="s">
-        <v>145</v>
-      </c>
-      <c r="D84" s="87">
-        <v>302017</v>
-      </c>
-      <c r="E84" s="87" t="s">
-        <v>177</v>
-      </c>
-      <c r="F84" s="87" t="s">
-        <v>34</v>
-      </c>
-      <c r="G84" s="87">
-        <v>2020003</v>
-      </c>
-      <c r="H84" s="87" t="s">
-        <v>61</v>
-      </c>
-      <c r="I84" s="87"/>
-      <c r="J84" s="87"/>
-      <c r="K84" s="89">
-        <v>10200325</v>
-      </c>
-      <c r="L84" s="87" t="s">
-        <v>178</v>
-      </c>
-      <c r="M84" s="87"/>
-      <c r="N84" s="87"/>
-      <c r="O84" s="87"/>
-      <c r="P84" s="87"/>
-      <c r="Q84" s="117" t="s">
-        <v>163</v>
-      </c>
-      <c r="R84" s="118" t="s">
-        <v>40</v>
-      </c>
-      <c r="S84" s="90"/>
-    </row>
-    <row r="85" s="11" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A85" s="87">
-        <v>30200018</v>
-      </c>
-      <c r="B85" s="88">
-        <v>102000</v>
-      </c>
-      <c r="C85" s="88" t="s">
-        <v>145</v>
-      </c>
-      <c r="D85" s="87">
-        <v>302018</v>
-      </c>
-      <c r="E85" s="87" t="s">
-        <v>179</v>
-      </c>
-      <c r="F85" s="87" t="s">
-        <v>34</v>
-      </c>
-      <c r="G85" s="87">
-        <v>2020003</v>
-      </c>
-      <c r="H85" s="87" t="s">
-        <v>61</v>
-      </c>
-      <c r="I85" s="87"/>
-      <c r="J85" s="87"/>
-      <c r="K85" s="89">
-        <v>10200425</v>
-      </c>
-      <c r="L85" s="87" t="s">
-        <v>180</v>
-      </c>
-      <c r="M85" s="87"/>
-      <c r="N85" s="87"/>
-      <c r="O85" s="87"/>
-      <c r="P85" s="87"/>
-      <c r="Q85" s="117" t="s">
-        <v>163</v>
-      </c>
-      <c r="R85" s="118" t="s">
-        <v>40</v>
-      </c>
-      <c r="S85" s="90"/>
-    </row>
-    <row r="86" s="14" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A86" s="99">
-        <v>30380001</v>
-      </c>
-      <c r="B86" s="100">
-        <v>103800</v>
-      </c>
-      <c r="C86" s="100" t="s">
-        <v>181</v>
-      </c>
-      <c r="D86" s="99">
-        <v>303801</v>
-      </c>
-      <c r="E86" s="99" t="s">
-        <v>182</v>
-      </c>
-      <c r="F86" s="99" t="s">
-        <v>183</v>
-      </c>
-      <c r="G86" s="99">
-        <v>2038001</v>
-      </c>
-      <c r="H86" s="99" t="s">
-        <v>61</v>
-      </c>
-      <c r="I86" s="99"/>
-      <c r="J86" s="99"/>
-      <c r="K86" s="101" t="s">
-        <v>184</v>
-      </c>
-      <c r="L86" s="99" t="s">
-        <v>185</v>
-      </c>
-      <c r="M86" s="99"/>
-      <c r="N86" s="99"/>
-      <c r="O86" s="99"/>
-      <c r="P86" s="99"/>
-      <c r="Q86" s="119"/>
-      <c r="R86" s="120"/>
-      <c r="S86" s="102"/>
-    </row>
-    <row r="87" s="14" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A87" s="99">
-        <v>30380002</v>
-      </c>
-      <c r="B87" s="100">
-        <v>103800</v>
-      </c>
-      <c r="C87" s="100" t="s">
-        <v>181</v>
-      </c>
-      <c r="D87" s="99">
-        <v>303802</v>
-      </c>
-      <c r="E87" s="99" t="s">
-        <v>186</v>
-      </c>
-      <c r="F87" s="99" t="s">
-        <v>34</v>
-      </c>
-      <c r="G87" s="99">
-        <v>2038001</v>
-      </c>
-      <c r="H87" s="99" t="s">
-        <v>61</v>
-      </c>
-      <c r="I87" s="99"/>
-      <c r="J87" s="99"/>
-      <c r="K87" s="101"/>
-      <c r="L87" s="99"/>
-      <c r="M87" s="99" t="s">
-        <v>54</v>
-      </c>
-      <c r="N87" s="99"/>
-      <c r="O87" s="99" t="s">
-        <v>187</v>
-      </c>
-      <c r="P87" s="99"/>
-      <c r="Q87" s="119"/>
-      <c r="R87" s="120"/>
-      <c r="S87" s="102"/>
-    </row>
-    <row r="88" ht="16.5" spans="1:19">
-      <c r="K88" s="121"/>
-    </row>
-    <row r="89" ht="16.5" spans="1:19">
-      <c r="K89" s="121"/>
-    </row>
-    <row r="90" ht="16.5" spans="1:19">
-      <c r="A90" s="121"/>
+      <c r="J90" s="122"/>
+      <c r="K90" s="124" t="s">
+        <v>190</v>
+      </c>
+      <c r="L90" s="122" t="s">
+        <v>191</v>
+      </c>
+      <c r="M90" s="122"/>
+      <c r="N90" s="122"/>
+      <c r="O90" s="122"/>
+      <c r="P90" s="122"/>
+      <c r="Q90" s="125"/>
+      <c r="R90" s="126"/>
+      <c r="S90" s="127"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2">
@@ -6082,10 +6251,10 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="B1" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -6093,7 +6262,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -6101,7 +6270,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:8">
@@ -6109,16 +6278,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:8">
@@ -6126,16 +6295,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:8">
@@ -6143,16 +6312,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:8">
@@ -6160,16 +6329,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="F7" s="1">
         <v>2</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:8">
@@ -6177,16 +6346,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="F8" s="1">
         <v>3</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:8">
@@ -6194,16 +6363,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="F9" s="1">
         <v>4</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:8">
@@ -6211,16 +6380,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="F10" s="1">
         <v>5</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:8">
@@ -6228,16 +6397,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="F11" s="1">
         <v>6</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:8">
@@ -6245,16 +6414,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="F12" s="1">
         <v>7</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:8">
@@ -6262,16 +6431,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="F13" s="1">
         <v>8</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:8">
@@ -6279,16 +6448,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="F14" s="1">
         <v>9</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:8">
@@ -6296,16 +6465,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="F15" s="1">
         <v>10</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:8">
@@ -6313,16 +6482,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="F16" s="1">
         <v>11</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:8">
@@ -6330,16 +6499,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="F17" s="1">
         <v>12</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:8">
@@ -6347,7 +6516,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="F18" s="1">
         <v>13</v>
@@ -6356,7 +6525,7 @@
         <v>186</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:8">
@@ -6364,16 +6533,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="F19" s="1">
         <v>14</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:8">
@@ -6381,16 +6550,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="F20" s="1">
         <v>15</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:8">
@@ -6398,16 +6567,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="F21" s="1">
         <v>16</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:8">
@@ -6415,16 +6584,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="F22" s="1">
         <v>17</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:8">
@@ -6432,16 +6601,16 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="F23" s="1">
         <v>18</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:8">
@@ -6449,16 +6618,16 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="F24" s="1">
         <v>19</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -6466,7 +6635,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -6474,7 +6643,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -6482,7 +6651,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -6490,7 +6659,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -6498,7 +6667,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -6506,7 +6675,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -6514,7 +6683,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -6522,7 +6691,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -6530,7 +6699,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -6538,7 +6707,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -6546,7 +6715,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -6554,7 +6723,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -6562,7 +6731,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -6570,7 +6739,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -6578,7 +6747,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -6586,7 +6755,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -6594,7 +6763,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -6602,7 +6771,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -6610,7 +6779,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -6618,7 +6787,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -6626,7 +6795,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -6634,7 +6803,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -6642,7 +6811,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialAuxiliary.xlsx
+++ b/slots/resources/sample/SpecialAuxiliary.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialAuxiliary" sheetId="1" r:id="rId1"/>
@@ -268,7 +268,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="311">
   <si>
     <t>小游戏模式ID</t>
   </si>
@@ -916,6 +916,27 @@
   </si>
   <si>
     <t>1_200|2_500|3_300</t>
+  </si>
+  <si>
+    <t>潘金莲</t>
+  </si>
+  <si>
+    <t>免费游戏-免费旋转-5次</t>
+  </si>
+  <si>
+    <t>5_1</t>
+  </si>
+  <si>
+    <t>10400002|10400006|10400007|10400008</t>
+  </si>
+  <si>
+    <t>愤怒的小鸡</t>
+  </si>
+  <si>
+    <t>转轴上出现符号5时在随机位置上改出1个wild</t>
+  </si>
+  <si>
+    <t>改出百搭符号</t>
   </si>
   <si>
     <t>typeID</t>
@@ -1369,11 +1390,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
@@ -1381,7 +1397,6 @@
     </font>
     <font>
       <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1394,13 +1409,12 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
@@ -1412,8 +1426,15 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="51">
+  <fills count="52">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1513,6 +1534,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1845,7 +1872,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1869,16 +1896,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="23" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="24" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="25" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1887,92 +1914,92 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="143">
+  <cellXfs count="154">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1996,6 +2023,8 @@
     <xf numFmtId="0" fontId="3" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2047,18 +2076,10 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2066,7 +2087,15 @@
     <xf numFmtId="0" fontId="1" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -2256,6 +2285,23 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="1" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="52">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2597,7 +2643,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T95"/>
+  <dimension ref="A1:T111"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14.125" customWidth="1"/>
@@ -2609,7 +2655,7 @@
     <col min="8" max="8" width="16.25" customWidth="1"/>
     <col min="9" max="9" width="29.375" customWidth="1"/>
     <col min="10" max="10" width="42.5" customWidth="1"/>
-    <col min="11" max="11" width="41.25" style="21" customWidth="1"/>
+    <col min="11" max="11" width="41.25" style="23" customWidth="1"/>
     <col min="12" max="12" width="45.2916666666667" style="3" customWidth="1"/>
     <col min="13" max="13" width="34.4083333333333" style="3" customWidth="1"/>
     <col min="14" max="14" width="7.93333333333333" style="3" customWidth="1"/>
@@ -2618,7 +2664,7 @@
     <col min="17" max="17" width="93.375" customWidth="1"/>
     <col min="18" max="18" width="22.6416666666667" customWidth="1"/>
     <col min="19" max="19" width="10.625" customWidth="1"/>
-    <col min="20" max="20" width="23.75" style="22" customWidth="1"/>
+    <col min="20" max="20" width="23.75" style="24" customWidth="1"/>
     <col min="21" max="21" width="60.875" customWidth="1"/>
     <col min="22" max="23" width="11.5"/>
   </cols>
@@ -2627,693 +2673,693 @@
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23" t="s">
+      <c r="C1" s="25"/>
+      <c r="D1" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23" t="s">
+      <c r="E1" s="25"/>
+      <c r="F1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="23" t="s">
+      <c r="G1" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23" t="s">
+      <c r="H1" s="25"/>
+      <c r="I1" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="24" t="s">
+      <c r="J1" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="25" t="s">
+      <c r="K1" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="23"/>
-      <c r="M1" s="23" t="s">
+      <c r="L1" s="25"/>
+      <c r="M1" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="23"/>
-      <c r="O1" s="26" t="s">
+      <c r="N1" s="25"/>
+      <c r="O1" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="26" t="s">
+      <c r="P1" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="Q1" s="26" t="s">
+      <c r="Q1" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="R1" s="27" t="s">
+      <c r="R1" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="S1" s="28" t="s">
+      <c r="S1" s="30" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="2" s="3" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23" t="s">
+      <c r="C2" s="25"/>
+      <c r="D2" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="23"/>
-      <c r="F2" s="26" t="s">
+      <c r="E2" s="25"/>
+      <c r="F2" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="23" t="s">
+      <c r="G2" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="23"/>
-      <c r="I2" s="23"/>
-      <c r="J2" s="27" t="s">
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="K2" s="30" t="s">
+      <c r="K2" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="L2" s="26"/>
-      <c r="M2" s="27" t="s">
+      <c r="L2" s="28"/>
+      <c r="M2" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="N2" s="23"/>
-      <c r="O2" s="26" t="s">
+      <c r="N2" s="25"/>
+      <c r="O2" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="P2" s="26" t="s">
+      <c r="P2" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="Q2" s="27" t="s">
+      <c r="Q2" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="R2" s="27" t="s">
+      <c r="R2" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="S2" s="28" t="s">
+      <c r="S2" s="30" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="3" s="3" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="31" t="s">
+      <c r="B3" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31" t="s">
+      <c r="C3" s="33"/>
+      <c r="D3" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31" t="s">
+      <c r="E3" s="33"/>
+      <c r="F3" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="32" t="s">
+      <c r="G3" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="33" t="s">
+      <c r="H3" s="33"/>
+      <c r="I3" s="33"/>
+      <c r="J3" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="K3" s="34" t="s">
+      <c r="K3" s="36" t="s">
         <v>27</v>
       </c>
-      <c r="L3" s="31"/>
-      <c r="M3" s="31" t="s">
+      <c r="L3" s="33"/>
+      <c r="M3" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="N3" s="31"/>
-      <c r="O3" s="26" t="s">
+      <c r="N3" s="33"/>
+      <c r="O3" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="P3" s="26" t="s">
+      <c r="P3" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="Q3" s="26" t="s">
+      <c r="Q3" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="R3" s="35" t="s">
+      <c r="R3" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="S3" s="36" t="s">
+      <c r="S3" s="38" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="4" s="3" customFormat="1" ht="16.5" spans="1:20">
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="23"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="37"/>
-      <c r="K4" s="25"/>
-      <c r="L4" s="23"/>
-      <c r="M4" s="23"/>
-      <c r="N4" s="23"/>
-      <c r="O4" s="23"/>
-      <c r="P4" s="23"/>
-      <c r="Q4" s="23"/>
-      <c r="R4" s="23"/>
-      <c r="S4" s="23"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="39"/>
+      <c r="K4" s="27"/>
+      <c r="L4" s="25"/>
+      <c r="M4" s="25"/>
+      <c r="N4" s="25"/>
+      <c r="O4" s="25"/>
+      <c r="P4" s="25"/>
+      <c r="Q4" s="25"/>
+      <c r="R4" s="25"/>
+      <c r="S4" s="25"/>
     </row>
     <row r="5" s="3" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A5" s="38">
+      <c r="A5" s="40">
         <v>30010001</v>
       </c>
-      <c r="B5" s="39">
+      <c r="B5" s="41">
         <v>100100</v>
       </c>
-      <c r="C5" s="39" t="s">
+      <c r="C5" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="38">
+      <c r="D5" s="40">
         <v>31001</v>
       </c>
-      <c r="E5" s="38" t="s">
+      <c r="E5" s="40" t="s">
         <v>35</v>
       </c>
-      <c r="F5" s="38" t="s">
+      <c r="F5" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="G5" s="38"/>
-      <c r="H5" s="38"/>
-      <c r="I5" s="38" t="s">
+      <c r="G5" s="40"/>
+      <c r="H5" s="40"/>
+      <c r="I5" s="40" t="s">
         <v>37</v>
       </c>
-      <c r="J5" s="38"/>
-      <c r="K5" s="40"/>
-      <c r="L5" s="23" t="s">
+      <c r="J5" s="40"/>
+      <c r="K5" s="42"/>
+      <c r="L5" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="M5" s="38" t="s">
+      <c r="M5" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="N5" s="38" t="s">
+      <c r="N5" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="O5" s="38"/>
-      <c r="P5" s="38"/>
-      <c r="Q5" s="41" t="s">
+      <c r="O5" s="40"/>
+      <c r="P5" s="40"/>
+      <c r="Q5" s="43" t="s">
         <v>41</v>
       </c>
-      <c r="R5" s="42"/>
-      <c r="S5" s="42" t="s">
+      <c r="R5" s="44"/>
+      <c r="S5" s="44" t="s">
         <v>42</v>
       </c>
-      <c r="T5" s="43" t="s">
+      <c r="T5" s="45" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="6" s="3" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A6" s="38">
+      <c r="A6" s="40">
         <v>30010002</v>
       </c>
-      <c r="B6" s="39">
+      <c r="B6" s="41">
         <v>100100</v>
       </c>
-      <c r="C6" s="39" t="s">
+      <c r="C6" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="38">
+      <c r="D6" s="40">
         <v>31002</v>
       </c>
-      <c r="E6" s="38" t="s">
+      <c r="E6" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="F6" s="38" t="s">
+      <c r="F6" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="G6" s="38"/>
-      <c r="H6" s="38"/>
-      <c r="I6" s="38" t="s">
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40" t="s">
         <v>45</v>
       </c>
-      <c r="J6" s="38"/>
-      <c r="K6" s="40"/>
-      <c r="L6" s="23" t="s">
+      <c r="J6" s="40"/>
+      <c r="K6" s="42"/>
+      <c r="L6" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="M6" s="38" t="s">
+      <c r="M6" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="N6" s="38" t="s">
+      <c r="N6" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="O6" s="38"/>
-      <c r="P6" s="38"/>
-      <c r="Q6" s="41" t="s">
+      <c r="O6" s="40"/>
+      <c r="P6" s="40"/>
+      <c r="Q6" s="43" t="s">
         <v>47</v>
       </c>
-      <c r="R6" s="42"/>
-      <c r="S6" s="42" t="s">
+      <c r="R6" s="44"/>
+      <c r="S6" s="44" t="s">
         <v>42</v>
       </c>
-      <c r="T6" s="43"/>
+      <c r="T6" s="45"/>
     </row>
     <row r="7" s="3" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A7" s="38">
+      <c r="A7" s="40">
         <v>30010003</v>
       </c>
-      <c r="B7" s="39">
+      <c r="B7" s="41">
         <v>100100</v>
       </c>
-      <c r="C7" s="39" t="s">
+      <c r="C7" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="38">
+      <c r="D7" s="40">
         <v>31003</v>
       </c>
-      <c r="E7" s="38" t="s">
+      <c r="E7" s="40" t="s">
         <v>48</v>
       </c>
-      <c r="F7" s="38" t="s">
+      <c r="F7" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="G7" s="38"/>
-      <c r="H7" s="38"/>
-      <c r="I7" s="38" t="s">
+      <c r="G7" s="40"/>
+      <c r="H7" s="40"/>
+      <c r="I7" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="J7" s="38"/>
-      <c r="K7" s="40"/>
-      <c r="L7" s="23" t="s">
+      <c r="J7" s="40"/>
+      <c r="K7" s="42"/>
+      <c r="L7" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="M7" s="38" t="s">
+      <c r="M7" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="N7" s="38" t="s">
+      <c r="N7" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="O7" s="38"/>
-      <c r="P7" s="38"/>
-      <c r="Q7" s="41" t="s">
+      <c r="O7" s="40"/>
+      <c r="P7" s="40"/>
+      <c r="Q7" s="43" t="s">
         <v>50</v>
       </c>
-      <c r="R7" s="42"/>
-      <c r="S7" s="42" t="s">
+      <c r="R7" s="44"/>
+      <c r="S7" s="44" t="s">
         <v>42</v>
       </c>
-      <c r="T7" s="43"/>
+      <c r="T7" s="45"/>
     </row>
     <row r="8" s="3" customFormat="1" ht="15" customHeight="1" spans="1:20">
-      <c r="A8" s="38">
+      <c r="A8" s="40">
         <v>30010004</v>
       </c>
-      <c r="B8" s="39">
+      <c r="B8" s="41">
         <v>100100</v>
       </c>
-      <c r="C8" s="39" t="s">
+      <c r="C8" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="38">
+      <c r="D8" s="40">
         <v>31004</v>
       </c>
-      <c r="E8" s="38" t="s">
+      <c r="E8" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="F8" s="38" t="s">
+      <c r="F8" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="G8" s="38"/>
-      <c r="H8" s="38"/>
-      <c r="I8" s="38" t="s">
+      <c r="G8" s="40"/>
+      <c r="H8" s="40"/>
+      <c r="I8" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="J8" s="38"/>
-      <c r="K8" s="40"/>
-      <c r="L8" s="23" t="s">
+      <c r="J8" s="40"/>
+      <c r="K8" s="42"/>
+      <c r="L8" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="M8" s="38" t="s">
+      <c r="M8" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="N8" s="38" t="s">
+      <c r="N8" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="O8" s="38"/>
-      <c r="P8" s="38"/>
-      <c r="Q8" s="41" t="s">
+      <c r="O8" s="40"/>
+      <c r="P8" s="40"/>
+      <c r="Q8" s="43" t="s">
         <v>53</v>
       </c>
-      <c r="R8" s="42"/>
-      <c r="S8" s="42" t="s">
+      <c r="R8" s="44"/>
+      <c r="S8" s="44" t="s">
         <v>42</v>
       </c>
-      <c r="T8" s="43"/>
+      <c r="T8" s="45"/>
     </row>
     <row r="9" s="3" customFormat="1" ht="15" customHeight="1" spans="1:20">
-      <c r="A9" s="23">
+      <c r="A9" s="25">
         <v>30010005</v>
       </c>
-      <c r="B9" s="36">
+      <c r="B9" s="38">
         <v>100100</v>
       </c>
-      <c r="C9" s="39" t="s">
+      <c r="C9" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="23">
+      <c r="D9" s="25">
         <v>31101</v>
       </c>
-      <c r="E9" s="23" t="s">
+      <c r="E9" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="F9" s="23" t="s">
+      <c r="F9" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="G9" s="23"/>
-      <c r="H9" s="23"/>
-      <c r="I9" s="23" t="s">
+      <c r="G9" s="25"/>
+      <c r="H9" s="25"/>
+      <c r="I9" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="J9" s="23"/>
-      <c r="K9" s="25"/>
-      <c r="L9" s="23" t="s">
+      <c r="J9" s="25"/>
+      <c r="K9" s="27"/>
+      <c r="L9" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="M9" s="23" t="s">
+      <c r="M9" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="N9" s="23"/>
-      <c r="O9" s="23" t="s">
+      <c r="N9" s="25"/>
+      <c r="O9" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="P9" s="23"/>
-      <c r="Q9" s="26"/>
-      <c r="R9" s="26"/>
-      <c r="S9" s="26"/>
-      <c r="T9" s="43"/>
+      <c r="P9" s="25"/>
+      <c r="Q9" s="28"/>
+      <c r="R9" s="28"/>
+      <c r="S9" s="28"/>
+      <c r="T9" s="45"/>
     </row>
     <row r="10" s="3" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A10" s="44">
+      <c r="A10" s="46">
         <v>30010006</v>
       </c>
-      <c r="B10" s="45">
+      <c r="B10" s="47">
         <v>100100</v>
       </c>
-      <c r="C10" s="39" t="s">
+      <c r="C10" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="44">
+      <c r="D10" s="46">
         <v>31102</v>
       </c>
-      <c r="E10" s="44" t="s">
+      <c r="E10" s="46" t="s">
         <v>58</v>
       </c>
-      <c r="F10" s="44" t="s">
+      <c r="F10" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="G10" s="44"/>
-      <c r="H10" s="44"/>
-      <c r="I10" s="44" t="s">
+      <c r="G10" s="46"/>
+      <c r="H10" s="46"/>
+      <c r="I10" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="J10" s="44"/>
-      <c r="K10" s="46"/>
-      <c r="L10" s="44" t="s">
+      <c r="J10" s="46"/>
+      <c r="K10" s="48"/>
+      <c r="L10" s="46" t="s">
         <v>46</v>
       </c>
-   